--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -10,10 +10,12 @@
   <sheets>
     <sheet name="Mode d'emploi" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Prospects" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Plateformes" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Particuliers" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Plateformes pros" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Règles" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Prospects!$A$1:$M$23</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Prospects!$A$1:$P$112</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -30,7 +32,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -38,13 +40,13 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">1 = revendeur, peut reprendre un gros lot
-2 = pose ou aménage, achète par chantier
-3 = piste plus large</t>
+          <t xml:space="preserve">1 = revendeur ou gros chantiers, peut reprendre un lot
+2 = pose ou prescrit de la pierre régulièrement
+3 = piste possible</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -52,7 +54,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Fiches d'annuaires en ligne (118712, PagesJaunes, travaux.obat.fr, site Diffazur), consultées le 08/10/2026. Le téléphone figure sur la fiche. Vérifiez avant d'appeler : les annuaires peuvent être anciens.</t>
+          <t xml:space="preserve">Page où l'entreprise a été trouvée et vérifiée (site de l'entreprise, 118712, Houzz, travaux.obat.fr, PagesJaunes...). Recherches du 08/10 et du 12/10/2026.</t>
         </r>
       </text>
     </comment>
@@ -61,24 +63,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="712">
   <si>
     <t xml:space="preserve">Prospection MINYALA — mode d'emploi</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Onglet Prospects : commencez par la priorité 1 (revendeurs, ils peuvent reprendre un gros lot).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Cliquez « Voir la fiche » pour obtenir le téléphone, puis appelez ou écrivez (message prêt dans le kit de vente, section 4).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Remplissez uniquement les cases jaunes : Statut, Date du contact, Prochaine action, Notes, m² vendus.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Le tableau de suivi ci-dessous se met à jour tout seul.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Les entreprises viennent d'annuaires en ligne consultés le 08/10/2026 : vérifiez-les avant de les contacter.</t>
+    <t xml:space="preserve">1. Prospects : 111 entreprises (22 de la 1re liste + 89 nouvelles). Filtrez la colonne « Liste » pour ne voir que les nouvelles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Commencez par la priorité 1 (revendeurs, showrooms, marbreries : ils peuvent reprendre un gros lot), puis la 2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Appelez ou écrivez avec le message du kit de vente (section 4). Remplissez seulement les cases jaunes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Particuliers : pas de liste de personnes (interdit sans leur accord). L'onglet Particuliers liste où les trouver : annonces, forums, foires, publicité.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. Onglet Règles : ce qui est autorisé pour appeler, écrire ou publier. Important : on ne peut plus appeler un particulier sans son accord.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les entreprises ont été vérifiées sur leur site ou un annuaire en ligne (08/10 et 12/10/2026). Vérifiez avant de vous déplacer.</t>
   </si>
   <si>
     <t xml:space="preserve">Exemple de ligne remplie</t>
@@ -93,13 +98,13 @@
     <t xml:space="preserve">Date du contact</t>
   </si>
   <si>
-    <t xml:space="preserve">09/10/2026</t>
+    <t xml:space="preserve">13/10/2026</t>
   </si>
   <si>
     <t xml:space="preserve">Prochaine action</t>
   </si>
   <si>
-    <t xml:space="preserve">Rappeler mardi 14/10</t>
+    <t xml:space="preserve">Rappeler mardi 20/10</t>
   </si>
   <si>
     <t xml:space="preserve">Notes</t>
@@ -156,6 +161,9 @@
     <t xml:space="preserve">N°</t>
   </si>
   <si>
+    <t xml:space="preserve">Liste</t>
+  </si>
+  <si>
     <t xml:space="preserve">Priorité</t>
   </si>
   <si>
@@ -174,10 +182,19 @@
     <t xml:space="preserve">Pourquoi les contacter</t>
   </si>
   <si>
-    <t xml:space="preserve">Source (fiche annuaire)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revendeur / négoce</t>
+    <t xml:space="preserve">Site web</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Téléphone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1re liste (08/10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Négoce / revendeur</t>
   </si>
   <si>
     <t xml:space="preserve">Carrelages Pedrazzini</t>
@@ -192,7 +209,7 @@
     <t xml:space="preserve">Vend de la pierre naturelle, showroom et stock important : peut reprendre un gros lot.</t>
   </si>
   <si>
-    <t xml:space="preserve">Voir la fiche</t>
+    <t xml:space="preserve">Voir</t>
   </si>
   <si>
     <t xml:space="preserve">Paco</t>
@@ -231,10 +248,13 @@
     <t xml:space="preserve">Normandie</t>
   </si>
   <si>
-    <t xml:space="preserve">Showrooms carrelage et dallage, dont pierre naturelle et dallage terrasse. Tél. annuaire : 02 79 02 73 91.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Poseur pierre / marbre</t>
+    <t xml:space="preserve">Showrooms carrelage et dallage, dont pierre naturelle et dallage terrasse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 79 02 73 91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carreleur / poseur pierre</t>
   </si>
   <si>
     <t xml:space="preserve">Badiaga Renov</t>
@@ -246,6 +266,9 @@
     <t xml:space="preserve">Marbrerie et pose de pierres naturelles.</t>
   </si>
   <si>
+    <t xml:space="preserve">Marbrerie</t>
+  </si>
+  <si>
     <t xml:space="preserve">Marbrerie Peixeiro</t>
   </si>
   <si>
@@ -363,9 +386,6 @@
     <t xml:space="preserve">Paysagiste, création d'espaces extérieurs. Près de Rouen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Carreleur</t>
-  </si>
-  <si>
     <t xml:space="preserve">GBT-Toktas</t>
   </si>
   <si>
@@ -402,97 +422,1783 @@
     <t xml:space="preserve">Paysagiste, aménagement de jardins. Près du Havre.</t>
   </si>
   <si>
+    <t xml:space="preserve">Nouveaux (12/10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrelage Roger Herblay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herblay-sur-Seine (95220)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce négociant indépendant vend déjà de la pierre naturelle et du carrelage de terrasse dans son showroom d'Herblay : il pourrait référencer MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.carrelage-roger.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 39 31 93 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Société Nouvelle NMC (SNNMC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argenteuil (95100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce négoce d'Argenteuil, voisin de Gennevilliers, vend carrelages et dallages en pierre aux artisans et particuliers et pratique le déstockage : il peut écouler un lot de MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">negoce.france-materiaux.fr/369-societe-nouvelle-nmc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 39 81 60 33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Showroom carrelage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrelage Design 95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint-Ouen-l'Aumône (95310)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce cash &amp; carry du Val-d'Oise vend déjà pierre naturelle et travertin sur stock, donc il peut racheter un lot de MINYALA et le revendre aux particuliers et aux carreleurs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.carrelage-design-95.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07 83 34 77 88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palatino</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nanterre (92000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Négociant en pierre naturelle à Nanterre, tout près de Gennevilliers, avec 1 500 m² de stockage, il peut racheter un lot complet de MINYALA pour sa clientèle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.palatino.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 42 04 90 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parquet-Carrelage.com (showroom Paris 17e)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paris (75017)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce distributeur parisien de sols, avec un gros stock et plusieurs showrooms, référence déjà pierre naturelle et travertin : un débouché possible en volume pour MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.parquet-carrelage.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 48 82 58 58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDY - Marbrerie des Yvelines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Versailles (78000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette marbrerie de Versailles, qui a aussi un showroom à Pont-l'Évêque, vend déjà du dallage en pierre naturelle pour terrasses et abords de piscine : MINYALA peut entrer dans sa gamme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.mdy-france.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 39 24 17 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMC Marbrerie (Pierres Marbreries Carrelages)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montigny-lès-Cormeilles (95370)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette marbrerie du Val-d'Oise vend déjà dallages et pierres naturelles depuis plus de 30 ans, donc un calcaire en stock à 35 €/m² peut compléter son offre de sols.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.pmc-marbrerie.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 39 89 79 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belles Piscines (concessionnaire Mondial Piscine)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coignières (78310)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Son showroom vend déjà carrelages extérieurs, margelles et dallages : MINYALA pourrait compléter sa gamme de plages de piscine dans les Yvelines.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">coignieres.mondial-piscine.eu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 34 89 64 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Monde des Jardins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deuil-la-Barre (95170)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce paysagiste du Val-d'Oise fait de la pierre naturelle son matériau de prédilection et utilise déjà un calcaire à patine dorée : MINYALA, crème veiné d'or, peut compléter sa gamme pour terrasses et dallages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lemondedesjardins.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 34 28 80 46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sauvaje</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magny-les-Hameaux (78114)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce paysagiste fondé en 1987, qui fait du dallage et des terrasses pour des particuliers, des sièges d'entreprise et des palaces, peut commander MINYALA en volume.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.sauvaje.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 39 44 99 33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigMat MVR Matériaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Évreux (27000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce négoce BigMat de 8 magasins dans l'Eure et en Seine-Maritime vend carrelages et dallages et peut acheter un lot de MINYALA pour tout son réseau.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">magasins.bigmat.fr/normandie/eure/evreux/bigmat-evreux-mvr-materiaux-144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 32 31 20 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Monde de la Pierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rolleville (76133)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce négociant en pierre naturelle près du Havre fait aussi des dallages et des aménagements extérieurs : il peut racheter un lot de calcaire égyptien MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.lemondedelapierre.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 35 53 15 31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pillaud Matériaux (agence de Caen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cormelles-le-Royal (14123)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce négoce de 29 agences, dont Caen, Le Havre, Lisieux et Pont-Audemer, vend déjà des dalles et pierres pour terrasses et peut prendre un lot entier de MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.pillaud-materiaux.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 82 44 35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torchio (showroom Caen/Ifs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ifs (14123)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce spécialiste du carrelage intérieur et extérieur, avec 9 showrooms et un réseau de poseurs partenaires, peut acheter un lot de MINYALA pour ses terrasses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.torchio.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 35 05 05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bati Centre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romainville (93230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce revendeur de carrelages, dallages et pierres naturelles, avec showroom en Seine-Saint-Denis, peut acheter MINYALA par lots pour sa clientèle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.baticentre.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 48 57 44 56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceramica Fusaro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paris (75007)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand distributeur de carrelage et de marbre avec showroom à Paris 7e et un stock important, il pourrait ajouter un calcaire naturel disponible immédiatement à son catalogue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.ceramica.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 60 18 19 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Triomphe Carrelages et Salles de Bains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce showroom de 600 m² à Nanterre, tout près de Gennevilliers, vend du carrelage intérieur et extérieur et du dallage en pierre, il pourrait exposer et revendre MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.triomphe-home.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 47 73 92 82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPG - Marbre Pierre Granit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Queue-en-Brie (94510)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette marbrerie réalise déjà des dallages en calcaire pour des hôtels et bureaux parisiens, elle pourrait utiliser MINYALA comme calcaire disponible en stock sur ses chantiers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.marbreriempg.paris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 45 76 15 70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planstone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neuilly-sur-Seine (92200)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce spécialiste de la pierre naturelle avec showroom à Neuilly réalise aussi sols et terrasses pour une clientèle haut de gamme, il pourrait proposer MINYALA à ses clients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">planstone.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 40 80 06 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aqua Garden</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les Essarts-le-Roi (78690)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce pisciniste fait aussi la maçonnerie et les aménagements extérieurs et paysagers : il peut poser MINYALA en plage ou en terrasse autour de ses bassins.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aquagarden78.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 30 46 06 70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idoine Piscines &amp; Spa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paris (75013)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce pisciniste parisien haut de gamme, qui travaille pour des particuliers et des hôtels de luxe, peut prescrire MINYALA pour les plages et les sols de spa.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.idoine-piscines.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03 23 73 15 90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idéal Piscine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bouafle (78410)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constructeur de piscines béton sur mesure dans le 78 et le 92 qui réalise aussi terrasses et margelles autour des bassins, il pourrait poser MINYALA sur des plages de piscine haut de gamme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.idealpiscine.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 34 92 91 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kristech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sèvres (92310)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce constructeur de piscines béton de Sèvres propose déjà des margelles en pierre naturelle dans toute l'Île-de-France, donc MINYALA peut compléter son offre de margelles et de plages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.kristech.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 87 20 65 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Boutique de la Piscine et du Spa (concessionnaire Magiline 92/95)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce constructeur de piscines béton, qui intervient à Colombes, Nanterre et Argenteuil, tout près de Gennevilliers, pourrait proposer MINYALA pour les plages et abords de ses bassins.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.la-boutique-piscine-spa.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 47 49 74 69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piscines du Vexin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce pisciniste du Val-d'Oise réalise déjà des terrasses et plages en travertin et pierre naturelle : MINYALA peut entrer dans ses devis de dallage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.piscines-spas-iledefrance.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 34 46 09 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Socorebat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cergy (95000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce constructeur de piscines béton du Val-d'Oise pose déjà des margelles en pierre, des dallages et des pourtours de piscine, un usage direct pour MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.socorebat-95.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 72 12 39 99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agave Paysage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce paysagiste parisien pose des dallages en pierre sur plots ou sur lit de sable pour des terrasses, une pose compatible avec MINYALA en 2 cm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">agavepaysage.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 65 78 30 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apis Florae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce paysagiste de Rueil primé sur Houzz fait de la maçonnerie, des terrasses et des abords de piscine : il pourrait proposer MINYALA à ses clients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.apisflorae.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 86 90 59 31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art des Jardins-Zory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette entreprise de maçonnerie paysagère d'Argenteuil, qui pose dallages et pierres naturelles, peut venir chercher MINYALA à Gennevilliers pour ses terrasses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.artdesjardins-zory.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 39 82 22 86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atelier Concept Paysage (ACP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce paysagiste voisin de Gennevilliers pose des dallages de jardin et du pavage, un usage direct pour les dalles MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.atelier-concept-paysage.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 56 83 10 45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eden Vatinel &amp; Associés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montesson (78360)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce paysagiste de la boucle de Seine pose déjà pierre naturelle et travertin sur terrasses et abords de piscine : MINYALA est une alternative en stock à 35 €/m².</t>
+  </si>
+  <si>
+    <t xml:space="preserve">edenvatinel.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 77 86 09 46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fontaine Paysage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franconville (95130)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce paysagiste du Val-d'Oise pose déjà des terrasses en dallage de pierre naturelle jusqu'à Colombes et Asnières, donc MINYALA peut entrer dans ses devis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.fontainepaysage.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 73 76 43 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'esprit au vert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puteaux (92800)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce concepteur de terrasses de Puteaux, tout près de Gennevilliers, a déjà réalisé une terrasse méditerranéenne en pierre naturelle à Nanterre, un projet type pour MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">l-esprit-au-vert-71b05.houzzsite.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 54 25 52 77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les Jardins de Julien</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce paysagiste concepteur installé à quelques kilomètres de Gennevilliers crée des terrasses en pierre, des murets et des allées : il peut prescrire et poser MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.jardinsdejulien.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">09 85 20 70 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les Jardins de la Vallée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce paysagiste-pisciniste des Yvelines pose déjà des terrasses en travertin calcaire : MINYALA est une alternative directe pour ses terrasses et abords de piscine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.jardinsdelavallee.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 30 57 07 07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pensée au Jardin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint-Germain-en-Laye (78100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce paysagiste de Saint-Germain-en-Laye fait du dallage, du pavage et de la maçonnerie paysagère, il pourrait utiliser MINYALA pour les terrasses et allées de ses clients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.penseeaujardin.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 70 93 96 93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrasse et Jardin de Paris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paris (75016)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce paysagiste parisien avec showroom dans le 16e réalise les sols de terrasses et rooftops d'hôtels et de restaurants, il pourrait y poser MINYALA sur plots.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">terrasseetjardindeparis.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 49 65 06 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entreprise Boisseleau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce carreleur certifié Qualibat 6313 pose de la pierre naturelle en sols et terrasses pour une clientèle haut de gamme : il peut utiliser MINYALA sur ses chantiers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.carrelage-marbre-iledefrance.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 34 51 01 22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entreprise Radiguet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marcq (78770)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce carreleur des Yvelines pose des dallages en pierre naturelle, des terrasses et des carrelages de piscine, il pourrait acheter et poser MINYALA pour ses clients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rénovation haut de gamme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entreprise Kenny</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chatou (78400)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette entreprise de rénovation de Chatou pose déjà marbre, travertin et dallages en pierre pour architectes et copropriétés : elle pourrait acheter MINYALA pour ses chantiers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.kenny-entreprise.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 30 53 46 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modern Works</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette entreprise de rénovation tous corps d'état pose de la pierre naturelle dans des rénovations haut de gamme à Paris : elle pourrait utiliser MINYALA pour ses sols.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">modernworks.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 09 71 65 91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wild Rénovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paris (75008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce contractant général en rénovation de luxe choisit et pose lui-même des pierres naturelles calcaires dans des intérieurs parisiens, et peut prescrire MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.wildrenovation.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 42 65 03 96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architecte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">atelier mmnk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette agence a déjà prescrit du calcaire au sol de l'hôtel Villa Gypsy à Deauville et mène de nombreux projets de restaurants et boutiques à Paris : elle peut prescrire MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mmnk.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frazzi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint-Étienne-du-Rouvray (76800)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce showroom carrelage et dallage de 1 500 m² dans l'agglomération rouennaise peut revendre MINYALA à ses clients pour sols intérieurs et terrasses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.frazzi.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maillard (salle d'exposition Colombelles)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colombelles (14460)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce distributeur normand, avec des showrooms et des comptoirs pros à Caen, Touques, au Havre et à Rouen, vend du carrelage de sol extérieur et peut référencer MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.maillard.fr/magasins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 72 61 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Murésol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Petit-Quevilly (76140)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce fournisseur-poseur de sols haut de gamme, implanté à Rouen et au Havre, pose déjà du carrelage de terrasse et peut proposer MINYALA à ses clients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.muretsol.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 59 22 99 56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atelier de la Pierre Marbre et Granits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hérouvillette (14850)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette marbrerie près de Caen et de Cabourg vend et pose pierres naturelles et revêtements de sol depuis 1987, donc elle peut proposer MINYALA à ses clients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">atelierdelapierremarbreetgranits.site-solocal.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 78 82 93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granits et Matériaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Houlme (76770)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce spécialiste de la pierre naturelle près de Rouen fournit des dallages et aménagements extérieurs aux maîtres d'ouvrage et aux paysagistes, il peut intégrer MINYALA à son offre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">granits-materiaux.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 35 75 64 07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Roche Taillée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cet atelier rouennais de taille de pierre vend déjà dallages et margelles de piscine en calcaire : il peut proposer MINYALA brut à sa clientèle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.la-roche-taillee.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marbres et Tendances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eslettes (76710)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette marbrerie près de Rouen réalise des dallages en pierre naturelle en intérieur, sur terrasses et autour des piscines, un relais possible pour MINYALA en Normandie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.marbresettendances.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 35 05 22 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bohin Jardin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bacqueville-en-Caux (76730)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce constructeur de piscines béton haut de gamme de Seine-Maritime réalise déjà des terrasses et plages de piscine en grandes dalles, exactement l'usage de MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.bohinjardin.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 34 88 23 41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delalande Piscines &amp; Spas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Touques (14800)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pisciniste de la Côte Fleurie avec showrooms à Deauville et Pont-l'Évêque, il propose margelles et terrasses autour de piscines haut de gamme où MINYALA a sa place.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.piscines-delalande.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 88 85 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jardin Passions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bois-Guillaume (76230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce pisciniste rouennais construit des terrasses périphériques en bois ou en pierre autour de ses piscines, un usage direct pour les dalles MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.jardinpassions.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 35 59 19 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Larcher Piscines (membre L'Esprit Piscine)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint-Arnoult (Deauville) (14800)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce constructeur de piscines béton de la Côte Fleurie, qui rénove aussi des bassins, peut poser MINYALA en margelles et en plages pour une clientèle aisée.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.larcher.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 58 06 00 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les Piscines Moreau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franqueville-Saint-Pierre (76520)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce pisciniste rouennais rénove margelles et plages : MINYALA peut remplacer d'anciennes plages lors de ses chantiers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.lespiscinesmoreau.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 34 88 22 88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piscines de France 76 (agence Le Havre)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montivilliers (76290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette agence de la région du Havre construit des piscines et réalise allées, terrasses et remplacement de margelles, des chantiers adaptés à MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.piscines-de-france.fr/piscinistes/pisciniste-le-havre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 32 40 00 42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piscines et Abris Nord-Ouest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angerville-l'Orcher (76280)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce pisciniste du pays de Caux propose déjà des margelles en pierre naturelle ou en travertin de la région du Havre jusqu'à Deauville et Évreux : MINYALA peut servir pour ses plages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.piscinesetabrisnordouest.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 34 88 21 04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barbedette Paysage (Barbedette Jardins)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gravigny (27930)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce paysagiste de l'agglomération d'Évreux, actif depuis 1987, réalise dallages, terrasses et maçonnerie paysagère et peut utiliser MINYALA sur ses chantiers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">barbedettepaysage.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 32 33 01 51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rpay Jardins &amp; Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Firfol (14100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce paysagiste haut de gamme du Pays d'Auge construit des piscines et pose margelles et terrasses : MINYALA convient pour ses plages et ses patios.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.rpay.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architecte d'intérieur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arcytis (Ollivier Bidon-Maraboeuf)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caen (14000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette agence caennaise aménage hôtels, restaurants et commerces (Mercure Caen notamment) : elle peut prescrire MINYALA en sol de hall, de boutique ou de restaurant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.arcytis.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 39 54 01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atelier Hemon Architectes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint-Gatien-des-Bois (14130)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cet atelier d'architecture de la région de Deauville, avec plus de 2 000 projets dont des hôtels et des maisons haut de gamme, peut prescrire MINYALA sur des chantiers importants.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.hemon-architectes.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 89 18 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maître d'œuvre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concept Intérieur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deauville (14800)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce maître d'œuvre de Deauville réalise des terrasses, des piscines et des rénovations : il peut prescrire MINYALA en dallage de terrasse ou en plage de piscine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.conceptinterieurdeauville.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 88 44 75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Art &amp; Sud Deco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paris (75014)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette boutique parisienne de carrelages et dallages orientaux (zellige, bejmat) pourrait ajouter un calcaire naturel comme MINYALA à son offre de sols.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 43 22 50 91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real Marbre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paris (75001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette marbrerie de luxe pose des dallages sur mesure dans des palaces et des boutiques, et peut proposer MINYALA pour des projets hôteliers ou commerciaux.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">real-marbre.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 42 61 84 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aqua System (membre L'Esprit Piscine)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freneuse (78840)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constructeur et rénovateur de piscines béton sur mesure dans les Yvelines, il pourrait proposer MINYALA pour les plages de ses bassins neufs ou rénovés.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.aqua-system.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 30 42 26 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ouest Piscines Services (OPS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croissy-sur-Seine (78290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce pisciniste de Croissy-sur-Seine, qui construit et rénove des bassins dans le 78, le 92 et le 95, peut proposer MINYALA en margelles et en plages lors de ses chantiers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.ops-ouestpiscines.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 39 73 53 74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Albizia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce paysagiste de Colombes, limitrophe de Gennevilliers, fait du dallage de jardin et de la maçonnerie paysagère : il peut retirer de petits lots de MINYALA à l'entrepôt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balcoon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paris (75011)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cet atelier parisien aménage des terrasses d'hôtels, des rooftops et des terrasses de particuliers, et cite la pierre naturelle parmi ses revêtements : il peut prescrire MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">balcoon.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 808 806 250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jardins de l'Orangerie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montmorency (95160)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce paysagiste certifié Qualipaysage fait du dallage et des terrasses dans le Val-d'Oise : il pourrait utiliser MINYALA pour ses créations de jardins.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.jardinsdelorangerie.com/jardins-orangerie-montmorency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 34 12 40 98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réflexe paysage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce paysagiste de Croissy-sur-Seine réalise maçonnerie paysagère, terrasses et dallages de jardin, des chantiers où MINYALA peut être posé.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simonson Landscape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paris (75010)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce concepteur-réalisateur parisien choisit les matériaux de ses terrasses et jardins avec piscine : il pourrait prescrire MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.simonsonlandscape.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 43 44 47 42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrasol TP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette entreprise de Croissy-sur-Seine construit des terrasses et réalise des dallages de jardin, ce qui en fait un poseur possible de MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terrasses des Oliviers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Levallois-Perret (92300)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce paysagiste de Levallois, tout près de Gennevilliers, propose la pierre naturelle parmi les matériaux de ses terrasses et peut intégrer MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.terrassesdesoliviers.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 40 95 33 02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SGC - Saint Georges Carrelage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villeneuve-Saint-Georges (94190)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce carreleur du Val-de-Marne pose des dallages en pierre naturelle et des plages de piscine, donc il peut être un client direct pour MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belmard Bâtiment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paris (75020)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette entreprise de rénovation haut de gamme parisienne refait les sols d'appartements de standing, elle pourrait y poser MINYALA en sol intérieur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.belmard-batiment.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 70 94 98 06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franpierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette entreprise de rénovation tous corps d'état du 95 et du 78 construit des terrasses et pose des revêtements de sol, donc elle peut acheter MINYALA pour ses chantiers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.franpierre-herblay.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 39 60 69 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atelier Ceben</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce cabinet d'architecture intérieure de Saint-Germain-en-Laye conçoit et suit des rénovations de logements et de commerces, il peut prescrire MINYALA en sol intérieur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.atelierceben.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 51 45 53 87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D+B Interior Design Studio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette agence parisienne aménage hôtels, boutique-hôtels et restaurants, jusqu'à Honfleur : elle peut prescrire de gros volumes de pierre pour des sols.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERSI Architecture</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce studio parisien d'architecture intérieure conçoit des restaurants, des cafés et des boutiques au style « quiet luxury », et peut prescrire MINYALA en sol.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.mersi-architecture.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magic'Piscines (concessionnaire Magiline Évreux)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sainte-Colombe-la-Commanderie (27110)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce constructeur de piscines enterrées de l'Eure pourrait proposer MINYALA en plage de piscine à ses clients autour d'Évreux.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 32 24 28 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seine et Mer Piscines (concessionnaire Mondial Piscine Rouen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce pisciniste de l'est rouennais, avec plus de 150 piscines neuves et 80 rénovations, peut proposer MINYALA en plages et en margelles à ses clients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rouen.mondial-piscine.eu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 35 32 85 84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fdpaysage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint-Désir (14100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce paysagiste du Pays d'Auge pose dallages de jardin, murets et décors minéraux : il peut utiliser MINYALA pour ses allées et terrasses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carreleur Mosaïste 2M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Havre (76620)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce maçon-carreleur du Havre pose déjà des dallages en pierre et peut acheter MINYALA pour ses chantiers de rénovation intérieure et extérieure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laurence Vermont Architecture d'intérieur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonsecours (76240)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette architecte d'intérieur près de Rouen rénove des maisons patrimoniales et chiffre les fournitures de ses projets, elle pourrait y prescrire MINYALA en sol.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">laurencevermontdecoration.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 65 69 67 08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nicolas Guérin (architecte d'intérieur)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cet architecte d'intérieur caennais agence restaurants, bars, cafés et magasins : MINYALA peut convenir aux sols de ces commerces.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Studio Alexandra Barluet (AB Décoration)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rouen (76160)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce studio rouennais d'architecture intérieure conçoit des maisons, des appartements et des restaurants, et peut proposer MINYALA en sol de pièce de vie ou de salle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abdecoration.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 58 13 15 32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Studio ELC Design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce studio d'architecture intérieure de Deauville travaille sur des villas et un hôtel de la Côte Fleurie, une clientèle qui peut demander des sols en calcaire comme MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 16 79 46 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ynspir (architecte d'intérieur Caen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cette architecte d'intérieur caennaise du réseau Ynspir privilégie les matériaux nobles et la pierre calcaire, donc elle peut prescrire MINYALA en sol.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ynspir.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07 80 96 48 84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACT Création</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce maître d'œuvre et architecte d'intérieur caennais mène des rénovations clés en main à Caen et à Deauville, et choisit les sols de ses clients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.act-mo.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 20 86 70 71</t>
+  </si>
+  <si>
     <t xml:space="preserve">Canal</t>
   </si>
   <si>
-    <t xml:space="preserve">Acheteurs visés</t>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qui on y touche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dates / zone</t>
   </si>
   <si>
     <t xml:space="preserve">Ce qu'il faut faire</t>
   </si>
   <si>
+    <t xml:space="preserve">Coût</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lien</t>
   </si>
   <si>
+    <t xml:space="preserve">Fait le</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leboncoin — compte Pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annonces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Particuliers et petits artisans qui cherchent de la pierre près de chez eux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annonce localisée à Gennevilliers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ouvrir un compte Pro (obligatoire pour une entreprise). Une annonce par usage : terrasse, plage de piscine, sol intérieur. Prix au m², minimum 25 m², retrait sur rendez-vous. Republier au printemps.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compte Pro gratuit ; 50 annonces offertes en Maison &amp; Jardin, puis payant (à vérifier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ouvrir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiche Google (Google Business Profile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personnes qui cherchent « pierre naturelle » ou « dallage » près de Gennevilliers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recherche locale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Créer la fiche du point de retrait : catégorie fournisseur de pierre, retrait sur rendez-vous, photos réelles, lien vers la fiche MINYALA. Demander un avis à chaque client.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gratuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houzz — profil pro « Pierres et plans de travail »</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Particuliers en projet et architectes qui cherchent un fournisseur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recherche par ville (rayon 10 à 100 km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Créer un profil pro situé à Gennevilliers avec photos de MINYALA posé, prix au m² et minimum de commande. Demander des avis clients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inscription gratuite (options payantes à vérifier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PagesJaunes — fiche professionnelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recherches par ville et par métier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Créer ou revendiquer la fiche Pierre d'Égypte, rubriques pierre naturelle et carrelage, avec photos et lien vers le site.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiche gratuite (options payantes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vivastreet — Bricolage, jardinage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Particuliers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lire les règles de l'Espace Pro, puis publier une annonce pro identifiée avec photos et prix au m².</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Certaines catégories payantes (à vérifier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Facebook — Page entreprise (pas Marketplace)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réseau social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Particuliers d'Île-de-France et de Normandie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketplace est réservé aux ventes entre particuliers et Meta peut bloquer les vendeurs pros. Créer une Page Pierre d'Égypte et utiliser les publicités Meta à la place. Ne jamais publier en se faisant passer pour un particulier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Page gratuite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groupes Facebook locaux (à chercher vous-même)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propriétaires qui préparent des travaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92, 95, 78, 93, Normandie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aucun groupe n'a pu être vérifié par la recherche. Dans Facebook, cherchez « travaux maison 92 », « piscine Île-de-France », « jardin Normandie », « bons plans matériaux », « déstockage matériaux ». Lisez le règlement : ne publiez que là où les pros sont autorisés, idéalement avec l'accord des administrateurs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForumConstruire — Terrasse « en dur »</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forum de construction très fréquenté par des propriétaires de maison.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France entière</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Créer un compte clairement identifié comme professionnel et répondre aux questions sur la pierre calcaire (pose, joints, entretien), sans publicité. Avec l'accord d'un client, publier un récit de chantier avec photos.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForumConstruire — Allées et chemins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Répondre aux questions sur les allées en pierre (pose sur lit de mortier ou sur dalle, joints). Le format 30×60 convient aux chemins de jardin. Pas de lien commercial dans les messages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForumConstruire — Carrelage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intervenir sur les sujets pierre naturelle et travertin pour les sols intérieurs, en conseil technique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForumConstruire — Rénovation et extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Répondre aux questions de remplacement de sols ou de terrasse. Laisser les membres demander vos coordonnées.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForumPiscine — Terrasse (autour de la piscine)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propriétaires de piscine qui choisissent leur plage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Répondre sur le choix, la pose et l'entretien d'une plage en pierre. La charte pro interdit toute publicité, signature commerciale ou lien vers le site.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForumPiscine — Piscine maçonnée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propriétaires en cours de construction, avant le choix de la plage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repérer les projets au stade du chantier et apporter des réponses techniques sur la pierre autour du bassin, sans promotion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houzz — Discussions (paysage, jardin, piscine, rénovation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Particuliers en projet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Répondre avec le profil pro Houzz et des photos de réalisations. Les réponses renvoient vers votre profil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForumConstruire — avis sur les boutiques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Futurs acheteurs qui vérifient un vendeur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inviter les clients satisfaits à laisser un avis spontané. Ne jamais rédiger de faux avis (sanctionné).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foire de Rouen 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand public normand en projet maison et jardin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27 mars – 4 avril 2027, Parc des Expositions de Rouen (Le Grand-Quevilly)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demander le dossier exposant (univers Maison &amp; Jardin). Bon moment pour lancer la saison terrasse en Normandie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À vérifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foire de Paris 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand public francilien en projet maison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 avril – 10 mai 2027, Paris (lieu à confirmer, habituellement Porte de Versailles)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visiter pour repérer exposants terrasse et piscine et poseurs partenaires, et chiffrer un stand pour 2028. Sur un stand, ne collecter des contacts qu'avec consentement explicite.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foire internationale de Caen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand public du Calvados et de la Côte Fleurie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dates 2027 non publiées (2026 : 18–27 septembre, Parc des Expositions de Caen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surveiller les dates 2027 et demander un dossier exposant secteur Habitat &amp; Jardin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salon de la copropriété et de l'habitat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syndics, conseils syndicaux et copropriétaires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4–5 novembre 2026, Paris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y aller en visiteur pour présenter MINYALA pour des halls et des cours de copropriété.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Ads — Recherche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publicité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personnes qui cherchent activement de la pierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rayon autour de Gennevilliers ; Rouen, Le Havre, Caen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mots-clés du kit de vente (« dalle pierre naturelle terrasse », « pierre calcaire 30x60 », « déstockage pierre naturelle »…), option « présence » pour la zone de retrait. Exclure « gratuit » et « tuto ».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget libre (au clic)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meta (Facebook, Instagram) — publicités</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propriétaires de maisons avec jardin ou piscine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~30 km autour de Gennevilliers ; campagne séparée Normandie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cibler les centres d'intérêt (piscine, jardin, rénovation) et les communes pavillonnaires (Rueil, Chatou, Le Vésinet, Saint-Germain-en-Laye, Maisons-Laffitte, Montmorency…). Photos réelles du lot.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget libre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leboncoin Publicité — Local+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visiteurs des rubriques maison, jardin, bricolage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92, 95, 93, 78 (Normandie en option)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contacter l'équipe commerciale pour une campagne de février à juin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinterest Business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personnes qui cherchent des idées de terrasse et de sol</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publier des épingles de réalisations en MINYALA qui renvoient vers la fiche produit. Booster les meilleures de février à avril.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compte gratuit ; budget libre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ForumConstruire — publicité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Membres du forum, ciblage par département</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92, 95, 93, 78, 75, 76, 14, 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demander un devis pour des bannières ciblées ou un partenariat éditorial (article sur la pose de pierre en terrasse).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Au CPM (à vérifier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Habitatpresto (via des poseurs partenaires)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plateforme projets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Particuliers qui demandent des devis de travaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone choisie par le pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pierre d'Égypte ne pose pas : s'associer à des carreleurs ou paysagistes inscrits qui proposent MINYALA dans leurs devis de dallage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Idées de ciblage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Saison : préparer en janvier-février (fiche Google, Houzz, Pinterest), pousser de mars à juin pour les terrasses et piscines, puis viser sols intérieurs et cuisines de septembre à novembre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Piscines : visuels de plages en MINYALA diffusés d'avril à juin, avant l'ouverture des bassins.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Une terrasse familiale fait souvent plus de 25 m² : le minimum de commande n'est pas un frein, dites-le dans les annonces.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Reciblage des visiteurs du site seulement avec un bandeau cookies conforme (voir onglet Règles).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Collecter des contacts avec une case de consentement non pré-cochée (formulaire « recevoir les prix / le guide de pose », foires). Sans ce consentement, pas d'e-mail, de SMS ni d'appel à un particulier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• À décider : échantillons à retirer à Gennevilliers, tarif pour poseurs partenaires. Rien de cela n'existe aujourd'hui sur le site.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour qui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dates / lieu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backacia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pros du bâtiment (surplus, fins de série)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrepôt Ivry-sur-Seine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demander s'ils acceptent un lot de dallage en pierre et à quelles conditions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cycle Up</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architectes, constructeurs, négoces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketplace des surplus et stocks invendus du négoce. Demander s'ils prennent la pierre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOAMP — alertes marchés publics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communes, Paris La Défense, bailleurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filtrer 75, 92, 95, 76, 14, 27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Créer des alertes « pierre naturelle » et « dallage ». Contacter les entreprises qui gagnent ces marchés pour les approvisionner.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marché public : piscine de Chatou (78)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entreprises qui feront les travaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avis publié le 20/01/2026, travaux annoncés sept. 2026 – juil. 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suivre l'avis (procédure annoncée comme relancée) et contacter les entreprises retenues pour les plages et abords.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EquipHotel 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architectes et agenceurs d'hôtels et restaurants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2–5 novembre 2026, Paris Expo Porte de Versailles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visiter pour rencontrer des prescripteurs de sols et terrasses pour l'hôtellerie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piscine Global Europe 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piscinistes et réseaux (Mondial Piscine, Magiline, L'Esprit Piscine…)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17–20 novembre 2026, Eurexpo Lyon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visiter avec photos et prix pour rencontrer les réseaux de piscinistes dont plusieurs agences sont dans l'onglet Prospects.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salon des Maires et des Collectivités 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Services voirie et espaces publics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24–26 novembre 2026, Paris Expo Porte de Versailles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Présenter MINYALA pour places et parvis piétons, repérer les futurs appels d'offres.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paysalia + Rocalia 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paysagistes, marbriers, négociants (Rocalia = salon de la pierre)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 nov. – 2 déc. 2027, Eurexpo Lyon (dates Rocalia à confirmer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visiter ou exposer pour rencontrer les acheteurs de pierre en volume.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118712 — catégorie pierres naturelles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pros qui cherchent un fournisseur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vérifier que Pierre d'Égypte y figure, avec retrait sur rendez-vous et lien vers le site.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChatGPT (via Shopify)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acheteurs qui demandent conseil à ChatGPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disponibilité en France à vérifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shopify admin &gt; Paramètres &gt; Canaux de vente &gt; Agentic storefronts. Masquer d'abord les produits « Acompte ».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-mail / téléphone aux pros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les entreprises de l'onglet Prospects</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Message prêt dans le kit de vente (section 4). Autorisé si le message concerne leur métier, avec possibilité de refuser (voir Règles). 10 contacts par semaine, relance après 7 jours.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Situation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce que dit la règle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appeler un particulier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interdit sans son consentement préalable depuis le 11 août 2026 (art. L.223-1 Code de la consommation, loi du 30 juin 2025 ; décret n° 2026-662 du 23 juillet 2026). Filtrer avec Bloctel ne suffit plus. Avec consentement : du lundi au vendredi, 10 h–13 h et 14 h–20 h.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appeler un professionnel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autorisé si l'appel concerne son activité (ex. un paysagiste pour de la pierre). Il doit pouvoir refuser simplement et gratuitement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-mail ou SMS à un particulier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consentement préalable obligatoire (case non pré-cochée). Exception : vos clients existants, pour des produits similaires.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-mail ou SMS à un professionnel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autorisé si le message concerne son métier, avec un moyen simple de refuser les envois. Chaque message identifie l'expéditeur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Courrier postal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autorisé si la personne peut s'y opposer simplement. Chaque envoi identifie l'expéditeur.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Leboncoin</t>
   </si>
   <si>
-    <t xml:space="preserve">Particuliers et petits artisans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publier l'annonce du kit de vente (section 3) dans Bricolage &gt; Matériaux. Déclarez-vous comme professionnel. Remonter l'annonce chaque semaine.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.leboncoin.fr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Facebook Marketplace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Particuliers, Île-de-France et Normandie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Même annonce que Leboncoin, avec des photos réelles du lot.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.facebook.com/marketplace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Backacia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Professionnels du bâtiment (réemploi, surplus)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marketplace de surplus et fins de série, entrepôt à Ivry-sur-Seine. Demandez s'ils acceptent un lot de dallage en pierre et à quelles conditions.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.backacia.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cycle Up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Architectes, constructeurs, négoces</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marketplace qui fait circuler les surplus et stocks invendus du négoce. Demandez s'ils prennent la pierre.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.cycle-up.fr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Business Profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recherches locales (« pierre naturelle Gennevilliers »)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Créer ou compléter la fiche du point de retrait avec photos, horaires sur rendez-vous et lien vers MINYALA. Gratuit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/business/</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ChatGPT (via Shopify)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acheteurs qui demandent conseil à ChatGPT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopify admin &gt; Paramètres &gt; Canaux de vente &gt; Agentic storefronts. Vérifier la disponibilité en France. Masquer d'abord les produits « Acompte ».</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://shopify.dev/changelog/a-new-home-for-agentic-storefronts-in-your-admin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-mail / WhatsApp aux pros</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Les entreprises de l'onglet Prospects</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Message prêt dans le kit de vente (section 4). 10 contacts par semaine, relance après 7 jours.</t>
+    <t xml:space="preserve">Compte Pro obligatoire pour une entreprise qui vend un stock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se faire passer pour un particulier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pratique commerciale trompeuse : jusqu'à 2 ans de prison et 300 000 € d'amende. Vaut pour les marketplaces, forums et faux avis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forums</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La charte pro de ForumPiscine interdit publicité, signature commerciale et lien vers le site ; ForumConstruire sanctionne les faux avis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publicités et reciblage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pixel Meta ou balises Google Ads sur le site Shopify : bandeau de consentement aux cookies obligatoire avant le reciblage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vente en ligne à un particulier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 jours de rétractation à partir du lendemain de la réception. Le client doit en être informé avant la commande.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résumé non juridique, d'après les pages officielles consultées le 12/10/2026.</t>
   </si>
 </sst>
 </file>
@@ -682,7 +2388,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -691,8 +2397,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -747,6 +2453,10 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -771,16 +2481,16 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1096,12 +2806,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1109,128 +2819,126 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>10</v>
       </c>
       <c r="C11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>12</v>
       </c>
       <c r="C12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>14</v>
       </c>
       <c r="C13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="5"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>17</v>
       </c>
+      <c r="C15" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>19</v>
-      </c>
-      <c r="B18" s="8" t="n">
-        <f aca="false">COUNTIF(Prospects!$I$2:$I$200,A18)</f>
-        <v>22</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B19" s="8" t="n">
-        <f aca="false">COUNTIF(Prospects!$I$2:$I$200,A19)</f>
-        <v>0</v>
+        <f aca="false">COUNTIF(Prospects!$L$2:$L$400,A19)</f>
+        <v>111</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B20" s="8" t="n">
-        <f aca="false">COUNTIF(Prospects!$I$2:$I$200,A20)</f>
+        <f aca="false">COUNTIF(Prospects!$L$2:$L$400,A20)</f>
         <v>0</v>
       </c>
     </row>
@@ -1239,7 +2947,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="8" t="n">
-        <f aca="false">COUNTIF(Prospects!$I$2:$I$200,A21)</f>
+        <f aca="false">COUNTIF(Prospects!$L$2:$L$400,A21)</f>
         <v>0</v>
       </c>
     </row>
@@ -1248,7 +2956,7 @@
         <v>22</v>
       </c>
       <c r="B22" s="8" t="n">
-        <f aca="false">COUNTIF(Prospects!$I$2:$I$200,A22)</f>
+        <f aca="false">COUNTIF(Prospects!$L$2:$L$400,A22)</f>
         <v>0</v>
       </c>
     </row>
@@ -1257,7 +2965,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="8" t="n">
-        <f aca="false">COUNTIF(Prospects!$I$2:$I$200,A23)</f>
+        <f aca="false">COUNTIF(Prospects!$L$2:$L$400,A23)</f>
         <v>0</v>
       </c>
     </row>
@@ -1266,60 +2974,70 @@
         <v>24</v>
       </c>
       <c r="B24" s="8" t="n">
-        <f aca="false">COUNTIF(Prospects!$I$2:$I$200,A24)</f>
+        <f aca="false">COUNTIF(Prospects!$L$2:$L$400,A24)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="3" t="n">
-        <f aca="false">COUNTA(Prospects!$D$2:$D$200)</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="4" t="s">
+      <c r="B25" s="8" t="n">
+        <f aca="false">COUNTIF(Prospects!$L$2:$L$400,A25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="9" t="n">
-        <v>35</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>27</v>
+      <c r="B26" s="3" t="n">
+        <f aca="false">COUNTA(Prospects!$E$2:$E$400)</f>
+        <v>111</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B28" s="11" t="n">
-        <f aca="false">SUM(Prospects!$M$2:$M$200)</f>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B29" s="11" t="n">
+        <f aca="false">SUM(Prospects!$P$2:$P$400)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B29" s="12" t="n">
-        <f aca="false">B28*B27</f>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B30" s="12" t="n">
+        <f aca="false">B29*B28</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A3:C3"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A7:C7"/>
-    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="A8:C8"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1336,826 +3054,4802 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:P112"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="K1" s="13" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="L1" s="13" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="N1" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="13" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="14" t="n">
+      <c r="B2" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" s="14" t="s">
-        <v>40</v>
+      <c r="D2" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>44</v>
       </c>
       <c r="F2" s="14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G2" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="H2" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="18"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
+        <v>46</v>
+      </c>
+      <c r="H2" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" s="16"/>
+      <c r="J2" s="16"/>
+      <c r="K2" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" s="18" t="s">
+        <v>20</v>
+      </c>
       <c r="M2" s="19"/>
+      <c r="N2" s="18"/>
+      <c r="O2" s="18"/>
+      <c r="P2" s="20"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="14" t="n">
+      <c r="B3" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="14" t="s">
-        <v>45</v>
+      <c r="D3" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>49</v>
       </c>
       <c r="F3" s="14" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="18"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
+      <c r="H3" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>20</v>
+      </c>
       <c r="M3" s="19"/>
+      <c r="N3" s="18"/>
+      <c r="O3" s="18"/>
+      <c r="P3" s="20"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>48</v>
+      <c r="D4" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>52</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="H4" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" s="18"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
+        <v>46</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L4" s="18" t="s">
+        <v>20</v>
+      </c>
       <c r="M4" s="19"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="18"/>
+      <c r="P4" s="20"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="14" t="n">
+      <c r="B5" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>51</v>
+      <c r="D5" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>55</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J5" s="18"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="17"/>
+        <v>46</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="18" t="s">
+        <v>20</v>
+      </c>
       <c r="M5" s="19"/>
+      <c r="N5" s="18"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>54</v>
+      <c r="D6" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>58</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="18"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
+        <v>60</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="16"/>
+      <c r="J6" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="K6" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="18" t="s">
+        <v>20</v>
+      </c>
       <c r="M6" s="19"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="n">
+      <c r="N6" s="18"/>
+      <c r="O6" s="18"/>
+      <c r="P6" s="20"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="20" t="s">
-        <v>57</v>
-      </c>
       <c r="D7" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I7" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" s="18"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
+        <v>63</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" s="16"/>
+      <c r="J7" s="16"/>
+      <c r="K7" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" s="18" t="s">
+        <v>20</v>
+      </c>
       <c r="M7" s="19"/>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="20"/>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="n">
+      <c r="A8" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="20" t="n">
+      <c r="B8" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>57</v>
-      </c>
       <c r="D8" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I8" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" s="18"/>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
+        <v>67</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L8" s="18" t="s">
+        <v>20</v>
+      </c>
       <c r="M8" s="19"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="20"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="n">
+      <c r="A9" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="20" t="s">
-        <v>64</v>
-      </c>
       <c r="D9" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="H9" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I9" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J9" s="18"/>
-      <c r="K9" s="17"/>
-      <c r="L9" s="17"/>
+        <v>71</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+      <c r="K9" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="18" t="s">
+        <v>20</v>
+      </c>
       <c r="M9" s="19"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="n">
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="20"/>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="20" t="n">
+      <c r="B10" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="C10" s="20" t="s">
-        <v>64</v>
-      </c>
       <c r="D10" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G10" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="H10" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I10" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J10" s="18"/>
-      <c r="K10" s="17"/>
-      <c r="L10" s="17"/>
+        <v>71</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L10" s="18" t="s">
+        <v>20</v>
+      </c>
       <c r="M10" s="19"/>
+      <c r="N10" s="18"/>
+      <c r="O10" s="18"/>
+      <c r="P10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="n">
+      <c r="A11" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="21" t="n">
         <v>2</v>
-      </c>
-      <c r="C11" s="20" t="s">
-        <v>64</v>
       </c>
       <c r="D11" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="E11" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L11" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="19"/>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L12" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M12" s="19"/>
+      <c r="N12" s="18"/>
+      <c r="O12" s="18"/>
+      <c r="P12" s="20"/>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L13" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M13" s="19"/>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="20"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L14" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M14" s="19"/>
+      <c r="N14" s="18"/>
+      <c r="O14" s="18"/>
+      <c r="P14" s="20"/>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+      <c r="K15" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L15" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M15" s="19"/>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L16" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M16" s="19"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="18"/>
+      <c r="P16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L17" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M17" s="19"/>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="20"/>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L18" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M18" s="19"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="20"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L19" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M19" s="19"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="20"/>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M20" s="19"/>
+      <c r="N20" s="18"/>
+      <c r="O20" s="18"/>
+      <c r="P20" s="20"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+      <c r="K21" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L21" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M21" s="19"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="20"/>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="16" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+      <c r="K22" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L22" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M22" s="19"/>
+      <c r="N22" s="18"/>
+      <c r="O22" s="18"/>
+      <c r="P22" s="20"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+      <c r="K23" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L23" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M23" s="19"/>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="20"/>
+    </row>
+    <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="14" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="I24" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="J24" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="K24" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L24" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M24" s="19"/>
+      <c r="N24" s="18"/>
+      <c r="O24" s="18"/>
+      <c r="P24" s="20"/>
+    </row>
+    <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="F25" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="G25" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="I25" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="J25" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="K25" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L25" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M25" s="19"/>
+      <c r="N25" s="18"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="20"/>
+    </row>
+    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="14" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" s="17" t="s">
+        <v>134</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="K26" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L26" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M26" s="19"/>
+      <c r="N26" s="18"/>
+      <c r="O26" s="18"/>
+      <c r="P26" s="20"/>
+    </row>
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="F27" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="G27" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H27" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="I27" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="J27" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="K27" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L27" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M27" s="19"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="20"/>
+    </row>
+    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C28" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="G28" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="I28" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="J28" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="K28" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L28" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M28" s="19"/>
+      <c r="N28" s="18"/>
+      <c r="O28" s="18"/>
+      <c r="P28" s="20"/>
+    </row>
+    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C29" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="F29" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="G29" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H29" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="I29" s="17" t="s">
+        <v>149</v>
+      </c>
+      <c r="J29" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="K29" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L29" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M29" s="19"/>
+      <c r="N29" s="18"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="20"/>
+    </row>
+    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="14" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C30" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="F30" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="G30" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="I30" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="J30" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="K30" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L30" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M30" s="19"/>
+      <c r="N30" s="18"/>
+      <c r="O30" s="18"/>
+      <c r="P30" s="20"/>
+    </row>
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="14" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="F31" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="G31" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H31" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="I31" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="J31" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="K31" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L31" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M31" s="19"/>
+      <c r="N31" s="18"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="20"/>
+    </row>
+    <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C32" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E32" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="I32" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="J32" s="16" t="s">
+        <v>165</v>
+      </c>
+      <c r="K32" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L32" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M32" s="19"/>
+      <c r="N32" s="18"/>
+      <c r="O32" s="18"/>
+      <c r="P32" s="20"/>
+    </row>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E33" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H33" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="I33" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="J33" s="16" t="s">
+        <v>170</v>
+      </c>
+      <c r="K33" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L33" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M33" s="19"/>
+      <c r="N33" s="18"/>
+      <c r="O33" s="18"/>
+      <c r="P33" s="20"/>
+    </row>
+    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C34" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E34" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="I34" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="J34" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="K34" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L34" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M34" s="19"/>
+      <c r="N34" s="18"/>
+      <c r="O34" s="18"/>
+      <c r="P34" s="20"/>
+    </row>
+    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="14" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E35" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="F35" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H35" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="I35" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="J35" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="K35" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L35" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M35" s="19"/>
+      <c r="N35" s="18"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="20"/>
+    </row>
+    <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E36" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="F36" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="I36" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="J36" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="K36" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L36" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M36" s="19"/>
+      <c r="N36" s="18"/>
+      <c r="O36" s="18"/>
+      <c r="P36" s="20"/>
+    </row>
+    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C37" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E37" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="F37" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="I37" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="J37" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="K37" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L37" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M37" s="19"/>
+      <c r="N37" s="18"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="20"/>
+    </row>
+    <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C38" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="G38" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H38" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="I38" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="J38" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="K38" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L38" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M38" s="19"/>
+      <c r="N38" s="18"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="20"/>
+    </row>
+    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="21" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C39" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H39" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="I39" s="17" t="s">
+        <v>199</v>
+      </c>
+      <c r="J39" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="K39" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L39" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M39" s="19"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="20"/>
+    </row>
+    <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="21" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C40" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D40" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E40" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="F40" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="G40" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H40" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="I40" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="J40" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="K40" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L40" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M40" s="19"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="20"/>
+    </row>
+    <row r="41" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E41" s="22" t="s">
+        <v>205</v>
+      </c>
+      <c r="F41" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="G41" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H41" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="I41" s="17" t="s">
+        <v>208</v>
+      </c>
+      <c r="J41" s="16" t="s">
+        <v>209</v>
+      </c>
+      <c r="K41" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L41" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M41" s="19"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="18"/>
+      <c r="P41" s="20"/>
+    </row>
+    <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="21" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C42" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D42" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E42" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="F42" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="G42" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H42" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="I42" s="17" t="s">
+        <v>213</v>
+      </c>
+      <c r="J42" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="K42" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L42" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M42" s="19"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="18"/>
+      <c r="P42" s="20"/>
+    </row>
+    <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="21" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C43" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D43" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E43" s="22" t="s">
+        <v>215</v>
+      </c>
+      <c r="F43" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="G43" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H43" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="I43" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="J43" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="K43" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L43" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M43" s="19"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="18"/>
+      <c r="P43" s="20"/>
+    </row>
+    <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="21" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C44" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="F44" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="G44" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H44" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="I44" s="17" t="s">
+        <v>223</v>
+      </c>
+      <c r="J44" s="16" t="s">
+        <v>224</v>
+      </c>
+      <c r="K44" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L44" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M44" s="19"/>
+      <c r="N44" s="18"/>
+      <c r="O44" s="18"/>
+      <c r="P44" s="20"/>
+    </row>
+    <row r="45" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="21" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C45" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E45" s="22" t="s">
+        <v>225</v>
+      </c>
+      <c r="F45" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="G45" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H45" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="I45" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="J45" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="K45" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L45" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M45" s="19"/>
+      <c r="N45" s="18"/>
+      <c r="O45" s="18"/>
+      <c r="P45" s="20"/>
+    </row>
+    <row r="46" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="21" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C46" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E46" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="F46" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="G46" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H46" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="I46" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="J46" s="16" t="s">
+        <v>234</v>
+      </c>
+      <c r="K46" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L46" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M46" s="19"/>
+      <c r="N46" s="18"/>
+      <c r="O46" s="18"/>
+      <c r="P46" s="20"/>
+    </row>
+    <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="21" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C47" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D47" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" s="22" t="s">
+        <v>235</v>
+      </c>
+      <c r="F47" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="G47" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H47" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="I47" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="J47" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="K47" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L47" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M47" s="19"/>
+      <c r="N47" s="18"/>
+      <c r="O47" s="18"/>
+      <c r="P47" s="20"/>
+    </row>
+    <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="21" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C48" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E48" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="F48" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="G48" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H48" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="I48" s="17" t="s">
+        <v>241</v>
+      </c>
+      <c r="J48" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="K48" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L48" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M48" s="19"/>
+      <c r="N48" s="18"/>
+      <c r="O48" s="18"/>
+      <c r="P48" s="20"/>
+    </row>
+    <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="21" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C49" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E49" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="F49" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="G49" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H49" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="I49" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="J49" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="K49" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L49" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M49" s="19"/>
+      <c r="N49" s="18"/>
+      <c r="O49" s="18"/>
+      <c r="P49" s="20"/>
+    </row>
+    <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="21" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C50" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E50" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="G50" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H50" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="I50" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="J50" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="K50" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L50" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M50" s="19"/>
+      <c r="N50" s="18"/>
+      <c r="O50" s="18"/>
+      <c r="P50" s="20"/>
+    </row>
+    <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C51" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E51" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="F51" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="G51" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H51" s="21" t="s">
+        <v>253</v>
+      </c>
+      <c r="I51" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="J51" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="K51" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L51" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M51" s="19"/>
+      <c r="N51" s="18"/>
+      <c r="O51" s="18"/>
+      <c r="P51" s="20"/>
+    </row>
+    <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="21" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D52" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E52" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="F52" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="G52" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H52" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="I52" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="J52" s="16" t="s">
+        <v>259</v>
+      </c>
+      <c r="K52" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L52" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M52" s="19"/>
+      <c r="N52" s="18"/>
+      <c r="O52" s="18"/>
+      <c r="P52" s="20"/>
+    </row>
+    <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="21" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C53" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D53" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E53" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="F53" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G53" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H53" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="I53" s="17" t="s">
+        <v>262</v>
+      </c>
+      <c r="J53" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="K53" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L53" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M53" s="19"/>
+      <c r="N53" s="18"/>
+      <c r="O53" s="18"/>
+      <c r="P53" s="20"/>
+    </row>
+    <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="21" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C54" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E54" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="F54" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="G54" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H54" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="I54" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="J54" s="16" t="s">
+        <v>268</v>
+      </c>
+      <c r="K54" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L54" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M54" s="19"/>
+      <c r="N54" s="18"/>
+      <c r="O54" s="18"/>
+      <c r="P54" s="20"/>
+    </row>
+    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="21" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C55" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E55" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="G55" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H55" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="I55" s="17" t="s">
+        <v>272</v>
+      </c>
+      <c r="J55" s="16" t="s">
+        <v>273</v>
+      </c>
+      <c r="K55" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L55" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M55" s="19"/>
+      <c r="N55" s="18"/>
+      <c r="O55" s="18"/>
+      <c r="P55" s="20"/>
+    </row>
+    <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C56" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E56" s="22" t="s">
+        <v>274</v>
+      </c>
+      <c r="F56" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="G56" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H56" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="I56" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="J56" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="K56" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L56" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M56" s="19"/>
+      <c r="N56" s="18"/>
+      <c r="O56" s="18"/>
+      <c r="P56" s="20"/>
+    </row>
+    <row r="57" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="21" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C57" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E57" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="F57" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G57" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H57" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="I57" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="J57" s="16" t="s">
+        <v>282</v>
+      </c>
+      <c r="K57" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L57" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M57" s="19"/>
+      <c r="N57" s="18"/>
+      <c r="O57" s="18"/>
+      <c r="P57" s="20"/>
+    </row>
+    <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="21" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C58" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D58" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E58" s="22" t="s">
+        <v>283</v>
+      </c>
+      <c r="F58" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="G58" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H58" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="I58" s="17" t="s">
+        <v>285</v>
+      </c>
+      <c r="J58" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="K58" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L58" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M58" s="19"/>
+      <c r="N58" s="18"/>
+      <c r="O58" s="18"/>
+      <c r="P58" s="20"/>
+    </row>
+    <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="21" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C59" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D59" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E59" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="F59" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="G59" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H59" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="I59" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="J59" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="K59" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L59" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M59" s="19"/>
+      <c r="N59" s="18"/>
+      <c r="O59" s="18"/>
+      <c r="P59" s="20"/>
+    </row>
+    <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="21" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C60" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E60" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="F60" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="G60" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H60" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="I60" s="17" t="s">
+        <v>295</v>
+      </c>
+      <c r="J60" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="K60" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L60" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M60" s="19"/>
+      <c r="N60" s="18"/>
+      <c r="O60" s="18"/>
+      <c r="P60" s="20"/>
+    </row>
+    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="21" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C61" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E61" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="F61" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="G61" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H61" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="I61" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="J61" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="K61" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L61" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M61" s="19"/>
+      <c r="N61" s="18"/>
+      <c r="O61" s="18"/>
+      <c r="P61" s="20"/>
+    </row>
+    <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="21" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C62" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E62" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="F62" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="G62" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H62" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="I62" s="16"/>
+      <c r="J62" s="16"/>
+      <c r="K62" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L62" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M62" s="19"/>
+      <c r="N62" s="18"/>
+      <c r="O62" s="18"/>
+      <c r="P62" s="20"/>
+    </row>
+    <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="21" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="E63" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="F63" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="G63" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H63" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="I63" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="J63" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="K63" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L63" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M63" s="19"/>
+      <c r="N63" s="18"/>
+      <c r="O63" s="18"/>
+      <c r="P63" s="20"/>
+    </row>
+    <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="21" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C64" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="E64" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="F64" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="G64" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H64" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="I64" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="J64" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="K64" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L64" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M64" s="19"/>
+      <c r="N64" s="18"/>
+      <c r="O64" s="18"/>
+      <c r="P64" s="20"/>
+    </row>
+    <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="21" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C65" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D65" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="E65" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="F65" s="21" t="s">
+        <v>316</v>
+      </c>
+      <c r="G65" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H65" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="I65" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="J65" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="K65" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L65" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M65" s="19"/>
+      <c r="N65" s="18"/>
+      <c r="O65" s="18"/>
+      <c r="P65" s="20"/>
+    </row>
+    <row r="66" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="21" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C66" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="E66" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="F66" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="G66" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H66" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="I66" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="J66" s="16"/>
+      <c r="K66" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L66" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M66" s="19"/>
+      <c r="N66" s="18"/>
+      <c r="O66" s="18"/>
+      <c r="P66" s="20"/>
+    </row>
+    <row r="67" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="21" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C67" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D67" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E67" s="22" t="s">
+        <v>324</v>
+      </c>
+      <c r="F67" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="G67" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H67" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="I67" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="J67" s="16"/>
+      <c r="K67" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L67" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M67" s="19"/>
+      <c r="N67" s="18"/>
+      <c r="O67" s="18"/>
+      <c r="P67" s="20"/>
+    </row>
+    <row r="68" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="21" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C68" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E68" s="22" t="s">
+        <v>328</v>
+      </c>
+      <c r="F68" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="G68" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H68" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="I68" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="J68" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="K68" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L68" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M68" s="19"/>
+      <c r="N68" s="18"/>
+      <c r="O68" s="18"/>
+      <c r="P68" s="20"/>
+    </row>
+    <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="21" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C69" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E69" s="22" t="s">
+        <v>333</v>
+      </c>
+      <c r="F69" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="G69" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H69" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="I69" s="17" t="s">
+        <v>336</v>
+      </c>
+      <c r="J69" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="K69" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L69" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M69" s="19"/>
+      <c r="N69" s="18"/>
+      <c r="O69" s="18"/>
+      <c r="P69" s="20"/>
+    </row>
+    <row r="70" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="21" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C70" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E70" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="F70" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="G70" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H70" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="I70" s="17" t="s">
+        <v>341</v>
+      </c>
+      <c r="J70" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="K70" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L70" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M70" s="19"/>
+      <c r="N70" s="18"/>
+      <c r="O70" s="18"/>
+      <c r="P70" s="20"/>
+    </row>
+    <row r="71" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="21" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C71" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E71" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="F71" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="G71" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H71" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="I71" s="17" t="s">
+        <v>346</v>
+      </c>
+      <c r="J71" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="K71" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L71" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M71" s="19"/>
+      <c r="N71" s="18"/>
+      <c r="O71" s="18"/>
+      <c r="P71" s="20"/>
+    </row>
+    <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="21" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C72" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D72" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E72" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="F72" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="G72" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H72" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="I72" s="17" t="s">
+        <v>350</v>
+      </c>
+      <c r="J72" s="16"/>
+      <c r="K72" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L72" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M72" s="19"/>
+      <c r="N72" s="18"/>
+      <c r="O72" s="18"/>
+      <c r="P72" s="20"/>
+    </row>
+    <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="21" t="n">
         <v>72</v>
       </c>
-      <c r="F11" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G11" s="20" t="s">
+      <c r="B73" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C73" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E73" s="22" t="s">
+        <v>351</v>
+      </c>
+      <c r="F73" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="G73" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H73" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="I73" s="17" t="s">
+        <v>354</v>
+      </c>
+      <c r="J73" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="K73" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L73" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M73" s="19"/>
+      <c r="N73" s="18"/>
+      <c r="O73" s="18"/>
+      <c r="P73" s="20"/>
+    </row>
+    <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="21" t="n">
         <v>73</v>
       </c>
-      <c r="H11" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I11" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J11" s="18"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="19"/>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="20" t="n">
+      <c r="B74" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C74" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" s="21" t="s">
+      <c r="D74" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E74" s="22" t="s">
+        <v>356</v>
+      </c>
+      <c r="F74" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="G74" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H74" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="I74" s="17" t="s">
+        <v>359</v>
+      </c>
+      <c r="J74" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="K74" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L74" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M74" s="19"/>
+      <c r="N74" s="18"/>
+      <c r="O74" s="18"/>
+      <c r="P74" s="20"/>
+    </row>
+    <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="21" t="n">
         <v>74</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="B75" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C75" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D75" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E75" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="F75" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="G75" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H75" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="I75" s="17" t="s">
+        <v>364</v>
+      </c>
+      <c r="J75" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="K75" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L75" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M75" s="19"/>
+      <c r="N75" s="18"/>
+      <c r="O75" s="18"/>
+      <c r="P75" s="20"/>
+    </row>
+    <row r="76" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="21" t="n">
         <v>75</v>
       </c>
-      <c r="F12" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G12" s="20" t="s">
+      <c r="B76" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C76" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D76" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E76" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="F76" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="G76" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H76" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="I76" s="17" t="s">
+        <v>369</v>
+      </c>
+      <c r="J76" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="K76" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L76" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M76" s="19"/>
+      <c r="N76" s="18"/>
+      <c r="O76" s="18"/>
+      <c r="P76" s="20"/>
+    </row>
+    <row r="77" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="21" t="n">
         <v>76</v>
       </c>
-      <c r="H12" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I12" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J12" s="18"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="19"/>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="20" t="n">
+      <c r="B77" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C77" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" s="21" t="s">
+      <c r="D77" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E77" s="22" t="s">
+        <v>371</v>
+      </c>
+      <c r="F77" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="G77" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H77" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="I77" s="17" t="s">
+        <v>374</v>
+      </c>
+      <c r="J77" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="K77" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L77" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M77" s="19"/>
+      <c r="N77" s="18"/>
+      <c r="O77" s="18"/>
+      <c r="P77" s="20"/>
+    </row>
+    <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="21" t="n">
         <v>77</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="B78" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C78" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D78" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E78" s="22" t="s">
+        <v>376</v>
+      </c>
+      <c r="F78" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="G78" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H78" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="I78" s="17" t="s">
+        <v>379</v>
+      </c>
+      <c r="J78" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="K78" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L78" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M78" s="19"/>
+      <c r="N78" s="18"/>
+      <c r="O78" s="18"/>
+      <c r="P78" s="20"/>
+    </row>
+    <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="21" t="n">
         <v>78</v>
       </c>
-      <c r="F13" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="20" t="s">
+      <c r="B79" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C79" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D79" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E79" s="22" t="s">
+        <v>381</v>
+      </c>
+      <c r="F79" s="21" t="s">
+        <v>382</v>
+      </c>
+      <c r="G79" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H79" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="I79" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="J79" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="K79" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L79" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M79" s="19"/>
+      <c r="N79" s="18"/>
+      <c r="O79" s="18"/>
+      <c r="P79" s="20"/>
+    </row>
+    <row r="80" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="21" t="n">
         <v>79</v>
       </c>
-      <c r="H13" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I13" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J13" s="18"/>
-      <c r="K13" s="17"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="19"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="20" t="n">
+      <c r="B80" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C80" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="21" t="s">
+      <c r="D80" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E80" s="22" t="s">
+        <v>386</v>
+      </c>
+      <c r="F80" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="G80" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H80" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="I80" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="J80" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="K80" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L80" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M80" s="19"/>
+      <c r="N80" s="18"/>
+      <c r="O80" s="18"/>
+      <c r="P80" s="20"/>
+    </row>
+    <row r="81" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="21" t="n">
         <v>80</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="B81" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C81" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E81" s="22" t="s">
+        <v>391</v>
+      </c>
+      <c r="F81" s="21" t="s">
+        <v>392</v>
+      </c>
+      <c r="G81" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H81" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="I81" s="17" t="s">
+        <v>394</v>
+      </c>
+      <c r="J81" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="K81" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L81" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M81" s="19"/>
+      <c r="N81" s="18"/>
+      <c r="O81" s="18"/>
+      <c r="P81" s="20"/>
+    </row>
+    <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="21" t="n">
         <v>81</v>
       </c>
-      <c r="F14" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" s="20" t="s">
+      <c r="B82" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C82" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E82" s="22" t="s">
+        <v>396</v>
+      </c>
+      <c r="F82" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="G82" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H82" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="I82" s="17" t="s">
+        <v>399</v>
+      </c>
+      <c r="J82" s="16"/>
+      <c r="K82" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L82" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M82" s="19"/>
+      <c r="N82" s="18"/>
+      <c r="O82" s="18"/>
+      <c r="P82" s="20"/>
+    </row>
+    <row r="83" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="21" t="n">
         <v>82</v>
       </c>
-      <c r="H14" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I14" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J14" s="18"/>
-      <c r="K14" s="17"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="19"/>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="20" t="n">
+      <c r="B83" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C83" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="D83" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="E83" s="22" t="s">
+        <v>401</v>
+      </c>
+      <c r="F83" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="G83" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H83" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="I83" s="17" t="s">
+        <v>404</v>
+      </c>
+      <c r="J83" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="K83" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L83" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M83" s="19"/>
+      <c r="N83" s="18"/>
+      <c r="O83" s="18"/>
+      <c r="P83" s="20"/>
+    </row>
+    <row r="84" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="21" t="n">
         <v>83</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="B84" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C84" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D84" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="E84" s="22" t="s">
+        <v>406</v>
+      </c>
+      <c r="F84" s="21" t="s">
+        <v>407</v>
+      </c>
+      <c r="G84" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H84" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="I84" s="17" t="s">
+        <v>409</v>
+      </c>
+      <c r="J84" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="K84" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L84" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M84" s="19"/>
+      <c r="N84" s="18"/>
+      <c r="O84" s="18"/>
+      <c r="P84" s="20"/>
+    </row>
+    <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="21" t="n">
         <v>84</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="B85" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C85" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D85" s="21" t="s">
+        <v>411</v>
+      </c>
+      <c r="E85" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="F85" s="21" t="s">
+        <v>413</v>
+      </c>
+      <c r="G85" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H85" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="I85" s="17" t="s">
+        <v>415</v>
+      </c>
+      <c r="J85" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="K85" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L85" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M85" s="19"/>
+      <c r="N85" s="18"/>
+      <c r="O85" s="18"/>
+      <c r="P85" s="20"/>
+    </row>
+    <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="16" t="n">
         <v>85</v>
       </c>
-      <c r="F15" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="G15" s="20" t="s">
+      <c r="B86" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C86" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D86" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="E86" s="23" t="s">
+        <v>417</v>
+      </c>
+      <c r="F86" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="G86" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H86" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="I86" s="16"/>
+      <c r="J86" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="K86" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L86" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M86" s="19"/>
+      <c r="N86" s="18"/>
+      <c r="O86" s="18"/>
+      <c r="P86" s="20"/>
+    </row>
+    <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="16" t="n">
         <v>86</v>
       </c>
-      <c r="H15" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I15" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J15" s="18"/>
-      <c r="K15" s="17"/>
-      <c r="L15" s="17"/>
-      <c r="M15" s="19"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D16" s="21" t="s">
+      <c r="B87" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C87" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D87" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E87" s="23" t="s">
+        <v>421</v>
+      </c>
+      <c r="F87" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="G87" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H87" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="I87" s="17" t="s">
+        <v>424</v>
+      </c>
+      <c r="J87" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="K87" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L87" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M87" s="19"/>
+      <c r="N87" s="18"/>
+      <c r="O87" s="18"/>
+      <c r="P87" s="20"/>
+    </row>
+    <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="16" t="n">
         <v>87</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="B88" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C88" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D88" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E88" s="23" t="s">
+        <v>426</v>
+      </c>
+      <c r="F88" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="G88" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H88" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="I88" s="17" t="s">
+        <v>429</v>
+      </c>
+      <c r="J88" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="K88" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L88" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M88" s="19"/>
+      <c r="N88" s="18"/>
+      <c r="O88" s="18"/>
+      <c r="P88" s="20"/>
+    </row>
+    <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="16" t="n">
         <v>88</v>
       </c>
-      <c r="F16" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16" s="20" t="s">
+      <c r="B89" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C89" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D89" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E89" s="23" t="s">
+        <v>431</v>
+      </c>
+      <c r="F89" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="G89" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H89" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="I89" s="17" t="s">
+        <v>434</v>
+      </c>
+      <c r="J89" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="K89" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L89" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M89" s="19"/>
+      <c r="N89" s="18"/>
+      <c r="O89" s="18"/>
+      <c r="P89" s="20"/>
+    </row>
+    <row r="90" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="16" t="n">
         <v>89</v>
       </c>
-      <c r="H16" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I16" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J16" s="18"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="19"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="21" t="s">
+      <c r="B90" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C90" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D90" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E90" s="23" t="s">
+        <v>436</v>
+      </c>
+      <c r="F90" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="G90" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H90" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="I90" s="16"/>
+      <c r="J90" s="16"/>
+      <c r="K90" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L90" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M90" s="19"/>
+      <c r="N90" s="18"/>
+      <c r="O90" s="18"/>
+      <c r="P90" s="20"/>
+    </row>
+    <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="16" t="n">
         <v>90</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="B91" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C91" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D91" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E91" s="23" t="s">
+        <v>438</v>
+      </c>
+      <c r="F91" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="G91" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H91" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="I91" s="17" t="s">
+        <v>441</v>
+      </c>
+      <c r="J91" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="K91" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L91" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M91" s="19"/>
+      <c r="N91" s="18"/>
+      <c r="O91" s="18"/>
+      <c r="P91" s="20"/>
+    </row>
+    <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="16" t="n">
         <v>91</v>
       </c>
-      <c r="F17" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G17" s="20" t="s">
+      <c r="B92" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C92" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D92" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E92" s="23" t="s">
+        <v>443</v>
+      </c>
+      <c r="F92" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="G92" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H92" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="I92" s="17" t="s">
+        <v>446</v>
+      </c>
+      <c r="J92" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="K92" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L92" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M92" s="19"/>
+      <c r="N92" s="18"/>
+      <c r="O92" s="18"/>
+      <c r="P92" s="20"/>
+    </row>
+    <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="16" t="n">
         <v>92</v>
       </c>
-      <c r="H17" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I17" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J17" s="18"/>
-      <c r="K17" s="17"/>
-      <c r="L17" s="17"/>
-      <c r="M17" s="19"/>
-    </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="C18" s="20" t="s">
+      <c r="B93" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C93" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E93" s="23" t="s">
+        <v>448</v>
+      </c>
+      <c r="F93" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="G93" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H93" s="16" t="s">
+        <v>449</v>
+      </c>
+      <c r="I93" s="16"/>
+      <c r="J93" s="16"/>
+      <c r="K93" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L93" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M93" s="19"/>
+      <c r="N93" s="18"/>
+      <c r="O93" s="18"/>
+      <c r="P93" s="20"/>
+    </row>
+    <row r="94" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="16" t="n">
         <v>93</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="B94" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C94" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D94" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E94" s="23" t="s">
+        <v>450</v>
+      </c>
+      <c r="F94" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="G94" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H94" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="I94" s="17" t="s">
+        <v>453</v>
+      </c>
+      <c r="J94" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="K94" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L94" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M94" s="19"/>
+      <c r="N94" s="18"/>
+      <c r="O94" s="18"/>
+      <c r="P94" s="20"/>
+    </row>
+    <row r="95" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="16" t="n">
         <v>94</v>
       </c>
-      <c r="E18" s="20" t="s">
+      <c r="B95" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C95" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D95" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E95" s="23" t="s">
+        <v>455</v>
+      </c>
+      <c r="F95" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="G95" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H95" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="I95" s="16"/>
+      <c r="J95" s="16"/>
+      <c r="K95" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L95" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M95" s="19"/>
+      <c r="N95" s="18"/>
+      <c r="O95" s="18"/>
+      <c r="P95" s="20"/>
+    </row>
+    <row r="96" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="16" t="n">
         <v>95</v>
       </c>
-      <c r="F18" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18" s="20" t="s">
+      <c r="B96" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C96" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D96" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E96" s="23" t="s">
+        <v>457</v>
+      </c>
+      <c r="F96" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="G96" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H96" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="I96" s="17" t="s">
+        <v>460</v>
+      </c>
+      <c r="J96" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="K96" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L96" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M96" s="19"/>
+      <c r="N96" s="18"/>
+      <c r="O96" s="18"/>
+      <c r="P96" s="20"/>
+    </row>
+    <row r="97" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="16" t="n">
         <v>96</v>
       </c>
-      <c r="H18" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I18" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J18" s="18"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="19"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="21" t="s">
+      <c r="B97" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C97" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D97" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E97" s="23" t="s">
+        <v>462</v>
+      </c>
+      <c r="F97" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="G97" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H97" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="I97" s="16"/>
+      <c r="J97" s="16"/>
+      <c r="K97" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L97" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M97" s="19"/>
+      <c r="N97" s="18"/>
+      <c r="O97" s="18"/>
+      <c r="P97" s="20"/>
+    </row>
+    <row r="98" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="16" t="n">
         <v>97</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="B98" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C98" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D98" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="E98" s="23" t="s">
+        <v>465</v>
+      </c>
+      <c r="F98" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="G98" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H98" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="I98" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="J98" s="16" t="s">
+        <v>469</v>
+      </c>
+      <c r="K98" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L98" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M98" s="19"/>
+      <c r="N98" s="18"/>
+      <c r="O98" s="18"/>
+      <c r="P98" s="20"/>
+    </row>
+    <row r="99" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="16" t="n">
         <v>98</v>
       </c>
-      <c r="F19" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G19" s="20" t="s">
+      <c r="B99" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C99" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D99" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="E99" s="23" t="s">
+        <v>470</v>
+      </c>
+      <c r="F99" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="G99" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H99" s="16" t="s">
+        <v>471</v>
+      </c>
+      <c r="I99" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="J99" s="16" t="s">
+        <v>473</v>
+      </c>
+      <c r="K99" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L99" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M99" s="19"/>
+      <c r="N99" s="18"/>
+      <c r="O99" s="18"/>
+      <c r="P99" s="20"/>
+    </row>
+    <row r="100" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="16" t="n">
         <v>99</v>
       </c>
-      <c r="H19" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I19" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J19" s="18"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="19"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="C20" s="20" t="s">
+      <c r="B100" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C100" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D100" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="E100" s="23" t="s">
+        <v>474</v>
+      </c>
+      <c r="F100" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="G100" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H100" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="I100" s="17" t="s">
+        <v>476</v>
+      </c>
+      <c r="J100" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="K100" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L100" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M100" s="19"/>
+      <c r="N100" s="18"/>
+      <c r="O100" s="18"/>
+      <c r="P100" s="20"/>
+    </row>
+    <row r="101" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="B101" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C101" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D101" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="E101" s="23" t="s">
+        <v>478</v>
+      </c>
+      <c r="F101" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="G101" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H101" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="I101" s="16"/>
+      <c r="J101" s="16"/>
+      <c r="K101" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L101" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M101" s="19"/>
+      <c r="N101" s="18"/>
+      <c r="O101" s="18"/>
+      <c r="P101" s="20"/>
+    </row>
+    <row r="102" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="16" t="n">
         <v>101</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="B102" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C102" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D102" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="E102" s="23" t="s">
+        <v>480</v>
+      </c>
+      <c r="F102" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="G102" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H102" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="I102" s="17" t="s">
+        <v>482</v>
+      </c>
+      <c r="J102" s="16"/>
+      <c r="K102" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L102" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M102" s="19"/>
+      <c r="N102" s="18"/>
+      <c r="O102" s="18"/>
+      <c r="P102" s="20"/>
+    </row>
+    <row r="103" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="16" t="n">
         <v>102</v>
       </c>
-      <c r="F20" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G20" s="20" t="s">
+      <c r="B103" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C103" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D103" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E103" s="23" t="s">
+        <v>483</v>
+      </c>
+      <c r="F103" s="16" t="s">
+        <v>484</v>
+      </c>
+      <c r="G103" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H103" s="16" t="s">
+        <v>485</v>
+      </c>
+      <c r="I103" s="16"/>
+      <c r="J103" s="16" t="s">
+        <v>486</v>
+      </c>
+      <c r="K103" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L103" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M103" s="19"/>
+      <c r="N103" s="18"/>
+      <c r="O103" s="18"/>
+      <c r="P103" s="20"/>
+    </row>
+    <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="16" t="n">
         <v>103</v>
       </c>
-      <c r="H20" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I20" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J20" s="18"/>
-      <c r="K20" s="17"/>
-      <c r="L20" s="17"/>
-      <c r="M20" s="19"/>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="21" t="s">
+      <c r="B104" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C104" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D104" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E104" s="23" t="s">
+        <v>487</v>
+      </c>
+      <c r="F104" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="G104" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H104" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="I104" s="17" t="s">
+        <v>489</v>
+      </c>
+      <c r="J104" s="16" t="s">
+        <v>490</v>
+      </c>
+      <c r="K104" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L104" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M104" s="19"/>
+      <c r="N104" s="18"/>
+      <c r="O104" s="18"/>
+      <c r="P104" s="20"/>
+    </row>
+    <row r="105" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="16" t="n">
         <v>104</v>
       </c>
-      <c r="E21" s="20" t="s">
+      <c r="B105" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C105" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D105" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E105" s="23" t="s">
+        <v>491</v>
+      </c>
+      <c r="F105" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="G105" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H105" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="I105" s="16"/>
+      <c r="J105" s="16"/>
+      <c r="K105" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L105" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M105" s="19"/>
+      <c r="N105" s="18"/>
+      <c r="O105" s="18"/>
+      <c r="P105" s="20"/>
+    </row>
+    <row r="106" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="16" t="n">
         <v>105</v>
       </c>
-      <c r="F21" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="G21" s="20" t="s">
+      <c r="B106" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C106" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D106" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E106" s="23" t="s">
+        <v>494</v>
+      </c>
+      <c r="F106" s="16" t="s">
+        <v>495</v>
+      </c>
+      <c r="G106" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H106" s="16" t="s">
+        <v>496</v>
+      </c>
+      <c r="I106" s="16"/>
+      <c r="J106" s="16"/>
+      <c r="K106" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L106" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M106" s="19"/>
+      <c r="N106" s="18"/>
+      <c r="O106" s="18"/>
+      <c r="P106" s="20"/>
+    </row>
+    <row r="107" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="16" t="n">
         <v>106</v>
       </c>
-      <c r="H21" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I21" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J21" s="18"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="19"/>
-    </row>
-    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="22" t="n">
+      <c r="B107" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C107" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="D107" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="E107" s="23" t="s">
+        <v>497</v>
+      </c>
+      <c r="F107" s="16" t="s">
+        <v>498</v>
+      </c>
+      <c r="G107" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H107" s="16" t="s">
+        <v>499</v>
+      </c>
+      <c r="I107" s="17" t="s">
+        <v>500</v>
+      </c>
+      <c r="J107" s="16" t="s">
+        <v>501</v>
+      </c>
+      <c r="K107" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L107" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M107" s="19"/>
+      <c r="N107" s="18"/>
+      <c r="O107" s="18"/>
+      <c r="P107" s="20"/>
+    </row>
+    <row r="108" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="16" t="n">
         <v>107</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="B108" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C108" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D108" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="E108" s="23" t="s">
+        <v>502</v>
+      </c>
+      <c r="F108" s="16" t="s">
+        <v>402</v>
+      </c>
+      <c r="G108" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H108" s="16" t="s">
+        <v>503</v>
+      </c>
+      <c r="I108" s="16"/>
+      <c r="J108" s="16"/>
+      <c r="K108" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L108" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M108" s="19"/>
+      <c r="N108" s="18"/>
+      <c r="O108" s="18"/>
+      <c r="P108" s="20"/>
+    </row>
+    <row r="109" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="16" t="n">
         <v>108</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="B109" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C109" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D109" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="E109" s="23" t="s">
+        <v>504</v>
+      </c>
+      <c r="F109" s="16" t="s">
+        <v>505</v>
+      </c>
+      <c r="G109" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H109" s="16" t="s">
+        <v>506</v>
+      </c>
+      <c r="I109" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="J109" s="16" t="s">
+        <v>508</v>
+      </c>
+      <c r="K109" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L109" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M109" s="19"/>
+      <c r="N109" s="18"/>
+      <c r="O109" s="18"/>
+      <c r="P109" s="20"/>
+    </row>
+    <row r="110" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="16" t="n">
         <v>109</v>
       </c>
-      <c r="F22" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" s="22" t="s">
+      <c r="B110" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C110" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D110" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="E110" s="23" t="s">
+        <v>509</v>
+      </c>
+      <c r="F110" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="G110" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H110" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="I110" s="16"/>
+      <c r="J110" s="16" t="s">
+        <v>511</v>
+      </c>
+      <c r="K110" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L110" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M110" s="19"/>
+      <c r="N110" s="18"/>
+      <c r="O110" s="18"/>
+      <c r="P110" s="20"/>
+    </row>
+    <row r="111" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="16" t="n">
         <v>110</v>
       </c>
-      <c r="H22" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I22" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J22" s="18"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="19"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="22" t="n">
+      <c r="B111" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C111" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C23" s="22" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" s="23" t="s">
+      <c r="D111" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="E111" s="23" t="s">
+        <v>512</v>
+      </c>
+      <c r="F111" s="16" t="s">
+        <v>513</v>
+      </c>
+      <c r="G111" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H111" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="I111" s="17" t="s">
+        <v>515</v>
+      </c>
+      <c r="J111" s="16" t="s">
+        <v>516</v>
+      </c>
+      <c r="K111" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L111" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M111" s="19"/>
+      <c r="N111" s="18"/>
+      <c r="O111" s="18"/>
+      <c r="P111" s="20"/>
+    </row>
+    <row r="112" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="16" t="n">
         <v>111</v>
       </c>
-      <c r="E23" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="F23" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="G23" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="H23" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="I23" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="J23" s="18"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="19"/>
+      <c r="B112" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C112" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D112" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="E112" s="23" t="s">
+        <v>517</v>
+      </c>
+      <c r="F112" s="16" t="s">
+        <v>402</v>
+      </c>
+      <c r="G112" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H112" s="16" t="s">
+        <v>518</v>
+      </c>
+      <c r="I112" s="17" t="s">
+        <v>519</v>
+      </c>
+      <c r="J112" s="16" t="s">
+        <v>520</v>
+      </c>
+      <c r="K112" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L112" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M112" s="19"/>
+      <c r="N112" s="18"/>
+      <c r="O112" s="18"/>
+      <c r="P112" s="20"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M23"/>
+  <autoFilter ref="A1:P112"/>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" error="Choisissez un statut dans la liste." errorStyle="stop" errorTitle="Statut" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I200" type="list">
+    <dataValidation allowBlank="true" error="Choisissez un statut dans la liste." errorStyle="stop" errorTitle="Statut" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L2:L400" type="list">
       <formula1>"À contacter,Contacté,Intéressé,Échantillon / visite,Devis envoyé,Vendu,Pas intéressé"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M200" type="decimal">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P400" type="decimal">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId2" display="Voir la fiche"/>
-    <hyperlink ref="H3" r:id="rId3" display="Voir la fiche"/>
-    <hyperlink ref="H4" r:id="rId4" display="Voir la fiche"/>
-    <hyperlink ref="H5" r:id="rId5" display="Voir la fiche"/>
-    <hyperlink ref="H6" r:id="rId6" display="Voir la fiche"/>
-    <hyperlink ref="H7" r:id="rId7" display="Voir la fiche"/>
-    <hyperlink ref="H8" r:id="rId8" display="Voir la fiche"/>
-    <hyperlink ref="H9" r:id="rId9" display="Voir la fiche"/>
-    <hyperlink ref="H10" r:id="rId10" display="Voir la fiche"/>
-    <hyperlink ref="H11" r:id="rId11" display="Voir la fiche"/>
-    <hyperlink ref="H12" r:id="rId12" display="Voir la fiche"/>
-    <hyperlink ref="H13" r:id="rId13" display="Voir la fiche"/>
-    <hyperlink ref="H14" r:id="rId14" display="Voir la fiche"/>
-    <hyperlink ref="H15" r:id="rId15" display="Voir la fiche"/>
-    <hyperlink ref="H16" r:id="rId16" display="Voir la fiche"/>
-    <hyperlink ref="H17" r:id="rId17" display="Voir la fiche"/>
-    <hyperlink ref="H18" r:id="rId18" display="Voir la fiche"/>
-    <hyperlink ref="H19" r:id="rId19" display="Voir la fiche"/>
-    <hyperlink ref="H20" r:id="rId20" display="Voir la fiche"/>
-    <hyperlink ref="H21" r:id="rId21" display="Voir la fiche"/>
-    <hyperlink ref="H22" r:id="rId22" display="Voir la fiche"/>
-    <hyperlink ref="H23" r:id="rId23" display="Voir la fiche"/>
+    <hyperlink ref="K2" r:id="rId2" display="Voir"/>
+    <hyperlink ref="K3" r:id="rId3" display="Voir"/>
+    <hyperlink ref="K4" r:id="rId4" display="Voir"/>
+    <hyperlink ref="K5" r:id="rId5" display="Voir"/>
+    <hyperlink ref="K6" r:id="rId6" display="Voir"/>
+    <hyperlink ref="K7" r:id="rId7" display="Voir"/>
+    <hyperlink ref="K8" r:id="rId8" display="Voir"/>
+    <hyperlink ref="K9" r:id="rId9" display="Voir"/>
+    <hyperlink ref="K10" r:id="rId10" display="Voir"/>
+    <hyperlink ref="K11" r:id="rId11" display="Voir"/>
+    <hyperlink ref="K12" r:id="rId12" display="Voir"/>
+    <hyperlink ref="K13" r:id="rId13" display="Voir"/>
+    <hyperlink ref="K14" r:id="rId14" display="Voir"/>
+    <hyperlink ref="K15" r:id="rId15" display="Voir"/>
+    <hyperlink ref="K16" r:id="rId16" display="Voir"/>
+    <hyperlink ref="K17" r:id="rId17" display="Voir"/>
+    <hyperlink ref="K18" r:id="rId18" display="Voir"/>
+    <hyperlink ref="K19" r:id="rId19" display="Voir"/>
+    <hyperlink ref="K20" r:id="rId20" display="Voir"/>
+    <hyperlink ref="K21" r:id="rId21" display="Voir"/>
+    <hyperlink ref="K22" r:id="rId22" display="Voir"/>
+    <hyperlink ref="K23" r:id="rId23" display="Voir"/>
+    <hyperlink ref="I24" r:id="rId24" display="www.carrelage-roger.com"/>
+    <hyperlink ref="K24" r:id="rId25" display="Voir"/>
+    <hyperlink ref="I25" r:id="rId26" display="negoce.france-materiaux.fr/369-societe-nouvelle-nmc"/>
+    <hyperlink ref="K25" r:id="rId27" display="Voir"/>
+    <hyperlink ref="I26" r:id="rId28" display="www.carrelage-design-95.fr"/>
+    <hyperlink ref="K26" r:id="rId29" display="Voir"/>
+    <hyperlink ref="I27" r:id="rId30" display="www.palatino.fr"/>
+    <hyperlink ref="K27" r:id="rId31" display="Voir"/>
+    <hyperlink ref="I28" r:id="rId32" display="www.parquet-carrelage.com"/>
+    <hyperlink ref="K28" r:id="rId33" display="Voir"/>
+    <hyperlink ref="I29" r:id="rId34" display="www.mdy-france.com"/>
+    <hyperlink ref="K29" r:id="rId35" display="Voir"/>
+    <hyperlink ref="I30" r:id="rId36" display="www.pmc-marbrerie.com"/>
+    <hyperlink ref="K30" r:id="rId37" display="Voir"/>
+    <hyperlink ref="I31" r:id="rId38" display="coignieres.mondial-piscine.eu"/>
+    <hyperlink ref="K31" r:id="rId39" display="Voir"/>
+    <hyperlink ref="I32" r:id="rId40" display="lemondedesjardins.fr"/>
+    <hyperlink ref="K32" r:id="rId41" display="Voir"/>
+    <hyperlink ref="I33" r:id="rId42" display="www.sauvaje.fr"/>
+    <hyperlink ref="K33" r:id="rId43" display="Voir"/>
+    <hyperlink ref="I34" r:id="rId44" display="magasins.bigmat.fr/normandie/eure/evreux/bigmat-evreux-mvr-materiaux-144"/>
+    <hyperlink ref="K34" r:id="rId45" display="Voir"/>
+    <hyperlink ref="I35" r:id="rId46" display="www.lemondedelapierre.fr"/>
+    <hyperlink ref="K35" r:id="rId47" display="Voir"/>
+    <hyperlink ref="I36" r:id="rId48" display="www.pillaud-materiaux.com"/>
+    <hyperlink ref="K36" r:id="rId49" display="Voir"/>
+    <hyperlink ref="I37" r:id="rId50" display="www.torchio.fr"/>
+    <hyperlink ref="K37" r:id="rId51" display="Voir"/>
+    <hyperlink ref="I38" r:id="rId52" display="www.baticentre.fr"/>
+    <hyperlink ref="K38" r:id="rId53" display="Voir"/>
+    <hyperlink ref="I39" r:id="rId54" display="www.ceramica.fr"/>
+    <hyperlink ref="K39" r:id="rId55" display="Voir"/>
+    <hyperlink ref="I40" r:id="rId56" display="www.triomphe-home.fr"/>
+    <hyperlink ref="K40" r:id="rId57" display="Voir"/>
+    <hyperlink ref="I41" r:id="rId58" display="www.marbreriempg.paris"/>
+    <hyperlink ref="K41" r:id="rId59" display="Voir"/>
+    <hyperlink ref="I42" r:id="rId60" display="planstone.fr"/>
+    <hyperlink ref="K42" r:id="rId61" display="Voir"/>
+    <hyperlink ref="I43" r:id="rId62" display="aquagarden78.fr"/>
+    <hyperlink ref="K43" r:id="rId63" display="Voir"/>
+    <hyperlink ref="I44" r:id="rId64" display="www.idoine-piscines.com"/>
+    <hyperlink ref="K44" r:id="rId65" display="Voir"/>
+    <hyperlink ref="I45" r:id="rId66" display="www.idealpiscine.com"/>
+    <hyperlink ref="K45" r:id="rId67" display="Voir"/>
+    <hyperlink ref="I46" r:id="rId68" display="www.kristech.fr"/>
+    <hyperlink ref="K46" r:id="rId69" display="Voir"/>
+    <hyperlink ref="I47" r:id="rId70" display="www.la-boutique-piscine-spa.fr"/>
+    <hyperlink ref="K47" r:id="rId71" display="Voir"/>
+    <hyperlink ref="I48" r:id="rId72" display="www.piscines-spas-iledefrance.fr"/>
+    <hyperlink ref="K48" r:id="rId73" display="Voir"/>
+    <hyperlink ref="I49" r:id="rId74" display="www.socorebat-95.fr"/>
+    <hyperlink ref="K49" r:id="rId75" display="Voir"/>
+    <hyperlink ref="I50" r:id="rId76" display="agavepaysage.fr"/>
+    <hyperlink ref="K50" r:id="rId77" display="Voir"/>
+    <hyperlink ref="I51" r:id="rId78" display="www.apisflorae.com"/>
+    <hyperlink ref="K51" r:id="rId79" display="Voir"/>
+    <hyperlink ref="I52" r:id="rId80" display="www.artdesjardins-zory.fr"/>
+    <hyperlink ref="K52" r:id="rId81" display="Voir"/>
+    <hyperlink ref="I53" r:id="rId82" display="www.atelier-concept-paysage.com"/>
+    <hyperlink ref="K53" r:id="rId83" display="Voir"/>
+    <hyperlink ref="I54" r:id="rId84" display="edenvatinel.fr"/>
+    <hyperlink ref="K54" r:id="rId85" display="Voir"/>
+    <hyperlink ref="I55" r:id="rId86" display="www.fontainepaysage.fr"/>
+    <hyperlink ref="K55" r:id="rId87" display="Voir"/>
+    <hyperlink ref="I56" r:id="rId88" display="l-esprit-au-vert-71b05.houzzsite.com"/>
+    <hyperlink ref="K56" r:id="rId89" display="Voir"/>
+    <hyperlink ref="I57" r:id="rId90" display="www.jardinsdejulien.com"/>
+    <hyperlink ref="K57" r:id="rId91" display="Voir"/>
+    <hyperlink ref="I58" r:id="rId92" display="www.jardinsdelavallee.fr"/>
+    <hyperlink ref="K58" r:id="rId93" display="Voir"/>
+    <hyperlink ref="I59" r:id="rId94" display="www.penseeaujardin.fr"/>
+    <hyperlink ref="K59" r:id="rId95" display="Voir"/>
+    <hyperlink ref="I60" r:id="rId96" display="terrasseetjardindeparis.com"/>
+    <hyperlink ref="K60" r:id="rId97" display="Voir"/>
+    <hyperlink ref="I61" r:id="rId98" display="www.carrelage-marbre-iledefrance.fr"/>
+    <hyperlink ref="K61" r:id="rId99" display="Voir"/>
+    <hyperlink ref="K62" r:id="rId100" display="Voir"/>
+    <hyperlink ref="I63" r:id="rId101" display="www.kenny-entreprise.fr"/>
+    <hyperlink ref="K63" r:id="rId102" display="Voir"/>
+    <hyperlink ref="I64" r:id="rId103" display="modernworks.fr"/>
+    <hyperlink ref="K64" r:id="rId104" display="Voir"/>
+    <hyperlink ref="I65" r:id="rId105" display="www.wildrenovation.fr"/>
+    <hyperlink ref="K65" r:id="rId106" display="Voir"/>
+    <hyperlink ref="I66" r:id="rId107" display="mmnk.fr"/>
+    <hyperlink ref="K66" r:id="rId108" display="Voir"/>
+    <hyperlink ref="I67" r:id="rId109" display="www.frazzi.fr"/>
+    <hyperlink ref="K67" r:id="rId110" display="Voir"/>
+    <hyperlink ref="I68" r:id="rId111" display="www.maillard.fr/magasins"/>
+    <hyperlink ref="K68" r:id="rId112" display="Voir"/>
+    <hyperlink ref="I69" r:id="rId113" display="www.muretsol.fr"/>
+    <hyperlink ref="K69" r:id="rId114" display="Voir"/>
+    <hyperlink ref="I70" r:id="rId115" display="atelierdelapierremarbreetgranits.site-solocal.com"/>
+    <hyperlink ref="K70" r:id="rId116" display="Voir"/>
+    <hyperlink ref="I71" r:id="rId117" display="granits-materiaux.fr"/>
+    <hyperlink ref="K71" r:id="rId118" display="Voir"/>
+    <hyperlink ref="I72" r:id="rId119" display="www.la-roche-taillee.fr"/>
+    <hyperlink ref="K72" r:id="rId120" display="Voir"/>
+    <hyperlink ref="I73" r:id="rId121" display="www.marbresettendances.com"/>
+    <hyperlink ref="K73" r:id="rId122" display="Voir"/>
+    <hyperlink ref="I74" r:id="rId123" display="www.bohinjardin.fr"/>
+    <hyperlink ref="K74" r:id="rId124" display="Voir"/>
+    <hyperlink ref="I75" r:id="rId125" display="www.piscines-delalande.fr"/>
+    <hyperlink ref="K75" r:id="rId126" display="Voir"/>
+    <hyperlink ref="I76" r:id="rId127" display="www.jardinpassions.fr"/>
+    <hyperlink ref="K76" r:id="rId128" display="Voir"/>
+    <hyperlink ref="I77" r:id="rId129" display="www.larcher.fr"/>
+    <hyperlink ref="K77" r:id="rId130" display="Voir"/>
+    <hyperlink ref="I78" r:id="rId131" display="www.lespiscinesmoreau.com"/>
+    <hyperlink ref="K78" r:id="rId132" display="Voir"/>
+    <hyperlink ref="I79" r:id="rId133" display="www.piscines-de-france.fr/piscinistes/pisciniste-le-havre"/>
+    <hyperlink ref="K79" r:id="rId134" display="Voir"/>
+    <hyperlink ref="I80" r:id="rId135" display="www.piscinesetabrisnordouest.fr"/>
+    <hyperlink ref="K80" r:id="rId136" display="Voir"/>
+    <hyperlink ref="I81" r:id="rId137" display="barbedettepaysage.fr"/>
+    <hyperlink ref="K81" r:id="rId138" display="Voir"/>
+    <hyperlink ref="I82" r:id="rId139" display="www.rpay.fr"/>
+    <hyperlink ref="K82" r:id="rId140" display="Voir"/>
+    <hyperlink ref="I83" r:id="rId141" display="www.arcytis.com"/>
+    <hyperlink ref="K83" r:id="rId142" display="Voir"/>
+    <hyperlink ref="I84" r:id="rId143" display="www.hemon-architectes.com"/>
+    <hyperlink ref="K84" r:id="rId144" display="Voir"/>
+    <hyperlink ref="I85" r:id="rId145" display="www.conceptinterieurdeauville.com"/>
+    <hyperlink ref="K85" r:id="rId146" display="Voir"/>
+    <hyperlink ref="K86" r:id="rId147" display="Voir"/>
+    <hyperlink ref="I87" r:id="rId148" display="real-marbre.com"/>
+    <hyperlink ref="K87" r:id="rId149" display="Voir"/>
+    <hyperlink ref="I88" r:id="rId150" display="www.aqua-system.fr"/>
+    <hyperlink ref="K88" r:id="rId151" display="Voir"/>
+    <hyperlink ref="I89" r:id="rId152" display="www.ops-ouestpiscines.fr"/>
+    <hyperlink ref="K89" r:id="rId153" display="Voir"/>
+    <hyperlink ref="K90" r:id="rId154" display="Voir"/>
+    <hyperlink ref="I91" r:id="rId155" display="balcoon.fr"/>
+    <hyperlink ref="K91" r:id="rId156" display="Voir"/>
+    <hyperlink ref="I92" r:id="rId157" display="www.jardinsdelorangerie.com/jardins-orangerie-montmorency"/>
+    <hyperlink ref="K92" r:id="rId158" display="Voir"/>
+    <hyperlink ref="K93" r:id="rId159" display="Voir"/>
+    <hyperlink ref="I94" r:id="rId160" display="www.simonsonlandscape.com"/>
+    <hyperlink ref="K94" r:id="rId161" display="Voir"/>
+    <hyperlink ref="K95" r:id="rId162" display="Voir"/>
+    <hyperlink ref="I96" r:id="rId163" display="www.terrassesdesoliviers.com"/>
+    <hyperlink ref="K96" r:id="rId164" display="Voir"/>
+    <hyperlink ref="K97" r:id="rId165" display="Voir"/>
+    <hyperlink ref="I98" r:id="rId166" display="www.belmard-batiment.fr"/>
+    <hyperlink ref="K98" r:id="rId167" display="Voir"/>
+    <hyperlink ref="I99" r:id="rId168" display="www.franpierre-herblay.fr"/>
+    <hyperlink ref="K99" r:id="rId169" display="Voir"/>
+    <hyperlink ref="I100" r:id="rId170" display="www.atelierceben.com"/>
+    <hyperlink ref="K100" r:id="rId171" display="Voir"/>
+    <hyperlink ref="K101" r:id="rId172" display="Voir"/>
+    <hyperlink ref="I102" r:id="rId173" display="www.mersi-architecture.com"/>
+    <hyperlink ref="K102" r:id="rId174" display="Voir"/>
+    <hyperlink ref="K103" r:id="rId175" display="Voir"/>
+    <hyperlink ref="I104" r:id="rId176" display="rouen.mondial-piscine.eu"/>
+    <hyperlink ref="K104" r:id="rId177" display="Voir"/>
+    <hyperlink ref="K105" r:id="rId178" display="Voir"/>
+    <hyperlink ref="K106" r:id="rId179" display="Voir"/>
+    <hyperlink ref="I107" r:id="rId180" display="laurencevermontdecoration.fr"/>
+    <hyperlink ref="K107" r:id="rId181" display="Voir"/>
+    <hyperlink ref="K108" r:id="rId182" display="Voir"/>
+    <hyperlink ref="I109" r:id="rId183" display="abdecoration.fr"/>
+    <hyperlink ref="K109" r:id="rId184" display="Voir"/>
+    <hyperlink ref="K110" r:id="rId185" display="Voir"/>
+    <hyperlink ref="I111" r:id="rId186" display="ynspir.com"/>
+    <hyperlink ref="K111" r:id="rId187" display="Voir"/>
+    <hyperlink ref="I112" r:id="rId188" display="www.act-mo.fr"/>
+    <hyperlink ref="K112" r:id="rId189" display="Voir"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2164,8 +7858,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId24"/>
-  <legacyDrawing r:id="rId25"/>
+  <drawing r:id="rId190"/>
+  <legacyDrawing r:id="rId191"/>
 </worksheet>
 </file>
 
@@ -2174,133 +7868,1142 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
-        <v>113</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>114</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>116</v>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="13" t="s">
+        <v>521</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>522</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>523</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>524</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>525</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>526</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>527</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="23" t="s">
+        <v>529</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>530</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>531</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>532</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>533</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>534</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H2" s="19"/>
+    </row>
+    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="23" t="s">
+        <v>536</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>537</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>538</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>540</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="G3" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H3" s="19"/>
+    </row>
+    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="23" t="s">
+        <v>542</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>537</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>543</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>545</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>546</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H4" s="19"/>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="23" t="s">
+        <v>547</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>537</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>548</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>550</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>551</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H5" s="19"/>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="23" t="s">
+        <v>552</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>530</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>553</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>532</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>554</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>555</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H6" s="19"/>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="23" t="s">
+        <v>556</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>558</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>559</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>560</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>561</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H7" s="19"/>
+    </row>
+    <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="23" t="s">
+        <v>562</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>557</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>563</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>564</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>565</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="G8" s="16"/>
+      <c r="H8" s="19"/>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="23" t="s">
+        <v>566</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>568</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>570</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H9" s="19"/>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="23" t="s">
+        <v>571</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>568</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>572</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H10" s="19"/>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="23" t="s">
+        <v>573</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>568</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H11" s="19"/>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="23" t="s">
+        <v>575</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>568</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>576</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H12" s="19"/>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="23" t="s">
+        <v>577</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>578</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>579</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H13" s="19"/>
+    </row>
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="23" t="s">
+        <v>580</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>581</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>582</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H14" s="19"/>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="23" t="s">
+        <v>583</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>567</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>584</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>585</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H15" s="19"/>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="23" t="s">
+        <v>586</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>587</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>588</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>569</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>589</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>541</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H16" s="19"/>
+    </row>
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="23" t="s">
+        <v>590</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>591</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>592</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>593</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>594</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>595</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H17" s="19"/>
+    </row>
+    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="23" t="s">
+        <v>596</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>591</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>597</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>598</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>599</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>595</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H18" s="19"/>
+    </row>
+    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="23" t="s">
+        <v>600</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>591</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>601</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>603</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>595</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H19" s="19"/>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="23" t="s">
+        <v>604</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>605</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>606</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>607</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>608</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>595</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H20" s="19"/>
+    </row>
+    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="23" t="s">
+        <v>609</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>610</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>611</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>612</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>613</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>614</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H21" s="19"/>
+    </row>
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="23" t="s">
+        <v>615</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>610</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>616</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>617</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>618</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>619</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H22" s="19"/>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="23" t="s">
+        <v>620</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>610</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>621</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>622</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>623</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>595</v>
+      </c>
+      <c r="G23" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H23" s="19"/>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="23" t="s">
+        <v>624</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>610</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>625</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>549</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>626</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>627</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H24" s="19"/>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="23" t="s">
+        <v>628</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>610</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>629</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>630</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>631</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>632</v>
+      </c>
+      <c r="G25" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H25" s="19"/>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="23" t="s">
+        <v>633</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>634</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>635</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>636</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>637</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>595</v>
+      </c>
+      <c r="G26" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="H26" s="19"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+    </row>
+    <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A34:F34"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="G2" r:id="rId1" display="Ouvrir"/>
+    <hyperlink ref="G3" r:id="rId2" display="Ouvrir"/>
+    <hyperlink ref="G4" r:id="rId3" display="Ouvrir"/>
+    <hyperlink ref="G5" r:id="rId4" display="Ouvrir"/>
+    <hyperlink ref="G6" r:id="rId5" display="Ouvrir"/>
+    <hyperlink ref="G7" r:id="rId6" display="Ouvrir"/>
+    <hyperlink ref="G9" r:id="rId7" display="Ouvrir"/>
+    <hyperlink ref="G10" r:id="rId8" display="Ouvrir"/>
+    <hyperlink ref="G11" r:id="rId9" display="Ouvrir"/>
+    <hyperlink ref="G12" r:id="rId10" display="Ouvrir"/>
+    <hyperlink ref="G13" r:id="rId11" display="Ouvrir"/>
+    <hyperlink ref="G14" r:id="rId12" display="Ouvrir"/>
+    <hyperlink ref="G15" r:id="rId13" display="Ouvrir"/>
+    <hyperlink ref="G16" r:id="rId14" display="Ouvrir"/>
+    <hyperlink ref="G17" r:id="rId15" display="Ouvrir"/>
+    <hyperlink ref="G18" r:id="rId16" display="Ouvrir"/>
+    <hyperlink ref="G19" r:id="rId17" display="Ouvrir"/>
+    <hyperlink ref="G20" r:id="rId18" display="Ouvrir"/>
+    <hyperlink ref="G21" r:id="rId19" display="Ouvrir"/>
+    <hyperlink ref="G22" r:id="rId20" display="Ouvrir"/>
+    <hyperlink ref="G23" r:id="rId21" display="Ouvrir"/>
+    <hyperlink ref="G24" r:id="rId22" display="Ouvrir"/>
+    <hyperlink ref="G25" r:id="rId23" display="Ouvrir"/>
+    <hyperlink ref="G26" r:id="rId24" display="Ouvrir"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="13" t="s">
+        <v>521</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>645</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>646</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>525</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="23" t="s">
+        <v>647</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>648</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>649</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>650</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="23" t="s">
+        <v>651</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>652</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>653</v>
+      </c>
+      <c r="E3" s="24" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="23" t="s">
+        <v>654</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>655</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>656</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>657</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="23" t="s">
+        <v>658</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>659</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>660</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>661</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="23" t="s">
+        <v>662</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>663</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>664</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>665</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="23" t="s">
+        <v>666</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>667</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>668</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>669</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="23" t="s">
+        <v>670</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>671</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>672</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>673</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="23" t="s">
+        <v>674</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>675</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>676</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>677</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="23" t="s">
+        <v>678</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>679</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>680</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="23" t="s">
+        <v>681</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>682</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>683</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>684</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="23" t="s">
+        <v>685</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>686</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>687</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>688</v>
+      </c>
+      <c r="E12" s="25"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" display="Ouvrir"/>
+    <hyperlink ref="E3" r:id="rId2" display="Ouvrir"/>
+    <hyperlink ref="E4" r:id="rId3" display="Ouvrir"/>
+    <hyperlink ref="E5" r:id="rId4" display="Ouvrir"/>
+    <hyperlink ref="E6" r:id="rId5" display="Ouvrir"/>
+    <hyperlink ref="E7" r:id="rId6" display="Ouvrir"/>
+    <hyperlink ref="E8" r:id="rId7" display="Ouvrir"/>
+    <hyperlink ref="E9" r:id="rId8" display="Ouvrir"/>
+    <hyperlink ref="E10" r:id="rId9" display="Ouvrir"/>
+    <hyperlink ref="E11" r:id="rId10" display="Ouvrir"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="80"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="13" t="s">
+        <v>689</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>690</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>119</v>
-      </c>
-      <c r="D2" s="16" t="s">
-        <v>120</v>
+        <v>691</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>692</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>693</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>694</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>128</v>
+        <v>695</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>696</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>130</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>697</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>698</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>135</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>699</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>700</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>138</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>139</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>140</v>
+        <v>701</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>702</v>
+      </c>
+      <c r="C7" s="24" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="D8" s="22"/>
+        <v>703</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>704</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="23" t="s">
+        <v>705</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>706</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="23" t="s">
+        <v>707</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>708</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="23" t="s">
+        <v>709</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>710</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="10" t="s">
+        <v>711</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="https://www.leboncoin.fr"/>
-    <hyperlink ref="D3" r:id="rId2" display="https://www.facebook.com/marketplace"/>
-    <hyperlink ref="D4" r:id="rId3" display="https://www.backacia.com"/>
-    <hyperlink ref="D5" r:id="rId4" display="https://www.cycle-up.fr"/>
-    <hyperlink ref="D6" r:id="rId5" display="https://www.google.com/business/"/>
-    <hyperlink ref="D7" r:id="rId6" display="https://shopify.dev/changelog/a-new-home-for-agentic-storefronts-in-your-admin"/>
+    <hyperlink ref="C2" r:id="rId1" display="Ouvrir"/>
+    <hyperlink ref="C3" r:id="rId2" display="Ouvrir"/>
+    <hyperlink ref="C4" r:id="rId3" display="Ouvrir"/>
+    <hyperlink ref="C5" r:id="rId4" display="Ouvrir"/>
+    <hyperlink ref="C6" r:id="rId5" display="Ouvrir"/>
+    <hyperlink ref="C7" r:id="rId6" display="Ouvrir"/>
+    <hyperlink ref="C8" r:id="rId7" display="Ouvrir"/>
+    <hyperlink ref="C9" r:id="rId8" display="Ouvrir"/>
+    <hyperlink ref="C10" r:id="rId9" display="Ouvrir"/>
+    <hyperlink ref="C11" r:id="rId10" display="Ouvrir"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Règles" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Prospects!$A$1:$P$112</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Prospects!$A$1:$P$198</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -63,12 +63,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1372" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2327" uniqueCount="1186">
   <si>
     <t xml:space="preserve">Prospection MINYALA — mode d'emploi</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Prospects : 111 entreprises (22 de la 1re liste + 89 nouvelles). Filtrez la colonne « Liste » pour ne voir que les nouvelles.</t>
+    <t xml:space="preserve">1. Prospects : 197 entreprises (22 de la 1re liste, 89 de la 2e, 86 de la 3e). Filtrez la colonne « Liste » pour voir une liste à la fois.</t>
   </si>
   <si>
     <t xml:space="preserve">2. Commencez par la priorité 1 (revendeurs, showrooms, marbreries : ils peuvent reprendre un gros lot), puis la 2.</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">Paysagiste, aménagement de jardins. Près du Havre.</t>
   </si>
   <si>
-    <t xml:space="preserve">Nouveaux (12/10)</t>
+    <t xml:space="preserve">2e liste (12/10)</t>
   </si>
   <si>
     <t xml:space="preserve">Carrelage Roger Herblay</t>
@@ -1628,6 +1628,1164 @@
     <t xml:space="preserve">06 20 86 70 71</t>
   </si>
   <si>
+    <t xml:space="preserve">3e liste (12/10)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigMat Aubert Matériaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mareil-sur-Mauldre (78124)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Négoce BigMat des Yvelines doté de showrooms carrelage et aménagement extérieur, il pourrait stocker MINYALA pour ses artisans et ses clients particuliers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 30 90 71 75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gedimat Aux Docks de Clamart (Concept Store Sols &amp; Bains)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clamart (92140)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Négoce Gedimat avec rayon pavés et dallages et un showroom Sols &amp; Bains, qui pourrait référencer MINYALA en dallage extérieur comme en sol intérieur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.gedimat.fr/2264-magasin-gedimat-aux-docks-de-clamart-clamart.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 46 01 52 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gedimat Sefor Houilles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houilles (78800)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grand négoce de 25 000 m² avec exposition revêtements, sols et terrasses et un responsable carrelage et aménagement extérieur : il pourrait acheter un lot de MINYALA pour ses clients pros et particuliers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.gedimat.fr/2034-magasin-gedimat-sefor-houilles.htm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 39 57 10 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Holloco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Négoce du Val-d'Oise avec trois agences, une offre de dalles et pavés pour l'extérieur et des espaces d'exposition carrelage : il pourrait référencer MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">leholloco.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 34 50 95 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCA Matériaux Cuisines Aménagements (France Matériaux)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Achères (78260)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Négoce du réseau France Matériaux avec showroom carrelage et une offre aménagement extérieur : il pourrait proposer MINYALA à ses clients pros et particuliers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.mca-materiaux.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 30 06 00 07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pierlux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auvers-Saint-Georges (91580)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Négociant en pierres naturelles et matériaux d'aménagement extérieur qui fournit artisans, paysagistes et architectes, il pourrait référencer MINYALA dans sa gamme de dallages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.pierluxpierrenaturelle.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raboni (Le Studio Raboni)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boulogne-Billancourt (92100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Négoce francilien multi-agences avec un showroom carrelage (Studio Raboni) et une offre de carrelages et dallages, capable de référencer un lot de MINYALA pour ses clients pros et particuliers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">raboni.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Batimantes (showrooms carrelage et salle de bains)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distributeur avec plusieurs showrooms carrelage et salle de bains dans le 92, le 78 et le 95 : il pourrait ajouter MINYALA à son offre pour les sols intérieurs et les salles de bains.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.batimantes.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 47 82 82 36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceramico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sarcelles (95200)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Déstockeur de carrelage au gros stock qui vend déjà marbre, travertin et dallage en pierre naturelle, il est un acheteur naturel pour un lot de MINYALA disponible à 35 €/m².</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.ceramico.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 86 04 82 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kap Carrelage Domont</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Domont (95330)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Showroom carrelage du Val-d'Oise qui vend aux particuliers et aux pros, pour terrasses et piscines, et fait du déstockage : il pourrait acheter MINYALA en lot pour le revendre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kap-carrelage.store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 30 18 50 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qua Ceramic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piscop (95350)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revendeur de carrelages et dallages pour terrasses et piscines qui propose déjà travertin et pierre : un calcaire crème veiné d'or comme MINYALA pourrait compléter sa gamme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Décomarbre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bry-sur-Marne (94360)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marbrerie avec showroom qui garde un stock permanent de dallages et travaille déjà le travertin, elle pourrait ajouter MINYALA en 30×60 à son stock de dallages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.decomarbre.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 48 81 28 49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marbrier Pierre Taille (MPT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chilly-Mazarin (91380)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fournisseur-poseur de pierres naturelles en sols et façades, avec des références hôtelières : il pourrait acheter MINYALA par lots pour ses dallages.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.mpt-marbrier.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 69 74 12 80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FLIPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pantin (93500)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entreprise de Pantin dont le pôle carrelage et marbrerie pose pierre et marbre dans tous formats, y compris en espaces balnéo et pour l'hôtellerie : elle pourrait proposer MINYALA sur ses chantiers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">flipo.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 48 91 20 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jardinerie / matériaux paysage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pierres Nat'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linas (91310)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revendeur de pierre naturelle depuis 1994 avec un showroom extérieur de 2 500 m² et une clientèle de professionnels et de particuliers, il pourrait revendre MINYALA en dallage de terrasse et d'allée.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pierres-nat.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 69 80 68 15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midi Carrelage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spécialiste carrelage et salle de bains depuis plus de 30 ans, avec espace pro et showroom, qui vend déjà du dallage en pierre, il pourrait référencer MINYALA pour ses clients artisans et particuliers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.midi-carrelage.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 35 65 27 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solmur (agence d'Évreux)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agence d'un distributeur régional de revêtements qui vend déjà carrelage extérieur et travertin : elle pourrait revendre MINYALA à Évreux et dans l'Eure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.solmur.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carrelages Dente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yvetot (76190)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spécialiste du carrelage à Yvetot depuis 1959, avec grand showroom, déstockage et pierres naturelles déjà en gamme : il pourrait acheter MINYALA en lot pour l'intérieur et la terrasse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.carrelages-dente.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 35 56 87 87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nivault</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bénouville (14970)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magasin de carrelage près de Caen avec un showroom de 1 000 m² et une offre de dalles de terrasse : il pourrait exposer et revendre MINYALA en intérieur et en extérieur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.nivault.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 46 12 34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tendance Carrelage Rouen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rouen (76000)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Showroom rouennais de carrelages et pierres naturelles qui vend déjà marbre et dalles de terrasse de 2 cm : il pourrait ajouter MINYALA à sa gamme pierre.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.tendancecarrelagesrouen.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 35 36 36 36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paysages Conseil – Agence de Caen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gros paysagiste normand (75 compagnons, plusieurs agences) qui réalise des terrasses en pierre naturelle et des aménagements autour des piscines et spas, MINYALA pourrait servir sur ses chantiers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.paysagesconseil.fr/paysagiste-caen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 68 69 68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tragin SAS (Tragin et Associés)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pont-l'Évêque (14130)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entreprise familiale de pose fondée en 1956, avec 21 poseurs, qui pose marbres, pierres naturelles et terrasses sur plots pour des architectes et promoteurs de la Côte Fleurie : elle pourrait acheter MINYALA par lots.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.tragin-sa.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 88 25 78</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABL Négoce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Molay-Littry (14330)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Négoce d'aménagement extérieur du Calvados qui vend déjà des pierres naturelles à des paysagistes, architectes et collectivités : il pourrait ajouter MINYALA à sa gamme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.abl-negoce.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 22 96 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promoteur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sedelka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promoteur avec un showroom dans chaque agence où les acquéreurs choisissent carrelage et parquet : MINYALA pourrait y entrer comme option de sol en pierre naturelle sur ses programmes normands.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.sedelka.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 08 34 88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sté Ouest Carrelage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meulan-en-Yvelines (78250)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revendeur de carrelage multimarque des Yvelines, qui vend aussi des tomettes en terre cuite : il pourrait ajouter une pierre naturelle en stock comme MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blocstone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gazeran (78125)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atelier de pierres naturelles avec showroom près de Rambouillet, qui réalise sols, dallages et escaliers sur mesure : il pourrait proposer MINYALA pour les sols de ses clients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.blocstone.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marbrerie de l'Emperador</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitry-sur-Seine (94400)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marbrerie avec showroom qui vend des pierres naturelles et réalise des salles de bains : elle pourrait proposer MINYALA à ses clients pour les sols.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SFM Cochois (Société Française de Marbrerie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ballainvilliers (91160)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marbrerie qui travaille toutes les roches naturelles pour architectes, décorateurs et particuliers et dispose de ses propres poseurs, elle pourrait prescrire et poser MINYALA en sols et salles de bains.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.marbrerie.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 88 28 76 67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jardins et Ambiances</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dourdan (91410)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paysagiste du sud de l'Essonne, actif jusqu'à Rambouillet, qui réalise des terrasses en pierre naturelle : MINYALA pourrait faire partie de ses choix de matériaux.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.jardins-et-ambiances.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 64 59 68 91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les Jardins de Chevreuse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clairefontaine-en-Yvelines (78120)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paysagiste du secteur de Rambouillet qui pose déjà des dallages en calcaire de Bourgogne et en travertin : MINYALA serait une autre option de calcaire pour ses terrasses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.lesjardinsdechevreuse.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 34 84 50 77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI Rénovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jumeauville (78580)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entreprise des Yvelines qui pose déjà des terrasses en pierre naturelle (travertin, quartzite, granit), traditionnellement ou sur plots : MINYALA pourrait entrer dans ses choix de dallage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ci-renovation-78.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 33 48 92 19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EP Bati Renov</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auvers-sur-Oise (95430)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entreprise du Val-d'Oise qui pose du dallage en pierre et construit des terrasses : elle pourrait acheter MINYALA pour ses chantiers de terrasses et d'extensions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sica Marbre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noisy-le-Grand (93160)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Poseur de dallages et de pierres naturelles en Seine-Saint-Denis : MINYALA pourrait lui fournir un calcaire en stock à Gennevilliers pour ses chantiers de sols.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architéa Vallée de la Seine-Ouest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buchelay (78200)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contractant général du secteur Mantes-Vernon qui réalise extensions, cuisines, salles de bains, piscines et terrasses, dont des terrasses en pierre naturelle, il pourrait choisir MINYALA pour ses chantiers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.architea.fr/architea-vallee-de-la-seine-ouest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 89 43 02 63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maison Laborde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malakoff (92240)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entreprise de rénovation haut de gamme des Hauts-de-Seine qui rénove cuisines et salles de bains et réalise des extensions, elle pourrait proposer MINYALA à ses clients pour les sols de ces pièces.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.maison-laborde.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 13 18 73 67</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constructeur de maisons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Archivim</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constructeur de maisons individuelles haut de gamme sur mesure dans l'ouest francilien : ses maisons peuvent recevoir des sols et des terrasses en pierre naturelle comme MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.archivim.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 39 58 56 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hôtel / restaurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crowne Plaza Paris Marne-la-Vallée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magny-le-Hongre (77700)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancien Radisson Blu rénové par IHG qui prévoit une piscine extérieure avec bar pour le printemps 2027 : ses plages et terrasses sont une occasion pour MINYALA selon la finition et la pose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spa / hammam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPS France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installateur de hammams maçonnés en Île-de-France dont les cabines ont des bancs en pierre ou en marbre : MINYALA pourrait habiller les sols et les banquettes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.dps-france.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 51 10 63 22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FTP Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concepteur-installateur de hammams et saunas livrés prêts à carreler pour l'hôtellerie et le wellness, il pourrait prescrire MINYALA pour les sols et abords des espaces bien-être qu'il réalise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.ftp-services.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 33 88 95 84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hôtel Barrière Le Grand Hôtel Enghien-les-Bains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enghien-les-Bains (95880)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'hôtel est fermé depuis juillet 2026 pour 21 mois de travaux et rouvrira en 2028 avec 100 chambres : les lots de sols et de terrasses de cette restructuration sont une piste pour MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.hotelsbarriere.com/fr/enghien-les-bains/le-grand-hotel.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+33 1 73 60 01 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maisons ArchiDesign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chevreuse (78460)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constructeur de maisons 100 % sur mesure présent dans toute l'Île-de-France, qui réalise maisons avec piscine et terrasse et propose le carrelage parmi ses finitions, il pourrait proposer MINYALA pour les sols intérieurs et les terrasses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.maisonsarchidesign.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 88 31 66 06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yvelines Tradition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecquevilly (78920)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constructeur yvelinois de maisons sur mesure haut de gamme (budgets de 250 000 € à 1 M€) : il pourrait proposer MINYALA pour les sols et terrasses de ses villas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.yvelinestradition.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 39 29 02 39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BigMat Guillot et Cie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ézy-sur-Eure (27530)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Négoce BigMat de l'Eure avec rayons carrelage et aménagement extérieur tenus par des vendeurs spécialisés, il pourrait stocker MINYALA pour ses artisans et ses particuliers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 37 64 71 47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matériaux Dubos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brionne (27800)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Négoce de matériaux de l'Eure classé en pierres naturelles, qui fait aussi de l'aménagement extérieur : il pourrait référencer MINYALA pour terrasses et allées.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entreprise Poupart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisieux (14100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entreprise de Lisieux spécialisée dans la vente et la pose de carrelages et de dallages : elle pourrait ajouter une pierre naturelle comme MINYALA à son offre dans le Pays d'Auge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 31 65 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GINI Carrelage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rouen (76100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Showroom carrelage et salle de bains rouennais doté d'une rubrique déstockage et promotions, il pourrait proposer MINYALA à prix stock à ses clients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ginicarrelage.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07 70 78 63 48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frédérick Hanache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Vaupalière (76150)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artisan près de Rouen qui travaille marbre, granit et pierre naturelle pour des salles de bains et cuisines et pose des dallages : MINYALA pourrait lui servir pour les sols et les murs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 35 74 19 61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motte Décoration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Pré-d'Auge (14340)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petite marbrerie du Pays d'Auge qui vend aussi carrelages et dallages et travaille la pierre naturelle pour salles de bains et cuisines : elle pourrait revendre ou poser MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 32 22 00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vincent Locquet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Torpt (27210)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constructeur de piscines près de Honfleur qui pose des terrasses en pierre naturelle et installe des hammams : il pourrait utiliser MINYALA pour ses plages et ses espaces bien-être.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.vincent-locquet.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 32 41 00 91</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bertrand Dufour Paysages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trouville-sur-Mer (14360)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paysagiste de Trouville qui réalise allées pavées, dallage de jardin et aménagements autour des piscines : MINYALA pourrait servir en terrasse et en abords de piscine selon la finition et la pose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 58 42 48 61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boivent Paysages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paysagiste certifié Qualipaysage installé près de Deauville qui réalise dallage de jardin, maçonnerie paysagère et terrasses, MINYALA pourrait lui servir en terrasses et allées.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 85 98 62 55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GUERIN Parcs et Jardins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint-Vaast-en-Auge (14640)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paysagiste de la Côte Fleurie qui a déjà réalisé une terrasse en travertin à Villers-sur-Mer et aménage les abords de piscines, il pourrait poser MINYALA en terrasses et allées.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.paysagiste-auberville.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 50 55 55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SARL Foyer Dumouchel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villers-sur-Mer (14640)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paysagiste de la côte du Calvados qui pose dallages, terrasses en pierre et tours de piscine pour des résidences secondaires : bon débouché pour MINYALA en extérieur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.dumouchel.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 24 65 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piolain Carrelage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint-Manvieu-Norrey (14740)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carreleur caennais qui pose déjà dallages en pierre naturelle et marbre, il pourrait poser MINYALA sur ses chantiers intérieurs et extérieurs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.piolain-carrelage.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 25 21 95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yoann Lambert SARL (YL Carrelage)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gonfreville-l'Orcher (76700)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carreleur normand qui réalise des hammams et pose déjà de la pierre naturelle (Bourgogne, Comblanchien, marbre), il pourrait proposer MINYALA comme autre pierre claire à ses clients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yl-carrelage.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 35 41 74 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Architéa Pays d'Auge - Côte Fleurie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint-Julien-de-Mailloc (14290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contractant général qui rénove manoirs, hôtels et restaurants de prestige et crée des piscines avec terrasses en matériaux nobles : il pourrait prescrire MINYALA pour les sols et abords de piscine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.architea.fr/architea-pays-auge-cote-fleurie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 52 56 30 33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argiles Décoration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les Préaux (27500)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entreprise générale de rénovation près de Pont-Audemer spécialisée dans les maisons anciennes et les sols en pierre ou en tomettes, elle pourrait utiliser MINYALA dans ses rénovations normandes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.argilesdecoration.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 76 31 86 41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entreprise de rénovation voisine de Deauville (salles de bains, cuisines, terrasses en pierres naturelles) : elle pourrait utiliser MINYALA sur ses chantiers de la Côte Fleurie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.vma14.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 98 21 53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bien-Être &amp; Confort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bretteville-l'Orgueilleuse (14740)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricant normand de hammams et saunas sur mesure pour hôtels et particuliers, dont les hammams traditionnels sont habillés de carrelage ou de marbre : il pourrait prescrire MINYALA dans les espaces bien-être qu'il aménage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.bienetreconfort.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 51 15 70</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cailloux Drive Caen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blainville-sur-Orne (14550)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dépôt de matériaux d'aménagement extérieur classé en pierres naturelles, qui vend déjà pavés et ardoise : il pourrait proposer MINYALA en dalles de terrasse et d'allée.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07 86 00 01 06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honnet Constructions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bourg-Achard (27310)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constructeur de maisons normandes à colombages et en pierre, qui fait aussi rénovation et extensions : MINYALA pourrait servir pour les sols et terrasses de ses constructions.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.honnetconstructions.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 44 10 03 40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les Demeures de Province</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constructeur familial normand (plus de 4 000 maisons, 5 agences) qui personnalise chaque maison : il pourrait proposer MINYALA en option de sol ou de terrasse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.lesdemeuresdeprovince.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 32 62 81 62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maisons Lucas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Isneauville (76230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constructeur rouennais qui ne fait que du sur mesure avec un positionnement premium et des maisons de 115 à 400 m², il pourrait proposer MINYALA pour les sols et terrasses de ses grandes maisons.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.maisonslucas.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 35 34 35 55</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volkaert Constructions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constructeur de maisons normandes haut de gamme sur la Côte Fleurie, qui fait aussi extensions et terrasses : MINYALA pourrait habiller les sols et terrasses de ses chantiers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.volkaert-constructions.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 98 55 58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marbrerie de Vitry (Exploit Marbrerie Vitry)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Choisy-le-Roi (94600)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marbrerie historique fondée en 1925, qui fabrique, pose et rénove marbre et pierre, dallages compris, pour l'aménagement haut de gamme : MINYALA pourrait servir à ses projets de sols.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.marbreriedevitry.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 46 80 28 64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Omillimetre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bondoufle (91070)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marbrerie-graniterie qui fait de l'agencement d'hôtel et de l'agencement haut de gamme, MINYALA pourrait convenir à ses projets de sols et de salles de bains.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Océa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crécy-la-Chapelle (77580)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constructeur seine-et-marnais de piscines béton et d'espaces bien-être (spas, saunas, hammams) : MINYALA pourrait servir pour les abords de bassin et les sols de ses espaces détente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.oceapiscine.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 64 63 08 62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Antunes Jardinage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rambouillet (78120)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paysagiste du sud des Yvelines qui réalise de la maçonnerie paysagère et des terrasses en pierre, il pourrait utiliser MINYALA pour ses terrasses et allées.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.antunesjardinage.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 34 85 28 61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duhamel Paysagiste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Pin (77181)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paysagiste du nord de la Seine-et-Marne qui propose des terrasses et allées en dallage de pierre naturelle, il pourrait utiliser MINYALA pour ses terrasses et allées.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">duhamel-paysagiste.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 60 27 12 84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les Paysages Vivants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vélizy-Villacoublay (78140)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paysagiste près de Versailles qui fait du dallage de jardin et des terrasses : MINYALA pourrait lui servir pour des allées et terrasses dallées.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natur'O Paysages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sonchamp (78120)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paysagiste du secteur de Rambouillet qui crée des terrasses en dalles, souvent en pierre naturelle : MINYALA pourrait entrer dans son offre de dallage.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.naturo-paysages.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 34 84 42 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Vert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paysagiste versaillais qui pose des terrasses et allées en dalles de pierre naturelle : MINYALA pourrait lui servir pour ces chantiers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.paysagiste-pro-vert.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 30 43 56 77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Benebatti</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bougival (78380)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entreprise d'extensions et de rénovations haut de gamme dans le 78 et le 92, qui fait aussi de la maçonnerie en pierre : elle pourrait prescrire MINYALA pour les sols et terrasses de ses chantiers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.benebatti.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 85 39 00 87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maisons Serge Gautier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint-Prix (95390)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maître d'œuvre qui construit et restaure des maisons de caractère en soignant le choix des carrelages et des matériaux, il pourrait prescrire un calcaire naturel comme MINYALA pour les sols intérieurs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.serge-gautier.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">01 34 16 64 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France-Maisons-idf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grosrouvre (78490)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constructeur familial de maisons sur mesure haut de gamme dans l'ouest francilien, dont des maisons avec piscine et terrasse : MINYALA pourrait convenir à leurs sols et extérieurs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.francemaisons-idf.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 08 13 39 98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henocque Piscines et Spas (boutique de L'Isle-Adam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'Isle-Adam (95290)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pisciniste familial du Val-d'Oise qui construit des piscines avec plage et installe saunas et hammams, il pourrait utiliser MINYALA pour les plages et abords de ses bassins.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.henocquepiscines.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 14 13 31 11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artech Piscines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sainte-Adresse (76310)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pisciniste de Sainte-Adresse qui construit et rénove des piscines sur mesure et propose spas, saunas et hammams : MINYALA pourrait l'intéresser pour les plages et abords de piscine selon la finition.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piscines du Pays d'Auge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarbec (14130)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pisciniste du Pays d'Auge qui construit des piscines et installe spas, saunas et hammams autour de Deauville : MINYALA pourrait servir pour les plages de piscine selon la finition et la pose.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 84 59 00 74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Éric Devaux (SARL Devaux)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thiberville (27230)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entreprise de l'Eure qui pose du pavage et du dallage en pierre naturelle pour allées, cours et terrasses dans toute la Normandie : elle pourrait utiliser MINYALA pour ses terrasses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.eric-devaux.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 32 46 87 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alliance 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tourgéville (14800)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entreprise générale de Tourgéville sur des projets de 50 000 € à 1 M€ (rénovation de luxe, terrasses, piscine à Deauville) : elle pourrait acheter MINYALA pour les terrasses et sols de villas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">06 44 04 41 65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC3S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constructeur caennais de maisons sur mesure qui réalise aussi des extensions : MINYALA pourrait habiller les sols et terrasses de ses projets haut de gamme.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.ec3s.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 28 27 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gueudry Constructions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Trait (76580)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constructeur normand de maisons individuelles sur mesure depuis plus de 65 ans, avec des agences dans l'Eure : il pourrait proposer MINYALA en option de sol ou de terrasse.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.gueudry.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 35 37 64 04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salle de bains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ma Solution Habitat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fontenay-le-Marmion (14320)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maître artisan près de Caen qui rénove des salles de bains clé en main (carrelage compris), installe hammams et saunas et crée des terrasses, il pourrait poser MINYALA en sols de salles d'eau ou de terrasses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">masolution-habitat.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">07 76 09 62 57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maisons Socoren (agence de Caen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constructeur de maisons bois haut de gamme sur mesure dont les réalisations dans le Calvados comprennent piscine et terrasse, il pourrait proposer MINYALA pour les abords et les sols de ces maisons.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.socoren.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">02 31 34 08 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terralia Immobilier (agence Normandie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beuzeville (27210)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promoteur qui développe à Deauville une résidence confidentielle de 12 appartements avec terrasses panoramiques et prépare d'autres programmes normands, il pourrait prescrire MINYALA pour les halls, sols et terrasses de ses prochaines opérations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">terralia-immobilier.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">03 87 500 300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRIBE Cabourg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabourg (14390)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hôtel de 79 chambres en construction face au marché de Cabourg, avec grand jardin et sauna, ouverture prévue en mars 2027 : les terrasses ou les sols restent peut-être à fournir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tribehotels.com/en/france/cabourg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Canal</t>
   </si>
   <si>
@@ -1979,6 +3137,210 @@
     <t xml:space="preserve">Pierre d'Égypte ne pose pas : s'associer à des carreleurs ou paysagistes inscrits qui proposent MINYALA dans leurs devis de dallage.</t>
   </si>
   <si>
+    <t xml:space="preserve">Salon Maison &amp; Jardin du Havre 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Particuliers du Havre et de la Pointe de Caux en projet maison ou jardin (~12 000 visiteurs attendus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26–28 février 2027, Carré des Docks, Le Havre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réserver un stand auprès de LÉO : petite terrasse ou plage de piscine en MINYALA, prix au m² affiché, demandes de devis avec consentement écrit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrée 5 € ; stand sur demande</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salon Maison de Lisieux 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propriétaires du Pays d'Auge, dont résidences secondaires (~6 000 visiteurs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12–14 février 2027, Parc des Expositions de Lisieux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stand pour toucher le Calvados est : terrasses, allées, sols de longères rénovées, salles de bains.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrée 4 € ; stand sur demande</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salon Habitat de Dreux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Particuliers d'Eure-et-Loir, du sud de l'Eure et de l'ouest des Yvelines (~5 000 visiteurs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13–15 novembre 2026, Parc des Expositions de Dreux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juste hors zone (Évreux à ~45 km). Demander un stand de dernière minute, sinon viser 2027.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salon Vivre Autrement 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Franciliens attentifs aux matériaux naturels et à l'écohabitat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26–29 mars 2027, Parc Floral de Paris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demander le dossier exposant et vérifier que le secteur habitat / matériaux est accepté. Présenter MINYALA comme pierre naturelle.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dossier d'admission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fête des Plantes de Saint-Jean de Beauregard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jardiniers et propriétaires de maisons avec jardin (91, 78, 92), 200+ exposants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Printemps et automne ; dates 2027 à confirmer (2026 : 10–12 avril et 25–27 septembre)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Candidater dans la catégorie aménagement du jardin avec une petite allée en MINYALA. Vérifier les dates avant de s'engager.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stand sur demande</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annuaire des entreprises de Gennevilliers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Habitants et entreprises de la Boucle Nord des Hauts-de-Seine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gennevilliers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demander au service Économie et commerces l'inscription du point de retrait (rubrique Matériel de construction), et si Gennevilliers Magazine accepte la publicité.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probablement gratuit (à confirmer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apple Business (fiche sur Plans)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Utilisateurs d'iPhone qui cherchent un fournisseur près de Gennevilliers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Point de retrait de Gennevilliers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Créer la fiche avec photos, « sur rendez-vous » et lien vers la boutique, comme la fiche Google.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guide-Piscine.fr — fiche entreprise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propriétaires et futurs propriétaires de piscine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France, ciblage par zone possible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Créer la fiche gratuite (MINYALA pour plages et abords, « selon finition et pose »). Demander les offres de visibilité Île-de-France et Normandie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiche gratuite ; publicité sur devis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AlloVoisins Pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Particuliers qui publient des demandes de travaux près de chez eux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France, filtrage local</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profil pro gratuit ; répondre aux demandes terrasse, dallage, carrelage. Lire la charte avant de proposer une vente de produit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inscription gratuite ; options payantes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annonces Tendance Ouest — espace pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Particuliers normands (rubriques Bricolage et Jardinage)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ouvrir un compte pro et demander les conditions pour un vendeur de matériaux, puis publier « Dalles calcaire naturel 30×60, 35 €/m² ».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Régie Ouest (radio Tendance Ouest, Le Courrier Cauchois, La Manche Libre)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lecteurs et auditeurs de toute la Normandie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demander un devis pour une campagne de printemps (mars–mai) sur le thème terrasse, jardin et piscine.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sur devis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radio Evasion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auditeurs des Yvelines, de l'Essonne, de Seine-et-Marne et de Seine-Maritime (beaucoup de maisons avec jardin)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Décrochages Yvelines et Seine-Maritime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spots courts au printemps (« terrasse en pierre naturelle à 35 €/m² ») renvoyant vers la fiche produit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Patrimoine Normand (revue trimestrielle)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propriétaires de maisons anciennes, manoirs et jardins normands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demander les conditions annonceurs. Préciser que MINYALA est un calcaire égyptien, pas une pierre normande.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sur demande</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mediaposte — flyers ciblés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Foyers des quartiers pavillonnaires choisis (Colombes, Bois-Colombes, Argenteuil, Rueil…)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Île-de-France et Normandie, à la carte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flyer « terrasse et piscine en pierre naturelle » avec QR code vers la boutique, distribué dans les zones de maisons autour de Gennevilliers. Respecter les Stop Pub et les règles Oui Pub locales.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">InfoNormandie (site d'actualité locale)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lecteurs de Rouen, Le Havre, Dieppe, Évreux, Vernon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seine-Maritime, Eure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposer un sujet (chantier réalisé en Normandie) via la page de soumission et demander s'il existe des formats publicitaires.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aucune offre publiée</t>
+  </si>
+  <si>
     <t xml:space="preserve">Idées de ciblage</t>
   </si>
   <si>
@@ -2106,6 +3468,66 @@
   </si>
   <si>
     <t xml:space="preserve">Vérifier que Pierre d'Égypte y figure, avec retrait sur rendez-vous et lien vers le site.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les Thermalies 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exploitants de spas et de thalassos (dont Côte Fleurie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21–24 janvier 2027, Carrousel du Louvre, Paris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repérer les spas qui préparent une rénovation (pavillons « Luxury Spa » et « Innovation Design »).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trouville-sur-Mer — réaménagement de la rue des Bains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ville, entreprises de voirie, restaurants de la rue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réseaux jusqu'au 3 avril 2027, puis nouveau revêtement (date à confirmer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suivre le futur marché de revêtement et contacter les restaurants dont les terrasses seront refaites.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIMI 2026 (immobilier d'entreprise)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Promoteurs et aménageurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8–10 décembre 2026, Palais des Congrès de Paris (à confirmer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contacts promoteurs pour halls, commerces en pied d'immeuble et extérieurs. Salon surtout tertiaire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annuaire des showrooms Espace Aubade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Showrooms carrelage indépendants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Par département (Île-de-France, Normandie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcourir l'annuaire par département pour trouver d'autres showrooms indépendants à qui proposer MINYALA.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annuaire des magasins Gedimat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Négoces indépendants avec rayon pavés-dallages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92, 78, 94, 77, 27, 76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contacter les magasins qui ont un rayon Pavés-Dallages et une salle d'exposition (deux sont déjà dans Prospects : Clamart et Houilles).</t>
   </si>
   <si>
     <t xml:space="preserve">ChatGPT (via Shopify)</t>
@@ -2930,7 +4352,7 @@
       </c>
       <c r="B19" s="8" t="n">
         <f aca="false">COUNTIF(Prospects!$L$2:$L$400,A19)</f>
-        <v>111</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2993,7 +4415,7 @@
       </c>
       <c r="B26" s="3" t="n">
         <f aca="false">COUNTA(Prospects!$E$2:$E$400)</f>
-        <v>111</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3054,7 +4476,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P112"/>
+  <dimension ref="A1:P198"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -7649,8 +9071,3550 @@
       <c r="O112" s="18"/>
       <c r="P112" s="20"/>
     </row>
+    <row r="113" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="14" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C113" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D113" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E113" s="15" t="s">
+        <v>522</v>
+      </c>
+      <c r="F113" s="14" t="s">
+        <v>523</v>
+      </c>
+      <c r="G113" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H113" s="14" t="s">
+        <v>524</v>
+      </c>
+      <c r="I113" s="16"/>
+      <c r="J113" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="K113" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L113" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M113" s="19"/>
+      <c r="N113" s="18"/>
+      <c r="O113" s="18"/>
+      <c r="P113" s="20"/>
+    </row>
+    <row r="114" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="14" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C114" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D114" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E114" s="15" t="s">
+        <v>526</v>
+      </c>
+      <c r="F114" s="14" t="s">
+        <v>527</v>
+      </c>
+      <c r="G114" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H114" s="14" t="s">
+        <v>528</v>
+      </c>
+      <c r="I114" s="17" t="s">
+        <v>529</v>
+      </c>
+      <c r="J114" s="16" t="s">
+        <v>530</v>
+      </c>
+      <c r="K114" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L114" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M114" s="19"/>
+      <c r="N114" s="18"/>
+      <c r="O114" s="18"/>
+      <c r="P114" s="20"/>
+    </row>
+    <row r="115" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="14" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C115" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D115" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E115" s="15" t="s">
+        <v>531</v>
+      </c>
+      <c r="F115" s="14" t="s">
+        <v>532</v>
+      </c>
+      <c r="G115" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H115" s="14" t="s">
+        <v>533</v>
+      </c>
+      <c r="I115" s="17" t="s">
+        <v>534</v>
+      </c>
+      <c r="J115" s="16" t="s">
+        <v>535</v>
+      </c>
+      <c r="K115" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L115" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M115" s="19"/>
+      <c r="N115" s="18"/>
+      <c r="O115" s="18"/>
+      <c r="P115" s="20"/>
+    </row>
+    <row r="116" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="14" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C116" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D116" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E116" s="15" t="s">
+        <v>536</v>
+      </c>
+      <c r="F116" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="G116" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H116" s="14" t="s">
+        <v>537</v>
+      </c>
+      <c r="I116" s="17" t="s">
+        <v>538</v>
+      </c>
+      <c r="J116" s="16" t="s">
+        <v>539</v>
+      </c>
+      <c r="K116" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L116" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M116" s="19"/>
+      <c r="N116" s="18"/>
+      <c r="O116" s="18"/>
+      <c r="P116" s="20"/>
+    </row>
+    <row r="117" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C117" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D117" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E117" s="15" t="s">
+        <v>540</v>
+      </c>
+      <c r="F117" s="14" t="s">
+        <v>541</v>
+      </c>
+      <c r="G117" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H117" s="14" t="s">
+        <v>542</v>
+      </c>
+      <c r="I117" s="17" t="s">
+        <v>543</v>
+      </c>
+      <c r="J117" s="16" t="s">
+        <v>544</v>
+      </c>
+      <c r="K117" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L117" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M117" s="19"/>
+      <c r="N117" s="18"/>
+      <c r="O117" s="18"/>
+      <c r="P117" s="20"/>
+    </row>
+    <row r="118" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="14" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C118" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D118" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E118" s="15" t="s">
+        <v>545</v>
+      </c>
+      <c r="F118" s="14" t="s">
+        <v>546</v>
+      </c>
+      <c r="G118" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H118" s="14" t="s">
+        <v>547</v>
+      </c>
+      <c r="I118" s="17" t="s">
+        <v>548</v>
+      </c>
+      <c r="J118" s="16"/>
+      <c r="K118" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L118" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M118" s="19"/>
+      <c r="N118" s="18"/>
+      <c r="O118" s="18"/>
+      <c r="P118" s="20"/>
+    </row>
+    <row r="119" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="14" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C119" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D119" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E119" s="15" t="s">
+        <v>549</v>
+      </c>
+      <c r="F119" s="14" t="s">
+        <v>550</v>
+      </c>
+      <c r="G119" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H119" s="14" t="s">
+        <v>551</v>
+      </c>
+      <c r="I119" s="17" t="s">
+        <v>552</v>
+      </c>
+      <c r="J119" s="16"/>
+      <c r="K119" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L119" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M119" s="19"/>
+      <c r="N119" s="18"/>
+      <c r="O119" s="18"/>
+      <c r="P119" s="20"/>
+    </row>
+    <row r="120" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="14" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C120" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D120" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E120" s="15" t="s">
+        <v>553</v>
+      </c>
+      <c r="F120" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G120" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H120" s="14" t="s">
+        <v>554</v>
+      </c>
+      <c r="I120" s="17" t="s">
+        <v>555</v>
+      </c>
+      <c r="J120" s="16" t="s">
+        <v>556</v>
+      </c>
+      <c r="K120" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L120" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M120" s="19"/>
+      <c r="N120" s="18"/>
+      <c r="O120" s="18"/>
+      <c r="P120" s="20"/>
+    </row>
+    <row r="121" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="14" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C121" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D121" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E121" s="15" t="s">
+        <v>557</v>
+      </c>
+      <c r="F121" s="14" t="s">
+        <v>558</v>
+      </c>
+      <c r="G121" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H121" s="14" t="s">
+        <v>559</v>
+      </c>
+      <c r="I121" s="17" t="s">
+        <v>560</v>
+      </c>
+      <c r="J121" s="16" t="s">
+        <v>561</v>
+      </c>
+      <c r="K121" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L121" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M121" s="19"/>
+      <c r="N121" s="18"/>
+      <c r="O121" s="18"/>
+      <c r="P121" s="20"/>
+    </row>
+    <row r="122" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="14" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C122" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D122" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E122" s="15" t="s">
+        <v>562</v>
+      </c>
+      <c r="F122" s="14" t="s">
+        <v>563</v>
+      </c>
+      <c r="G122" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H122" s="14" t="s">
+        <v>564</v>
+      </c>
+      <c r="I122" s="17" t="s">
+        <v>565</v>
+      </c>
+      <c r="J122" s="16" t="s">
+        <v>566</v>
+      </c>
+      <c r="K122" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L122" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M122" s="19"/>
+      <c r="N122" s="18"/>
+      <c r="O122" s="18"/>
+      <c r="P122" s="20"/>
+    </row>
+    <row r="123" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="14" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C123" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D123" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E123" s="15" t="s">
+        <v>567</v>
+      </c>
+      <c r="F123" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="G123" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H123" s="14" t="s">
+        <v>569</v>
+      </c>
+      <c r="I123" s="16"/>
+      <c r="J123" s="16"/>
+      <c r="K123" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L123" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M123" s="19"/>
+      <c r="N123" s="18"/>
+      <c r="O123" s="18"/>
+      <c r="P123" s="20"/>
+    </row>
+    <row r="124" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="14" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C124" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D124" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E124" s="15" t="s">
+        <v>570</v>
+      </c>
+      <c r="F124" s="14" t="s">
+        <v>571</v>
+      </c>
+      <c r="G124" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H124" s="14" t="s">
+        <v>572</v>
+      </c>
+      <c r="I124" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="J124" s="16" t="s">
+        <v>574</v>
+      </c>
+      <c r="K124" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L124" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M124" s="19"/>
+      <c r="N124" s="18"/>
+      <c r="O124" s="18"/>
+      <c r="P124" s="20"/>
+    </row>
+    <row r="125" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="14" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C125" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D125" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E125" s="15" t="s">
+        <v>575</v>
+      </c>
+      <c r="F125" s="14" t="s">
+        <v>576</v>
+      </c>
+      <c r="G125" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H125" s="14" t="s">
+        <v>577</v>
+      </c>
+      <c r="I125" s="17" t="s">
+        <v>578</v>
+      </c>
+      <c r="J125" s="16" t="s">
+        <v>579</v>
+      </c>
+      <c r="K125" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L125" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M125" s="19"/>
+      <c r="N125" s="18"/>
+      <c r="O125" s="18"/>
+      <c r="P125" s="20"/>
+    </row>
+    <row r="126" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="14" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C126" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D126" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E126" s="15" t="s">
+        <v>580</v>
+      </c>
+      <c r="F126" s="14" t="s">
+        <v>581</v>
+      </c>
+      <c r="G126" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H126" s="14" t="s">
+        <v>582</v>
+      </c>
+      <c r="I126" s="17" t="s">
+        <v>583</v>
+      </c>
+      <c r="J126" s="16" t="s">
+        <v>584</v>
+      </c>
+      <c r="K126" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L126" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M126" s="19"/>
+      <c r="N126" s="18"/>
+      <c r="O126" s="18"/>
+      <c r="P126" s="20"/>
+    </row>
+    <row r="127" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="14" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C127" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D127" s="14" t="s">
+        <v>585</v>
+      </c>
+      <c r="E127" s="15" t="s">
+        <v>586</v>
+      </c>
+      <c r="F127" s="14" t="s">
+        <v>587</v>
+      </c>
+      <c r="G127" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="H127" s="14" t="s">
+        <v>588</v>
+      </c>
+      <c r="I127" s="17" t="s">
+        <v>589</v>
+      </c>
+      <c r="J127" s="16" t="s">
+        <v>590</v>
+      </c>
+      <c r="K127" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L127" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M127" s="19"/>
+      <c r="N127" s="18"/>
+      <c r="O127" s="18"/>
+      <c r="P127" s="20"/>
+    </row>
+    <row r="128" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="14" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C128" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D128" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E128" s="15" t="s">
+        <v>591</v>
+      </c>
+      <c r="F128" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="G128" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H128" s="14" t="s">
+        <v>592</v>
+      </c>
+      <c r="I128" s="17" t="s">
+        <v>593</v>
+      </c>
+      <c r="J128" s="16" t="s">
+        <v>594</v>
+      </c>
+      <c r="K128" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L128" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M128" s="19"/>
+      <c r="N128" s="18"/>
+      <c r="O128" s="18"/>
+      <c r="P128" s="20"/>
+    </row>
+    <row r="129" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="14" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C129" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D129" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E129" s="15" t="s">
+        <v>595</v>
+      </c>
+      <c r="F129" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="G129" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H129" s="14" t="s">
+        <v>596</v>
+      </c>
+      <c r="I129" s="17" t="s">
+        <v>597</v>
+      </c>
+      <c r="J129" s="16"/>
+      <c r="K129" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L129" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M129" s="19"/>
+      <c r="N129" s="18"/>
+      <c r="O129" s="18"/>
+      <c r="P129" s="20"/>
+    </row>
+    <row r="130" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="14" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C130" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E130" s="15" t="s">
+        <v>598</v>
+      </c>
+      <c r="F130" s="14" t="s">
+        <v>599</v>
+      </c>
+      <c r="G130" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H130" s="14" t="s">
+        <v>600</v>
+      </c>
+      <c r="I130" s="17" t="s">
+        <v>601</v>
+      </c>
+      <c r="J130" s="16" t="s">
+        <v>602</v>
+      </c>
+      <c r="K130" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L130" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M130" s="19"/>
+      <c r="N130" s="18"/>
+      <c r="O130" s="18"/>
+      <c r="P130" s="20"/>
+    </row>
+    <row r="131" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="14" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C131" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D131" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E131" s="15" t="s">
+        <v>603</v>
+      </c>
+      <c r="F131" s="14" t="s">
+        <v>604</v>
+      </c>
+      <c r="G131" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H131" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="I131" s="17" t="s">
+        <v>606</v>
+      </c>
+      <c r="J131" s="16" t="s">
+        <v>607</v>
+      </c>
+      <c r="K131" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L131" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M131" s="19"/>
+      <c r="N131" s="18"/>
+      <c r="O131" s="18"/>
+      <c r="P131" s="20"/>
+    </row>
+    <row r="132" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="14" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C132" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D132" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E132" s="15" t="s">
+        <v>608</v>
+      </c>
+      <c r="F132" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="G132" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H132" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="I132" s="17" t="s">
+        <v>611</v>
+      </c>
+      <c r="J132" s="16" t="s">
+        <v>612</v>
+      </c>
+      <c r="K132" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L132" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M132" s="19"/>
+      <c r="N132" s="18"/>
+      <c r="O132" s="18"/>
+      <c r="P132" s="20"/>
+    </row>
+    <row r="133" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="14" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C133" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D133" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="E133" s="15" t="s">
+        <v>613</v>
+      </c>
+      <c r="F133" s="14" t="s">
+        <v>402</v>
+      </c>
+      <c r="G133" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H133" s="14" t="s">
+        <v>614</v>
+      </c>
+      <c r="I133" s="17" t="s">
+        <v>615</v>
+      </c>
+      <c r="J133" s="16" t="s">
+        <v>616</v>
+      </c>
+      <c r="K133" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L133" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M133" s="19"/>
+      <c r="N133" s="18"/>
+      <c r="O133" s="18"/>
+      <c r="P133" s="20"/>
+    </row>
+    <row r="134" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="14" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C134" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D134" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E134" s="15" t="s">
+        <v>617</v>
+      </c>
+      <c r="F134" s="14" t="s">
+        <v>618</v>
+      </c>
+      <c r="G134" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H134" s="14" t="s">
+        <v>619</v>
+      </c>
+      <c r="I134" s="17" t="s">
+        <v>620</v>
+      </c>
+      <c r="J134" s="16" t="s">
+        <v>621</v>
+      </c>
+      <c r="K134" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L134" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M134" s="19"/>
+      <c r="N134" s="18"/>
+      <c r="O134" s="18"/>
+      <c r="P134" s="20"/>
+    </row>
+    <row r="135" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="14" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C135" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D135" s="14" t="s">
+        <v>585</v>
+      </c>
+      <c r="E135" s="15" t="s">
+        <v>622</v>
+      </c>
+      <c r="F135" s="14" t="s">
+        <v>623</v>
+      </c>
+      <c r="G135" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H135" s="14" t="s">
+        <v>624</v>
+      </c>
+      <c r="I135" s="17" t="s">
+        <v>625</v>
+      </c>
+      <c r="J135" s="16" t="s">
+        <v>626</v>
+      </c>
+      <c r="K135" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L135" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M135" s="19"/>
+      <c r="N135" s="18"/>
+      <c r="O135" s="18"/>
+      <c r="P135" s="20"/>
+    </row>
+    <row r="136" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="14" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="C136" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D136" s="14" t="s">
+        <v>627</v>
+      </c>
+      <c r="E136" s="15" t="s">
+        <v>628</v>
+      </c>
+      <c r="F136" s="14" t="s">
+        <v>513</v>
+      </c>
+      <c r="G136" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="H136" s="14" t="s">
+        <v>629</v>
+      </c>
+      <c r="I136" s="17" t="s">
+        <v>630</v>
+      </c>
+      <c r="J136" s="16" t="s">
+        <v>631</v>
+      </c>
+      <c r="K136" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L136" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M136" s="19"/>
+      <c r="N136" s="18"/>
+      <c r="O136" s="18"/>
+      <c r="P136" s="20"/>
+    </row>
+    <row r="137" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="21" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C137" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D137" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E137" s="22" t="s">
+        <v>632</v>
+      </c>
+      <c r="F137" s="21" t="s">
+        <v>633</v>
+      </c>
+      <c r="G137" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H137" s="21" t="s">
+        <v>634</v>
+      </c>
+      <c r="I137" s="16"/>
+      <c r="J137" s="16"/>
+      <c r="K137" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L137" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M137" s="19"/>
+      <c r="N137" s="18"/>
+      <c r="O137" s="18"/>
+      <c r="P137" s="20"/>
+    </row>
+    <row r="138" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="21" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C138" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D138" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E138" s="22" t="s">
+        <v>635</v>
+      </c>
+      <c r="F138" s="21" t="s">
+        <v>636</v>
+      </c>
+      <c r="G138" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H138" s="21" t="s">
+        <v>637</v>
+      </c>
+      <c r="I138" s="17" t="s">
+        <v>638</v>
+      </c>
+      <c r="J138" s="16"/>
+      <c r="K138" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L138" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M138" s="19"/>
+      <c r="N138" s="18"/>
+      <c r="O138" s="18"/>
+      <c r="P138" s="20"/>
+    </row>
+    <row r="139" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="21" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C139" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D139" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E139" s="22" t="s">
+        <v>639</v>
+      </c>
+      <c r="F139" s="21" t="s">
+        <v>640</v>
+      </c>
+      <c r="G139" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H139" s="21" t="s">
+        <v>641</v>
+      </c>
+      <c r="I139" s="16"/>
+      <c r="J139" s="16"/>
+      <c r="K139" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L139" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M139" s="19"/>
+      <c r="N139" s="18"/>
+      <c r="O139" s="18"/>
+      <c r="P139" s="20"/>
+    </row>
+    <row r="140" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="21" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C140" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D140" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E140" s="22" t="s">
+        <v>642</v>
+      </c>
+      <c r="F140" s="21" t="s">
+        <v>643</v>
+      </c>
+      <c r="G140" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H140" s="21" t="s">
+        <v>644</v>
+      </c>
+      <c r="I140" s="17" t="s">
+        <v>645</v>
+      </c>
+      <c r="J140" s="16" t="s">
+        <v>646</v>
+      </c>
+      <c r="K140" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L140" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M140" s="19"/>
+      <c r="N140" s="18"/>
+      <c r="O140" s="18"/>
+      <c r="P140" s="20"/>
+    </row>
+    <row r="141" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="21" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C141" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D141" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E141" s="22" t="s">
+        <v>647</v>
+      </c>
+      <c r="F141" s="21" t="s">
+        <v>648</v>
+      </c>
+      <c r="G141" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H141" s="21" t="s">
+        <v>649</v>
+      </c>
+      <c r="I141" s="17" t="s">
+        <v>650</v>
+      </c>
+      <c r="J141" s="16" t="s">
+        <v>651</v>
+      </c>
+      <c r="K141" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L141" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M141" s="19"/>
+      <c r="N141" s="18"/>
+      <c r="O141" s="18"/>
+      <c r="P141" s="20"/>
+    </row>
+    <row r="142" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="21" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C142" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D142" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E142" s="22" t="s">
+        <v>652</v>
+      </c>
+      <c r="F142" s="21" t="s">
+        <v>653</v>
+      </c>
+      <c r="G142" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H142" s="21" t="s">
+        <v>654</v>
+      </c>
+      <c r="I142" s="17" t="s">
+        <v>655</v>
+      </c>
+      <c r="J142" s="16" t="s">
+        <v>656</v>
+      </c>
+      <c r="K142" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L142" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M142" s="19"/>
+      <c r="N142" s="18"/>
+      <c r="O142" s="18"/>
+      <c r="P142" s="20"/>
+    </row>
+    <row r="143" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="21" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C143" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D143" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E143" s="22" t="s">
+        <v>657</v>
+      </c>
+      <c r="F143" s="21" t="s">
+        <v>658</v>
+      </c>
+      <c r="G143" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H143" s="21" t="s">
+        <v>659</v>
+      </c>
+      <c r="I143" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="J143" s="16" t="s">
+        <v>661</v>
+      </c>
+      <c r="K143" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L143" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M143" s="19"/>
+      <c r="N143" s="18"/>
+      <c r="O143" s="18"/>
+      <c r="P143" s="20"/>
+    </row>
+    <row r="144" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="21" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C144" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D144" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E144" s="22" t="s">
+        <v>662</v>
+      </c>
+      <c r="F144" s="21" t="s">
+        <v>663</v>
+      </c>
+      <c r="G144" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H144" s="21" t="s">
+        <v>664</v>
+      </c>
+      <c r="I144" s="16"/>
+      <c r="J144" s="16"/>
+      <c r="K144" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L144" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M144" s="19"/>
+      <c r="N144" s="18"/>
+      <c r="O144" s="18"/>
+      <c r="P144" s="20"/>
+    </row>
+    <row r="145" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="21" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C145" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D145" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E145" s="22" t="s">
+        <v>665</v>
+      </c>
+      <c r="F145" s="21" t="s">
+        <v>666</v>
+      </c>
+      <c r="G145" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H145" s="21" t="s">
+        <v>667</v>
+      </c>
+      <c r="I145" s="16"/>
+      <c r="J145" s="16"/>
+      <c r="K145" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L145" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M145" s="19"/>
+      <c r="N145" s="18"/>
+      <c r="O145" s="18"/>
+      <c r="P145" s="20"/>
+    </row>
+    <row r="146" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="21" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C146" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D146" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="E146" s="22" t="s">
+        <v>668</v>
+      </c>
+      <c r="F146" s="21" t="s">
+        <v>669</v>
+      </c>
+      <c r="G146" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H146" s="21" t="s">
+        <v>670</v>
+      </c>
+      <c r="I146" s="17" t="s">
+        <v>671</v>
+      </c>
+      <c r="J146" s="16" t="s">
+        <v>672</v>
+      </c>
+      <c r="K146" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L146" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M146" s="19"/>
+      <c r="N146" s="18"/>
+      <c r="O146" s="18"/>
+      <c r="P146" s="20"/>
+    </row>
+    <row r="147" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="21" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C147" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D147" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="E147" s="22" t="s">
+        <v>673</v>
+      </c>
+      <c r="F147" s="21" t="s">
+        <v>674</v>
+      </c>
+      <c r="G147" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H147" s="21" t="s">
+        <v>675</v>
+      </c>
+      <c r="I147" s="17" t="s">
+        <v>676</v>
+      </c>
+      <c r="J147" s="16" t="s">
+        <v>677</v>
+      </c>
+      <c r="K147" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L147" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M147" s="19"/>
+      <c r="N147" s="18"/>
+      <c r="O147" s="18"/>
+      <c r="P147" s="20"/>
+    </row>
+    <row r="148" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="21" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C148" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D148" s="21" t="s">
+        <v>678</v>
+      </c>
+      <c r="E148" s="22" t="s">
+        <v>679</v>
+      </c>
+      <c r="F148" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="G148" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H148" s="21" t="s">
+        <v>680</v>
+      </c>
+      <c r="I148" s="17" t="s">
+        <v>681</v>
+      </c>
+      <c r="J148" s="16" t="s">
+        <v>682</v>
+      </c>
+      <c r="K148" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L148" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M148" s="19"/>
+      <c r="N148" s="18"/>
+      <c r="O148" s="18"/>
+      <c r="P148" s="20"/>
+    </row>
+    <row r="149" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="21" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C149" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D149" s="21" t="s">
+        <v>683</v>
+      </c>
+      <c r="E149" s="22" t="s">
+        <v>684</v>
+      </c>
+      <c r="F149" s="21" t="s">
+        <v>685</v>
+      </c>
+      <c r="G149" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H149" s="21" t="s">
+        <v>686</v>
+      </c>
+      <c r="I149" s="16"/>
+      <c r="J149" s="16"/>
+      <c r="K149" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L149" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M149" s="19"/>
+      <c r="N149" s="18"/>
+      <c r="O149" s="18"/>
+      <c r="P149" s="20"/>
+    </row>
+    <row r="150" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="21" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C150" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D150" s="21" t="s">
+        <v>687</v>
+      </c>
+      <c r="E150" s="22" t="s">
+        <v>688</v>
+      </c>
+      <c r="F150" s="21" t="s">
+        <v>463</v>
+      </c>
+      <c r="G150" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H150" s="21" t="s">
+        <v>689</v>
+      </c>
+      <c r="I150" s="17" t="s">
+        <v>690</v>
+      </c>
+      <c r="J150" s="16" t="s">
+        <v>691</v>
+      </c>
+      <c r="K150" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L150" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M150" s="19"/>
+      <c r="N150" s="18"/>
+      <c r="O150" s="18"/>
+      <c r="P150" s="20"/>
+    </row>
+    <row r="151" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C151" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D151" s="21" t="s">
+        <v>687</v>
+      </c>
+      <c r="E151" s="22" t="s">
+        <v>692</v>
+      </c>
+      <c r="F151" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="G151" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H151" s="21" t="s">
+        <v>693</v>
+      </c>
+      <c r="I151" s="17" t="s">
+        <v>694</v>
+      </c>
+      <c r="J151" s="16" t="s">
+        <v>695</v>
+      </c>
+      <c r="K151" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L151" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M151" s="19"/>
+      <c r="N151" s="18"/>
+      <c r="O151" s="18"/>
+      <c r="P151" s="20"/>
+    </row>
+    <row r="152" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="21" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C152" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D152" s="21" t="s">
+        <v>683</v>
+      </c>
+      <c r="E152" s="22" t="s">
+        <v>696</v>
+      </c>
+      <c r="F152" s="21" t="s">
+        <v>697</v>
+      </c>
+      <c r="G152" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H152" s="21" t="s">
+        <v>698</v>
+      </c>
+      <c r="I152" s="17" t="s">
+        <v>699</v>
+      </c>
+      <c r="J152" s="16" t="s">
+        <v>700</v>
+      </c>
+      <c r="K152" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L152" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M152" s="19"/>
+      <c r="N152" s="18"/>
+      <c r="O152" s="18"/>
+      <c r="P152" s="20"/>
+    </row>
+    <row r="153" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="21" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C153" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D153" s="21" t="s">
+        <v>678</v>
+      </c>
+      <c r="E153" s="22" t="s">
+        <v>701</v>
+      </c>
+      <c r="F153" s="21" t="s">
+        <v>702</v>
+      </c>
+      <c r="G153" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H153" s="21" t="s">
+        <v>703</v>
+      </c>
+      <c r="I153" s="17" t="s">
+        <v>704</v>
+      </c>
+      <c r="J153" s="16" t="s">
+        <v>705</v>
+      </c>
+      <c r="K153" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L153" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M153" s="19"/>
+      <c r="N153" s="18"/>
+      <c r="O153" s="18"/>
+      <c r="P153" s="20"/>
+    </row>
+    <row r="154" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="21" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C154" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D154" s="21" t="s">
+        <v>678</v>
+      </c>
+      <c r="E154" s="22" t="s">
+        <v>706</v>
+      </c>
+      <c r="F154" s="21" t="s">
+        <v>707</v>
+      </c>
+      <c r="G154" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="H154" s="21" t="s">
+        <v>708</v>
+      </c>
+      <c r="I154" s="17" t="s">
+        <v>709</v>
+      </c>
+      <c r="J154" s="16" t="s">
+        <v>710</v>
+      </c>
+      <c r="K154" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L154" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M154" s="19"/>
+      <c r="N154" s="18"/>
+      <c r="O154" s="18"/>
+      <c r="P154" s="20"/>
+    </row>
+    <row r="155" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="21" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C155" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D155" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E155" s="22" t="s">
+        <v>711</v>
+      </c>
+      <c r="F155" s="21" t="s">
+        <v>712</v>
+      </c>
+      <c r="G155" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H155" s="21" t="s">
+        <v>713</v>
+      </c>
+      <c r="I155" s="16"/>
+      <c r="J155" s="16" t="s">
+        <v>714</v>
+      </c>
+      <c r="K155" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L155" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M155" s="19"/>
+      <c r="N155" s="18"/>
+      <c r="O155" s="18"/>
+      <c r="P155" s="20"/>
+    </row>
+    <row r="156" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="21" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C156" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D156" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="E156" s="22" t="s">
+        <v>715</v>
+      </c>
+      <c r="F156" s="21" t="s">
+        <v>716</v>
+      </c>
+      <c r="G156" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H156" s="21" t="s">
+        <v>717</v>
+      </c>
+      <c r="I156" s="16"/>
+      <c r="J156" s="16"/>
+      <c r="K156" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L156" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M156" s="19"/>
+      <c r="N156" s="18"/>
+      <c r="O156" s="18"/>
+      <c r="P156" s="20"/>
+    </row>
+    <row r="157" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="21" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C157" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D157" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E157" s="22" t="s">
+        <v>718</v>
+      </c>
+      <c r="F157" s="21" t="s">
+        <v>719</v>
+      </c>
+      <c r="G157" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H157" s="21" t="s">
+        <v>720</v>
+      </c>
+      <c r="I157" s="16"/>
+      <c r="J157" s="16" t="s">
+        <v>721</v>
+      </c>
+      <c r="K157" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L157" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M157" s="19"/>
+      <c r="N157" s="18"/>
+      <c r="O157" s="18"/>
+      <c r="P157" s="20"/>
+    </row>
+    <row r="158" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="21" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C158" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D158" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="E158" s="22" t="s">
+        <v>722</v>
+      </c>
+      <c r="F158" s="21" t="s">
+        <v>723</v>
+      </c>
+      <c r="G158" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H158" s="21" t="s">
+        <v>724</v>
+      </c>
+      <c r="I158" s="17" t="s">
+        <v>725</v>
+      </c>
+      <c r="J158" s="16" t="s">
+        <v>726</v>
+      </c>
+      <c r="K158" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L158" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M158" s="19"/>
+      <c r="N158" s="18"/>
+      <c r="O158" s="18"/>
+      <c r="P158" s="20"/>
+    </row>
+    <row r="159" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="21" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C159" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D159" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E159" s="22" t="s">
+        <v>727</v>
+      </c>
+      <c r="F159" s="21" t="s">
+        <v>728</v>
+      </c>
+      <c r="G159" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H159" s="21" t="s">
+        <v>729</v>
+      </c>
+      <c r="I159" s="16"/>
+      <c r="J159" s="16" t="s">
+        <v>730</v>
+      </c>
+      <c r="K159" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L159" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M159" s="19"/>
+      <c r="N159" s="18"/>
+      <c r="O159" s="18"/>
+      <c r="P159" s="20"/>
+    </row>
+    <row r="160" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="21" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C160" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D160" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="E160" s="22" t="s">
+        <v>731</v>
+      </c>
+      <c r="F160" s="21" t="s">
+        <v>732</v>
+      </c>
+      <c r="G160" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H160" s="21" t="s">
+        <v>733</v>
+      </c>
+      <c r="I160" s="16"/>
+      <c r="J160" s="16" t="s">
+        <v>734</v>
+      </c>
+      <c r="K160" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L160" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M160" s="19"/>
+      <c r="N160" s="18"/>
+      <c r="O160" s="18"/>
+      <c r="P160" s="20"/>
+    </row>
+    <row r="161" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="21" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C161" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D161" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="E161" s="22" t="s">
+        <v>735</v>
+      </c>
+      <c r="F161" s="21" t="s">
+        <v>736</v>
+      </c>
+      <c r="G161" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H161" s="21" t="s">
+        <v>737</v>
+      </c>
+      <c r="I161" s="17" t="s">
+        <v>738</v>
+      </c>
+      <c r="J161" s="16" t="s">
+        <v>739</v>
+      </c>
+      <c r="K161" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L161" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M161" s="19"/>
+      <c r="N161" s="18"/>
+      <c r="O161" s="18"/>
+      <c r="P161" s="20"/>
+    </row>
+    <row r="162" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="21" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C162" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D162" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E162" s="22" t="s">
+        <v>740</v>
+      </c>
+      <c r="F162" s="21" t="s">
+        <v>741</v>
+      </c>
+      <c r="G162" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H162" s="21" t="s">
+        <v>742</v>
+      </c>
+      <c r="I162" s="16"/>
+      <c r="J162" s="16" t="s">
+        <v>743</v>
+      </c>
+      <c r="K162" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L162" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M162" s="19"/>
+      <c r="N162" s="18"/>
+      <c r="O162" s="18"/>
+      <c r="P162" s="20"/>
+    </row>
+    <row r="163" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="21" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C163" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D163" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E163" s="22" t="s">
+        <v>744</v>
+      </c>
+      <c r="F163" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="G163" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H163" s="21" t="s">
+        <v>745</v>
+      </c>
+      <c r="I163" s="16"/>
+      <c r="J163" s="16" t="s">
+        <v>746</v>
+      </c>
+      <c r="K163" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L163" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M163" s="19"/>
+      <c r="N163" s="18"/>
+      <c r="O163" s="18"/>
+      <c r="P163" s="20"/>
+    </row>
+    <row r="164" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="21" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C164" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D164" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E164" s="22" t="s">
+        <v>747</v>
+      </c>
+      <c r="F164" s="21" t="s">
+        <v>748</v>
+      </c>
+      <c r="G164" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H164" s="21" t="s">
+        <v>749</v>
+      </c>
+      <c r="I164" s="17" t="s">
+        <v>750</v>
+      </c>
+      <c r="J164" s="16" t="s">
+        <v>751</v>
+      </c>
+      <c r="K164" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L164" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M164" s="19"/>
+      <c r="N164" s="18"/>
+      <c r="O164" s="18"/>
+      <c r="P164" s="20"/>
+    </row>
+    <row r="165" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="21" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C165" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D165" s="21" t="s">
+        <v>71</v>
+      </c>
+      <c r="E165" s="22" t="s">
+        <v>752</v>
+      </c>
+      <c r="F165" s="21" t="s">
+        <v>753</v>
+      </c>
+      <c r="G165" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H165" s="21" t="s">
+        <v>754</v>
+      </c>
+      <c r="I165" s="17" t="s">
+        <v>755</v>
+      </c>
+      <c r="J165" s="16" t="s">
+        <v>756</v>
+      </c>
+      <c r="K165" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L165" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M165" s="19"/>
+      <c r="N165" s="18"/>
+      <c r="O165" s="18"/>
+      <c r="P165" s="20"/>
+    </row>
+    <row r="166" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="21" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C166" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D166" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E166" s="22" t="s">
+        <v>757</v>
+      </c>
+      <c r="F166" s="21" t="s">
+        <v>758</v>
+      </c>
+      <c r="G166" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H166" s="21" t="s">
+        <v>759</v>
+      </c>
+      <c r="I166" s="17" t="s">
+        <v>760</v>
+      </c>
+      <c r="J166" s="16" t="s">
+        <v>761</v>
+      </c>
+      <c r="K166" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L166" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M166" s="19"/>
+      <c r="N166" s="18"/>
+      <c r="O166" s="18"/>
+      <c r="P166" s="20"/>
+    </row>
+    <row r="167" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="21" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C167" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D167" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="E167" s="22" t="s">
+        <v>762</v>
+      </c>
+      <c r="F167" s="21" t="s">
+        <v>763</v>
+      </c>
+      <c r="G167" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H167" s="21" t="s">
+        <v>764</v>
+      </c>
+      <c r="I167" s="17" t="s">
+        <v>765</v>
+      </c>
+      <c r="J167" s="16" t="s">
+        <v>766</v>
+      </c>
+      <c r="K167" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L167" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M167" s="19"/>
+      <c r="N167" s="18"/>
+      <c r="O167" s="18"/>
+      <c r="P167" s="20"/>
+    </row>
+    <row r="168" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="21" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C168" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D168" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="E168" s="22" t="s">
+        <v>767</v>
+      </c>
+      <c r="F168" s="21" t="s">
+        <v>768</v>
+      </c>
+      <c r="G168" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H168" s="21" t="s">
+        <v>769</v>
+      </c>
+      <c r="I168" s="17" t="s">
+        <v>770</v>
+      </c>
+      <c r="J168" s="16" t="s">
+        <v>771</v>
+      </c>
+      <c r="K168" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L168" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M168" s="19"/>
+      <c r="N168" s="18"/>
+      <c r="O168" s="18"/>
+      <c r="P168" s="20"/>
+    </row>
+    <row r="169" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="21" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C169" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D169" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="E169" s="22" t="s">
+        <v>772</v>
+      </c>
+      <c r="F169" s="21" t="s">
+        <v>773</v>
+      </c>
+      <c r="G169" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H169" s="21" t="s">
+        <v>774</v>
+      </c>
+      <c r="I169" s="17" t="s">
+        <v>775</v>
+      </c>
+      <c r="J169" s="16" t="s">
+        <v>776</v>
+      </c>
+      <c r="K169" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L169" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M169" s="19"/>
+      <c r="N169" s="18"/>
+      <c r="O169" s="18"/>
+      <c r="P169" s="20"/>
+    </row>
+    <row r="170" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="21" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C170" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D170" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="E170" s="22" t="s">
+        <v>777</v>
+      </c>
+      <c r="F170" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="G170" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H170" s="21" t="s">
+        <v>778</v>
+      </c>
+      <c r="I170" s="17" t="s">
+        <v>779</v>
+      </c>
+      <c r="J170" s="16" t="s">
+        <v>780</v>
+      </c>
+      <c r="K170" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L170" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M170" s="19"/>
+      <c r="N170" s="18"/>
+      <c r="O170" s="18"/>
+      <c r="P170" s="20"/>
+    </row>
+    <row r="171" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="21" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C171" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D171" s="21" t="s">
+        <v>687</v>
+      </c>
+      <c r="E171" s="22" t="s">
+        <v>781</v>
+      </c>
+      <c r="F171" s="21" t="s">
+        <v>782</v>
+      </c>
+      <c r="G171" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H171" s="21" t="s">
+        <v>783</v>
+      </c>
+      <c r="I171" s="17" t="s">
+        <v>784</v>
+      </c>
+      <c r="J171" s="16" t="s">
+        <v>785</v>
+      </c>
+      <c r="K171" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L171" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M171" s="19"/>
+      <c r="N171" s="18"/>
+      <c r="O171" s="18"/>
+      <c r="P171" s="20"/>
+    </row>
+    <row r="172" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="21" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C172" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D172" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="E172" s="22" t="s">
+        <v>786</v>
+      </c>
+      <c r="F172" s="21" t="s">
+        <v>787</v>
+      </c>
+      <c r="G172" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H172" s="21" t="s">
+        <v>788</v>
+      </c>
+      <c r="I172" s="16"/>
+      <c r="J172" s="16" t="s">
+        <v>789</v>
+      </c>
+      <c r="K172" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L172" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M172" s="19"/>
+      <c r="N172" s="18"/>
+      <c r="O172" s="18"/>
+      <c r="P172" s="20"/>
+    </row>
+    <row r="173" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="21" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C173" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D173" s="21" t="s">
+        <v>678</v>
+      </c>
+      <c r="E173" s="22" t="s">
+        <v>790</v>
+      </c>
+      <c r="F173" s="21" t="s">
+        <v>791</v>
+      </c>
+      <c r="G173" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H173" s="21" t="s">
+        <v>792</v>
+      </c>
+      <c r="I173" s="17" t="s">
+        <v>793</v>
+      </c>
+      <c r="J173" s="16" t="s">
+        <v>794</v>
+      </c>
+      <c r="K173" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L173" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M173" s="19"/>
+      <c r="N173" s="18"/>
+      <c r="O173" s="18"/>
+      <c r="P173" s="20"/>
+    </row>
+    <row r="174" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="21" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C174" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D174" s="21" t="s">
+        <v>678</v>
+      </c>
+      <c r="E174" s="22" t="s">
+        <v>795</v>
+      </c>
+      <c r="F174" s="21" t="s">
+        <v>172</v>
+      </c>
+      <c r="G174" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H174" s="21" t="s">
+        <v>796</v>
+      </c>
+      <c r="I174" s="17" t="s">
+        <v>797</v>
+      </c>
+      <c r="J174" s="16" t="s">
+        <v>798</v>
+      </c>
+      <c r="K174" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L174" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M174" s="19"/>
+      <c r="N174" s="18"/>
+      <c r="O174" s="18"/>
+      <c r="P174" s="20"/>
+    </row>
+    <row r="175" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="21" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C175" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D175" s="21" t="s">
+        <v>678</v>
+      </c>
+      <c r="E175" s="22" t="s">
+        <v>799</v>
+      </c>
+      <c r="F175" s="21" t="s">
+        <v>800</v>
+      </c>
+      <c r="G175" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H175" s="21" t="s">
+        <v>801</v>
+      </c>
+      <c r="I175" s="17" t="s">
+        <v>802</v>
+      </c>
+      <c r="J175" s="16" t="s">
+        <v>803</v>
+      </c>
+      <c r="K175" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L175" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M175" s="19"/>
+      <c r="N175" s="18"/>
+      <c r="O175" s="18"/>
+      <c r="P175" s="20"/>
+    </row>
+    <row r="176" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="21" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" s="21" t="s">
+        <v>521</v>
+      </c>
+      <c r="C176" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D176" s="21" t="s">
+        <v>678</v>
+      </c>
+      <c r="E176" s="22" t="s">
+        <v>804</v>
+      </c>
+      <c r="F176" s="21" t="s">
+        <v>413</v>
+      </c>
+      <c r="G176" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="H176" s="21" t="s">
+        <v>805</v>
+      </c>
+      <c r="I176" s="17" t="s">
+        <v>806</v>
+      </c>
+      <c r="J176" s="16" t="s">
+        <v>807</v>
+      </c>
+      <c r="K176" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L176" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M176" s="19"/>
+      <c r="N176" s="18"/>
+      <c r="O176" s="18"/>
+      <c r="P176" s="20"/>
+    </row>
+    <row r="177" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="16" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C177" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D177" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E177" s="23" t="s">
+        <v>808</v>
+      </c>
+      <c r="F177" s="16" t="s">
+        <v>809</v>
+      </c>
+      <c r="G177" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H177" s="16" t="s">
+        <v>810</v>
+      </c>
+      <c r="I177" s="17" t="s">
+        <v>811</v>
+      </c>
+      <c r="J177" s="16" t="s">
+        <v>812</v>
+      </c>
+      <c r="K177" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L177" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M177" s="19"/>
+      <c r="N177" s="18"/>
+      <c r="O177" s="18"/>
+      <c r="P177" s="20"/>
+    </row>
+    <row r="178" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="16" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C178" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D178" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E178" s="23" t="s">
+        <v>813</v>
+      </c>
+      <c r="F178" s="16" t="s">
+        <v>814</v>
+      </c>
+      <c r="G178" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H178" s="16" t="s">
+        <v>815</v>
+      </c>
+      <c r="I178" s="16"/>
+      <c r="J178" s="16"/>
+      <c r="K178" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L178" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M178" s="19"/>
+      <c r="N178" s="18"/>
+      <c r="O178" s="18"/>
+      <c r="P178" s="20"/>
+    </row>
+    <row r="179" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="16" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C179" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D179" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E179" s="23" t="s">
+        <v>816</v>
+      </c>
+      <c r="F179" s="16" t="s">
+        <v>817</v>
+      </c>
+      <c r="G179" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H179" s="16" t="s">
+        <v>818</v>
+      </c>
+      <c r="I179" s="17" t="s">
+        <v>819</v>
+      </c>
+      <c r="J179" s="16" t="s">
+        <v>820</v>
+      </c>
+      <c r="K179" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L179" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M179" s="19"/>
+      <c r="N179" s="18"/>
+      <c r="O179" s="18"/>
+      <c r="P179" s="20"/>
+    </row>
+    <row r="180" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="16" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C180" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D180" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E180" s="23" t="s">
+        <v>821</v>
+      </c>
+      <c r="F180" s="16" t="s">
+        <v>822</v>
+      </c>
+      <c r="G180" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H180" s="16" t="s">
+        <v>823</v>
+      </c>
+      <c r="I180" s="17" t="s">
+        <v>824</v>
+      </c>
+      <c r="J180" s="16" t="s">
+        <v>825</v>
+      </c>
+      <c r="K180" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L180" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M180" s="19"/>
+      <c r="N180" s="18"/>
+      <c r="O180" s="18"/>
+      <c r="P180" s="20"/>
+    </row>
+    <row r="181" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="16" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C181" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D181" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E181" s="23" t="s">
+        <v>826</v>
+      </c>
+      <c r="F181" s="16" t="s">
+        <v>827</v>
+      </c>
+      <c r="G181" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H181" s="16" t="s">
+        <v>828</v>
+      </c>
+      <c r="I181" s="17" t="s">
+        <v>829</v>
+      </c>
+      <c r="J181" s="16" t="s">
+        <v>830</v>
+      </c>
+      <c r="K181" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L181" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M181" s="19"/>
+      <c r="N181" s="18"/>
+      <c r="O181" s="18"/>
+      <c r="P181" s="20"/>
+    </row>
+    <row r="182" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="16" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C182" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D182" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E182" s="23" t="s">
+        <v>831</v>
+      </c>
+      <c r="F182" s="16" t="s">
+        <v>832</v>
+      </c>
+      <c r="G182" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H182" s="16" t="s">
+        <v>833</v>
+      </c>
+      <c r="I182" s="16"/>
+      <c r="J182" s="16"/>
+      <c r="K182" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L182" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M182" s="19"/>
+      <c r="N182" s="18"/>
+      <c r="O182" s="18"/>
+      <c r="P182" s="20"/>
+    </row>
+    <row r="183" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="16" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C183" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D183" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E183" s="23" t="s">
+        <v>834</v>
+      </c>
+      <c r="F183" s="16" t="s">
+        <v>835</v>
+      </c>
+      <c r="G183" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H183" s="16" t="s">
+        <v>836</v>
+      </c>
+      <c r="I183" s="17" t="s">
+        <v>837</v>
+      </c>
+      <c r="J183" s="16" t="s">
+        <v>838</v>
+      </c>
+      <c r="K183" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L183" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M183" s="19"/>
+      <c r="N183" s="18"/>
+      <c r="O183" s="18"/>
+      <c r="P183" s="20"/>
+    </row>
+    <row r="184" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="16" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C184" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D184" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E184" s="23" t="s">
+        <v>839</v>
+      </c>
+      <c r="F184" s="16" t="s">
+        <v>147</v>
+      </c>
+      <c r="G184" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H184" s="16" t="s">
+        <v>840</v>
+      </c>
+      <c r="I184" s="17" t="s">
+        <v>841</v>
+      </c>
+      <c r="J184" s="16" t="s">
+        <v>842</v>
+      </c>
+      <c r="K184" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L184" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M184" s="19"/>
+      <c r="N184" s="18"/>
+      <c r="O184" s="18"/>
+      <c r="P184" s="20"/>
+    </row>
+    <row r="185" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="16" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C185" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D185" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="E185" s="23" t="s">
+        <v>843</v>
+      </c>
+      <c r="F185" s="16" t="s">
+        <v>844</v>
+      </c>
+      <c r="G185" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H185" s="16" t="s">
+        <v>845</v>
+      </c>
+      <c r="I185" s="17" t="s">
+        <v>846</v>
+      </c>
+      <c r="J185" s="16" t="s">
+        <v>847</v>
+      </c>
+      <c r="K185" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L185" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M185" s="19"/>
+      <c r="N185" s="18"/>
+      <c r="O185" s="18"/>
+      <c r="P185" s="20"/>
+    </row>
+    <row r="186" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="16" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C186" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D186" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="E186" s="23" t="s">
+        <v>848</v>
+      </c>
+      <c r="F186" s="16" t="s">
+        <v>849</v>
+      </c>
+      <c r="G186" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H186" s="16" t="s">
+        <v>850</v>
+      </c>
+      <c r="I186" s="17" t="s">
+        <v>851</v>
+      </c>
+      <c r="J186" s="16" t="s">
+        <v>852</v>
+      </c>
+      <c r="K186" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L186" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M186" s="19"/>
+      <c r="N186" s="18"/>
+      <c r="O186" s="18"/>
+      <c r="P186" s="20"/>
+    </row>
+    <row r="187" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="16" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C187" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D187" s="16" t="s">
+        <v>678</v>
+      </c>
+      <c r="E187" s="23" t="s">
+        <v>853</v>
+      </c>
+      <c r="F187" s="16" t="s">
+        <v>854</v>
+      </c>
+      <c r="G187" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H187" s="16" t="s">
+        <v>855</v>
+      </c>
+      <c r="I187" s="17" t="s">
+        <v>856</v>
+      </c>
+      <c r="J187" s="16" t="s">
+        <v>857</v>
+      </c>
+      <c r="K187" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L187" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M187" s="19"/>
+      <c r="N187" s="18"/>
+      <c r="O187" s="18"/>
+      <c r="P187" s="20"/>
+    </row>
+    <row r="188" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="16" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C188" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D188" s="16" t="s">
+        <v>687</v>
+      </c>
+      <c r="E188" s="23" t="s">
+        <v>858</v>
+      </c>
+      <c r="F188" s="16" t="s">
+        <v>859</v>
+      </c>
+      <c r="G188" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H188" s="16" t="s">
+        <v>860</v>
+      </c>
+      <c r="I188" s="17" t="s">
+        <v>861</v>
+      </c>
+      <c r="J188" s="16" t="s">
+        <v>862</v>
+      </c>
+      <c r="K188" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L188" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M188" s="19"/>
+      <c r="N188" s="18"/>
+      <c r="O188" s="18"/>
+      <c r="P188" s="20"/>
+    </row>
+    <row r="189" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="16" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C189" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D189" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E189" s="23" t="s">
+        <v>863</v>
+      </c>
+      <c r="F189" s="16" t="s">
+        <v>864</v>
+      </c>
+      <c r="G189" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H189" s="16" t="s">
+        <v>865</v>
+      </c>
+      <c r="I189" s="16"/>
+      <c r="J189" s="16"/>
+      <c r="K189" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L189" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M189" s="19"/>
+      <c r="N189" s="18"/>
+      <c r="O189" s="18"/>
+      <c r="P189" s="20"/>
+    </row>
+    <row r="190" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="16" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C190" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D190" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="E190" s="23" t="s">
+        <v>866</v>
+      </c>
+      <c r="F190" s="16" t="s">
+        <v>867</v>
+      </c>
+      <c r="G190" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H190" s="16" t="s">
+        <v>868</v>
+      </c>
+      <c r="I190" s="16"/>
+      <c r="J190" s="16" t="s">
+        <v>869</v>
+      </c>
+      <c r="K190" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L190" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M190" s="19"/>
+      <c r="N190" s="18"/>
+      <c r="O190" s="18"/>
+      <c r="P190" s="20"/>
+    </row>
+    <row r="191" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="16" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C191" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D191" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E191" s="23" t="s">
+        <v>870</v>
+      </c>
+      <c r="F191" s="16" t="s">
+        <v>871</v>
+      </c>
+      <c r="G191" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H191" s="16" t="s">
+        <v>872</v>
+      </c>
+      <c r="I191" s="17" t="s">
+        <v>873</v>
+      </c>
+      <c r="J191" s="16" t="s">
+        <v>874</v>
+      </c>
+      <c r="K191" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L191" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M191" s="19"/>
+      <c r="N191" s="18"/>
+      <c r="O191" s="18"/>
+      <c r="P191" s="20"/>
+    </row>
+    <row r="192" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="16" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C192" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D192" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="E192" s="23" t="s">
+        <v>875</v>
+      </c>
+      <c r="F192" s="16" t="s">
+        <v>876</v>
+      </c>
+      <c r="G192" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H192" s="16" t="s">
+        <v>877</v>
+      </c>
+      <c r="I192" s="16"/>
+      <c r="J192" s="16" t="s">
+        <v>878</v>
+      </c>
+      <c r="K192" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L192" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M192" s="19"/>
+      <c r="N192" s="18"/>
+      <c r="O192" s="18"/>
+      <c r="P192" s="20"/>
+    </row>
+    <row r="193" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="16" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C193" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D193" s="16" t="s">
+        <v>678</v>
+      </c>
+      <c r="E193" s="23" t="s">
+        <v>879</v>
+      </c>
+      <c r="F193" s="16" t="s">
+        <v>402</v>
+      </c>
+      <c r="G193" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H193" s="16" t="s">
+        <v>880</v>
+      </c>
+      <c r="I193" s="17" t="s">
+        <v>881</v>
+      </c>
+      <c r="J193" s="16" t="s">
+        <v>882</v>
+      </c>
+      <c r="K193" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L193" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M193" s="19"/>
+      <c r="N193" s="18"/>
+      <c r="O193" s="18"/>
+      <c r="P193" s="20"/>
+    </row>
+    <row r="194" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="16" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C194" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D194" s="16" t="s">
+        <v>678</v>
+      </c>
+      <c r="E194" s="23" t="s">
+        <v>883</v>
+      </c>
+      <c r="F194" s="16" t="s">
+        <v>884</v>
+      </c>
+      <c r="G194" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H194" s="16" t="s">
+        <v>885</v>
+      </c>
+      <c r="I194" s="17" t="s">
+        <v>886</v>
+      </c>
+      <c r="J194" s="16" t="s">
+        <v>887</v>
+      </c>
+      <c r="K194" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L194" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M194" s="19"/>
+      <c r="N194" s="18"/>
+      <c r="O194" s="18"/>
+      <c r="P194" s="20"/>
+    </row>
+    <row r="195" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="16" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C195" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D195" s="16" t="s">
+        <v>888</v>
+      </c>
+      <c r="E195" s="23" t="s">
+        <v>889</v>
+      </c>
+      <c r="F195" s="16" t="s">
+        <v>890</v>
+      </c>
+      <c r="G195" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H195" s="16" t="s">
+        <v>891</v>
+      </c>
+      <c r="I195" s="17" t="s">
+        <v>892</v>
+      </c>
+      <c r="J195" s="16" t="s">
+        <v>893</v>
+      </c>
+      <c r="K195" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L195" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M195" s="19"/>
+      <c r="N195" s="18"/>
+      <c r="O195" s="18"/>
+      <c r="P195" s="20"/>
+    </row>
+    <row r="196" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="16" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C196" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D196" s="16" t="s">
+        <v>678</v>
+      </c>
+      <c r="E196" s="23" t="s">
+        <v>894</v>
+      </c>
+      <c r="F196" s="16" t="s">
+        <v>187</v>
+      </c>
+      <c r="G196" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H196" s="16" t="s">
+        <v>895</v>
+      </c>
+      <c r="I196" s="17" t="s">
+        <v>896</v>
+      </c>
+      <c r="J196" s="16" t="s">
+        <v>897</v>
+      </c>
+      <c r="K196" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L196" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M196" s="19"/>
+      <c r="N196" s="18"/>
+      <c r="O196" s="18"/>
+      <c r="P196" s="20"/>
+    </row>
+    <row r="197" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="16" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C197" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D197" s="16" t="s">
+        <v>627</v>
+      </c>
+      <c r="E197" s="23" t="s">
+        <v>898</v>
+      </c>
+      <c r="F197" s="16" t="s">
+        <v>899</v>
+      </c>
+      <c r="G197" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H197" s="16" t="s">
+        <v>900</v>
+      </c>
+      <c r="I197" s="17" t="s">
+        <v>901</v>
+      </c>
+      <c r="J197" s="16" t="s">
+        <v>902</v>
+      </c>
+      <c r="K197" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L197" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M197" s="19"/>
+      <c r="N197" s="18"/>
+      <c r="O197" s="18"/>
+      <c r="P197" s="20"/>
+    </row>
+    <row r="198" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="16" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="C198" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D198" s="16" t="s">
+        <v>683</v>
+      </c>
+      <c r="E198" s="23" t="s">
+        <v>903</v>
+      </c>
+      <c r="F198" s="16" t="s">
+        <v>904</v>
+      </c>
+      <c r="G198" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="H198" s="16" t="s">
+        <v>905</v>
+      </c>
+      <c r="I198" s="17" t="s">
+        <v>906</v>
+      </c>
+      <c r="J198" s="16"/>
+      <c r="K198" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="L198" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="M198" s="19"/>
+      <c r="N198" s="18"/>
+      <c r="O198" s="18"/>
+      <c r="P198" s="20"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P112"/>
+  <autoFilter ref="A1:P198"/>
   <dataValidations count="2">
     <dataValidation allowBlank="true" error="Choisissez un statut dans la liste." errorStyle="stop" errorTitle="Statut" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L2:L400" type="list">
       <formula1>"À contacter,Contacté,Intéressé,Échantillon / visite,Devis envoyé,Vendu,Pas intéressé"</formula1>
@@ -7850,6 +12814,158 @@
     <hyperlink ref="K111" r:id="rId187" display="Voir"/>
     <hyperlink ref="I112" r:id="rId188" display="www.act-mo.fr"/>
     <hyperlink ref="K112" r:id="rId189" display="Voir"/>
+    <hyperlink ref="K113" r:id="rId190" display="Voir"/>
+    <hyperlink ref="I114" r:id="rId191" display="www.gedimat.fr/2264-magasin-gedimat-aux-docks-de-clamart-clamart.htm"/>
+    <hyperlink ref="K114" r:id="rId192" display="Voir"/>
+    <hyperlink ref="I115" r:id="rId193" display="www.gedimat.fr/2034-magasin-gedimat-sefor-houilles.htm"/>
+    <hyperlink ref="K115" r:id="rId194" display="Voir"/>
+    <hyperlink ref="I116" r:id="rId195" display="leholloco.com"/>
+    <hyperlink ref="K116" r:id="rId196" display="Voir"/>
+    <hyperlink ref="I117" r:id="rId197" display="www.mca-materiaux.com"/>
+    <hyperlink ref="K117" r:id="rId198" display="Voir"/>
+    <hyperlink ref="I118" r:id="rId199" display="www.pierluxpierrenaturelle.fr"/>
+    <hyperlink ref="K118" r:id="rId200" display="Voir"/>
+    <hyperlink ref="I119" r:id="rId201" display="raboni.fr"/>
+    <hyperlink ref="K119" r:id="rId202" display="Voir"/>
+    <hyperlink ref="I120" r:id="rId203" display="www.batimantes.fr"/>
+    <hyperlink ref="K120" r:id="rId204" display="Voir"/>
+    <hyperlink ref="I121" r:id="rId205" display="www.ceramico.fr"/>
+    <hyperlink ref="K121" r:id="rId206" display="Voir"/>
+    <hyperlink ref="I122" r:id="rId207" display="kap-carrelage.store"/>
+    <hyperlink ref="K122" r:id="rId208" display="Voir"/>
+    <hyperlink ref="K123" r:id="rId209" display="Voir"/>
+    <hyperlink ref="I124" r:id="rId210" display="www.decomarbre.fr"/>
+    <hyperlink ref="K124" r:id="rId211" display="Voir"/>
+    <hyperlink ref="I125" r:id="rId212" display="www.mpt-marbrier.fr"/>
+    <hyperlink ref="K125" r:id="rId213" display="Voir"/>
+    <hyperlink ref="I126" r:id="rId214" display="flipo.fr"/>
+    <hyperlink ref="K126" r:id="rId215" display="Voir"/>
+    <hyperlink ref="I127" r:id="rId216" display="pierres-nat.com"/>
+    <hyperlink ref="K127" r:id="rId217" display="Voir"/>
+    <hyperlink ref="I128" r:id="rId218" display="www.midi-carrelage.fr"/>
+    <hyperlink ref="K128" r:id="rId219" display="Voir"/>
+    <hyperlink ref="I129" r:id="rId220" display="www.solmur.fr"/>
+    <hyperlink ref="K129" r:id="rId221" display="Voir"/>
+    <hyperlink ref="I130" r:id="rId222" display="www.carrelages-dente.fr"/>
+    <hyperlink ref="K130" r:id="rId223" display="Voir"/>
+    <hyperlink ref="I131" r:id="rId224" display="www.nivault.com"/>
+    <hyperlink ref="K131" r:id="rId225" display="Voir"/>
+    <hyperlink ref="I132" r:id="rId226" display="www.tendancecarrelagesrouen.fr"/>
+    <hyperlink ref="K132" r:id="rId227" display="Voir"/>
+    <hyperlink ref="I133" r:id="rId228" display="www.paysagesconseil.fr/paysagiste-caen"/>
+    <hyperlink ref="K133" r:id="rId229" display="Voir"/>
+    <hyperlink ref="I134" r:id="rId230" display="www.tragin-sa.com"/>
+    <hyperlink ref="K134" r:id="rId231" display="Voir"/>
+    <hyperlink ref="I135" r:id="rId232" display="www.abl-negoce.fr"/>
+    <hyperlink ref="K135" r:id="rId233" display="Voir"/>
+    <hyperlink ref="I136" r:id="rId234" display="www.sedelka.fr"/>
+    <hyperlink ref="K136" r:id="rId235" display="Voir"/>
+    <hyperlink ref="K137" r:id="rId236" display="Voir"/>
+    <hyperlink ref="I138" r:id="rId237" display="www.blocstone.com"/>
+    <hyperlink ref="K138" r:id="rId238" display="Voir"/>
+    <hyperlink ref="K139" r:id="rId239" display="Voir"/>
+    <hyperlink ref="I140" r:id="rId240" display="www.marbrerie.com"/>
+    <hyperlink ref="K140" r:id="rId241" display="Voir"/>
+    <hyperlink ref="I141" r:id="rId242" display="www.jardins-et-ambiances.com"/>
+    <hyperlink ref="K141" r:id="rId243" display="Voir"/>
+    <hyperlink ref="I142" r:id="rId244" display="www.lesjardinsdechevreuse.fr"/>
+    <hyperlink ref="K142" r:id="rId245" display="Voir"/>
+    <hyperlink ref="I143" r:id="rId246" display="ci-renovation-78.fr"/>
+    <hyperlink ref="K143" r:id="rId247" display="Voir"/>
+    <hyperlink ref="K144" r:id="rId248" display="Voir"/>
+    <hyperlink ref="K145" r:id="rId249" display="Voir"/>
+    <hyperlink ref="I146" r:id="rId250" display="www.architea.fr/architea-vallee-de-la-seine-ouest"/>
+    <hyperlink ref="K146" r:id="rId251" display="Voir"/>
+    <hyperlink ref="I147" r:id="rId252" display="www.maison-laborde.fr"/>
+    <hyperlink ref="K147" r:id="rId253" display="Voir"/>
+    <hyperlink ref="I148" r:id="rId254" display="www.archivim.fr"/>
+    <hyperlink ref="K148" r:id="rId255" display="Voir"/>
+    <hyperlink ref="K149" r:id="rId256" display="Voir"/>
+    <hyperlink ref="I150" r:id="rId257" display="www.dps-france.fr"/>
+    <hyperlink ref="K150" r:id="rId258" display="Voir"/>
+    <hyperlink ref="I151" r:id="rId259" display="www.ftp-services.fr"/>
+    <hyperlink ref="K151" r:id="rId260" display="Voir"/>
+    <hyperlink ref="I152" r:id="rId261" display="www.hotelsbarriere.com/fr/enghien-les-bains/le-grand-hotel.html"/>
+    <hyperlink ref="K152" r:id="rId262" display="Voir"/>
+    <hyperlink ref="I153" r:id="rId263" display="www.maisonsarchidesign.com"/>
+    <hyperlink ref="K153" r:id="rId264" display="Voir"/>
+    <hyperlink ref="I154" r:id="rId265" display="www.yvelinestradition.fr"/>
+    <hyperlink ref="K154" r:id="rId266" display="Voir"/>
+    <hyperlink ref="K155" r:id="rId267" display="Voir"/>
+    <hyperlink ref="K156" r:id="rId268" display="Voir"/>
+    <hyperlink ref="K157" r:id="rId269" display="Voir"/>
+    <hyperlink ref="I158" r:id="rId270" display="ginicarrelage.fr"/>
+    <hyperlink ref="K158" r:id="rId271" display="Voir"/>
+    <hyperlink ref="K159" r:id="rId272" display="Voir"/>
+    <hyperlink ref="K160" r:id="rId273" display="Voir"/>
+    <hyperlink ref="I161" r:id="rId274" display="www.vincent-locquet.fr"/>
+    <hyperlink ref="K161" r:id="rId275" display="Voir"/>
+    <hyperlink ref="K162" r:id="rId276" display="Voir"/>
+    <hyperlink ref="K163" r:id="rId277" display="Voir"/>
+    <hyperlink ref="I164" r:id="rId278" display="www.paysagiste-auberville.fr"/>
+    <hyperlink ref="K164" r:id="rId279" display="Voir"/>
+    <hyperlink ref="I165" r:id="rId280" display="www.dumouchel.fr"/>
+    <hyperlink ref="K165" r:id="rId281" display="Voir"/>
+    <hyperlink ref="I166" r:id="rId282" display="www.piolain-carrelage.fr"/>
+    <hyperlink ref="K166" r:id="rId283" display="Voir"/>
+    <hyperlink ref="I167" r:id="rId284" display="yl-carrelage.fr"/>
+    <hyperlink ref="K167" r:id="rId285" display="Voir"/>
+    <hyperlink ref="I168" r:id="rId286" display="www.architea.fr/architea-pays-auge-cote-fleurie"/>
+    <hyperlink ref="K168" r:id="rId287" display="Voir"/>
+    <hyperlink ref="I169" r:id="rId288" display="www.argilesdecoration.com"/>
+    <hyperlink ref="K169" r:id="rId289" display="Voir"/>
+    <hyperlink ref="I170" r:id="rId290" display="www.vma14.com"/>
+    <hyperlink ref="K170" r:id="rId291" display="Voir"/>
+    <hyperlink ref="I171" r:id="rId292" display="www.bienetreconfort.fr"/>
+    <hyperlink ref="K171" r:id="rId293" display="Voir"/>
+    <hyperlink ref="K172" r:id="rId294" display="Voir"/>
+    <hyperlink ref="I173" r:id="rId295" display="www.honnetconstructions.fr"/>
+    <hyperlink ref="K173" r:id="rId296" display="Voir"/>
+    <hyperlink ref="I174" r:id="rId297" display="www.lesdemeuresdeprovince.fr"/>
+    <hyperlink ref="K174" r:id="rId298" display="Voir"/>
+    <hyperlink ref="I175" r:id="rId299" display="www.maisonslucas.fr"/>
+    <hyperlink ref="K175" r:id="rId300" display="Voir"/>
+    <hyperlink ref="I176" r:id="rId301" display="www.volkaert-constructions.fr"/>
+    <hyperlink ref="K176" r:id="rId302" display="Voir"/>
+    <hyperlink ref="I177" r:id="rId303" display="www.marbreriedevitry.fr"/>
+    <hyperlink ref="K177" r:id="rId304" display="Voir"/>
+    <hyperlink ref="K178" r:id="rId305" display="Voir"/>
+    <hyperlink ref="I179" r:id="rId306" display="www.oceapiscine.fr"/>
+    <hyperlink ref="K179" r:id="rId307" display="Voir"/>
+    <hyperlink ref="I180" r:id="rId308" display="www.antunesjardinage.fr"/>
+    <hyperlink ref="K180" r:id="rId309" display="Voir"/>
+    <hyperlink ref="I181" r:id="rId310" display="duhamel-paysagiste.fr"/>
+    <hyperlink ref="K181" r:id="rId311" display="Voir"/>
+    <hyperlink ref="K182" r:id="rId312" display="Voir"/>
+    <hyperlink ref="I183" r:id="rId313" display="www.naturo-paysages.fr"/>
+    <hyperlink ref="K183" r:id="rId314" display="Voir"/>
+    <hyperlink ref="I184" r:id="rId315" display="www.paysagiste-pro-vert.fr"/>
+    <hyperlink ref="K184" r:id="rId316" display="Voir"/>
+    <hyperlink ref="I185" r:id="rId317" display="www.benebatti.fr"/>
+    <hyperlink ref="K185" r:id="rId318" display="Voir"/>
+    <hyperlink ref="I186" r:id="rId319" display="www.serge-gautier.com"/>
+    <hyperlink ref="K186" r:id="rId320" display="Voir"/>
+    <hyperlink ref="I187" r:id="rId321" display="www.francemaisons-idf.com"/>
+    <hyperlink ref="K187" r:id="rId322" display="Voir"/>
+    <hyperlink ref="I188" r:id="rId323" display="www.henocquepiscines.fr"/>
+    <hyperlink ref="K188" r:id="rId324" display="Voir"/>
+    <hyperlink ref="K189" r:id="rId325" display="Voir"/>
+    <hyperlink ref="K190" r:id="rId326" display="Voir"/>
+    <hyperlink ref="I191" r:id="rId327" display="www.eric-devaux.fr"/>
+    <hyperlink ref="K191" r:id="rId328" display="Voir"/>
+    <hyperlink ref="K192" r:id="rId329" display="Voir"/>
+    <hyperlink ref="I193" r:id="rId330" display="www.ec3s.fr"/>
+    <hyperlink ref="K193" r:id="rId331" display="Voir"/>
+    <hyperlink ref="I194" r:id="rId332" display="www.gueudry.fr"/>
+    <hyperlink ref="K194" r:id="rId333" display="Voir"/>
+    <hyperlink ref="I195" r:id="rId334" display="masolution-habitat.fr"/>
+    <hyperlink ref="K195" r:id="rId335" display="Voir"/>
+    <hyperlink ref="I196" r:id="rId336" display="www.socoren.com"/>
+    <hyperlink ref="K196" r:id="rId337" display="Voir"/>
+    <hyperlink ref="I197" r:id="rId338" display="terralia-immobilier.fr"/>
+    <hyperlink ref="K197" r:id="rId339" display="Voir"/>
+    <hyperlink ref="I198" r:id="rId340" display="tribehotels.com/en/france/cabourg"/>
+    <hyperlink ref="K198" r:id="rId341" display="Voir"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7858,8 +12974,8 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId190"/>
-  <legacyDrawing r:id="rId191"/>
+  <drawing r:id="rId342"/>
+  <legacyDrawing r:id="rId343"/>
 </worksheet>
 </file>
 
@@ -7868,7 +12984,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -7882,701 +12998,1061 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>521</v>
+        <v>907</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>522</v>
+        <v>908</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>523</v>
+        <v>909</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>524</v>
+        <v>910</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>525</v>
+        <v>911</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>526</v>
+        <v>912</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>527</v>
+        <v>913</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>528</v>
+        <v>914</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>529</v>
+        <v>915</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>530</v>
+        <v>916</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>531</v>
+        <v>917</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>532</v>
+        <v>918</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>533</v>
+        <v>919</v>
       </c>
       <c r="F2" s="16" t="s">
-        <v>534</v>
+        <v>920</v>
       </c>
       <c r="G2" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H2" s="19"/>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>536</v>
+        <v>922</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>537</v>
+        <v>923</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>538</v>
+        <v>924</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>539</v>
+        <v>925</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>540</v>
+        <v>926</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>541</v>
+        <v>927</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H3" s="19"/>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>542</v>
+        <v>928</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>537</v>
+        <v>923</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>543</v>
+        <v>929</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>544</v>
+        <v>930</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>545</v>
+        <v>931</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>546</v>
+        <v>932</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H4" s="19"/>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>547</v>
+        <v>933</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>537</v>
+        <v>923</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>548</v>
+        <v>934</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>549</v>
+        <v>935</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>550</v>
+        <v>936</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>551</v>
+        <v>937</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H5" s="19"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>552</v>
+        <v>938</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>530</v>
+        <v>916</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>553</v>
+        <v>939</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>532</v>
+        <v>918</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>554</v>
+        <v>940</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>555</v>
+        <v>941</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H6" s="19"/>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>556</v>
+        <v>942</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>557</v>
+        <v>943</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>558</v>
+        <v>944</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>559</v>
+        <v>945</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>560</v>
+        <v>946</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>561</v>
+        <v>947</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H7" s="19"/>
     </row>
     <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>562</v>
+        <v>948</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>557</v>
+        <v>943</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>563</v>
+        <v>949</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>564</v>
+        <v>950</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>565</v>
+        <v>951</v>
       </c>
       <c r="F8" s="16" t="s">
-        <v>541</v>
+        <v>927</v>
       </c>
       <c r="G8" s="16"/>
       <c r="H8" s="19"/>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>566</v>
+        <v>952</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>567</v>
+        <v>953</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>568</v>
+        <v>954</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>569</v>
+        <v>955</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>570</v>
+        <v>956</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>541</v>
+        <v>927</v>
       </c>
       <c r="G9" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H9" s="19"/>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>571</v>
+        <v>957</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>567</v>
+        <v>953</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>568</v>
+        <v>954</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>569</v>
+        <v>955</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>572</v>
+        <v>958</v>
       </c>
       <c r="F10" s="16" t="s">
-        <v>541</v>
+        <v>927</v>
       </c>
       <c r="G10" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H10" s="19"/>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>573</v>
+        <v>959</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>567</v>
+        <v>953</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>568</v>
+        <v>954</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>569</v>
+        <v>955</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>574</v>
+        <v>960</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>541</v>
+        <v>927</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H11" s="19"/>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>575</v>
+        <v>961</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>567</v>
+        <v>953</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>568</v>
+        <v>954</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>569</v>
+        <v>955</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>576</v>
+        <v>962</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>541</v>
+        <v>927</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H12" s="19"/>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>577</v>
+        <v>963</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>567</v>
+        <v>953</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>578</v>
+        <v>964</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>569</v>
+        <v>955</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>579</v>
+        <v>965</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>541</v>
+        <v>927</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H13" s="19"/>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>580</v>
+        <v>966</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>567</v>
+        <v>953</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>581</v>
+        <v>967</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>569</v>
+        <v>955</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>582</v>
+        <v>968</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>541</v>
+        <v>927</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H14" s="19"/>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>583</v>
+        <v>969</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>567</v>
+        <v>953</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>584</v>
+        <v>970</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>569</v>
+        <v>955</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>585</v>
+        <v>971</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>541</v>
+        <v>927</v>
       </c>
       <c r="G15" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H15" s="19"/>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>586</v>
+        <v>972</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>587</v>
+        <v>973</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>588</v>
+        <v>974</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>569</v>
+        <v>955</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>589</v>
+        <v>975</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>541</v>
+        <v>927</v>
       </c>
       <c r="G16" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H16" s="19"/>
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="s">
-        <v>590</v>
+        <v>976</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>591</v>
+        <v>977</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>592</v>
+        <v>978</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>593</v>
+        <v>979</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>594</v>
+        <v>980</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>595</v>
+        <v>981</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H17" s="19"/>
     </row>
     <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>596</v>
+        <v>982</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>591</v>
+        <v>977</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>597</v>
+        <v>983</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>598</v>
+        <v>984</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>599</v>
+        <v>985</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>595</v>
+        <v>981</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H18" s="19"/>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>600</v>
+        <v>986</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>591</v>
+        <v>977</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>601</v>
+        <v>987</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>602</v>
+        <v>988</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>603</v>
+        <v>989</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>595</v>
+        <v>981</v>
       </c>
       <c r="G19" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H19" s="19"/>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>604</v>
+        <v>990</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>605</v>
+        <v>991</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>606</v>
+        <v>992</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>607</v>
+        <v>993</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>608</v>
+        <v>994</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>595</v>
+        <v>981</v>
       </c>
       <c r="G20" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H20" s="19"/>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>609</v>
+        <v>995</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>610</v>
+        <v>996</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>611</v>
+        <v>997</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>612</v>
+        <v>998</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>613</v>
+        <v>999</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>614</v>
+        <v>1000</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H21" s="19"/>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="s">
-        <v>615</v>
+        <v>1001</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>610</v>
+        <v>996</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>616</v>
+        <v>1002</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>617</v>
+        <v>1003</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>618</v>
+        <v>1004</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>619</v>
+        <v>1005</v>
       </c>
       <c r="G22" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H22" s="19"/>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="s">
-        <v>620</v>
+        <v>1006</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>610</v>
+        <v>996</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>621</v>
+        <v>1007</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>622</v>
+        <v>1008</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>623</v>
+        <v>1009</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>595</v>
+        <v>981</v>
       </c>
       <c r="G23" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H23" s="19"/>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="s">
-        <v>624</v>
+        <v>1010</v>
       </c>
       <c r="B24" s="16" t="s">
-        <v>610</v>
+        <v>996</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>625</v>
+        <v>1011</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>549</v>
+        <v>935</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>626</v>
+        <v>1012</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>627</v>
+        <v>1013</v>
       </c>
       <c r="G24" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H24" s="19"/>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
-        <v>628</v>
+        <v>1014</v>
       </c>
       <c r="B25" s="16" t="s">
-        <v>610</v>
+        <v>996</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>629</v>
+        <v>1015</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>630</v>
+        <v>1016</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>631</v>
+        <v>1017</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>632</v>
+        <v>1018</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H25" s="19"/>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="s">
-        <v>633</v>
+        <v>1019</v>
       </c>
       <c r="B26" s="16" t="s">
-        <v>634</v>
+        <v>1020</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>635</v>
+        <v>1021</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>636</v>
+        <v>1022</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>637</v>
+        <v>1023</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>595</v>
+        <v>981</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
       <c r="H26" s="19"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-    </row>
-    <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
-        <v>640</v>
-      </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
-        <v>641</v>
-      </c>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-    </row>
-    <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-    </row>
-    <row r="33" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
-        <v>643</v>
-      </c>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-    </row>
-    <row r="34" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
+    <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="23" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>991</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>1028</v>
+      </c>
+      <c r="G27" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="H27" s="19"/>
+    </row>
+    <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="23" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>991</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="H28" s="19"/>
+    </row>
+    <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="23" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>991</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>1033</v>
+      </c>
+      <c r="G29" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="H29" s="19"/>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="23" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>991</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G30" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="H30" s="19"/>
+    </row>
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="23" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>991</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>1044</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>1045</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="H31" s="19"/>
+    </row>
+    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="23" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>923</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="H32" s="19"/>
+    </row>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="23" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>923</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>1055</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>1056</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>981</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="H33" s="19"/>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="23" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>923</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>1061</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="H34" s="19"/>
+    </row>
+    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="23" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>1063</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>1066</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="H35" s="19"/>
+    </row>
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="23" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>916</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>981</v>
+      </c>
+      <c r="G36" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="H36" s="19"/>
+    </row>
+    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="23" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>996</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="H37" s="19"/>
+    </row>
+    <row r="38" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="23" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>996</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G38" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="H38" s="19"/>
+    </row>
+    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="23" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>996</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="H39" s="19"/>
+    </row>
+    <row r="40" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="23" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>996</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G40" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="H40" s="19"/>
+    </row>
+    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="23" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G41" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="H41" s="19"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="6" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+    </row>
+    <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+    </row>
+    <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+    </row>
+    <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+    </row>
+    <row r="48" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+    </row>
+    <row r="49" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A49:F49"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="Ouvrir"/>
@@ -8603,6 +14079,21 @@
     <hyperlink ref="G24" r:id="rId22" display="Ouvrir"/>
     <hyperlink ref="G25" r:id="rId23" display="Ouvrir"/>
     <hyperlink ref="G26" r:id="rId24" display="Ouvrir"/>
+    <hyperlink ref="G27" r:id="rId25" display="Ouvrir"/>
+    <hyperlink ref="G28" r:id="rId26" display="Ouvrir"/>
+    <hyperlink ref="G29" r:id="rId27" display="Ouvrir"/>
+    <hyperlink ref="G30" r:id="rId28" display="Ouvrir"/>
+    <hyperlink ref="G31" r:id="rId29" display="Ouvrir"/>
+    <hyperlink ref="G32" r:id="rId30" display="Ouvrir"/>
+    <hyperlink ref="G33" r:id="rId31" display="Ouvrir"/>
+    <hyperlink ref="G34" r:id="rId32" display="Ouvrir"/>
+    <hyperlink ref="G35" r:id="rId33" display="Ouvrir"/>
+    <hyperlink ref="G36" r:id="rId34" display="Ouvrir"/>
+    <hyperlink ref="G37" r:id="rId35" display="Ouvrir"/>
+    <hyperlink ref="G38" r:id="rId36" display="Ouvrir"/>
+    <hyperlink ref="G39" r:id="rId37" display="Ouvrir"/>
+    <hyperlink ref="G40" r:id="rId38" display="Ouvrir"/>
+    <hyperlink ref="G41" r:id="rId39" display="Ouvrir"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8619,7 +14110,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -8630,205 +14121,290 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>521</v>
+        <v>907</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>645</v>
+        <v>1099</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>646</v>
+        <v>1100</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>525</v>
+        <v>911</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>527</v>
+        <v>913</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>647</v>
+        <v>1101</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>648</v>
+        <v>1102</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>649</v>
+        <v>1103</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>650</v>
+        <v>1104</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>651</v>
+        <v>1105</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>652</v>
+        <v>1106</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>311</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>653</v>
+        <v>1107</v>
       </c>
       <c r="E3" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>654</v>
+        <v>1108</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>655</v>
+        <v>1109</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>656</v>
+        <v>1110</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>657</v>
+        <v>1111</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>658</v>
+        <v>1112</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>659</v>
+        <v>1113</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>660</v>
+        <v>1114</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>661</v>
+        <v>1115</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>662</v>
+        <v>1116</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>663</v>
+        <v>1117</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>664</v>
+        <v>1118</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>665</v>
+        <v>1119</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>666</v>
+        <v>1120</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>667</v>
+        <v>1121</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>668</v>
+        <v>1122</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>669</v>
+        <v>1123</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>670</v>
+        <v>1124</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>671</v>
+        <v>1125</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>672</v>
+        <v>1126</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>673</v>
+        <v>1127</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>674</v>
+        <v>1128</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>675</v>
+        <v>1129</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>676</v>
+        <v>1130</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>677</v>
+        <v>1131</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>678</v>
+        <v>1132</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>679</v>
+        <v>1133</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>680</v>
+        <v>1134</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>681</v>
+        <v>1135</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>682</v>
+        <v>1136</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>683</v>
+        <v>1137</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>684</v>
+        <v>1138</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>685</v>
+        <v>1139</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>686</v>
+        <v>1140</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>687</v>
+        <v>1141</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>688</v>
-      </c>
-      <c r="E12" s="25"/>
+        <v>1142</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="23" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="23" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>1148</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>1149</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E15" s="24" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="23" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E16" s="24" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="23" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>1161</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E17" s="25"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -8842,6 +14418,11 @@
     <hyperlink ref="E9" r:id="rId8" display="Ouvrir"/>
     <hyperlink ref="E10" r:id="rId9" display="Ouvrir"/>
     <hyperlink ref="E11" r:id="rId10" display="Ouvrir"/>
+    <hyperlink ref="E12" r:id="rId11" display="Ouvrir"/>
+    <hyperlink ref="E13" r:id="rId12" display="Ouvrir"/>
+    <hyperlink ref="E14" r:id="rId13" display="Ouvrir"/>
+    <hyperlink ref="E15" r:id="rId14" display="Ouvrir"/>
+    <hyperlink ref="E16" r:id="rId15" display="Ouvrir"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -8868,10 +14449,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>689</v>
+        <v>1163</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>690</v>
+        <v>1164</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>41</v>
@@ -8879,117 +14460,117 @@
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>691</v>
+        <v>1165</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>692</v>
+        <v>1166</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>693</v>
+        <v>1167</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>694</v>
+        <v>1168</v>
       </c>
       <c r="C3" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>695</v>
+        <v>1169</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>696</v>
+        <v>1170</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>697</v>
+        <v>1171</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>698</v>
+        <v>1172</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>699</v>
+        <v>1173</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>700</v>
+        <v>1174</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>701</v>
+        <v>1175</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>702</v>
+        <v>1176</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>703</v>
+        <v>1177</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>704</v>
+        <v>1178</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>705</v>
+        <v>1179</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>706</v>
+        <v>1180</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>707</v>
+        <v>1181</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>708</v>
+        <v>1182</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>709</v>
+        <v>1183</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>710</v>
+        <v>1184</v>
       </c>
       <c r="C11" s="24" t="s">
-        <v>535</v>
+        <v>921</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>711</v>
+        <v>1185</v>
       </c>
     </row>
   </sheetData>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -11,8 +11,9 @@
     <sheet name="Mode d'emploi" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Prospects" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Particuliers" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Plateformes pros" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Règles" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Groupes Facebook" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Plateformes pros" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Règles" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Prospects!$A$1:$P$198</definedName>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2327" uniqueCount="1186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2480" uniqueCount="1254">
   <si>
     <t xml:space="preserve">Prospection MINYALA — mode d'emploi</t>
   </si>
@@ -80,7 +81,7 @@
     <t xml:space="preserve">4. Particuliers : pas de liste de personnes (interdit sans leur accord). L'onglet Particuliers liste où les trouver : annonces, forums, foires, publicité.</t>
   </si>
   <si>
-    <t xml:space="preserve">5. Onglet Règles : ce qui est autorisé pour appeler, écrire ou publier. Important : on ne peut plus appeler un particulier sans son accord.</t>
+    <t xml:space="preserve">5. Onglet Groupes Facebook : groupes repérés, à approcher avec l'accord des administrateurs (jamais d'extraction de membres). Onglet Règles : ce qui est autorisé pour appeler, écrire ou publier. Important : on ne peut plus appeler un particulier sans son accord.</t>
   </si>
   <si>
     <t xml:space="preserve">Les entreprises ont été vérifiées sur leur site ou un annuaire en ligne (08/10 et 12/10/2026). Vérifiez avant de vous déplacer.</t>
@@ -3360,6 +3361,210 @@
   </si>
   <si>
     <t xml:space="preserve">• À décider : échantillons à retirer à Gennevilliers, tarif pour poseurs partenaires. Rien de cela n'existe aujourd'hui sur le site.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groupe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Membres (source, date)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demande admin le</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réponse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publié le</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu sais que tu viens de Rouen quand…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rouen (76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communauté de ville</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~48 000 (ici.fr, 2019)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prioritaire Normandie. Rejoindre avec la Page, lire le règlement, écrire à l'admin avant de publier une seule annonce. Tous les messages y sont validés par l'admin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réseau « Tu sais que tu viens de… » (≈50 groupes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seine-Maritime, Eure, Caen, Lisieux…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réseau de groupes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~500 000 abonnés au total (ici.fr, 2019)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plutôt qu'un groupe à la fois : demander à l'administrateur du réseau s'il existe une offre commerçant ou un partenariat payant (« Tu sais que tu viens de gagner » en 2019, à vérifier).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu sais que tu viens de… Caen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caen (14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non publié</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejoindre avec la Page, lire le règlement, écrire à l'admin avant de publier une seule annonce.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu sais que tu viens de… Le Havre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Havre (76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu sais que tu viens de… Évreux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Évreux (27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 000+ (ici.fr, 2016–2019)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu sais que tu viens de… Louviers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Louviers (27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu sais que tu viens de… Bernay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bernay (27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejoindre avec la Page, lire le règlement, écrire à l'admin avant de publier une seule annonce. Beaucoup de maisons avec jardin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu sais que tu viens de… Le Neubourg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Neubourg (27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu sais que tu viens de… Dieppe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dieppe (76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vérifier qu'il est actif (source 2016). Rejoindre avec la Page, lire le règlement, écrire à l'admin avant de publier une seule annonce.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu sais que tu viens de… Fécamp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fécamp (76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résidences secondaires du littoral. Rejoindre avec la Page, lire le règlement, écrire à l'admin avant de publier une seule annonce.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu sais que tu viens de… Yvetot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yvetot (76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu sais que tu viens de… Barentin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barentin (76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu sais que tu viens de… Bolbec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bolbec (76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu sais que tu viens de… Pavilly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pavilly (76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu sais que tu viens de… Lillebonne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lillebonne (76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu sais que tu viens de… Notre-Dame-de-Gravenchon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Port-Jérôme-sur-Seine (76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petit groupe, priorité basse. Rejoindre avec la Page, lire le règlement, écrire à l'admin avant de publier une seule annonce.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tu sais que tu viens de… Saint-Romain-de-Colbosc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint-Romain-de-Colbosc (76)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groupe de la ville de Rueil-Malmaison</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rueil-Malmaison (92)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 000+ (ici.fr, 2024)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prioritaire Île-de-France : les commerçants y publient déjà. Rejoindre avec la Page, lire le règlement, écrire à l'admin avant de publier une seule annonce.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groupe de quartier Vallée de Fécamp / Picpus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paris 12e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priorité basse (surtout des appartements). Seulement si le règlement accepte les pros.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artisans et Auto-entrepreneurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France (B2B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Groupe pro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~5 400, privé (2023)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se présenter comme fournisseur aux carreleurs, maçons et paysagistes. Pas de démarchage en message privé.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Liens et effectifs viennent d'articles de presse (2016–2024) : vérifiez que chaque groupe existe toujours, son nom exact et son règlement une fois connecté.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Une Page ne peut que demander à rejoindre un groupe ; si les Pages ne sont pas admises, demandez à l'admin comment un professionnel peut publier.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Aucun groupe thématique (piscine, jardin, déstockage) ni groupe de Gennevilliers, du 95, du 78 ou du 93 n'a pu être confirmé : cherchez-les vous-même dans Facebook avec « travaux maison 92 », « piscine Île-de-France », « bons plans matériaux ».</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Jamais d'extraction de membres ni de messages privés non sollicités aux membres (RGPD et règles de Facebook).</t>
   </si>
   <si>
     <t xml:space="preserve">Pour qui</t>
@@ -14110,6 +14315,678 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="13" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>908</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>911</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>913</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>1101</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>1102</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="23" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>1108</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H2" s="19"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="19"/>
+    </row>
+    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="23" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F3" s="16"/>
+      <c r="G3" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="19"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="19"/>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="23" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G4" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="19"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="19"/>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="23" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G5" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="19"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="19"/>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="23" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="19"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="19"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="23" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G7" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="19"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="19"/>
+    </row>
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="23" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8" s="19"/>
+      <c r="I8" s="18"/>
+      <c r="J8" s="19"/>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="23" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H9" s="19"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="19"/>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="23" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="19"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="19"/>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="23" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="19"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="19"/>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="23" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="19"/>
+      <c r="I12" s="18"/>
+      <c r="J12" s="19"/>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="23" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G13" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="19"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="19"/>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="23" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="19"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="19"/>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="23" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15" s="19"/>
+      <c r="I15" s="18"/>
+      <c r="J15" s="19"/>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="23" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16" s="19"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="19"/>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="23" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H17" s="19"/>
+      <c r="I17" s="18"/>
+      <c r="J17" s="19"/>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="23" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H18" s="19"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="19"/>
+    </row>
+    <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F19" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G19" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="19"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="19"/>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="23" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>1116</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H20" s="19"/>
+      <c r="I20" s="18"/>
+      <c r="J20" s="19"/>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="23" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>921</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="H21" s="19"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="19"/>
+    </row>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A26:F26"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I80" type="list">
+      <formula1>"En attente,Accepté,Refusé,Pages non admises"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" display="Ouvrir"/>
+    <hyperlink ref="G2" r:id="rId2" display="Voir"/>
+    <hyperlink ref="G3" r:id="rId3" display="Voir"/>
+    <hyperlink ref="F4" r:id="rId4" display="Ouvrir"/>
+    <hyperlink ref="G4" r:id="rId5" display="Voir"/>
+    <hyperlink ref="F5" r:id="rId6" display="Ouvrir"/>
+    <hyperlink ref="G5" r:id="rId7" display="Voir"/>
+    <hyperlink ref="F6" r:id="rId8" display="Ouvrir"/>
+    <hyperlink ref="G6" r:id="rId9" display="Voir"/>
+    <hyperlink ref="F7" r:id="rId10" display="Ouvrir"/>
+    <hyperlink ref="G7" r:id="rId11" display="Voir"/>
+    <hyperlink ref="F8" r:id="rId12" display="Ouvrir"/>
+    <hyperlink ref="G8" r:id="rId13" display="Voir"/>
+    <hyperlink ref="F9" r:id="rId14" display="Ouvrir"/>
+    <hyperlink ref="G9" r:id="rId15" display="Voir"/>
+    <hyperlink ref="F10" r:id="rId16" display="Ouvrir"/>
+    <hyperlink ref="G10" r:id="rId17" display="Voir"/>
+    <hyperlink ref="F11" r:id="rId18" display="Ouvrir"/>
+    <hyperlink ref="G11" r:id="rId19" display="Voir"/>
+    <hyperlink ref="F12" r:id="rId20" display="Ouvrir"/>
+    <hyperlink ref="G12" r:id="rId21" display="Voir"/>
+    <hyperlink ref="F13" r:id="rId22" display="Ouvrir"/>
+    <hyperlink ref="G13" r:id="rId23" display="Voir"/>
+    <hyperlink ref="F14" r:id="rId24" display="Ouvrir"/>
+    <hyperlink ref="G14" r:id="rId25" display="Voir"/>
+    <hyperlink ref="F15" r:id="rId26" display="Ouvrir"/>
+    <hyperlink ref="G15" r:id="rId27" display="Voir"/>
+    <hyperlink ref="F16" r:id="rId28" display="Ouvrir"/>
+    <hyperlink ref="G16" r:id="rId29" display="Voir"/>
+    <hyperlink ref="F17" r:id="rId30" display="Ouvrir"/>
+    <hyperlink ref="G17" r:id="rId31" display="Voir"/>
+    <hyperlink ref="F18" r:id="rId32" display="Ouvrir"/>
+    <hyperlink ref="G18" r:id="rId33" display="Voir"/>
+    <hyperlink ref="F19" r:id="rId34" display="Ouvrir"/>
+    <hyperlink ref="G19" r:id="rId35" display="Voir"/>
+    <hyperlink ref="F20" r:id="rId36" display="Ouvrir"/>
+    <hyperlink ref="G20" r:id="rId37" display="Voir"/>
+    <hyperlink ref="F21" r:id="rId38" display="Ouvrir"/>
+    <hyperlink ref="G21" r:id="rId39" display="Voir"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -14124,10 +15001,10 @@
         <v>907</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>1099</v>
+        <v>1167</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>1100</v>
+        <v>1168</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>911</v>
@@ -14138,16 +15015,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>1101</v>
+        <v>1169</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>1102</v>
+        <v>1170</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>1103</v>
+        <v>1171</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>1104</v>
+        <v>1172</v>
       </c>
       <c r="E2" s="24" t="s">
         <v>921</v>
@@ -14155,16 +15032,16 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>1105</v>
+        <v>1173</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>1106</v>
+        <v>1174</v>
       </c>
       <c r="C3" s="16" t="s">
         <v>311</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>1107</v>
+        <v>1175</v>
       </c>
       <c r="E3" s="24" t="s">
         <v>921</v>
@@ -14172,16 +15049,16 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>1108</v>
+        <v>1176</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>1109</v>
+        <v>1177</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>1110</v>
+        <v>1178</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>1111</v>
+        <v>1179</v>
       </c>
       <c r="E4" s="24" t="s">
         <v>921</v>
@@ -14189,16 +15066,16 @@
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>1112</v>
+        <v>1180</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>1113</v>
+        <v>1181</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>1114</v>
+        <v>1182</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>1115</v>
+        <v>1183</v>
       </c>
       <c r="E5" s="24" t="s">
         <v>921</v>
@@ -14206,16 +15083,16 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>1116</v>
+        <v>1184</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>1117</v>
+        <v>1185</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>1118</v>
+        <v>1186</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>1119</v>
+        <v>1187</v>
       </c>
       <c r="E6" s="24" t="s">
         <v>921</v>
@@ -14223,16 +15100,16 @@
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>1120</v>
+        <v>1188</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>1121</v>
+        <v>1189</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>1122</v>
+        <v>1190</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>1123</v>
+        <v>1191</v>
       </c>
       <c r="E7" s="24" t="s">
         <v>921</v>
@@ -14240,16 +15117,16 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>1124</v>
+        <v>1192</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>1125</v>
+        <v>1193</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>1126</v>
+        <v>1194</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>1127</v>
+        <v>1195</v>
       </c>
       <c r="E8" s="24" t="s">
         <v>921</v>
@@ -14257,16 +15134,16 @@
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>1128</v>
+        <v>1196</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>1129</v>
+        <v>1197</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>1130</v>
+        <v>1198</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>1131</v>
+        <v>1199</v>
       </c>
       <c r="E9" s="24" t="s">
         <v>921</v>
@@ -14274,16 +15151,16 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>1132</v>
+        <v>1200</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>1133</v>
+        <v>1201</v>
       </c>
       <c r="C10" s="16" t="s">
         <v>46</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>1134</v>
+        <v>1202</v>
       </c>
       <c r="E10" s="24" t="s">
         <v>921</v>
@@ -14291,16 +15168,16 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>1135</v>
+        <v>1203</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>1136</v>
+        <v>1204</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>1137</v>
+        <v>1205</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>1138</v>
+        <v>1206</v>
       </c>
       <c r="E11" s="24" t="s">
         <v>921</v>
@@ -14308,16 +15185,16 @@
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>1139</v>
+        <v>1207</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>1140</v>
+        <v>1208</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>1141</v>
+        <v>1209</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>1142</v>
+        <v>1210</v>
       </c>
       <c r="E12" s="24" t="s">
         <v>921</v>
@@ -14325,16 +15202,16 @@
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>1143</v>
+        <v>1211</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>1144</v>
+        <v>1212</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>1145</v>
+        <v>1213</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>1146</v>
+        <v>1214</v>
       </c>
       <c r="E13" s="24" t="s">
         <v>921</v>
@@ -14342,16 +15219,16 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>1147</v>
+        <v>1215</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>1148</v>
+        <v>1216</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>1149</v>
+        <v>1217</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>1150</v>
+        <v>1218</v>
       </c>
       <c r="E14" s="24" t="s">
         <v>921</v>
@@ -14359,16 +15236,16 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>1151</v>
+        <v>1219</v>
       </c>
       <c r="B15" s="16" t="s">
-        <v>1152</v>
+        <v>1220</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>1153</v>
+        <v>1221</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>1154</v>
+        <v>1222</v>
       </c>
       <c r="E15" s="24" t="s">
         <v>921</v>
@@ -14376,16 +15253,16 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>1155</v>
+        <v>1223</v>
       </c>
       <c r="B16" s="16" t="s">
-        <v>1156</v>
+        <v>1224</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>1157</v>
+        <v>1225</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>1158</v>
+        <v>1226</v>
       </c>
       <c r="E16" s="24" t="s">
         <v>921</v>
@@ -14393,16 +15270,16 @@
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="s">
-        <v>1159</v>
+        <v>1227</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>1160</v>
+        <v>1228</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>1161</v>
+        <v>1229</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>1162</v>
+        <v>1230</v>
       </c>
       <c r="E17" s="25"/>
     </row>
@@ -14434,7 +15311,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -14449,10 +15326,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="13" t="s">
-        <v>1163</v>
+        <v>1231</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>1164</v>
+        <v>1232</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>41</v>
@@ -14460,10 +15337,10 @@
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="23" t="s">
-        <v>1165</v>
+        <v>1233</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>1166</v>
+        <v>1234</v>
       </c>
       <c r="C2" s="24" t="s">
         <v>921</v>
@@ -14471,10 +15348,10 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="23" t="s">
-        <v>1167</v>
+        <v>1235</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>1168</v>
+        <v>1236</v>
       </c>
       <c r="C3" s="24" t="s">
         <v>921</v>
@@ -14482,10 +15359,10 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>1169</v>
+        <v>1237</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>1170</v>
+        <v>1238</v>
       </c>
       <c r="C4" s="24" t="s">
         <v>921</v>
@@ -14493,10 +15370,10 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>1171</v>
+        <v>1239</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>1172</v>
+        <v>1240</v>
       </c>
       <c r="C5" s="24" t="s">
         <v>921</v>
@@ -14504,10 +15381,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>1173</v>
+        <v>1241</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>1174</v>
+        <v>1242</v>
       </c>
       <c r="C6" s="24" t="s">
         <v>921</v>
@@ -14515,10 +15392,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>1175</v>
+        <v>1243</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>1176</v>
+        <v>1244</v>
       </c>
       <c r="C7" s="24" t="s">
         <v>921</v>
@@ -14526,10 +15403,10 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>1177</v>
+        <v>1245</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>1178</v>
+        <v>1246</v>
       </c>
       <c r="C8" s="24" t="s">
         <v>921</v>
@@ -14537,10 +15414,10 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>1179</v>
+        <v>1247</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>1180</v>
+        <v>1248</v>
       </c>
       <c r="C9" s="24" t="s">
         <v>921</v>
@@ -14548,10 +15425,10 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>1181</v>
+        <v>1249</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>1182</v>
+        <v>1250</v>
       </c>
       <c r="C10" s="24" t="s">
         <v>921</v>
@@ -14559,10 +15436,10 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>1183</v>
+        <v>1251</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>1184</v>
+        <v>1252</v>
       </c>
       <c r="C11" s="24" t="s">
         <v>921</v>
@@ -14570,7 +15447,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>1185</v>
+        <v>1253</v>
       </c>
     </row>
   </sheetData>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -11,11 +11,13 @@
     <sheet name="Mode d'emploi" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Prospects" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Particuliers" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Groupes Facebook" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Plateformes pros" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Règles" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Demandes RFQ" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Groupes Facebook" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Plateformes pros" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Règles" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Demandes RFQ'!$A$1:$N$53</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Prospects!$A$1:$Q$198</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -76,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2499" uniqueCount="1269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3140" uniqueCount="1616">
   <si>
     <t xml:space="preserve">Prospection MINYALA — mode d'emploi</t>
   </si>
@@ -93,7 +95,7 @@
     <t xml:space="preserve">4. Particuliers : pas de liste de personnes (interdit sans leur accord). L'onglet Particuliers liste où les trouver : annonces, forums, foires, publicité.</t>
   </si>
   <si>
-    <t xml:space="preserve">5. Onglet Groupes Facebook : groupes repérés, à approcher avec l'accord des administrateurs (jamais d'extraction de membres). Onglet Règles : ce qui est autorisé pour appeler, écrire ou publier. Important : on ne peut plus appeler un particulier sans son accord.</t>
+    <t xml:space="preserve">5. Onglet Demandes RFQ : demandes d'acheteurs pros repérées sur StoneContact, StoneAdd, Alibaba, go4WorldBusiness, TradeKey (répondre depuis votre compte). Onglet Groupes Facebook : groupes repérés, à approcher avec l'accord des administrateurs (jamais d'extraction de membres). Onglet Règles : ce qui est autorisé pour appeler, écrire ou publier. Important : on ne peut plus appeler un particulier sans son accord.</t>
   </si>
   <si>
     <t xml:space="preserve">Les entreprises ont été vérifiées sur leur site ou un annuaire en ligne (08/10 et 12/10/2026). Vérifiez avant de vous déplacer.</t>
@@ -3387,6 +3389,993 @@
     <t xml:space="preserve">• À décider : échantillons à retirer à Gennevilliers, tarif pour poseurs partenaires. Rien de cela n'existe aujourd'hui sur le site.</t>
   </si>
   <si>
+    <t xml:space="preserve">Correspondance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vérifiée ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plateforme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demande</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pourquoi / attention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Répondu le</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StoneAdd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy Sunny Marble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunny Marble (catégorie « Egypt Marbles »), donc la pierre calcaire Sunny de Minya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">non précisée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">non précisé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Autriche (livraisons Autriche et sud de l'Allemagne)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pierre égyptienne Sunny, de la même famille que la Minyala (Minya). L'acheteur est un grossiste qui livre toute l'Autriche et le sud de l'Allemagne, ce qui en fait un débouché européen proche. Il demande si la pierre résiste au gel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À étudier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ataija Creme Limestone Inquiry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcaire crème Ataija (Portugal) pour terrasse et piscine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belgique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demande de calcaire crème en petite quantité (100 m²) depuis la Belgique, à distance de camion de Gennevilliers. La Minyala peut être proposée comme alternative beige. Attention : l'usage est extérieur (piscine), il faut donc vérifier la résistance au gel et l'antidérapant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alibaba RFQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfekte Steinfliesen aus Kalkstein und Marmor für Innenräume, Natürliche Kalksteinplatten für Hausrenovierung und Wohnprojekte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carreaux de sol en pierre naturelle (calcaire ou marbre) pour l'intérieur et la rénovation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40 pièces (MOQ en m² demandé)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suisse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">affiché « 10 days ago » le 2026-10-12 (vers le 2026-10-02)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carreaux de calcaire pour sol intérieur, acheteur en Suisse, pays voisin de la France. Il demande un catalogue et un MOQ en m², ce qui correspond à une vente sur stock à partir de 25 m². Pour répondre sur Alibaba, il faut un abonnement vendeur payant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non (StoneContact bloqué)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StoneContact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beaumaniere Limestone Slabs &amp; Tiles, France Beige Limestone from France (buyer request on the listing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unpolished limestone tile, warm beige, grey or brown, not too light (Beaumaniere given as the reference)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">about 150 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">at least 60x30 or 60x40 cm, unpolished</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rotterdam, Netherlands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcaire beige non poli, format minimum 60x30, 150 m², destination Pays-Bas (Rotterdam) : correspond très bien à MINYALA 30x60 en stock. Mais la demande n'est pas datée et est probablement ancienne.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sinai Pearl Grey Limestone Slabs&amp;Tiles from Egypt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sinai Pearl Grey limestone (Egyptian) tiles, with a sample requested before ordering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France (clients in France and the UK)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entreprise française de rénovation qui cherche du calcaire égyptien pour des clients en France et au Royaume-Uni, 150 m², échantillon d'abord : le stock de Gennevilliers permet un échantillon et une livraison rapides. La teinte demandée est grise et non crème, et la demande n'est pas datée.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Possible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marble Slabs Inquiry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tranches de marbre, environ 150 m², achat sur stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">environ 150 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'acheteur est en France et veut environ 150 m² disponibles en stock, avec visite sur place. Un stock à Gennevilliers convient très bien sur la logistique. En revanche, il cherche du « marbre » en tranches et non des carreaux 30×60 : à proposer comme alternative.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">go4WorldBusiness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wanted : Marble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marbre blanc ou crème, dimensions sur mesure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 conteneur 20'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sur mesure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Espagne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acheteur espagnol qui cherche du marbre crème et préfère un fournisseur européen, ce qui avantage un vendeur basé en France. Le volume (1 conteneur 20') dépasse sans doute le stock, et le paiement se fait FOB par virement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wanted : Stone Articles Like Marble, Granite, Limestone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Articles en pierre (marbre, granit, calcaire, ardoise) pour la construction et la revente (HS 680299)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acheteur en France qui inclut le calcaire, pour la revente et la distribution. Le produit reste vague (articles décoratifs) et porte sur 1 conteneur 20'. La proximité est un atout.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wanted : Natural Stones Like Sandstone, Limestone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grès, calcaire et mosaïques de pierre naturelle, tailles sur mesure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allemagne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acheteur allemand qui inclut le calcaire en tailles sur mesure. La quantité (1 conteneur 20') et la couleur ne sont pas précisées. L'annonce, du 26 juin, approche de sa date d'expiration.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy Crema Marfil tiles 305x305x1cm Standard Range</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carreaux de marbre beige Crema Marfil 30,5×30,5×1 cm, polis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30,5×30,5×1 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carreaux de marbre beige demandés depuis l'Espagne, avec une question sur le stock. Le format (30,5×30,5×1 cm) et la pierre (espagnole) ne sont pas les mêmes que la Minyala 30×60×2. À proposer comme alternative moins chère. La demande date d'avril.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy Moscato Beige Marble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marbre beige Moscato (Espagne)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Irlande</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pierre beige, acheteur en Irlande (UE). La demande vise une référence espagnole précise et ne donne ni format ni quantité.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy THALA BEIGE Marbles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thala Beige (pierre beige tunisienne)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pierre beige nord-africaine du même registre que la Minyala, acheteur en Italie. La demande est générique et sans quantité.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy Sinai Pearl Limestone Stairs and Steps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marches et escaliers en calcaire égyptien Sinai Pearl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">marches (non précisé)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kosovo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcaire égyptien, acheteur au Kosovo (Europe hors UE). Il cherche des marches et non des carreaux 30×60, et la Sinai Pearl vient du Sinaï, pas de Minya.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy Turkey Ivory Travertine Slab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travertin ivoire (Turquie), 120 m², livraison à Kalamata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kalamata, Grèce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pierre claire en petite quantité (120 m²) pour la Grèce, dans l'UE. C'est du travertin et non du calcaire, et le transport jusqu'à Kalamata coûte cher depuis Paris.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beige Travertine KARAMAN Inquiry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Travertin beige de Karaman : dalles 1,2×40,6×61, margelles 3×33×61 et angles 3×48×48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">non précisée (importateur d'environ 40 conteneurs par an)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,2×40,6×61 cm ; 3×33×61 cm ; 3×48×48 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France (Sud-Ouest)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Importateur français de pierre beige installé dans le Sud-Ouest (environ 40 conteneurs par an), insatisfait de ses fournisseurs actuels. C'est un bon prospect commercial, mais il demande du travertin turc dans des formats précis, pas du calcaire 30×60.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galala Extra - Galala Marble Quarry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commercial-grade Galala Extra (Egyptian beige), bush-hammered top face, other faces sawn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">about 3,950 m² in total (2,570 m² of it in 60x30)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60x30x7.5, 60x25x7.5, 30x30x7.5, 100x30x7.5, 100x50x7.5 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France (French project)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pierre beige égyptienne pour un projet en France avec un gros volume en 60x30, mais l'épaisseur demandée est de 7,5 cm (dallage), contre 2 cm pour MINYALA. Demande non datée.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sinai Pearl Limestone Tiles &amp; Slabs, Grey Limestone Egypt Polished Floor Covering Tiles, Walling Tiles from Egypt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honed Sinai Pearl limestone tiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">600x400x15 mm, honed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cardiff, Wales, UK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petit volume (30 m², au-dessus du minimum de 25 m²) de calcaire égyptien adouci livré au Royaume-Uni : MINYALA peut proposer le 30x60x2 comme alternative au 60x40x1,5. Demande non datée.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buyers from United Kingdom - Global Stone Buyer Center (RFQ for Oman White Limestone)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oman White limestone, as slabs or cut-to-size tiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slabs or cut-to-size, 20 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, UK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May 14, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demande récente (mai 2026), 65 m² en 20 mm livrés à Londres : volume et épaisseur conviennent. La couleur demandée est blanche (Oman White), pas crème, donc MINYALA ne peut être proposé qu'en alternative.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Westhill Limestone Honed Tiles from United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Honed beige limestone tiles (Westhill), larger formats around 1000x500 also asked about</t>
+  </si>
+  <si>
+    <t xml:space="preserve">about 63 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">honed; asks about about 1000x500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page dated 2025-02-08 (request date not confirmed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcaire beige adouci pour une rénovation à Londres, environ 63 m² : petit volume compatible avec le stock. L'acheteur demande un prix au m² ; il vise une pierre précise et peut-être un grand format.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beige Limestone Floor Tiles from United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polished grey-beige Jura limestone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 m (as written by the buyer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60x40 cm, polished</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcaire beige, 150 m² sur une annonce britannique : MINYALA pourrait être proposé en 30x60 à la place du 60x40 Jura poli. Destination non confirmée et demande non datée.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunny Menia Marble Slabs, Tiles from Egypt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slabs and tiles 2-4 cm thick in various formats, 'specially Sinai Pearl or similar' (on a Sunny Menia listing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2, 3 and 4 cm; various formats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barcelona, Spain (CIF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acheteur espagnol (CIF Barcelone) intéressé par la pierre beige égyptienne « Sinai Pearl ou similaire » sur une annonce Sunny Menia, donc la famille de MINYALA. Formats variés de 2 à 4 cm ; demande non datée.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galala Beige Marble Tiles &amp; Slab from Egypt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galala (Egyptian beige), 80x80x2 honed tiles filled with epoxy resin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7,000 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80x80x2 cm, honed, epoxy-filled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain (Spanish company)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projet espagnol de 7 000 m² en pierre beige égyptienne de 2 cm adoucie : la teinte et l'épaisseur conviennent, mais le format 80x80 et le volume dépassent le stock. Demande non datée.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dijon Limestone Honed Finish Floor Tiles from United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dijon beige limestone for exterior paving</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,000 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60x30, 60x20, 60x15, 40x40 cm; 5 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spain (company located in Spain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcaire beige en 60x30 demandé par une société espagnole d'import-export (2 000 m²), mais pour du dallage extérieur en 5 cm : l'épaisseur ne correspond pas aux 2 cm de MINYALA. Demande non datée.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Stone Buyer Center (RFQ for Portuguese Moleanos Beige Limestone)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cut-to-size honed tiles in Moleanos Beige limestone (Portugal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cut-to-size, honed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Russia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May 26, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcaire beige adouci sur mesure, demande récente (mai 2026), mais l'acheteur veut du Moleanos portugais et livraison en Russie (EXW). La substitution par MINYALA est peu probable et le volume (2 000 m²) dépasse le stock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sinai Pearl Limestone - Tumbled Limestone - Egyptian Limestone Supplier from Egypt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sinai Pearl limestone tiles (Egyptian)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 to 200 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">preferably 600x900 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petit volume (100 à 200 m²) de calcaire égyptien, adapté à un stock disponible. Format souhaité 60x90, destination non indiquée, demande non datée.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sinai Pearl Limestone - Beige Limestone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sinai Pearl limestone (Egyptian), for a trader's client</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,000 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Négociant qui cherche du calcaire beige égyptien pour un client : piste pour proposer MINYALA en alternative, mais 4 000 m² dépasse probablement le stock. Destination et date non indiquées.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buyers from France - Global Stone Buyer Center (RFQ for beige sandstone flooring)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beige sandstone flooring with a natural surface (photos attached)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">about 300 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 21, 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acheteur en France, environ 300 m² de dallage beige : MINYALA pourrait être proposé comme alternative calcaire. La demande vise du grès et date d'août 2025, juste au-delà de 12 mois.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buyers from France - Global Stone Buyer Center (RFQ for Buffon Banc Limestone)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buffon Banc limestone (French beige limestone); photos and price per m² requested</t>
+  </si>
+  <si>
+    <t xml:space="preserve">July 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acheteur français de calcaire beige : on peut lui proposer MINYALA comme alternative moins chère livrée depuis Gennevilliers. Il vise toutefois une pierre française précise, et la demande date de juillet 2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buyers from Ireland - Global Stone Buyer Center (RFQ for Jerusalem Gold Limestone tiles and cobbles)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem Gold limestone: sanded exterior slabs, kerbs, tumbled cobbles (landscaping)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a few hundred metres</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sanded finish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ireland</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 27, 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcaire doré-beige pour l'extérieur en Irlande, « quelques centaines de mètres » : MINYALA peut être proposé pour les dalles. Il s'agit surtout d'aménagement paysager, et la demande date d'août 2025.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oui (corrigée)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunny Beige Marble Tiles Quotation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carreaux de Sunny Beige égyptien en petit format (2×2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2×2 (pouces)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">États-Unis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correction : Size: '2x2' (units not stated on the page; the buyer also asks whether smaller sizes exist). Quantity: not stated. Destination: USA. Date: 2026-05-06. — Le produit est exactement la famille Sunny de Minya, mais l'acheteur est aux États-Unis et veut des mosaïques 2×2 pouces. La destination est lointaine et le format ne correspond pas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulk Inquiry - 11000 M2 Beige Marble Slabs 60x120cmx2cm EXW Factory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaques de marbre beige clair/crème 60×120×2 cm pour façade, type Silvia Menia ou Sunny Light</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 000 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60×120×2 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Égypte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La pierre de référence est de la famille Minya, mais l'acheteur est en Égypte, achète EXW usine et veut 11 000 m² en 60×120. Sans rapport avec un stock de 30×60 à Paris.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIY Interlock Modern Outdoor Anti-slip Stone Deck Tile Floor Marble Tile Limestone Deck Tile Stone ...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalles clipsables en travertin beige 300×300×20 sur base plastique (réf. fournisseur PBST-008)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">155 pièces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300×300×20 mm (10 mm de pierre et 10 mm de plastique)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Londres, Royaume-Uni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">affiché « 1 days ago » le 2026-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destination Londres et petite quantité, mais l'acheteur veut un produit précis : des dalles de travertin clipsables sur support plastique, différentes de la Minyala.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bathroom tiles walls and floors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carreaux de salle de bain murs et sols, aspect pierre naturelle chaude et neutre, mat, R10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portugal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">affiché « 4 days ago » le 2026-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correction : Product: full-body porcelain floor tiles with a warm neutral natural-stone look, matt, R10, rectified, with matching wall tiles (not natural stone). Size: 800x800x10 mm. Quantity: 26 m². Destination: Portugal. Date: posted 2026-10-08. — Petite quantité au Portugal, mais la description (R10, chauffage au sol, coupes à 45°) évoque plutôt du grès cérame aspect pierre. Le produit n'est pas précisé.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YDSTONE Beige Tumbled French Pattern Travertine Tile Limestone for Indoor Outdoor Staircases ...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalles extérieures en travertin beige adouci, 30 mm minimum, au moins 300×600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">au moins 300×600, épaisseur 30 mm minimum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">affiché « 5 days ago » le 2026-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Correction : Product: outdoor travertine pavers for wet areas, slip-resistant, honed (not polished). Size: width at least 300 mm, length at least 600 mm, thickness at least 30 mm. Quantity: 150 m². Destination: Perth, Australia (buyer account listed as United States). Date: posted 2026-10-06. — Pierre beige au format 30×60 environ, mais l'acheteur est aux États-Unis et demande une épaisseur de 30 mm minimum, alors que la Minyala fait 20 mm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TradeKey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEMANDE PRIX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaque de marbre 60×70 cm pour une salle d'exposition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 à 10 plaques, puis prix au m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60×70 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acheteur en France qui veut un prix livré, mais la quantité est minime (1 à 10 plaques) et le format 60×70 diffère du 30×60. Réponse réservée aux membres payants. Les dates TradeKey semblent rafraîchies.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Floor tiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carreaux de sol (tags : limestone, marble, travertine, slate…)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Royaume-Uni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acheteur au Royaume-Uni, mais la demande se résume à « I want to buy floor tiles ». Aucune spécification, et la réponse est réservée aux membres Premium.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wanted : Natural Stones Like Sawn And Tumbled Finish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dalles 500×500×30 sciées et vieillies : travertin beige 640 m², gris foncé 447 m², jaune cristal 521 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">640 m² (beige), plus d'autres teintes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">500×500×30 mm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oman</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pierre beige vieillie, mais l'acheteur est à Oman, loin de l'Europe, et demande du 50×50×3 cm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wanted : Natural Stone Like Sandstone, Limestone, Natural Stones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grès et calcaire sur mesure, noir, brun ou gris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Split, Croatie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcaire pour l'Europe (Split, Croatie), mais les couleurs voulues sont sombres (noir, brun, gris) et le paiement se fait par L/C pour 1 conteneur.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request sample for Limestone Beige Split Face</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Échantillon de parement en calcaire beige éclaté (Bulgarie)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">échantillon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">parement éclaté</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcaire beige pour le Royaume-Uni, mais il s'agit d'un parement mural éclaté et seulement d'une demande d'échantillon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buyers from France - Global Stone Buyer Center (RFQ for limestone stone veneer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glued stone veneer in Anstrude Clair and Massangis Clair limestone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">veneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">September 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acheteur en France, mais le produit demandé est un placage collé en pierres françaises précises (Anstrude, Massangis), pas du carrelage 30x60.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buyers from Germany - Global Stone Buyer Center (Inquire About Verona Beige Marble)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verona Beige marble, regular supply wanted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regular supply (no quantity stated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 23, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Importateur allemand qui cherche une pierre beige en approvisionnement régulier : on peut le contacter, mais il demande un marbre précis (Verona Beige, Pakistan), pas du calcaire égyptien.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buyers from Portugal - Global Stone Buyer Center (RFQ for Victory Beige Marble)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Victory Beige marble slabs, 2 cm, honed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">slabs, 2 cm, honed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oct 8, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demande très récente (oct. 2026) d'une pierre beige de 2 cm adoucie au Portugal, mais en tranches et en marbre précis : substitution par du carrelage 30x60 peu probable.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buyers from Italy - Global Stone Buyer Center (Caliza Capri Limestone)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caliza Capri limestone blocks (about 2 for a trial)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">about 2 blocks for a trial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">blocks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Italy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 4, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acheteur en Italie (août 2026), mais il demande des blocs d'un calcaire précis : sans intérêt pour un stock de carreaux.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[RFQ]Inquire About Galala Marble, Black Granite (Buyers from Bahrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polished Galala marble (Egypt origin): flooring and wall cladding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">600x600x20 mm (floor); 1200x600 and 1500x600 mm (cladding)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bahrain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">July 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pierre beige égyptienne demandée en juillet 2026, mais destination lointaine (Bahreïn), finition polie et formats 60x60 et 120x60 : peu adapté à un stock en France.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buyers from Kuwait - Global Stone Buyer Center (Turkish light limestone)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turkish light limestone, off-white, honed tiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">about 2,000 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40x80x3 cm, honed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kuwait</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mar 9, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcaire clair adouci, 2 000 m² (mars 2026), mais destination Koweït, origine turque demandée et épaisseur 3 cm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buyers from Kuwait - Global Stone Buyer Center (Kota Beige Limestone)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kota Beige limestone (India) for exterior walls</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60x120x3 cm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">July 2026 (Jul 11, 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcaire beige, 100 m², mais destination Koweït, format 60x120x3 et pierre indienne précise.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buyers from United States - Global Stone Buyer Center (Jura Beige Limestone)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jura Beige limestone, large-format tiles and slabs, leather finish, interior flooring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">about 10,000 sq ft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24x48 in, 1/2 in, leather finish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcaire beige chaud pour sol intérieur (juillet 2026), mais destination États-Unis, format 24x48 pouces et grand volume.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Natural Stone Buyers from Qatar (Limra Limestone, villa in Doha)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cut-to-size Limra limestone for a villa exterior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">about 2,288 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cut-to-size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doha, Qatar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sep 29, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Demande récente (29 sept. 2026) mais destination lointaine (Doha) et calcaire blanc turc (Limra) en dimensions sur mesure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buyers from Saudi Arabia - Global Stone Buyer Center (Riyadh Stone or similar beige limestone, facades)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riyadh Stone or a similar beige limestone for facades</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45,000 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60x30 cm, thickness to be confirmed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saudi Arabia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">April 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calcaire beige en 60x30, mais volume énorme (45 000 m²), destination Arabie saoudite et préférence déclarée pour des fournisseurs saoudiens.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riyadh Limestone Tile from Saudi Arabia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beige Riyadh limestone, bush-hammered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,700 m²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30x60x3 cm, bush-hammered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">about 112 days ago (relative to the index snapshot)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le format 30x60 correspond, mais il s'agit de pierre saoudienne de 3 cm bouchardée, avec destination probablement au Moyen-Orient.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global Stone Buyer Center - page 3 (RFQ for beige-cream flamed limestone cladding and paving)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beige-cream limestone, flamed finish, for cladding and paving (technical data sheets requested)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 mm; slabs about 140-180 x 250-300 cm; flamed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egypt (per a search summary, unconfirmed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 25, 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La couleur beige-crème et les 20 mm correspondent, mais la demande porte sur de grandes tranches flammées et des fiches techniques pour un projet. Destination incertaine (Égypte selon un résumé).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunny Menia Marble - Beige Marble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunny Menia (Minya stone), acid-washed / honed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">300x300x18 mm, acid-washed / honed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shenzhen, China</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exactement la famille de pierre de MINYALA (Sunny Menia, Minya), mais destination Chine (Shenzhen) et format 30x30x1,8 : sans intérêt pour un stock en France.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• « Vérifiée ? = Oui » : la demande a été retrouvée sur la page publique de la plateforme le 12/10/2026.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• StoneContact bloque les accès automatisés : ses demandes viennent de résultats de recherche et n'ont pas pu être revérifiées. Ouvrez-les une fois connecté ; beaucoup sont anciennes ou sans date.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Les coordonnées des acheteurs sont réservées aux membres connectés ou payants. Aucun nom ni contact d'acheteur n'est enregistré ici.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Liens Alibaba : ils peuvent dépendre de la session ; si un lien ne s'ouvre pas, cherchez le titre dans la liste des RFQ Alibaba.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Avant de répondre : lire l'onglet Règles et la section sécurité de rfq-kit.md (jamais de frais à payer, marchandise remise après paiement reçu).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Groupe</t>
   </si>
   <si>
@@ -3790,6 +4779,60 @@
   </si>
   <si>
     <t xml:space="preserve">Contacter les magasins qui ont un rayon Pavés-Dallages et une salle d'exposition (deux sont déjà dans Prospects : Clamart et Houilles).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destockplus (déstockage B2B France)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pros qui achètent des lots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France — annonce gratuite (publiée sous 72 h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publier le lot MINYALA (500–2 000 m², 27 €/m² TTC pro, dès 25 m², Gennevilliers et Vernon). Concurrent présent à 27 €/m² avec 160 m² minimum.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StoneAdd (demandes d'acheteurs pierre)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Importateurs, grossistes, poseurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International — 27 000+ demandes publiques</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inscription gratuite, coordonnées des acheteurs réservées au Premium. Meilleures demandes trouvées ici (Autriche, Belgique, France) : voir onglet Demandes RFQ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acheteurs de pierre du monde entier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Créer le compte gratuit et publier la fiche MINYALA (textes dans rfq-kit.md). Ne payer Diamond (≈ 2 000 $/an, non confirmé) qu'après un mois de mesure.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Europages</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acheteurs professionnels européens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Europe — page entreprise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Créer la page entreprise gratuite ; tester le « Request Hub » fournisseur (essai gratuit annoncé).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Importateurs (souvent par conteneur)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International — abonnement dès 75 $/mois</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seulement si StoneAdd et StoneContact ne suffisent pas : plusieurs demandes européennes de calcaire / marbre crème.</t>
   </si>
   <si>
     <t xml:space="preserve">ChatGPT (via Shopify)</t>
@@ -4322,6 +5365,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
@@ -15196,6 +16243,2250 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:N59"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="28"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="14" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1104</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>1109</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>1110</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>1111</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>1112</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>917</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>1113</v>
+      </c>
+      <c r="M1" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="N1" s="14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="15" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>1121</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>1122</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>1123</v>
+      </c>
+      <c r="K2" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L2" s="20"/>
+      <c r="M2" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N2" s="19"/>
+    </row>
+    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="15" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>1128</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>1129</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>1130</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L3" s="20"/>
+      <c r="M3" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N3" s="19"/>
+    </row>
+    <row r="4" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="15" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>1134</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>1135</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>1136</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>1137</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L4" s="20"/>
+      <c r="M4" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N4" s="19"/>
+    </row>
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="15" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>1142</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>1144</v>
+      </c>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15" t="s">
+        <v>1145</v>
+      </c>
+      <c r="K5" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L5" s="20"/>
+      <c r="M5" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N5" s="19"/>
+    </row>
+    <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15" t="s">
+        <v>1149</v>
+      </c>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15" t="s">
+        <v>1150</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L6" s="20"/>
+      <c r="M6" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N6" s="19"/>
+    </row>
+    <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C7" s="23" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>1154</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H7" s="23" t="s">
+        <v>939</v>
+      </c>
+      <c r="I7" s="23" t="s">
+        <v>1155</v>
+      </c>
+      <c r="J7" s="23" t="s">
+        <v>1156</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L7" s="20"/>
+      <c r="M7" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N7" s="19"/>
+    </row>
+    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>1162</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>1163</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>1164</v>
+      </c>
+      <c r="K8" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L8" s="20"/>
+      <c r="M8" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N8" s="19"/>
+    </row>
+    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B9" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C9" s="23" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H9" s="23" t="s">
+        <v>939</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>1167</v>
+      </c>
+      <c r="J9" s="23" t="s">
+        <v>1168</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L9" s="20"/>
+      <c r="M9" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N9" s="19"/>
+    </row>
+    <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>1171</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>1172</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>1173</v>
+      </c>
+      <c r="K10" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L10" s="20"/>
+      <c r="M10" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N10" s="19"/>
+    </row>
+    <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>1176</v>
+      </c>
+      <c r="H11" s="23" t="s">
+        <v>1162</v>
+      </c>
+      <c r="I11" s="23" t="s">
+        <v>1177</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>1178</v>
+      </c>
+      <c r="K11" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L11" s="20"/>
+      <c r="M11" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N11" s="19"/>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>1181</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>1182</v>
+      </c>
+      <c r="J12" s="23" t="s">
+        <v>1183</v>
+      </c>
+      <c r="K12" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L12" s="20"/>
+      <c r="M12" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N12" s="19"/>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B13" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C13" s="23" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>1186</v>
+      </c>
+      <c r="I13" s="23" t="s">
+        <v>1187</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>1188</v>
+      </c>
+      <c r="K13" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L13" s="20"/>
+      <c r="M13" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N13" s="19"/>
+    </row>
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C14" s="23" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>1189</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>1192</v>
+      </c>
+      <c r="I14" s="23" t="s">
+        <v>1193</v>
+      </c>
+      <c r="J14" s="23" t="s">
+        <v>1194</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L14" s="20"/>
+      <c r="M14" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N14" s="19"/>
+    </row>
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B15" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C15" s="23" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>1197</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>1199</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>1200</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L15" s="20"/>
+      <c r="M15" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N15" s="19"/>
+    </row>
+    <row r="16" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F16" s="23" t="s">
+        <v>1203</v>
+      </c>
+      <c r="G16" s="23" t="s">
+        <v>1204</v>
+      </c>
+      <c r="H16" s="23" t="s">
+        <v>1205</v>
+      </c>
+      <c r="I16" s="23" t="s">
+        <v>1206</v>
+      </c>
+      <c r="J16" s="23" t="s">
+        <v>1207</v>
+      </c>
+      <c r="K16" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L16" s="20"/>
+      <c r="M16" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N16" s="19"/>
+    </row>
+    <row r="17" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>1208</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>1210</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>1211</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>1212</v>
+      </c>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23" t="s">
+        <v>1213</v>
+      </c>
+      <c r="K17" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L17" s="20"/>
+      <c r="M17" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N17" s="19"/>
+    </row>
+    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>1214</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>1215</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>1216</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>1217</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>1218</v>
+      </c>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23" t="s">
+        <v>1219</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L18" s="20"/>
+      <c r="M18" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N18" s="19"/>
+    </row>
+    <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>1222</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>1223</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>1225</v>
+      </c>
+      <c r="J19" s="23" t="s">
+        <v>1226</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L19" s="20"/>
+      <c r="M19" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N19" s="19"/>
+    </row>
+    <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>1229</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>1230</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>1224</v>
+      </c>
+      <c r="I20" s="23" t="s">
+        <v>1231</v>
+      </c>
+      <c r="J20" s="23" t="s">
+        <v>1232</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L20" s="20"/>
+      <c r="M20" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N20" s="19"/>
+    </row>
+    <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B21" s="23" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C21" s="23" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>1233</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>1234</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>1236</v>
+      </c>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23" t="s">
+        <v>1237</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L21" s="20"/>
+      <c r="M21" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N21" s="19"/>
+    </row>
+    <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F22" s="23"/>
+      <c r="G22" s="23" t="s">
+        <v>1240</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>1241</v>
+      </c>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23" t="s">
+        <v>1242</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L22" s="20"/>
+      <c r="M22" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N22" s="19"/>
+    </row>
+    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C23" s="23" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>1243</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>1244</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>1245</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>1246</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>1247</v>
+      </c>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23" t="s">
+        <v>1248</v>
+      </c>
+      <c r="K23" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L23" s="20"/>
+      <c r="M23" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N23" s="19"/>
+    </row>
+    <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>1250</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>1252</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>1253</v>
+      </c>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23" t="s">
+        <v>1254</v>
+      </c>
+      <c r="K24" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L24" s="20"/>
+      <c r="M24" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N24" s="19"/>
+    </row>
+    <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C25" s="23" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D25" s="24" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>1256</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G25" s="23" t="s">
+        <v>1257</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>1258</v>
+      </c>
+      <c r="I25" s="23" t="s">
+        <v>1259</v>
+      </c>
+      <c r="J25" s="23" t="s">
+        <v>1260</v>
+      </c>
+      <c r="K25" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L25" s="20"/>
+      <c r="M25" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N25" s="19"/>
+    </row>
+    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C26" s="23" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D26" s="24" t="s">
+        <v>1261</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F26" s="23" t="s">
+        <v>1263</v>
+      </c>
+      <c r="G26" s="23" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="23" t="s">
+        <v>1265</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L26" s="20"/>
+      <c r="M26" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N26" s="19"/>
+    </row>
+    <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B27" s="23" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D27" s="24" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F27" s="23" t="s">
+        <v>1268</v>
+      </c>
+      <c r="G27" s="23"/>
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23" t="s">
+        <v>1269</v>
+      </c>
+      <c r="K27" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L27" s="20"/>
+      <c r="M27" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N27" s="19"/>
+    </row>
+    <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B28" s="23" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C28" s="23" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D28" s="24" t="s">
+        <v>1270</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F28" s="23" t="s">
+        <v>1272</v>
+      </c>
+      <c r="G28" s="23"/>
+      <c r="H28" s="23" t="s">
+        <v>939</v>
+      </c>
+      <c r="I28" s="23" t="s">
+        <v>1273</v>
+      </c>
+      <c r="J28" s="23" t="s">
+        <v>1274</v>
+      </c>
+      <c r="K28" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L28" s="20"/>
+      <c r="M28" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N28" s="19"/>
+    </row>
+    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B29" s="23" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C29" s="23" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>1275</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>1276</v>
+      </c>
+      <c r="F29" s="23"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23" t="s">
+        <v>939</v>
+      </c>
+      <c r="I29" s="23" t="s">
+        <v>1277</v>
+      </c>
+      <c r="J29" s="23" t="s">
+        <v>1278</v>
+      </c>
+      <c r="K29" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L29" s="20"/>
+      <c r="M29" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N29" s="19"/>
+    </row>
+    <row r="30" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="23" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D30" s="24" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F30" s="23" t="s">
+        <v>1281</v>
+      </c>
+      <c r="G30" s="23" t="s">
+        <v>1282</v>
+      </c>
+      <c r="H30" s="23" t="s">
+        <v>1283</v>
+      </c>
+      <c r="I30" s="23" t="s">
+        <v>1284</v>
+      </c>
+      <c r="J30" s="23" t="s">
+        <v>1285</v>
+      </c>
+      <c r="K30" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L30" s="20"/>
+      <c r="M30" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N30" s="19"/>
+    </row>
+    <row r="31" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C31" s="17" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E31" s="17" t="s">
+        <v>1289</v>
+      </c>
+      <c r="F31" s="17" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G31" s="17" t="s">
+        <v>1290</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>1291</v>
+      </c>
+      <c r="I31" s="17" t="s">
+        <v>1292</v>
+      </c>
+      <c r="J31" s="17" t="s">
+        <v>1293</v>
+      </c>
+      <c r="K31" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L31" s="20"/>
+      <c r="M31" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N31" s="19"/>
+    </row>
+    <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>1294</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>1295</v>
+      </c>
+      <c r="F32" s="17" t="s">
+        <v>1296</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>1297</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>1298</v>
+      </c>
+      <c r="I32" s="17" t="s">
+        <v>1299</v>
+      </c>
+      <c r="J32" s="17" t="s">
+        <v>1300</v>
+      </c>
+      <c r="K32" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L32" s="20"/>
+      <c r="M32" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N32" s="19"/>
+    </row>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E33" s="17" t="s">
+        <v>1302</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>1303</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>1304</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>1305</v>
+      </c>
+      <c r="I33" s="17" t="s">
+        <v>1306</v>
+      </c>
+      <c r="J33" s="17" t="s">
+        <v>1307</v>
+      </c>
+      <c r="K33" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L33" s="20"/>
+      <c r="M33" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N33" s="19"/>
+    </row>
+    <row r="34" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C34" s="17" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E34" s="17" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F34" s="17" t="s">
+        <v>1310</v>
+      </c>
+      <c r="G34" s="17" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H34" s="17" t="s">
+        <v>1311</v>
+      </c>
+      <c r="I34" s="17" t="s">
+        <v>1312</v>
+      </c>
+      <c r="J34" s="17" t="s">
+        <v>1313</v>
+      </c>
+      <c r="K34" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L34" s="20"/>
+      <c r="M34" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N34" s="19"/>
+    </row>
+    <row r="35" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>1314</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>1315</v>
+      </c>
+      <c r="F35" s="17" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G35" s="17" t="s">
+        <v>1316</v>
+      </c>
+      <c r="H35" s="17" t="s">
+        <v>1291</v>
+      </c>
+      <c r="I35" s="17" t="s">
+        <v>1317</v>
+      </c>
+      <c r="J35" s="17" t="s">
+        <v>1318</v>
+      </c>
+      <c r="K35" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L35" s="20"/>
+      <c r="M35" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N35" s="19"/>
+    </row>
+    <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C36" s="17" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E36" s="17" t="s">
+        <v>1321</v>
+      </c>
+      <c r="F36" s="17" t="s">
+        <v>1322</v>
+      </c>
+      <c r="G36" s="17" t="s">
+        <v>1323</v>
+      </c>
+      <c r="H36" s="17" t="s">
+        <v>939</v>
+      </c>
+      <c r="I36" s="17" t="s">
+        <v>1324</v>
+      </c>
+      <c r="J36" s="17" t="s">
+        <v>1325</v>
+      </c>
+      <c r="K36" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L36" s="20"/>
+      <c r="M36" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N36" s="19"/>
+    </row>
+    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C37" s="17" t="s">
+        <v>1319</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>1327</v>
+      </c>
+      <c r="F37" s="17" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G37" s="17" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H37" s="17" t="s">
+        <v>1328</v>
+      </c>
+      <c r="I37" s="17" t="s">
+        <v>1329</v>
+      </c>
+      <c r="J37" s="17" t="s">
+        <v>1330</v>
+      </c>
+      <c r="K37" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L37" s="20"/>
+      <c r="M37" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N37" s="19"/>
+    </row>
+    <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>1332</v>
+      </c>
+      <c r="F38" s="17" t="s">
+        <v>1333</v>
+      </c>
+      <c r="G38" s="17" t="s">
+        <v>1334</v>
+      </c>
+      <c r="H38" s="17" t="s">
+        <v>1335</v>
+      </c>
+      <c r="I38" s="17" t="s">
+        <v>1336</v>
+      </c>
+      <c r="J38" s="17" t="s">
+        <v>1337</v>
+      </c>
+      <c r="K38" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L38" s="20"/>
+      <c r="M38" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N38" s="19"/>
+    </row>
+    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C39" s="17" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D39" s="25" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G39" s="17" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H39" s="17" t="s">
+        <v>1340</v>
+      </c>
+      <c r="I39" s="17" t="s">
+        <v>1341</v>
+      </c>
+      <c r="J39" s="17" t="s">
+        <v>1342</v>
+      </c>
+      <c r="K39" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L39" s="20"/>
+      <c r="M39" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N39" s="19"/>
+    </row>
+    <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C40" s="17" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F40" s="17" t="s">
+        <v>1345</v>
+      </c>
+      <c r="G40" s="17" t="s">
+        <v>1346</v>
+      </c>
+      <c r="H40" s="17" t="s">
+        <v>1328</v>
+      </c>
+      <c r="I40" s="17" t="s">
+        <v>1347</v>
+      </c>
+      <c r="J40" s="17" t="s">
+        <v>1348</v>
+      </c>
+      <c r="K40" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L40" s="20"/>
+      <c r="M40" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N40" s="19"/>
+    </row>
+    <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C41" s="17" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D41" s="25" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>1350</v>
+      </c>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17" t="s">
+        <v>1351</v>
+      </c>
+      <c r="H41" s="17" t="s">
+        <v>939</v>
+      </c>
+      <c r="I41" s="17" t="s">
+        <v>1352</v>
+      </c>
+      <c r="J41" s="17" t="s">
+        <v>1353</v>
+      </c>
+      <c r="K41" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L41" s="20"/>
+      <c r="M41" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N41" s="19"/>
+    </row>
+    <row r="42" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C42" s="17" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D42" s="25" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E42" s="17" t="s">
+        <v>1355</v>
+      </c>
+      <c r="F42" s="17" t="s">
+        <v>1356</v>
+      </c>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17" t="s">
+        <v>1357</v>
+      </c>
+      <c r="I42" s="17" t="s">
+        <v>1358</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>1359</v>
+      </c>
+      <c r="K42" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L42" s="20"/>
+      <c r="M42" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N42" s="19"/>
+    </row>
+    <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D43" s="25" t="s">
+        <v>1360</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>1361</v>
+      </c>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17" t="s">
+        <v>1362</v>
+      </c>
+      <c r="H43" s="17" t="s">
+        <v>1311</v>
+      </c>
+      <c r="I43" s="17" t="s">
+        <v>1363</v>
+      </c>
+      <c r="J43" s="17" t="s">
+        <v>1364</v>
+      </c>
+      <c r="K43" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L43" s="20"/>
+      <c r="M43" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N43" s="19"/>
+    </row>
+    <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D44" s="25" t="s">
+        <v>1365</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>1366</v>
+      </c>
+      <c r="F44" s="17" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G44" s="17" t="s">
+        <v>1368</v>
+      </c>
+      <c r="H44" s="17" t="s">
+        <v>1369</v>
+      </c>
+      <c r="I44" s="17" t="s">
+        <v>1370</v>
+      </c>
+      <c r="J44" s="17" t="s">
+        <v>1371</v>
+      </c>
+      <c r="K44" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L44" s="20"/>
+      <c r="M44" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N44" s="19"/>
+    </row>
+    <row r="45" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C45" s="17" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>1372</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>1373</v>
+      </c>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17" t="s">
+        <v>1374</v>
+      </c>
+      <c r="H45" s="17" t="s">
+        <v>1375</v>
+      </c>
+      <c r="I45" s="17" t="s">
+        <v>1376</v>
+      </c>
+      <c r="J45" s="17" t="s">
+        <v>1377</v>
+      </c>
+      <c r="K45" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L45" s="20"/>
+      <c r="M45" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N45" s="19"/>
+    </row>
+    <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C46" s="17" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D46" s="25" t="s">
+        <v>1378</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>1379</v>
+      </c>
+      <c r="F46" s="17" t="s">
+        <v>1380</v>
+      </c>
+      <c r="G46" s="17" t="s">
+        <v>1381</v>
+      </c>
+      <c r="H46" s="17" t="s">
+        <v>1382</v>
+      </c>
+      <c r="I46" s="17" t="s">
+        <v>1383</v>
+      </c>
+      <c r="J46" s="17" t="s">
+        <v>1384</v>
+      </c>
+      <c r="K46" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L46" s="20"/>
+      <c r="M46" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N46" s="19"/>
+    </row>
+    <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C47" s="17" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D47" s="25" t="s">
+        <v>1385</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>1386</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>1127</v>
+      </c>
+      <c r="G47" s="17" t="s">
+        <v>1387</v>
+      </c>
+      <c r="H47" s="17" t="s">
+        <v>1382</v>
+      </c>
+      <c r="I47" s="17" t="s">
+        <v>1388</v>
+      </c>
+      <c r="J47" s="17" t="s">
+        <v>1389</v>
+      </c>
+      <c r="K47" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L47" s="20"/>
+      <c r="M47" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N47" s="19"/>
+    </row>
+    <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C48" s="17" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D48" s="25" t="s">
+        <v>1390</v>
+      </c>
+      <c r="E48" s="17" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G48" s="17" t="s">
+        <v>1393</v>
+      </c>
+      <c r="H48" s="17" t="s">
+        <v>1394</v>
+      </c>
+      <c r="I48" s="17" t="s">
+        <v>1376</v>
+      </c>
+      <c r="J48" s="17" t="s">
+        <v>1395</v>
+      </c>
+      <c r="K48" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L48" s="20"/>
+      <c r="M48" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N48" s="19"/>
+    </row>
+    <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C49" s="17" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D49" s="25" t="s">
+        <v>1396</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>1397</v>
+      </c>
+      <c r="F49" s="17" t="s">
+        <v>1398</v>
+      </c>
+      <c r="G49" s="17" t="s">
+        <v>1399</v>
+      </c>
+      <c r="H49" s="17" t="s">
+        <v>1400</v>
+      </c>
+      <c r="I49" s="17" t="s">
+        <v>1401</v>
+      </c>
+      <c r="J49" s="17" t="s">
+        <v>1402</v>
+      </c>
+      <c r="K49" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L49" s="20"/>
+      <c r="M49" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N49" s="19"/>
+    </row>
+    <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B50" s="17" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D50" s="25" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>1404</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>1405</v>
+      </c>
+      <c r="G50" s="17" t="s">
+        <v>1406</v>
+      </c>
+      <c r="H50" s="17" t="s">
+        <v>1407</v>
+      </c>
+      <c r="I50" s="17" t="s">
+        <v>1408</v>
+      </c>
+      <c r="J50" s="17" t="s">
+        <v>1409</v>
+      </c>
+      <c r="K50" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L50" s="20"/>
+      <c r="M50" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N50" s="19"/>
+    </row>
+    <row r="51" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C51" s="17" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D51" s="25" t="s">
+        <v>1410</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>1411</v>
+      </c>
+      <c r="F51" s="17" t="s">
+        <v>1412</v>
+      </c>
+      <c r="G51" s="17" t="s">
+        <v>1413</v>
+      </c>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J51" s="17" t="s">
+        <v>1415</v>
+      </c>
+      <c r="K51" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L51" s="20"/>
+      <c r="M51" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N51" s="19"/>
+    </row>
+    <row r="52" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D52" s="25" t="s">
+        <v>1416</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>1417</v>
+      </c>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17" t="s">
+        <v>1418</v>
+      </c>
+      <c r="H52" s="17" t="s">
+        <v>1419</v>
+      </c>
+      <c r="I52" s="17" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J52" s="17" t="s">
+        <v>1421</v>
+      </c>
+      <c r="K52" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L52" s="20"/>
+      <c r="M52" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N52" s="19"/>
+    </row>
+    <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="17" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C53" s="17" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D53" s="25" t="s">
+        <v>1422</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>1423</v>
+      </c>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17" t="s">
+        <v>1424</v>
+      </c>
+      <c r="H53" s="17" t="s">
+        <v>1425</v>
+      </c>
+      <c r="I53" s="17"/>
+      <c r="J53" s="17" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K53" s="18" t="s">
+        <v>925</v>
+      </c>
+      <c r="L53" s="20"/>
+      <c r="M53" s="19" t="s">
+        <v>1124</v>
+      </c>
+      <c r="N53" s="19"/>
+    </row>
+    <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+    </row>
+    <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+    </row>
+    <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+    </row>
+    <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="D59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:N53"/>
+  <mergeCells count="5">
+    <mergeCell ref="A55:J55"/>
+    <mergeCell ref="A56:J56"/>
+    <mergeCell ref="A57:J57"/>
+    <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A59:J59"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M132" type="list">
+      <formula1>"À étudier,Répondu,Pas pertinent,Gagné,Perdu"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="K2" r:id="rId1" display="Ouvrir"/>
+    <hyperlink ref="K3" r:id="rId2" display="Ouvrir"/>
+    <hyperlink ref="K4" r:id="rId3" display="Ouvrir"/>
+    <hyperlink ref="K5" r:id="rId4" display="Ouvrir"/>
+    <hyperlink ref="K6" r:id="rId5" display="Ouvrir"/>
+    <hyperlink ref="K7" r:id="rId6" display="Ouvrir"/>
+    <hyperlink ref="K8" r:id="rId7" display="Ouvrir"/>
+    <hyperlink ref="K9" r:id="rId8" display="Ouvrir"/>
+    <hyperlink ref="K10" r:id="rId9" display="Ouvrir"/>
+    <hyperlink ref="K11" r:id="rId10" display="Ouvrir"/>
+    <hyperlink ref="K12" r:id="rId11" display="Ouvrir"/>
+    <hyperlink ref="K13" r:id="rId12" display="Ouvrir"/>
+    <hyperlink ref="K14" r:id="rId13" display="Ouvrir"/>
+    <hyperlink ref="K15" r:id="rId14" display="Ouvrir"/>
+    <hyperlink ref="K16" r:id="rId15" display="Ouvrir"/>
+    <hyperlink ref="K17" r:id="rId16" display="Ouvrir"/>
+    <hyperlink ref="K18" r:id="rId17" display="Ouvrir"/>
+    <hyperlink ref="K19" r:id="rId18" display="Ouvrir"/>
+    <hyperlink ref="K20" r:id="rId19" display="Ouvrir"/>
+    <hyperlink ref="K21" r:id="rId20" display="Ouvrir"/>
+    <hyperlink ref="K22" r:id="rId21" display="Ouvrir"/>
+    <hyperlink ref="K23" r:id="rId22" display="Ouvrir"/>
+    <hyperlink ref="K24" r:id="rId23" display="Ouvrir"/>
+    <hyperlink ref="K25" r:id="rId24" display="Ouvrir"/>
+    <hyperlink ref="K26" r:id="rId25" display="Ouvrir"/>
+    <hyperlink ref="K27" r:id="rId26" display="Ouvrir"/>
+    <hyperlink ref="K28" r:id="rId27" display="Ouvrir"/>
+    <hyperlink ref="K29" r:id="rId28" display="Ouvrir"/>
+    <hyperlink ref="K30" r:id="rId29" display="Ouvrir"/>
+    <hyperlink ref="K31" r:id="rId30" display="Ouvrir"/>
+    <hyperlink ref="K32" r:id="rId31" display="Ouvrir"/>
+    <hyperlink ref="K33" r:id="rId32" display="Ouvrir"/>
+    <hyperlink ref="K34" r:id="rId33" display="Ouvrir"/>
+    <hyperlink ref="K35" r:id="rId34" display="Ouvrir"/>
+    <hyperlink ref="K36" r:id="rId35" display="Ouvrir"/>
+    <hyperlink ref="K37" r:id="rId36" display="Ouvrir"/>
+    <hyperlink ref="K38" r:id="rId37" display="Ouvrir"/>
+    <hyperlink ref="K39" r:id="rId38" display="Ouvrir"/>
+    <hyperlink ref="K40" r:id="rId39" display="Ouvrir"/>
+    <hyperlink ref="K41" r:id="rId40" display="Ouvrir"/>
+    <hyperlink ref="K42" r:id="rId41" display="Ouvrir"/>
+    <hyperlink ref="K43" r:id="rId42" display="Ouvrir"/>
+    <hyperlink ref="K44" r:id="rId43" display="Ouvrir"/>
+    <hyperlink ref="K45" r:id="rId44" display="Ouvrir"/>
+    <hyperlink ref="K46" r:id="rId45" display="Ouvrir"/>
+    <hyperlink ref="K47" r:id="rId46" display="Ouvrir"/>
+    <hyperlink ref="K48" r:id="rId47" display="Ouvrir"/>
+    <hyperlink ref="K49" r:id="rId48" display="Ouvrir"/>
+    <hyperlink ref="K50" r:id="rId49" display="Ouvrir"/>
+    <hyperlink ref="K51" r:id="rId50" display="Ouvrir"/>
+    <hyperlink ref="K52" r:id="rId51" display="Ouvrir"/>
+    <hyperlink ref="K53" r:id="rId52" display="Ouvrir"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId53"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:J28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -15211,7 +18502,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>1103</v>
+        <v>1432</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>40</v>
@@ -15220,7 +18511,7 @@
         <v>912</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>1104</v>
+        <v>1433</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>915</v>
@@ -15232,84 +18523,84 @@
         <v>44</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>1105</v>
+        <v>1434</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>1106</v>
+        <v>1435</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>1107</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>1108</v>
+        <v>1437</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>939</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>1109</v>
+        <v>1438</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>1110</v>
+        <v>1439</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>1111</v>
+        <v>1440</v>
       </c>
       <c r="F2" s="17"/>
       <c r="G2" s="26" t="s">
-        <v>1112</v>
+        <v>1441</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>1113</v>
+        <v>1442</v>
       </c>
       <c r="I2" s="19" t="s">
-        <v>1114</v>
+        <v>1443</v>
       </c>
       <c r="J2" s="20"/>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>1115</v>
+        <v>1444</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>939</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>1116</v>
+        <v>1445</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>1117</v>
+        <v>1446</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>1118</v>
+        <v>1447</v>
       </c>
       <c r="F3" s="17"/>
       <c r="G3" s="26" t="s">
-        <v>1112</v>
+        <v>1441</v>
       </c>
       <c r="H3" s="20"/>
       <c r="I3" s="19"/>
       <c r="J3" s="20" t="s">
-        <v>1119</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>1120</v>
+        <v>1449</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1121</v>
+        <v>1450</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>1122</v>
+        <v>1451</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>1123</v>
+        <v>1452</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>1124</v>
+        <v>1453</v>
       </c>
       <c r="F4" s="18" t="s">
         <v>925</v>
@@ -15323,19 +18614,19 @@
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>1125</v>
+        <v>1454</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1126</v>
+        <v>1455</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>1127</v>
+        <v>1456</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>1128</v>
+        <v>1457</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>1129</v>
+        <v>1458</v>
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="18" t="s">
@@ -15347,19 +18638,19 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>1130</v>
+        <v>1459</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1131</v>
+        <v>1460</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>1122</v>
+        <v>1451</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>1132</v>
+        <v>1461</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>1133</v>
+        <v>1462</v>
       </c>
       <c r="F6" s="18" t="s">
         <v>925</v>
@@ -15373,19 +18664,19 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>1134</v>
+        <v>1463</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>1135</v>
+        <v>1464</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>1122</v>
+        <v>1451</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>1132</v>
+        <v>1461</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>1133</v>
+        <v>1462</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>925</v>
@@ -15399,19 +18690,19 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>1136</v>
+        <v>1465</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1137</v>
+        <v>1466</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>1122</v>
+        <v>1451</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>1138</v>
+        <v>1467</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>1133</v>
+        <v>1462</v>
       </c>
       <c r="F8" s="18" t="s">
         <v>925</v>
@@ -15425,19 +18716,19 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>1139</v>
+        <v>1468</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1140</v>
+        <v>1469</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>1122</v>
+        <v>1451</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>1132</v>
+        <v>1461</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>1133</v>
+        <v>1462</v>
       </c>
       <c r="F9" s="18" t="s">
         <v>925</v>
@@ -15451,19 +18742,19 @@
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>1141</v>
+        <v>1470</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1142</v>
+        <v>1471</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>1122</v>
+        <v>1451</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>1132</v>
+        <v>1461</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>1143</v>
+        <v>1472</v>
       </c>
       <c r="F10" s="18" t="s">
         <v>925</v>
@@ -15477,19 +18768,19 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>1144</v>
+        <v>1473</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>1145</v>
+        <v>1474</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>1122</v>
+        <v>1451</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>1132</v>
+        <v>1461</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>1133</v>
+        <v>1462</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>925</v>
@@ -15503,19 +18794,19 @@
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>1146</v>
+        <v>1475</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>1147</v>
+        <v>1476</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>1122</v>
+        <v>1451</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>1132</v>
+        <v>1461</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>1148</v>
+        <v>1477</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>925</v>
@@ -15529,19 +18820,19 @@
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>1149</v>
+        <v>1478</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>1150</v>
+        <v>1479</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>1122</v>
+        <v>1451</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>1132</v>
+        <v>1461</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>1151</v>
+        <v>1480</v>
       </c>
       <c r="F13" s="18" t="s">
         <v>925</v>
@@ -15555,19 +18846,19 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>1152</v>
+        <v>1481</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>1153</v>
+        <v>1482</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>1122</v>
+        <v>1451</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>1132</v>
+        <v>1461</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>1133</v>
+        <v>1462</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>925</v>
@@ -15581,19 +18872,19 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>1154</v>
+        <v>1483</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>1155</v>
+        <v>1484</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>1122</v>
+        <v>1451</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>1132</v>
+        <v>1461</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>1133</v>
+        <v>1462</v>
       </c>
       <c r="F15" s="18" t="s">
         <v>925</v>
@@ -15607,19 +18898,19 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>1156</v>
+        <v>1485</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>1157</v>
+        <v>1486</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>1122</v>
+        <v>1451</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>1132</v>
+        <v>1461</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>1133</v>
+        <v>1462</v>
       </c>
       <c r="F16" s="18" t="s">
         <v>925</v>
@@ -15633,19 +18924,19 @@
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>1158</v>
+        <v>1487</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>1159</v>
+        <v>1488</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>1122</v>
+        <v>1451</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>1132</v>
+        <v>1461</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>1133</v>
+        <v>1462</v>
       </c>
       <c r="F17" s="18" t="s">
         <v>925</v>
@@ -15659,19 +18950,19 @@
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>1160</v>
+        <v>1489</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>1161</v>
+        <v>1490</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>1122</v>
+        <v>1451</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>1132</v>
+        <v>1461</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>1133</v>
+        <v>1462</v>
       </c>
       <c r="F18" s="18" t="s">
         <v>925</v>
@@ -15685,19 +18976,19 @@
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>1162</v>
+        <v>1491</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>1163</v>
+        <v>1492</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>1122</v>
+        <v>1451</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>1132</v>
+        <v>1461</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>1164</v>
+        <v>1493</v>
       </c>
       <c r="F19" s="18" t="s">
         <v>925</v>
@@ -15711,19 +19002,19 @@
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>1165</v>
+        <v>1494</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>1166</v>
+        <v>1495</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>1122</v>
+        <v>1451</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>1132</v>
+        <v>1461</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>1164</v>
+        <v>1493</v>
       </c>
       <c r="F20" s="18" t="s">
         <v>925</v>
@@ -15737,19 +19028,19 @@
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>1167</v>
+        <v>1496</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>1168</v>
+        <v>1497</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>1122</v>
+        <v>1451</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>1169</v>
+        <v>1498</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>1170</v>
+        <v>1499</v>
       </c>
       <c r="F21" s="18" t="s">
         <v>925</v>
@@ -15763,19 +19054,19 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>1171</v>
+        <v>1500</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>1172</v>
+        <v>1501</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>1122</v>
+        <v>1451</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>1132</v>
+        <v>1461</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>1173</v>
+        <v>1502</v>
       </c>
       <c r="F22" s="18" t="s">
         <v>925</v>
@@ -15789,19 +19080,19 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>1174</v>
+        <v>1503</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>1175</v>
+        <v>1504</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>1116</v>
+        <v>1445</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>1176</v>
+        <v>1505</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>1177</v>
+        <v>1506</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>925</v>
@@ -15815,7 +19106,7 @@
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>1178</v>
+        <v>1507</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -15825,7 +19116,7 @@
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>1179</v>
+        <v>1508</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -15835,7 +19126,7 @@
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>1180</v>
+        <v>1509</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -15845,7 +19136,7 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>1181</v>
+        <v>1510</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -15917,12 +19208,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
@@ -15936,10 +19227,10 @@
         <v>911</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1182</v>
+        <v>1511</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>1183</v>
+        <v>1512</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>915</v>
@@ -15950,16 +19241,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>1184</v>
+        <v>1513</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>1185</v>
+        <v>1514</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>1186</v>
+        <v>1515</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>1187</v>
+        <v>1516</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>925</v>
@@ -15967,16 +19258,16 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>1188</v>
+        <v>1517</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1189</v>
+        <v>1518</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>315</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>1190</v>
+        <v>1519</v>
       </c>
       <c r="E3" s="27" t="s">
         <v>925</v>
@@ -15984,16 +19275,16 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>1191</v>
+        <v>1520</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1192</v>
+        <v>1521</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>1193</v>
+        <v>1522</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>1194</v>
+        <v>1523</v>
       </c>
       <c r="E4" s="27" t="s">
         <v>925</v>
@@ -16001,16 +19292,16 @@
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>1195</v>
+        <v>1524</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1196</v>
+        <v>1525</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>1197</v>
+        <v>1526</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>1198</v>
+        <v>1527</v>
       </c>
       <c r="E5" s="27" t="s">
         <v>925</v>
@@ -16018,16 +19309,16 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>1199</v>
+        <v>1528</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1200</v>
+        <v>1529</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>1201</v>
+        <v>1530</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>1202</v>
+        <v>1531</v>
       </c>
       <c r="E6" s="27" t="s">
         <v>925</v>
@@ -16035,16 +19326,16 @@
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>1203</v>
+        <v>1532</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>1204</v>
+        <v>1533</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>1205</v>
+        <v>1534</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>1206</v>
+        <v>1535</v>
       </c>
       <c r="E7" s="27" t="s">
         <v>925</v>
@@ -16052,16 +19343,16 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>1207</v>
+        <v>1536</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1208</v>
+        <v>1537</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>1209</v>
+        <v>1538</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>1210</v>
+        <v>1539</v>
       </c>
       <c r="E8" s="27" t="s">
         <v>925</v>
@@ -16069,16 +19360,16 @@
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>1211</v>
+        <v>1540</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1212</v>
+        <v>1541</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>1213</v>
+        <v>1542</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>1214</v>
+        <v>1543</v>
       </c>
       <c r="E9" s="27" t="s">
         <v>925</v>
@@ -16086,16 +19377,16 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>1215</v>
+        <v>1544</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1216</v>
+        <v>1545</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>50</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>1217</v>
+        <v>1546</v>
       </c>
       <c r="E10" s="27" t="s">
         <v>925</v>
@@ -16103,16 +19394,16 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>1218</v>
+        <v>1547</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>1219</v>
+        <v>1548</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>1220</v>
+        <v>1549</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>1221</v>
+        <v>1550</v>
       </c>
       <c r="E11" s="27" t="s">
         <v>925</v>
@@ -16120,16 +19411,16 @@
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>1222</v>
+        <v>1551</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>1223</v>
+        <v>1552</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>1224</v>
+        <v>1553</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>1225</v>
+        <v>1554</v>
       </c>
       <c r="E12" s="27" t="s">
         <v>925</v>
@@ -16137,16 +19428,16 @@
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>1226</v>
+        <v>1555</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>1227</v>
+        <v>1556</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>1228</v>
+        <v>1557</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>1229</v>
+        <v>1558</v>
       </c>
       <c r="E13" s="27" t="s">
         <v>925</v>
@@ -16154,16 +19445,16 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>1230</v>
+        <v>1559</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>1231</v>
+        <v>1560</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>1232</v>
+        <v>1561</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>1233</v>
+        <v>1562</v>
       </c>
       <c r="E14" s="27" t="s">
         <v>925</v>
@@ -16171,33 +19462,33 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>1234</v>
+        <v>1563</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>1235</v>
+        <v>1564</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>1236</v>
+        <v>1565</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>1237</v>
+        <v>1566</v>
       </c>
       <c r="E15" s="27" t="s">
         <v>925</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>1238</v>
+        <v>1567</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>1239</v>
+        <v>1568</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>1240</v>
+        <v>1569</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>1241</v>
+        <v>1570</v>
       </c>
       <c r="E16" s="27" t="s">
         <v>925</v>
@@ -16205,18 +19496,103 @@
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>1242</v>
+        <v>1571</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>1243</v>
+        <v>1572</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>1244</v>
+        <v>1573</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>1245</v>
-      </c>
-      <c r="E17" s="28"/>
+        <v>1574</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="25" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>1575</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>1576</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>1577</v>
+      </c>
+      <c r="E18" s="27" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="25" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>1579</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>1580</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>1581</v>
+      </c>
+      <c r="E19" s="27" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="25" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E20" s="27" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="25" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>1587</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>1588</v>
+      </c>
+      <c r="E21" s="27" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="25" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>1591</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>1592</v>
+      </c>
+      <c r="E22" s="28"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -16235,6 +19611,11 @@
     <hyperlink ref="E14" r:id="rId13" display="Ouvrir"/>
     <hyperlink ref="E15" r:id="rId14" display="Ouvrir"/>
     <hyperlink ref="E16" r:id="rId15" display="Ouvrir"/>
+    <hyperlink ref="E17" r:id="rId16" display="Ouvrir"/>
+    <hyperlink ref="E18" r:id="rId17" display="Ouvrir"/>
+    <hyperlink ref="E19" r:id="rId18" display="Ouvrir"/>
+    <hyperlink ref="E20" r:id="rId19" display="Ouvrir"/>
+    <hyperlink ref="E21" r:id="rId20" display="Ouvrir"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -16246,7 +19627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -16261,10 +19642,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>1246</v>
+        <v>1593</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1247</v>
+        <v>1594</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>44</v>
@@ -16272,10 +19653,10 @@
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>1248</v>
+        <v>1595</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>1249</v>
+        <v>1596</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>925</v>
@@ -16283,10 +19664,10 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>1250</v>
+        <v>1597</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1251</v>
+        <v>1598</v>
       </c>
       <c r="C3" s="27" t="s">
         <v>925</v>
@@ -16294,10 +19675,10 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>1252</v>
+        <v>1599</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1253</v>
+        <v>1600</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>925</v>
@@ -16305,10 +19686,10 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>1254</v>
+        <v>1601</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1255</v>
+        <v>1602</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>925</v>
@@ -16316,10 +19697,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>1256</v>
+        <v>1603</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1257</v>
+        <v>1604</v>
       </c>
       <c r="C6" s="27" t="s">
         <v>925</v>
@@ -16327,10 +19708,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>1258</v>
+        <v>1605</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>1259</v>
+        <v>1606</v>
       </c>
       <c r="C7" s="27" t="s">
         <v>925</v>
@@ -16338,10 +19719,10 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>1260</v>
+        <v>1607</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1261</v>
+        <v>1608</v>
       </c>
       <c r="C8" s="27" t="s">
         <v>925</v>
@@ -16349,10 +19730,10 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>1262</v>
+        <v>1609</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1263</v>
+        <v>1610</v>
       </c>
       <c r="C9" s="27" t="s">
         <v>925</v>
@@ -16360,10 +19741,10 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>1264</v>
+        <v>1611</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1265</v>
+        <v>1612</v>
       </c>
       <c r="C10" s="27" t="s">
         <v>925</v>
@@ -16371,10 +19752,10 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>1266</v>
+        <v>1613</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>1267</v>
+        <v>1614</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>925</v>
@@ -16382,7 +19763,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>1268</v>
+        <v>1615</v>
       </c>
     </row>
   </sheetData>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'Demandes RFQ'!$A$1:$N$53</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Prospects!$A$1:$Q$198</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">Prospects!$A$1:$Q$400</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3140" uniqueCount="1616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3140" uniqueCount="1617">
   <si>
     <t xml:space="preserve">Prospection MINYALA — mode d'emploi</t>
   </si>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">2. Commencez par la priorité 1 (revendeurs, showrooms, marbreries : ils peuvent reprendre un gros lot), puis la 2.</t>
   </si>
   <si>
-    <t xml:space="preserve">3. Appelez ou écrivez avec le message du kit de vente (section 4). Remplissez seulement les cases jaunes.</t>
+    <t xml:space="preserve">3. Appelez ou écrivez avec le message du kit de vente (section 4). Au téléphone, proposez de ne plus rappeler et notez tout refus dans Notes. Remplissez seulement les cases jaunes.</t>
   </si>
   <si>
     <t xml:space="preserve">4. Particuliers : pas de liste de personnes (interdit sans leur accord). L'onglet Particuliers liste où les trouver : annonces, forums, foires, publicité.</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">Paris, couvre le 92 et le 95</t>
   </si>
   <si>
-    <t xml:space="preserve">Constructeur de piscines : les plages et abords se font en dallage.</t>
+    <t xml:space="preserve">Constructeur de piscines : les plages et abords se font en dallage (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">SARL A.C. Paysages</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">Gennevilliers (92230)</t>
   </si>
   <si>
-    <t xml:space="preserve">Entreprise de construction installée à Gennevilliers, comme votre point de retrait.</t>
+    <t xml:space="preserve">Entreprise de construction installée à Gennevilliers, comme votre point de retrait francilien.</t>
   </si>
   <si>
     <t xml:space="preserve">Translin Aurelien</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">Versailles (78000)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cette marbrerie de Versailles, qui a aussi un showroom à Pont-l'Évêque, vend déjà du dallage en pierre naturelle pour terrasses et abords de piscine : MINYALA peut entrer dans sa gamme.</t>
+    <t xml:space="preserve">Cette marbrerie de Versailles, qui a aussi un showroom à Pont-l'Évêque, vend déjà du dallage en pierre naturelle pour terrasses et abords de piscine : MINYALA peut entrer dans sa gamme (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.mdy-france.com</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">Coignières (78310)</t>
   </si>
   <si>
-    <t xml:space="preserve">Son showroom vend déjà carrelages extérieurs, margelles et dallages : MINYALA pourrait compléter sa gamme de plages de piscine dans les Yvelines.</t>
+    <t xml:space="preserve">Son showroom vend déjà carrelages extérieurs, margelles et dallages : MINYALA pourrait compléter sa gamme de plages de piscine dans les Yvelines (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">coignieres.mondial-piscine.eu</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">Deuil-la-Barre (95170)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce paysagiste du Val-d'Oise fait de la pierre naturelle son matériau de prédilection et utilise déjà un calcaire à patine dorée : MINYALA, crème veiné d'or, peut compléter sa gamme pour terrasses et dallages.</t>
+    <t xml:space="preserve">Ce paysagiste du Val-d'Oise fait de la pierre naturelle son matériau de prédilection et utilise déjà un calcaire à patine dorée : MINYALA, de teinte crème, peut compléter sa gamme pour terrasses et dallages.</t>
   </si>
   <si>
     <t xml:space="preserve">lemondedesjardins.fr</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">Les Essarts-le-Roi (78690)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce pisciniste fait aussi la maçonnerie et les aménagements extérieurs et paysagers : il peut poser MINYALA en plage ou en terrasse autour de ses bassins.</t>
+    <t xml:space="preserve">Ce pisciniste fait aussi la maçonnerie et les aménagements extérieurs et paysagers : il peut poser MINYALA en plage ou en terrasse autour de ses bassins (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">aquagarden78.fr</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">Paris (75013)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce pisciniste parisien haut de gamme, qui travaille pour des particuliers et des hôtels de luxe, peut prescrire MINYALA pour les plages et les sols de spa.</t>
+    <t xml:space="preserve">Ce pisciniste parisien haut de gamme, qui travaille pour des particuliers et des hôtels de luxe, peut prescrire MINYALA pour les plages et les sols de spa (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.idoine-piscines.com</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">Bouafle (78410)</t>
   </si>
   <si>
-    <t xml:space="preserve">Constructeur de piscines béton sur mesure dans le 78 et le 92 qui réalise aussi terrasses et margelles autour des bassins, il pourrait poser MINYALA sur des plages de piscine haut de gamme.</t>
+    <t xml:space="preserve">Constructeur de piscines béton sur mesure dans le 78 et le 92 qui réalise aussi terrasses et margelles autour des bassins, il pourrait poser MINYALA sur des plages de piscine haut de gamme (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.idealpiscine.com</t>
@@ -788,7 +788,7 @@
     <t xml:space="preserve">Sèvres (92310)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce constructeur de piscines béton de Sèvres propose déjà des margelles en pierre naturelle dans toute l'Île-de-France, donc MINYALA peut compléter son offre de margelles et de plages.</t>
+    <t xml:space="preserve">Ce constructeur de piscines béton de Sèvres propose déjà des margelles en pierre naturelle dans toute l'Île-de-France, donc MINYALA peut compléter son offre de margelles et de plages (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.kristech.fr</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">La Boutique de la Piscine et du Spa (concessionnaire Magiline 92/95)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce constructeur de piscines béton, qui intervient à Colombes, Nanterre et Argenteuil, tout près de Gennevilliers, pourrait proposer MINYALA pour les plages et abords de ses bassins.</t>
+    <t xml:space="preserve">Ce constructeur de piscines béton, qui intervient à Colombes, Nanterre et Argenteuil, tout près de Gennevilliers, pourrait proposer MINYALA pour les plages et abords de ses bassins (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.la-boutique-piscine-spa.fr</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">Piscines du Vexin</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce pisciniste du Val-d'Oise réalise déjà des terrasses et plages en travertin et pierre naturelle : MINYALA peut entrer dans ses devis de dallage.</t>
+    <t xml:space="preserve">Ce pisciniste du Val-d'Oise réalise déjà des terrasses et plages en travertin et pierre naturelle : MINYALA peut entrer dans ses devis de dallage (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.piscines-spas-iledefrance.fr</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">Cergy (95000)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce constructeur de piscines béton du Val-d'Oise pose déjà des margelles en pierre, des dallages et des pourtours de piscine, un usage direct pour MINYALA.</t>
+    <t xml:space="preserve">Ce constructeur de piscines béton du Val-d'Oise pose déjà des margelles en pierre, des dallages et des pourtours de piscine, MINYALA peut y être proposé selon finition et pose.</t>
   </si>
   <si>
     <t xml:space="preserve">www.socorebat-95.fr</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">Agave Paysage</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce paysagiste parisien pose des dallages en pierre sur plots ou sur lit de sable pour des terrasses, une pose compatible avec MINYALA en 2 cm.</t>
+    <t xml:space="preserve">Ce paysagiste parisien pose des dallages en pierre sur plots ou sur lit de sable pour des terrasses, à vérifier avec lui : un calcaire de 2 cm est déconseillé sur plots sans avis technique.</t>
   </si>
   <si>
     <t xml:space="preserve">agavepaysage.fr</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">Apis Florae</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce paysagiste de Rueil primé sur Houzz fait de la maçonnerie, des terrasses et des abords de piscine : il pourrait proposer MINYALA à ses clients.</t>
+    <t xml:space="preserve">Ce paysagiste de Rueil primé sur Houzz fait de la maçonnerie, des terrasses et des abords de piscine : il pourrait proposer MINYALA à ses clients (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.apisflorae.com</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">Atelier Concept Paysage (ACP)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce paysagiste voisin de Gennevilliers pose des dallages de jardin et du pavage, un usage direct pour les dalles MINYALA.</t>
+    <t xml:space="preserve">Ce paysagiste voisin de Gennevilliers pose des dallages de jardin et du pavage, MINYALA peut y être proposé selon finition et pose.</t>
   </si>
   <si>
     <t xml:space="preserve">www.atelier-concept-paysage.com</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">Montesson (78360)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce paysagiste de la boucle de Seine pose déjà pierre naturelle et travertin sur terrasses et abords de piscine : MINYALA est une alternative en stock à 27 €/m² TTC (prix pro).</t>
+    <t xml:space="preserve">Ce paysagiste de la boucle de Seine pose déjà pierre naturelle et travertin sur terrasses et abords de piscine : MINYALA est une alternative en stock à 27 €/m² TTC (prix pro) (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">edenvatinel.fr</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">Les Jardins de la Vallée</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce paysagiste-pisciniste des Yvelines pose déjà des terrasses en travertin calcaire : MINYALA est une alternative directe pour ses terrasses et abords de piscine.</t>
+    <t xml:space="preserve">Ce paysagiste-pisciniste des Yvelines pose déjà des terrasses en travertin calcaire : MINYALA est une alternative directe pour ses terrasses et abords de piscine (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.jardinsdelavallee.fr</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">Paris (75016)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce paysagiste parisien avec showroom dans le 16e réalise les sols de terrasses et rooftops d'hôtels et de restaurants, il pourrait y poser MINYALA sur plots.</t>
+    <t xml:space="preserve">Ce paysagiste parisien avec showroom dans le 16e réalise les sols de terrasses et rooftops d'hôtels et de restaurants, il pourrait y proposer MINYALA (pose sur plots déconseillée en 2 cm sans avis technique).</t>
   </si>
   <si>
     <t xml:space="preserve">terrasseetjardindeparis.com</t>
@@ -1001,7 +1001,7 @@
     <t xml:space="preserve">Marcq (78770)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce carreleur des Yvelines pose des dallages en pierre naturelle, des terrasses et des carrelages de piscine, il pourrait acheter et poser MINYALA pour ses clients.</t>
+    <t xml:space="preserve">Ce carreleur des Yvelines pose des dallages en pierre naturelle, des terrasses et des carrelages de piscine, il pourrait acheter et poser MINYALA pour ses clients (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">Rénovation haut de gamme</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">La Roche Taillée</t>
   </si>
   <si>
-    <t xml:space="preserve">Cet atelier rouennais de taille de pierre vend déjà dallages et margelles de piscine en calcaire : il peut proposer MINYALA brut à sa clientèle.</t>
+    <t xml:space="preserve">Cet atelier rouennais de taille de pierre vend déjà dallages et margelles de piscine en calcaire : il peut proposer MINYALA brut à sa clientèle (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.la-roche-taillee.fr</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">Eslettes (76710)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cette marbrerie près de Rouen réalise des dallages en pierre naturelle en intérieur, sur terrasses et autour des piscines, un relais possible pour MINYALA en Normandie.</t>
+    <t xml:space="preserve">Cette marbrerie près de Rouen réalise des dallages en pierre naturelle en intérieur, sur terrasses et autour des piscines, un relais possible pour MINYALA en Normandie (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.marbresettendances.com</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">Bacqueville-en-Caux (76730)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce constructeur de piscines béton haut de gamme de Seine-Maritime réalise déjà des terrasses et plages de piscine en grandes dalles, exactement l'usage de MINYALA.</t>
+    <t xml:space="preserve">Ce constructeur de piscines béton haut de gamme de Seine-Maritime réalise déjà des terrasses et plages de piscine en grandes dalles, un usage possible de MINYALA selon finition et pose.</t>
   </si>
   <si>
     <t xml:space="preserve">www.bohinjardin.fr</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">Touques (14800)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pisciniste de la Côte Fleurie avec showrooms à Deauville et Pont-l'Évêque, il propose margelles et terrasses autour de piscines haut de gamme où MINYALA a sa place.</t>
+    <t xml:space="preserve">Pisciniste de la Côte Fleurie avec showrooms à Deauville et Pont-l'Évêque, il propose margelles et terrasses autour de piscines haut de gamme où MINYALA a sa place (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.piscines-delalande.fr</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">Bois-Guillaume (76230)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce pisciniste rouennais construit des terrasses périphériques en bois ou en pierre autour de ses piscines, un usage direct pour les dalles MINYALA.</t>
+    <t xml:space="preserve">Ce pisciniste rouennais construit des terrasses périphériques en bois ou en pierre autour de ses piscines, MINYALA peut y être proposé selon finition et pose.</t>
   </si>
   <si>
     <t xml:space="preserve">www.jardinpassions.fr</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">Saint-Arnoult (Deauville) (14800)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce constructeur de piscines béton de la Côte Fleurie, qui rénove aussi des bassins, peut poser MINYALA en margelles et en plages pour une clientèle aisée.</t>
+    <t xml:space="preserve">Ce constructeur de piscines béton de la Côte Fleurie, qui rénove aussi des bassins, peut poser MINYALA en margelles et en plages pour une clientèle aisée (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.larcher.fr</t>
@@ -1226,7 +1226,7 @@
     <t xml:space="preserve">Franqueville-Saint-Pierre (76520)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce pisciniste rouennais rénove margelles et plages : MINYALA peut remplacer d'anciennes plages lors de ses chantiers.</t>
+    <t xml:space="preserve">Ce pisciniste rouennais rénove margelles et plages : MINYALA peut remplacer d'anciennes plages lors de ses chantiers (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.lespiscinesmoreau.com</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">Montivilliers (76290)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cette agence de la région du Havre construit des piscines et réalise allées, terrasses et remplacement de margelles, des chantiers adaptés à MINYALA.</t>
+    <t xml:space="preserve">Cette agence de la région du Havre construit des piscines et réalise allées, terrasses et remplacement de margelles, des chantiers adaptés à MINYALA (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.piscines-de-france.fr/piscinistes/pisciniste-le-havre</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">Angerville-l'Orcher (76280)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce pisciniste du pays de Caux propose déjà des margelles en pierre naturelle ou en travertin de la région du Havre jusqu'à Deauville et Évreux : MINYALA peut servir pour ses plages.</t>
+    <t xml:space="preserve">Ce pisciniste du pays de Caux propose déjà des margelles en pierre naturelle ou en travertin de la région du Havre jusqu'à Deauville et Évreux : MINYALA peut servir pour ses plages (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.piscinesetabrisnordouest.fr</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">Firfol (14100)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce paysagiste haut de gamme du Pays d'Auge construit des piscines et pose margelles et terrasses : MINYALA convient pour ses plages et ses patios.</t>
+    <t xml:space="preserve">Ce paysagiste haut de gamme du Pays d'Auge construit des piscines et pose margelles et terrasses : MINYALA convient pour ses plages et ses patios (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.rpay.fr</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">Deauville (14800)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce maître d'œuvre de Deauville réalise des terrasses, des piscines et des rénovations : il peut prescrire MINYALA en dallage de terrasse ou en plage de piscine.</t>
+    <t xml:space="preserve">Ce maître d'œuvre de Deauville réalise des terrasses, des piscines et des rénovations : il peut prescrire MINYALA en dallage de terrasse ou en plage de piscine (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.conceptinterieurdeauville.com</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">Freneuse (78840)</t>
   </si>
   <si>
-    <t xml:space="preserve">Constructeur et rénovateur de piscines béton sur mesure dans les Yvelines, il pourrait proposer MINYALA pour les plages de ses bassins neufs ou rénovés.</t>
+    <t xml:space="preserve">Constructeur et rénovateur de piscines béton sur mesure dans les Yvelines, il pourrait proposer MINYALA pour les plages de ses bassins neufs ou rénovés (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.aqua-system.fr</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">Croissy-sur-Seine (78290)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce pisciniste de Croissy-sur-Seine, qui construit et rénove des bassins dans le 78, le 92 et le 95, peut proposer MINYALA en margelles et en plages lors de ses chantiers.</t>
+    <t xml:space="preserve">Ce pisciniste de Croissy-sur-Seine, qui construit et rénove des bassins dans le 78, le 92 et le 95, peut proposer MINYALA en margelles et en plages lors de ses chantiers (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.ops-ouestpiscines.fr</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">Paris (75010)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce concepteur-réalisateur parisien choisit les matériaux de ses terrasses et jardins avec piscine : il pourrait prescrire MINYALA.</t>
+    <t xml:space="preserve">Ce concepteur-réalisateur parisien choisit les matériaux de ses terrasses et jardins avec piscine : il pourrait prescrire MINYALA (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.simonsonlandscape.com</t>
@@ -1484,7 +1484,7 @@
     <t xml:space="preserve">Villeneuve-Saint-Georges (94190)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce carreleur du Val-de-Marne pose des dallages en pierre naturelle et des plages de piscine, donc il peut être un client direct pour MINYALA.</t>
+    <t xml:space="preserve">Ce carreleur du Val-de-Marne pose des dallages en pierre naturelle et des plages de piscine, donc il peut être un client direct pour MINYALA (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">Belmard Bâtiment</t>
@@ -1547,7 +1547,7 @@
     <t xml:space="preserve">Sainte-Colombe-la-Commanderie (27110)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce constructeur de piscines enterrées de l'Eure pourrait proposer MINYALA en plage de piscine à ses clients autour d'Évreux.</t>
+    <t xml:space="preserve">Ce constructeur de piscines enterrées de l'Eure pourrait proposer MINYALA en plage de piscine à ses clients autour d'Évreux (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">02 32 24 28 11</t>
@@ -1556,7 +1556,7 @@
     <t xml:space="preserve">Seine et Mer Piscines (concessionnaire Mondial Piscine Rouen)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ce pisciniste de l'est rouennais, avec plus de 150 piscines neuves et 80 rénovations, peut proposer MINYALA en plages et en margelles à ses clients.</t>
+    <t xml:space="preserve">Ce pisciniste de l'est rouennais, avec plus de 150 piscines neuves et 80 rénovations, peut proposer MINYALA en plages et en margelles à ses clients (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">rouen.mondial-piscine.eu</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">Domont (95330)</t>
   </si>
   <si>
-    <t xml:space="preserve">Showroom carrelage du Val-d'Oise qui vend aux particuliers et aux pros, pour terrasses et piscines, et fait du déstockage : il pourrait acheter MINYALA en lot pour le revendre.</t>
+    <t xml:space="preserve">Showroom carrelage du Val-d'Oise qui vend aux particuliers et aux pros, pour terrasses et piscines, et fait du déstockage : il pourrait acheter MINYALA en lot pour le revendre (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">kap-carrelage.store</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">Piscop (95350)</t>
   </si>
   <si>
-    <t xml:space="preserve">Revendeur de carrelages et dallages pour terrasses et piscines qui propose déjà travertin et pierre : un calcaire crème veiné d'or comme MINYALA pourrait compléter sa gamme.</t>
+    <t xml:space="preserve">Revendeur de carrelages et dallages pour terrasses et piscines qui propose déjà travertin et pierre : un calcaire crème comme MINYALA pourrait compléter sa gamme (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">Décomarbre</t>
@@ -1934,7 +1934,7 @@
     <t xml:space="preserve">Paysages Conseil – Agence de Caen</t>
   </si>
   <si>
-    <t xml:space="preserve">Gros paysagiste normand (75 compagnons, plusieurs agences) qui réalise des terrasses en pierre naturelle et des aménagements autour des piscines et spas, MINYALA pourrait servir sur ses chantiers.</t>
+    <t xml:space="preserve">Gros paysagiste normand (75 compagnons, plusieurs agences) qui réalise des terrasses en pierre naturelle et des aménagements autour des piscines et spas, MINYALA pourrait servir sur ses chantiers (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.paysagesconseil.fr/paysagiste-caen</t>
@@ -1949,7 +1949,7 @@
     <t xml:space="preserve">Pont-l'Évêque (14130)</t>
   </si>
   <si>
-    <t xml:space="preserve">Entreprise familiale de pose fondée en 1956, avec 21 poseurs, qui pose marbres, pierres naturelles et terrasses sur plots pour des architectes et promoteurs de la Côte Fleurie : elle pourrait acheter MINYALA par lots.</t>
+    <t xml:space="preserve">Entreprise familiale de pose fondée en 1956, avec 21 poseurs, qui pose marbres, pierres naturelles et terrasses sur plots pour des architectes et promoteurs de la Côte Fleurie : elle pourrait acheter MINYALA par lots (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.tragin-sa.com</t>
@@ -2069,7 +2069,7 @@
     <t xml:space="preserve">Jumeauville (78580)</t>
   </si>
   <si>
-    <t xml:space="preserve">Entreprise des Yvelines qui pose déjà des terrasses en pierre naturelle (travertin, quartzite, granit), traditionnellement ou sur plots : MINYALA pourrait entrer dans ses choix de dallage.</t>
+    <t xml:space="preserve">Entreprise des Yvelines qui pose déjà des terrasses en pierre naturelle (travertin, quartzite, granit), traditionnellement ou sur plots : MINYALA pourrait entrer dans ses choix de dallage (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">ci-renovation-78.fr</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">Buchelay (78200)</t>
   </si>
   <si>
-    <t xml:space="preserve">Contractant général du secteur Mantes-Vernon qui réalise extensions, cuisines, salles de bains, piscines et terrasses, dont des terrasses en pierre naturelle, il pourrait choisir MINYALA pour ses chantiers.</t>
+    <t xml:space="preserve">Contractant général du secteur Mantes-Vernon qui réalise extensions, cuisines, salles de bains, piscines et terrasses, dont des terrasses en pierre naturelle, il pourrait choisir MINYALA pour ses chantiers (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.architea.fr/architea-vallee-de-la-seine-ouest</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">Magny-le-Hongre (77700)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ancien Radisson Blu rénové par IHG qui prévoit une piscine extérieure avec bar pour le printemps 2027 : ses plages et terrasses sont une occasion pour MINYALA selon la finition et la pose.</t>
+    <t xml:space="preserve">Ancien Radisson Blu rénové par IHG qui prévoit une piscine extérieure avec bar pour le printemps 2027 : ses plages et terrasses sont une occasion pour MINYALA selon la finition et la pose (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">Spa / hammam</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">DPS France</t>
   </si>
   <si>
-    <t xml:space="preserve">Installateur de hammams maçonnés en Île-de-France dont les cabines ont des bancs en pierre ou en marbre : MINYALA pourrait habiller les sols et les banquettes.</t>
+    <t xml:space="preserve">Installateur de hammams maçonnés en Île-de-France dont les cabines ont des bancs en pierre ou en marbre : MINYALA pourrait habiller les sols et les banquettes (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.dps-france.fr</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">FTP Services</t>
   </si>
   <si>
-    <t xml:space="preserve">Concepteur-installateur de hammams et saunas livrés prêts à carreler pour l'hôtellerie et le wellness, il pourrait prescrire MINYALA pour les sols et abords des espaces bien-être qu'il réalise.</t>
+    <t xml:space="preserve">Concepteur-installateur de hammams et saunas livrés prêts à carreler pour l'hôtellerie et le wellness, il pourrait prescrire MINYALA pour les sols et abords des espaces bien-être qu'il réalise (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.ftp-services.fr</t>
@@ -2201,7 +2201,7 @@
     <t xml:space="preserve">Chevreuse (78460)</t>
   </si>
   <si>
-    <t xml:space="preserve">Constructeur de maisons 100 % sur mesure présent dans toute l'Île-de-France, qui réalise maisons avec piscine et terrasse et propose le carrelage parmi ses finitions, il pourrait proposer MINYALA pour les sols intérieurs et les terrasses.</t>
+    <t xml:space="preserve">Constructeur de maisons 100 % sur mesure présent dans toute l'Île-de-France, qui réalise maisons avec piscine et terrasse et propose le carrelage parmi ses finitions, il pourrait proposer MINYALA pour les sols intérieurs et les terrasses (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.maisonsarchidesign.com</t>
@@ -2303,7 +2303,7 @@
     <t xml:space="preserve">Le Torpt (27210)</t>
   </si>
   <si>
-    <t xml:space="preserve">Constructeur de piscines près de Honfleur qui pose des terrasses en pierre naturelle et installe des hammams : il pourrait utiliser MINYALA pour ses plages et ses espaces bien-être.</t>
+    <t xml:space="preserve">Constructeur de piscines près de Honfleur qui pose des terrasses en pierre naturelle et installe des hammams : il pourrait utiliser MINYALA pour ses plages et ses espaces bien-être (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.vincent-locquet.fr</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">Trouville-sur-Mer (14360)</t>
   </si>
   <si>
-    <t xml:space="preserve">Paysagiste de Trouville qui réalise allées pavées, dallage de jardin et aménagements autour des piscines : MINYALA pourrait servir en terrasse et en abords de piscine selon la finition et la pose.</t>
+    <t xml:space="preserve">Paysagiste de Trouville qui réalise allées pavées, dallage de jardin et aménagements autour des piscines : MINYALA pourrait servir en terrasse et en abords de piscine selon la finition et la pose (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">06 58 42 48 61</t>
@@ -2339,7 +2339,7 @@
     <t xml:space="preserve">Saint-Vaast-en-Auge (14640)</t>
   </si>
   <si>
-    <t xml:space="preserve">Paysagiste de la Côte Fleurie qui a déjà réalisé une terrasse en travertin à Villers-sur-Mer et aménage les abords de piscines, il pourrait poser MINYALA en terrasses et allées.</t>
+    <t xml:space="preserve">Paysagiste de la Côte Fleurie qui a déjà réalisé une terrasse en travertin à Villers-sur-Mer et aménage les abords de piscines, il pourrait poser MINYALA en terrasses et allées (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.paysagiste-auberville.fr</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">Villers-sur-Mer (14640)</t>
   </si>
   <si>
-    <t xml:space="preserve">Paysagiste de la côte du Calvados qui pose dallages, terrasses en pierre et tours de piscine pour des résidences secondaires : bon débouché pour MINYALA en extérieur.</t>
+    <t xml:space="preserve">Paysagiste de la côte du Calvados qui pose dallages, terrasses en pierre et tours de piscine pour des résidences secondaires : bon débouché pour MINYALA en extérieur (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.dumouchel.fr</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">Gonfreville-l'Orcher (76700)</t>
   </si>
   <si>
-    <t xml:space="preserve">Carreleur normand qui réalise des hammams et pose déjà de la pierre naturelle (Bourgogne, Comblanchien, marbre), il pourrait proposer MINYALA comme autre pierre claire à ses clients.</t>
+    <t xml:space="preserve">Carreleur normand qui réalise des hammams et pose déjà de la pierre naturelle (Bourgogne, Comblanchien, marbre), il pourrait proposer MINYALA comme autre pierre claire à ses clients (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">yl-carrelage.fr</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">Saint-Julien-de-Mailloc (14290)</t>
   </si>
   <si>
-    <t xml:space="preserve">Contractant général qui rénove manoirs, hôtels et restaurants de prestige et crée des piscines avec terrasses en matériaux nobles : il pourrait prescrire MINYALA pour les sols et abords de piscine.</t>
+    <t xml:space="preserve">Contractant général qui rénove manoirs, hôtels et restaurants de prestige et crée des piscines avec terrasses en matériaux nobles : il pourrait prescrire MINYALA pour les sols et abords de piscine (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.architea.fr/architea-pays-auge-cote-fleurie</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">Bretteville-l'Orgueilleuse (14740)</t>
   </si>
   <si>
-    <t xml:space="preserve">Fabricant normand de hammams et saunas sur mesure pour hôtels et particuliers, dont les hammams traditionnels sont habillés de carrelage ou de marbre : il pourrait prescrire MINYALA dans les espaces bien-être qu'il aménage.</t>
+    <t xml:space="preserve">Fabricant normand de hammams et saunas sur mesure pour hôtels et particuliers, dont les hammams traditionnels sont habillés de carrelage ou de marbre : il pourrait prescrire MINYALA dans les espaces bien-être qu'il aménage (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.bienetreconfort.fr</t>
@@ -2546,7 +2546,7 @@
     <t xml:space="preserve">Crécy-la-Chapelle (77580)</t>
   </si>
   <si>
-    <t xml:space="preserve">Constructeur seine-et-marnais de piscines béton et d'espaces bien-être (spas, saunas, hammams) : MINYALA pourrait servir pour les abords de bassin et les sols de ses espaces détente.</t>
+    <t xml:space="preserve">Constructeur seine-et-marnais de piscines béton et d'espaces bien-être (spas, saunas, hammams) : MINYALA pourrait servir pour les abords de bassin et les sols de ses espaces détente (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.oceapiscine.fr</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">Grosrouvre (78490)</t>
   </si>
   <si>
-    <t xml:space="preserve">Constructeur familial de maisons sur mesure haut de gamme dans l'ouest francilien, dont des maisons avec piscine et terrasse : MINYALA pourrait convenir à leurs sols et extérieurs.</t>
+    <t xml:space="preserve">Constructeur familial de maisons sur mesure haut de gamme dans l'ouest francilien, dont des maisons avec piscine et terrasse : MINYALA pourrait convenir à leurs sols et extérieurs (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.francemaisons-idf.com</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">L'Isle-Adam (95290)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pisciniste familial du Val-d'Oise qui construit des piscines avec plage et installe saunas et hammams, il pourrait utiliser MINYALA pour les plages et abords de ses bassins.</t>
+    <t xml:space="preserve">Pisciniste familial du Val-d'Oise qui construit des piscines avec plage et installe saunas et hammams, il pourrait utiliser MINYALA pour les plages et abords de ses bassins (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.henocquepiscines.fr</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">Sainte-Adresse (76310)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pisciniste de Sainte-Adresse qui construit et rénove des piscines sur mesure et propose spas, saunas et hammams : MINYALA pourrait l'intéresser pour les plages et abords de piscine selon la finition.</t>
+    <t xml:space="preserve">Pisciniste de Sainte-Adresse qui construit et rénove des piscines sur mesure et propose spas, saunas et hammams : MINYALA pourrait l'intéresser pour les plages et abords de piscine selon la finition (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">Piscines du Pays d'Auge</t>
@@ -2696,7 +2696,7 @@
     <t xml:space="preserve">Clarbec (14130)</t>
   </si>
   <si>
-    <t xml:space="preserve">Pisciniste du Pays d'Auge qui construit des piscines et installe spas, saunas et hammams autour de Deauville : MINYALA pourrait servir pour les plages de piscine selon la finition et la pose.</t>
+    <t xml:space="preserve">Pisciniste du Pays d'Auge qui construit des piscines et installe spas, saunas et hammams autour de Deauville : MINYALA pourrait servir pour les plages de piscine selon la finition et la pose (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">06 84 59 00 74</t>
@@ -2723,7 +2723,7 @@
     <t xml:space="preserve">Tourgéville (14800)</t>
   </si>
   <si>
-    <t xml:space="preserve">Entreprise générale de Tourgéville sur des projets de 50 000 € à 1 M€ (rénovation de luxe, terrasses, piscine à Deauville) : elle pourrait acheter MINYALA pour les terrasses et sols de villas.</t>
+    <t xml:space="preserve">Entreprise générale de Tourgéville sur des projets de 50 000 € à 1 M€ (rénovation de luxe, terrasses, piscine à Deauville) : elle pourrait acheter MINYALA pour les terrasses et sols de villas (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">06 44 04 41 65</t>
@@ -2765,7 +2765,7 @@
     <t xml:space="preserve">Fontenay-le-Marmion (14320)</t>
   </si>
   <si>
-    <t xml:space="preserve">Maître artisan près de Caen qui rénove des salles de bains clé en main (carrelage compris), installe hammams et saunas et crée des terrasses, il pourrait poser MINYALA en sols de salles d'eau ou de terrasses.</t>
+    <t xml:space="preserve">Maître artisan près de Caen qui rénove des salles de bains clé en main (carrelage compris), installe hammams et saunas et crée des terrasses, il pourrait poser MINYALA en sols de salles d'eau ou de terrasses (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">masolution-habitat.fr</t>
@@ -2777,7 +2777,7 @@
     <t xml:space="preserve">Maisons Socoren (agence de Caen)</t>
   </si>
   <si>
-    <t xml:space="preserve">Constructeur de maisons bois haut de gamme sur mesure dont les réalisations dans le Calvados comprennent piscine et terrasse, il pourrait proposer MINYALA pour les abords et les sols de ces maisons.</t>
+    <t xml:space="preserve">Constructeur de maisons bois haut de gamme sur mesure dont les réalisations dans le Calvados comprennent piscine et terrasse, il pourrait proposer MINYALA pour les abords et les sols de ces maisons (usage à valider avec lui : finition, gel, glissance, humidité).</t>
   </si>
   <si>
     <t xml:space="preserve">www.socoren.com</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">Particuliers et petits artisans qui cherchent de la pierre près de chez eux</t>
   </si>
   <si>
-    <t xml:space="preserve">Annonce localisée à Gennevilliers</t>
+    <t xml:space="preserve">Annonce localisée à Gennevilliers, et une 2e à Vernon (27) dès que l'adresse est connue</t>
   </si>
   <si>
     <t xml:space="preserve">Ouvrir un compte Pro (obligatoire pour une entreprise). Une annonce par usage : terrasse, plage de piscine, sol intérieur. Prix au m², minimum 25 m², retrait sur rendez-vous. Republier au printemps.</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">Recherche locale</t>
   </si>
   <si>
-    <t xml:space="preserve">Créer la fiche du point de retrait : catégorie fournisseur de pierre, retrait sur rendez-vous, photos réelles, lien vers la fiche MINYALA. Demander un avis à chaque client.</t>
+    <t xml:space="preserve">Créer une fiche par point de retrait (Gennevilliers, puis Vernon dès que l'adresse est connue) : catégorie fournisseur de pierre, retrait sur rendez-vous, photos réelles, lien vers la fiche MINYALA. Demander un avis à chaque client.</t>
   </si>
   <si>
     <t xml:space="preserve">Gratuit</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">Recherche par ville (rayon 10 à 100 km)</t>
   </si>
   <si>
-    <t xml:space="preserve">Créer un profil pro situé à Gennevilliers avec photos de MINYALA posé, prix au m² et minimum de commande. Demander des avis clients.</t>
+    <t xml:space="preserve">Créer un profil pro situé à Gennevilliers (zone d'intervention incluant l'Eure / Vernon) avec photos de MINYALA posé, prix au m² et minimum de commande. Demander des avis clients.</t>
   </si>
   <si>
     <t xml:space="preserve">Inscription gratuite (options payantes à vérifier)</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">92, 95, 78, 93, Normandie</t>
   </si>
   <si>
-    <t xml:space="preserve">Aucun groupe n'a pu être vérifié par la recherche. Dans Facebook, cherchez « travaux maison 92 », « piscine Île-de-France », « jardin Normandie », « bons plans matériaux », « déstockage matériaux ». Lisez le règlement : ne publiez que là où les pros sont autorisés, idéalement avec l'accord des administrateurs.</t>
+    <t xml:space="preserve">Voir l'onglet Groupes Facebook (22 groupes repérés). Pour d'autres groupes locaux, dans Facebook, cherchez « travaux maison 92 », « piscine Île-de-France », « jardin Normandie », « bons plans matériaux », « déstockage matériaux ». Lisez le règlement : ne publiez que là où les pros sont autorisés, idéalement avec l'accord des administrateurs.</t>
   </si>
   <si>
     <t xml:space="preserve">ForumConstruire — Terrasse « en dur »</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">Futurs acheteurs qui vérifient un vendeur</t>
   </si>
   <si>
-    <t xml:space="preserve">Inviter les clients satisfaits à laisser un avis spontané. Ne jamais rédiger de faux avis (sanctionné).</t>
+    <t xml:space="preserve">Inviter chaque client, sans tri, à laisser un avis après le retrait ou la livraison. Ne jamais rédiger de faux avis ni offrir de contrepartie (sanctionné).</t>
   </si>
   <si>
     <t xml:space="preserve">Foire de Rouen 2027</t>
@@ -3086,10 +3086,10 @@
     <t xml:space="preserve">Personnes qui cherchent activement de la pierre</t>
   </si>
   <si>
-    <t xml:space="preserve">Rayon autour de Gennevilliers ; Rouen, Le Havre, Caen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mots-clés du kit de vente (« dalle pierre naturelle terrasse », « pierre calcaire 30x60 », « déstockage pierre naturelle »…), option « présence » pour la zone de retrait. Exclure « gratuit » et « tuto ».</t>
+    <t xml:space="preserve">Rayons autour de Gennevilliers (92) et de Vernon (27) ; Rouen, Le Havre, Caen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mots-clés du kit de vente, section 5 (« pierre naturelle terrasse », « dalle calcaire 30x60 », « pierre calcaire extérieur »…), option « présence » pour la zone de retrait. Exclure « gratuit » et « tuto ».</t>
   </si>
   <si>
     <t xml:space="preserve">Budget libre (au clic)</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">Zone choisie par le pro</t>
   </si>
   <si>
-    <t xml:space="preserve">Pierre d'Égypte ne pose pas : s'associer à des carreleurs ou paysagistes inscrits qui proposent MINYALA dans leurs devis de dallage.</t>
+    <t xml:space="preserve">Pierre d'Égypte propose livraison et pose sur devis à partir de 100 m² ; en dessous, s'associer à des carreleurs ou paysagistes inscrits qui proposent MINYALA dans leurs devis de dallage.</t>
   </si>
   <si>
     <t xml:space="preserve">Salon Maison &amp; Jardin du Havre 2027</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">Utilisateurs d'iPhone qui cherchent un fournisseur près de Gennevilliers</t>
   </si>
   <si>
-    <t xml:space="preserve">Point de retrait de Gennevilliers</t>
+    <t xml:space="preserve">Point de retrait de Gennevilliers, puis Vernon (27) dès que l'adresse est connue</t>
   </si>
   <si>
     <t xml:space="preserve">Créer la fiche avec photos, « sur rendez-vous » et lien vers la boutique, comme la fiche Google.</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">Décrochages Yvelines et Seine-Maritime</t>
   </si>
   <si>
-    <t xml:space="preserve">Spots courts au printemps (« terrasse en pierre naturelle à 35 €/m² ») renvoyant vers la fiche produit.</t>
+    <t xml:space="preserve">Spots courts au printemps (« pierre naturelle pour terrasse : 35 €/m² pierre seule, dès 25 m², à retirer à Gennevilliers ou Vernon ») renvoyant vers la fiche produit.</t>
   </si>
   <si>
     <t xml:space="preserve">Patrimoine Normand (revue trimestrielle)</t>
@@ -3386,7 +3386,7 @@
     <t xml:space="preserve">• Collecter des contacts avec une case de consentement non pré-cochée (formulaire « recevoir les prix / le guide de pose », foires). Sans ce consentement, pas d'e-mail, de SMS ni d'appel à un particulier.</t>
   </si>
   <si>
-    <t xml:space="preserve">• À décider : échantillons à retirer à Gennevilliers, tarif pour poseurs partenaires. Rien de cela n'existe aujourd'hui sur le site.</t>
+    <t xml:space="preserve">• À décider : échantillons à retirer à Gennevilliers ou Vernon. Le tarif pro (27 € TTC) existe désormais, par devis et facture uniquement.</t>
   </si>
   <si>
     <t xml:space="preserve">Correspondance</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">2026-05-19</t>
   </si>
   <si>
-    <t xml:space="preserve">Pierre égyptienne Sunny, de la même famille que la Minyala (Minya). L'acheteur est un grossiste qui livre toute l'Autriche et le sud de l'Allemagne, ce qui en fait un débouché européen proche. Il demande si la pierre résiste au gel.</t>
+    <t xml:space="preserve">Pierre égyptienne Sunny (région de Minya) : même famille que MINYALA seulement si l'origine Minya est confirmée. L'acheteur est un grossiste qui livre toute l'Autriche et le sud de l'Allemagne, ce qui en fait un débouché européen proche. Il demande si la pierre résiste au gel.</t>
   </si>
   <si>
     <t xml:space="preserve">À étudier</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">2026-05-06</t>
   </si>
   <si>
-    <t xml:space="preserve">Correction : Size: '2x2' (units not stated on the page; the buyer also asks whether smaller sizes exist). Quantity: not stated. Destination: USA. Date: 2026-05-06. — Le produit est exactement la famille Sunny de Minya, mais l'acheteur est aux États-Unis et veut des mosaïques 2×2 pouces. La destination est lointaine et le format ne correspond pas.</t>
+    <t xml:space="preserve">Correction : Size: '2x2' (units not stated on the page; the buyer also asks whether smaller sizes exist). Quantity: not stated. Destination: USA. Date: 2026-05-06. — Le produit est de la famille Sunny de Minya (proche de MINYALA si l'origine est confirmée), mais l'acheteur est aux États-Unis et veut des mosaïques 2×2 pouces. La destination est lointaine et le format ne correspond pas.</t>
   </si>
   <si>
     <t xml:space="preserve">Bulk Inquiry - 11000 M2 Beige Marble Slabs 60x120cmx2cm EXW Factory</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">2026-08-31</t>
   </si>
   <si>
-    <t xml:space="preserve">La pierre de référence est de la famille Minya, mais l'acheteur est en Égypte, achète EXW usine et veut 11 000 m² en 60×120. Sans rapport avec un stock de 30×60 à Paris.</t>
+    <t xml:space="preserve">La pierre de référence vient de Minya (lien avec MINYALA à confirmer), mais l'acheteur est en Égypte, achète EXW usine et veut 11 000 m² en 60×120. Sans rapport avec un stock de 30×60 à Paris.</t>
   </si>
   <si>
     <t xml:space="preserve">DIY Interlock Modern Outdoor Anti-slip Stone Deck Tile Floor Marble Tile Limestone Deck Tile Stone ...</t>
@@ -4358,7 +4358,7 @@
     <t xml:space="preserve">Shenzhen, China</t>
   </si>
   <si>
-    <t xml:space="preserve">Exactement la famille de pierre de MINYALA (Sunny Menia, Minya), mais destination Chine (Shenzhen) et format 30x30x1,8 : sans intérêt pour un stock en France.</t>
+    <t xml:space="preserve">Famille Sunny Menia (Minya), proche de MINYALA seulement si l'origine Minya est confirmée, mais destination Chine (Shenzhen) et format 30x30x1,8 : sans intérêt pour un stock en France.</t>
   </si>
   <si>
     <t xml:space="preserve">• « Vérifiée ? = Oui » : la demande a été retrouvée sur la page publique de la plateforme le 12/10/2026.</t>
@@ -4400,7 +4400,7 @@
     <t xml:space="preserve">46,5 K (vu le 12/10/2026)</t>
   </si>
   <si>
-    <t xml:space="preserve">Annonce MINYALA à 27 €/m² TTC postée le 12/10/2026, en attente de validation. Une fois publiée, préciser en commentaire : « Prix pro / gros volume. Particuliers : 35 €/m² sur pierredegypte.online ».</t>
+    <t xml:space="preserve">Groupe mixte pros + particuliers. Annonce à 27 €/m² TTC en attente depuis le 12/10/2026 : demander à l'admin de la modifier ou la retirer AVANT validation, puis republier au prix public 35 €/m² pierre seule avec « Professionnels et gros volumes : tarif sur demande (devis et facture) ». Lien du groupe à ajouter.</t>
   </si>
   <si>
     <t xml:space="preserve">Capture du 12/10</t>
@@ -4421,7 +4421,7 @@
     <t xml:space="preserve">Non relevé</t>
   </si>
   <si>
-    <t xml:space="preserve">Annonce déjà présente (doublon évité le 12/10/2026) : ne pas republier, répondre aux commentaires et messages.</t>
+    <t xml:space="preserve">Annonce déjà présente (doublon évité le 12/10/2026) : ne pas republier, répondre aux commentaires et messages. Lien du groupe à ajouter.</t>
   </si>
   <si>
     <t xml:space="preserve">avant le 12/10/2026</t>
@@ -4481,7 +4481,10 @@
     <t xml:space="preserve">Évreux (27)</t>
   </si>
   <si>
-    <t xml:space="preserve">29 000+ (ici.fr, 2016–2019)</t>
+    <t xml:space="preserve">29 000+ (ici.fr, 2016–2019 ; article de 2016 indisponible)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejoindre avec la Page, lire le règlement, écrire à l'admin avant de publier une seule annonce. (Lien relevé dans un article ici.fr de 2016 aujourd'hui indisponible ; source jointe : article ici.fr de 2019 sur le même réseau.)</t>
   </si>
   <si>
     <t xml:space="preserve">Tu sais que tu viens de… Louviers</t>
@@ -4511,7 +4514,7 @@
     <t xml:space="preserve">Dieppe (76)</t>
   </si>
   <si>
-    <t xml:space="preserve">Vérifier qu'il est actif (source 2016). Rejoindre avec la Page, lire le règlement, écrire à l'admin avant de publier une seule annonce.</t>
+    <t xml:space="preserve">Vérifier qu'il est actif (source 2016). Rejoindre avec la Page, lire le règlement, écrire à l'admin avant de publier une seule annonce. (Lien relevé dans un article ici.fr de 2016 aujourd'hui indisponible ; source jointe : article ici.fr de 2019 sur le même réseau.)</t>
   </si>
   <si>
     <t xml:space="preserve">Tu sais que tu viens de… Fécamp</t>
@@ -4520,7 +4523,7 @@
     <t xml:space="preserve">Fécamp (76)</t>
   </si>
   <si>
-    <t xml:space="preserve">Résidences secondaires du littoral. Rejoindre avec la Page, lire le règlement, écrire à l'admin avant de publier une seule annonce.</t>
+    <t xml:space="preserve">Résidences secondaires du littoral. Rejoindre avec la Page, lire le règlement, écrire à l'admin avant de publier une seule annonce. (Lien relevé dans un article ici.fr de 2016 aujourd'hui indisponible ; source jointe : article ici.fr de 2019 sur le même réseau.)</t>
   </si>
   <si>
     <t xml:space="preserve">Tu sais que tu viens de… Yvetot</t>
@@ -4559,7 +4562,7 @@
     <t xml:space="preserve">Port-Jérôme-sur-Seine (76)</t>
   </si>
   <si>
-    <t xml:space="preserve">Petit groupe, priorité basse. Rejoindre avec la Page, lire le règlement, écrire à l'admin avant de publier une seule annonce.</t>
+    <t xml:space="preserve">Petit groupe, priorité basse. Rejoindre avec la Page, lire le règlement, écrire à l'admin avant de publier une seule annonce. (Lien relevé dans un article ici.fr de 2016 aujourd'hui indisponible ; source jointe : article ici.fr de 2019 sur le même réseau.)</t>
   </si>
   <si>
     <t xml:space="preserve">Tu sais que tu viens de… Saint-Romain-de-Colbosc</t>
@@ -4607,7 +4610,7 @@
     <t xml:space="preserve">• Une Page ne peut que demander à rejoindre un groupe ; si les Pages ne sont pas admises, demandez à l'admin comment un professionnel peut publier.</t>
   </si>
   <si>
-    <t xml:space="preserve">• Aucun groupe thématique (piscine, jardin, déstockage) ni groupe de Gennevilliers, du 95, du 78 ou du 93 n'a pu être confirmé : cherchez-les vous-même dans Facebook avec « travaux maison 92 », « piscine Île-de-France », « bons plans matériaux ».</t>
+    <t xml:space="preserve">• En dehors de VendezVosMateriaux.fr et LES PRO DU BÂTIMENT, aucun groupe thématique (piscine, jardin, déstockage) ni groupe de Gennevilliers, du 95, du 78 ou du 93 n'a pu être confirmé : cherchez-les vous-même dans Facebook avec « travaux maison 92 », « piscine Île-de-France », « bons plans matériaux ».</t>
   </si>
   <si>
     <t xml:space="preserve">• Jamais d'extraction de membres ni de messages privés non sollicités aux membres (RGPD et règles de Facebook).</t>
@@ -4697,7 +4700,7 @@
     <t xml:space="preserve">24–26 novembre 2026, Paris Expo Porte de Versailles</t>
   </si>
   <si>
-    <t xml:space="preserve">Présenter MINYALA pour places et parvis piétons, repérer les futurs appels d'offres.</t>
+    <t xml:space="preserve">Repérer les futurs appels d'offres de dallage. Ne proposer MINYALA pour l'espace public qu'avec des essais (glissance, gel, flexion) adaptés à un calcaire de 2 cm.</t>
   </si>
   <si>
     <t xml:space="preserve">Paysalia + Rocalia 2027</t>
@@ -4790,7 +4793,7 @@
     <t xml:space="preserve">France — annonce gratuite (publiée sous 72 h)</t>
   </si>
   <si>
-    <t xml:space="preserve">Publier le lot MINYALA (500–2 000 m², 27 €/m² TTC pro, dès 25 m², Gennevilliers et Vernon). Concurrent présent à 27 €/m² avec 160 m² minimum.</t>
+    <t xml:space="preserve">Publier le lot MINYALA (500–2 000 m², prix pro 22,50 € HT/m² soit 27 € TTC — saisir 22,50 dans le champ prix HT —, dès 25 m², Gennevilliers et Vernon). Concurrent affiché à 27 €/m² avec 160 m² minimum : vérifier s'il s'agit de HT ou de TTC.</t>
   </si>
   <si>
     <t xml:space="preserve">StoneAdd (demandes d'acheteurs pierre)</t>
@@ -4880,7 +4883,7 @@
     <t xml:space="preserve">E-mail ou SMS à un particulier</t>
   </si>
   <si>
-    <t xml:space="preserve">Consentement préalable obligatoire (case non pré-cochée). Exception : vos clients existants, pour des produits similaires.</t>
+    <t xml:space="preserve">Consentement préalable obligatoire (case non pré-cochée). Règle maison : aucun e-mail ni SMS commercial à un particulier sans case cochée. (L'exception légale « clients existants, produits analogues » exige qu'ils aient pu refuser gratuitement lors de la commande et un lien de désinscription dans chaque message ; elle ne vaut jamais pour le téléphone.)</t>
   </si>
   <si>
     <t xml:space="preserve">E-mail ou SMS à un professionnel</t>
@@ -5241,7 +5244,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -5269,6 +5272,14 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -5817,7 +5828,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q198"/>
+  <dimension ref="A1:Q400"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -6440,7 +6451,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="n">
         <v>14</v>
       </c>
@@ -7048,7 +7059,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="15" t="n">
         <v>28</v>
       </c>
@@ -7140,7 +7151,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="n">
         <v>30</v>
       </c>
@@ -7692,7 +7703,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="23" t="n">
         <v>42</v>
       </c>
@@ -7738,7 +7749,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="23" t="n">
         <v>43</v>
       </c>
@@ -7784,7 +7795,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="23" t="n">
         <v>44</v>
       </c>
@@ -7830,7 +7841,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="23" t="n">
         <v>45</v>
       </c>
@@ -7876,7 +7887,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="23" t="n">
         <v>46</v>
       </c>
@@ -7922,7 +7933,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="23" t="n">
         <v>47</v>
       </c>
@@ -8014,7 +8025,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="23" t="n">
         <v>49</v>
       </c>
@@ -8060,7 +8071,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="23" t="n">
         <v>50</v>
       </c>
@@ -8198,7 +8209,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="23" t="n">
         <v>53</v>
       </c>
@@ -8382,7 +8393,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="23" t="n">
         <v>57</v>
       </c>
@@ -8474,7 +8485,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="23" t="n">
         <v>59</v>
       </c>
@@ -8566,7 +8577,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="23" t="n">
         <v>61</v>
       </c>
@@ -9018,7 +9029,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="23" t="n">
         <v>71</v>
       </c>
@@ -9062,7 +9073,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="23" t="n">
         <v>72</v>
       </c>
@@ -9108,7 +9119,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="23" t="n">
         <v>73</v>
       </c>
@@ -9154,7 +9165,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="23" t="n">
         <v>74</v>
       </c>
@@ -9246,7 +9257,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="23" t="n">
         <v>76</v>
       </c>
@@ -9292,7 +9303,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="23" t="n">
         <v>77</v>
       </c>
@@ -9338,7 +9349,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="23" t="n">
         <v>78</v>
       </c>
@@ -9384,7 +9395,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="23" t="n">
         <v>79</v>
       </c>
@@ -9476,7 +9487,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="23" t="n">
         <v>81</v>
       </c>
@@ -9612,7 +9623,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="23" t="n">
         <v>84</v>
       </c>
@@ -9748,7 +9759,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="17" t="n">
         <v>87</v>
       </c>
@@ -9794,7 +9805,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="17" t="n">
         <v>88</v>
       </c>
@@ -10016,7 +10027,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="17" t="n">
         <v>93</v>
       </c>
@@ -10150,7 +10161,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="17" t="n">
         <v>96</v>
       </c>
@@ -10416,7 +10427,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="17" t="n">
         <v>102</v>
       </c>
@@ -10460,7 +10471,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="17" t="n">
         <v>103</v>
       </c>
@@ -11268,7 +11279,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="15" t="n">
         <v>121</v>
       </c>
@@ -11768,7 +11779,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="15" t="n">
         <v>132</v>
       </c>
@@ -11814,7 +11825,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="15" t="n">
         <v>133</v>
       </c>
@@ -12218,7 +12229,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="23" t="n">
         <v>142</v>
       </c>
@@ -12348,7 +12359,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="23" t="n">
         <v>145</v>
       </c>
@@ -12486,7 +12497,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="23" t="n">
         <v>148</v>
       </c>
@@ -12528,7 +12539,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="23" t="n">
         <v>149</v>
       </c>
@@ -12574,7 +12585,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="23" t="n">
         <v>150</v>
       </c>
@@ -12666,7 +12677,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="23" t="n">
         <v>152</v>
       </c>
@@ -13022,7 +13033,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="23" t="n">
         <v>160</v>
       </c>
@@ -13068,7 +13079,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="23" t="n">
         <v>161</v>
       </c>
@@ -13156,7 +13167,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="23" t="n">
         <v>163</v>
       </c>
@@ -13202,7 +13213,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="23" t="n">
         <v>164</v>
       </c>
@@ -13294,7 +13305,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="23" t="n">
         <v>166</v>
       </c>
@@ -13340,7 +13351,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="23" t="n">
         <v>167</v>
       </c>
@@ -13478,7 +13489,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="23" t="n">
         <v>170</v>
       </c>
@@ -13840,7 +13851,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="17" t="n">
         <v>178</v>
       </c>
@@ -14204,7 +14215,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="17" t="n">
         <v>186</v>
       </c>
@@ -14250,7 +14261,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="17" t="n">
         <v>187</v>
       </c>
@@ -14296,7 +14307,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="17" t="n">
         <v>188</v>
       </c>
@@ -14338,7 +14349,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="17" t="n">
         <v>189</v>
       </c>
@@ -14428,7 +14439,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="17" t="n">
         <v>191</v>
       </c>
@@ -14564,7 +14575,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="17" t="n">
         <v>194</v>
       </c>
@@ -14610,7 +14621,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="17" t="n">
         <v>195</v>
       </c>
@@ -14746,8 +14757,1220 @@
         <v>27</v>
       </c>
     </row>
+    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q199" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q200" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q201" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q202" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q203" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q204" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q205" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q206" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q207" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q208" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q209" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q210" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q211" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q212" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q213" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q214" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q215" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q216" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q217" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q218" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q219" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q220" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q221" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q222" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q223" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q224" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q225" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q226" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q227" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q228" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q229" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q230" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q231" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q232" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q233" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q234" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q235" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q236" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q237" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q238" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q239" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q240" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q241" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q242" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q243" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q244" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q245" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q246" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q247" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q248" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q249" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q250" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q251" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q252" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q253" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q254" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q255" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q256" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q257" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q258" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q259" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q260" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q261" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q262" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q263" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q264" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q265" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q266" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q267" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q268" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q269" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q270" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q271" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q272" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q273" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q274" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q275" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q276" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q277" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q278" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q279" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q280" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q281" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q282" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q283" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q284" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q285" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q286" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q287" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q288" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q289" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q290" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q291" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q292" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q293" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q294" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q295" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q296" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q297" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q298" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q299" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q300" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q301" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q302" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q303" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q304" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q305" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q306" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q307" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q308" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q309" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q310" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q311" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q312" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q313" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q314" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q315" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q316" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q317" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q318" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q319" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q320" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q321" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q322" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q323" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q324" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q325" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q326" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q327" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q328" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q329" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q330" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q331" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q332" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q333" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q334" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q335" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q336" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q337" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q338" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q339" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q340" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q341" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q342" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q343" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q344" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q345" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q346" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q347" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q348" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q349" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q350" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q351" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q352" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q353" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q354" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q355" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q356" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q357" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q358" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q359" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q360" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q361" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q362" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q363" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q364" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q365" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q366" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q367" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q368" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q369" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q370" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q371" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q372" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q373" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q374" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q375" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q376" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q377" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q378" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q379" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q380" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q381" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q382" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q383" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q384" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q385" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q386" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q387" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q388" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q389" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q390" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q391" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q392" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q393" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q394" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q395" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q396" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q397" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q398" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q399" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q400" s="11" t="n">
+        <f aca="false">'Mode d''emploi'!$B$29</f>
+        <v>27</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q198"/>
+  <autoFilter ref="A1:Q400"/>
   <dataValidations count="2">
     <dataValidation allowBlank="true" error="Choisissez un statut dans la liste." errorStyle="stop" errorTitle="Statut" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L2:L400" type="list">
       <formula1>"À contacter,Contacté,Intéressé,Échantillon / visite,Devis envoyé,Vendu,Pas intéressé"</formula1>
@@ -15179,7 +16402,7 @@
       </c>
       <c r="H2" s="20"/>
     </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
         <v>926</v>
       </c>
@@ -15251,7 +16474,7 @@
       </c>
       <c r="H5" s="20"/>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
         <v>942</v>
       </c>
@@ -15489,7 +16712,7 @@
       </c>
       <c r="H15" s="20"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
         <v>976</v>
       </c>
@@ -15729,7 +16952,7 @@
       </c>
       <c r="H25" s="20"/>
     </row>
-    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="25" t="s">
         <v>1023</v>
       </c>
@@ -16306,7 +17529,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
         <v>1114</v>
       </c>
@@ -17428,7 +18651,7 @@
       </c>
       <c r="N30" s="19"/>
     </row>
-    <row r="31" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="s">
         <v>1286</v>
       </c>
@@ -18296,7 +19519,7 @@
       </c>
       <c r="N52" s="19"/>
     </row>
-    <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="17" t="s">
         <v>1286</v>
       </c>
@@ -18532,7 +19755,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
         <v>1437</v>
       </c>
@@ -18560,7 +19783,7 @@
       </c>
       <c r="J2" s="20"/>
     </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
         <v>1444</v>
       </c>
@@ -18688,7 +19911,7 @@
       <c r="I7" s="19"/>
       <c r="J7" s="20"/>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
         <v>1465</v>
       </c>
@@ -18702,7 +19925,7 @@
         <v>1467</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>1462</v>
+        <v>1468</v>
       </c>
       <c r="F8" s="18" t="s">
         <v>925</v>
@@ -18716,10 +19939,10 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="C9" s="17" t="s">
         <v>1451</v>
@@ -18742,10 +19965,10 @@
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>1451</v>
@@ -18754,7 +19977,7 @@
         <v>1461</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="F10" s="18" t="s">
         <v>925</v>
@@ -18768,10 +19991,10 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="C11" s="17" t="s">
         <v>1451</v>
@@ -18792,12 +20015,12 @@
       <c r="I11" s="19"/>
       <c r="J11" s="20"/>
     </row>
-    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="C12" s="17" t="s">
         <v>1451</v>
@@ -18806,7 +20029,7 @@
         <v>1461</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>925</v>
@@ -18818,12 +20041,12 @@
       <c r="I12" s="19"/>
       <c r="J12" s="20"/>
     </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="C13" s="17" t="s">
         <v>1451</v>
@@ -18832,7 +20055,7 @@
         <v>1461</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="F13" s="18" t="s">
         <v>925</v>
@@ -18844,12 +20067,12 @@
       <c r="I13" s="19"/>
       <c r="J13" s="20"/>
     </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="C14" s="17" t="s">
         <v>1451</v>
@@ -18858,7 +20081,7 @@
         <v>1461</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>1462</v>
+        <v>1468</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>925</v>
@@ -18870,12 +20093,12 @@
       <c r="I14" s="19"/>
       <c r="J14" s="20"/>
     </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="C15" s="17" t="s">
         <v>1451</v>
@@ -18884,7 +20107,7 @@
         <v>1461</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>1462</v>
+        <v>1468</v>
       </c>
       <c r="F15" s="18" t="s">
         <v>925</v>
@@ -18896,12 +20119,12 @@
       <c r="I15" s="19"/>
       <c r="J15" s="20"/>
     </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="C16" s="17" t="s">
         <v>1451</v>
@@ -18910,7 +20133,7 @@
         <v>1461</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>1462</v>
+        <v>1468</v>
       </c>
       <c r="F16" s="18" t="s">
         <v>925</v>
@@ -18922,12 +20145,12 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="C17" s="17" t="s">
         <v>1451</v>
@@ -18936,7 +20159,7 @@
         <v>1461</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>1462</v>
+        <v>1468</v>
       </c>
       <c r="F17" s="18" t="s">
         <v>925</v>
@@ -18948,12 +20171,12 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="C18" s="17" t="s">
         <v>1451</v>
@@ -18962,7 +20185,7 @@
         <v>1461</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>1462</v>
+        <v>1468</v>
       </c>
       <c r="F18" s="18" t="s">
         <v>925</v>
@@ -18974,12 +20197,12 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="C19" s="17" t="s">
         <v>1451</v>
@@ -18988,7 +20211,7 @@
         <v>1461</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="F19" s="18" t="s">
         <v>925</v>
@@ -19000,12 +20223,12 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="C20" s="17" t="s">
         <v>1451</v>
@@ -19014,7 +20237,7 @@
         <v>1461</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="F20" s="18" t="s">
         <v>925</v>
@@ -19028,19 +20251,19 @@
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="C21" s="17" t="s">
         <v>1451</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="F21" s="18" t="s">
         <v>925</v>
@@ -19054,10 +20277,10 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="C22" s="17" t="s">
         <v>1451</v>
@@ -19066,7 +20289,7 @@
         <v>1461</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="F22" s="18" t="s">
         <v>925</v>
@@ -19080,19 +20303,19 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="C23" s="17" t="s">
         <v>1445</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>925</v>
@@ -19106,7 +20329,7 @@
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -19116,7 +20339,7 @@
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -19126,7 +20349,7 @@
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -19136,7 +20359,7 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -19227,10 +20450,10 @@
         <v>911</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>915</v>
@@ -19241,16 +20464,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>925</v>
@@ -19258,16 +20481,16 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>315</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="E3" s="27" t="s">
         <v>925</v>
@@ -19275,16 +20498,16 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="E4" s="27" t="s">
         <v>925</v>
@@ -19292,16 +20515,16 @@
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="E5" s="27" t="s">
         <v>925</v>
@@ -19309,16 +20532,16 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="E6" s="27" t="s">
         <v>925</v>
@@ -19326,33 +20549,33 @@
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="E7" s="27" t="s">
         <v>925</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="E8" s="27" t="s">
         <v>925</v>
@@ -19360,16 +20583,16 @@
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="E9" s="27" t="s">
         <v>925</v>
@@ -19377,16 +20600,16 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>50</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="E10" s="27" t="s">
         <v>925</v>
@@ -19394,16 +20617,16 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="E11" s="27" t="s">
         <v>925</v>
@@ -19411,16 +20634,16 @@
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="E12" s="27" t="s">
         <v>925</v>
@@ -19428,16 +20651,16 @@
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="E13" s="27" t="s">
         <v>925</v>
@@ -19445,16 +20668,16 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="E14" s="27" t="s">
         <v>925</v>
@@ -19462,33 +20685,33 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="E15" s="27" t="s">
         <v>925</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="E16" s="27" t="s">
         <v>925</v>
@@ -19496,16 +20719,16 @@
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="E17" s="27" t="s">
         <v>925</v>
@@ -19516,13 +20739,13 @@
         <v>1139</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="E18" s="27" t="s">
         <v>925</v>
@@ -19530,16 +20753,16 @@
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="E19" s="27" t="s">
         <v>925</v>
@@ -19550,13 +20773,13 @@
         <v>1157</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>925</v>
@@ -19564,16 +20787,16 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="E21" s="27" t="s">
         <v>925</v>
@@ -19581,16 +20804,16 @@
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="E22" s="28"/>
     </row>
@@ -19642,10 +20865,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>44</v>
@@ -19653,10 +20876,10 @@
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>925</v>
@@ -19664,21 +20887,21 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="C3" s="27" t="s">
         <v>925</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>925</v>
@@ -19686,10 +20909,10 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>925</v>
@@ -19697,10 +20920,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="C6" s="27" t="s">
         <v>925</v>
@@ -19708,10 +20931,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="C7" s="27" t="s">
         <v>925</v>
@@ -19719,10 +20942,10 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="C8" s="27" t="s">
         <v>925</v>
@@ -19730,10 +20953,10 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="C9" s="27" t="s">
         <v>925</v>
@@ -19741,10 +20964,10 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="C10" s="27" t="s">
         <v>925</v>
@@ -19752,10 +20975,10 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>925</v>
@@ -19763,7 +20986,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
   </sheetData>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3140" uniqueCount="1617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3140" uniqueCount="1619">
   <si>
     <t xml:space="preserve">Prospection MINYALA — mode d'emploi</t>
   </si>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">Annonce localisée à Gennevilliers, et une 2e à Vernon (27) dès que l'adresse est connue</t>
   </si>
   <si>
-    <t xml:space="preserve">Ouvrir un compte Pro (obligatoire pour une entreprise). Une annonce par usage : terrasse, plage de piscine, sol intérieur. Prix au m², minimum 25 m², retrait sur rendez-vous. Republier au printemps.</t>
+    <t xml:space="preserve">Ouvrir un compte Pro (obligatoire pour une entreprise). Une annonce par usage : terrasse, abords de piscine (selon finition et pose, à écrire dans le titre et le texte), sol intérieur. Prix au m², minimum 25 m², retrait sur rendez-vous. Republier au printemps.</t>
   </si>
   <si>
     <t xml:space="preserve">Compte Pro gratuit ; 50 annonces offertes en Maison &amp; Jardin, puis payant (à vérifier)</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">Particuliers normands (rubriques Bricolage et Jardinage)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ouvrir un compte pro et demander les conditions pour un vendeur de matériaux, puis publier « Dalles calcaire naturel 30×60, 35 €/m² ».</t>
+    <t xml:space="preserve">Ouvrir un compte pro et demander les conditions pour un vendeur de matériaux, puis publier « Dalles calcaire naturel 30×60, 35 €/m² pierre seule ».</t>
   </si>
   <si>
     <t xml:space="preserve">Régie Ouest (radio Tendance Ouest, Le Courrier Cauchois, La Manche Libre)</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">Décrochages Yvelines et Seine-Maritime</t>
   </si>
   <si>
-    <t xml:space="preserve">Spots courts au printemps (« pierre naturelle pour terrasse : 35 €/m² pierre seule, dès 25 m², à retirer à Gennevilliers ou Vernon ») renvoyant vers la fiche produit.</t>
+    <t xml:space="preserve">Spots courts au printemps (« pierre naturelle pour sol ou terrasse selon pose : 35 €/m² pierre seule, dès 25 m², à retirer à Gennevilliers ou Vernon ») renvoyant vers la fiche produit.</t>
   </si>
   <si>
     <t xml:space="preserve">Patrimoine Normand (revue trimestrielle)</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">Île-de-France et Normandie, à la carte</t>
   </si>
   <si>
-    <t xml:space="preserve">Flyer « terrasse et piscine en pierre naturelle » avec QR code vers la boutique, distribué dans les zones de maisons autour de Gennevilliers. Respecter les Stop Pub et les règles Oui Pub locales.</t>
+    <t xml:space="preserve">Flyer « sol, terrasse et abords de piscine en pierre naturelle, selon finition et pose — 35 €/m² pierre seule » avec QR code vers la boutique, distribué dans les zones de maisons autour de Gennevilliers. Respecter les Stop Pub et les règles Oui Pub locales.</t>
   </si>
   <si>
     <t xml:space="preserve">InfoNormandie (site d'actualité locale)</t>
@@ -3614,7 +3614,7 @@
     <t xml:space="preserve">2026-04-18</t>
   </si>
   <si>
-    <t xml:space="preserve">Carreaux de marbre beige demandés depuis l'Espagne, avec une question sur le stock. Le format (30,5×30,5×1 cm) et la pierre (espagnole) ne sont pas les mêmes que la Minyala 30×60×2. À proposer comme alternative moins chère. La demande date d'avril.</t>
+    <t xml:space="preserve">Carreaux de marbre beige demandés depuis l'Espagne, avec une question sur le stock. Le format (30,5×30,5×1 cm) et la pierre (espagnole) ne sont pas les mêmes que la Minyala 30×60×2. À proposer comme alternative. La demande date d'avril.</t>
   </si>
   <si>
     <t xml:space="preserve">Buy Moscato Beige Marble</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">Barcelona, Spain (CIF)</t>
   </si>
   <si>
-    <t xml:space="preserve">Acheteur espagnol (CIF Barcelone) intéressé par la pierre beige égyptienne « Sinai Pearl ou similaire » sur une annonce Sunny Menia, donc la famille de MINYALA. Formats variés de 2 à 4 cm ; demande non datée.</t>
+    <t xml:space="preserve">Acheteur espagnol (CIF Barcelone) intéressé par la pierre beige égyptienne « Sinai Pearl ou similaire » sur une annonce Sunny Menia : même famille que MINYALA seulement si l'origine Minya est confirmée. Formats variés de 2 à 4 cm ; demande non datée.</t>
   </si>
   <si>
     <t xml:space="preserve">Galala Beige Marble Tiles &amp; Slab from Egypt</t>
@@ -3914,7 +3914,7 @@
     <t xml:space="preserve">July 2025</t>
   </si>
   <si>
-    <t xml:space="preserve">Acheteur français de calcaire beige : on peut lui proposer MINYALA comme alternative moins chère livrée depuis Gennevilliers. Il vise toutefois une pierre française précise, et la demande date de juillet 2025.</t>
+    <t xml:space="preserve">Acheteur français de calcaire beige : on peut lui proposer MINYALA comme alternative avec retrait à Gennevilliers ou Vernon, ou livraison sur devis dès 100 m². Il vise toutefois une pierre française précise, et la demande date de juillet 2025.</t>
   </si>
   <si>
     <t xml:space="preserve">Buyers from Ireland - Global Stone Buyer Center (RFQ for Jerusalem Gold Limestone tiles and cobbles)</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">Carreaux de Sunny Beige égyptien en petit format (2×2)</t>
   </si>
   <si>
-    <t xml:space="preserve">2×2 (pouces)</t>
+    <t xml:space="preserve">2×2 (unité non précisée)</t>
   </si>
   <si>
     <t xml:space="preserve">États-Unis</t>
@@ -3959,7 +3959,7 @@
     <t xml:space="preserve">2026-05-06</t>
   </si>
   <si>
-    <t xml:space="preserve">Correction : Size: '2x2' (units not stated on the page; the buyer also asks whether smaller sizes exist). Quantity: not stated. Destination: USA. Date: 2026-05-06. — Le produit est de la famille Sunny de Minya (proche de MINYALA si l'origine est confirmée), mais l'acheteur est aux États-Unis et veut des mosaïques 2×2 pouces. La destination est lointaine et le format ne correspond pas.</t>
+    <t xml:space="preserve">Famille Sunny de Minya (proche de MINYALA seulement si l'origine Minya est confirmée), mais l'acheteur est aux États-Unis et demande de très petits formats « 2×2 » (unité non précisée) : destination lointaine et format sans rapport.</t>
   </si>
   <si>
     <t xml:space="preserve">Bulk Inquiry - 11000 M2 Beige Marble Slabs 60x120cmx2cm EXW Factory</t>
@@ -4007,34 +4007,40 @@
     <t xml:space="preserve">bathroom tiles walls and floors</t>
   </si>
   <si>
-    <t xml:space="preserve">Carreaux de salle de bain murs et sols, aspect pierre naturelle chaude et neutre, mat, R10</t>
+    <t xml:space="preserve">Grès cérame pleine masse aspect pierre, mat, R10, rectifié (pas de pierre naturelle)</t>
   </si>
   <si>
     <t xml:space="preserve">26 m²</t>
   </si>
   <si>
+    <t xml:space="preserve">800×800×10 mm</t>
+  </si>
+  <si>
     <t xml:space="preserve">Portugal</t>
   </si>
   <si>
     <t xml:space="preserve">affiché « 4 days ago » le 2026-10-12</t>
   </si>
   <si>
-    <t xml:space="preserve">Correction : Product: full-body porcelain floor tiles with a warm neutral natural-stone look, matt, R10, rectified, with matching wall tiles (not natural stone). Size: 800x800x10 mm. Quantity: 26 m². Destination: Portugal. Date: posted 2026-10-08. — Petite quantité au Portugal, mais la description (R10, chauffage au sol, coupes à 45°) évoque plutôt du grès cérame aspect pierre. Le produit n'est pas précisé.</t>
+    <t xml:space="preserve">Petite quantité (26 m²) au Portugal, mais l'acheteur veut du grès cérame aspect pierre en 80×80, pas de la pierre naturelle : ne correspond pas.</t>
   </si>
   <si>
     <t xml:space="preserve">YDSTONE Beige Tumbled French Pattern Travertine Tile Limestone for Indoor Outdoor Staircases ...</t>
   </si>
   <si>
-    <t xml:space="preserve">Dalles extérieures en travertin beige adouci, 30 mm minimum, au moins 300×600</t>
-  </si>
-  <si>
-    <t xml:space="preserve">au moins 300×600, épaisseur 30 mm minimum</t>
+    <t xml:space="preserve">Pavés de travertin extérieurs pour zones humides, adoucis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">au moins 300×600 mm, épaisseur 30 mm minimum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perth, Australie (compte acheteur aux États-Unis)</t>
   </si>
   <si>
     <t xml:space="preserve">affiché « 5 days ago » le 2026-10-12</t>
   </si>
   <si>
-    <t xml:space="preserve">Correction : Product: outdoor travertine pavers for wet areas, slip-resistant, honed (not polished). Size: width at least 300 mm, length at least 600 mm, thickness at least 30 mm. Quantity: 150 m². Destination: Perth, Australia (buyer account listed as United States). Date: posted 2026-10-06. — Pierre beige au format 30×60 environ, mais l'acheteur est aux États-Unis et demande une épaisseur de 30 mm minimum, alors que la Minyala fait 20 mm.</t>
+    <t xml:space="preserve">Pierre beige en format proche du 30×60, mais pour l'Australie (Perth) et en 30 mm minimum, alors que MINYALA fait 20 mm : ne correspond pas.</t>
   </si>
   <si>
     <t xml:space="preserve">TradeKey</t>
@@ -4436,7 +4442,7 @@
     <t xml:space="preserve">Communauté de ville</t>
   </si>
   <si>
-    <t xml:space="preserve">~48 000 (ici.fr, 2019)</t>
+    <t xml:space="preserve">45 000+ (Tendance Ouest, 2018) ; ~48 000 (ici.fr, 2019)</t>
   </si>
   <si>
     <t xml:space="preserve">Prioritaire Normandie. Rejoindre avec la Page, lire le règlement, écrire à l'admin avant de publier une seule annonce. Tous les messages y sont validés par l'admin.</t>
@@ -15972,11 +15978,11 @@
   </sheetData>
   <autoFilter ref="A1:Q400"/>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" error="Choisissez un statut dans la liste." errorStyle="stop" errorTitle="Statut" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L2:L400" type="list">
+    <dataValidation allowBlank="true" error="Choisissez un statut dans la liste." errorStyle="stop" errorTitle="Statut" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="L2:L400" type="list">
       <formula1>"À contacter,Contacté,Intéressé,Échantillon / visite,Devis envoyé,Vendu,Pas intéressé"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="P2:P400" type="decimal">
+    <dataValidation allowBlank="true" error="Entrez un nombre de m² (sans « m² »), 0 ou plus." errorStyle="stop" errorTitle="m² vendus" operator="greaterThanOrEqual" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="P2:P400" type="decimal">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -17192,7 +17198,7 @@
       </c>
       <c r="H35" s="20"/>
     </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="25" t="s">
         <v>1071</v>
       </c>
@@ -18315,7 +18321,7 @@
       </c>
       <c r="N21" s="19"/>
     </row>
-    <row r="22" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="s">
         <v>1151</v>
       </c>
@@ -18575,7 +18581,7 @@
       </c>
       <c r="N28" s="19"/>
     </row>
-    <row r="29" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="23" t="s">
         <v>1151</v>
       </c>
@@ -18651,7 +18657,7 @@
       </c>
       <c r="N30" s="19"/>
     </row>
-    <row r="31" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="s">
         <v>1286</v>
       </c>
@@ -18771,7 +18777,7 @@
       </c>
       <c r="N33" s="19"/>
     </row>
-    <row r="34" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
         <v>1286</v>
       </c>
@@ -18791,16 +18797,16 @@
         <v>1310</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>1120</v>
+        <v>1311</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="K34" s="18" t="s">
         <v>925</v>
@@ -18811,7 +18817,7 @@
       </c>
       <c r="N34" s="19"/>
     </row>
-    <row r="35" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
         <v>1286</v>
       </c>
@@ -18822,25 +18828,25 @@
         <v>1131</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="F35" s="17" t="s">
         <v>1148</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>1291</v>
+        <v>1318</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="K35" s="18" t="s">
         <v>925</v>
@@ -18859,28 +18865,28 @@
         <v>1115</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>939</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="K36" s="18" t="s">
         <v>925</v>
@@ -18899,13 +18905,13 @@
         <v>1115</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="F37" s="17" t="s">
         <v>1119</v>
@@ -18914,13 +18920,13 @@
         <v>1120</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="K37" s="18" t="s">
         <v>925</v>
@@ -18942,25 +18948,25 @@
         <v>1157</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="I38" s="17" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="K38" s="18" t="s">
         <v>925</v>
@@ -18982,10 +18988,10 @@
         <v>1157</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="F39" s="17" t="s">
         <v>1160</v>
@@ -18994,13 +19000,13 @@
         <v>1161</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="K39" s="18" t="s">
         <v>925</v>
@@ -19022,25 +19028,25 @@
         <v>1116</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="K40" s="18" t="s">
         <v>925</v>
@@ -19062,23 +19068,23 @@
         <v>1139</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="F41" s="17"/>
       <c r="G41" s="17" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>939</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="K41" s="18" t="s">
         <v>925</v>
@@ -19100,23 +19106,23 @@
         <v>1139</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="G42" s="17"/>
       <c r="H42" s="17" t="s">
-        <v>1357</v>
+        <v>1359</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>1358</v>
+        <v>1360</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>1359</v>
+        <v>1361</v>
       </c>
       <c r="K42" s="18" t="s">
         <v>925</v>
@@ -19138,23 +19144,23 @@
         <v>1139</v>
       </c>
       <c r="D43" s="25" t="s">
-        <v>1360</v>
+        <v>1362</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>1361</v>
+        <v>1363</v>
       </c>
       <c r="F43" s="17"/>
       <c r="G43" s="17" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>1364</v>
+        <v>1366</v>
       </c>
       <c r="K43" s="18" t="s">
         <v>925</v>
@@ -19176,25 +19182,25 @@
         <v>1139</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>1365</v>
+        <v>1367</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>1366</v>
+        <v>1368</v>
       </c>
       <c r="F44" s="17" t="s">
-        <v>1367</v>
+        <v>1369</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>1368</v>
+        <v>1370</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>1369</v>
+        <v>1371</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>1370</v>
+        <v>1372</v>
       </c>
       <c r="J44" s="17" t="s">
-        <v>1371</v>
+        <v>1373</v>
       </c>
       <c r="K44" s="18" t="s">
         <v>925</v>
@@ -19216,23 +19222,23 @@
         <v>1139</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>1372</v>
+        <v>1374</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>1373</v>
+        <v>1375</v>
       </c>
       <c r="F45" s="17"/>
       <c r="G45" s="17" t="s">
-        <v>1374</v>
+        <v>1376</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>1375</v>
+        <v>1377</v>
       </c>
       <c r="I45" s="17" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>1377</v>
+        <v>1379</v>
       </c>
       <c r="K45" s="18" t="s">
         <v>925</v>
@@ -19254,25 +19260,25 @@
         <v>1139</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>1378</v>
+        <v>1380</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="I46" s="17" t="s">
-        <v>1383</v>
+        <v>1385</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>1384</v>
+        <v>1386</v>
       </c>
       <c r="K46" s="18" t="s">
         <v>925</v>
@@ -19294,25 +19300,25 @@
         <v>1139</v>
       </c>
       <c r="D47" s="25" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="F47" s="17" t="s">
         <v>1127</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>1387</v>
+        <v>1389</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="I47" s="17" t="s">
-        <v>1388</v>
+        <v>1390</v>
       </c>
       <c r="J47" s="17" t="s">
-        <v>1389</v>
+        <v>1391</v>
       </c>
       <c r="K47" s="18" t="s">
         <v>925</v>
@@ -19334,25 +19340,25 @@
         <v>1139</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="F48" s="17" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="I48" s="17" t="s">
-        <v>1376</v>
+        <v>1378</v>
       </c>
       <c r="J48" s="17" t="s">
-        <v>1395</v>
+        <v>1397</v>
       </c>
       <c r="K48" s="18" t="s">
         <v>925</v>
@@ -19374,25 +19380,25 @@
         <v>1139</v>
       </c>
       <c r="D49" s="25" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="F49" s="17" t="s">
-        <v>1398</v>
+        <v>1400</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>1399</v>
+        <v>1401</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>1400</v>
+        <v>1402</v>
       </c>
       <c r="I49" s="17" t="s">
-        <v>1401</v>
+        <v>1403</v>
       </c>
       <c r="J49" s="17" t="s">
-        <v>1402</v>
+        <v>1404</v>
       </c>
       <c r="K49" s="18" t="s">
         <v>925</v>
@@ -19414,25 +19420,25 @@
         <v>1139</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="I50" s="17" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
       <c r="J50" s="17" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="K50" s="18" t="s">
         <v>925</v>
@@ -19454,23 +19460,23 @@
         <v>1139</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="F51" s="17" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>1413</v>
+        <v>1415</v>
       </c>
       <c r="H51" s="17"/>
       <c r="I51" s="17" t="s">
-        <v>1414</v>
+        <v>1416</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>1415</v>
+        <v>1417</v>
       </c>
       <c r="K51" s="18" t="s">
         <v>925</v>
@@ -19492,23 +19498,23 @@
         <v>1139</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>1416</v>
+        <v>1418</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
       <c r="F52" s="17"/>
       <c r="G52" s="17" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="I52" s="17" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="J52" s="17" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="K52" s="18" t="s">
         <v>925</v>
@@ -19530,21 +19536,21 @@
         <v>1139</v>
       </c>
       <c r="D53" s="25" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="F53" s="17"/>
       <c r="G53" s="17" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="I53" s="17"/>
       <c r="J53" s="17" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="K53" s="18" t="s">
         <v>925</v>
@@ -19557,7 +19563,7 @@
     </row>
     <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -19571,7 +19577,7 @@
     </row>
     <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -19585,7 +19591,7 @@
     </row>
     <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -19599,7 +19605,7 @@
     </row>
     <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -19613,7 +19619,7 @@
     </row>
     <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -19635,7 +19641,7 @@
     <mergeCell ref="A59:J59"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="M2:M132" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M2:M132" type="list">
       <formula1>"À étudier,Répondu,Pas pertinent,Gagné,Perdu"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -19725,7 +19731,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>40</v>
@@ -19734,7 +19740,7 @@
         <v>912</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>915</v>
@@ -19746,84 +19752,84 @@
         <v>44</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>939</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="F2" s="17"/>
       <c r="G2" s="26" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="I2" s="19" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="J2" s="20"/>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>939</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="F3" s="17"/>
       <c r="G3" s="26" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="H3" s="20"/>
       <c r="I3" s="19"/>
       <c r="J3" s="20" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="F4" s="18" t="s">
         <v>925</v>
@@ -19837,19 +19843,19 @@
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="18" t="s">
@@ -19861,19 +19867,19 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="F6" s="18" t="s">
         <v>925</v>
@@ -19887,19 +19893,19 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>1463</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="E7" s="17" t="s">
         <v>1464</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>1451</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>1461</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>1462</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>925</v>
@@ -19913,19 +19919,19 @@
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="F8" s="18" t="s">
         <v>925</v>
@@ -19939,19 +19945,19 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="F9" s="18" t="s">
         <v>925</v>
@@ -19965,19 +19971,19 @@
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="F10" s="18" t="s">
         <v>925</v>
@@ -19991,19 +19997,19 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>925</v>
@@ -20017,19 +20023,19 @@
     </row>
     <row r="12" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>925</v>
@@ -20043,19 +20049,19 @@
     </row>
     <row r="13" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="F13" s="18" t="s">
         <v>925</v>
@@ -20069,19 +20075,19 @@
     </row>
     <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>925</v>
@@ -20095,19 +20101,19 @@
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="F15" s="18" t="s">
         <v>925</v>
@@ -20121,19 +20127,19 @@
     </row>
     <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="F16" s="18" t="s">
         <v>925</v>
@@ -20147,19 +20153,19 @@
     </row>
     <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="F17" s="18" t="s">
         <v>925</v>
@@ -20173,19 +20179,19 @@
     </row>
     <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="F18" s="18" t="s">
         <v>925</v>
@@ -20199,19 +20205,19 @@
     </row>
     <row r="19" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="F19" s="18" t="s">
         <v>925</v>
@@ -20225,19 +20231,19 @@
     </row>
     <row r="20" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="B20" s="17" t="s">
+        <v>1498</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>1463</v>
+      </c>
+      <c r="E20" s="17" t="s">
         <v>1496</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>1451</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>1461</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>1494</v>
       </c>
       <c r="F20" s="18" t="s">
         <v>925</v>
@@ -20251,19 +20257,19 @@
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="F21" s="18" t="s">
         <v>925</v>
@@ -20277,19 +20283,19 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="F22" s="18" t="s">
         <v>925</v>
@@ -20303,19 +20309,19 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>925</v>
@@ -20329,7 +20335,7 @@
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -20339,7 +20345,7 @@
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -20349,7 +20355,7 @@
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -20359,7 +20365,7 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -20375,7 +20381,7 @@
     <mergeCell ref="A28:F28"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I2:I82" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I2:I82" type="list">
       <formula1>"En attente,Accepté,Refusé,Pages non admises"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -20450,10 +20456,10 @@
         <v>911</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>915</v>
@@ -20464,16 +20470,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>925</v>
@@ -20481,16 +20487,16 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>315</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="E3" s="27" t="s">
         <v>925</v>
@@ -20498,16 +20504,16 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="E4" s="27" t="s">
         <v>925</v>
@@ -20515,16 +20521,16 @@
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="E5" s="27" t="s">
         <v>925</v>
@@ -20532,16 +20538,16 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="E6" s="27" t="s">
         <v>925</v>
@@ -20549,16 +20555,16 @@
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="E7" s="27" t="s">
         <v>925</v>
@@ -20566,16 +20572,16 @@
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="E8" s="27" t="s">
         <v>925</v>
@@ -20583,16 +20589,16 @@
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="E9" s="27" t="s">
         <v>925</v>
@@ -20600,16 +20606,16 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>50</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="E10" s="27" t="s">
         <v>925</v>
@@ -20617,16 +20623,16 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="E11" s="27" t="s">
         <v>925</v>
@@ -20634,16 +20640,16 @@
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="E12" s="27" t="s">
         <v>925</v>
@@ -20651,16 +20657,16 @@
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="E13" s="27" t="s">
         <v>925</v>
@@ -20668,16 +20674,16 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="E14" s="27" t="s">
         <v>925</v>
@@ -20685,16 +20691,16 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="E15" s="27" t="s">
         <v>925</v>
@@ -20702,16 +20708,16 @@
     </row>
     <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="E16" s="27" t="s">
         <v>925</v>
@@ -20719,16 +20725,16 @@
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="E17" s="27" t="s">
         <v>925</v>
@@ -20739,13 +20745,13 @@
         <v>1139</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="E18" s="27" t="s">
         <v>925</v>
@@ -20753,16 +20759,16 @@
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="E19" s="27" t="s">
         <v>925</v>
@@ -20773,13 +20779,13 @@
         <v>1157</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>925</v>
@@ -20787,16 +20793,16 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="E21" s="27" t="s">
         <v>925</v>
@@ -20804,16 +20810,16 @@
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="E22" s="28"/>
     </row>
@@ -20865,10 +20871,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>44</v>
@@ -20876,10 +20882,10 @@
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>925</v>
@@ -20887,10 +20893,10 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="C3" s="27" t="s">
         <v>925</v>
@@ -20898,10 +20904,10 @@
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>925</v>
@@ -20909,10 +20915,10 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>925</v>
@@ -20920,10 +20926,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="C6" s="27" t="s">
         <v>925</v>
@@ -20931,10 +20937,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="C7" s="27" t="s">
         <v>925</v>
@@ -20942,10 +20948,10 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="C8" s="27" t="s">
         <v>925</v>
@@ -20953,10 +20959,10 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="C9" s="27" t="s">
         <v>925</v>
@@ -20964,10 +20970,10 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="C10" s="27" t="s">
         <v>925</v>
@@ -20975,10 +20981,10 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>925</v>
@@ -20986,7 +20992,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
     </row>
   </sheetData>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">Annonce localisée à Gennevilliers, et une 2e à Vernon (27) dès que l'adresse est connue</t>
   </si>
   <si>
-    <t xml:space="preserve">Ouvrir un compte Pro (obligatoire pour une entreprise). Une annonce par usage : terrasse, abords de piscine (selon finition et pose, à écrire dans le titre et le texte), sol intérieur. Prix au m², minimum 25 m², retrait sur rendez-vous. Republier au printemps.</t>
+    <t xml:space="preserve">Ouvrir un compte Pro (obligatoire pour une entreprise). Une annonce par usage : terrasse, abords de piscine, sol intérieur — pour chaque annonce extérieure (terrasse, piscine), écrire « selon finition et pose » dans le titre et le texte. Prix au m², minimum 25 m², retrait sur rendez-vous. Republier au printemps.</t>
   </si>
   <si>
     <t xml:space="preserve">Compte Pro gratuit ; 50 annonces offertes en Maison &amp; Jardin, puis payant (à vérifier)</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">Non relevé</t>
   </si>
   <si>
-    <t xml:space="preserve">Annonce déjà présente (doublon évité le 12/10/2026) : ne pas republier, répondre aux commentaires et messages. Lien du groupe à ajouter.</t>
+    <t xml:space="preserve">Annonce déjà présente (doublon évité le 12/10/2026). Vérifier : groupe privé et réservé aux pros ? Quel prix affiche l'annonce ? Si le groupe est ouvert aux particuliers, modifier l'annonce au prix public 35 €/m² pierre seule + « Pros : tarif sur demande ». Sinon, répondre seulement. Lien du groupe à ajouter.</t>
   </si>
   <si>
     <t xml:space="preserve">avant le 12/10/2026</t>
@@ -4607,7 +4607,7 @@
     <t xml:space="preserve">~5 400, privé (2023)</t>
   </si>
   <si>
-    <t xml:space="preserve">Se présenter comme fournisseur aux carreleurs, maçons et paysagistes. Pas de démarchage en message privé.</t>
+    <t xml:space="preserve">Groupe privé (~5 400, 2023). Vérifier qu'il est réservé aux pros avant d'y publier le prix pro. Se présenter comme fournisseur ; pas de démarchage en message privé.</t>
   </si>
   <si>
     <t xml:space="preserve">• Liens et effectifs viennent d'articles de presse (2016–2024) : vérifiez que chaque groupe existe toujours, son nom exact et son règlement une fois connecté.</t>
@@ -19789,7 +19789,7 @@
       </c>
       <c r="J2" s="20"/>
     </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
         <v>1446</v>
       </c>
@@ -20307,7 +20307,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
         <v>1506</v>
       </c>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3140" uniqueCount="1619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3140" uniqueCount="1620">
   <si>
     <t xml:space="preserve">Prospection MINYALA — mode d'emploi</t>
   </si>
@@ -2846,72 +2846,75 @@
     <t xml:space="preserve">Particuliers et petits artisans qui cherchent de la pierre près de chez eux</t>
   </si>
   <si>
+    <t xml:space="preserve">Une annonce localisée à Gennevilliers ; Vernon seulement quand l'adresse, les horaires et le stock y sont</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compte Pro obligatoire. Une seule annonce au départ : lot de 25 m² à 875 €, vraies photos sans texte, IDU de la filière REP, pas de lien ni de paiement en ligne Leboncoin pour l'instant. Texte, photos et liste de contrôle : leboncoin.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compte Pro gratuit ; 50 dépôts offerts au total en Maison &amp; Jardin ; 12 % de commission si paiement en ligne</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ouvrir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiche Google (Google Business Profile)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personnes qui cherchent « pierre naturelle » ou « dallage » près de Gennevilliers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recherche locale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Créer une fiche par point de retrait (Gennevilliers, puis Vernon dès que l'adresse est connue) : catégorie fournisseur de pierre, retrait sur rendez-vous, photos réelles, lien vers la fiche MINYALA. Demander un avis à chaque client.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gratuit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Houzz — profil pro « Pierres et plans de travail »</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Particuliers en projet et architectes qui cherchent un fournisseur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recherche par ville (rayon 10 à 100 km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Créer un profil pro situé à Gennevilliers (zone d'intervention incluant l'Eure / Vernon) avec photos de MINYALA posé, prix au m² et minimum de commande. Demander des avis clients.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inscription gratuite (options payantes à vérifier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PagesJaunes — fiche professionnelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recherches par ville et par métier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">France</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Créer ou revendiquer la fiche Pierre d'Égypte, rubriques pierre naturelle et carrelage, avec photos et lien vers le site.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiche gratuite (options payantes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vivastreet — Bricolage, jardinage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Particuliers</t>
+  </si>
+  <si>
     <t xml:space="preserve">Annonce localisée à Gennevilliers, et une 2e à Vernon (27) dès que l'adresse est connue</t>
   </si>
   <si>
-    <t xml:space="preserve">Ouvrir un compte Pro (obligatoire pour une entreprise). Une annonce par usage : terrasse, abords de piscine, sol intérieur — pour chaque annonce extérieure (terrasse, piscine), écrire « selon finition et pose » dans le titre et le texte. Prix au m², minimum 25 m², retrait sur rendez-vous. Republier au printemps.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compte Pro gratuit ; 50 annonces offertes en Maison &amp; Jardin, puis payant (à vérifier)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ouvrir</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiche Google (Google Business Profile)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiche</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Personnes qui cherchent « pierre naturelle » ou « dallage » près de Gennevilliers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recherche locale</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Créer une fiche par point de retrait (Gennevilliers, puis Vernon dès que l'adresse est connue) : catégorie fournisseur de pierre, retrait sur rendez-vous, photos réelles, lien vers la fiche MINYALA. Demander un avis à chaque client.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gratuit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Houzz — profil pro « Pierres et plans de travail »</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Particuliers en projet et architectes qui cherchent un fournisseur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recherche par ville (rayon 10 à 100 km)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Créer un profil pro situé à Gennevilliers (zone d'intervention incluant l'Eure / Vernon) avec photos de MINYALA posé, prix au m² et minimum de commande. Demander des avis clients.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inscription gratuite (options payantes à vérifier)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PagesJaunes — fiche professionnelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recherches par ville et par métier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Créer ou revendiquer la fiche Pierre d'Égypte, rubriques pierre naturelle et carrelage, avec photos et lien vers le site.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiche gratuite (options payantes)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vivastreet — Bricolage, jardinage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Particuliers</t>
-  </si>
-  <si>
     <t xml:space="preserve">Lire les règles de l'Espace Pro, puis publier une annonce pro identifiée avec photos et prix au m².</t>
   </si>
   <si>
@@ -3287,10 +3290,10 @@
     <t xml:space="preserve">France, filtrage local</t>
   </si>
   <si>
-    <t xml:space="preserve">Profil pro gratuit ; répondre aux demandes terrasse, dallage, carrelage. Lire la charte avant de proposer une vente de produit.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inscription gratuite ; options payantes</t>
+    <t xml:space="preserve">Ne pas payer Premier ni Booster : un compte pro gratuit ne peut répondre à rien, Premier engage 12 mois et les demandes locales portent sur la pose. Au plus : l'essai gratuit de 14 jours, sur Gennevilliers, résilié au 12e jour. Voir allovoisins.md.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premier dès 29,99 €/mois (auto-entrepreneur) ou 99,99 € HT/mois (entreprise), engagement 12 mois</t>
   </si>
   <si>
     <t xml:space="preserve">Annonces Tendance Ouest — espace pro</t>
@@ -16384,7 +16387,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
         <v>919</v>
       </c>
@@ -16491,13 +16494,13 @@
         <v>943</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>922</v>
+        <v>944</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="G6" s="18" t="s">
         <v>925</v>
@@ -16506,22 +16509,22 @@
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="G7" s="18" t="s">
         <v>925</v>
@@ -16530,19 +16533,19 @@
     </row>
     <row r="8" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F8" s="17" t="s">
         <v>931</v>
@@ -16552,19 +16555,19 @@
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F9" s="17" t="s">
         <v>931</v>
@@ -16576,19 +16579,19 @@
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="F10" s="17" t="s">
         <v>931</v>
@@ -16600,19 +16603,19 @@
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="F11" s="17" t="s">
         <v>931</v>
@@ -16624,19 +16627,19 @@
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F12" s="17" t="s">
         <v>931</v>
@@ -16648,19 +16651,19 @@
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="F13" s="17" t="s">
         <v>931</v>
@@ -16672,19 +16675,19 @@
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="F14" s="17" t="s">
         <v>931</v>
@@ -16696,19 +16699,19 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F15" s="17" t="s">
         <v>931</v>
@@ -16720,19 +16723,19 @@
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>931</v>
@@ -16744,22 +16747,22 @@
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="G17" s="18" t="s">
         <v>925</v>
@@ -16768,22 +16771,22 @@
     </row>
     <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
+        <v>987</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>982</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>988</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>989</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>990</v>
+      </c>
+      <c r="F18" s="17" t="s">
         <v>986</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>981</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>987</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>988</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>989</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>985</v>
       </c>
       <c r="G18" s="18" t="s">
         <v>925</v>
@@ -16792,22 +16795,22 @@
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F19" s="17" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="G19" s="18" t="s">
         <v>925</v>
@@ -16816,22 +16819,22 @@
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F20" s="17" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="G20" s="18" t="s">
         <v>925</v>
@@ -16840,22 +16843,22 @@
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="F21" s="17" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="G21" s="18" t="s">
         <v>925</v>
@@ -16864,22 +16867,22 @@
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="G22" s="18" t="s">
         <v>925</v>
@@ -16888,22 +16891,22 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="F23" s="17" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="G23" s="18" t="s">
         <v>925</v>
@@ -16912,22 +16915,22 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="25" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C24" s="17" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D24" s="17" t="s">
         <v>939</v>
       </c>
       <c r="E24" s="17" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="F24" s="17" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="G24" s="18" t="s">
         <v>925</v>
@@ -16936,22 +16939,22 @@
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="25" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="G25" s="18" t="s">
         <v>925</v>
@@ -16960,22 +16963,22 @@
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="25" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C26" s="17" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F26" s="17" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="G26" s="18" t="s">
         <v>925</v>
@@ -16984,22 +16987,22 @@
     </row>
     <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="25" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="G27" s="18" t="s">
         <v>925</v>
@@ -17008,22 +17011,22 @@
     </row>
     <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="25" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C28" s="17" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F28" s="17" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="G28" s="18" t="s">
         <v>925</v>
@@ -17032,22 +17035,22 @@
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="25" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>996</v>
+      </c>
+      <c r="C29" s="17" t="s">
+        <v>1040</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E29" s="17" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F29" s="17" t="s">
         <v>1038</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>995</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>1040</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>1041</v>
-      </c>
-      <c r="F29" s="17" t="s">
-        <v>1037</v>
       </c>
       <c r="G29" s="18" t="s">
         <v>925</v>
@@ -17056,22 +17059,22 @@
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="25" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B30" s="17" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C30" s="17" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="E30" s="17" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F30" s="17" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="G30" s="18" t="s">
         <v>925</v>
@@ -17080,22 +17083,22 @@
     </row>
     <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="25" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="G31" s="18" t="s">
         <v>925</v>
@@ -17104,22 +17107,22 @@
     </row>
     <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="25" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B32" s="17" t="s">
         <v>927</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="G32" s="18" t="s">
         <v>925</v>
@@ -17128,22 +17131,22 @@
     </row>
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="25" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B33" s="17" t="s">
         <v>927</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="G33" s="18" t="s">
         <v>925</v>
@@ -17152,46 +17155,46 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="25" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B34" s="17" t="s">
         <v>927</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="G34" s="18" t="s">
         <v>925</v>
       </c>
       <c r="H34" s="20"/>
     </row>
-    <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="25" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="G35" s="18" t="s">
         <v>925</v>
@@ -17200,22 +17203,22 @@
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="25" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B36" s="17" t="s">
         <v>920</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="D36" s="17" t="s">
         <v>64</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="G36" s="18" t="s">
         <v>925</v>
@@ -17224,22 +17227,22 @@
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="25" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D37" s="17" t="s">
         <v>64</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="G37" s="18" t="s">
         <v>925</v>
@@ -17248,22 +17251,22 @@
     </row>
     <row r="38" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="25" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D38" s="17" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E38" s="17" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F38" s="17" t="s">
         <v>1078</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C38" s="17" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D38" s="17" t="s">
-        <v>1080</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>1081</v>
-      </c>
-      <c r="F38" s="17" t="s">
-        <v>1077</v>
       </c>
       <c r="G38" s="18" t="s">
         <v>925</v>
@@ -17272,22 +17275,22 @@
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="25" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D39" s="17" t="s">
         <v>64</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="G39" s="18" t="s">
         <v>925</v>
@@ -17296,22 +17299,22 @@
     </row>
     <row r="40" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="25" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="G40" s="18" t="s">
         <v>925</v>
@@ -17320,22 +17323,22 @@
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="25" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="G41" s="18" t="s">
         <v>925</v>
@@ -17344,12 +17347,12 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -17359,7 +17362,7 @@
     </row>
     <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="2" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -17369,7 +17372,7 @@
     </row>
     <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="2" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -17379,7 +17382,7 @@
     </row>
     <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -17389,7 +17392,7 @@
     </row>
     <row r="48" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="2" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -17399,7 +17402,7 @@
     </row>
     <row r="49" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -17493,40 +17496,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="K1" s="14" t="s">
         <v>917</v>
       </c>
       <c r="L1" s="14" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="M1" s="14" t="s">
         <v>8</v>
@@ -17537,1065 +17540,1065 @@
     </row>
     <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D2" s="16" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="K2" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L2" s="20"/>
       <c r="M2" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N2" s="19"/>
     </row>
     <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="K3" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L3" s="20"/>
       <c r="M3" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N3" s="19"/>
     </row>
     <row r="4" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="J4" s="15" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="K4" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L4" s="20"/>
       <c r="M4" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N4" s="19"/>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="G5" s="15" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="H5" s="15" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="I5" s="15"/>
       <c r="J5" s="15" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="K5" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L5" s="20"/>
       <c r="M5" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N5" s="19"/>
     </row>
     <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="G6" s="15"/>
       <c r="H6" s="15" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="I6" s="15"/>
       <c r="J6" s="15" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="K6" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L6" s="20"/>
       <c r="M6" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N6" s="19"/>
     </row>
     <row r="7" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="E7" s="23" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="F7" s="23" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="G7" s="23" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H7" s="23" t="s">
         <v>939</v>
       </c>
       <c r="I7" s="23" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="K7" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L7" s="20"/>
       <c r="M7" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N7" s="19"/>
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="F8" s="23" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="G8" s="23" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H8" s="23" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="I8" s="23" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="J8" s="23" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="K8" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L8" s="20"/>
       <c r="M8" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N8" s="19"/>
     </row>
     <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="F9" s="23" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="G9" s="23" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H9" s="23" t="s">
         <v>939</v>
       </c>
       <c r="I9" s="23" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="J9" s="23" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="K9" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L9" s="20"/>
       <c r="M9" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N9" s="19"/>
     </row>
     <row r="10" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="F10" s="23" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="G10" s="23" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H10" s="23" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="I10" s="23" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="J10" s="23" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="K10" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L10" s="20"/>
       <c r="M10" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N10" s="19"/>
     </row>
     <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D11" s="24" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="F11" s="23" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="G11" s="23" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="H11" s="23" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="K11" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L11" s="20"/>
       <c r="M11" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N11" s="19"/>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="F12" s="23" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="G12" s="23" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H12" s="23" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="I12" s="23" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="J12" s="23" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="K12" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L12" s="20"/>
       <c r="M12" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N12" s="19"/>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D13" s="24" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="I13" s="23" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="J13" s="23" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="K13" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L13" s="20"/>
       <c r="M13" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N13" s="19"/>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="F14" s="23" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="G14" s="23" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="H14" s="23" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="I14" s="23" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="J14" s="23" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="K14" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L14" s="20"/>
       <c r="M14" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N14" s="19"/>
     </row>
     <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="I15" s="23" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="J15" s="23" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="K15" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L15" s="20"/>
       <c r="M15" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N15" s="19"/>
     </row>
     <row r="16" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C16" s="23" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="F16" s="23" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="G16" s="23" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H16" s="23" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="I16" s="23" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="J16" s="23" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="K16" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L16" s="20"/>
       <c r="M16" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N16" s="19"/>
     </row>
     <row r="17" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D17" s="24" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="I17" s="23"/>
       <c r="J17" s="23" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="K17" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L17" s="20"/>
       <c r="M17" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N17" s="19"/>
     </row>
     <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="F18" s="23" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="G18" s="23" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="H18" s="23" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="I18" s="23"/>
       <c r="J18" s="23" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="K18" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L18" s="20"/>
       <c r="M18" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N18" s="19"/>
     </row>
     <row r="19" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D19" s="24" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H19" s="23" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="I19" s="23" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="J19" s="23" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="K19" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L19" s="20"/>
       <c r="M19" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N19" s="19"/>
     </row>
     <row r="20" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D20" s="24" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="H20" s="23" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="J20" s="23" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="K20" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L20" s="20"/>
       <c r="M20" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N20" s="19"/>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D21" s="24" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="H21" s="23"/>
       <c r="I21" s="23"/>
       <c r="J21" s="23" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="K21" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L21" s="20"/>
       <c r="M21" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N21" s="19"/>
     </row>
     <row r="22" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="F22" s="23"/>
       <c r="G22" s="23" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="I22" s="23"/>
       <c r="J22" s="23" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="K22" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L22" s="20"/>
       <c r="M22" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N22" s="19"/>
     </row>
     <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="I23" s="23"/>
       <c r="J23" s="23" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="K23" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L23" s="20"/>
       <c r="M23" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N23" s="19"/>
     </row>
     <row r="24" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="F24" s="23" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="G24" s="23" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H24" s="23" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="I24" s="23"/>
       <c r="J24" s="23" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="K24" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L24" s="20"/>
       <c r="M24" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N24" s="19"/>
     </row>
     <row r="25" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D25" s="24" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="I25" s="23" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="J25" s="23" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="K25" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L25" s="20"/>
       <c r="M25" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N25" s="19"/>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D26" s="24" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="F26" s="23" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="G26" s="23" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H26" s="23"/>
       <c r="I26" s="23"/>
       <c r="J26" s="23" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="K26" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L26" s="20"/>
       <c r="M26" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N26" s="19"/>
     </row>
     <row r="27" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D27" s="24" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="E27" s="23" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="F27" s="23" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="G27" s="23"/>
       <c r="H27" s="23"/>
       <c r="I27" s="23"/>
       <c r="J27" s="23" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="K27" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L27" s="20"/>
       <c r="M27" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N27" s="19"/>
     </row>
     <row r="28" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D28" s="24" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="G28" s="23"/>
       <c r="H28" s="23" t="s">
         <v>939</v>
       </c>
       <c r="I28" s="23" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="J28" s="23" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="K28" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L28" s="20"/>
       <c r="M28" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N28" s="19"/>
     </row>
     <row r="29" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D29" s="24" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="E29" s="23" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="F29" s="23"/>
       <c r="G29" s="23"/>
@@ -18603,967 +18606,967 @@
         <v>939</v>
       </c>
       <c r="I29" s="23" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="J29" s="23" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="K29" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L29" s="20"/>
       <c r="M29" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N29" s="19"/>
     </row>
     <row r="30" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="23" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D30" s="24" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="G30" s="23" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H30" s="23" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="I30" s="23" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="J30" s="23" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="K30" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L30" s="20"/>
       <c r="M30" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N30" s="19"/>
     </row>
     <row r="31" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B31" s="17" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C31" s="17" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D31" s="25" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="E31" s="17" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="F31" s="17" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="G31" s="17" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="K31" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L31" s="20"/>
       <c r="M31" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N31" s="19"/>
     </row>
     <row r="32" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B32" s="17" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C32" s="17" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="I32" s="17" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="K32" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L32" s="20"/>
       <c r="M32" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N32" s="19"/>
     </row>
     <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B33" s="17" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C33" s="17" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D33" s="25" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="E33" s="17" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="K33" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L33" s="20"/>
       <c r="M33" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N33" s="19"/>
     </row>
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B34" s="17" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C34" s="17" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="E34" s="17" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="F34" s="17" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="K34" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L34" s="20"/>
       <c r="M34" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N34" s="19"/>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B35" s="17" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C35" s="17" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D35" s="25" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="E35" s="17" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="F35" s="17" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="K35" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L35" s="20"/>
       <c r="M35" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N35" s="19"/>
     </row>
     <row r="36" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B36" s="17" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C36" s="17" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="E36" s="17" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="F36" s="17" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>939</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="K36" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L36" s="20"/>
       <c r="M36" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N36" s="19"/>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B37" s="17" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C37" s="17" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="D37" s="25" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="E37" s="17" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="F37" s="17" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="G37" s="17" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="K37" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L37" s="20"/>
       <c r="M37" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N37" s="19"/>
     </row>
     <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B38" s="17" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C38" s="17" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="E38" s="17" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="F38" s="17" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="G38" s="17" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="I38" s="17" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="K38" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L38" s="20"/>
       <c r="M38" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N38" s="19"/>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B39" s="17" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C39" s="17" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="D39" s="25" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="E39" s="17" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="F39" s="17" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="G39" s="17" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="I39" s="17" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="K39" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L39" s="20"/>
       <c r="M39" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N39" s="19"/>
     </row>
     <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B40" s="17" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C40" s="17" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="E40" s="17" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="F40" s="17" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="G40" s="17" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H40" s="17" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="K40" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L40" s="20"/>
       <c r="M40" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N40" s="19"/>
     </row>
     <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B41" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C41" s="17" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D41" s="25" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="E41" s="17" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="F41" s="17"/>
       <c r="G41" s="17" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H41" s="17" t="s">
         <v>939</v>
       </c>
       <c r="I41" s="17" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="K41" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L41" s="20"/>
       <c r="M41" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N41" s="19"/>
     </row>
     <row r="42" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B42" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="E42" s="17" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="G42" s="17"/>
       <c r="H42" s="17" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="I42" s="17" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="J42" s="17" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="K42" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L42" s="20"/>
       <c r="M42" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N42" s="19"/>
     </row>
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B43" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C43" s="17" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D43" s="25" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="E43" s="17" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="F43" s="17"/>
       <c r="G43" s="17" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H43" s="17" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="J43" s="17" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="K43" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L43" s="20"/>
       <c r="M43" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N43" s="19"/>
     </row>
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B44" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C44" s="17" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="E44" s="17" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="F44" s="17" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="G44" s="17" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="H44" s="17" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="I44" s="17" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="J44" s="17" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="K44" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L44" s="20"/>
       <c r="M44" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N44" s="19"/>
     </row>
     <row r="45" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B45" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C45" s="17" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D45" s="25" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="E45" s="17" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="F45" s="17"/>
       <c r="G45" s="17" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="H45" s="17" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="I45" s="17" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="J45" s="17" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="K45" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L45" s="20"/>
       <c r="M45" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N45" s="19"/>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B46" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C46" s="17" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="E46" s="17" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="G46" s="17" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="H46" s="17" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="I46" s="17" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="J46" s="17" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="K46" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L46" s="20"/>
       <c r="M46" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N46" s="19"/>
     </row>
     <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B47" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C47" s="17" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D47" s="25" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="E47" s="17" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="F47" s="17" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="G47" s="17" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="H47" s="17" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="I47" s="17" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="J47" s="17" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="K47" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L47" s="20"/>
       <c r="M47" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N47" s="19"/>
     </row>
     <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B48" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C48" s="17" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="E48" s="17" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="F48" s="17" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="G48" s="17" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H48" s="17" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="I48" s="17" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="J48" s="17" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="K48" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L48" s="20"/>
       <c r="M48" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N48" s="19"/>
     </row>
     <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B49" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C49" s="17" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D49" s="25" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="E49" s="17" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="F49" s="17" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="G49" s="17" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="I49" s="17" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="J49" s="17" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="K49" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L49" s="20"/>
       <c r="M49" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N49" s="19"/>
     </row>
     <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B50" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C50" s="17" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="E50" s="17" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="F50" s="17" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="G50" s="17" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H50" s="17" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="I50" s="17" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="J50" s="17" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="K50" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L50" s="20"/>
       <c r="M50" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N50" s="19"/>
     </row>
     <row r="51" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B51" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C51" s="17" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D51" s="25" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="E51" s="17" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="F51" s="17" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="G51" s="17" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H51" s="17"/>
       <c r="I51" s="17" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="J51" s="17" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="K51" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L51" s="20"/>
       <c r="M51" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N51" s="19"/>
     </row>
     <row r="52" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B52" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C52" s="17" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="E52" s="17" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="F52" s="17"/>
       <c r="G52" s="17" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H52" s="17" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="I52" s="17" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="J52" s="17" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="K52" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L52" s="20"/>
       <c r="M52" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N52" s="19"/>
     </row>
     <row r="53" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="17" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B53" s="17" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C53" s="17" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D53" s="25" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="E53" s="17" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="F53" s="17"/>
       <c r="G53" s="17" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H53" s="17" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="I53" s="17"/>
       <c r="J53" s="17" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="K53" s="18" t="s">
         <v>925</v>
       </c>
       <c r="L53" s="20"/>
       <c r="M53" s="19" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N53" s="19"/>
     </row>
     <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -19577,7 +19580,7 @@
     </row>
     <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="2" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
@@ -19591,7 +19594,7 @@
     </row>
     <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
@@ -19605,7 +19608,7 @@
     </row>
     <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -19619,7 +19622,7 @@
     </row>
     <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -19731,7 +19734,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>40</v>
@@ -19740,7 +19743,7 @@
         <v>912</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="E1" s="14" t="s">
         <v>915</v>
@@ -19752,84 +19755,84 @@
         <v>44</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="J1" s="14" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>939</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="F2" s="17"/>
       <c r="G2" s="26" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="I2" s="19" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="J2" s="20"/>
     </row>
     <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B3" s="17" t="s">
         <v>939</v>
       </c>
       <c r="C3" s="17" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="F3" s="17"/>
       <c r="G3" s="26" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H3" s="20"/>
       <c r="I3" s="19"/>
       <c r="J3" s="20" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="F4" s="18" t="s">
         <v>925</v>
@@ -19843,19 +19846,19 @@
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="18" t="s">
@@ -19867,19 +19870,19 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="F6" s="18" t="s">
         <v>925</v>
@@ -19893,19 +19896,19 @@
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>1467</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E7" s="17" t="s">
         <v>1465</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>1466</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>1453</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>1463</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>1464</v>
       </c>
       <c r="F7" s="18" t="s">
         <v>925</v>
@@ -19919,19 +19922,19 @@
     </row>
     <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="F8" s="18" t="s">
         <v>925</v>
@@ -19945,19 +19948,19 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="F9" s="18" t="s">
         <v>925</v>
@@ -19971,19 +19974,19 @@
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="F10" s="18" t="s">
         <v>925</v>
@@ -19997,19 +20000,19 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>925</v>
@@ -20023,19 +20026,19 @@
     </row>
     <row r="12" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>925</v>
@@ -20049,19 +20052,19 @@
     </row>
     <row r="13" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="F13" s="18" t="s">
         <v>925</v>
@@ -20075,19 +20078,19 @@
     </row>
     <row r="14" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="F14" s="18" t="s">
         <v>925</v>
@@ -20101,19 +20104,19 @@
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="F15" s="18" t="s">
         <v>925</v>
@@ -20127,19 +20130,19 @@
     </row>
     <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E16" s="17" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="F16" s="18" t="s">
         <v>925</v>
@@ -20153,19 +20156,19 @@
     </row>
     <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="F17" s="18" t="s">
         <v>925</v>
@@ -20179,19 +20182,19 @@
     </row>
     <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="F18" s="18" t="s">
         <v>925</v>
@@ -20205,19 +20208,19 @@
     </row>
     <row r="19" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="F19" s="18" t="s">
         <v>925</v>
@@ -20231,19 +20234,19 @@
     </row>
     <row r="20" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>1464</v>
+      </c>
+      <c r="E20" s="17" t="s">
         <v>1497</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>1498</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>1453</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>1463</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>1496</v>
       </c>
       <c r="F20" s="18" t="s">
         <v>925</v>
@@ -20257,19 +20260,19 @@
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="F21" s="18" t="s">
         <v>925</v>
@@ -20283,19 +20286,19 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="F22" s="18" t="s">
         <v>925</v>
@@ -20309,19 +20312,19 @@
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="E23" s="17" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="F23" s="18" t="s">
         <v>925</v>
@@ -20335,7 +20338,7 @@
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="2" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -20345,7 +20348,7 @@
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="2" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -20355,7 +20358,7 @@
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="2" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -20365,7 +20368,7 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -20456,10 +20459,10 @@
         <v>911</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>915</v>
@@ -20470,16 +20473,16 @@
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="D2" s="17" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="E2" s="27" t="s">
         <v>925</v>
@@ -20487,16 +20490,16 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="C3" s="17" t="s">
         <v>315</v>
       </c>
       <c r="D3" s="17" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="E3" s="27" t="s">
         <v>925</v>
@@ -20504,16 +20507,16 @@
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="E4" s="27" t="s">
         <v>925</v>
@@ -20521,16 +20524,16 @@
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="E5" s="27" t="s">
         <v>925</v>
@@ -20538,16 +20541,16 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="E6" s="27" t="s">
         <v>925</v>
@@ -20555,16 +20558,16 @@
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="E7" s="27" t="s">
         <v>925</v>
@@ -20572,16 +20575,16 @@
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="E8" s="27" t="s">
         <v>925</v>
@@ -20589,16 +20592,16 @@
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="E9" s="27" t="s">
         <v>925</v>
@@ -20606,16 +20609,16 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="C10" s="17" t="s">
         <v>50</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="E10" s="27" t="s">
         <v>925</v>
@@ -20623,16 +20626,16 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="E11" s="27" t="s">
         <v>925</v>
@@ -20640,16 +20643,16 @@
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="E12" s="27" t="s">
         <v>925</v>
@@ -20657,16 +20660,16 @@
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="E13" s="27" t="s">
         <v>925</v>
@@ -20674,16 +20677,16 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="E14" s="27" t="s">
         <v>925</v>
@@ -20691,16 +20694,16 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="C15" s="17" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="E15" s="27" t="s">
         <v>925</v>
@@ -20708,16 +20711,16 @@
     </row>
     <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B16" s="17" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="C16" s="17" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="E16" s="27" t="s">
         <v>925</v>
@@ -20725,16 +20728,16 @@
     </row>
     <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="C17" s="17" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="E17" s="27" t="s">
         <v>925</v>
@@ -20742,16 +20745,16 @@
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="E18" s="27" t="s">
         <v>925</v>
@@ -20759,16 +20762,16 @@
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="C19" s="17" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="E19" s="27" t="s">
         <v>925</v>
@@ -20776,16 +20779,16 @@
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="C20" s="17" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="E20" s="27" t="s">
         <v>925</v>
@@ -20793,16 +20796,16 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="C21" s="17" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="E21" s="27" t="s">
         <v>925</v>
@@ -20810,16 +20813,16 @@
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="C22" s="17" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="E22" s="28"/>
     </row>
@@ -20871,10 +20874,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>44</v>
@@ -20882,10 +20885,10 @@
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="25" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>925</v>
@@ -20893,10 +20896,10 @@
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="25" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B3" s="17" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="C3" s="27" t="s">
         <v>925</v>
@@ -20904,10 +20907,10 @@
     </row>
     <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="25" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="C4" s="27" t="s">
         <v>925</v>
@@ -20915,10 +20918,10 @@
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="C5" s="27" t="s">
         <v>925</v>
@@ -20926,10 +20929,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="C6" s="27" t="s">
         <v>925</v>
@@ -20937,10 +20940,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="C7" s="27" t="s">
         <v>925</v>
@@ -20948,10 +20951,10 @@
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="C8" s="27" t="s">
         <v>925</v>
@@ -20959,10 +20962,10 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="C9" s="27" t="s">
         <v>925</v>
@@ -20970,10 +20973,10 @@
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="C10" s="27" t="s">
         <v>925</v>
@@ -20981,10 +20984,10 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="C11" s="27" t="s">
         <v>925</v>
@@ -20992,7 +20995,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
   </sheetData>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -4853,10 +4853,10 @@
     <t xml:space="preserve">Acheteurs qui demandent conseil à ChatGPT</t>
   </si>
   <si>
-    <t xml:space="preserve">Disponibilité en France à vérifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shopify admin &gt; Paramètres &gt; Canaux de vente &gt; Agentic storefronts. Masquer d'abord les produits « Acompte ».</t>
+    <t xml:space="preserve">Non disponible (13/10/2026) : réservé aux boutiques qui vendent aux États-Unis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pas de canal de vente possible pour l'instant. Visibilité gratuite : les pages du site peuvent être citées par la recherche de ChatGPT. D'ici là : passer les produits « Acompte » en « Non répertorié », remplir les CGV et la politique de remboursement, ajouter des photos réelles.</t>
   </si>
   <si>
     <t xml:space="preserve">E-mail / téléphone aux pros</t>
@@ -20794,7 +20794,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
         <v>1589</v>
       </c>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3245" uniqueCount="1660">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3238" uniqueCount="1659">
   <si>
     <t xml:space="preserve">Prospection MINYALA — mode d'emploi</t>
   </si>
@@ -1775,6 +1775,12 @@
     <t xml:space="preserve">01 30 06 00 07</t>
   </si>
   <si>
+    <t xml:space="preserve">E-mail « 27 €/m² » envoyé le 12/10/2026 à 15:03 depuis la boîte Hotmail personnelle (copie reçue en INBOX).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact@mca-materiaux.net</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pierlux</t>
   </si>
   <si>
@@ -2894,25 +2900,16 @@
     <t xml:space="preserve">Envoi du 12/10 (hors liste)</t>
   </si>
   <si>
-    <t xml:space="preserve">MCA Matériaux — Achères</t>
+    <t xml:space="preserve">À préciser (carrelage)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISL Carrelage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À préciser</t>
   </si>
   <si>
     <t xml:space="preserve">Destinataire de l'envoi du 12/10 absent de la liste d'origine : fiche à compléter.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-mail « 27 €/m² » envoyé le 12/10/2026 à 15:03 depuis la boîte Hotmail personnelle (copie reçue en INBOX).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contact@mca-materiaux.net</t>
-  </si>
-  <si>
-    <t xml:space="preserve">À préciser (carrelage)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ISL Carrelage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">À préciser</t>
   </si>
   <si>
     <t xml:space="preserve">E-mail « 27 €/m² » envoyé le 12/10/2026 à 17:56 depuis la boîte Hotmail personnelle (copie reçue en INBOX).</t>
@@ -5312,7 +5309,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5825,7 +5822,7 @@
       </c>
       <c r="B19" s="9" t="n">
         <f aca="false">COUNTIF(Prospects!$L$2:$L$400,A19)</f>
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5888,7 +5885,7 @@
       </c>
       <c r="B26" s="4" t="n">
         <f aca="false">COUNTA(Prospects!$E$2:$E$400)</f>
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5989,7 +5986,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7209,7 +7206,7 @@
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
       </c>
-      <c r="R28" s="0" t="s">
+      <c r="R28" s="1" t="s">
         <v>154</v>
       </c>
     </row>
@@ -7264,7 +7261,7 @@
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
       </c>
-      <c r="R29" s="0" t="s">
+      <c r="R29" s="1" t="s">
         <v>161</v>
       </c>
     </row>
@@ -7319,7 +7316,7 @@
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
       </c>
-      <c r="R30" s="0" t="s">
+      <c r="R30" s="1" t="s">
         <v>168</v>
       </c>
     </row>
@@ -7466,7 +7463,7 @@
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
       </c>
-      <c r="R33" s="0" t="s">
+      <c r="R33" s="1" t="s">
         <v>185</v>
       </c>
     </row>
@@ -11147,7 +11144,7 @@
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
       </c>
-      <c r="R114" s="0" t="s">
+      <c r="R114" s="1" t="s">
         <v>547</v>
       </c>
     </row>
@@ -11202,7 +11199,7 @@
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
       </c>
-      <c r="R115" s="0" t="s">
+      <c r="R115" s="1" t="s">
         <v>553</v>
       </c>
     </row>
@@ -11257,7 +11254,7 @@
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
       </c>
-      <c r="R116" s="0" t="s">
+      <c r="R116" s="1" t="s">
         <v>559</v>
       </c>
     </row>
@@ -11296,15 +11293,24 @@
         <v>53</v>
       </c>
       <c r="L117" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="M117" s="22"/>
-      <c r="N117" s="21"/>
-      <c r="O117" s="21"/>
+        <v>9</v>
+      </c>
+      <c r="M117" s="22" t="s">
+        <v>151</v>
+      </c>
+      <c r="N117" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="O117" s="21" t="s">
+        <v>565</v>
+      </c>
       <c r="P117" s="23"/>
       <c r="Q117" s="24" t="n">
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
+      </c>
+      <c r="R117" s="1" t="s">
+        <v>566</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11321,19 +11327,19 @@
         <v>48</v>
       </c>
       <c r="E118" s="18" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="F118" s="17" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="G118" s="17" t="s">
         <v>51</v>
       </c>
       <c r="H118" s="17" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="I118" s="20" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="J118" s="19"/>
       <c r="K118" s="20" t="s">
@@ -11365,19 +11371,19 @@
         <v>48</v>
       </c>
       <c r="E119" s="18" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="F119" s="17" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="G119" s="17" t="s">
         <v>51</v>
       </c>
       <c r="H119" s="17" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="I119" s="20" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="J119" s="19"/>
       <c r="K119" s="20" t="s">
@@ -11409,7 +11415,7 @@
         <v>135</v>
       </c>
       <c r="E120" s="18" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="F120" s="17" t="s">
         <v>78</v>
@@ -11418,13 +11424,13 @@
         <v>51</v>
       </c>
       <c r="H120" s="17" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="I120" s="20" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="J120" s="19" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="K120" s="20" t="s">
         <v>53</v>
@@ -11446,8 +11452,8 @@
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
       </c>
-      <c r="R120" s="0" t="s">
-        <v>577</v>
+      <c r="R120" s="1" t="s">
+        <v>579</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11464,22 +11470,22 @@
         <v>135</v>
       </c>
       <c r="E121" s="18" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="F121" s="17" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="G121" s="17" t="s">
         <v>51</v>
       </c>
       <c r="H121" s="17" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="I121" s="20" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="J121" s="19" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="K121" s="20" t="s">
         <v>53</v>
@@ -11510,22 +11516,22 @@
         <v>135</v>
       </c>
       <c r="E122" s="18" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="F122" s="17" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="G122" s="17" t="s">
         <v>51</v>
       </c>
       <c r="H122" s="17" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="I122" s="20" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="J122" s="19" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="K122" s="20" t="s">
         <v>53</v>
@@ -11540,15 +11546,15 @@
         <v>152</v>
       </c>
       <c r="O122" s="21" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="P122" s="23"/>
       <c r="Q122" s="24" t="n">
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
       </c>
-      <c r="R122" s="0" t="s">
-        <v>589</v>
+      <c r="R122" s="1" t="s">
+        <v>591</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11565,16 +11571,16 @@
         <v>135</v>
       </c>
       <c r="E123" s="18" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="F123" s="17" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="G123" s="17" t="s">
         <v>51</v>
       </c>
       <c r="H123" s="17" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="I123" s="19"/>
       <c r="J123" s="19"/>
@@ -11591,15 +11597,15 @@
         <v>152</v>
       </c>
       <c r="O123" s="21" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="P123" s="23"/>
       <c r="Q123" s="24" t="n">
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
       </c>
-      <c r="R123" s="0" t="s">
-        <v>593</v>
+      <c r="R123" s="1" t="s">
+        <v>595</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11616,22 +11622,22 @@
         <v>72</v>
       </c>
       <c r="E124" s="18" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="F124" s="17" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="G124" s="17" t="s">
         <v>51</v>
       </c>
       <c r="H124" s="17" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="I124" s="20" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="J124" s="19" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="K124" s="20" t="s">
         <v>53</v>
@@ -11662,22 +11668,22 @@
         <v>72</v>
       </c>
       <c r="E125" s="18" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="F125" s="17" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="G125" s="17" t="s">
         <v>51</v>
       </c>
       <c r="H125" s="17" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="I125" s="20" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="J125" s="19" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="K125" s="20" t="s">
         <v>53</v>
@@ -11708,22 +11714,22 @@
         <v>68</v>
       </c>
       <c r="E126" s="18" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="F126" s="17" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="G126" s="17" t="s">
         <v>51</v>
       </c>
       <c r="H126" s="17" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="I126" s="20" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="J126" s="19" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="K126" s="20" t="s">
         <v>53</v>
@@ -11738,15 +11744,15 @@
         <v>152</v>
       </c>
       <c r="O126" s="21" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="P126" s="23"/>
       <c r="Q126" s="24" t="n">
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
       </c>
-      <c r="R126" s="0" t="s">
-        <v>609</v>
+      <c r="R126" s="1" t="s">
+        <v>611</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11760,25 +11766,25 @@
         <v>1</v>
       </c>
       <c r="D127" s="17" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E127" s="18" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="F127" s="17" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="G127" s="17" t="s">
         <v>51</v>
       </c>
       <c r="H127" s="17" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="I127" s="20" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="J127" s="19" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="K127" s="20" t="s">
         <v>53</v>
@@ -11809,7 +11815,7 @@
         <v>48</v>
       </c>
       <c r="E128" s="18" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="F128" s="17" t="s">
         <v>113</v>
@@ -11818,13 +11824,13 @@
         <v>65</v>
       </c>
       <c r="H128" s="17" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="I128" s="20" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="J128" s="19" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="K128" s="20" t="s">
         <v>53</v>
@@ -11855,7 +11861,7 @@
         <v>48</v>
       </c>
       <c r="E129" s="18" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="F129" s="17" t="s">
         <v>187</v>
@@ -11864,10 +11870,10 @@
         <v>65</v>
       </c>
       <c r="H129" s="17" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="I129" s="20" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="J129" s="19"/>
       <c r="K129" s="20" t="s">
@@ -11899,22 +11905,22 @@
         <v>135</v>
       </c>
       <c r="E130" s="18" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="F130" s="17" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="G130" s="17" t="s">
         <v>65</v>
       </c>
       <c r="H130" s="17" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="I130" s="20" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="J130" s="19" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="K130" s="20" t="s">
         <v>53</v>
@@ -11936,8 +11942,8 @@
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
       </c>
-      <c r="R130" s="0" t="s">
-        <v>628</v>
+      <c r="R130" s="1" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11954,22 +11960,22 @@
         <v>135</v>
       </c>
       <c r="E131" s="18" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="F131" s="17" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G131" s="17" t="s">
         <v>65</v>
       </c>
       <c r="H131" s="17" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="I131" s="20" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="J131" s="19" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="K131" s="20" t="s">
         <v>53</v>
@@ -11991,8 +11997,8 @@
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
       </c>
-      <c r="R131" s="0" t="s">
-        <v>634</v>
+      <c r="R131" s="1" t="s">
+        <v>636</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12009,22 +12015,22 @@
         <v>135</v>
       </c>
       <c r="E132" s="18" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="F132" s="17" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="G132" s="17" t="s">
         <v>65</v>
       </c>
       <c r="H132" s="17" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="I132" s="20" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="J132" s="19" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="K132" s="20" t="s">
         <v>53</v>
@@ -12055,7 +12061,7 @@
         <v>76</v>
       </c>
       <c r="E133" s="18" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="F133" s="17" t="s">
         <v>417</v>
@@ -12064,13 +12070,13 @@
         <v>65</v>
       </c>
       <c r="H133" s="17" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="I133" s="20" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="J133" s="19" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="K133" s="20" t="s">
         <v>53</v>
@@ -12101,22 +12107,22 @@
         <v>68</v>
       </c>
       <c r="E134" s="18" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="F134" s="17" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="G134" s="17" t="s">
         <v>65</v>
       </c>
       <c r="H134" s="17" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="I134" s="20" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="J134" s="19" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="K134" s="20" t="s">
         <v>53</v>
@@ -12138,8 +12144,8 @@
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
       </c>
-      <c r="R134" s="0" t="s">
-        <v>649</v>
+      <c r="R134" s="1" t="s">
+        <v>651</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12153,25 +12159,25 @@
         <v>1</v>
       </c>
       <c r="D135" s="17" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E135" s="18" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F135" s="17" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="G135" s="17" t="s">
         <v>65</v>
       </c>
       <c r="H135" s="17" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="I135" s="20" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="J135" s="19" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="K135" s="20" t="s">
         <v>53</v>
@@ -12186,15 +12192,15 @@
         <v>152</v>
       </c>
       <c r="O135" s="21" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="P135" s="23"/>
       <c r="Q135" s="24" t="n">
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
       </c>
-      <c r="R135" s="0" t="s">
-        <v>656</v>
+      <c r="R135" s="1" t="s">
+        <v>658</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12208,10 +12214,10 @@
         <v>1</v>
       </c>
       <c r="D136" s="17" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E136" s="18" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="F136" s="17" t="s">
         <v>528</v>
@@ -12220,13 +12226,13 @@
         <v>65</v>
       </c>
       <c r="H136" s="17" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="I136" s="20" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="J136" s="19" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="K136" s="20" t="s">
         <v>53</v>
@@ -12257,16 +12263,16 @@
         <v>135</v>
       </c>
       <c r="E137" s="26" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="F137" s="25" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="G137" s="25" t="s">
         <v>51</v>
       </c>
       <c r="H137" s="25" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="I137" s="19"/>
       <c r="J137" s="19"/>
@@ -12299,19 +12305,19 @@
         <v>72</v>
       </c>
       <c r="E138" s="26" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="F138" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="G138" s="25" t="s">
         <v>51</v>
       </c>
       <c r="H138" s="25" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="I138" s="20" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="J138" s="19"/>
       <c r="K138" s="20" t="s">
@@ -12343,16 +12349,16 @@
         <v>72</v>
       </c>
       <c r="E139" s="26" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="F139" s="25" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="G139" s="25" t="s">
         <v>51</v>
       </c>
       <c r="H139" s="25" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="I139" s="19"/>
       <c r="J139" s="19"/>
@@ -12385,22 +12391,22 @@
         <v>72</v>
       </c>
       <c r="E140" s="26" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="F140" s="25" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="G140" s="25" t="s">
         <v>51</v>
       </c>
       <c r="H140" s="25" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="I140" s="20" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="J140" s="19" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="K140" s="20" t="s">
         <v>53</v>
@@ -12431,22 +12437,22 @@
         <v>76</v>
       </c>
       <c r="E141" s="26" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="F141" s="25" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="G141" s="25" t="s">
         <v>51</v>
       </c>
       <c r="H141" s="25" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="I141" s="20" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="J141" s="19" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="K141" s="20" t="s">
         <v>53</v>
@@ -12477,22 +12483,22 @@
         <v>76</v>
       </c>
       <c r="E142" s="26" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="F142" s="25" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="G142" s="25" t="s">
         <v>51</v>
       </c>
       <c r="H142" s="25" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="I142" s="20" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="J142" s="19" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="K142" s="20" t="s">
         <v>53</v>
@@ -12523,22 +12529,22 @@
         <v>68</v>
       </c>
       <c r="E143" s="26" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="F143" s="25" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="G143" s="25" t="s">
         <v>51</v>
       </c>
       <c r="H143" s="25" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="I143" s="20" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="J143" s="19" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="K143" s="20" t="s">
         <v>53</v>
@@ -12569,16 +12575,16 @@
         <v>68</v>
       </c>
       <c r="E144" s="26" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="F144" s="25" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="G144" s="25" t="s">
         <v>51</v>
       </c>
       <c r="H144" s="25" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="I144" s="19"/>
       <c r="J144" s="19"/>
@@ -12611,16 +12617,16 @@
         <v>68</v>
       </c>
       <c r="E145" s="26" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="F145" s="25" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="G145" s="25" t="s">
         <v>51</v>
       </c>
       <c r="H145" s="25" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="I145" s="19"/>
       <c r="J145" s="19"/>
@@ -12653,22 +12659,22 @@
         <v>319</v>
       </c>
       <c r="E146" s="26" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="F146" s="25" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="G146" s="25" t="s">
         <v>51</v>
       </c>
       <c r="H146" s="25" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="I146" s="20" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="J146" s="19" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="K146" s="20" t="s">
         <v>53</v>
@@ -12699,22 +12705,22 @@
         <v>319</v>
       </c>
       <c r="E147" s="26" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="F147" s="25" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="G147" s="25" t="s">
         <v>51</v>
       </c>
       <c r="H147" s="25" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="I147" s="20" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="J147" s="19" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="K147" s="20" t="s">
         <v>53</v>
@@ -12742,10 +12748,10 @@
         <v>2</v>
       </c>
       <c r="D148" s="25" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E148" s="26" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="F148" s="25" t="s">
         <v>303</v>
@@ -12754,13 +12760,13 @@
         <v>51</v>
       </c>
       <c r="H148" s="25" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="I148" s="20" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="J148" s="19" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="K148" s="20" t="s">
         <v>53</v>
@@ -12788,19 +12794,19 @@
         <v>2</v>
       </c>
       <c r="D149" s="25" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E149" s="26" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="F149" s="25" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="G149" s="25" t="s">
         <v>51</v>
       </c>
       <c r="H149" s="25" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="I149" s="19"/>
       <c r="J149" s="19"/>
@@ -12830,10 +12836,10 @@
         <v>2</v>
       </c>
       <c r="D150" s="25" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E150" s="26" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="F150" s="25" t="s">
         <v>478</v>
@@ -12842,13 +12848,13 @@
         <v>51</v>
       </c>
       <c r="H150" s="25" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="I150" s="20" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="J150" s="19" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="K150" s="20" t="s">
         <v>53</v>
@@ -12876,10 +12882,10 @@
         <v>2</v>
       </c>
       <c r="D151" s="25" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E151" s="26" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="F151" s="25" t="s">
         <v>61</v>
@@ -12888,13 +12894,13 @@
         <v>51</v>
       </c>
       <c r="H151" s="25" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="I151" s="20" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="J151" s="19" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="K151" s="20" t="s">
         <v>53</v>
@@ -12922,25 +12928,25 @@
         <v>2</v>
       </c>
       <c r="D152" s="25" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E152" s="26" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="F152" s="25" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="G152" s="25" t="s">
         <v>51</v>
       </c>
       <c r="H152" s="25" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="I152" s="20" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="J152" s="19" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="K152" s="20" t="s">
         <v>53</v>
@@ -12968,25 +12974,25 @@
         <v>2</v>
       </c>
       <c r="D153" s="25" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E153" s="26" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="F153" s="25" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="G153" s="25" t="s">
         <v>51</v>
       </c>
       <c r="H153" s="25" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="I153" s="20" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="J153" s="19" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="K153" s="20" t="s">
         <v>53</v>
@@ -13014,25 +13020,25 @@
         <v>2</v>
       </c>
       <c r="D154" s="25" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E154" s="26" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="F154" s="25" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="G154" s="25" t="s">
         <v>51</v>
       </c>
       <c r="H154" s="25" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="I154" s="20" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="J154" s="19" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="K154" s="20" t="s">
         <v>53</v>
@@ -13063,20 +13069,20 @@
         <v>48</v>
       </c>
       <c r="E155" s="26" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="F155" s="25" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="G155" s="25" t="s">
         <v>65</v>
       </c>
       <c r="H155" s="25" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="I155" s="19"/>
       <c r="J155" s="19" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="K155" s="20" t="s">
         <v>53</v>
@@ -13107,16 +13113,16 @@
         <v>48</v>
       </c>
       <c r="E156" s="26" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="F156" s="25" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="G156" s="25" t="s">
         <v>65</v>
       </c>
       <c r="H156" s="25" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="I156" s="19"/>
       <c r="J156" s="19"/>
@@ -13149,20 +13155,20 @@
         <v>135</v>
       </c>
       <c r="E157" s="26" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="F157" s="25" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="G157" s="25" t="s">
         <v>65</v>
       </c>
       <c r="H157" s="25" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="I157" s="19"/>
       <c r="J157" s="19" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="K157" s="20" t="s">
         <v>53</v>
@@ -13193,22 +13199,22 @@
         <v>135</v>
       </c>
       <c r="E158" s="26" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="F158" s="25" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="G158" s="25" t="s">
         <v>65</v>
       </c>
       <c r="H158" s="25" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="I158" s="20" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="J158" s="19" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="K158" s="20" t="s">
         <v>53</v>
@@ -13239,20 +13245,20 @@
         <v>72</v>
       </c>
       <c r="E159" s="26" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="F159" s="25" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="G159" s="25" t="s">
         <v>65</v>
       </c>
       <c r="H159" s="25" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="I159" s="19"/>
       <c r="J159" s="19" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="K159" s="20" t="s">
         <v>53</v>
@@ -13283,20 +13289,20 @@
         <v>72</v>
       </c>
       <c r="E160" s="26" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="F160" s="25" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="G160" s="25" t="s">
         <v>65</v>
       </c>
       <c r="H160" s="25" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="I160" s="19"/>
       <c r="J160" s="19" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="K160" s="20" t="s">
         <v>53</v>
@@ -13327,22 +13333,22 @@
         <v>95</v>
       </c>
       <c r="E161" s="26" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="F161" s="25" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="G161" s="25" t="s">
         <v>65</v>
       </c>
       <c r="H161" s="25" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I161" s="20" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="J161" s="19" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="K161" s="20" t="s">
         <v>53</v>
@@ -13373,20 +13379,20 @@
         <v>76</v>
       </c>
       <c r="E162" s="26" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="F162" s="25" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G162" s="25" t="s">
         <v>65</v>
       </c>
       <c r="H162" s="25" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="I162" s="19"/>
       <c r="J162" s="19" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="K162" s="20" t="s">
         <v>53</v>
@@ -13417,7 +13423,7 @@
         <v>76</v>
       </c>
       <c r="E163" s="26" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="F163" s="25" t="s">
         <v>377</v>
@@ -13426,11 +13432,11 @@
         <v>65</v>
       </c>
       <c r="H163" s="25" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="I163" s="19"/>
       <c r="J163" s="19" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="K163" s="20" t="s">
         <v>53</v>
@@ -13461,22 +13467,22 @@
         <v>76</v>
       </c>
       <c r="E164" s="26" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="F164" s="25" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="G164" s="25" t="s">
         <v>65</v>
       </c>
       <c r="H164" s="25" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="I164" s="20" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="J164" s="19" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="K164" s="20" t="s">
         <v>53</v>
@@ -13507,22 +13513,22 @@
         <v>76</v>
       </c>
       <c r="E165" s="26" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="F165" s="25" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="G165" s="25" t="s">
         <v>65</v>
       </c>
       <c r="H165" s="25" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="I165" s="20" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="J165" s="19" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="K165" s="20" t="s">
         <v>53</v>
@@ -13553,22 +13559,22 @@
         <v>68</v>
       </c>
       <c r="E166" s="26" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="F166" s="25" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="G166" s="25" t="s">
         <v>65</v>
       </c>
       <c r="H166" s="25" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="I166" s="20" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="J166" s="19" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="K166" s="20" t="s">
         <v>53</v>
@@ -13599,22 +13605,22 @@
         <v>68</v>
       </c>
       <c r="E167" s="26" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="F167" s="25" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="G167" s="25" t="s">
         <v>65</v>
       </c>
       <c r="H167" s="25" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="I167" s="20" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="J167" s="19" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="K167" s="20" t="s">
         <v>53</v>
@@ -13645,22 +13651,22 @@
         <v>319</v>
       </c>
       <c r="E168" s="26" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="F168" s="25" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="G168" s="25" t="s">
         <v>65</v>
       </c>
       <c r="H168" s="25" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="I168" s="20" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="J168" s="19" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="K168" s="20" t="s">
         <v>53</v>
@@ -13691,22 +13697,22 @@
         <v>319</v>
       </c>
       <c r="E169" s="26" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="F169" s="25" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="G169" s="25" t="s">
         <v>65</v>
       </c>
       <c r="H169" s="25" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="I169" s="20" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="J169" s="19" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="K169" s="20" t="s">
         <v>53</v>
@@ -13737,7 +13743,7 @@
         <v>319</v>
       </c>
       <c r="E170" s="26" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="F170" s="25" t="s">
         <v>377</v>
@@ -13746,13 +13752,13 @@
         <v>65</v>
       </c>
       <c r="H170" s="25" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="I170" s="20" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="J170" s="19" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="K170" s="20" t="s">
         <v>53</v>
@@ -13780,25 +13786,25 @@
         <v>2</v>
       </c>
       <c r="D171" s="25" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E171" s="26" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="F171" s="25" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="G171" s="25" t="s">
         <v>65</v>
       </c>
       <c r="H171" s="25" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="I171" s="20" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="J171" s="19" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="K171" s="20" t="s">
         <v>53</v>
@@ -13826,23 +13832,23 @@
         <v>2</v>
       </c>
       <c r="D172" s="25" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="E172" s="26" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="F172" s="25" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="G172" s="25" t="s">
         <v>65</v>
       </c>
       <c r="H172" s="25" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="I172" s="19"/>
       <c r="J172" s="19" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="K172" s="20" t="s">
         <v>53</v>
@@ -13870,25 +13876,25 @@
         <v>2</v>
       </c>
       <c r="D173" s="25" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E173" s="26" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="F173" s="25" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="G173" s="25" t="s">
         <v>65</v>
       </c>
       <c r="H173" s="25" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="I173" s="20" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="J173" s="19" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="K173" s="20" t="s">
         <v>53</v>
@@ -13916,10 +13922,10 @@
         <v>2</v>
       </c>
       <c r="D174" s="25" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E174" s="26" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="F174" s="25" t="s">
         <v>187</v>
@@ -13928,13 +13934,13 @@
         <v>65</v>
       </c>
       <c r="H174" s="25" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="I174" s="20" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="J174" s="19" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="K174" s="20" t="s">
         <v>53</v>
@@ -13962,25 +13968,25 @@
         <v>2</v>
       </c>
       <c r="D175" s="25" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E175" s="26" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="F175" s="25" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="G175" s="25" t="s">
         <v>65</v>
       </c>
       <c r="H175" s="25" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="I175" s="20" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="J175" s="19" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="K175" s="20" t="s">
         <v>53</v>
@@ -14008,10 +14014,10 @@
         <v>2</v>
       </c>
       <c r="D176" s="25" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E176" s="26" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="F176" s="25" t="s">
         <v>428</v>
@@ -14020,13 +14026,13 @@
         <v>65</v>
       </c>
       <c r="H176" s="25" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="I176" s="20" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="J176" s="19" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="K176" s="20" t="s">
         <v>53</v>
@@ -14057,22 +14063,22 @@
         <v>72</v>
       </c>
       <c r="E177" s="27" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="F177" s="19" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="G177" s="19" t="s">
         <v>51</v>
       </c>
       <c r="H177" s="19" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="I177" s="20" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="J177" s="19" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="K177" s="20" t="s">
         <v>53</v>
@@ -14103,16 +14109,16 @@
         <v>72</v>
       </c>
       <c r="E178" s="27" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="F178" s="19" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="G178" s="19" t="s">
         <v>51</v>
       </c>
       <c r="H178" s="19" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="I178" s="19"/>
       <c r="J178" s="19"/>
@@ -14145,22 +14151,22 @@
         <v>95</v>
       </c>
       <c r="E179" s="27" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="F179" s="19" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="G179" s="19" t="s">
         <v>51</v>
       </c>
       <c r="H179" s="19" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="I179" s="20" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="J179" s="19" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="K179" s="20" t="s">
         <v>53</v>
@@ -14191,22 +14197,22 @@
         <v>76</v>
       </c>
       <c r="E180" s="27" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="F180" s="19" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="G180" s="19" t="s">
         <v>51</v>
       </c>
       <c r="H180" s="19" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="I180" s="20" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="J180" s="19" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="K180" s="20" t="s">
         <v>53</v>
@@ -14237,22 +14243,22 @@
         <v>76</v>
       </c>
       <c r="E181" s="27" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="F181" s="19" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="G181" s="19" t="s">
         <v>51</v>
       </c>
       <c r="H181" s="19" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="I181" s="20" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="J181" s="19" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="K181" s="20" t="s">
         <v>53</v>
@@ -14283,16 +14289,16 @@
         <v>76</v>
       </c>
       <c r="E182" s="27" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="F182" s="19" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="G182" s="19" t="s">
         <v>51</v>
       </c>
       <c r="H182" s="19" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="I182" s="19"/>
       <c r="J182" s="19"/>
@@ -14325,22 +14331,22 @@
         <v>76</v>
       </c>
       <c r="E183" s="27" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="F183" s="19" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="G183" s="19" t="s">
         <v>51</v>
       </c>
       <c r="H183" s="19" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="I183" s="20" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="J183" s="19" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="K183" s="20" t="s">
         <v>53</v>
@@ -14371,7 +14377,7 @@
         <v>76</v>
       </c>
       <c r="E184" s="27" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="F184" s="19" t="s">
         <v>156</v>
@@ -14380,13 +14386,13 @@
         <v>51</v>
       </c>
       <c r="H184" s="19" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="I184" s="20" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="J184" s="19" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="K184" s="20" t="s">
         <v>53</v>
@@ -14417,22 +14423,22 @@
         <v>319</v>
       </c>
       <c r="E185" s="27" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="F185" s="19" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="G185" s="19" t="s">
         <v>51</v>
       </c>
       <c r="H185" s="19" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="I185" s="20" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="J185" s="19" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="K185" s="20" t="s">
         <v>53</v>
@@ -14463,22 +14469,22 @@
         <v>426</v>
       </c>
       <c r="E186" s="27" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="F186" s="19" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="G186" s="19" t="s">
         <v>51</v>
       </c>
       <c r="H186" s="19" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="I186" s="20" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="J186" s="19" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="K186" s="20" t="s">
         <v>53</v>
@@ -14506,25 +14512,25 @@
         <v>3</v>
       </c>
       <c r="D187" s="19" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E187" s="27" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="F187" s="19" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="G187" s="19" t="s">
         <v>51</v>
       </c>
       <c r="H187" s="19" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="I187" s="20" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="J187" s="19" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="K187" s="20" t="s">
         <v>53</v>
@@ -14552,25 +14558,25 @@
         <v>3</v>
       </c>
       <c r="D188" s="19" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="E188" s="27" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="F188" s="19" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="G188" s="19" t="s">
         <v>51</v>
       </c>
       <c r="H188" s="19" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="I188" s="20" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="J188" s="19" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="K188" s="20" t="s">
         <v>53</v>
@@ -14601,16 +14607,16 @@
         <v>95</v>
       </c>
       <c r="E189" s="27" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="F189" s="19" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="G189" s="19" t="s">
         <v>65</v>
       </c>
       <c r="H189" s="19" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="I189" s="19"/>
       <c r="J189" s="19"/>
@@ -14643,20 +14649,20 @@
         <v>95</v>
       </c>
       <c r="E190" s="27" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="F190" s="19" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="G190" s="19" t="s">
         <v>65</v>
       </c>
       <c r="H190" s="19" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="I190" s="19"/>
       <c r="J190" s="19" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="K190" s="20" t="s">
         <v>53</v>
@@ -14687,22 +14693,22 @@
         <v>68</v>
       </c>
       <c r="E191" s="27" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="F191" s="19" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="G191" s="19" t="s">
         <v>65</v>
       </c>
       <c r="H191" s="19" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="I191" s="20" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="J191" s="19" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="K191" s="20" t="s">
         <v>53</v>
@@ -14733,20 +14739,20 @@
         <v>319</v>
       </c>
       <c r="E192" s="27" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="F192" s="19" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="G192" s="19" t="s">
         <v>65</v>
       </c>
       <c r="H192" s="19" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="I192" s="19"/>
       <c r="J192" s="19" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="K192" s="20" t="s">
         <v>53</v>
@@ -14774,10 +14780,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="19" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E193" s="27" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="F193" s="19" t="s">
         <v>417</v>
@@ -14786,13 +14792,13 @@
         <v>65</v>
       </c>
       <c r="H193" s="19" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="I193" s="20" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="J193" s="19" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="K193" s="20" t="s">
         <v>53</v>
@@ -14820,25 +14826,25 @@
         <v>3</v>
       </c>
       <c r="D194" s="19" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E194" s="27" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="F194" s="19" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="G194" s="19" t="s">
         <v>65</v>
       </c>
       <c r="H194" s="19" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="I194" s="20" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="J194" s="19" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="K194" s="20" t="s">
         <v>53</v>
@@ -14866,25 +14872,25 @@
         <v>3</v>
       </c>
       <c r="D195" s="19" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="E195" s="27" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="F195" s="19" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="G195" s="19" t="s">
         <v>65</v>
       </c>
       <c r="H195" s="19" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="I195" s="20" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="J195" s="19" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="K195" s="20" t="s">
         <v>53</v>
@@ -14912,10 +14918,10 @@
         <v>3</v>
       </c>
       <c r="D196" s="19" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="E196" s="27" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="F196" s="19" t="s">
         <v>202</v>
@@ -14924,13 +14930,13 @@
         <v>65</v>
       </c>
       <c r="H196" s="19" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="I196" s="20" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="J196" s="19" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="K196" s="20" t="s">
         <v>53</v>
@@ -14958,25 +14964,25 @@
         <v>3</v>
       </c>
       <c r="D197" s="19" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E197" s="27" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="F197" s="19" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="G197" s="19" t="s">
         <v>65</v>
       </c>
       <c r="H197" s="19" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="I197" s="20" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="J197" s="19" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="K197" s="20" t="s">
         <v>53</v>
@@ -15004,22 +15010,22 @@
         <v>3</v>
       </c>
       <c r="D198" s="19" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="E198" s="27" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="F198" s="19" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="G198" s="19" t="s">
         <v>65</v>
       </c>
       <c r="H198" s="19" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="I198" s="20" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="J198" s="19"/>
       <c r="K198" s="20" t="s">
@@ -15039,28 +15045,28 @@
     </row>
     <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="1" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B199" s="1" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C199" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>48</v>
+        <v>940</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>561</v>
+        <v>942</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>51</v>
+        <v>942</v>
       </c>
       <c r="H199" s="1" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="L199" s="28" t="s">
         <v>9</v>
@@ -15072,40 +15078,40 @@
         <v>152</v>
       </c>
       <c r="O199" s="1" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="Q199" s="12" t="n">
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
       </c>
-      <c r="R199" s="0" t="s">
-        <v>941</v>
+      <c r="R199" s="1" t="s">
+        <v>945</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="1" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B200" s="1" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C200" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D200" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="F200" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="E200" s="1" t="s">
+      <c r="G200" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="H200" s="1" t="s">
         <v>943</v>
-      </c>
-      <c r="F200" s="1" t="s">
-        <v>944</v>
-      </c>
-      <c r="G200" s="1" t="s">
-        <v>944</v>
-      </c>
-      <c r="H200" s="1" t="s">
-        <v>939</v>
       </c>
       <c r="L200" s="28" t="s">
         <v>9</v>
@@ -15117,40 +15123,40 @@
         <v>152</v>
       </c>
       <c r="O200" s="1" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="Q200" s="12" t="n">
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
       </c>
-      <c r="R200" s="0" t="s">
-        <v>946</v>
+      <c r="R200" s="1" t="s">
+        <v>948</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="1" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C201" s="1" t="n">
         <v>2</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>76</v>
+        <v>942</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="H201" s="1" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="L201" s="28" t="s">
         <v>9</v>
@@ -15162,59 +15168,21 @@
         <v>152</v>
       </c>
       <c r="O201" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="Q201" s="12" t="n">
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
       </c>
-      <c r="R201" s="0" t="s">
-        <v>949</v>
+      <c r="R201" s="1" t="s">
+        <v>950</v>
       </c>
     </row>
     <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A202" s="1" t="n">
-        <v>201</v>
-      </c>
-      <c r="B202" s="1" t="s">
-        <v>937</v>
-      </c>
-      <c r="C202" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>944</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>950</v>
-      </c>
-      <c r="F202" s="1" t="s">
-        <v>944</v>
-      </c>
-      <c r="G202" s="1" t="s">
-        <v>944</v>
-      </c>
-      <c r="H202" s="1" t="s">
-        <v>939</v>
-      </c>
-      <c r="L202" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="M202" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="N202" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="O202" s="1" t="s">
-        <v>948</v>
-      </c>
+      <c r="L202" s="28"/>
       <c r="Q202" s="12" t="n">
         <f aca="false">'Mode d''emploi'!$B$29</f>
         <v>27</v>
-      </c>
-      <c r="R202" s="0" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16598,10 +16566,6 @@
     </row>
     <row r="400" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="L400" s="28"/>
-      <c r="Q400" s="12" t="n">
-        <f aca="false">'Mode d''emploi'!$B$29</f>
-        <v>27</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q400"/>
@@ -16988,996 +16952,996 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
+        <v>951</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>952</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="C1" s="15" t="s">
         <v>953</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="D1" s="15" t="s">
         <v>954</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="E1" s="15" t="s">
         <v>955</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="F1" s="15" t="s">
         <v>956</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="G1" s="15" t="s">
         <v>957</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="H1" s="15" t="s">
         <v>958</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
+        <v>959</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>960</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="C2" s="19" t="s">
         <v>961</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="D2" s="19" t="s">
         <v>962</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="E2" s="19" t="s">
         <v>963</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="F2" s="19" t="s">
         <v>964</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="G2" s="20" t="s">
         <v>965</v>
-      </c>
-      <c r="G2" s="20" t="s">
-        <v>966</v>
       </c>
       <c r="H2" s="22"/>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="27" t="s">
+        <v>966</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>967</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="C3" s="19" t="s">
         <v>968</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="D3" s="19" t="s">
         <v>969</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="E3" s="19" t="s">
         <v>970</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="F3" s="19" t="s">
         <v>971</v>
       </c>
-      <c r="F3" s="19" t="s">
-        <v>972</v>
-      </c>
       <c r="G3" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H3" s="22"/>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="27" t="s">
+        <v>972</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>967</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>973</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>968</v>
-      </c>
-      <c r="C4" s="19" t="s">
+      <c r="D4" s="19" t="s">
         <v>974</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="E4" s="19" t="s">
         <v>975</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="F4" s="19" t="s">
         <v>976</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>977</v>
-      </c>
       <c r="G4" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H4" s="22"/>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
+        <v>977</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>967</v>
+      </c>
+      <c r="C5" s="19" t="s">
         <v>978</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>968</v>
-      </c>
-      <c r="C5" s="19" t="s">
+      <c r="D5" s="19" t="s">
         <v>979</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="E5" s="19" t="s">
         <v>980</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="F5" s="19" t="s">
         <v>981</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>982</v>
-      </c>
       <c r="G5" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H5" s="22"/>
     </row>
     <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
+        <v>982</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>960</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>983</v>
       </c>
-      <c r="B6" s="19" t="s">
-        <v>961</v>
-      </c>
-      <c r="C6" s="19" t="s">
+      <c r="D6" s="19" t="s">
         <v>984</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="E6" s="19" t="s">
         <v>985</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="F6" s="19" t="s">
         <v>986</v>
       </c>
-      <c r="F6" s="19" t="s">
-        <v>987</v>
-      </c>
       <c r="G6" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H6" s="22"/>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
+        <v>987</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>988</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="C7" s="19" t="s">
         <v>989</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="D7" s="19" t="s">
         <v>990</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="E7" s="19" t="s">
         <v>991</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="F7" s="19" t="s">
         <v>992</v>
       </c>
-      <c r="F7" s="19" t="s">
-        <v>993</v>
-      </c>
       <c r="G7" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H7" s="22"/>
     </row>
     <row r="8" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
+        <v>993</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>988</v>
+      </c>
+      <c r="C8" s="19" t="s">
         <v>994</v>
       </c>
-      <c r="B8" s="19" t="s">
-        <v>989</v>
-      </c>
-      <c r="C8" s="19" t="s">
+      <c r="D8" s="19" t="s">
         <v>995</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="E8" s="19" t="s">
         <v>996</v>
       </c>
-      <c r="E8" s="19" t="s">
-        <v>997</v>
-      </c>
       <c r="F8" s="19" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G8" s="19"/>
       <c r="H8" s="22"/>
     </row>
     <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
+        <v>997</v>
+      </c>
+      <c r="B9" s="19" t="s">
         <v>998</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="C9" s="19" t="s">
         <v>999</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="D9" s="19" t="s">
         <v>1000</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="E9" s="19" t="s">
         <v>1001</v>
       </c>
-      <c r="E9" s="19" t="s">
-        <v>1002</v>
-      </c>
       <c r="F9" s="19" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H9" s="22"/>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>998</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>999</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E10" s="19" t="s">
         <v>1003</v>
       </c>
-      <c r="B10" s="19" t="s">
-        <v>999</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>1004</v>
-      </c>
       <c r="F10" s="19" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H10" s="22"/>
     </row>
     <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>998</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>999</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E11" s="19" t="s">
         <v>1005</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>999</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>1006</v>
-      </c>
       <c r="F11" s="19" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H11" s="22"/>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>998</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>999</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="19" t="s">
         <v>1007</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>999</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>1008</v>
-      </c>
       <c r="F12" s="19" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H12" s="22"/>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>998</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>1009</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>999</v>
-      </c>
-      <c r="C13" s="19" t="s">
+      <c r="D13" s="19" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E13" s="19" t="s">
         <v>1010</v>
       </c>
-      <c r="D13" s="19" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>1011</v>
-      </c>
       <c r="F13" s="19" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H13" s="22"/>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>998</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>1012</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>999</v>
-      </c>
-      <c r="C14" s="19" t="s">
+      <c r="D14" s="19" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E14" s="19" t="s">
         <v>1013</v>
       </c>
-      <c r="D14" s="19" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>1014</v>
-      </c>
       <c r="F14" s="19" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H14" s="22"/>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B15" s="19" t="s">
+        <v>998</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>1015</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>999</v>
-      </c>
-      <c r="C15" s="19" t="s">
+      <c r="D15" s="19" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="19" t="s">
         <v>1016</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>1017</v>
-      </c>
       <c r="F15" s="19" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H15" s="22"/>
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="27" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B16" s="19" t="s">
         <v>1018</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="C16" s="19" t="s">
         <v>1019</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="D16" s="19" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E16" s="19" t="s">
         <v>1020</v>
       </c>
-      <c r="D16" s="19" t="s">
-        <v>1001</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>1021</v>
-      </c>
       <c r="F16" s="19" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H16" s="22"/>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B17" s="19" t="s">
         <v>1022</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="C17" s="19" t="s">
         <v>1023</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="D17" s="19" t="s">
         <v>1024</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="E17" s="19" t="s">
         <v>1025</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="F17" s="19" t="s">
         <v>1026</v>
       </c>
-      <c r="F17" s="19" t="s">
-        <v>1027</v>
-      </c>
       <c r="G17" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H17" s="22"/>
     </row>
     <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>1028</v>
       </c>
-      <c r="B18" s="19" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C18" s="19" t="s">
+      <c r="D18" s="19" t="s">
         <v>1029</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="E18" s="19" t="s">
         <v>1030</v>
       </c>
-      <c r="E18" s="19" t="s">
-        <v>1031</v>
-      </c>
       <c r="F18" s="19" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H18" s="22"/>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C19" s="19" t="s">
         <v>1032</v>
       </c>
-      <c r="B19" s="19" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C19" s="19" t="s">
+      <c r="D19" s="19" t="s">
         <v>1033</v>
       </c>
-      <c r="D19" s="19" t="s">
+      <c r="E19" s="19" t="s">
         <v>1034</v>
       </c>
-      <c r="E19" s="19" t="s">
-        <v>1035</v>
-      </c>
       <c r="F19" s="19" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H19" s="22"/>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B20" s="19" t="s">
         <v>1036</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="C20" s="19" t="s">
         <v>1037</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="D20" s="19" t="s">
         <v>1038</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="E20" s="19" t="s">
         <v>1039</v>
       </c>
-      <c r="E20" s="19" t="s">
-        <v>1040</v>
-      </c>
       <c r="F20" s="19" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H20" s="22"/>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B21" s="19" t="s">
         <v>1041</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="C21" s="19" t="s">
         <v>1042</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="D21" s="19" t="s">
         <v>1043</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="E21" s="19" t="s">
         <v>1044</v>
       </c>
-      <c r="E21" s="19" t="s">
+      <c r="F21" s="19" t="s">
         <v>1045</v>
       </c>
-      <c r="F21" s="19" t="s">
-        <v>1046</v>
-      </c>
       <c r="G21" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H21" s="22"/>
     </row>
     <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C22" s="19" t="s">
         <v>1047</v>
       </c>
-      <c r="B22" s="19" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C22" s="19" t="s">
+      <c r="D22" s="19" t="s">
         <v>1048</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="E22" s="19" t="s">
         <v>1049</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="F22" s="19" t="s">
         <v>1050</v>
       </c>
-      <c r="F22" s="19" t="s">
-        <v>1051</v>
-      </c>
       <c r="G22" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C23" s="19" t="s">
         <v>1052</v>
       </c>
-      <c r="B23" s="19" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C23" s="19" t="s">
+      <c r="D23" s="19" t="s">
         <v>1053</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="E23" s="19" t="s">
         <v>1054</v>
       </c>
-      <c r="E23" s="19" t="s">
-        <v>1055</v>
-      </c>
       <c r="F23" s="19" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="27" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C24" s="19" t="s">
         <v>1056</v>
       </c>
-      <c r="B24" s="19" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C24" s="19" t="s">
+      <c r="D24" s="19" t="s">
+        <v>979</v>
+      </c>
+      <c r="E24" s="19" t="s">
         <v>1057</v>
       </c>
-      <c r="D24" s="19" t="s">
-        <v>980</v>
-      </c>
-      <c r="E24" s="19" t="s">
+      <c r="F24" s="19" t="s">
         <v>1058</v>
       </c>
-      <c r="F24" s="19" t="s">
-        <v>1059</v>
-      </c>
       <c r="G24" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H24" s="22"/>
     </row>
     <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="27" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C25" s="19" t="s">
         <v>1060</v>
       </c>
-      <c r="B25" s="19" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C25" s="19" t="s">
+      <c r="D25" s="19" t="s">
         <v>1061</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="E25" s="19" t="s">
         <v>1062</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="F25" s="19" t="s">
         <v>1063</v>
       </c>
-      <c r="F25" s="19" t="s">
-        <v>1064</v>
-      </c>
       <c r="G25" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H25" s="22"/>
     </row>
     <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="27" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B26" s="19" t="s">
         <v>1065</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="C26" s="19" t="s">
         <v>1066</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="D26" s="19" t="s">
         <v>1067</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="E26" s="19" t="s">
         <v>1068</v>
       </c>
-      <c r="E26" s="19" t="s">
-        <v>1069</v>
-      </c>
       <c r="F26" s="19" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H26" s="22"/>
     </row>
     <row r="27" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="27" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C27" s="19" t="s">
         <v>1070</v>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C27" s="19" t="s">
+      <c r="D27" s="19" t="s">
         <v>1071</v>
       </c>
-      <c r="D27" s="19" t="s">
+      <c r="E27" s="19" t="s">
         <v>1072</v>
       </c>
-      <c r="E27" s="19" t="s">
+      <c r="F27" s="19" t="s">
         <v>1073</v>
       </c>
-      <c r="F27" s="19" t="s">
-        <v>1074</v>
-      </c>
       <c r="G27" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H27" s="22"/>
     </row>
     <row r="28" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="27" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B28" s="19" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C28" s="19" t="s">
         <v>1075</v>
       </c>
-      <c r="B28" s="19" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C28" s="19" t="s">
+      <c r="D28" s="19" t="s">
         <v>1076</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="E28" s="19" t="s">
         <v>1077</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="F28" s="19" t="s">
         <v>1078</v>
       </c>
-      <c r="F28" s="19" t="s">
-        <v>1079</v>
-      </c>
       <c r="G28" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H28" s="22"/>
     </row>
     <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="27" t="s">
+        <v>1079</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C29" s="19" t="s">
         <v>1080</v>
       </c>
-      <c r="B29" s="19" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C29" s="19" t="s">
+      <c r="D29" s="19" t="s">
         <v>1081</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="E29" s="19" t="s">
         <v>1082</v>
       </c>
-      <c r="E29" s="19" t="s">
-        <v>1083</v>
-      </c>
       <c r="F29" s="19" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H29" s="22"/>
     </row>
     <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="27" t="s">
+        <v>1083</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>1084</v>
       </c>
-      <c r="B30" s="19" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C30" s="19" t="s">
+      <c r="D30" s="19" t="s">
         <v>1085</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="E30" s="19" t="s">
         <v>1086</v>
       </c>
-      <c r="E30" s="19" t="s">
+      <c r="F30" s="19" t="s">
         <v>1087</v>
       </c>
-      <c r="F30" s="19" t="s">
-        <v>1088</v>
-      </c>
       <c r="G30" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H30" s="22"/>
     </row>
     <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="27" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C31" s="19" t="s">
         <v>1089</v>
       </c>
-      <c r="B31" s="19" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C31" s="19" t="s">
+      <c r="D31" s="19" t="s">
         <v>1090</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="E31" s="19" t="s">
         <v>1091</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="F31" s="19" t="s">
         <v>1092</v>
       </c>
-      <c r="F31" s="19" t="s">
-        <v>1093</v>
-      </c>
       <c r="G31" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H31" s="22"/>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="27" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>967</v>
+      </c>
+      <c r="C32" s="19" t="s">
         <v>1094</v>
       </c>
-      <c r="B32" s="19" t="s">
-        <v>968</v>
-      </c>
-      <c r="C32" s="19" t="s">
+      <c r="D32" s="19" t="s">
         <v>1095</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="E32" s="19" t="s">
         <v>1096</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="F32" s="19" t="s">
         <v>1097</v>
       </c>
-      <c r="F32" s="19" t="s">
-        <v>1098</v>
-      </c>
       <c r="G32" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H32" s="22"/>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="27" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>967</v>
+      </c>
+      <c r="C33" s="19" t="s">
         <v>1099</v>
       </c>
-      <c r="B33" s="19" t="s">
-        <v>968</v>
-      </c>
-      <c r="C33" s="19" t="s">
+      <c r="D33" s="19" t="s">
         <v>1100</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="E33" s="19" t="s">
         <v>1101</v>
       </c>
-      <c r="E33" s="19" t="s">
-        <v>1102</v>
-      </c>
       <c r="F33" s="19" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H33" s="22"/>
     </row>
     <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="27" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>967</v>
+      </c>
+      <c r="C34" s="19" t="s">
         <v>1103</v>
       </c>
-      <c r="B34" s="19" t="s">
-        <v>968</v>
-      </c>
-      <c r="C34" s="19" t="s">
+      <c r="D34" s="19" t="s">
         <v>1104</v>
       </c>
-      <c r="D34" s="19" t="s">
+      <c r="E34" s="19" t="s">
         <v>1105</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="F34" s="19" t="s">
         <v>1106</v>
       </c>
-      <c r="F34" s="19" t="s">
-        <v>1107</v>
-      </c>
       <c r="G34" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H34" s="22"/>
     </row>
     <row r="35" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="27" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B35" s="19" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C35" s="19" t="s">
         <v>1108</v>
       </c>
-      <c r="B35" s="19" t="s">
-        <v>1066</v>
-      </c>
-      <c r="C35" s="19" t="s">
+      <c r="D35" s="19" t="s">
         <v>1109</v>
       </c>
-      <c r="D35" s="19" t="s">
+      <c r="E35" s="19" t="s">
         <v>1110</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="F35" s="19" t="s">
         <v>1111</v>
       </c>
-      <c r="F35" s="19" t="s">
-        <v>1112</v>
-      </c>
       <c r="G35" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H35" s="22"/>
     </row>
     <row r="36" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="27" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>960</v>
+      </c>
+      <c r="C36" s="19" t="s">
         <v>1113</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>961</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>1114</v>
       </c>
       <c r="D36" s="19" t="s">
         <v>65</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="F36" s="19" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H36" s="22"/>
     </row>
     <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="27" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B37" s="19" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C37" s="19" t="s">
         <v>1116</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C37" s="19" t="s">
-        <v>1117</v>
       </c>
       <c r="D37" s="19" t="s">
         <v>65</v>
       </c>
       <c r="E37" s="19" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F37" s="19" t="s">
         <v>1118</v>
       </c>
-      <c r="F37" s="19" t="s">
-        <v>1119</v>
-      </c>
       <c r="G37" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H37" s="22"/>
     </row>
     <row r="38" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="27" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B38" s="19" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C38" s="19" t="s">
         <v>1120</v>
       </c>
-      <c r="B38" s="19" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C38" s="19" t="s">
+      <c r="D38" s="19" t="s">
         <v>1121</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="E38" s="19" t="s">
         <v>1122</v>
       </c>
-      <c r="E38" s="19" t="s">
-        <v>1123</v>
-      </c>
       <c r="F38" s="19" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G38" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H38" s="22"/>
     </row>
     <row r="39" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="27" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C39" s="19" t="s">
         <v>1124</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C39" s="19" t="s">
-        <v>1125</v>
       </c>
       <c r="D39" s="19" t="s">
         <v>65</v>
       </c>
       <c r="E39" s="19" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F39" s="19" t="s">
         <v>1126</v>
       </c>
-      <c r="F39" s="19" t="s">
-        <v>1127</v>
-      </c>
       <c r="G39" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H39" s="22"/>
     </row>
     <row r="40" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="27" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C40" s="19" t="s">
         <v>1128</v>
       </c>
-      <c r="B40" s="19" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C40" s="19" t="s">
+      <c r="D40" s="19" t="s">
         <v>1129</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="E40" s="19" t="s">
         <v>1130</v>
       </c>
-      <c r="E40" s="19" t="s">
-        <v>1131</v>
-      </c>
       <c r="F40" s="19" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H40" s="22"/>
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="27" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B41" s="19" t="s">
         <v>1132</v>
       </c>
-      <c r="B41" s="19" t="s">
+      <c r="C41" s="19" t="s">
         <v>1133</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="D41" s="19" t="s">
         <v>1134</v>
       </c>
-      <c r="D41" s="19" t="s">
+      <c r="E41" s="19" t="s">
         <v>1135</v>
       </c>
-      <c r="E41" s="19" t="s">
+      <c r="F41" s="19" t="s">
         <v>1136</v>
       </c>
-      <c r="F41" s="19" t="s">
-        <v>1137</v>
-      </c>
       <c r="G41" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H41" s="22"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -17987,7 +17951,7 @@
     </row>
     <row r="45" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -17997,7 +17961,7 @@
     </row>
     <row r="46" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -18007,7 +17971,7 @@
     </row>
     <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="3" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -18017,7 +17981,7 @@
     </row>
     <row r="48" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="3" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -18027,7 +17991,7 @@
     </row>
     <row r="49" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="3" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -18121,40 +18085,40 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>1145</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="C1" s="15" t="s">
         <v>1146</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="D1" s="15" t="s">
         <v>1147</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="E1" s="15" t="s">
         <v>1148</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="F1" s="15" t="s">
         <v>1149</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="G1" s="15" t="s">
         <v>1150</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="H1" s="15" t="s">
         <v>1151</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="I1" s="15" t="s">
         <v>1152</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="J1" s="15" t="s">
         <v>1153</v>
       </c>
-      <c r="J1" s="15" t="s">
+      <c r="K1" s="15" t="s">
+        <v>957</v>
+      </c>
+      <c r="L1" s="15" t="s">
         <v>1154</v>
-      </c>
-      <c r="K1" s="15" t="s">
-        <v>958</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>1155</v>
       </c>
       <c r="M1" s="15" t="s">
         <v>8</v>
@@ -18165,2033 +18129,2033 @@
     </row>
     <row r="2" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="17" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>1156</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="C2" s="17" t="s">
         <v>1157</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="D2" s="18" t="s">
         <v>1158</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>1159</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="F2" s="17" t="s">
         <v>1160</v>
       </c>
-      <c r="F2" s="17" t="s">
+      <c r="G2" s="17" t="s">
         <v>1161</v>
       </c>
-      <c r="G2" s="17" t="s">
+      <c r="H2" s="17" t="s">
         <v>1162</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="I2" s="17" t="s">
         <v>1163</v>
       </c>
-      <c r="I2" s="17" t="s">
+      <c r="J2" s="17" t="s">
         <v>1164</v>
       </c>
-      <c r="J2" s="17" t="s">
-        <v>1165</v>
-      </c>
       <c r="K2" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L2" s="22"/>
       <c r="M2" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N2" s="21"/>
     </row>
     <row r="3" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="17" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B3" s="17" t="s">
         <v>1156</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="C3" s="17" t="s">
         <v>1157</v>
       </c>
-      <c r="C3" s="17" t="s">
-        <v>1158</v>
-      </c>
       <c r="D3" s="18" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E3" s="17" t="s">
         <v>1167</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="F3" s="17" t="s">
         <v>1168</v>
       </c>
-      <c r="F3" s="17" t="s">
+      <c r="G3" s="17" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H3" s="17" t="s">
         <v>1169</v>
       </c>
-      <c r="G3" s="17" t="s">
-        <v>1162</v>
-      </c>
-      <c r="H3" s="17" t="s">
+      <c r="I3" s="17" t="s">
         <v>1170</v>
       </c>
-      <c r="I3" s="17" t="s">
+      <c r="J3" s="17" t="s">
         <v>1171</v>
       </c>
-      <c r="J3" s="17" t="s">
-        <v>1172</v>
-      </c>
       <c r="K3" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L3" s="22"/>
       <c r="M3" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N3" s="21"/>
     </row>
     <row r="4" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>1156</v>
       </c>
-      <c r="B4" s="17" t="s">
-        <v>1157</v>
-      </c>
       <c r="C4" s="17" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D4" s="18" t="s">
         <v>1173</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="E4" s="17" t="s">
         <v>1174</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="F4" s="17" t="s">
         <v>1175</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="G4" s="17" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H4" s="17" t="s">
         <v>1176</v>
       </c>
-      <c r="G4" s="17" t="s">
-        <v>1162</v>
-      </c>
-      <c r="H4" s="17" t="s">
+      <c r="I4" s="17" t="s">
         <v>1177</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="J4" s="17" t="s">
         <v>1178</v>
       </c>
-      <c r="J4" s="17" t="s">
-        <v>1179</v>
-      </c>
       <c r="K4" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L4" s="22"/>
       <c r="M4" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N4" s="21"/>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="17" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B5" s="17" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C5" s="17" t="s">
         <v>1180</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="D5" s="18" t="s">
         <v>1181</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="E5" s="17" t="s">
         <v>1182</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="F5" s="17" t="s">
         <v>1183</v>
       </c>
-      <c r="F5" s="17" t="s">
+      <c r="G5" s="17" t="s">
         <v>1184</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="H5" s="17" t="s">
         <v>1185</v>
-      </c>
-      <c r="H5" s="17" t="s">
-        <v>1186</v>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="17" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="K5" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L5" s="22"/>
       <c r="M5" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N5" s="21"/>
     </row>
     <row r="6" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="17" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="B6" s="17" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C6" s="17" t="s">
         <v>1180</v>
       </c>
-      <c r="C6" s="17" t="s">
-        <v>1181</v>
-      </c>
       <c r="D6" s="18" t="s">
+        <v>1187</v>
+      </c>
+      <c r="E6" s="17" t="s">
         <v>1188</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="F6" s="17" t="s">
         <v>1189</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>1190</v>
       </c>
       <c r="G6" s="17"/>
       <c r="H6" s="17" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="K6" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L6" s="22"/>
       <c r="M6" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N6" s="21"/>
     </row>
     <row r="7" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D7" s="26" t="s">
         <v>1193</v>
       </c>
-      <c r="B7" s="25" t="s">
-        <v>1157</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>1158</v>
-      </c>
-      <c r="D7" s="26" t="s">
+      <c r="E7" s="25" t="s">
         <v>1194</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="F7" s="25" t="s">
         <v>1195</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="G7" s="25" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>979</v>
+      </c>
+      <c r="I7" s="25" t="s">
         <v>1196</v>
       </c>
-      <c r="G7" s="25" t="s">
-        <v>1162</v>
-      </c>
-      <c r="H7" s="25" t="s">
-        <v>980</v>
-      </c>
-      <c r="I7" s="25" t="s">
+      <c r="J7" s="25" t="s">
         <v>1197</v>
       </c>
-      <c r="J7" s="25" t="s">
-        <v>1198</v>
-      </c>
       <c r="K7" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L7" s="22"/>
       <c r="M7" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N7" s="21"/>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C8" s="25" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D8" s="26" t="s">
         <v>1199</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="E8" s="25" t="s">
         <v>1200</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="F8" s="25" t="s">
         <v>1201</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="G8" s="25" t="s">
         <v>1202</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="H8" s="25" t="s">
         <v>1203</v>
       </c>
-      <c r="H8" s="25" t="s">
+      <c r="I8" s="25" t="s">
         <v>1204</v>
       </c>
-      <c r="I8" s="25" t="s">
+      <c r="J8" s="25" t="s">
         <v>1205</v>
       </c>
-      <c r="J8" s="25" t="s">
-        <v>1206</v>
-      </c>
       <c r="K8" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L8" s="22"/>
       <c r="M8" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N8" s="21"/>
     </row>
     <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D9" s="26" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E9" s="25" t="s">
         <v>1207</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="F9" s="25" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H9" s="25" t="s">
+        <v>979</v>
+      </c>
+      <c r="I9" s="25" t="s">
         <v>1208</v>
       </c>
-      <c r="F9" s="25" t="s">
-        <v>1202</v>
-      </c>
-      <c r="G9" s="25" t="s">
-        <v>1162</v>
-      </c>
-      <c r="H9" s="25" t="s">
-        <v>980</v>
-      </c>
-      <c r="I9" s="25" t="s">
+      <c r="J9" s="25" t="s">
         <v>1209</v>
       </c>
-      <c r="J9" s="25" t="s">
-        <v>1210</v>
-      </c>
       <c r="K9" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L9" s="22"/>
       <c r="M9" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N9" s="21"/>
     </row>
     <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D10" s="26" t="s">
+        <v>1210</v>
+      </c>
+      <c r="E10" s="25" t="s">
         <v>1211</v>
       </c>
-      <c r="E10" s="25" t="s">
+      <c r="F10" s="25" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>1202</v>
+      </c>
+      <c r="H10" s="25" t="s">
         <v>1212</v>
       </c>
-      <c r="F10" s="25" t="s">
-        <v>1202</v>
-      </c>
-      <c r="G10" s="25" t="s">
-        <v>1203</v>
-      </c>
-      <c r="H10" s="25" t="s">
+      <c r="I10" s="25" t="s">
         <v>1213</v>
       </c>
-      <c r="I10" s="25" t="s">
+      <c r="J10" s="25" t="s">
         <v>1214</v>
       </c>
-      <c r="J10" s="25" t="s">
-        <v>1215</v>
-      </c>
       <c r="K10" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L10" s="22"/>
       <c r="M10" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N10" s="21"/>
     </row>
     <row r="11" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B11" s="25" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C11" s="25" t="s">
         <v>1157</v>
       </c>
-      <c r="C11" s="25" t="s">
-        <v>1158</v>
-      </c>
       <c r="D11" s="26" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E11" s="25" t="s">
         <v>1216</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="F11" s="25" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G11" s="25" t="s">
         <v>1217</v>
       </c>
-      <c r="F11" s="25" t="s">
-        <v>1161</v>
-      </c>
-      <c r="G11" s="25" t="s">
+      <c r="H11" s="25" t="s">
+        <v>1203</v>
+      </c>
+      <c r="I11" s="25" t="s">
         <v>1218</v>
       </c>
-      <c r="H11" s="25" t="s">
-        <v>1204</v>
-      </c>
-      <c r="I11" s="25" t="s">
+      <c r="J11" s="25" t="s">
         <v>1219</v>
       </c>
-      <c r="J11" s="25" t="s">
-        <v>1220</v>
-      </c>
       <c r="K11" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L11" s="22"/>
       <c r="M11" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N11" s="21"/>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B12" s="25" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C12" s="25" t="s">
         <v>1157</v>
       </c>
-      <c r="C12" s="25" t="s">
-        <v>1158</v>
-      </c>
       <c r="D12" s="26" t="s">
+        <v>1220</v>
+      </c>
+      <c r="E12" s="25" t="s">
         <v>1221</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="F12" s="25" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H12" s="25" t="s">
         <v>1222</v>
       </c>
-      <c r="F12" s="25" t="s">
-        <v>1161</v>
-      </c>
-      <c r="G12" s="25" t="s">
-        <v>1162</v>
-      </c>
-      <c r="H12" s="25" t="s">
+      <c r="I12" s="25" t="s">
         <v>1223</v>
       </c>
-      <c r="I12" s="25" t="s">
+      <c r="J12" s="25" t="s">
         <v>1224</v>
       </c>
-      <c r="J12" s="25" t="s">
-        <v>1225</v>
-      </c>
       <c r="K12" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L12" s="22"/>
       <c r="M12" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N12" s="21"/>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B13" s="25" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C13" s="25" t="s">
         <v>1157</v>
       </c>
-      <c r="C13" s="25" t="s">
-        <v>1158</v>
-      </c>
       <c r="D13" s="26" t="s">
+        <v>1225</v>
+      </c>
+      <c r="E13" s="25" t="s">
         <v>1226</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="F13" s="25" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H13" s="25" t="s">
         <v>1227</v>
       </c>
-      <c r="F13" s="25" t="s">
-        <v>1161</v>
-      </c>
-      <c r="G13" s="25" t="s">
-        <v>1162</v>
-      </c>
-      <c r="H13" s="25" t="s">
+      <c r="I13" s="25" t="s">
         <v>1228</v>
       </c>
-      <c r="I13" s="25" t="s">
+      <c r="J13" s="25" t="s">
         <v>1229</v>
       </c>
-      <c r="J13" s="25" t="s">
-        <v>1230</v>
-      </c>
       <c r="K13" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L13" s="22"/>
       <c r="M13" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N13" s="21"/>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B14" s="25" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C14" s="25" t="s">
         <v>1157</v>
       </c>
-      <c r="C14" s="25" t="s">
-        <v>1158</v>
-      </c>
       <c r="D14" s="26" t="s">
+        <v>1230</v>
+      </c>
+      <c r="E14" s="25" t="s">
         <v>1231</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="F14" s="25" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G14" s="25" t="s">
         <v>1232</v>
       </c>
-      <c r="F14" s="25" t="s">
-        <v>1161</v>
-      </c>
-      <c r="G14" s="25" t="s">
+      <c r="H14" s="25" t="s">
         <v>1233</v>
       </c>
-      <c r="H14" s="25" t="s">
+      <c r="I14" s="25" t="s">
         <v>1234</v>
       </c>
-      <c r="I14" s="25" t="s">
+      <c r="J14" s="25" t="s">
         <v>1235</v>
       </c>
-      <c r="J14" s="25" t="s">
-        <v>1236</v>
-      </c>
       <c r="K14" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L14" s="22"/>
       <c r="M14" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N14" s="21"/>
     </row>
     <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B15" s="25" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C15" s="25" t="s">
         <v>1157</v>
       </c>
-      <c r="C15" s="25" t="s">
-        <v>1158</v>
-      </c>
       <c r="D15" s="26" t="s">
+        <v>1236</v>
+      </c>
+      <c r="E15" s="25" t="s">
         <v>1237</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="F15" s="25" t="s">
         <v>1238</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="G15" s="25" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H15" s="25" t="s">
         <v>1239</v>
       </c>
-      <c r="G15" s="25" t="s">
-        <v>1162</v>
-      </c>
-      <c r="H15" s="25" t="s">
+      <c r="I15" s="25" t="s">
         <v>1240</v>
       </c>
-      <c r="I15" s="25" t="s">
+      <c r="J15" s="25" t="s">
         <v>1241</v>
       </c>
-      <c r="J15" s="25" t="s">
-        <v>1242</v>
-      </c>
       <c r="K15" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L15" s="22"/>
       <c r="M15" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N15" s="21"/>
     </row>
     <row r="16" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B16" s="25" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C16" s="25" t="s">
         <v>1157</v>
       </c>
-      <c r="C16" s="25" t="s">
-        <v>1158</v>
-      </c>
       <c r="D16" s="26" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E16" s="25" t="s">
         <v>1243</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="F16" s="25" t="s">
         <v>1244</v>
       </c>
-      <c r="F16" s="25" t="s">
+      <c r="G16" s="25" t="s">
         <v>1245</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="H16" s="25" t="s">
         <v>1246</v>
       </c>
-      <c r="H16" s="25" t="s">
+      <c r="I16" s="25" t="s">
         <v>1247</v>
       </c>
-      <c r="I16" s="25" t="s">
+      <c r="J16" s="25" t="s">
         <v>1248</v>
       </c>
-      <c r="J16" s="25" t="s">
-        <v>1249</v>
-      </c>
       <c r="K16" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L16" s="22"/>
       <c r="M16" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N16" s="21"/>
     </row>
     <row r="17" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B17" s="25" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C17" s="25" t="s">
         <v>1180</v>
       </c>
-      <c r="C17" s="25" t="s">
-        <v>1181</v>
-      </c>
       <c r="D17" s="26" t="s">
+        <v>1249</v>
+      </c>
+      <c r="E17" s="25" t="s">
         <v>1250</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="F17" s="25" t="s">
         <v>1251</v>
       </c>
-      <c r="F17" s="25" t="s">
+      <c r="G17" s="25" t="s">
         <v>1252</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="H17" s="25" t="s">
         <v>1253</v>
-      </c>
-      <c r="H17" s="25" t="s">
-        <v>1254</v>
       </c>
       <c r="I17" s="25"/>
       <c r="J17" s="25" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L17" s="22"/>
       <c r="M17" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N17" s="21"/>
     </row>
     <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B18" s="25" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C18" s="25" t="s">
         <v>1180</v>
       </c>
-      <c r="C18" s="25" t="s">
-        <v>1181</v>
-      </c>
       <c r="D18" s="26" t="s">
+        <v>1255</v>
+      </c>
+      <c r="E18" s="25" t="s">
         <v>1256</v>
       </c>
-      <c r="E18" s="25" t="s">
+      <c r="F18" s="25" t="s">
         <v>1257</v>
       </c>
-      <c r="F18" s="25" t="s">
+      <c r="G18" s="25" t="s">
         <v>1258</v>
       </c>
-      <c r="G18" s="25" t="s">
+      <c r="H18" s="25" t="s">
         <v>1259</v>
-      </c>
-      <c r="H18" s="25" t="s">
-        <v>1260</v>
       </c>
       <c r="I18" s="25"/>
       <c r="J18" s="25" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="K18" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L18" s="22"/>
       <c r="M18" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N18" s="21"/>
     </row>
     <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B19" s="25" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C19" s="25" t="s">
         <v>1180</v>
       </c>
-      <c r="C19" s="25" t="s">
-        <v>1181</v>
-      </c>
       <c r="D19" s="26" t="s">
+        <v>1261</v>
+      </c>
+      <c r="E19" s="25" t="s">
         <v>1262</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="F19" s="25" t="s">
         <v>1263</v>
       </c>
-      <c r="F19" s="25" t="s">
+      <c r="G19" s="25" t="s">
         <v>1264</v>
       </c>
-      <c r="G19" s="25" t="s">
+      <c r="H19" s="25" t="s">
         <v>1265</v>
       </c>
-      <c r="H19" s="25" t="s">
+      <c r="I19" s="25" t="s">
         <v>1266</v>
       </c>
-      <c r="I19" s="25" t="s">
+      <c r="J19" s="25" t="s">
         <v>1267</v>
       </c>
-      <c r="J19" s="25" t="s">
-        <v>1268</v>
-      </c>
       <c r="K19" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L19" s="22"/>
       <c r="M19" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N19" s="21"/>
     </row>
     <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B20" s="25" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C20" s="25" t="s">
         <v>1180</v>
       </c>
-      <c r="C20" s="25" t="s">
-        <v>1181</v>
-      </c>
       <c r="D20" s="26" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E20" s="25" t="s">
         <v>1269</v>
       </c>
-      <c r="E20" s="25" t="s">
+      <c r="F20" s="25" t="s">
         <v>1270</v>
       </c>
-      <c r="F20" s="25" t="s">
+      <c r="G20" s="25" t="s">
         <v>1271</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="H20" s="25" t="s">
+        <v>1265</v>
+      </c>
+      <c r="I20" s="25" t="s">
         <v>1272</v>
       </c>
-      <c r="H20" s="25" t="s">
-        <v>1266</v>
-      </c>
-      <c r="I20" s="25" t="s">
+      <c r="J20" s="25" t="s">
         <v>1273</v>
       </c>
-      <c r="J20" s="25" t="s">
-        <v>1274</v>
-      </c>
       <c r="K20" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L20" s="22"/>
       <c r="M20" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N20" s="21"/>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B21" s="25" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C21" s="25" t="s">
         <v>1180</v>
       </c>
-      <c r="C21" s="25" t="s">
-        <v>1181</v>
-      </c>
       <c r="D21" s="26" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E21" s="25" t="s">
         <v>1275</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="F21" s="25" t="s">
         <v>1276</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="G21" s="25" t="s">
         <v>1277</v>
-      </c>
-      <c r="G21" s="25" t="s">
-        <v>1278</v>
       </c>
       <c r="H21" s="25"/>
       <c r="I21" s="25"/>
       <c r="J21" s="25" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="K21" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L21" s="22"/>
       <c r="M21" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N21" s="21"/>
     </row>
     <row r="22" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B22" s="25" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C22" s="25" t="s">
         <v>1180</v>
       </c>
-      <c r="C22" s="25" t="s">
-        <v>1181</v>
-      </c>
       <c r="D22" s="26" t="s">
+        <v>1279</v>
+      </c>
+      <c r="E22" s="25" t="s">
         <v>1280</v>
-      </c>
-      <c r="E22" s="25" t="s">
-        <v>1281</v>
       </c>
       <c r="F22" s="25"/>
       <c r="G22" s="25" t="s">
+        <v>1281</v>
+      </c>
+      <c r="H22" s="25" t="s">
         <v>1282</v>
-      </c>
-      <c r="H22" s="25" t="s">
-        <v>1283</v>
       </c>
       <c r="I22" s="25"/>
       <c r="J22" s="25" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
       <c r="K22" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L22" s="22"/>
       <c r="M22" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B23" s="25" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C23" s="25" t="s">
         <v>1180</v>
       </c>
-      <c r="C23" s="25" t="s">
-        <v>1181</v>
-      </c>
       <c r="D23" s="26" t="s">
+        <v>1284</v>
+      </c>
+      <c r="E23" s="25" t="s">
         <v>1285</v>
       </c>
-      <c r="E23" s="25" t="s">
+      <c r="F23" s="25" t="s">
         <v>1286</v>
       </c>
-      <c r="F23" s="25" t="s">
+      <c r="G23" s="25" t="s">
         <v>1287</v>
       </c>
-      <c r="G23" s="25" t="s">
+      <c r="H23" s="25" t="s">
         <v>1288</v>
-      </c>
-      <c r="H23" s="25" t="s">
-        <v>1289</v>
       </c>
       <c r="I23" s="25"/>
       <c r="J23" s="25" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="K23" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L23" s="22"/>
       <c r="M23" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N23" s="21"/>
     </row>
     <row r="24" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B24" s="25" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C24" s="25" t="s">
         <v>1180</v>
       </c>
-      <c r="C24" s="25" t="s">
-        <v>1181</v>
-      </c>
       <c r="D24" s="26" t="s">
+        <v>1290</v>
+      </c>
+      <c r="E24" s="25" t="s">
         <v>1291</v>
       </c>
-      <c r="E24" s="25" t="s">
+      <c r="F24" s="25" t="s">
         <v>1292</v>
       </c>
-      <c r="F24" s="25" t="s">
+      <c r="G24" s="25" t="s">
         <v>1293</v>
       </c>
-      <c r="G24" s="25" t="s">
+      <c r="H24" s="25" t="s">
         <v>1294</v>
-      </c>
-      <c r="H24" s="25" t="s">
-        <v>1295</v>
       </c>
       <c r="I24" s="25"/>
       <c r="J24" s="25" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
       <c r="K24" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L24" s="22"/>
       <c r="M24" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N24" s="21"/>
     </row>
     <row r="25" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B25" s="25" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C25" s="25" t="s">
         <v>1180</v>
       </c>
-      <c r="C25" s="25" t="s">
-        <v>1181</v>
-      </c>
       <c r="D25" s="26" t="s">
+        <v>1296</v>
+      </c>
+      <c r="E25" s="25" t="s">
         <v>1297</v>
       </c>
-      <c r="E25" s="25" t="s">
+      <c r="F25" s="25" t="s">
+        <v>1292</v>
+      </c>
+      <c r="G25" s="25" t="s">
         <v>1298</v>
       </c>
-      <c r="F25" s="25" t="s">
-        <v>1293</v>
-      </c>
-      <c r="G25" s="25" t="s">
+      <c r="H25" s="25" t="s">
         <v>1299</v>
       </c>
-      <c r="H25" s="25" t="s">
+      <c r="I25" s="25" t="s">
         <v>1300</v>
       </c>
-      <c r="I25" s="25" t="s">
+      <c r="J25" s="25" t="s">
         <v>1301</v>
       </c>
-      <c r="J25" s="25" t="s">
-        <v>1302</v>
-      </c>
       <c r="K25" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L25" s="22"/>
       <c r="M25" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N25" s="21"/>
     </row>
     <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B26" s="25" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C26" s="25" t="s">
         <v>1180</v>
       </c>
-      <c r="C26" s="25" t="s">
-        <v>1181</v>
-      </c>
       <c r="D26" s="26" t="s">
+        <v>1302</v>
+      </c>
+      <c r="E26" s="25" t="s">
         <v>1303</v>
       </c>
-      <c r="E26" s="25" t="s">
+      <c r="F26" s="25" t="s">
         <v>1304</v>
       </c>
-      <c r="F26" s="25" t="s">
+      <c r="G26" s="25" t="s">
         <v>1305</v>
-      </c>
-      <c r="G26" s="25" t="s">
-        <v>1306</v>
       </c>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
       <c r="J26" s="25" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="K26" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L26" s="22"/>
       <c r="M26" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N26" s="21"/>
     </row>
     <row r="27" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B27" s="25" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C27" s="25" t="s">
         <v>1180</v>
       </c>
-      <c r="C27" s="25" t="s">
-        <v>1181</v>
-      </c>
       <c r="D27" s="26" t="s">
+        <v>1307</v>
+      </c>
+      <c r="E27" s="25" t="s">
         <v>1308</v>
       </c>
-      <c r="E27" s="25" t="s">
+      <c r="F27" s="25" t="s">
         <v>1309</v>
-      </c>
-      <c r="F27" s="25" t="s">
-        <v>1310</v>
       </c>
       <c r="G27" s="25"/>
       <c r="H27" s="25"/>
       <c r="I27" s="25"/>
       <c r="J27" s="25" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="K27" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L27" s="22"/>
       <c r="M27" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N27" s="21"/>
     </row>
     <row r="28" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B28" s="25" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C28" s="25" t="s">
         <v>1180</v>
       </c>
-      <c r="C28" s="25" t="s">
-        <v>1181</v>
-      </c>
       <c r="D28" s="26" t="s">
+        <v>1311</v>
+      </c>
+      <c r="E28" s="25" t="s">
         <v>1312</v>
       </c>
-      <c r="E28" s="25" t="s">
+      <c r="F28" s="25" t="s">
         <v>1313</v>
-      </c>
-      <c r="F28" s="25" t="s">
-        <v>1314</v>
       </c>
       <c r="G28" s="25"/>
       <c r="H28" s="25" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="I28" s="25" t="s">
+        <v>1314</v>
+      </c>
+      <c r="J28" s="25" t="s">
         <v>1315</v>
       </c>
-      <c r="J28" s="25" t="s">
-        <v>1316</v>
-      </c>
       <c r="K28" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L28" s="22"/>
       <c r="M28" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N28" s="21"/>
     </row>
     <row r="29" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B29" s="25" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C29" s="25" t="s">
         <v>1180</v>
       </c>
-      <c r="C29" s="25" t="s">
-        <v>1181</v>
-      </c>
       <c r="D29" s="26" t="s">
+        <v>1316</v>
+      </c>
+      <c r="E29" s="25" t="s">
         <v>1317</v>
-      </c>
-      <c r="E29" s="25" t="s">
-        <v>1318</v>
       </c>
       <c r="F29" s="25"/>
       <c r="G29" s="25"/>
       <c r="H29" s="25" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="I29" s="25" t="s">
+        <v>1318</v>
+      </c>
+      <c r="J29" s="25" t="s">
         <v>1319</v>
       </c>
-      <c r="J29" s="25" t="s">
-        <v>1320</v>
-      </c>
       <c r="K29" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L29" s="22"/>
       <c r="M29" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N29" s="21"/>
     </row>
     <row r="30" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="25" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B30" s="25" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C30" s="25" t="s">
         <v>1180</v>
       </c>
-      <c r="C30" s="25" t="s">
-        <v>1181</v>
-      </c>
       <c r="D30" s="26" t="s">
+        <v>1320</v>
+      </c>
+      <c r="E30" s="25" t="s">
         <v>1321</v>
       </c>
-      <c r="E30" s="25" t="s">
+      <c r="F30" s="25" t="s">
         <v>1322</v>
       </c>
-      <c r="F30" s="25" t="s">
+      <c r="G30" s="25" t="s">
         <v>1323</v>
       </c>
-      <c r="G30" s="25" t="s">
+      <c r="H30" s="25" t="s">
         <v>1324</v>
       </c>
-      <c r="H30" s="25" t="s">
+      <c r="I30" s="25" t="s">
         <v>1325</v>
       </c>
-      <c r="I30" s="25" t="s">
+      <c r="J30" s="25" t="s">
         <v>1326</v>
       </c>
-      <c r="J30" s="25" t="s">
-        <v>1327</v>
-      </c>
       <c r="K30" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L30" s="22"/>
       <c r="M30" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N30" s="21"/>
     </row>
     <row r="31" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B31" s="19" t="s">
         <v>1328</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="C31" s="19" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D31" s="27" t="s">
         <v>1329</v>
       </c>
-      <c r="C31" s="19" t="s">
-        <v>1158</v>
-      </c>
-      <c r="D31" s="27" t="s">
+      <c r="E31" s="19" t="s">
         <v>1330</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="F31" s="19" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G31" s="19" t="s">
         <v>1331</v>
       </c>
-      <c r="F31" s="19" t="s">
-        <v>1161</v>
-      </c>
-      <c r="G31" s="19" t="s">
+      <c r="H31" s="19" t="s">
         <v>1332</v>
       </c>
-      <c r="H31" s="19" t="s">
+      <c r="I31" s="19" t="s">
         <v>1333</v>
       </c>
-      <c r="I31" s="19" t="s">
+      <c r="J31" s="19" t="s">
         <v>1334</v>
       </c>
-      <c r="J31" s="19" t="s">
-        <v>1335</v>
-      </c>
       <c r="K31" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L31" s="22"/>
       <c r="M31" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N31" s="21"/>
     </row>
     <row r="32" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B32" s="19" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C32" s="19" t="s">
         <v>1157</v>
       </c>
-      <c r="C32" s="19" t="s">
-        <v>1158</v>
-      </c>
       <c r="D32" s="27" t="s">
+        <v>1335</v>
+      </c>
+      <c r="E32" s="19" t="s">
         <v>1336</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="F32" s="19" t="s">
         <v>1337</v>
       </c>
-      <c r="F32" s="19" t="s">
+      <c r="G32" s="19" t="s">
         <v>1338</v>
       </c>
-      <c r="G32" s="19" t="s">
+      <c r="H32" s="19" t="s">
         <v>1339</v>
       </c>
-      <c r="H32" s="19" t="s">
+      <c r="I32" s="19" t="s">
         <v>1340</v>
       </c>
-      <c r="I32" s="19" t="s">
+      <c r="J32" s="19" t="s">
         <v>1341</v>
       </c>
-      <c r="J32" s="19" t="s">
-        <v>1342</v>
-      </c>
       <c r="K32" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L32" s="22"/>
       <c r="M32" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N32" s="21"/>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D33" s="27" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E33" s="19" t="s">
         <v>1343</v>
       </c>
-      <c r="E33" s="19" t="s">
+      <c r="F33" s="19" t="s">
         <v>1344</v>
       </c>
-      <c r="F33" s="19" t="s">
+      <c r="G33" s="19" t="s">
         <v>1345</v>
       </c>
-      <c r="G33" s="19" t="s">
+      <c r="H33" s="19" t="s">
         <v>1346</v>
       </c>
-      <c r="H33" s="19" t="s">
+      <c r="I33" s="19" t="s">
         <v>1347</v>
       </c>
-      <c r="I33" s="19" t="s">
+      <c r="J33" s="19" t="s">
         <v>1348</v>
       </c>
-      <c r="J33" s="19" t="s">
-        <v>1349</v>
-      </c>
       <c r="K33" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L33" s="22"/>
       <c r="M33" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N33" s="21"/>
     </row>
     <row r="34" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B34" s="19" t="s">
         <v>1328</v>
       </c>
-      <c r="B34" s="19" t="s">
-        <v>1329</v>
-      </c>
       <c r="C34" s="19" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D34" s="27" t="s">
+        <v>1349</v>
+      </c>
+      <c r="E34" s="19" t="s">
         <v>1350</v>
       </c>
-      <c r="E34" s="19" t="s">
+      <c r="F34" s="19" t="s">
         <v>1351</v>
       </c>
-      <c r="F34" s="19" t="s">
+      <c r="G34" s="19" t="s">
         <v>1352</v>
       </c>
-      <c r="G34" s="19" t="s">
+      <c r="H34" s="19" t="s">
         <v>1353</v>
       </c>
-      <c r="H34" s="19" t="s">
+      <c r="I34" s="19" t="s">
         <v>1354</v>
       </c>
-      <c r="I34" s="19" t="s">
+      <c r="J34" s="19" t="s">
         <v>1355</v>
       </c>
-      <c r="J34" s="19" t="s">
-        <v>1356</v>
-      </c>
       <c r="K34" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L34" s="22"/>
       <c r="M34" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N34" s="21"/>
     </row>
     <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B35" s="19" t="s">
         <v>1328</v>
       </c>
-      <c r="B35" s="19" t="s">
-        <v>1329</v>
-      </c>
       <c r="C35" s="19" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D35" s="27" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E35" s="19" t="s">
         <v>1357</v>
       </c>
-      <c r="E35" s="19" t="s">
+      <c r="F35" s="19" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G35" s="19" t="s">
         <v>1358</v>
       </c>
-      <c r="F35" s="19" t="s">
-        <v>1190</v>
-      </c>
-      <c r="G35" s="19" t="s">
+      <c r="H35" s="19" t="s">
         <v>1359</v>
       </c>
-      <c r="H35" s="19" t="s">
+      <c r="I35" s="19" t="s">
         <v>1360</v>
       </c>
-      <c r="I35" s="19" t="s">
+      <c r="J35" s="19" t="s">
         <v>1361</v>
       </c>
-      <c r="J35" s="19" t="s">
-        <v>1362</v>
-      </c>
       <c r="K35" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L35" s="22"/>
       <c r="M35" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N35" s="21"/>
     </row>
     <row r="36" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B36" s="19" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C36" s="19" t="s">
+        <v>1362</v>
+      </c>
+      <c r="D36" s="27" t="s">
         <v>1363</v>
       </c>
-      <c r="D36" s="27" t="s">
+      <c r="E36" s="19" t="s">
         <v>1364</v>
       </c>
-      <c r="E36" s="19" t="s">
+      <c r="F36" s="19" t="s">
         <v>1365</v>
       </c>
-      <c r="F36" s="19" t="s">
+      <c r="G36" s="19" t="s">
         <v>1366</v>
       </c>
-      <c r="G36" s="19" t="s">
+      <c r="H36" s="19" t="s">
+        <v>979</v>
+      </c>
+      <c r="I36" s="19" t="s">
         <v>1367</v>
       </c>
-      <c r="H36" s="19" t="s">
-        <v>980</v>
-      </c>
-      <c r="I36" s="19" t="s">
+      <c r="J36" s="19" t="s">
         <v>1368</v>
       </c>
-      <c r="J36" s="19" t="s">
-        <v>1369</v>
-      </c>
       <c r="K36" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L36" s="22"/>
       <c r="M36" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N36" s="21"/>
     </row>
     <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B37" s="19" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
       <c r="D37" s="27" t="s">
+        <v>1369</v>
+      </c>
+      <c r="E37" s="19" t="s">
         <v>1370</v>
       </c>
-      <c r="E37" s="19" t="s">
+      <c r="F37" s="19" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G37" s="19" t="s">
+        <v>1161</v>
+      </c>
+      <c r="H37" s="19" t="s">
         <v>1371</v>
       </c>
-      <c r="F37" s="19" t="s">
-        <v>1161</v>
-      </c>
-      <c r="G37" s="19" t="s">
-        <v>1162</v>
-      </c>
-      <c r="H37" s="19" t="s">
+      <c r="I37" s="19" t="s">
         <v>1372</v>
       </c>
-      <c r="I37" s="19" t="s">
+      <c r="J37" s="19" t="s">
         <v>1373</v>
       </c>
-      <c r="J37" s="19" t="s">
-        <v>1374</v>
-      </c>
       <c r="K37" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L37" s="22"/>
       <c r="M37" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N37" s="21"/>
     </row>
     <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B38" s="19" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C38" s="19" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D38" s="27" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E38" s="19" t="s">
         <v>1375</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="F38" s="19" t="s">
         <v>1376</v>
       </c>
-      <c r="F38" s="19" t="s">
+      <c r="G38" s="19" t="s">
         <v>1377</v>
       </c>
-      <c r="G38" s="19" t="s">
+      <c r="H38" s="19" t="s">
         <v>1378</v>
       </c>
-      <c r="H38" s="19" t="s">
+      <c r="I38" s="19" t="s">
         <v>1379</v>
       </c>
-      <c r="I38" s="19" t="s">
+      <c r="J38" s="19" t="s">
         <v>1380</v>
       </c>
-      <c r="J38" s="19" t="s">
-        <v>1381</v>
-      </c>
       <c r="K38" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L38" s="22"/>
       <c r="M38" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N38" s="21"/>
     </row>
     <row r="39" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B39" s="19" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="D39" s="27" t="s">
+        <v>1381</v>
+      </c>
+      <c r="E39" s="19" t="s">
         <v>1382</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="F39" s="19" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G39" s="19" t="s">
+        <v>1202</v>
+      </c>
+      <c r="H39" s="19" t="s">
         <v>1383</v>
       </c>
-      <c r="F39" s="19" t="s">
-        <v>1202</v>
-      </c>
-      <c r="G39" s="19" t="s">
-        <v>1203</v>
-      </c>
-      <c r="H39" s="19" t="s">
+      <c r="I39" s="19" t="s">
         <v>1384</v>
       </c>
-      <c r="I39" s="19" t="s">
+      <c r="J39" s="19" t="s">
         <v>1385</v>
       </c>
-      <c r="J39" s="19" t="s">
-        <v>1386</v>
-      </c>
       <c r="K39" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L39" s="22"/>
       <c r="M39" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N39" s="21"/>
     </row>
     <row r="40" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B40" s="19" t="s">
+        <v>1156</v>
+      </c>
+      <c r="C40" s="19" t="s">
         <v>1157</v>
       </c>
-      <c r="C40" s="19" t="s">
-        <v>1158</v>
-      </c>
       <c r="D40" s="27" t="s">
+        <v>1386</v>
+      </c>
+      <c r="E40" s="19" t="s">
         <v>1387</v>
       </c>
-      <c r="E40" s="19" t="s">
+      <c r="F40" s="19" t="s">
         <v>1388</v>
       </c>
-      <c r="F40" s="19" t="s">
+      <c r="G40" s="19" t="s">
         <v>1389</v>
       </c>
-      <c r="G40" s="19" t="s">
+      <c r="H40" s="19" t="s">
+        <v>1371</v>
+      </c>
+      <c r="I40" s="19" t="s">
         <v>1390</v>
       </c>
-      <c r="H40" s="19" t="s">
-        <v>1372</v>
-      </c>
-      <c r="I40" s="19" t="s">
+      <c r="J40" s="19" t="s">
         <v>1391</v>
       </c>
-      <c r="J40" s="19" t="s">
-        <v>1392</v>
-      </c>
       <c r="K40" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L40" s="22"/>
       <c r="M40" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N40" s="21"/>
     </row>
     <row r="41" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B41" s="19" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C41" s="19" t="s">
         <v>1180</v>
       </c>
-      <c r="C41" s="19" t="s">
-        <v>1181</v>
-      </c>
       <c r="D41" s="27" t="s">
+        <v>1392</v>
+      </c>
+      <c r="E41" s="19" t="s">
         <v>1393</v>
-      </c>
-      <c r="E41" s="19" t="s">
-        <v>1394</v>
       </c>
       <c r="F41" s="19"/>
       <c r="G41" s="19" t="s">
+        <v>1394</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>979</v>
+      </c>
+      <c r="I41" s="19" t="s">
         <v>1395</v>
       </c>
-      <c r="H41" s="19" t="s">
-        <v>980</v>
-      </c>
-      <c r="I41" s="19" t="s">
+      <c r="J41" s="19" t="s">
         <v>1396</v>
       </c>
-      <c r="J41" s="19" t="s">
-        <v>1397</v>
-      </c>
       <c r="K41" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L41" s="22"/>
       <c r="M41" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N41" s="21"/>
     </row>
     <row r="42" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B42" s="19" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C42" s="19" t="s">
         <v>1180</v>
       </c>
-      <c r="C42" s="19" t="s">
-        <v>1181</v>
-      </c>
       <c r="D42" s="27" t="s">
+        <v>1397</v>
+      </c>
+      <c r="E42" s="19" t="s">
         <v>1398</v>
       </c>
-      <c r="E42" s="19" t="s">
+      <c r="F42" s="19" t="s">
         <v>1399</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>1400</v>
       </c>
       <c r="G42" s="19"/>
       <c r="H42" s="19" t="s">
+        <v>1400</v>
+      </c>
+      <c r="I42" s="19" t="s">
         <v>1401</v>
       </c>
-      <c r="I42" s="19" t="s">
+      <c r="J42" s="19" t="s">
         <v>1402</v>
       </c>
-      <c r="J42" s="19" t="s">
-        <v>1403</v>
-      </c>
       <c r="K42" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L42" s="22"/>
       <c r="M42" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N42" s="21"/>
     </row>
     <row r="43" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B43" s="19" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C43" s="19" t="s">
         <v>1180</v>
       </c>
-      <c r="C43" s="19" t="s">
-        <v>1181</v>
-      </c>
       <c r="D43" s="27" t="s">
+        <v>1403</v>
+      </c>
+      <c r="E43" s="19" t="s">
         <v>1404</v>
-      </c>
-      <c r="E43" s="19" t="s">
-        <v>1405</v>
       </c>
       <c r="F43" s="19"/>
       <c r="G43" s="19" t="s">
+        <v>1405</v>
+      </c>
+      <c r="H43" s="19" t="s">
+        <v>1353</v>
+      </c>
+      <c r="I43" s="19" t="s">
         <v>1406</v>
       </c>
-      <c r="H43" s="19" t="s">
-        <v>1354</v>
-      </c>
-      <c r="I43" s="19" t="s">
+      <c r="J43" s="19" t="s">
         <v>1407</v>
       </c>
-      <c r="J43" s="19" t="s">
-        <v>1408</v>
-      </c>
       <c r="K43" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L43" s="22"/>
       <c r="M43" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N43" s="21"/>
     </row>
     <row r="44" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B44" s="19" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C44" s="19" t="s">
         <v>1180</v>
       </c>
-      <c r="C44" s="19" t="s">
-        <v>1181</v>
-      </c>
       <c r="D44" s="27" t="s">
+        <v>1408</v>
+      </c>
+      <c r="E44" s="19" t="s">
         <v>1409</v>
       </c>
-      <c r="E44" s="19" t="s">
+      <c r="F44" s="19" t="s">
         <v>1410</v>
       </c>
-      <c r="F44" s="19" t="s">
+      <c r="G44" s="19" t="s">
         <v>1411</v>
       </c>
-      <c r="G44" s="19" t="s">
+      <c r="H44" s="19" t="s">
         <v>1412</v>
       </c>
-      <c r="H44" s="19" t="s">
+      <c r="I44" s="19" t="s">
         <v>1413</v>
       </c>
-      <c r="I44" s="19" t="s">
+      <c r="J44" s="19" t="s">
         <v>1414</v>
       </c>
-      <c r="J44" s="19" t="s">
-        <v>1415</v>
-      </c>
       <c r="K44" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L44" s="22"/>
       <c r="M44" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N44" s="21"/>
     </row>
     <row r="45" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B45" s="19" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C45" s="19" t="s">
         <v>1180</v>
       </c>
-      <c r="C45" s="19" t="s">
-        <v>1181</v>
-      </c>
       <c r="D45" s="27" t="s">
+        <v>1415</v>
+      </c>
+      <c r="E45" s="19" t="s">
         <v>1416</v>
-      </c>
-      <c r="E45" s="19" t="s">
-        <v>1417</v>
       </c>
       <c r="F45" s="19"/>
       <c r="G45" s="19" t="s">
+        <v>1417</v>
+      </c>
+      <c r="H45" s="19" t="s">
         <v>1418</v>
       </c>
-      <c r="H45" s="19" t="s">
+      <c r="I45" s="19" t="s">
         <v>1419</v>
       </c>
-      <c r="I45" s="19" t="s">
+      <c r="J45" s="19" t="s">
         <v>1420</v>
       </c>
-      <c r="J45" s="19" t="s">
-        <v>1421</v>
-      </c>
       <c r="K45" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L45" s="22"/>
       <c r="M45" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N45" s="21"/>
     </row>
     <row r="46" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B46" s="19" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C46" s="19" t="s">
         <v>1180</v>
       </c>
-      <c r="C46" s="19" t="s">
-        <v>1181</v>
-      </c>
       <c r="D46" s="27" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E46" s="19" t="s">
         <v>1422</v>
       </c>
-      <c r="E46" s="19" t="s">
+      <c r="F46" s="19" t="s">
         <v>1423</v>
       </c>
-      <c r="F46" s="19" t="s">
+      <c r="G46" s="19" t="s">
         <v>1424</v>
       </c>
-      <c r="G46" s="19" t="s">
+      <c r="H46" s="19" t="s">
         <v>1425</v>
       </c>
-      <c r="H46" s="19" t="s">
+      <c r="I46" s="19" t="s">
         <v>1426</v>
       </c>
-      <c r="I46" s="19" t="s">
+      <c r="J46" s="19" t="s">
         <v>1427</v>
       </c>
-      <c r="J46" s="19" t="s">
-        <v>1428</v>
-      </c>
       <c r="K46" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L46" s="22"/>
       <c r="M46" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N46" s="21"/>
     </row>
     <row r="47" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B47" s="19" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C47" s="19" t="s">
         <v>1180</v>
       </c>
-      <c r="C47" s="19" t="s">
-        <v>1181</v>
-      </c>
       <c r="D47" s="27" t="s">
+        <v>1428</v>
+      </c>
+      <c r="E47" s="19" t="s">
         <v>1429</v>
       </c>
-      <c r="E47" s="19" t="s">
+      <c r="F47" s="19" t="s">
+        <v>1168</v>
+      </c>
+      <c r="G47" s="19" t="s">
         <v>1430</v>
       </c>
-      <c r="F47" s="19" t="s">
-        <v>1169</v>
-      </c>
-      <c r="G47" s="19" t="s">
+      <c r="H47" s="19" t="s">
+        <v>1425</v>
+      </c>
+      <c r="I47" s="19" t="s">
         <v>1431</v>
       </c>
-      <c r="H47" s="19" t="s">
-        <v>1426</v>
-      </c>
-      <c r="I47" s="19" t="s">
+      <c r="J47" s="19" t="s">
         <v>1432</v>
       </c>
-      <c r="J47" s="19" t="s">
-        <v>1433</v>
-      </c>
       <c r="K47" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L47" s="22"/>
       <c r="M47" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N47" s="21"/>
     </row>
     <row r="48" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B48" s="19" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C48" s="19" t="s">
         <v>1180</v>
       </c>
-      <c r="C48" s="19" t="s">
-        <v>1181</v>
-      </c>
       <c r="D48" s="27" t="s">
+        <v>1433</v>
+      </c>
+      <c r="E48" s="19" t="s">
         <v>1434</v>
       </c>
-      <c r="E48" s="19" t="s">
+      <c r="F48" s="19" t="s">
         <v>1435</v>
       </c>
-      <c r="F48" s="19" t="s">
+      <c r="G48" s="19" t="s">
         <v>1436</v>
       </c>
-      <c r="G48" s="19" t="s">
+      <c r="H48" s="19" t="s">
         <v>1437</v>
       </c>
-      <c r="H48" s="19" t="s">
+      <c r="I48" s="19" t="s">
+        <v>1419</v>
+      </c>
+      <c r="J48" s="19" t="s">
         <v>1438</v>
       </c>
-      <c r="I48" s="19" t="s">
-        <v>1420</v>
-      </c>
-      <c r="J48" s="19" t="s">
-        <v>1439</v>
-      </c>
       <c r="K48" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L48" s="22"/>
       <c r="M48" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N48" s="21"/>
     </row>
     <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B49" s="19" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C49" s="19" t="s">
         <v>1180</v>
       </c>
-      <c r="C49" s="19" t="s">
-        <v>1181</v>
-      </c>
       <c r="D49" s="27" t="s">
+        <v>1439</v>
+      </c>
+      <c r="E49" s="19" t="s">
         <v>1440</v>
       </c>
-      <c r="E49" s="19" t="s">
+      <c r="F49" s="19" t="s">
         <v>1441</v>
       </c>
-      <c r="F49" s="19" t="s">
+      <c r="G49" s="19" t="s">
         <v>1442</v>
       </c>
-      <c r="G49" s="19" t="s">
+      <c r="H49" s="19" t="s">
         <v>1443</v>
       </c>
-      <c r="H49" s="19" t="s">
+      <c r="I49" s="19" t="s">
         <v>1444</v>
       </c>
-      <c r="I49" s="19" t="s">
+      <c r="J49" s="19" t="s">
         <v>1445</v>
       </c>
-      <c r="J49" s="19" t="s">
-        <v>1446</v>
-      </c>
       <c r="K49" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L49" s="22"/>
       <c r="M49" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N49" s="21"/>
     </row>
     <row r="50" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B50" s="19" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C50" s="19" t="s">
         <v>1180</v>
       </c>
-      <c r="C50" s="19" t="s">
-        <v>1181</v>
-      </c>
       <c r="D50" s="27" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E50" s="19" t="s">
         <v>1447</v>
       </c>
-      <c r="E50" s="19" t="s">
+      <c r="F50" s="19" t="s">
         <v>1448</v>
       </c>
-      <c r="F50" s="19" t="s">
+      <c r="G50" s="19" t="s">
         <v>1449</v>
       </c>
-      <c r="G50" s="19" t="s">
+      <c r="H50" s="19" t="s">
         <v>1450</v>
       </c>
-      <c r="H50" s="19" t="s">
+      <c r="I50" s="19" t="s">
         <v>1451</v>
       </c>
-      <c r="I50" s="19" t="s">
+      <c r="J50" s="19" t="s">
         <v>1452</v>
       </c>
-      <c r="J50" s="19" t="s">
-        <v>1453</v>
-      </c>
       <c r="K50" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L50" s="22"/>
       <c r="M50" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N50" s="21"/>
     </row>
     <row r="51" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B51" s="19" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C51" s="19" t="s">
         <v>1180</v>
       </c>
-      <c r="C51" s="19" t="s">
-        <v>1181</v>
-      </c>
       <c r="D51" s="27" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E51" s="19" t="s">
         <v>1454</v>
       </c>
-      <c r="E51" s="19" t="s">
+      <c r="F51" s="19" t="s">
         <v>1455</v>
       </c>
-      <c r="F51" s="19" t="s">
+      <c r="G51" s="19" t="s">
         <v>1456</v>
-      </c>
-      <c r="G51" s="19" t="s">
-        <v>1457</v>
       </c>
       <c r="H51" s="19"/>
       <c r="I51" s="19" t="s">
+        <v>1457</v>
+      </c>
+      <c r="J51" s="19" t="s">
         <v>1458</v>
       </c>
-      <c r="J51" s="19" t="s">
-        <v>1459</v>
-      </c>
       <c r="K51" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L51" s="22"/>
       <c r="M51" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N51" s="21"/>
     </row>
     <row r="52" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B52" s="19" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C52" s="19" t="s">
         <v>1180</v>
       </c>
-      <c r="C52" s="19" t="s">
-        <v>1181</v>
-      </c>
       <c r="D52" s="27" t="s">
+        <v>1459</v>
+      </c>
+      <c r="E52" s="19" t="s">
         <v>1460</v>
-      </c>
-      <c r="E52" s="19" t="s">
-        <v>1461</v>
       </c>
       <c r="F52" s="19"/>
       <c r="G52" s="19" t="s">
+        <v>1461</v>
+      </c>
+      <c r="H52" s="19" t="s">
         <v>1462</v>
       </c>
-      <c r="H52" s="19" t="s">
+      <c r="I52" s="19" t="s">
         <v>1463</v>
       </c>
-      <c r="I52" s="19" t="s">
+      <c r="J52" s="19" t="s">
         <v>1464</v>
       </c>
-      <c r="J52" s="19" t="s">
-        <v>1465</v>
-      </c>
       <c r="K52" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L52" s="22"/>
       <c r="M52" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N52" s="21"/>
     </row>
     <row r="53" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="19" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B53" s="19" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C53" s="19" t="s">
         <v>1180</v>
       </c>
-      <c r="C53" s="19" t="s">
-        <v>1181</v>
-      </c>
       <c r="D53" s="27" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E53" s="19" t="s">
         <v>1466</v>
-      </c>
-      <c r="E53" s="19" t="s">
-        <v>1467</v>
       </c>
       <c r="F53" s="19"/>
       <c r="G53" s="19" t="s">
+        <v>1467</v>
+      </c>
+      <c r="H53" s="19" t="s">
         <v>1468</v>
-      </c>
-      <c r="H53" s="19" t="s">
-        <v>1469</v>
       </c>
       <c r="I53" s="19"/>
       <c r="J53" s="19" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="K53" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="L53" s="22"/>
       <c r="M53" s="21" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N53" s="21"/>
     </row>
     <row r="55" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -20205,7 +20169,7 @@
     </row>
     <row r="56" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -20219,7 +20183,7 @@
     </row>
     <row r="57" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="3" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -20233,7 +20197,7 @@
     </row>
     <row r="58" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -20247,7 +20211,7 @@
     </row>
     <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="3" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -20359,108 +20323,108 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>40</v>
       </c>
       <c r="C1" s="15" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="D1" s="15" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="G1" s="15" t="s">
         <v>44</v>
       </c>
       <c r="H1" s="15" t="s">
+        <v>1477</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>1478</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="J1" s="15" t="s">
         <v>1479</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>1480</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="68.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>979</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>1481</v>
       </c>
-      <c r="B2" s="19" t="s">
-        <v>980</v>
-      </c>
-      <c r="C2" s="19" t="s">
+      <c r="D2" s="19" t="s">
         <v>1482</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="E2" s="19" t="s">
         <v>1483</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>1484</v>
       </c>
       <c r="F2" s="19"/>
       <c r="G2" s="29" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H2" s="22" t="s">
         <v>151</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="J2" s="22"/>
     </row>
     <row r="3" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="27" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>979</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>1487</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>980</v>
-      </c>
-      <c r="C3" s="19" t="s">
+      <c r="D3" s="19" t="s">
         <v>1488</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="E3" s="19" t="s">
         <v>1489</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>1490</v>
       </c>
       <c r="F3" s="19"/>
       <c r="G3" s="29" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="H3" s="22"/>
       <c r="I3" s="21"/>
       <c r="J3" s="22" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="27" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B4" s="19" t="s">
         <v>1492</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="C4" s="19" t="s">
         <v>1493</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="D4" s="19" t="s">
         <v>1494</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="E4" s="19" t="s">
         <v>1495</v>
       </c>
-      <c r="E4" s="19" t="s">
-        <v>1496</v>
-      </c>
       <c r="F4" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>53</v>
@@ -20471,19 +20435,19 @@
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>1497</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="C5" s="19" t="s">
         <v>1498</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="D5" s="19" t="s">
         <v>1499</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="E5" s="19" t="s">
         <v>1500</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>1501</v>
       </c>
       <c r="F5" s="19"/>
       <c r="G5" s="20" t="s">
@@ -20495,22 +20459,22 @@
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B6" s="19" t="s">
         <v>1502</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="C6" s="19" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D6" s="19" t="s">
         <v>1503</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>1494</v>
-      </c>
-      <c r="D6" s="19" t="s">
+      <c r="E6" s="19" t="s">
         <v>1504</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>1505</v>
-      </c>
       <c r="F6" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>53</v>
@@ -20521,22 +20485,22 @@
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>1506</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>1507</v>
-      </c>
       <c r="C7" s="19" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D7" s="19" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E7" s="19" t="s">
         <v>1504</v>
       </c>
-      <c r="E7" s="19" t="s">
-        <v>1505</v>
-      </c>
       <c r="F7" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>53</v>
@@ -20547,22 +20511,22 @@
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B8" s="19" t="s">
         <v>1508</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="C8" s="19" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D8" s="19" t="s">
         <v>1509</v>
       </c>
-      <c r="C8" s="19" t="s">
-        <v>1494</v>
-      </c>
-      <c r="D8" s="19" t="s">
+      <c r="E8" s="19" t="s">
         <v>1510</v>
       </c>
-      <c r="E8" s="19" t="s">
-        <v>1511</v>
-      </c>
       <c r="F8" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G8" s="20" t="s">
         <v>53</v>
@@ -20573,22 +20537,22 @@
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B9" s="19" t="s">
         <v>1512</v>
       </c>
-      <c r="B9" s="19" t="s">
-        <v>1513</v>
-      </c>
       <c r="C9" s="19" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D9" s="19" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E9" s="19" t="s">
         <v>1504</v>
       </c>
-      <c r="E9" s="19" t="s">
-        <v>1505</v>
-      </c>
       <c r="F9" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>53</v>
@@ -20599,22 +20563,22 @@
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B10" s="19" t="s">
         <v>1514</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="C10" s="19" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E10" s="19" t="s">
         <v>1515</v>
       </c>
-      <c r="C10" s="19" t="s">
-        <v>1494</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>1504</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>1516</v>
-      </c>
       <c r="F10" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>53</v>
@@ -20625,22 +20589,22 @@
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B11" s="19" t="s">
         <v>1517</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>1518</v>
-      </c>
       <c r="C11" s="19" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D11" s="19" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E11" s="19" t="s">
         <v>1504</v>
       </c>
-      <c r="E11" s="19" t="s">
-        <v>1505</v>
-      </c>
       <c r="F11" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>53</v>
@@ -20651,22 +20615,22 @@
     </row>
     <row r="12" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B12" s="19" t="s">
         <v>1519</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="C12" s="19" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E12" s="19" t="s">
         <v>1520</v>
       </c>
-      <c r="C12" s="19" t="s">
-        <v>1494</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>1504</v>
-      </c>
-      <c r="E12" s="19" t="s">
-        <v>1521</v>
-      </c>
       <c r="F12" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>53</v>
@@ -20677,22 +20641,22 @@
     </row>
     <row r="13" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B13" s="19" t="s">
         <v>1522</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="C13" s="19" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E13" s="19" t="s">
         <v>1523</v>
       </c>
-      <c r="C13" s="19" t="s">
-        <v>1494</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>1504</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>1524</v>
-      </c>
       <c r="F13" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>53</v>
@@ -20703,22 +20667,22 @@
     </row>
     <row r="14" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B14" s="19" t="s">
         <v>1525</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>1526</v>
-      </c>
       <c r="C14" s="19" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="F14" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>53</v>
@@ -20729,22 +20693,22 @@
     </row>
     <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B15" s="19" t="s">
         <v>1527</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>1528</v>
-      </c>
       <c r="C15" s="19" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>53</v>
@@ -20755,22 +20719,22 @@
     </row>
     <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="27" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B16" s="19" t="s">
         <v>1529</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>1530</v>
-      </c>
       <c r="C16" s="19" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="F16" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G16" s="20" t="s">
         <v>53</v>
@@ -20781,22 +20745,22 @@
     </row>
     <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B17" s="19" t="s">
         <v>1531</v>
       </c>
-      <c r="B17" s="19" t="s">
-        <v>1532</v>
-      </c>
       <c r="C17" s="19" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>53</v>
@@ -20807,22 +20771,22 @@
     </row>
     <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="s">
+        <v>1532</v>
+      </c>
+      <c r="B18" s="19" t="s">
         <v>1533</v>
       </c>
-      <c r="B18" s="19" t="s">
-        <v>1534</v>
-      </c>
       <c r="C18" s="19" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="F18" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G18" s="20" t="s">
         <v>53</v>
@@ -20833,22 +20797,22 @@
     </row>
     <row r="19" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
+        <v>1534</v>
+      </c>
+      <c r="B19" s="19" t="s">
         <v>1535</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="C19" s="19" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E19" s="19" t="s">
         <v>1536</v>
       </c>
-      <c r="C19" s="19" t="s">
-        <v>1494</v>
-      </c>
-      <c r="D19" s="19" t="s">
-        <v>1504</v>
-      </c>
-      <c r="E19" s="19" t="s">
-        <v>1537</v>
-      </c>
       <c r="F19" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G19" s="20" t="s">
         <v>53</v>
@@ -20859,22 +20823,22 @@
     </row>
     <row r="20" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
+        <v>1537</v>
+      </c>
+      <c r="B20" s="19" t="s">
         <v>1538</v>
       </c>
-      <c r="B20" s="19" t="s">
-        <v>1539</v>
-      </c>
       <c r="C20" s="19" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>53</v>
@@ -20885,22 +20849,22 @@
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B21" s="19" t="s">
         <v>1540</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="C21" s="19" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D21" s="19" t="s">
         <v>1541</v>
       </c>
-      <c r="C21" s="19" t="s">
-        <v>1494</v>
-      </c>
-      <c r="D21" s="19" t="s">
+      <c r="E21" s="19" t="s">
         <v>1542</v>
       </c>
-      <c r="E21" s="19" t="s">
-        <v>1543</v>
-      </c>
       <c r="F21" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G21" s="20" t="s">
         <v>53</v>
@@ -20911,22 +20875,22 @@
     </row>
     <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B22" s="19" t="s">
         <v>1544</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="C22" s="19" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D22" s="19" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E22" s="19" t="s">
         <v>1545</v>
       </c>
-      <c r="C22" s="19" t="s">
-        <v>1494</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>1504</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>1546</v>
-      </c>
       <c r="F22" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G22" s="20" t="s">
         <v>53</v>
@@ -20937,22 +20901,22 @@
     </row>
     <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="27" t="s">
+        <v>1546</v>
+      </c>
+      <c r="B23" s="19" t="s">
         <v>1547</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="C23" s="19" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D23" s="19" t="s">
         <v>1548</v>
       </c>
-      <c r="C23" s="19" t="s">
-        <v>1488</v>
-      </c>
-      <c r="D23" s="19" t="s">
+      <c r="E23" s="19" t="s">
         <v>1549</v>
       </c>
-      <c r="E23" s="19" t="s">
-        <v>1550</v>
-      </c>
       <c r="F23" s="20" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G23" s="20" t="s">
         <v>53</v>
@@ -20963,7 +20927,7 @@
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -20973,7 +20937,7 @@
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -20983,7 +20947,7 @@
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -20993,7 +20957,7 @@
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -21081,373 +21045,373 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="B1" s="15" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>1555</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>1556</v>
-      </c>
       <c r="D1" s="15" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>1557</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="C2" s="19" t="s">
         <v>1558</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="D2" s="19" t="s">
         <v>1559</v>
       </c>
-      <c r="D2" s="19" t="s">
-        <v>1560</v>
-      </c>
       <c r="E2" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="27" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>1561</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>1562</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>326</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="E3" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="27" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B4" s="19" t="s">
         <v>1564</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="C4" s="19" t="s">
         <v>1565</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="D4" s="19" t="s">
         <v>1566</v>
       </c>
-      <c r="D4" s="19" t="s">
-        <v>1567</v>
-      </c>
       <c r="E4" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>1568</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="C5" s="19" t="s">
         <v>1569</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="D5" s="19" t="s">
         <v>1570</v>
       </c>
-      <c r="D5" s="19" t="s">
-        <v>1571</v>
-      </c>
       <c r="E5" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B6" s="19" t="s">
         <v>1572</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="C6" s="19" t="s">
         <v>1573</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="D6" s="19" t="s">
         <v>1574</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>1575</v>
-      </c>
       <c r="E6" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>1576</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="C7" s="19" t="s">
         <v>1577</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="D7" s="19" t="s">
         <v>1578</v>
       </c>
-      <c r="D7" s="19" t="s">
-        <v>1579</v>
-      </c>
       <c r="E7" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B8" s="19" t="s">
         <v>1580</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="C8" s="19" t="s">
         <v>1581</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="D8" s="19" t="s">
         <v>1582</v>
       </c>
-      <c r="D8" s="19" t="s">
-        <v>1583</v>
-      </c>
       <c r="E8" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B9" s="19" t="s">
         <v>1584</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="C9" s="19" t="s">
         <v>1585</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="D9" s="19" t="s">
         <v>1586</v>
       </c>
-      <c r="D9" s="19" t="s">
-        <v>1587</v>
-      </c>
       <c r="E9" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B10" s="19" t="s">
         <v>1588</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>1589</v>
       </c>
       <c r="C10" s="19" t="s">
         <v>51</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="E10" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B11" s="19" t="s">
         <v>1591</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="C11" s="19" t="s">
         <v>1592</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="D11" s="19" t="s">
         <v>1593</v>
       </c>
-      <c r="D11" s="19" t="s">
-        <v>1594</v>
-      </c>
       <c r="E11" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="27" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B12" s="19" t="s">
         <v>1595</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="C12" s="19" t="s">
         <v>1596</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="D12" s="19" t="s">
         <v>1597</v>
       </c>
-      <c r="D12" s="19" t="s">
-        <v>1598</v>
-      </c>
       <c r="E12" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="27" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B13" s="19" t="s">
         <v>1599</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="C13" s="19" t="s">
         <v>1600</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="D13" s="19" t="s">
         <v>1601</v>
       </c>
-      <c r="D13" s="19" t="s">
-        <v>1602</v>
-      </c>
       <c r="E13" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="27" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B14" s="19" t="s">
         <v>1603</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="C14" s="19" t="s">
         <v>1604</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="D14" s="19" t="s">
         <v>1605</v>
       </c>
-      <c r="D14" s="19" t="s">
-        <v>1606</v>
-      </c>
       <c r="E14" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="27" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B15" s="19" t="s">
         <v>1607</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="C15" s="19" t="s">
         <v>1608</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="D15" s="19" t="s">
         <v>1609</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>1610</v>
-      </c>
       <c r="E15" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="27" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B16" s="19" t="s">
         <v>1611</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="C16" s="19" t="s">
         <v>1612</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="D16" s="19" t="s">
         <v>1613</v>
       </c>
-      <c r="D16" s="19" t="s">
-        <v>1614</v>
-      </c>
       <c r="E16" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="27" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B17" s="19" t="s">
         <v>1615</v>
       </c>
-      <c r="B17" s="19" t="s">
+      <c r="C17" s="19" t="s">
         <v>1616</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="D17" s="19" t="s">
         <v>1617</v>
       </c>
-      <c r="D17" s="19" t="s">
-        <v>1618</v>
-      </c>
       <c r="E17" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="27" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B18" s="19" t="s">
+        <v>1618</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>1619</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="D18" s="19" t="s">
         <v>1620</v>
       </c>
-      <c r="D18" s="19" t="s">
-        <v>1621</v>
-      </c>
       <c r="E18" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="27" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B19" s="19" t="s">
         <v>1622</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="C19" s="19" t="s">
         <v>1623</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="D19" s="19" t="s">
         <v>1624</v>
       </c>
-      <c r="D19" s="19" t="s">
-        <v>1625</v>
-      </c>
       <c r="E19" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="27" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
       <c r="B20" s="19" t="s">
+        <v>1625</v>
+      </c>
+      <c r="C20" s="19" t="s">
         <v>1626</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="D20" s="19" t="s">
         <v>1627</v>
       </c>
-      <c r="D20" s="19" t="s">
-        <v>1628</v>
-      </c>
       <c r="E20" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="27" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B21" s="19" t="s">
         <v>1629</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="C21" s="19" t="s">
         <v>1630</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="D21" s="19" t="s">
         <v>1631</v>
       </c>
-      <c r="D21" s="19" t="s">
-        <v>1632</v>
-      </c>
       <c r="E21" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="27" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B22" s="19" t="s">
         <v>1633</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="C22" s="19" t="s">
         <v>1634</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="D22" s="19" t="s">
         <v>1635</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>1636</v>
       </c>
       <c r="E22" s="31"/>
     </row>
@@ -21499,10 +21463,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="15" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>1637</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>1638</v>
       </c>
       <c r="C1" s="15" t="s">
         <v>44</v>
@@ -21510,117 +21474,117 @@
     </row>
     <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>1639</v>
       </c>
-      <c r="B2" s="19" t="s">
-        <v>1640</v>
-      </c>
       <c r="C2" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="27" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B3" s="19" t="s">
         <v>1641</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>1642</v>
-      </c>
       <c r="C3" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="27" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B4" s="19" t="s">
         <v>1643</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>1644</v>
-      </c>
       <c r="C4" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="27" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B5" s="19" t="s">
         <v>1645</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>1646</v>
-      </c>
       <c r="C5" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="27" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B6" s="19" t="s">
         <v>1647</v>
       </c>
-      <c r="B6" s="19" t="s">
-        <v>1648</v>
-      </c>
       <c r="C6" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="27" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B7" s="19" t="s">
         <v>1649</v>
       </c>
-      <c r="B7" s="19" t="s">
-        <v>1650</v>
-      </c>
       <c r="C7" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="27" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B8" s="19" t="s">
         <v>1651</v>
       </c>
-      <c r="B8" s="19" t="s">
-        <v>1652</v>
-      </c>
       <c r="C8" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="27" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B9" s="19" t="s">
         <v>1653</v>
       </c>
-      <c r="B9" s="19" t="s">
-        <v>1654</v>
-      </c>
       <c r="C9" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="27" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B10" s="19" t="s">
         <v>1655</v>
       </c>
-      <c r="B10" s="19" t="s">
-        <v>1656</v>
-      </c>
       <c r="C10" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="27" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B11" s="19" t="s">
         <v>1657</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>1658</v>
-      </c>
       <c r="C11" s="30" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="11" t="s">
-        <v>1659</v>
+        <v>1658</v>
       </c>
     </row>
   </sheetData>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -1023,8 +1023,8 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="B14:C14"/>
@@ -14414,7 +14414,62 @@
       </c>
     </row>
     <row r="202" ht="15" customHeight="1" s="33">
-      <c r="L202" s="32" t="n"/>
+      <c r="A202" t="n">
+        <v>202</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>StoneContact</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>1</v>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Négoce / revendeur</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>FABIAN (demande StoneContact)</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Demande ~500 m², dalles 55×85 cm (format non disponible : contre-proposer le 30×60×2).</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>StoneContact</t>
+        </is>
+      </c>
+      <c r="L202" s="32" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>Répondre via StoneContact avec la contre-proposition préparée — Une seule voie de contact par piste ; répondre avec le message préparé (minyala/reponses-pistes-2026-10.md) et noter la date ici</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>[15/10] Conditions pro sur devis écrit après SIRET ; ne pas payer l'abonnement avant d'avoir vu les détails gratuits.</t>
+        </is>
+      </c>
       <c r="Q202" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
@@ -15800,7 +15855,24 @@
       </c>
     </row>
     <row r="400" ht="15" customHeight="1" s="33">
+      <c r="A400" s="32" t="n"/>
+      <c r="B400" s="32" t="n"/>
+      <c r="C400" s="32" t="n"/>
+      <c r="D400" s="32" t="n"/>
+      <c r="E400" s="32" t="n"/>
+      <c r="F400" s="32" t="n"/>
+      <c r="G400" s="32" t="n"/>
+      <c r="H400" s="32" t="n"/>
+      <c r="I400" s="32" t="n"/>
+      <c r="J400" s="32" t="n"/>
+      <c r="K400" s="32" t="n"/>
       <c r="L400" s="32" t="n"/>
+      <c r="M400" s="32" t="n"/>
+      <c r="N400" s="32" t="n"/>
+      <c r="O400" s="32" t="n"/>
+      <c r="P400" s="32" t="n"/>
+      <c r="Q400" s="32" t="n"/>
+      <c r="R400" s="32" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Q400"/>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -14414,43 +14414,43 @@
       </c>
     </row>
     <row r="202" ht="15" customHeight="1" s="33">
-      <c r="A202" t="n">
+      <c r="A202" s="32" t="n">
         <v>202</v>
       </c>
-      <c r="B202" t="inlineStr">
+      <c r="B202" s="32" t="inlineStr">
         <is>
           <t>StoneContact</t>
         </is>
       </c>
-      <c r="C202" t="n">
+      <c r="C202" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="D202" s="32" t="inlineStr">
         <is>
           <t>Négoce / revendeur</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
+      <c r="E202" s="32" t="inlineStr">
         <is>
           <t>FABIAN (demande StoneContact)</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
+      <c r="F202" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
+      <c r="G202" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
+      <c r="H202" s="32" t="inlineStr">
         <is>
           <t>Demande ~500 m², dalles 55×85 cm (format non disponible : contre-proposer le 30×60×2).</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr">
+      <c r="K202" s="32" t="inlineStr">
         <is>
           <t>StoneContact</t>
         </is>
@@ -14460,12 +14460,12 @@
           <t>À contacter</t>
         </is>
       </c>
-      <c r="N202" t="inlineStr">
+      <c r="N202" s="32" t="inlineStr">
         <is>
           <t>Répondre via StoneContact avec la contre-proposition préparée — Une seule voie de contact par piste ; répondre avec le message préparé (minyala/reponses-pistes-2026-10.md) et noter la date ici</t>
         </is>
       </c>
-      <c r="O202" t="inlineStr">
+      <c r="O202" s="32" t="inlineStr">
         <is>
           <t>[15/10] Conditions pro sur devis écrit après SIRET ; ne pas payer l'abonnement avant d'avoir vu les détails gratuits.</t>
         </is>
@@ -14476,14 +14476,124 @@
       </c>
     </row>
     <row r="203" ht="15" customHeight="1" s="33">
-      <c r="L203" s="32" t="n"/>
+      <c r="A203" t="n">
+        <v>203</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>StoneContact</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>2</v>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>À qualifier</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Teodosiu (demande StoneContact — travertin)</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>À préciser</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>À préciser</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Cherche du travertin : MINYALA en substitution possible.</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>StoneContact</t>
+        </is>
+      </c>
+      <c r="L203" s="32" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>Répondre via StoneContact avec le message « alternative travertin » (reponses-pistes-2026-10.md) ; noter la date ici</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>[16/10] Demande de TRAVERTIN sur StoneContact — nous n'en vendons pas : alternative MINYALA (30×60×2) à proposer. Première réponse = 2 questions (recherche en cours ? alternative acceptable ?), aucun volume ni tarif. Aucune coordonnée vérifiée ; une seule voie de contact : StoneContact.</t>
+        </is>
+      </c>
       <c r="Q203" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
     </row>
     <row r="204" ht="15" customHeight="1" s="33">
-      <c r="L204" s="32" t="n"/>
+      <c r="A204" t="n">
+        <v>204</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>StoneContact</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>2</v>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>À qualifier</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Cristina (demande StoneContact — travertin)</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>À préciser</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>À préciser</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Cherche du travertin : MINYALA en substitution possible.</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>StoneContact</t>
+        </is>
+      </c>
+      <c r="L204" s="32" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Répondre via StoneContact avec le message « alternative travertin » (reponses-pistes-2026-10.md) ; noter la date ici</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>[16/10] Demande de TRAVERTIN sur StoneContact — nous n'en vendons pas : alternative MINYALA (30×60×2) à proposer. Première réponse = 2 questions (recherche en cours ? alternative acceptable ?), aucun volume ni tarif. Aucune coordonnée vérifiée ; une seule voie de contact : StoneContact.</t>
+        </is>
+      </c>
       <c r="Q204" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -3101,14 +3101,22 @@
       </c>
       <c r="L31" s="53" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="M31" s="54" t="n"/>
-      <c r="N31" s="53" t="n"/>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M31" s="54" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="N31" s="53" t="inlineStr">
+        <is>
+          <t>Attendre la réponse ; pas de relance avant le 22/10</t>
+        </is>
+      </c>
       <c r="O31" s="53" t="inlineStr">
         <is>
-          <t>[13/10] Lien « Envoyer un e-mail » de la page Notre agence (Coignières).</t>
+          <t>[13/10] Lien « Envoyer un e-mail » de la page Notre agence (Coignières). | [15/10] Message A (version courte) envoyé depuis Gmail (constaté dans les éléments envoyés, voir registre-envois-2026-10-15.csv) ; remise non confirmée, aucune réponse au 16/10.</t>
         </is>
       </c>
       <c r="P31" s="55" t="n"/>
@@ -3491,14 +3499,22 @@
       </c>
       <c r="L36" s="53" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="M36" s="54" t="n"/>
-      <c r="N36" s="53" t="n"/>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M36" s="54" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="N36" s="53" t="inlineStr">
+        <is>
+          <t>Attendre la réponse ; pas de relance avant le 22/10</t>
+        </is>
+      </c>
       <c r="O36" s="53" t="inlineStr">
         <is>
-          <t>[13/10] Page agence de Caen du site Pillaud.</t>
+          <t>[13/10] Page agence de Caen du site Pillaud. | [15/10] Message A (version courte) envoyé depuis Gmail (constaté dans les éléments envoyés, voir registre-envois-2026-10-15.csv) ; remise non confirmée, aucune réponse au 16/10.</t>
         </is>
       </c>
       <c r="P36" s="55" t="n"/>
@@ -3566,14 +3582,22 @@
       </c>
       <c r="L37" s="53" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="M37" s="54" t="n"/>
-      <c r="N37" s="53" t="n"/>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M37" s="54" t="inlineStr">
+        <is>
+          <t>15/10/2026</t>
+        </is>
+      </c>
+      <c r="N37" s="53" t="inlineStr">
+        <is>
+          <t>Attendre la réponse ; pas de relance avant le 22/10</t>
+        </is>
+      </c>
       <c r="O37" s="53" t="inlineStr">
         <is>
-          <t>[13/10] Affiché en forme anti-spam « info[@]torchio.fr » sur les mentions légales du site.</t>
+          <t>[13/10] Affiché en forme anti-spam « info[@]torchio.fr » sur les mentions légales du site. | [15/10] Message A (version courte) envoyé depuis Gmail (constaté dans les éléments envoyés, voir registre-envois-2026-10-15.csv) ; remise non confirmée, aucune réponse au 16/10.</t>
         </is>
       </c>
       <c r="P37" s="55" t="n"/>
@@ -14476,43 +14500,43 @@
       </c>
     </row>
     <row r="203" ht="15" customHeight="1" s="33">
-      <c r="A203" t="n">
+      <c r="A203" s="32" t="n">
         <v>203</v>
       </c>
-      <c r="B203" t="inlineStr">
+      <c r="B203" s="32" t="inlineStr">
         <is>
           <t>StoneContact</t>
         </is>
       </c>
-      <c r="C203" t="n">
+      <c r="C203" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D203" t="inlineStr">
+      <c r="D203" s="32" t="inlineStr">
         <is>
           <t>À qualifier</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
+      <c r="E203" s="32" t="inlineStr">
         <is>
           <t>Teodosiu (demande StoneContact — travertin)</t>
         </is>
       </c>
-      <c r="F203" t="inlineStr">
+      <c r="F203" s="32" t="inlineStr">
         <is>
           <t>À préciser</t>
         </is>
       </c>
-      <c r="G203" t="inlineStr">
+      <c r="G203" s="32" t="inlineStr">
         <is>
           <t>À préciser</t>
         </is>
       </c>
-      <c r="H203" t="inlineStr">
+      <c r="H203" s="32" t="inlineStr">
         <is>
           <t>Cherche du travertin : MINYALA en substitution possible.</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr">
+      <c r="K203" s="32" t="inlineStr">
         <is>
           <t>StoneContact</t>
         </is>
@@ -14522,12 +14546,12 @@
           <t>À contacter</t>
         </is>
       </c>
-      <c r="N203" t="inlineStr">
+      <c r="N203" s="32" t="inlineStr">
         <is>
           <t>Répondre via StoneContact avec le message « alternative travertin » (reponses-pistes-2026-10.md) ; noter la date ici</t>
         </is>
       </c>
-      <c r="O203" t="inlineStr">
+      <c r="O203" s="32" t="inlineStr">
         <is>
           <t>[16/10] Demande de TRAVERTIN sur StoneContact — nous n'en vendons pas : alternative MINYALA (30×60×2) à proposer. Première réponse = 2 questions (recherche en cours ? alternative acceptable ?), aucun volume ni tarif. Aucune coordonnée vérifiée ; une seule voie de contact : StoneContact.</t>
         </is>
@@ -14538,43 +14562,43 @@
       </c>
     </row>
     <row r="204" ht="15" customHeight="1" s="33">
-      <c r="A204" t="n">
+      <c r="A204" s="32" t="n">
         <v>204</v>
       </c>
-      <c r="B204" t="inlineStr">
+      <c r="B204" s="32" t="inlineStr">
         <is>
           <t>StoneContact</t>
         </is>
       </c>
-      <c r="C204" t="n">
+      <c r="C204" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D204" t="inlineStr">
+      <c r="D204" s="32" t="inlineStr">
         <is>
           <t>À qualifier</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
+      <c r="E204" s="32" t="inlineStr">
         <is>
           <t>Cristina (demande StoneContact — travertin)</t>
         </is>
       </c>
-      <c r="F204" t="inlineStr">
+      <c r="F204" s="32" t="inlineStr">
         <is>
           <t>À préciser</t>
         </is>
       </c>
-      <c r="G204" t="inlineStr">
+      <c r="G204" s="32" t="inlineStr">
         <is>
           <t>À préciser</t>
         </is>
       </c>
-      <c r="H204" t="inlineStr">
+      <c r="H204" s="32" t="inlineStr">
         <is>
           <t>Cherche du travertin : MINYALA en substitution possible.</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr">
+      <c r="K204" s="32" t="inlineStr">
         <is>
           <t>StoneContact</t>
         </is>
@@ -14584,12 +14608,12 @@
           <t>À contacter</t>
         </is>
       </c>
-      <c r="N204" t="inlineStr">
+      <c r="N204" s="32" t="inlineStr">
         <is>
           <t>Répondre via StoneContact avec le message « alternative travertin » (reponses-pistes-2026-10.md) ; noter la date ici</t>
         </is>
       </c>
-      <c r="O204" t="inlineStr">
+      <c r="O204" s="32" t="inlineStr">
         <is>
           <t>[16/10] Demande de TRAVERTIN sur StoneContact — nous n'en vendons pas : alternative MINYALA (30×60×2) à proposer. Première réponse = 2 questions (recherche en cours ? alternative acceptable ?), aucun volume ni tarif. Aucune coordonnée vérifiée ; une seule voie de contact : StoneContact.</t>
         </is>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -1480,18 +1480,22 @@
       </c>
       <c r="L6" s="53" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="M6" s="54" t="n"/>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M6" s="54" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
       <c r="N6" s="53" t="inlineStr">
         <is>
-          <t>Prochain contact depuis la boîte Gmail (pas Hotmail), après fusion du suivi</t>
+          <t>Attendre la réponse ; pas de relance avant le 23/10</t>
         </is>
       </c>
       <c r="O6" s="53" t="inlineStr">
         <is>
-          <t>Rapprochement du 13/10 (autre assistant) : dernier envoi rejeté (échec de remise) — à confirmer, puis trouver une autre adresse. | [13/10] Tentative depuis Hotmail rejetée EN SORTIE (5.7.520 : contenu classé spam par Microsoft) — message non remis ; l'adresse n'est pas forcément invalide. Prochain contact depuis la boîte Gmail, nouveau modèle, jamais depuis Hotmail.</t>
+          <t>Rapprochement du 13/10 (autre assistant) : dernier envoi rejeté (échec de remise) — à confirmer, puis trouver une autre adresse. | [13/10] Tentative depuis Hotmail rejetée EN SORTIE (5.7.520 : contenu classé spam par Microsoft) — message non remis ; l'adresse n'est pas forcément invalide. Prochain contact depuis la boîte Gmail, nouveau modèle, jamais depuis Hotmail. | [16/10] Message A (version courte) envoyé depuis Gmail à 10h38 UTC (registre-envois-2026-10-16.csv) ; adresse précédemment visée par un rejet 5.7.520 côté Hotmail (jamais remise) : ceci est le premier contact réel. Remise non confirmée.</t>
         </is>
       </c>
       <c r="P6" s="55" t="n"/>
@@ -9349,18 +9353,22 @@
       </c>
       <c r="L124" s="53" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="M124" s="54" t="n"/>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M124" s="54" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
       <c r="N124" s="53" t="inlineStr">
         <is>
-          <t>Prochain contact depuis la boîte Gmail (pas Hotmail), après fusion du suivi</t>
+          <t>Attendre la réponse ; pas de relance avant le 23/10</t>
         </is>
       </c>
       <c r="O124" s="53" t="inlineStr">
         <is>
-          <t>[13/10] Tentative depuis Hotmail rejetée EN SORTIE (5.7.520 : contenu classé spam par Microsoft) — message non remis ; l'adresse n'est pas forcément invalide. Prochain contact depuis la boîte Gmail, nouveau modèle, jamais depuis Hotmail.</t>
+          <t>[13/10] Tentative depuis Hotmail rejetée EN SORTIE (5.7.520 : contenu classé spam par Microsoft) — message non remis ; l'adresse n'est pas forcément invalide. Prochain contact depuis la boîte Gmail, nouveau modèle, jamais depuis Hotmail. | [16/10] Message A (version courte) envoyé depuis Gmail à 10h38 UTC (registre-envois-2026-10-16.csv) ; adresse précédemment visée par un rejet 5.7.520 côté Hotmail (jamais remise) : ceci est le premier contact réel. Remise non confirmée.</t>
         </is>
       </c>
       <c r="P124" s="55" t="n"/>
@@ -9643,18 +9651,22 @@
       </c>
       <c r="L128" s="53" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="M128" s="54" t="n"/>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M128" s="54" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
       <c r="N128" s="53" t="inlineStr">
         <is>
-          <t>Prochain contact depuis la boîte Gmail (pas Hotmail), après fusion du suivi</t>
+          <t>Attendre la réponse ; pas de relance avant le 23/10</t>
         </is>
       </c>
       <c r="O128" s="53" t="inlineStr">
         <is>
-          <t>[13/10] Tentative depuis Hotmail rejetée EN SORTIE (5.7.520 : contenu classé spam par Microsoft) — message non remis ; l'adresse n'est pas forcément invalide. Prochain contact depuis la boîte Gmail, nouveau modèle, jamais depuis Hotmail.</t>
+          <t>[13/10] Tentative depuis Hotmail rejetée EN SORTIE (5.7.520 : contenu classé spam par Microsoft) — message non remis ; l'adresse n'est pas forcément invalide. Prochain contact depuis la boîte Gmail, nouveau modèle, jamais depuis Hotmail. | [16/10] Message A (version courte) envoyé depuis Gmail à 10h38 UTC (registre-envois-2026-10-16.csv) ; adresse précédemment visée par un rejet 5.7.520 côté Hotmail (jamais remise) : ceci est le premier contact réel. Remise non confirmée.</t>
         </is>
       </c>
       <c r="P128" s="55" t="n"/>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -1210,11 +1210,20 @@
       </c>
       <c r="M2" s="54" t="n"/>
       <c r="N2" s="53" t="n"/>
-      <c r="O2" s="53" t="n"/>
+      <c r="O2" s="53" t="inlineStr">
+        <is>
+          <t>[16/10] E-mail du pied de page/page contact du site officiel pedrazzini.fr (showroom Voisenon confirmé).</t>
+        </is>
+      </c>
       <c r="P2" s="55" t="n"/>
       <c r="Q2" s="56">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>contact@pedrazzini.fr</t>
+        </is>
       </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="33">
@@ -2635,13 +2644,18 @@
       <c r="N25" s="53" t="n"/>
       <c r="O25" s="53" t="inlineStr">
         <is>
-          <t>[13/10] Aucun e-mail propre à SNNMC publié : formulaire sur la fiche France Matériaux, ou téléphone.</t>
+          <t>[13/10] Aucun e-mail propre à SNNMC publié : formulaire sur la fiche France Matériaux, ou téléphone. | [16/10] E-mail du site officiel materiaux-batiment.fr (accueil + page contact, itemprop=email). Site parfois en 503 : réessayer. Ne PAS utiliser contact@france-materiaux.fr (réseau, pas SNNMC).</t>
         </is>
       </c>
       <c r="P25" s="55" t="n"/>
       <c r="Q25" s="56">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>contact@materiaux-batiment.fr</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="34.5" customHeight="1" s="33">
@@ -3357,7 +3371,7 @@
       <c r="N34" s="53" t="n"/>
       <c r="O34" s="53" t="inlineStr">
         <is>
-          <t>[13/10] Aucun e-mail publié : formulaire de la fiche magasin BigMat Évreux uniquement.</t>
+          <t>[13/10] Aucun e-mail publié : formulaire de la fiche magasin BigMat Évreux uniquement. | [16/10] Pas d'e-mail publié (fiche officielle magasins.bigmat.fr : formulaire seul). Tél. 02 32 31 20 17. Contact par formulaire ou téléphone.</t>
         </is>
       </c>
       <c r="P34" s="55" t="n"/>
@@ -8516,7 +8530,11 @@
       </c>
       <c r="M113" s="54" t="n"/>
       <c r="N113" s="53" t="n"/>
-      <c r="O113" s="53" t="n"/>
+      <c r="O113" s="53" t="inlineStr">
+        <is>
+          <t>[16/10] Pas d'e-mail publié (fiche officielle magasins.bigmat.fr : formulaire seul). Tél. 01 30 90 71 75. Contact par formulaire ou téléphone.</t>
+        </is>
+      </c>
       <c r="P113" s="55" t="n"/>
       <c r="Q113" s="56">
         <f>'Mode d''emploi'!$B$29</f>
@@ -8985,11 +9003,20 @@
       </c>
       <c r="M119" s="54" t="n"/>
       <c r="N119" s="53" t="n"/>
-      <c r="O119" s="53" t="n"/>
+      <c r="O119" s="53" t="inlineStr">
+        <is>
+          <t>[16/10] Adresse générique RABONI IDF lue sur lestudioraboni.fr/mentions-legales — pas propre au showroom de Boulogne (sa page contact = formulaire seul, tél. 01 46 09 54 80). raboni.fr protégé anti-bot.</t>
+        </is>
+      </c>
       <c r="P119" s="55" t="n"/>
       <c r="Q119" s="56">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>contact@raboni.fr</t>
+        </is>
       </c>
     </row>
     <row r="120" ht="34.5" customHeight="1" s="33">
@@ -9134,11 +9161,20 @@
       </c>
       <c r="M121" s="54" t="n"/>
       <c r="N121" s="53" t="n"/>
-      <c r="O121" s="53" t="n"/>
+      <c r="O121" s="53" t="inlineStr">
+        <is>
+          <t>[16/10] E-mail du magasin de Sarcelles sur ceramico.fr (accueil, bloc « Magasin 1 &amp; Dépôt — Sarcelles »). Ne PAS utiliser commercial@ceramico.fr (magasin du Perreux).</t>
+        </is>
+      </c>
       <c r="P121" s="55" t="n"/>
       <c r="Q121" s="56">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>info@ceramico.fr</t>
+        </is>
       </c>
     </row>
     <row r="122" ht="45.75" customHeight="1" s="33">
@@ -9441,11 +9477,20 @@
       </c>
       <c r="M125" s="54" t="n"/>
       <c r="N125" s="53" t="n"/>
-      <c r="O125" s="53" t="n"/>
+      <c r="O125" s="53" t="inlineStr">
+        <is>
+          <t>[16/10] E-mail général du pied de page (mpt-marbrier.fr/contact) ; domaine de l'adresse ≠ domaine du site, tel qu'affiché par le site officiel.</t>
+        </is>
+      </c>
       <c r="P125" s="55" t="n"/>
       <c r="Q125" s="56">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>accueil@marbrierpierretaille.fr</t>
+        </is>
       </c>
     </row>
     <row r="126" ht="45.75" customHeight="1" s="33">
@@ -9590,11 +9635,20 @@
       </c>
       <c r="M127" s="54" t="n"/>
       <c r="N127" s="53" t="n"/>
-      <c r="O127" s="53" t="n"/>
+      <c r="O127" s="53" t="inlineStr">
+        <is>
+          <t>[16/10] Unique e-mail du site officiel pierres-nat.com (page contact, en-tête, pied de page ; adresse Linas confirmée).</t>
+        </is>
+      </c>
       <c r="P127" s="55" t="n"/>
       <c r="Q127" s="56">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>pierres.nat@gmail.com</t>
+        </is>
       </c>
     </row>
     <row r="128" ht="45.75" customHeight="1" s="33">
@@ -9735,11 +9789,20 @@
       </c>
       <c r="M129" s="54" t="n"/>
       <c r="N129" s="53" t="n"/>
-      <c r="O129" s="53" t="n"/>
+      <c r="O129" s="53" t="inlineStr">
+        <is>
+          <t>[16/10] E-mail « Espace Pro » de la fiche agence Évreux sur solmur.fr (tél. 02 32 62 94 80). Ne PAS utiliser espace.pro.bihorel@ (pied de page = siège Bihorel).</t>
+        </is>
+      </c>
       <c r="P129" s="55" t="n"/>
       <c r="Q129" s="56">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>espace.pro.evreux@solmur.fr</t>
+        </is>
       </c>
     </row>
     <row r="130" ht="45.75" customHeight="1" s="33">
@@ -9967,11 +10030,20 @@
       </c>
       <c r="M132" s="54" t="n"/>
       <c r="N132" s="53" t="n"/>
-      <c r="O132" s="53" t="n"/>
+      <c r="O132" s="53" t="inlineStr">
+        <is>
+          <t>[16/10] Seule adresse affichée sur le site officiel (page contact) — semi-nominative sur hotmail.com, pas de générique. À utiliser telle quelle.</t>
+        </is>
+      </c>
       <c r="P132" s="55" t="n"/>
       <c r="Q132" s="56">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>anthony.tendance@hotmail.com</t>
+        </is>
       </c>
     </row>
     <row r="133" ht="57" customHeight="1" s="33">
@@ -10033,7 +10105,11 @@
       </c>
       <c r="M133" s="54" t="n"/>
       <c r="N133" s="53" t="n"/>
-      <c r="O133" s="53" t="n"/>
+      <c r="O133" s="53" t="inlineStr">
+        <is>
+          <t>[16/10] Aucun e-mail publié (formulaire avec choix d'agence uniquement, mentions légales comprises). Tél. agence de Caen : 02 31 68 69 68.</t>
+        </is>
+      </c>
       <c r="P133" s="55" t="n"/>
       <c r="Q133" s="56">
         <f>'Mode d''emploi'!$B$29</f>
@@ -10265,11 +10341,20 @@
       </c>
       <c r="M136" s="54" t="n"/>
       <c r="N136" s="53" t="n"/>
-      <c r="O136" s="53" t="n"/>
+      <c r="O136" s="53" t="inlineStr">
+        <is>
+          <t>[16/10] E-mail de l'éditeur sur sedelka.fr/mentions-legales (dpo@ réservé aux données personnelles).</t>
+        </is>
+      </c>
       <c r="P136" s="55" t="n"/>
       <c r="Q136" s="56">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>contact@sedelka.fr</t>
+        </is>
       </c>
     </row>
     <row r="137" ht="34.5" customHeight="1" s="33">

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -1220,7 +1220,7 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="32" t="inlineStr">
         <is>
           <t>contact@pedrazzini.fr</t>
         </is>
@@ -1272,18 +1272,22 @@
       </c>
       <c r="L3" s="53" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="M3" s="54" t="n"/>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M3" s="54" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
       <c r="N3" s="53" t="inlineStr">
         <is>
-          <t>Prochain contact depuis la boîte Gmail (pas Hotmail), après fusion du suivi</t>
+          <t>Attendre la réponse ; pas de relance avant le 23/10</t>
         </is>
       </c>
       <c r="O3" s="53" t="inlineStr">
         <is>
-          <t>Rapprochement du 13/10 (autre assistant) : dernier envoi rejeté (échec de remise) — à confirmer, puis trouver une autre adresse. | [13/10] Tentative depuis Hotmail rejetée EN SORTIE (5.7.520 : contenu classé spam par Microsoft) — message non remis ; l'adresse n'est pas forcément invalide. Prochain contact depuis la boîte Gmail, nouveau modèle, jamais depuis Hotmail.</t>
+          <t>Rapprochement du 13/10 (autre assistant) : dernier envoi rejeté (échec de remise) — à confirmer, puis trouver une autre adresse. | [13/10] Tentative depuis Hotmail rejetée EN SORTIE (5.7.520 : contenu classé spam par Microsoft) — message non remis ; l'adresse n'est pas forcément invalide. Prochain contact depuis la boîte Gmail, nouveau modèle, jamais depuis Hotmail. | [16/10] Message A (version courte) envoyé depuis Gmail à 13h42 UTC (registre-envois-2026-10-16.csv) ; adresse précédemment visée par un rejet 5.7.520 côté Hotmail (jamais remise) : premier contact réel. Remise non confirmée.</t>
         </is>
       </c>
       <c r="P3" s="55" t="n"/>
@@ -1343,18 +1347,22 @@
       </c>
       <c r="L4" s="53" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="M4" s="54" t="n"/>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M4" s="54" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
       <c r="N4" s="53" t="inlineStr">
         <is>
-          <t>Prochain contact depuis la boîte Gmail (pas Hotmail), après fusion du suivi</t>
+          <t>Attendre la réponse ; pas de relance avant le 23/10</t>
         </is>
       </c>
       <c r="O4" s="53" t="inlineStr">
         <is>
-          <t>Rapprochement du 13/10 (autre assistant) : dernier envoi rejeté (échec de remise) — à confirmer, puis trouver une autre adresse. | [13/10] Tentative depuis Hotmail rejetée EN SORTIE (5.7.520 : contenu classé spam par Microsoft) — message non remis ; l'adresse n'est pas forcément invalide. Prochain contact depuis la boîte Gmail, nouveau modèle, jamais depuis Hotmail.</t>
+          <t>Rapprochement du 13/10 (autre assistant) : dernier envoi rejeté (échec de remise) — à confirmer, puis trouver une autre adresse. | [13/10] Tentative depuis Hotmail rejetée EN SORTIE (5.7.520 : contenu classé spam par Microsoft) — message non remis ; l'adresse n'est pas forcément invalide. Prochain contact depuis la boîte Gmail, nouveau modèle, jamais depuis Hotmail. | [16/10] Message A (version courte) envoyé depuis Gmail à 13h42 UTC (registre-envois-2026-10-16.csv) ; adresse précédemment visée par un rejet 5.7.520 côté Hotmail (jamais remise) : premier contact réel. Remise non confirmée.</t>
         </is>
       </c>
       <c r="P4" s="55" t="n"/>
@@ -1414,18 +1422,22 @@
       </c>
       <c r="L5" s="53" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="M5" s="54" t="n"/>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M5" s="54" t="inlineStr">
+        <is>
+          <t>16/10/2026</t>
+        </is>
+      </c>
       <c r="N5" s="53" t="inlineStr">
         <is>
-          <t>Prochain contact depuis la boîte Gmail (pas Hotmail), après fusion du suivi</t>
+          <t>Attendre la réponse ; pas de relance avant le 23/10</t>
         </is>
       </c>
       <c r="O5" s="53" t="inlineStr">
         <is>
-          <t>Rapprochement du 13/10 (autre assistant) : dernier envoi rejeté (échec de remise) — à confirmer, puis trouver une autre adresse. | [13/10] Tentative depuis Hotmail rejetée EN SORTIE (5.7.520 : contenu classé spam par Microsoft) — message non remis ; l'adresse n'est pas forcément invalide. Prochain contact depuis la boîte Gmail, nouveau modèle, jamais depuis Hotmail.</t>
+          <t>Rapprochement du 13/10 (autre assistant) : dernier envoi rejeté (échec de remise) — à confirmer, puis trouver une autre adresse. | [13/10] Tentative depuis Hotmail rejetée EN SORTIE (5.7.520 : contenu classé spam par Microsoft) — message non remis ; l'adresse n'est pas forcément invalide. Prochain contact depuis la boîte Gmail, nouveau modèle, jamais depuis Hotmail. | [16/10] Message A (version courte) envoyé depuis Gmail à 13h42 UTC (registre-envois-2026-10-16.csv) ; adresse précédemment visée par un rejet 5.7.520 côté Hotmail (jamais remise) : premier contact réel. Remise non confirmée.</t>
         </is>
       </c>
       <c r="P5" s="55" t="n"/>
@@ -2652,7 +2664,7 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="R25" s="32" t="inlineStr">
         <is>
           <t>contact@materiaux-batiment.fr</t>
         </is>
@@ -9013,7 +9025,7 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R119" t="inlineStr">
+      <c r="R119" s="32" t="inlineStr">
         <is>
           <t>contact@raboni.fr</t>
         </is>
@@ -9171,7 +9183,7 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R121" t="inlineStr">
+      <c r="R121" s="32" t="inlineStr">
         <is>
           <t>info@ceramico.fr</t>
         </is>
@@ -9487,7 +9499,7 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R125" t="inlineStr">
+      <c r="R125" s="32" t="inlineStr">
         <is>
           <t>accueil@marbrierpierretaille.fr</t>
         </is>
@@ -9645,7 +9657,7 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R127" t="inlineStr">
+      <c r="R127" s="32" t="inlineStr">
         <is>
           <t>pierres.nat@gmail.com</t>
         </is>
@@ -9799,7 +9811,7 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R129" t="inlineStr">
+      <c r="R129" s="32" t="inlineStr">
         <is>
           <t>espace.pro.evreux@solmur.fr</t>
         </is>
@@ -10040,7 +10052,7 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R132" t="inlineStr">
+      <c r="R132" s="32" t="inlineStr">
         <is>
           <t>anthony.tendance@hotmail.com</t>
         </is>
@@ -10351,7 +10363,7 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R136" t="inlineStr">
+      <c r="R136" s="32" t="inlineStr">
         <is>
           <t>contact@sedelka.fr</t>
         </is>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -1205,14 +1205,22 @@
       </c>
       <c r="L2" s="53" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="M2" s="54" t="n"/>
-      <c r="N2" s="53" t="n"/>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M2" s="54" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="N2" s="53" t="inlineStr">
+        <is>
+          <t>Attendre la réponse ; pas de relance avant le 24/10</t>
+        </is>
+      </c>
       <c r="O2" s="53" t="inlineStr">
         <is>
-          <t>[16/10] E-mail du pied de page/page contact du site officiel pedrazzini.fr (showroom Voisenon confirmé).</t>
+          <t>[16/10] E-mail du pied de page/page contact du site officiel pedrazzini.fr (showroom Voisenon confirmé). | [17/10] Message A (version courte) envoyé depuis Gmail à 08h47 UTC (registre-envois-2026-10-17.csv) ; remise non confirmée.</t>
         </is>
       </c>
       <c r="P2" s="55" t="n"/>
@@ -9010,14 +9018,22 @@
       </c>
       <c r="L119" s="53" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="M119" s="54" t="n"/>
-      <c r="N119" s="53" t="n"/>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M119" s="54" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="N119" s="53" t="inlineStr">
+        <is>
+          <t>Attendre la réponse ; pas de relance avant le 24/10</t>
+        </is>
+      </c>
       <c r="O119" s="53" t="inlineStr">
         <is>
-          <t>[16/10] Adresse générique RABONI IDF lue sur lestudioraboni.fr/mentions-legales — pas propre au showroom de Boulogne (sa page contact = formulaire seul, tél. 01 46 09 54 80). raboni.fr protégé anti-bot.</t>
+          <t>[16/10] Adresse générique RABONI IDF lue sur lestudioraboni.fr/mentions-legales — pas propre au showroom de Boulogne (sa page contact = formulaire seul, tél. 01 46 09 54 80). raboni.fr protégé anti-bot. | [17/10] Message A (version courte) envoyé depuis Gmail à 08h47 UTC (registre-envois-2026-10-17.csv) ; remise non confirmée.</t>
         </is>
       </c>
       <c r="P119" s="55" t="n"/>
@@ -9168,14 +9184,22 @@
       </c>
       <c r="L121" s="53" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="M121" s="54" t="n"/>
-      <c r="N121" s="53" t="n"/>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M121" s="54" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="N121" s="53" t="inlineStr">
+        <is>
+          <t>Attendre la réponse ; pas de relance avant le 24/10</t>
+        </is>
+      </c>
       <c r="O121" s="53" t="inlineStr">
         <is>
-          <t>[16/10] E-mail du magasin de Sarcelles sur ceramico.fr (accueil, bloc « Magasin 1 &amp; Dépôt — Sarcelles »). Ne PAS utiliser commercial@ceramico.fr (magasin du Perreux).</t>
+          <t>[16/10] E-mail du magasin de Sarcelles sur ceramico.fr (accueil, bloc « Magasin 1 &amp; Dépôt — Sarcelles »). Ne PAS utiliser commercial@ceramico.fr (magasin du Perreux). | [17/10] Message A (version courte) envoyé depuis Gmail à 08h47 UTC (registre-envois-2026-10-17.csv) ; remise non confirmée.</t>
         </is>
       </c>
       <c r="P121" s="55" t="n"/>
@@ -9484,14 +9508,22 @@
       </c>
       <c r="L125" s="53" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="M125" s="54" t="n"/>
-      <c r="N125" s="53" t="n"/>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M125" s="54" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="N125" s="53" t="inlineStr">
+        <is>
+          <t>Attendre la réponse ; pas de relance avant le 24/10</t>
+        </is>
+      </c>
       <c r="O125" s="53" t="inlineStr">
         <is>
-          <t>[16/10] E-mail général du pied de page (mpt-marbrier.fr/contact) ; domaine de l'adresse ≠ domaine du site, tel qu'affiché par le site officiel.</t>
+          <t>[16/10] E-mail général du pied de page (mpt-marbrier.fr/contact) ; domaine de l'adresse ≠ domaine du site, tel qu'affiché par le site officiel. | [17/10] Message A (version courte) envoyé depuis Gmail à 08h47 UTC (registre-envois-2026-10-17.csv) ; remise non confirmée.</t>
         </is>
       </c>
       <c r="P125" s="55" t="n"/>
@@ -9642,14 +9674,22 @@
       </c>
       <c r="L127" s="53" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="M127" s="54" t="n"/>
-      <c r="N127" s="53" t="n"/>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M127" s="54" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="N127" s="53" t="inlineStr">
+        <is>
+          <t>Attendre la réponse ; pas de relance avant le 24/10</t>
+        </is>
+      </c>
       <c r="O127" s="53" t="inlineStr">
         <is>
-          <t>[16/10] Unique e-mail du site officiel pierres-nat.com (page contact, en-tête, pied de page ; adresse Linas confirmée).</t>
+          <t>[16/10] Unique e-mail du site officiel pierres-nat.com (page contact, en-tête, pied de page ; adresse Linas confirmée). | [17/10] Message A (version courte) envoyé depuis Gmail à 08h47 UTC (registre-envois-2026-10-17.csv) ; remise non confirmée.</t>
         </is>
       </c>
       <c r="P127" s="55" t="n"/>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -14773,63 +14773,658 @@
       </c>
     </row>
     <row r="205" ht="15" customHeight="1" s="33">
-      <c r="L205" s="32" t="n"/>
+      <c r="A205" t="n">
+        <v>205</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>4e liste — importateurs (17/10)</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>1</v>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Importateur / grossiste</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>NR Distribution (SARL Natural Rock Distribution)</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Avignon (84140)</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>PACA / Sud-Est</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Importateur-grossiste de travertin et pierres naturelles, livre les revendeurs pros dans toute la France depuis son parc d'Avignon ; page dédiée « Grossiste pierre d'Égypte » (pierre extraite au Sinaï) — meilleure adéquation du lot.</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>https://www.nr-distribution.fr/</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Site officiel (vérifié 17/10)</t>
+        </is>
+      </c>
+      <c r="L205" s="32" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>[17/10] E-mail lu sur les mentions légales (https://www.nr-distribution.fr/mentions-legales/) — la page contact n'a qu'un formulaire, sans e-mail ni téléphone. Page Égypte : nr-distribution.fr/nos-prestations/grossiste-pierre-degypte-en-normandie/. Vérifié sur site officiel le 17/10.</t>
+        </is>
+      </c>
       <c r="Q205" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>nrd@nr-distribution.fr</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="15" customHeight="1" s="33">
-      <c r="L206" s="32" t="n"/>
+      <c r="A206" t="n">
+        <v>206</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>4e liste — importateurs (17/10)</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>1</v>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Importateur / grossiste</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>FrancePierre</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Paris (75007) — showrooms Nîmes, Béziers, Périgueux</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Page dédiée pierre d'Égypte (variétés GALALA et SINAI PEARL) ; se présente en « fabricant de pierre naturelle — vente directe » plutôt que grossiste.</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>https://www.francepierre.fr/</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Site officiel (vérifié 17/10)</t>
+        </is>
+      </c>
+      <c r="L206" s="32" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>[17/10] E-mail confirmé sur l'accueil, le pied de page et la page Égypte (francepierre.fr/pierres-d-ailleurs/pierre-d-egypte/). Domaine francepierre.fr au registre-rejets du 12/10 (5.7.520 — jamais livré) : premier contact légitime. Positionnement « sur mesure, sans volume » — accroche lot fin de stock adaptée.</t>
+        </is>
+      </c>
       <c r="Q206" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>contact@francepierre.fr</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="15" customHeight="1" s="33">
-      <c r="L207" s="32" t="n"/>
+      <c r="A207" t="n">
+        <v>207</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>4e liste — importateurs (17/10)</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>1</v>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Négoce / revendeur</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Créa Stone (CREA STONE)</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Feillens (01570) ; siège Brignoles (83170)</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Ain / Var</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>« Fournisseur et grossiste de pierre naturelle » (site dallage-pierre.com ; crea-stone.com y redirige).</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>https://dallage-pierre.com/</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>04 12 16 05 26</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Site officiel (vérifié 17/10)</t>
+        </is>
+      </c>
+      <c r="L207" s="32" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>[17/10] E-mail confirmé au pied de page de dallage-pierre.com. AUCUNE mention de l'Égypte sur le site (cite le marbre de Turquie) — ne pas le présenter comme importateur de calcaire égyptien : Message A standard uniquement, sans ligne importateur.</t>
+        </is>
+      </c>
       <c r="Q207" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>info@crea-stone.com</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="15" customHeight="1" s="33">
-      <c r="L208" s="32" t="n"/>
+      <c r="A208" t="n">
+        <v>208</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>4e liste — importateurs (17/10)</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>1</v>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Importateur / grossiste</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>ELK International</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>La Roche-Jaudy (22450)</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Bretagne</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>« Importateur direct de pierre naturelle » (2 500+ conteneurs importés, approvisionnement direct en carrière/usine) ; « PIERRE D'EGYPTE » figure au catalogue.</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>https://www.elk-international.com</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Site officiel (vérifié 17/10)</t>
+        </is>
+      </c>
+      <c r="L208" s="32" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>[17/10] E-mail lu sur la page d'accueil du site officiel. Gamme : grès, granit, ardoise, porphyre, calcaire, travertin. Vérifié sur site officiel le 17/10.</t>
+        </is>
+      </c>
       <c r="Q208" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>contact@elk-international.com</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="15" customHeight="1" s="33">
-      <c r="L209" s="32" t="n"/>
+      <c r="A209" t="n">
+        <v>209</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>4e liste — importateurs (17/10)</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>1</v>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Importateur / grossiste</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Stones Partner</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Mouazé (35250)</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Bretagne</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>Importateur B2B pour distributeurs de matériaux d'aménagement, « commander en container ou en commande groupée » ; l'Égypte figure parmi ses « Pays Partner ».</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>https://www.stonespartner.com</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>02 99 54 97 50</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Site officiel (vérifié 17/10)</t>
+        </is>
+      </c>
+      <c r="L209" s="32" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>[17/10] E-mail lu sur le site officiel. Gammes : travertin, grès, tandur, ardoise, parements. Vérifié sur site officiel le 17/10.</t>
+        </is>
+      </c>
       <c r="Q209" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>contact@stonespartner.com</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="15" customHeight="1" s="33">
-      <c r="L210" s="32" t="n"/>
+      <c r="A210" t="n">
+        <v>210</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>4e liste — importateurs (17/10)</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>1</v>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Importateur / grossiste</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Européenne de Négoce</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Pontarmé (60520)</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Hauts-de-France</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>« Distributeur et importateur de pierres naturelles » (pavés, bordures, dallages ; catégorie pavés calcaire) avec parc de stockage à Pontarmé (~12 000 m² selon Opalis — le chiffre de 40 000 m² n'est pas confirmé).</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>https://www.europeennedenegoce.fr</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Site officiel (vérifié 17/10)</t>
+        </is>
+      </c>
+      <c r="L210" s="32" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>[17/10] E-mail lu en clair sur europeennedenegoce.fr. Contacter UNIQUEMENT europeennedenegoce@orange.fr — La Maison du Pavé (lamaisondupave.fr) est la MÊME entreprise (même adresse à Pontarmé, confirmé sur les deux sites) : jamais les deux adresses.</t>
+        </is>
+      </c>
       <c r="Q210" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>europeennedenegoce@orange.fr</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="15" customHeight="1" s="33">
-      <c r="L211" s="32" t="n"/>
+      <c r="A211" t="n">
+        <v>211</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>4e liste — importateurs (17/10)</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>1</v>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Importateur / grossiste</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Azur Pierre Agencement</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Grasse (06130)</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>PACA</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Importateur-grossiste approvisionné « directement depuis les carrières partenaires » : « arrivages réguliers de pierres calcaires d'Égypte … en gros », « dalles calcaires égyptiennes en grand format » — très bonne adéquation.</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>https://www.azurpierre.com</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>04 69 00 16 12</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Site officiel (vérifié 17/10)</t>
+        </is>
+      </c>
+      <c r="L211" s="32" t="inlineStr">
+        <is>
+          <t>À contacter</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>[17/10] E-mail lu sur la page contact (azurpierre.com/contact) et au pied de page. Téléphone du site = celui fourni (04 69 00 16 12). Vérifié sur site officiel le 17/10.</t>
+        </is>
+      </c>
       <c r="Q211" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>info@azurpierre.com</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="15" customHeight="1" s="33">
-      <c r="L212" s="32" t="n"/>
+      <c r="A212" t="n">
+        <v>212</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>4e liste — importateurs (17/10)</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>3</v>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Doublon (e-commerce EdN)</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>La Maison du Pavé</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Pontarmé (60520) — même adresse qu'Européenne de Négoce</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Hauts-de-France</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Boutique e-commerce de l'Européenne de Négoce (pavés, dallages, margelles, bordures).</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>https://www.lamaisondupave.fr</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Site officiel (vérifié 17/10)</t>
+        </is>
+      </c>
+      <c r="L212" s="32" t="inlineStr">
+        <is>
+          <t>Doublon — ne pas contacter</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Aucune — passer par Européenne de Négoce uniquement</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>[17/10] MÊME entreprise que l'Européenne de Négoce (confirmé sur les deux sites : « Qui sommes-nous ? », pied de page, même adresse 5003F Route de Paris). NE PAS CONTACTER — doublon. (Adresse contact@lamaisondupave.fr décodée de la protection anti-spam : ne pas l'utiliser.)</t>
+        </is>
+      </c>
       <c r="Q212" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
     </row>
     <row r="213" ht="15" customHeight="1" s="33">
-      <c r="L213" s="32" t="n"/>
+      <c r="A213" t="n">
+        <v>213</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>4e liste — importateurs (17/10)</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>1</v>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Importateur / grossiste</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>La Pierre &amp; le Marbre</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Aubagne (13400)</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>PACA</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>Importateur-grossiste de marbre, pierre naturelle, granit près de Marseille ; pages prestations dédiées « Achat et vente de pierre d'Égypte, pierre du Sinaï » — la pierre d'Égypte est explicitement au catalogue.</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>https://lapierreetlemarbre.com</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>04 42 70 12 44</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Site officiel (vérifié 17/10)</t>
+        </is>
+      </c>
+      <c r="L213" s="32" t="inlineStr">
+        <is>
+          <t>À contacter (formulaire/tél)</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>Contacter via le formulaire https://lapierreetlemarbre.com/contact/ ou par téléphone — AUCUN e-mail publié, ne pas deviner d'adresse</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>[17/10] Aucune adresse e-mail publiée (page contact = formulaire seul ; mentions légales vides ; vérifié aussi sur l'accueil et les pages prestations). Tél 04 42 70 12 44, fax 04 42 70 12 45.</t>
+        </is>
+      </c>
       <c r="Q213" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -2657,14 +2657,22 @@
       </c>
       <c r="L25" s="53" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="M25" s="54" t="n"/>
-      <c r="N25" s="53" t="n"/>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M25" s="54" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="N25" s="53" t="inlineStr">
+        <is>
+          <t>Attendre la réponse ; pas de relance avant le 24/10</t>
+        </is>
+      </c>
       <c r="O25" s="53" t="inlineStr">
         <is>
-          <t>[13/10] Aucun e-mail propre à SNNMC publié : formulaire sur la fiche France Matériaux, ou téléphone. | [16/10] E-mail du site officiel materiaux-batiment.fr (accueil + page contact, itemprop=email). Site parfois en 503 : réessayer. Ne PAS utiliser contact@france-materiaux.fr (réseau, pas SNNMC).</t>
+          <t>[13/10] Aucun e-mail propre à SNNMC publié : formulaire sur la fiche France Matériaux, ou téléphone. | [16/10] E-mail du site officiel materiaux-batiment.fr (accueil + page contact, itemprop=email). Site parfois en 503 : réessayer. Ne PAS utiliser contact@france-materiaux.fr (réseau, pas SNNMC). E-mail de prospection MINYALA (Message A version courte) du 17/10 — sous-lot 2.</t>
         </is>
       </c>
       <c r="P25" s="55" t="n"/>
@@ -3552,7 +3560,7 @@
       </c>
       <c r="O36" s="53" t="inlineStr">
         <is>
-          <t>[13/10] Page agence de Caen du site Pillaud. | [15/10] Message A (version courte) envoyé depuis Gmail (constaté dans les éléments envoyés, voir registre-envois-2026-10-15.csv) ; remise non confirmée, aucune réponse au 16/10.</t>
+          <t>[13/10] Page agence de Caen du site Pillaud. | [15/10] Message A (version courte) envoyé depuis Gmail (constaté dans les éléments envoyés, voir registre-envois-2026-10-15.csv) ; remise non confirmée, aucune réponse au 16/10. [17/10] Mailinblack : l'envoi du 15/10 est RETENU par le filtre anti-robot du destinataire (invitations reçues 15/10) — message non remis tant que l'expéditeur n'est pas validé manuellement (action côté propriétaire).</t>
         </is>
       </c>
       <c r="P36" s="55" t="n"/>
@@ -9440,7 +9448,7 @@
       </c>
       <c r="O124" s="53" t="inlineStr">
         <is>
-          <t>[13/10] Tentative depuis Hotmail rejetée EN SORTIE (5.7.520 : contenu classé spam par Microsoft) — message non remis ; l'adresse n'est pas forcément invalide. Prochain contact depuis la boîte Gmail, nouveau modèle, jamais depuis Hotmail. | [16/10] Message A (version courte) envoyé depuis Gmail à 10h38 UTC (registre-envois-2026-10-16.csv) ; adresse précédemment visée par un rejet 5.7.520 côté Hotmail (jamais remise) : ceci est le premier contact réel. Remise non confirmée.</t>
+          <t>[13/10] Tentative depuis Hotmail rejetée EN SORTIE (5.7.520 : contenu classé spam par Microsoft) — message non remis ; l'adresse n'est pas forcément invalide. Prochain contact depuis la boîte Gmail, nouveau modèle, jamais depuis Hotmail. | [16/10] Message A (version courte) envoyé depuis Gmail à 10h38 UTC (registre-envois-2026-10-16.csv) ; adresse précédemment visée par un rejet 5.7.520 côté Hotmail (jamais remise) : ceci est le premier contact réel. Remise non confirmée. [17/10] Mailinblack : l'envoi du 16/10 est RETENU par le filtre anti-robot du destinataire (invitation reçue 16/10 10:38 UTC) — message non remis tant que l'expéditeur n'est pas validé manuellement (action côté propriétaire).</t>
         </is>
       </c>
       <c r="P124" s="55" t="n"/>
@@ -9836,14 +9844,22 @@
       </c>
       <c r="L129" s="53" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="M129" s="54" t="n"/>
-      <c r="N129" s="53" t="n"/>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M129" s="54" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="N129" s="53" t="inlineStr">
+        <is>
+          <t>Attendre la réponse ; pas de relance avant le 24/10</t>
+        </is>
+      </c>
       <c r="O129" s="53" t="inlineStr">
         <is>
-          <t>[16/10] E-mail « Espace Pro » de la fiche agence Évreux sur solmur.fr (tél. 02 32 62 94 80). Ne PAS utiliser espace.pro.bihorel@ (pied de page = siège Bihorel).</t>
+          <t>[16/10] E-mail « Espace Pro » de la fiche agence Évreux sur solmur.fr (tél. 02 32 62 94 80). Ne PAS utiliser espace.pro.bihorel@ (pied de page = siège Bihorel). E-mail de prospection MINYALA (Message A version courte) du 17/10 — sous-lot 2.</t>
         </is>
       </c>
       <c r="P129" s="55" t="n"/>
@@ -10077,14 +10093,22 @@
       </c>
       <c r="L132" s="53" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="M132" s="54" t="n"/>
-      <c r="N132" s="53" t="n"/>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M132" s="54" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="N132" s="53" t="inlineStr">
+        <is>
+          <t>Attendre la réponse ; pas de relance avant le 24/10</t>
+        </is>
+      </c>
       <c r="O132" s="53" t="inlineStr">
         <is>
-          <t>[16/10] Seule adresse affichée sur le site officiel (page contact) — semi-nominative sur hotmail.com, pas de générique. À utiliser telle quelle.</t>
+          <t>[16/10] Seule adresse affichée sur le site officiel (page contact) — semi-nominative sur hotmail.com, pas de générique. À utiliser telle quelle. E-mail de prospection MINYALA (Message A version courte) du 17/10 — sous-lot 2.</t>
         </is>
       </c>
       <c r="P132" s="55" t="n"/>
@@ -10388,14 +10412,22 @@
       </c>
       <c r="L136" s="53" t="inlineStr">
         <is>
-          <t>À contacter</t>
-        </is>
-      </c>
-      <c r="M136" s="54" t="n"/>
-      <c r="N136" s="53" t="n"/>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M136" s="54" t="inlineStr">
+        <is>
+          <t>17/10/2026</t>
+        </is>
+      </c>
+      <c r="N136" s="53" t="inlineStr">
+        <is>
+          <t>Attendre la réponse ; pas de relance avant le 24/10</t>
+        </is>
+      </c>
       <c r="O136" s="53" t="inlineStr">
         <is>
-          <t>[16/10] E-mail de l'éditeur sur sedelka.fr/mentions-legales (dpo@ réservé aux données personnelles).</t>
+          <t>[16/10] E-mail de l'éditeur sur sedelka.fr/mentions-legales (dpo@ réservé aux données personnelles). E-mail de prospection MINYALA (Message A version courte) du 17/10 — sous-lot 2.</t>
         </is>
       </c>
       <c r="P136" s="55" t="n"/>
@@ -14773,48 +14805,48 @@
       </c>
     </row>
     <row r="205" ht="15" customHeight="1" s="33">
-      <c r="A205" t="n">
+      <c r="A205" s="32" t="n">
         <v>205</v>
       </c>
-      <c r="B205" t="inlineStr">
+      <c r="B205" s="32" t="inlineStr">
         <is>
           <t>4e liste — importateurs (17/10)</t>
         </is>
       </c>
-      <c r="C205" t="n">
+      <c r="C205" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D205" t="inlineStr">
+      <c r="D205" s="32" t="inlineStr">
         <is>
           <t>Importateur / grossiste</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
+      <c r="E205" s="32" t="inlineStr">
         <is>
           <t>NR Distribution (SARL Natural Rock Distribution)</t>
         </is>
       </c>
-      <c r="F205" t="inlineStr">
+      <c r="F205" s="32" t="inlineStr">
         <is>
           <t>Avignon (84140)</t>
         </is>
       </c>
-      <c r="G205" t="inlineStr">
+      <c r="G205" s="32" t="inlineStr">
         <is>
           <t>PACA / Sud-Est</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
+      <c r="H205" s="32" t="inlineStr">
         <is>
           <t>Importateur-grossiste de travertin et pierres naturelles, livre les revendeurs pros dans toute la France depuis son parc d'Avignon ; page dédiée « Grossiste pierre d'Égypte » (pierre extraite au Sinaï) — meilleure adéquation du lot.</t>
         </is>
       </c>
-      <c r="I205" t="inlineStr">
+      <c r="I205" s="32" t="inlineStr">
         <is>
           <t>https://www.nr-distribution.fr/</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr">
+      <c r="K205" s="32" t="inlineStr">
         <is>
           <t>Site officiel (vérifié 17/10)</t>
         </is>
@@ -14824,12 +14856,12 @@
           <t>À contacter</t>
         </is>
       </c>
-      <c r="N205" t="inlineStr">
+      <c r="N205" s="32" t="inlineStr">
         <is>
           <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
         </is>
       </c>
-      <c r="O205" t="inlineStr">
+      <c r="O205" s="32" t="inlineStr">
         <is>
           <t>[17/10] E-mail lu sur les mentions légales (https://www.nr-distribution.fr/mentions-legales/) — la page contact n'a qu'un formulaire, sans e-mail ni téléphone. Page Égypte : nr-distribution.fr/nos-prestations/grossiste-pierre-degypte-en-normandie/. Vérifié sur site officiel le 17/10.</t>
         </is>
@@ -14838,55 +14870,55 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R205" t="inlineStr">
+      <c r="R205" s="32" t="inlineStr">
         <is>
           <t>nrd@nr-distribution.fr</t>
         </is>
       </c>
     </row>
     <row r="206" ht="15" customHeight="1" s="33">
-      <c r="A206" t="n">
+      <c r="A206" s="32" t="n">
         <v>206</v>
       </c>
-      <c r="B206" t="inlineStr">
+      <c r="B206" s="32" t="inlineStr">
         <is>
           <t>4e liste — importateurs (17/10)</t>
         </is>
       </c>
-      <c r="C206" t="n">
+      <c r="C206" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D206" t="inlineStr">
+      <c r="D206" s="32" t="inlineStr">
         <is>
           <t>Importateur / grossiste</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
+      <c r="E206" s="32" t="inlineStr">
         <is>
           <t>FrancePierre</t>
         </is>
       </c>
-      <c r="F206" t="inlineStr">
+      <c r="F206" s="32" t="inlineStr">
         <is>
           <t>Paris (75007) — showrooms Nîmes, Béziers, Périgueux</t>
         </is>
       </c>
-      <c r="G206" t="inlineStr">
+      <c r="G206" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
+      <c r="H206" s="32" t="inlineStr">
         <is>
           <t>Page dédiée pierre d'Égypte (variétés GALALA et SINAI PEARL) ; se présente en « fabricant de pierre naturelle — vente directe » plutôt que grossiste.</t>
         </is>
       </c>
-      <c r="I206" t="inlineStr">
+      <c r="I206" s="32" t="inlineStr">
         <is>
           <t>https://www.francepierre.fr/</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr">
+      <c r="K206" s="32" t="inlineStr">
         <is>
           <t>Site officiel (vérifié 17/10)</t>
         </is>
@@ -14896,12 +14928,12 @@
           <t>À contacter</t>
         </is>
       </c>
-      <c r="N206" t="inlineStr">
+      <c r="N206" s="32" t="inlineStr">
         <is>
           <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
         </is>
       </c>
-      <c r="O206" t="inlineStr">
+      <c r="O206" s="32" t="inlineStr">
         <is>
           <t>[17/10] E-mail confirmé sur l'accueil, le pied de page et la page Égypte (francepierre.fr/pierres-d-ailleurs/pierre-d-egypte/). Domaine francepierre.fr au registre-rejets du 12/10 (5.7.520 — jamais livré) : premier contact légitime. Positionnement « sur mesure, sans volume » — accroche lot fin de stock adaptée.</t>
         </is>
@@ -14910,60 +14942,60 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R206" t="inlineStr">
+      <c r="R206" s="32" t="inlineStr">
         <is>
           <t>contact@francepierre.fr</t>
         </is>
       </c>
     </row>
     <row r="207" ht="15" customHeight="1" s="33">
-      <c r="A207" t="n">
+      <c r="A207" s="32" t="n">
         <v>207</v>
       </c>
-      <c r="B207" t="inlineStr">
+      <c r="B207" s="32" t="inlineStr">
         <is>
           <t>4e liste — importateurs (17/10)</t>
         </is>
       </c>
-      <c r="C207" t="n">
+      <c r="C207" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="D207" s="32" t="inlineStr">
         <is>
           <t>Négoce / revendeur</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
+      <c r="E207" s="32" t="inlineStr">
         <is>
           <t>Créa Stone (CREA STONE)</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
+      <c r="F207" s="32" t="inlineStr">
         <is>
           <t>Feillens (01570) ; siège Brignoles (83170)</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
+      <c r="G207" s="32" t="inlineStr">
         <is>
           <t>Ain / Var</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
+      <c r="H207" s="32" t="inlineStr">
         <is>
           <t>« Fournisseur et grossiste de pierre naturelle » (site dallage-pierre.com ; crea-stone.com y redirige).</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr">
+      <c r="I207" s="32" t="inlineStr">
         <is>
           <t>https://dallage-pierre.com/</t>
         </is>
       </c>
-      <c r="J207" t="inlineStr">
+      <c r="J207" s="32" t="inlineStr">
         <is>
           <t>04 12 16 05 26</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr">
+      <c r="K207" s="32" t="inlineStr">
         <is>
           <t>Site officiel (vérifié 17/10)</t>
         </is>
@@ -14973,12 +15005,12 @@
           <t>À contacter</t>
         </is>
       </c>
-      <c r="N207" t="inlineStr">
+      <c r="N207" s="32" t="inlineStr">
         <is>
           <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
         </is>
       </c>
-      <c r="O207" t="inlineStr">
+      <c r="O207" s="32" t="inlineStr">
         <is>
           <t>[17/10] E-mail confirmé au pied de page de dallage-pierre.com. AUCUNE mention de l'Égypte sur le site (cite le marbre de Turquie) — ne pas le présenter comme importateur de calcaire égyptien : Message A standard uniquement, sans ligne importateur.</t>
         </is>
@@ -14987,55 +15019,55 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R207" t="inlineStr">
+      <c r="R207" s="32" t="inlineStr">
         <is>
           <t>info@crea-stone.com</t>
         </is>
       </c>
     </row>
     <row r="208" ht="15" customHeight="1" s="33">
-      <c r="A208" t="n">
+      <c r="A208" s="32" t="n">
         <v>208</v>
       </c>
-      <c r="B208" t="inlineStr">
+      <c r="B208" s="32" t="inlineStr">
         <is>
           <t>4e liste — importateurs (17/10)</t>
         </is>
       </c>
-      <c r="C208" t="n">
+      <c r="C208" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D208" t="inlineStr">
+      <c r="D208" s="32" t="inlineStr">
         <is>
           <t>Importateur / grossiste</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
+      <c r="E208" s="32" t="inlineStr">
         <is>
           <t>ELK International</t>
         </is>
       </c>
-      <c r="F208" t="inlineStr">
+      <c r="F208" s="32" t="inlineStr">
         <is>
           <t>La Roche-Jaudy (22450)</t>
         </is>
       </c>
-      <c r="G208" t="inlineStr">
+      <c r="G208" s="32" t="inlineStr">
         <is>
           <t>Bretagne</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
+      <c r="H208" s="32" t="inlineStr">
         <is>
           <t>« Importateur direct de pierre naturelle » (2 500+ conteneurs importés, approvisionnement direct en carrière/usine) ; « PIERRE D'EGYPTE » figure au catalogue.</t>
         </is>
       </c>
-      <c r="I208" t="inlineStr">
+      <c r="I208" s="32" t="inlineStr">
         <is>
           <t>https://www.elk-international.com</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr">
+      <c r="K208" s="32" t="inlineStr">
         <is>
           <t>Site officiel (vérifié 17/10)</t>
         </is>
@@ -15045,12 +15077,12 @@
           <t>À contacter</t>
         </is>
       </c>
-      <c r="N208" t="inlineStr">
+      <c r="N208" s="32" t="inlineStr">
         <is>
           <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
         </is>
       </c>
-      <c r="O208" t="inlineStr">
+      <c r="O208" s="32" t="inlineStr">
         <is>
           <t>[17/10] E-mail lu sur la page d'accueil du site officiel. Gamme : grès, granit, ardoise, porphyre, calcaire, travertin. Vérifié sur site officiel le 17/10.</t>
         </is>
@@ -15059,60 +15091,60 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R208" t="inlineStr">
+      <c r="R208" s="32" t="inlineStr">
         <is>
           <t>contact@elk-international.com</t>
         </is>
       </c>
     </row>
     <row r="209" ht="15" customHeight="1" s="33">
-      <c r="A209" t="n">
+      <c r="A209" s="32" t="n">
         <v>209</v>
       </c>
-      <c r="B209" t="inlineStr">
+      <c r="B209" s="32" t="inlineStr">
         <is>
           <t>4e liste — importateurs (17/10)</t>
         </is>
       </c>
-      <c r="C209" t="n">
+      <c r="C209" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D209" s="32" t="inlineStr">
         <is>
           <t>Importateur / grossiste</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
+      <c r="E209" s="32" t="inlineStr">
         <is>
           <t>Stones Partner</t>
         </is>
       </c>
-      <c r="F209" t="inlineStr">
+      <c r="F209" s="32" t="inlineStr">
         <is>
           <t>Mouazé (35250)</t>
         </is>
       </c>
-      <c r="G209" t="inlineStr">
+      <c r="G209" s="32" t="inlineStr">
         <is>
           <t>Bretagne</t>
         </is>
       </c>
-      <c r="H209" t="inlineStr">
+      <c r="H209" s="32" t="inlineStr">
         <is>
           <t>Importateur B2B pour distributeurs de matériaux d'aménagement, « commander en container ou en commande groupée » ; l'Égypte figure parmi ses « Pays Partner ».</t>
         </is>
       </c>
-      <c r="I209" t="inlineStr">
+      <c r="I209" s="32" t="inlineStr">
         <is>
           <t>https://www.stonespartner.com</t>
         </is>
       </c>
-      <c r="J209" t="inlineStr">
+      <c r="J209" s="32" t="inlineStr">
         <is>
           <t>02 99 54 97 50</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr">
+      <c r="K209" s="32" t="inlineStr">
         <is>
           <t>Site officiel (vérifié 17/10)</t>
         </is>
@@ -15122,12 +15154,12 @@
           <t>À contacter</t>
         </is>
       </c>
-      <c r="N209" t="inlineStr">
+      <c r="N209" s="32" t="inlineStr">
         <is>
           <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
         </is>
       </c>
-      <c r="O209" t="inlineStr">
+      <c r="O209" s="32" t="inlineStr">
         <is>
           <t>[17/10] E-mail lu sur le site officiel. Gammes : travertin, grès, tandur, ardoise, parements. Vérifié sur site officiel le 17/10.</t>
         </is>
@@ -15136,55 +15168,55 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R209" t="inlineStr">
+      <c r="R209" s="32" t="inlineStr">
         <is>
           <t>contact@stonespartner.com</t>
         </is>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1" s="33">
-      <c r="A210" t="n">
+      <c r="A210" s="32" t="n">
         <v>210</v>
       </c>
-      <c r="B210" t="inlineStr">
+      <c r="B210" s="32" t="inlineStr">
         <is>
           <t>4e liste — importateurs (17/10)</t>
         </is>
       </c>
-      <c r="C210" t="n">
+      <c r="C210" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D210" t="inlineStr">
+      <c r="D210" s="32" t="inlineStr">
         <is>
           <t>Importateur / grossiste</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
+      <c r="E210" s="32" t="inlineStr">
         <is>
           <t>Européenne de Négoce</t>
         </is>
       </c>
-      <c r="F210" t="inlineStr">
+      <c r="F210" s="32" t="inlineStr">
         <is>
           <t>Pontarmé (60520)</t>
         </is>
       </c>
-      <c r="G210" t="inlineStr">
+      <c r="G210" s="32" t="inlineStr">
         <is>
           <t>Hauts-de-France</t>
         </is>
       </c>
-      <c r="H210" t="inlineStr">
+      <c r="H210" s="32" t="inlineStr">
         <is>
           <t>« Distributeur et importateur de pierres naturelles » (pavés, bordures, dallages ; catégorie pavés calcaire) avec parc de stockage à Pontarmé (~12 000 m² selon Opalis — le chiffre de 40 000 m² n'est pas confirmé).</t>
         </is>
       </c>
-      <c r="I210" t="inlineStr">
+      <c r="I210" s="32" t="inlineStr">
         <is>
           <t>https://www.europeennedenegoce.fr</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr">
+      <c r="K210" s="32" t="inlineStr">
         <is>
           <t>Site officiel (vérifié 17/10)</t>
         </is>
@@ -15194,12 +15226,12 @@
           <t>À contacter</t>
         </is>
       </c>
-      <c r="N210" t="inlineStr">
+      <c r="N210" s="32" t="inlineStr">
         <is>
           <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
         </is>
       </c>
-      <c r="O210" t="inlineStr">
+      <c r="O210" s="32" t="inlineStr">
         <is>
           <t>[17/10] E-mail lu en clair sur europeennedenegoce.fr. Contacter UNIQUEMENT europeennedenegoce@orange.fr — La Maison du Pavé (lamaisondupave.fr) est la MÊME entreprise (même adresse à Pontarmé, confirmé sur les deux sites) : jamais les deux adresses.</t>
         </is>
@@ -15208,60 +15240,60 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R210" t="inlineStr">
+      <c r="R210" s="32" t="inlineStr">
         <is>
           <t>europeennedenegoce@orange.fr</t>
         </is>
       </c>
     </row>
     <row r="211" ht="15" customHeight="1" s="33">
-      <c r="A211" t="n">
+      <c r="A211" s="32" t="n">
         <v>211</v>
       </c>
-      <c r="B211" t="inlineStr">
+      <c r="B211" s="32" t="inlineStr">
         <is>
           <t>4e liste — importateurs (17/10)</t>
         </is>
       </c>
-      <c r="C211" t="n">
+      <c r="C211" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D211" t="inlineStr">
+      <c r="D211" s="32" t="inlineStr">
         <is>
           <t>Importateur / grossiste</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
+      <c r="E211" s="32" t="inlineStr">
         <is>
           <t>Azur Pierre Agencement</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
+      <c r="F211" s="32" t="inlineStr">
         <is>
           <t>Grasse (06130)</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="G211" s="32" t="inlineStr">
         <is>
           <t>PACA</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
+      <c r="H211" s="32" t="inlineStr">
         <is>
           <t>Importateur-grossiste approvisionné « directement depuis les carrières partenaires » : « arrivages réguliers de pierres calcaires d'Égypte … en gros », « dalles calcaires égyptiennes en grand format » — très bonne adéquation.</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
+      <c r="I211" s="32" t="inlineStr">
         <is>
           <t>https://www.azurpierre.com</t>
         </is>
       </c>
-      <c r="J211" t="inlineStr">
+      <c r="J211" s="32" t="inlineStr">
         <is>
           <t>04 69 00 16 12</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr">
+      <c r="K211" s="32" t="inlineStr">
         <is>
           <t>Site officiel (vérifié 17/10)</t>
         </is>
@@ -15271,12 +15303,12 @@
           <t>À contacter</t>
         </is>
       </c>
-      <c r="N211" t="inlineStr">
+      <c r="N211" s="32" t="inlineStr">
         <is>
           <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
         </is>
       </c>
-      <c r="O211" t="inlineStr">
+      <c r="O211" s="32" t="inlineStr">
         <is>
           <t>[17/10] E-mail lu sur la page contact (azurpierre.com/contact) et au pied de page. Téléphone du site = celui fourni (04 69 00 16 12). Vérifié sur site officiel le 17/10.</t>
         </is>
@@ -15285,55 +15317,55 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R211" t="inlineStr">
+      <c r="R211" s="32" t="inlineStr">
         <is>
           <t>info@azurpierre.com</t>
         </is>
       </c>
     </row>
     <row r="212" ht="15" customHeight="1" s="33">
-      <c r="A212" t="n">
+      <c r="A212" s="32" t="n">
         <v>212</v>
       </c>
-      <c r="B212" t="inlineStr">
+      <c r="B212" s="32" t="inlineStr">
         <is>
           <t>4e liste — importateurs (17/10)</t>
         </is>
       </c>
-      <c r="C212" t="n">
+      <c r="C212" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="D212" t="inlineStr">
+      <c r="D212" s="32" t="inlineStr">
         <is>
           <t>Doublon (e-commerce EdN)</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
+      <c r="E212" s="32" t="inlineStr">
         <is>
           <t>La Maison du Pavé</t>
         </is>
       </c>
-      <c r="F212" t="inlineStr">
+      <c r="F212" s="32" t="inlineStr">
         <is>
           <t>Pontarmé (60520) — même adresse qu'Européenne de Négoce</t>
         </is>
       </c>
-      <c r="G212" t="inlineStr">
+      <c r="G212" s="32" t="inlineStr">
         <is>
           <t>Hauts-de-France</t>
         </is>
       </c>
-      <c r="H212" t="inlineStr">
+      <c r="H212" s="32" t="inlineStr">
         <is>
           <t>Boutique e-commerce de l'Européenne de Négoce (pavés, dallages, margelles, bordures).</t>
         </is>
       </c>
-      <c r="I212" t="inlineStr">
+      <c r="I212" s="32" t="inlineStr">
         <is>
           <t>https://www.lamaisondupave.fr</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr">
+      <c r="K212" s="32" t="inlineStr">
         <is>
           <t>Site officiel (vérifié 17/10)</t>
         </is>
@@ -15343,12 +15375,12 @@
           <t>Doublon — ne pas contacter</t>
         </is>
       </c>
-      <c r="N212" t="inlineStr">
+      <c r="N212" s="32" t="inlineStr">
         <is>
           <t>Aucune — passer par Européenne de Négoce uniquement</t>
         </is>
       </c>
-      <c r="O212" t="inlineStr">
+      <c r="O212" s="32" t="inlineStr">
         <is>
           <t>[17/10] MÊME entreprise que l'Européenne de Négoce (confirmé sur les deux sites : « Qui sommes-nous ? », pied de page, même adresse 5003F Route de Paris). NE PAS CONTACTER — doublon. (Adresse contact@lamaisondupave.fr décodée de la protection anti-spam : ne pas l'utiliser.)</t>
         </is>
@@ -15359,53 +15391,53 @@
       </c>
     </row>
     <row r="213" ht="15" customHeight="1" s="33">
-      <c r="A213" t="n">
+      <c r="A213" s="32" t="n">
         <v>213</v>
       </c>
-      <c r="B213" t="inlineStr">
+      <c r="B213" s="32" t="inlineStr">
         <is>
           <t>4e liste — importateurs (17/10)</t>
         </is>
       </c>
-      <c r="C213" t="n">
+      <c r="C213" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D213" t="inlineStr">
+      <c r="D213" s="32" t="inlineStr">
         <is>
           <t>Importateur / grossiste</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
+      <c r="E213" s="32" t="inlineStr">
         <is>
           <t>La Pierre &amp; le Marbre</t>
         </is>
       </c>
-      <c r="F213" t="inlineStr">
+      <c r="F213" s="32" t="inlineStr">
         <is>
           <t>Aubagne (13400)</t>
         </is>
       </c>
-      <c r="G213" t="inlineStr">
+      <c r="G213" s="32" t="inlineStr">
         <is>
           <t>PACA</t>
         </is>
       </c>
-      <c r="H213" t="inlineStr">
+      <c r="H213" s="32" t="inlineStr">
         <is>
           <t>Importateur-grossiste de marbre, pierre naturelle, granit près de Marseille ; pages prestations dédiées « Achat et vente de pierre d'Égypte, pierre du Sinaï » — la pierre d'Égypte est explicitement au catalogue.</t>
         </is>
       </c>
-      <c r="I213" t="inlineStr">
+      <c r="I213" s="32" t="inlineStr">
         <is>
           <t>https://lapierreetlemarbre.com</t>
         </is>
       </c>
-      <c r="J213" t="inlineStr">
+      <c r="J213" s="32" t="inlineStr">
         <is>
           <t>04 42 70 12 44</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr">
+      <c r="K213" s="32" t="inlineStr">
         <is>
           <t>Site officiel (vérifié 17/10)</t>
         </is>
@@ -15415,12 +15447,12 @@
           <t>À contacter (formulaire/tél)</t>
         </is>
       </c>
-      <c r="N213" t="inlineStr">
+      <c r="N213" s="32" t="inlineStr">
         <is>
           <t>Contacter via le formulaire https://lapierreetlemarbre.com/contact/ ou par téléphone — AUCUN e-mail publié, ne pas deviner d'adresse</t>
         </is>
       </c>
-      <c r="O213" t="inlineStr">
+      <c r="O213" s="32" t="inlineStr">
         <is>
           <t>[17/10] Aucune adresse e-mail publiée (page contact = formulaire seul ; mentions légales vides ; vérifié aussi sur l'accueil et les pages prestations). Tél 04 42 70 12 44, fax 04 42 70 12 45.</t>
         </is>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -14853,17 +14853,22 @@
       </c>
       <c r="L205" s="32" t="inlineStr">
         <is>
-          <t>À contacter</t>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="N205" s="32" t="inlineStr">
         <is>
-          <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
+          <t>Attendre la réponse ; pas de relance avant le 31/10</t>
         </is>
       </c>
       <c r="O205" s="32" t="inlineStr">
         <is>
-          <t>[17/10] E-mail lu sur les mentions légales (https://www.nr-distribution.fr/mentions-legales/) — la page contact n'a qu'un formulaire, sans e-mail ni téléphone. Page Égypte : nr-distribution.fr/nos-prestations/grossiste-pierre-degypte-en-normandie/. Vérifié sur site officiel le 17/10.</t>
+          <t>[17/10] E-mail lu sur les mentions légales (https://www.nr-distribution.fr/mentions-legales/) — la page contact n'a qu'un formulaire, sans e-mail ni téléphone. Page Égypte : nr-distribution.fr/nos-prestations/grossiste-pierre-degypte-en-normandie/. Vérifié sur site officiel le 17/10. E-mail de prospection MINYALA (Message A + ligne importateur ; Créa Stone sans la ligne) du 24/10 — connecteur Gmail direct.</t>
         </is>
       </c>
       <c r="Q205" s="44">
@@ -14925,17 +14930,22 @@
       </c>
       <c r="L206" s="32" t="inlineStr">
         <is>
-          <t>À contacter</t>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="N206" s="32" t="inlineStr">
         <is>
-          <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
+          <t>Attendre la réponse ; pas de relance avant le 31/10</t>
         </is>
       </c>
       <c r="O206" s="32" t="inlineStr">
         <is>
-          <t>[17/10] E-mail confirmé sur l'accueil, le pied de page et la page Égypte (francepierre.fr/pierres-d-ailleurs/pierre-d-egypte/). Domaine francepierre.fr au registre-rejets du 12/10 (5.7.520 — jamais livré) : premier contact légitime. Positionnement « sur mesure, sans volume » — accroche lot fin de stock adaptée.</t>
+          <t>[17/10] E-mail confirmé sur l'accueil, le pied de page et la page Égypte (francepierre.fr/pierres-d-ailleurs/pierre-d-egypte/). Domaine francepierre.fr au registre-rejets du 12/10 (5.7.520 — jamais livré) : premier contact légitime. Positionnement « sur mesure, sans volume » — accroche lot fin de stock adaptée. E-mail de prospection MINYALA (Message A + ligne importateur ; Créa Stone sans la ligne) du 24/10 — connecteur Gmail direct.</t>
         </is>
       </c>
       <c r="Q206" s="44">
@@ -15002,17 +15012,22 @@
       </c>
       <c r="L207" s="32" t="inlineStr">
         <is>
-          <t>À contacter</t>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="N207" s="32" t="inlineStr">
         <is>
-          <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
+          <t>Attendre la réponse ; pas de relance avant le 31/10</t>
         </is>
       </c>
       <c r="O207" s="32" t="inlineStr">
         <is>
-          <t>[17/10] E-mail confirmé au pied de page de dallage-pierre.com. AUCUNE mention de l'Égypte sur le site (cite le marbre de Turquie) — ne pas le présenter comme importateur de calcaire égyptien : Message A standard uniquement, sans ligne importateur.</t>
+          <t>[17/10] E-mail confirmé au pied de page de dallage-pierre.com. AUCUNE mention de l'Égypte sur le site (cite le marbre de Turquie) — ne pas le présenter comme importateur de calcaire égyptien : Message A standard uniquement, sans ligne importateur. E-mail de prospection MINYALA (Message A + ligne importateur ; Créa Stone sans la ligne) du 24/10 — connecteur Gmail direct.</t>
         </is>
       </c>
       <c r="Q207" s="44">
@@ -15074,17 +15089,22 @@
       </c>
       <c r="L208" s="32" t="inlineStr">
         <is>
-          <t>À contacter</t>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="N208" s="32" t="inlineStr">
         <is>
-          <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
+          <t>Attendre la réponse ; pas de relance avant le 31/10</t>
         </is>
       </c>
       <c r="O208" s="32" t="inlineStr">
         <is>
-          <t>[17/10] E-mail lu sur la page d'accueil du site officiel. Gamme : grès, granit, ardoise, porphyre, calcaire, travertin. Vérifié sur site officiel le 17/10.</t>
+          <t>[17/10] E-mail lu sur la page d'accueil du site officiel. Gamme : grès, granit, ardoise, porphyre, calcaire, travertin. Vérifié sur site officiel le 17/10. E-mail de prospection MINYALA (Message A + ligne importateur ; Créa Stone sans la ligne) du 24/10 — connecteur Gmail direct.</t>
         </is>
       </c>
       <c r="Q208" s="44">
@@ -15151,17 +15171,22 @@
       </c>
       <c r="L209" s="32" t="inlineStr">
         <is>
-          <t>À contacter</t>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="N209" s="32" t="inlineStr">
         <is>
-          <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
+          <t>Attendre la réponse ; pas de relance avant le 31/10</t>
         </is>
       </c>
       <c r="O209" s="32" t="inlineStr">
         <is>
-          <t>[17/10] E-mail lu sur le site officiel. Gammes : travertin, grès, tandur, ardoise, parements. Vérifié sur site officiel le 17/10.</t>
+          <t>[17/10] E-mail lu sur le site officiel. Gammes : travertin, grès, tandur, ardoise, parements. Vérifié sur site officiel le 17/10. E-mail de prospection MINYALA (Message A + ligne importateur ; Créa Stone sans la ligne) du 24/10 — connecteur Gmail direct.</t>
         </is>
       </c>
       <c r="Q209" s="44">
@@ -15223,17 +15248,22 @@
       </c>
       <c r="L210" s="32" t="inlineStr">
         <is>
-          <t>À contacter</t>
+          <t>En négociation — canal propriétaire (Hotmail)</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>19/10/2026</t>
         </is>
       </c>
       <c r="N210" s="32" t="inlineStr">
         <is>
-          <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
+          <t>NE PAS prospecter — négociation en cours menée par Joseph depuis joseph.hanna@hotmail.fr (fil « MINYALA - À l'attention du service achats »)</t>
         </is>
       </c>
       <c r="O210" s="32" t="inlineStr">
         <is>
-          <t>[17/10] E-mail lu en clair sur europeennedenegoce.fr. Contacter UNIQUEMENT europeennedenegoce@orange.fr — La Maison du Pavé (lamaisondupave.fr) est la MÊME entreprise (même adresse à Pontarmé, confirmé sur les deux sites) : jamais les deux adresses.</t>
+          <t>[17/10] E-mail lu en clair sur europeennedenegoce.fr. Contacter UNIQUEMENT europeennedenegoce@orange.fr — La Maison du Pavé (lamaisondupave.fr) est la MÊME entreprise (même adresse à Pontarmé, confirmé sur les deux sites) : jamais les deux adresses. [24/10] Négociation DÉJÀ EN COURS, découverte dans Gmail (cc info@pierredegypte.online) : 19/10 proposition du propriétaire 1 500 m² à 25,90 €/m² livraison Pontarmé incluse, prix ferme ; 19/10 justification vs 35 €/m² public (2 cm vs 1,2 cm) ; 22/10 PHOTOS du lot envoyées (prises le jour même) avec invitation à faire une offre. Une seule voie de contact : le fil Hotmail du propriétaire. Retiré du lot d'envoi du 24/10.</t>
         </is>
       </c>
       <c r="Q210" s="44">
@@ -15300,17 +15330,22 @@
       </c>
       <c r="L211" s="32" t="inlineStr">
         <is>
-          <t>À contacter</t>
+          <t>Contacté</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>24/10/2026</t>
         </is>
       </c>
       <c r="N211" s="32" t="inlineStr">
         <is>
-          <t>Envoi programmé lundi 19/10 (Message A + ligne importateur, ≤10/jour, contrôles standard avant envoi)</t>
+          <t>Attendre la réponse ; pas de relance avant le 31/10</t>
         </is>
       </c>
       <c r="O211" s="32" t="inlineStr">
         <is>
-          <t>[17/10] E-mail lu sur la page contact (azurpierre.com/contact) et au pied de page. Téléphone du site = celui fourni (04 69 00 16 12). Vérifié sur site officiel le 17/10.</t>
+          <t>[17/10] E-mail lu sur la page contact (azurpierre.com/contact) et au pied de page. Téléphone du site = celui fourni (04 69 00 16 12). Vérifié sur site officiel le 17/10. E-mail de prospection MINYALA (Message A + ligne importateur ; Créa Stone sans la ligne) du 24/10 — connecteur Gmail direct.</t>
         </is>
       </c>
       <c r="Q211" s="44">

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -14856,7 +14856,7 @@
           <t>Contacté</t>
         </is>
       </c>
-      <c r="M205" t="inlineStr">
+      <c r="M205" s="32" t="inlineStr">
         <is>
           <t>24/10/2026</t>
         </is>
@@ -14930,22 +14930,22 @@
       </c>
       <c r="L206" s="32" t="inlineStr">
         <is>
-          <t>Contacté</t>
-        </is>
-      </c>
-      <c r="M206" t="inlineStr">
+          <t>En négociation</t>
+        </is>
+      </c>
+      <c r="M206" s="32" t="inlineStr">
         <is>
           <t>24/10/2026</t>
         </is>
       </c>
       <c r="N206" s="32" t="inlineStr">
         <is>
-          <t>Attendre la réponse ; pas de relance avant le 31/10</t>
+          <t>Relancer ou appeler Laurent Plainchamp (06 79 17 55 43) si silence — dernier mot à nous le 24/10 11:31 UTC</t>
         </is>
       </c>
       <c r="O206" s="32" t="inlineStr">
         <is>
-          <t>[17/10] E-mail confirmé sur l'accueil, le pied de page et la page Égypte (francepierre.fr/pierres-d-ailleurs/pierre-d-egypte/). Domaine francepierre.fr au registre-rejets du 12/10 (5.7.520 — jamais livré) : premier contact légitime. Positionnement « sur mesure, sans volume » — accroche lot fin de stock adaptée. E-mail de prospection MINYALA (Message A + ligne importateur ; Créa Stone sans la ligne) du 24/10 — connecteur Gmail direct.</t>
+          <t>[17/10] E-mail confirmé sur l'accueil, le pied de page et la page Égypte (francepierre.fr/pierres-d-ailleurs/pierre-d-egypte/). Domaine francepierre.fr au registre-rejets du 12/10 (5.7.520 — jamais livré) : premier contact légitime. Positionnement « sur mesure, sans volume » — accroche lot fin de stock adaptée. E-mail de prospection MINYALA (Message A + ligne importateur ; Créa Stone sans la ligne) du 24/10 — connecteur Gmail direct. [25/10] RÉPONSE le 24/10 (1 min après l'envoi !) — Laurent PLAINCHAMP, 06 79 17 55 43, francepierrecontact@gmail.com : « En dallage pourquoi pas » ; achète les dallages à 14 € HT. Négociation menée par le propriétaire depuis la boîte le 24/10 : offre faite 14 € HT/m² × 500 m² = 7 000 € HT, enlèvement par leurs soins, 30 % d'acompte ; FP « Non, nous pensions avoir mieux » ; tenue du 14 € (11:31 UTC). Dernier mot à nous — relance/appel conseillé si silence. NE PAS re-prospecter : négociation en cours.</t>
         </is>
       </c>
       <c r="Q206" s="44">
@@ -15015,7 +15015,7 @@
           <t>Contacté</t>
         </is>
       </c>
-      <c r="M207" t="inlineStr">
+      <c r="M207" s="32" t="inlineStr">
         <is>
           <t>24/10/2026</t>
         </is>
@@ -15092,7 +15092,7 @@
           <t>Contacté</t>
         </is>
       </c>
-      <c r="M208" t="inlineStr">
+      <c r="M208" s="32" t="inlineStr">
         <is>
           <t>24/10/2026</t>
         </is>
@@ -15174,7 +15174,7 @@
           <t>Contacté</t>
         </is>
       </c>
-      <c r="M209" t="inlineStr">
+      <c r="M209" s="32" t="inlineStr">
         <is>
           <t>24/10/2026</t>
         </is>
@@ -15251,7 +15251,7 @@
           <t>En négociation — canal propriétaire (Hotmail)</t>
         </is>
       </c>
-      <c r="M210" t="inlineStr">
+      <c r="M210" s="32" t="inlineStr">
         <is>
           <t>19/10/2026</t>
         </is>
@@ -15333,7 +15333,7 @@
           <t>Contacté</t>
         </is>
       </c>
-      <c r="M211" t="inlineStr">
+      <c r="M211" s="32" t="inlineStr">
         <is>
           <t>24/10/2026</t>
         </is>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -3555,12 +3555,12 @@
       </c>
       <c r="N36" s="53" t="inlineStr">
         <is>
-          <t>Attendre la réponse ; pas de relance avant le 22/10</t>
+          <t>Attendre la réponse ; pas de relance avant le 01/11 (message remis le 25/10 après validation Mailinblack)</t>
         </is>
       </c>
       <c r="O36" s="53" t="inlineStr">
         <is>
-          <t>[13/10] Page agence de Caen du site Pillaud. | [15/10] Message A (version courte) envoyé depuis Gmail (constaté dans les éléments envoyés, voir registre-envois-2026-10-15.csv) ; remise non confirmée, aucune réponse au 16/10. [17/10] Mailinblack : l'envoi du 15/10 est RETENU par le filtre anti-robot du destinataire (invitations reçues 15/10) — message non remis tant que l'expéditeur n'est pas validé manuellement (action côté propriétaire).</t>
+          <t>[13/10] Page agence de Caen du site Pillaud. | [15/10] Message A (version courte) envoyé depuis Gmail (constaté dans les éléments envoyés, voir registre-envois-2026-10-15.csv) ; remise non confirmée, aucune réponse au 16/10. [17/10] Mailinblack : l'envoi du 15/10 est RETENU par le filtre anti-robot du destinataire (invitations reçues 15/10) — message non remis tant que l'expéditeur n'est pas validé manuellement (action côté propriétaire). [25/10] Mailinblack VALIDÉ par le propriétaire le 25/10 — le message initial est maintenant remis en boîte de réception. Horloge de réponse repartie du 25/10 : pas de relance avant le 01/11.</t>
         </is>
       </c>
       <c r="P36" s="55" t="n"/>
@@ -9443,12 +9443,12 @@
       </c>
       <c r="N124" s="53" t="inlineStr">
         <is>
-          <t>Attendre la réponse ; pas de relance avant le 23/10</t>
+          <t>Attendre la réponse ; pas de relance avant le 01/11 (message remis le 25/10 après validation Mailinblack)</t>
         </is>
       </c>
       <c r="O124" s="53" t="inlineStr">
         <is>
-          <t>[13/10] Tentative depuis Hotmail rejetée EN SORTIE (5.7.520 : contenu classé spam par Microsoft) — message non remis ; l'adresse n'est pas forcément invalide. Prochain contact depuis la boîte Gmail, nouveau modèle, jamais depuis Hotmail. | [16/10] Message A (version courte) envoyé depuis Gmail à 10h38 UTC (registre-envois-2026-10-16.csv) ; adresse précédemment visée par un rejet 5.7.520 côté Hotmail (jamais remise) : ceci est le premier contact réel. Remise non confirmée. [17/10] Mailinblack : l'envoi du 16/10 est RETENU par le filtre anti-robot du destinataire (invitation reçue 16/10 10:38 UTC) — message non remis tant que l'expéditeur n'est pas validé manuellement (action côté propriétaire).</t>
+          <t>[13/10] Tentative depuis Hotmail rejetée EN SORTIE (5.7.520 : contenu classé spam par Microsoft) — message non remis ; l'adresse n'est pas forcément invalide. Prochain contact depuis la boîte Gmail, nouveau modèle, jamais depuis Hotmail. | [16/10] Message A (version courte) envoyé depuis Gmail à 10h38 UTC (registre-envois-2026-10-16.csv) ; adresse précédemment visée par un rejet 5.7.520 côté Hotmail (jamais remise) : ceci est le premier contact réel. Remise non confirmée. [17/10] Mailinblack : l'envoi du 16/10 est RETENU par le filtre anti-robot du destinataire (invitation reçue 16/10 10:38 UTC) — message non remis tant que l'expéditeur n'est pas validé manuellement (action côté propriétaire). [25/10] Mailinblack VALIDÉ par le propriétaire le 25/10 — le message initial est maintenant remis en boîte de réception. Horloge de réponse repartie du 25/10 : pas de relance avant le 01/11.</t>
         </is>
       </c>
       <c r="P124" s="55" t="n"/>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -3560,7 +3560,7 @@
       </c>
       <c r="O36" s="53" t="inlineStr">
         <is>
-          <t>[13/10] Page agence de Caen du site Pillaud. | [15/10] Message A (version courte) envoyé depuis Gmail (constaté dans les éléments envoyés, voir registre-envois-2026-10-15.csv) ; remise non confirmée, aucune réponse au 16/10. [17/10] Mailinblack : l'envoi du 15/10 est RETENU par le filtre anti-robot du destinataire (invitations reçues 15/10) — message non remis tant que l'expéditeur n'est pas validé manuellement (action côté propriétaire). [25/10] Mailinblack VALIDÉ par le propriétaire le 25/10 — le message initial est maintenant remis en boîte de réception. Horloge de réponse repartie du 25/10 : pas de relance avant le 01/11.</t>
+          <t>[13/10] Page agence de Caen du site Pillaud. | [15/10] Message A (version courte) envoyé depuis Gmail (constaté dans les éléments envoyés, voir registre-envois-2026-10-15.csv) ; remise non confirmée, aucune réponse au 16/10. [17/10] Mailinblack : l'envoi du 15/10 est RETENU par le filtre anti-robot du destinataire (invitations reçues 15/10) — message non remis tant que l'expéditeur n'est pas validé manuellement (action côté propriétaire). [25/10] Mailinblack VALIDÉ par le propriétaire le 25/10 — le message initial est maintenant remis en boîte de réception. Horloge de réponse repartie du 25/10 : pas de relance avant le 01/11. Preuve de retenue : invitations Mailinblack du 15/10 10:52/11:07 UTC, Gmail ids 1a13f3269baf04e3 et 1a13f3ed5f4dd439.</t>
         </is>
       </c>
       <c r="P36" s="55" t="n"/>
@@ -9448,7 +9448,7 @@
       </c>
       <c r="O124" s="53" t="inlineStr">
         <is>
-          <t>[13/10] Tentative depuis Hotmail rejetée EN SORTIE (5.7.520 : contenu classé spam par Microsoft) — message non remis ; l'adresse n'est pas forcément invalide. Prochain contact depuis la boîte Gmail, nouveau modèle, jamais depuis Hotmail. | [16/10] Message A (version courte) envoyé depuis Gmail à 10h38 UTC (registre-envois-2026-10-16.csv) ; adresse précédemment visée par un rejet 5.7.520 côté Hotmail (jamais remise) : ceci est le premier contact réel. Remise non confirmée. [17/10] Mailinblack : l'envoi du 16/10 est RETENU par le filtre anti-robot du destinataire (invitation reçue 16/10 10:38 UTC) — message non remis tant que l'expéditeur n'est pas validé manuellement (action côté propriétaire). [25/10] Mailinblack VALIDÉ par le propriétaire le 25/10 — le message initial est maintenant remis en boîte de réception. Horloge de réponse repartie du 25/10 : pas de relance avant le 01/11.</t>
+          <t>[13/10] Tentative depuis Hotmail rejetée EN SORTIE (5.7.520 : contenu classé spam par Microsoft) — message non remis ; l'adresse n'est pas forcément invalide. Prochain contact depuis la boîte Gmail, nouveau modèle, jamais depuis Hotmail. | [16/10] Message A (version courte) envoyé depuis Gmail à 10h38 UTC (registre-envois-2026-10-16.csv) ; adresse précédemment visée par un rejet 5.7.520 côté Hotmail (jamais remise) : ceci est le premier contact réel. Remise non confirmée. [17/10] Mailinblack : l'envoi du 16/10 est RETENU par le filtre anti-robot du destinataire (invitation reçue 16/10 10:38 UTC) — message non remis tant que l'expéditeur n'est pas validé manuellement (action côté propriétaire). [25/10] Mailinblack VALIDÉ par le propriétaire le 25/10 — le message initial est maintenant remis en boîte de réception. Horloge de réponse repartie du 25/10 : pas de relance avant le 01/11. Preuve de retenue : invitation Mailinblack du 16/10 10:38 UTC, Gmail id 1a1444aca3b8edcd.</t>
         </is>
       </c>
       <c r="P124" s="55" t="n"/>
@@ -14945,7 +14945,7 @@
       </c>
       <c r="O206" s="32" t="inlineStr">
         <is>
-          <t>[17/10] E-mail confirmé sur l'accueil, le pied de page et la page Égypte (francepierre.fr/pierres-d-ailleurs/pierre-d-egypte/). Domaine francepierre.fr au registre-rejets du 12/10 (5.7.520 — jamais livré) : premier contact légitime. Positionnement « sur mesure, sans volume » — accroche lot fin de stock adaptée. E-mail de prospection MINYALA (Message A + ligne importateur ; Créa Stone sans la ligne) du 24/10 — connecteur Gmail direct. [25/10] RÉPONSE le 24/10 (1 min après l'envoi !) — Laurent PLAINCHAMP, 06 79 17 55 43, francepierrecontact@gmail.com : « En dallage pourquoi pas » ; achète les dallages à 14 € HT. Négociation menée par le propriétaire depuis la boîte le 24/10 : offre faite 14 € HT/m² × 500 m² = 7 000 € HT, enlèvement par leurs soins, 30 % d'acompte ; FP « Non, nous pensions avoir mieux » ; tenue du 14 € (11:31 UTC). Dernier mot à nous — relance/appel conseillé si silence. NE PAS re-prospecter : négociation en cours.</t>
+          <t>[17/10] E-mail confirmé sur l'accueil, le pied de page et la page Égypte (francepierre.fr/pierres-d-ailleurs/pierre-d-egypte/). Domaine francepierre.fr au registre-rejets du 12/10 (5.7.520 — jamais livré) : premier contact légitime. Positionnement « sur mesure, sans volume » — accroche lot fin de stock adaptée. E-mail de prospection MINYALA (Message A + ligne importateur ; Créa Stone sans la ligne) du 24/10 — connecteur Gmail direct. [25/10] RÉPONSE le 24/10 (1 min après l'envoi !) — Laurent PLAINCHAMP, 06 79 17 55 43, francepierrecontact@gmail.com : « En dallage pourquoi pas » ; achète les dallages à 14 € HT. Négociation menée par le propriétaire depuis la boîte le 24/10 : offre faite 14 € HT/m² × 500 m² = 7 000 € HT, enlèvement par leurs soins, 30 % d'acompte ; FP « Non, nous pensions avoir mieux » ; tenue du 14 € (11:31 UTC). Dernier mot à nous — relance/appel conseillé si silence. NE PAS re-prospecter : négociation en cours. [25/10, rectif propriétaire] Négociation OUVERTE seulement : aucun accord ferme, aucun acompte confirmé — la dernière réponse de FP est « Non, nous pensions avoir mieux ».</t>
         </is>
       </c>
       <c r="Q206" s="44">
@@ -15248,7 +15248,7 @@
       </c>
       <c r="L210" s="32" t="inlineStr">
         <is>
-          <t>En négociation — canal propriétaire (Hotmail)</t>
+          <t>Refus le 19/10 — réouverture tentée (photos 22/10), en attente</t>
         </is>
       </c>
       <c r="M210" s="32" t="inlineStr">
@@ -15258,12 +15258,12 @@
       </c>
       <c r="N210" s="32" t="inlineStr">
         <is>
-          <t>NE PAS prospecter — négociation en cours menée par Joseph depuis joseph.hanna@hotmail.fr (fil « MINYALA - À l'attention du service achats »)</t>
+          <t>Ne reclasser « En négociation » QUE sur réponse de réouverture d'EdN (fil Hotmail du propriétaire) ; sinon statuer « Sans réponse — clos » après ~10 jours</t>
         </is>
       </c>
       <c r="O210" s="32" t="inlineStr">
         <is>
-          <t>[17/10] E-mail lu en clair sur europeennedenegoce.fr. Contacter UNIQUEMENT europeennedenegoce@orange.fr — La Maison du Pavé (lamaisondupave.fr) est la MÊME entreprise (même adresse à Pontarmé, confirmé sur les deux sites) : jamais les deux adresses. [24/10] Négociation DÉJÀ EN COURS, découverte dans Gmail (cc info@pierredegypte.online) : 19/10 proposition du propriétaire 1 500 m² à 25,90 €/m² livraison Pontarmé incluse, prix ferme ; 19/10 justification vs 35 €/m² public (2 cm vs 1,2 cm) ; 22/10 PHOTOS du lot envoyées (prises le jour même) avec invitation à faire une offre. Une seule voie de contact : le fil Hotmail du propriétaire. Retiré du lot d'envoi du 24/10.</t>
+          <t>[17/10] E-mail lu en clair sur europeennedenegoce.fr. Contacter UNIQUEMENT europeennedenegoce@orange.fr — La Maison du Pavé (lamaisondupave.fr) est la MÊME entreprise (même adresse à Pontarmé, confirmé sur les deux sites) : jamais les deux adresses. [24/10] Négociation DÉJÀ EN COURS, découverte dans Gmail (cc info@pierredegypte.online) : 19/10 proposition du propriétaire 1 500 m² à 25,90 €/m² livraison Pontarmé incluse, prix ferme ; 19/10 justification vs 35 €/m² public (2 cm vs 1,2 cm) ; 22/10 PHOTOS du lot envoyées (prises le jour même) avec invitation à faire une offre. Une seule voie de contact : le fil Hotmail du propriétaire. Retiré du lot d'envoi du 24/10. [25/10, rectif propriétaire] La dernière réponse EXPLICITE d'EdN est un REFUS le 19/10. L'envoi des photos du 22/10 est une tentative de réouverture, pas une négociation en cours : attendre une réponse de réouverture avant tout reclassement.</t>
         </is>
       </c>
       <c r="Q210" s="44">

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -15498,7 +15498,62 @@
       </c>
     </row>
     <row r="214" ht="15" customHeight="1" s="33">
-      <c r="L214" s="32" t="n"/>
+      <c r="A214" t="n">
+        <v>214</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Ajout propriétaire (26/10)</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>2</v>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>À qualifier</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Entreprise Koita</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>À préciser</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>À préciser</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Ajout direct du propriétaire — activité à qualifier.</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Propriétaire (26/10)</t>
+        </is>
+      </c>
+      <c r="L214" s="32" t="inlineStr">
+        <is>
+          <t>À contacter (coordonnées manquantes)</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>Obtenir du propriétaire (ou vérifier sur site officiel) : activité, ville, e-mail — puis Message A avec les contrôles standard</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>[26/10] Ajout demandé par le propriétaire (« entreprise Koita »). Coordonnées, ville et activité à préciser — aucune adresse e-mail connue : NE PAS envoyer tant que l'e-mail n'est pas confirmé (risque d'homonymie).</t>
+        </is>
+      </c>
       <c r="Q214" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -15498,60 +15498,65 @@
       </c>
     </row>
     <row r="214" ht="15" customHeight="1" s="33">
-      <c r="A214" t="n">
+      <c r="A214" s="32" t="n">
         <v>214</v>
       </c>
-      <c r="B214" t="inlineStr">
+      <c r="B214" s="32" t="inlineStr">
         <is>
           <t>Ajout propriétaire (26/10)</t>
         </is>
       </c>
-      <c r="C214" t="n">
-        <v>2</v>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>À qualifier</t>
-        </is>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>Entreprise Koita</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr">
-        <is>
-          <t>À préciser</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>À préciser</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Ajout direct du propriétaire — activité à qualifier.</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr">
+      <c r="C214" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D214" s="32" t="inlineStr">
+        <is>
+          <t>Rénovation / plomberie-chauffage</t>
+        </is>
+      </c>
+      <c r="E214" s="32" t="inlineStr">
+        <is>
+          <t>KOITA RENOVATION (Entreprise Koita)</t>
+        </is>
+      </c>
+      <c r="F214" s="32" t="inlineStr">
+        <is>
+          <t>Clamart (92140)</t>
+        </is>
+      </c>
+      <c r="G214" s="32" t="inlineStr">
+        <is>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="H214" s="32" t="inlineStr">
+        <is>
+          <t>Rénovation générale / plomberie / chauffage en Île-de-France — chantiers salle de bains et sols visibles sur son Instagram (236 K abonnés, compte vérifié) : acheteur potentiel de dallage pour ses chantiers, et relais d'audience possible.</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>06 12 38 05 34</t>
+        </is>
+      </c>
+      <c r="K214" s="32" t="inlineStr">
         <is>
           <t>Propriétaire (26/10)</t>
         </is>
       </c>
       <c r="L214" s="32" t="inlineStr">
         <is>
-          <t>À contacter (coordonnées manquantes)</t>
-        </is>
-      </c>
-      <c r="N214" t="inlineStr">
-        <is>
-          <t>Obtenir du propriétaire (ou vérifier sur site officiel) : activité, ville, e-mail — puis Message A avec les contrôles standard</t>
-        </is>
-      </c>
-      <c r="O214" t="inlineStr">
-        <is>
-          <t>[26/10] Ajout demandé par le propriétaire (« entreprise Koita »). Coordonnées, ville et activité à préciser — aucune adresse e-mail connue : NE PAS envoyer tant que l'e-mail n'est pas confirmé (risque d'homonymie).</t>
+          <t>À contacter (tél/Instagram — pas d’e-mail)</t>
+        </is>
+      </c>
+      <c r="N214" s="32" t="inlineStr">
+        <is>
+          <t>Choisir le canal (appel 06 12 38 05 34, DM Instagram, ou intro par Waldy) — action propriétaire ; pas d'e-mail connu</t>
+        </is>
+      </c>
+      <c r="O214" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Identifiée : KOITA RENOVATION, SAS au capital de 7 000 €, 7 rue du Nivernais 92140 CLAMART (même département que le dépôt !), SIREN 921 863 296, président Abodalahy Koita, créée le 18/10/2022 (source : fiche légale via recherche web + profil Instagram @entreprise_koita fourni par le propriétaire). AUCUN e-mail ni site web publiés. Canaux possibles : tél 06 12 38 05 34 (bio Instagram), DM Instagram, ou INTRO CHALEUREUSE via Waldy (waldy_nz suit le compte). UNE SEULE VOIE : choix du propriétaire ; pas d'e-mail possible à ce stade.</t>
         </is>
       </c>
       <c r="Q214" s="44">

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -5863,7 +5863,7 @@
       </c>
       <c r="J71" s="51" t="inlineStr">
         <is>
-          <t>02 35 75 64 07</t>
+          <t>06 60 18 31 14</t>
         </is>
       </c>
       <c r="K71" s="52" t="inlineStr">
@@ -5877,12 +5877,21 @@
         </is>
       </c>
       <c r="M71" s="54" t="n"/>
-      <c r="N71" s="53" t="n"/>
+      <c r="N71" s="53" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
       <c r="O71" s="53" t="n"/>
       <c r="P71" s="55" t="n"/>
       <c r="Q71" s="56">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>christophe.devaux@granits-materiaux.fr</t>
+        </is>
       </c>
     </row>
     <row r="72" ht="45.75" customHeight="1" s="33">
@@ -6005,12 +6014,21 @@
         </is>
       </c>
       <c r="M73" s="54" t="n"/>
-      <c r="N73" s="53" t="n"/>
+      <c r="N73" s="53" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
       <c r="O73" s="53" t="n"/>
       <c r="P73" s="55" t="n"/>
       <c r="Q73" s="56">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>marbrestendances@orange.fr</t>
+        </is>
       </c>
     </row>
     <row r="74" ht="45.75" customHeight="1" s="33">
@@ -15534,7 +15552,7 @@
           <t>Rénovation générale / plomberie / chauffage en Île-de-France — chantiers salle de bains et sols visibles sur son Instagram (236 K abonnés, compte vérifié) : acheteur potentiel de dallage pour ses chantiers, et relais d'audience possible.</t>
         </is>
       </c>
-      <c r="J214" t="inlineStr">
+      <c r="J214" s="32" t="inlineStr">
         <is>
           <t>06 12 38 05 34</t>
         </is>
@@ -15565,101 +15583,1021 @@
       </c>
     </row>
     <row r="215" ht="15" customHeight="1" s="33">
-      <c r="L215" s="32" t="n"/>
+      <c r="A215" t="n">
+        <v>215</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>5e liste — relais (26/10)</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Fournisseur dallage/pavage pro+particuli</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Adi Roc</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Evran (22)</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Bretagne</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Très forte adéquation : vend déjà de la pierre d'Égypte. Approche : échantillon + lot test puis palettes.</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>https://www.adi-roc.fr</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>06 28 04 92 93</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Relais assistant (26/10)</t>
+        </is>
+      </c>
+      <c r="L215" s="32" t="inlineStr">
+        <is>
+          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi. Pas d'e-mail publié : formulaire du site ou téléphone. NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
       <c r="Q215" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
     </row>
     <row r="216" ht="15" customHeight="1" s="33">
-      <c r="L216" s="32" t="n"/>
+      <c r="A216" t="n">
+        <v>216</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>5e liste — relais (26/10)</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>1</v>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Négoce pavage/dallage, stockage annoncé </t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Espace TP Distribution</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Vaux-le-Pénil (77)</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Cible majeure pour 25–500 m² ou revente par palettes.</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>https://www.espacetp.fr</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>01 64 19 19 16</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Relais assistant (26/10)</t>
+        </is>
+      </c>
+      <c r="L216" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
       <c r="Q216" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>contact@espacetp.fr</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="15" customHeight="1" s="33">
-      <c r="L217" s="32" t="n"/>
+      <c r="A217" t="n">
+        <v>217</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>5e liste — relais (26/10)</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>1</v>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Revendeur pierre naturelle, &gt;1 000 m² d'</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Kei-Stone Les Alluets-le-Roi</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Les Alluets-le-Roi (78)</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Présenter MINYALA comme gamme calcaire beige disponible rapidement depuis Gennevilliers.</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>https://www.kei-stone.fr</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>01 39 75 55 60</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Relais assistant (26/10)</t>
+        </is>
+      </c>
+      <c r="L217" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
       <c r="Q217" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>contact78@kei-stone.fr</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="15" customHeight="1" s="33">
-      <c r="L218" s="32" t="n"/>
+      <c r="A218" t="n">
+        <v>218</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>5e liste — relais (26/10)</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>1</v>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Négoce avec showroom 350 m² : dalles, pa</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Hestia Pierre &amp; Jardin</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Hillion (22)</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Bretagne</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Partenariat revendeur : échantillon + conditions par palette.</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>https://www.hestia.bzh</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>02 96 52 33 04</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Relais assistant (26/10)</t>
+        </is>
+      </c>
+      <c r="L218" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
       <c r="Q218" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>bonjour@hestia.bzh</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="15" customHeight="1" s="33">
-      <c r="L219" s="32" t="n"/>
+      <c r="A219" t="n">
+        <v>219</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>5e liste — relais (26/10)</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>1</v>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Importateur direct de calcaires et pierr</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Dalle Décor</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Galluis (78)</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Demander s'ils reprennent des lots déjà importés et disponibles localement.</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>09 74 56 22 36</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Relais assistant (26/10)</t>
+        </is>
+      </c>
+      <c r="L219" s="32" t="inlineStr">
+        <is>
+          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi. Pas d'e-mail publié : téléphone. NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
       <c r="Q219" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1" s="33">
-      <c r="L220" s="32" t="n"/>
+      <c r="A220" t="n">
+        <v>220</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>5e liste — relais (26/10)</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>1</v>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Vente et pose de dallages, pavés, bordur</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Les Paveurs d'Eure-et-Loir</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Cherisy (28)</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>IdF/Eure/Normandie</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Très bon profil pour fourniture de lots de 25 à plusieurs centaines de m² (la pose reste la leur).</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>06 87 53 33 76</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Relais assistant (26/10)</t>
+        </is>
+      </c>
+      <c r="L220" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
       <c r="Q220" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>lespaveurs.eureetloir@orange.fr</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="15" customHeight="1" s="33">
-      <c r="L221" s="32" t="n"/>
+      <c r="A221" t="n">
+        <v>221</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>5e liste — relais (26/10)</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>1</v>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Fournisseur pierre naturelle constructio</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>MC Pierre</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Courtry (77)</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Tester l'intérêt pour une gamme complémentaire calcaire égyptien 30×60×2.</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>06 25 28 12 12</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Relais assistant (26/10)</t>
+        </is>
+      </c>
+      <c r="L221" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
       <c r="Q221" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>contact@mc-pierre.com</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="15" customHeight="1" s="33">
-      <c r="L222" s="32" t="n"/>
+      <c r="A222" t="n">
+        <v>222</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>5e liste — relais (26/10)</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>2</v>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Bureau d'études paysager + showroom, ven</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Esprit Vert Design</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Ploërmel (56)</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Bretagne</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Fiche architecte (photos, texture, dimensions, prix) adaptée.</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>02 97 72 97 51</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Relais assistant (26/10)</t>
+        </is>
+      </c>
+      <c r="L222" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
       <c r="Q222" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>contact@esprit-vert-design.fr</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="15" customHeight="1" s="33">
-      <c r="L223" s="32" t="n"/>
+      <c r="A223" t="n">
+        <v>223</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>5e liste — relais (26/10)</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>2</v>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Terrassement et aménagements : dallage, </t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Guevel TP</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Betton (35)</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Bretagne</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Pierre pour terrasses/aménagements privés — ne pas lier l'offre à un marché public précis.</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>https://www.guevel-tp.fr</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>06 08 40 35 42</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Relais assistant (26/10)</t>
+        </is>
+      </c>
+      <c r="L223" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
       <c r="Q223" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>contact@guevel-tp.fr</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="15" customHeight="1" s="33">
-      <c r="L224" s="32" t="n"/>
+      <c r="A224" t="n">
+        <v>224</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>5e liste — relais (26/10)</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>2</v>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pavage/dallage bassin rennais, surfaces </t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Peron Aménagement Minéral</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Vieux-Vy-sur-Couesnon (35)</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Bretagne</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Correspond au minimum 25 m² : tarif pierre seule + transport séparé.</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>02 99 39 51 02</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Relais assistant (26/10)</t>
+        </is>
+      </c>
+      <c r="L224" s="32" t="inlineStr">
+        <is>
+          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi. Pas d'e-mail publié : téléphone. NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
       <c r="Q224" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1" s="33">
-      <c r="L225" s="32" t="n"/>
+      <c r="A225" t="n">
+        <v>225</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>5e liste — relais (26/10)</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>3</v>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>TP/voirie — lauréat d'un lot voirie Renn</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Eurovia Ille-et-Vilaine</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Rennes (35)</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Bretagne</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>Voirie marchés rennais — voir minyala/marches-publics.md : rien ne prouve que MINYALA (2 cm) convient ni qu'ils soumissionneront.</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>02 99 05 03 00</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Relais assistant (26/10)</t>
+        </is>
+      </c>
+      <c r="L225" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
       <c r="Q225" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>ille-et-vilaine@eurovia.com</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="15" customHeight="1" s="33">
-      <c r="L226" s="32" t="n"/>
+      <c r="A226" t="n">
+        <v>226</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>5e liste — relais (26/10)</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>3</v>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>TP/voirie — lauréat de plusieurs lots du</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Colas Rennes</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Rennes (35)</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Bretagne</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Idem Eurovia — prérequis techniques (FNTP 3451, DoP, essais) non réunis à ce jour.</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>02 99 59 25 91</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Relais assistant (26/10)</t>
+        </is>
+      </c>
+      <c r="L226" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
       <c r="Q226" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>contact.rennes@colas.com</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="15" customHeight="1" s="33">
-      <c r="L227" s="32" t="n"/>
+      <c r="A227" t="n">
+        <v>227</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>5e liste — relais (26/10)</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>3</v>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>TP/voirie — lauréat d'un lot</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Keravis (Groupe Lessard)</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>L'Hermitage (35)</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Bretagne</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>Idem — voir mémo marchés publics.</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>02 99 64 07 64</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Relais assistant (26/10)</t>
+        </is>
+      </c>
+      <c r="L227" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
       <c r="Q227" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>secretariat.keravis@lessard.fr</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="15" customHeight="1" s="33">
-      <c r="L228" s="32" t="n"/>
+      <c r="A228" t="n">
+        <v>228</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>5e liste — relais (26/10)</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>3</v>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>TP rennais : routes et aménagements</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>SRTP (Groupe Pigeon)</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Domloup (35)</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Bretagne</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>Idem — voir mémo marchés publics.</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>02 99 41 65 70</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Relais assistant (26/10)</t>
+        </is>
+      </c>
+      <c r="L228" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+        </is>
+      </c>
       <c r="Q228" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>srtp@groupe-pigeon.com</t>
+        </is>
       </c>
     </row>
     <row r="229" ht="15" customHeight="1" s="33">

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -5888,7 +5888,7 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="R71" s="32" t="inlineStr">
         <is>
           <t>christophe.devaux@granits-materiaux.fr</t>
         </is>
@@ -6025,7 +6025,7 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="R73" s="32" t="inlineStr">
         <is>
           <t>marbrestendances@orange.fr</t>
         </is>
@@ -15583,53 +15583,53 @@
       </c>
     </row>
     <row r="215" ht="15" customHeight="1" s="33">
-      <c r="A215" t="n">
+      <c r="A215" s="32" t="n">
         <v>215</v>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B215" s="32" t="inlineStr">
         <is>
           <t>5e liste — relais (26/10)</t>
         </is>
       </c>
-      <c r="C215" t="n">
+      <c r="C215" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D215" t="inlineStr">
+      <c r="D215" s="32" t="inlineStr">
         <is>
           <t>Fournisseur dallage/pavage pro+particuli</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
+      <c r="E215" s="32" t="inlineStr">
         <is>
           <t>Adi Roc</t>
         </is>
       </c>
-      <c r="F215" t="inlineStr">
+      <c r="F215" s="32" t="inlineStr">
         <is>
           <t>Evran (22)</t>
         </is>
       </c>
-      <c r="G215" t="inlineStr">
+      <c r="G215" s="32" t="inlineStr">
         <is>
           <t>Bretagne</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
+      <c r="H215" s="32" t="inlineStr">
         <is>
           <t>Très forte adéquation : vend déjà de la pierre d'Égypte. Approche : échantillon + lot test puis palettes.</t>
         </is>
       </c>
-      <c r="I215" t="inlineStr">
+      <c r="I215" s="32" t="inlineStr">
         <is>
           <t>https://www.adi-roc.fr</t>
         </is>
       </c>
-      <c r="J215" t="inlineStr">
+      <c r="J215" s="32" t="inlineStr">
         <is>
           <t>06 28 04 92 93</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
+      <c r="K215" s="32" t="inlineStr">
         <is>
           <t>Relais assistant (26/10)</t>
         </is>
@@ -15639,12 +15639,12 @@
           <t>À contacter (formulaire/tél) — EN ATTENTE</t>
         </is>
       </c>
-      <c r="N215" t="inlineStr">
+      <c r="N215" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
       </c>
-      <c r="O215" t="inlineStr">
+      <c r="O215" s="32" t="inlineStr">
         <is>
           <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi. Pas d'e-mail publié : formulaire du site ou téléphone. NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
@@ -15655,53 +15655,53 @@
       </c>
     </row>
     <row r="216" ht="15" customHeight="1" s="33">
-      <c r="A216" t="n">
+      <c r="A216" s="32" t="n">
         <v>216</v>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="B216" s="32" t="inlineStr">
         <is>
           <t>5e liste — relais (26/10)</t>
         </is>
       </c>
-      <c r="C216" t="n">
+      <c r="C216" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D216" t="inlineStr">
+      <c r="D216" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Négoce pavage/dallage, stockage annoncé </t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
+      <c r="E216" s="32" t="inlineStr">
         <is>
           <t>Espace TP Distribution</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
+      <c r="F216" s="32" t="inlineStr">
         <is>
           <t>Vaux-le-Pénil (77)</t>
         </is>
       </c>
-      <c r="G216" t="inlineStr">
+      <c r="G216" s="32" t="inlineStr">
         <is>
           <t>Île-de-France</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr">
+      <c r="H216" s="32" t="inlineStr">
         <is>
           <t>Cible majeure pour 25–500 m² ou revente par palettes.</t>
         </is>
       </c>
-      <c r="I216" t="inlineStr">
+      <c r="I216" s="32" t="inlineStr">
         <is>
           <t>https://www.espacetp.fr</t>
         </is>
       </c>
-      <c r="J216" t="inlineStr">
+      <c r="J216" s="32" t="inlineStr">
         <is>
           <t>01 64 19 19 16</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr">
+      <c r="K216" s="32" t="inlineStr">
         <is>
           <t>Relais assistant (26/10)</t>
         </is>
@@ -15711,12 +15711,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N216" t="inlineStr">
+      <c r="N216" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
       </c>
-      <c r="O216" t="inlineStr">
+      <c r="O216" s="32" t="inlineStr">
         <is>
           <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
@@ -15725,60 +15725,60 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R216" t="inlineStr">
+      <c r="R216" s="32" t="inlineStr">
         <is>
           <t>contact@espacetp.fr</t>
         </is>
       </c>
     </row>
     <row r="217" ht="15" customHeight="1" s="33">
-      <c r="A217" t="n">
+      <c r="A217" s="32" t="n">
         <v>217</v>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B217" s="32" t="inlineStr">
         <is>
           <t>5e liste — relais (26/10)</t>
         </is>
       </c>
-      <c r="C217" t="n">
+      <c r="C217" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D217" t="inlineStr">
+      <c r="D217" s="32" t="inlineStr">
         <is>
           <t>Revendeur pierre naturelle, &gt;1 000 m² d'</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
+      <c r="E217" s="32" t="inlineStr">
         <is>
           <t>Kei-Stone Les Alluets-le-Roi</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
+      <c r="F217" s="32" t="inlineStr">
         <is>
           <t>Les Alluets-le-Roi (78)</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
+      <c r="G217" s="32" t="inlineStr">
         <is>
           <t>Île-de-France</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
+      <c r="H217" s="32" t="inlineStr">
         <is>
           <t>Présenter MINYALA comme gamme calcaire beige disponible rapidement depuis Gennevilliers.</t>
         </is>
       </c>
-      <c r="I217" t="inlineStr">
+      <c r="I217" s="32" t="inlineStr">
         <is>
           <t>https://www.kei-stone.fr</t>
         </is>
       </c>
-      <c r="J217" t="inlineStr">
+      <c r="J217" s="32" t="inlineStr">
         <is>
           <t>01 39 75 55 60</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
+      <c r="K217" s="32" t="inlineStr">
         <is>
           <t>Relais assistant (26/10)</t>
         </is>
@@ -15788,12 +15788,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N217" t="inlineStr">
+      <c r="N217" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
       </c>
-      <c r="O217" t="inlineStr">
+      <c r="O217" s="32" t="inlineStr">
         <is>
           <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
@@ -15802,60 +15802,60 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R217" t="inlineStr">
+      <c r="R217" s="32" t="inlineStr">
         <is>
           <t>contact78@kei-stone.fr</t>
         </is>
       </c>
     </row>
     <row r="218" ht="15" customHeight="1" s="33">
-      <c r="A218" t="n">
+      <c r="A218" s="32" t="n">
         <v>218</v>
       </c>
-      <c r="B218" t="inlineStr">
+      <c r="B218" s="32" t="inlineStr">
         <is>
           <t>5e liste — relais (26/10)</t>
         </is>
       </c>
-      <c r="C218" t="n">
+      <c r="C218" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D218" t="inlineStr">
+      <c r="D218" s="32" t="inlineStr">
         <is>
           <t>Négoce avec showroom 350 m² : dalles, pa</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
+      <c r="E218" s="32" t="inlineStr">
         <is>
           <t>Hestia Pierre &amp; Jardin</t>
         </is>
       </c>
-      <c r="F218" t="inlineStr">
+      <c r="F218" s="32" t="inlineStr">
         <is>
           <t>Hillion (22)</t>
         </is>
       </c>
-      <c r="G218" t="inlineStr">
+      <c r="G218" s="32" t="inlineStr">
         <is>
           <t>Bretagne</t>
         </is>
       </c>
-      <c r="H218" t="inlineStr">
+      <c r="H218" s="32" t="inlineStr">
         <is>
           <t>Partenariat revendeur : échantillon + conditions par palette.</t>
         </is>
       </c>
-      <c r="I218" t="inlineStr">
+      <c r="I218" s="32" t="inlineStr">
         <is>
           <t>https://www.hestia.bzh</t>
         </is>
       </c>
-      <c r="J218" t="inlineStr">
+      <c r="J218" s="32" t="inlineStr">
         <is>
           <t>02 96 52 33 04</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
+      <c r="K218" s="32" t="inlineStr">
         <is>
           <t>Relais assistant (26/10)</t>
         </is>
@@ -15865,12 +15865,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N218" t="inlineStr">
+      <c r="N218" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
       </c>
-      <c r="O218" t="inlineStr">
+      <c r="O218" s="32" t="inlineStr">
         <is>
           <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
@@ -15879,55 +15879,55 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R218" t="inlineStr">
+      <c r="R218" s="32" t="inlineStr">
         <is>
           <t>bonjour@hestia.bzh</t>
         </is>
       </c>
     </row>
     <row r="219" ht="15" customHeight="1" s="33">
-      <c r="A219" t="n">
+      <c r="A219" s="32" t="n">
         <v>219</v>
       </c>
-      <c r="B219" t="inlineStr">
+      <c r="B219" s="32" t="inlineStr">
         <is>
           <t>5e liste — relais (26/10)</t>
         </is>
       </c>
-      <c r="C219" t="n">
+      <c r="C219" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D219" t="inlineStr">
+      <c r="D219" s="32" t="inlineStr">
         <is>
           <t>Importateur direct de calcaires et pierr</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
+      <c r="E219" s="32" t="inlineStr">
         <is>
           <t>Dalle Décor</t>
         </is>
       </c>
-      <c r="F219" t="inlineStr">
+      <c r="F219" s="32" t="inlineStr">
         <is>
           <t>Galluis (78)</t>
         </is>
       </c>
-      <c r="G219" t="inlineStr">
+      <c r="G219" s="32" t="inlineStr">
         <is>
           <t>Île-de-France</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr">
+      <c r="H219" s="32" t="inlineStr">
         <is>
           <t>Demander s'ils reprennent des lots déjà importés et disponibles localement.</t>
         </is>
       </c>
-      <c r="J219" t="inlineStr">
+      <c r="J219" s="32" t="inlineStr">
         <is>
           <t>09 74 56 22 36</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr">
+      <c r="K219" s="32" t="inlineStr">
         <is>
           <t>Relais assistant (26/10)</t>
         </is>
@@ -15937,12 +15937,12 @@
           <t>À contacter (formulaire/tél) — EN ATTENTE</t>
         </is>
       </c>
-      <c r="N219" t="inlineStr">
+      <c r="N219" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
       </c>
-      <c r="O219" t="inlineStr">
+      <c r="O219" s="32" t="inlineStr">
         <is>
           <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi. Pas d'e-mail publié : téléphone. NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
@@ -15953,48 +15953,48 @@
       </c>
     </row>
     <row r="220" ht="15" customHeight="1" s="33">
-      <c r="A220" t="n">
+      <c r="A220" s="32" t="n">
         <v>220</v>
       </c>
-      <c r="B220" t="inlineStr">
+      <c r="B220" s="32" t="inlineStr">
         <is>
           <t>5e liste — relais (26/10)</t>
         </is>
       </c>
-      <c r="C220" t="n">
+      <c r="C220" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D220" t="inlineStr">
+      <c r="D220" s="32" t="inlineStr">
         <is>
           <t>Vente et pose de dallages, pavés, bordur</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
+      <c r="E220" s="32" t="inlineStr">
         <is>
           <t>Les Paveurs d'Eure-et-Loir</t>
         </is>
       </c>
-      <c r="F220" t="inlineStr">
+      <c r="F220" s="32" t="inlineStr">
         <is>
           <t>Cherisy (28)</t>
         </is>
       </c>
-      <c r="G220" t="inlineStr">
+      <c r="G220" s="32" t="inlineStr">
         <is>
           <t>IdF/Eure/Normandie</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr">
+      <c r="H220" s="32" t="inlineStr">
         <is>
           <t>Très bon profil pour fourniture de lots de 25 à plusieurs centaines de m² (la pose reste la leur).</t>
         </is>
       </c>
-      <c r="J220" t="inlineStr">
+      <c r="J220" s="32" t="inlineStr">
         <is>
           <t>06 87 53 33 76</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr">
+      <c r="K220" s="32" t="inlineStr">
         <is>
           <t>Relais assistant (26/10)</t>
         </is>
@@ -16004,12 +16004,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N220" t="inlineStr">
+      <c r="N220" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
       </c>
-      <c r="O220" t="inlineStr">
+      <c r="O220" s="32" t="inlineStr">
         <is>
           <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
@@ -16018,55 +16018,55 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R220" t="inlineStr">
+      <c r="R220" s="32" t="inlineStr">
         <is>
           <t>lespaveurs.eureetloir@orange.fr</t>
         </is>
       </c>
     </row>
     <row r="221" ht="15" customHeight="1" s="33">
-      <c r="A221" t="n">
+      <c r="A221" s="32" t="n">
         <v>221</v>
       </c>
-      <c r="B221" t="inlineStr">
+      <c r="B221" s="32" t="inlineStr">
         <is>
           <t>5e liste — relais (26/10)</t>
         </is>
       </c>
-      <c r="C221" t="n">
+      <c r="C221" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D221" t="inlineStr">
+      <c r="D221" s="32" t="inlineStr">
         <is>
           <t>Fournisseur pierre naturelle constructio</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr">
+      <c r="E221" s="32" t="inlineStr">
         <is>
           <t>MC Pierre</t>
         </is>
       </c>
-      <c r="F221" t="inlineStr">
+      <c r="F221" s="32" t="inlineStr">
         <is>
           <t>Courtry (77)</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
+      <c r="G221" s="32" t="inlineStr">
         <is>
           <t>Île-de-France</t>
         </is>
       </c>
-      <c r="H221" t="inlineStr">
+      <c r="H221" s="32" t="inlineStr">
         <is>
           <t>Tester l'intérêt pour une gamme complémentaire calcaire égyptien 30×60×2.</t>
         </is>
       </c>
-      <c r="J221" t="inlineStr">
+      <c r="J221" s="32" t="inlineStr">
         <is>
           <t>06 25 28 12 12</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr">
+      <c r="K221" s="32" t="inlineStr">
         <is>
           <t>Relais assistant (26/10)</t>
         </is>
@@ -16076,12 +16076,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N221" t="inlineStr">
+      <c r="N221" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
       </c>
-      <c r="O221" t="inlineStr">
+      <c r="O221" s="32" t="inlineStr">
         <is>
           <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
@@ -16090,55 +16090,55 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R221" t="inlineStr">
+      <c r="R221" s="32" t="inlineStr">
         <is>
           <t>contact@mc-pierre.com</t>
         </is>
       </c>
     </row>
     <row r="222" ht="15" customHeight="1" s="33">
-      <c r="A222" t="n">
+      <c r="A222" s="32" t="n">
         <v>222</v>
       </c>
-      <c r="B222" t="inlineStr">
+      <c r="B222" s="32" t="inlineStr">
         <is>
           <t>5e liste — relais (26/10)</t>
         </is>
       </c>
-      <c r="C222" t="n">
+      <c r="C222" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D222" t="inlineStr">
+      <c r="D222" s="32" t="inlineStr">
         <is>
           <t>Bureau d'études paysager + showroom, ven</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr">
+      <c r="E222" s="32" t="inlineStr">
         <is>
           <t>Esprit Vert Design</t>
         </is>
       </c>
-      <c r="F222" t="inlineStr">
+      <c r="F222" s="32" t="inlineStr">
         <is>
           <t>Ploërmel (56)</t>
         </is>
       </c>
-      <c r="G222" t="inlineStr">
+      <c r="G222" s="32" t="inlineStr">
         <is>
           <t>Bretagne</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
+      <c r="H222" s="32" t="inlineStr">
         <is>
           <t>Fiche architecte (photos, texture, dimensions, prix) adaptée.</t>
         </is>
       </c>
-      <c r="J222" t="inlineStr">
+      <c r="J222" s="32" t="inlineStr">
         <is>
           <t>02 97 72 97 51</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr">
+      <c r="K222" s="32" t="inlineStr">
         <is>
           <t>Relais assistant (26/10)</t>
         </is>
@@ -16148,12 +16148,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N222" t="inlineStr">
+      <c r="N222" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
       </c>
-      <c r="O222" t="inlineStr">
+      <c r="O222" s="32" t="inlineStr">
         <is>
           <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
@@ -16162,60 +16162,60 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R222" t="inlineStr">
+      <c r="R222" s="32" t="inlineStr">
         <is>
           <t>contact@esprit-vert-design.fr</t>
         </is>
       </c>
     </row>
     <row r="223" ht="15" customHeight="1" s="33">
-      <c r="A223" t="n">
+      <c r="A223" s="32" t="n">
         <v>223</v>
       </c>
-      <c r="B223" t="inlineStr">
+      <c r="B223" s="32" t="inlineStr">
         <is>
           <t>5e liste — relais (26/10)</t>
         </is>
       </c>
-      <c r="C223" t="n">
+      <c r="C223" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D223" t="inlineStr">
+      <c r="D223" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Terrassement et aménagements : dallage, </t>
         </is>
       </c>
-      <c r="E223" t="inlineStr">
+      <c r="E223" s="32" t="inlineStr">
         <is>
           <t>Guevel TP</t>
         </is>
       </c>
-      <c r="F223" t="inlineStr">
+      <c r="F223" s="32" t="inlineStr">
         <is>
           <t>Betton (35)</t>
         </is>
       </c>
-      <c r="G223" t="inlineStr">
+      <c r="G223" s="32" t="inlineStr">
         <is>
           <t>Bretagne</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr">
+      <c r="H223" s="32" t="inlineStr">
         <is>
           <t>Pierre pour terrasses/aménagements privés — ne pas lier l'offre à un marché public précis.</t>
         </is>
       </c>
-      <c r="I223" t="inlineStr">
+      <c r="I223" s="32" t="inlineStr">
         <is>
           <t>https://www.guevel-tp.fr</t>
         </is>
       </c>
-      <c r="J223" t="inlineStr">
+      <c r="J223" s="32" t="inlineStr">
         <is>
           <t>06 08 40 35 42</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr">
+      <c r="K223" s="32" t="inlineStr">
         <is>
           <t>Relais assistant (26/10)</t>
         </is>
@@ -16225,12 +16225,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N223" t="inlineStr">
+      <c r="N223" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
       </c>
-      <c r="O223" t="inlineStr">
+      <c r="O223" s="32" t="inlineStr">
         <is>
           <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
@@ -16239,55 +16239,55 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R223" t="inlineStr">
+      <c r="R223" s="32" t="inlineStr">
         <is>
           <t>contact@guevel-tp.fr</t>
         </is>
       </c>
     </row>
     <row r="224" ht="15" customHeight="1" s="33">
-      <c r="A224" t="n">
+      <c r="A224" s="32" t="n">
         <v>224</v>
       </c>
-      <c r="B224" t="inlineStr">
+      <c r="B224" s="32" t="inlineStr">
         <is>
           <t>5e liste — relais (26/10)</t>
         </is>
       </c>
-      <c r="C224" t="n">
+      <c r="C224" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D224" t="inlineStr">
+      <c r="D224" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">Pavage/dallage bassin rennais, surfaces </t>
         </is>
       </c>
-      <c r="E224" t="inlineStr">
+      <c r="E224" s="32" t="inlineStr">
         <is>
           <t>Peron Aménagement Minéral</t>
         </is>
       </c>
-      <c r="F224" t="inlineStr">
+      <c r="F224" s="32" t="inlineStr">
         <is>
           <t>Vieux-Vy-sur-Couesnon (35)</t>
         </is>
       </c>
-      <c r="G224" t="inlineStr">
+      <c r="G224" s="32" t="inlineStr">
         <is>
           <t>Bretagne</t>
         </is>
       </c>
-      <c r="H224" t="inlineStr">
+      <c r="H224" s="32" t="inlineStr">
         <is>
           <t>Correspond au minimum 25 m² : tarif pierre seule + transport séparé.</t>
         </is>
       </c>
-      <c r="J224" t="inlineStr">
+      <c r="J224" s="32" t="inlineStr">
         <is>
           <t>02 99 39 51 02</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr">
+      <c r="K224" s="32" t="inlineStr">
         <is>
           <t>Relais assistant (26/10)</t>
         </is>
@@ -16297,12 +16297,12 @@
           <t>À contacter (formulaire/tél) — EN ATTENTE</t>
         </is>
       </c>
-      <c r="N224" t="inlineStr">
+      <c r="N224" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
       </c>
-      <c r="O224" t="inlineStr">
+      <c r="O224" s="32" t="inlineStr">
         <is>
           <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi. Pas d'e-mail publié : téléphone. NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
@@ -16313,48 +16313,48 @@
       </c>
     </row>
     <row r="225" ht="15" customHeight="1" s="33">
-      <c r="A225" t="n">
+      <c r="A225" s="32" t="n">
         <v>225</v>
       </c>
-      <c r="B225" t="inlineStr">
+      <c r="B225" s="32" t="inlineStr">
         <is>
           <t>5e liste — relais (26/10)</t>
         </is>
       </c>
-      <c r="C225" t="n">
+      <c r="C225" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="D225" t="inlineStr">
+      <c r="D225" s="32" t="inlineStr">
         <is>
           <t>TP/voirie — lauréat d'un lot voirie Renn</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr">
+      <c r="E225" s="32" t="inlineStr">
         <is>
           <t>Eurovia Ille-et-Vilaine</t>
         </is>
       </c>
-      <c r="F225" t="inlineStr">
+      <c r="F225" s="32" t="inlineStr">
         <is>
           <t>Rennes (35)</t>
         </is>
       </c>
-      <c r="G225" t="inlineStr">
+      <c r="G225" s="32" t="inlineStr">
         <is>
           <t>Bretagne</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
+      <c r="H225" s="32" t="inlineStr">
         <is>
           <t>Voirie marchés rennais — voir minyala/marches-publics.md : rien ne prouve que MINYALA (2 cm) convient ni qu'ils soumissionneront.</t>
         </is>
       </c>
-      <c r="J225" t="inlineStr">
+      <c r="J225" s="32" t="inlineStr">
         <is>
           <t>02 99 05 03 00</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr">
+      <c r="K225" s="32" t="inlineStr">
         <is>
           <t>Relais assistant (26/10)</t>
         </is>
@@ -16364,12 +16364,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N225" t="inlineStr">
+      <c r="N225" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
       </c>
-      <c r="O225" t="inlineStr">
+      <c r="O225" s="32" t="inlineStr">
         <is>
           <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
@@ -16378,55 +16378,55 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R225" t="inlineStr">
+      <c r="R225" s="32" t="inlineStr">
         <is>
           <t>ille-et-vilaine@eurovia.com</t>
         </is>
       </c>
     </row>
     <row r="226" ht="15" customHeight="1" s="33">
-      <c r="A226" t="n">
+      <c r="A226" s="32" t="n">
         <v>226</v>
       </c>
-      <c r="B226" t="inlineStr">
+      <c r="B226" s="32" t="inlineStr">
         <is>
           <t>5e liste — relais (26/10)</t>
         </is>
       </c>
-      <c r="C226" t="n">
+      <c r="C226" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="D226" s="32" t="inlineStr">
         <is>
           <t>TP/voirie — lauréat de plusieurs lots du</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="E226" s="32" t="inlineStr">
         <is>
           <t>Colas Rennes</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
+      <c r="F226" s="32" t="inlineStr">
         <is>
           <t>Rennes (35)</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
+      <c r="G226" s="32" t="inlineStr">
         <is>
           <t>Bretagne</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
+      <c r="H226" s="32" t="inlineStr">
         <is>
           <t>Idem Eurovia — prérequis techniques (FNTP 3451, DoP, essais) non réunis à ce jour.</t>
         </is>
       </c>
-      <c r="J226" t="inlineStr">
+      <c r="J226" s="32" t="inlineStr">
         <is>
           <t>02 99 59 25 91</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr">
+      <c r="K226" s="32" t="inlineStr">
         <is>
           <t>Relais assistant (26/10)</t>
         </is>
@@ -16436,12 +16436,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N226" t="inlineStr">
+      <c r="N226" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
       </c>
-      <c r="O226" t="inlineStr">
+      <c r="O226" s="32" t="inlineStr">
         <is>
           <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
@@ -16450,55 +16450,55 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R226" t="inlineStr">
+      <c r="R226" s="32" t="inlineStr">
         <is>
           <t>contact.rennes@colas.com</t>
         </is>
       </c>
     </row>
     <row r="227" ht="15" customHeight="1" s="33">
-      <c r="A227" t="n">
+      <c r="A227" s="32" t="n">
         <v>227</v>
       </c>
-      <c r="B227" t="inlineStr">
+      <c r="B227" s="32" t="inlineStr">
         <is>
           <t>5e liste — relais (26/10)</t>
         </is>
       </c>
-      <c r="C227" t="n">
+      <c r="C227" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="D227" t="inlineStr">
+      <c r="D227" s="32" t="inlineStr">
         <is>
           <t>TP/voirie — lauréat d'un lot</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr">
+      <c r="E227" s="32" t="inlineStr">
         <is>
           <t>Keravis (Groupe Lessard)</t>
         </is>
       </c>
-      <c r="F227" t="inlineStr">
+      <c r="F227" s="32" t="inlineStr">
         <is>
           <t>L'Hermitage (35)</t>
         </is>
       </c>
-      <c r="G227" t="inlineStr">
+      <c r="G227" s="32" t="inlineStr">
         <is>
           <t>Bretagne</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
+      <c r="H227" s="32" t="inlineStr">
         <is>
           <t>Idem — voir mémo marchés publics.</t>
         </is>
       </c>
-      <c r="J227" t="inlineStr">
+      <c r="J227" s="32" t="inlineStr">
         <is>
           <t>02 99 64 07 64</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr">
+      <c r="K227" s="32" t="inlineStr">
         <is>
           <t>Relais assistant (26/10)</t>
         </is>
@@ -16508,12 +16508,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N227" t="inlineStr">
+      <c r="N227" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
       </c>
-      <c r="O227" t="inlineStr">
+      <c r="O227" s="32" t="inlineStr">
         <is>
           <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
@@ -16522,55 +16522,55 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R227" t="inlineStr">
+      <c r="R227" s="32" t="inlineStr">
         <is>
           <t>secretariat.keravis@lessard.fr</t>
         </is>
       </c>
     </row>
     <row r="228" ht="15" customHeight="1" s="33">
-      <c r="A228" t="n">
+      <c r="A228" s="32" t="n">
         <v>228</v>
       </c>
-      <c r="B228" t="inlineStr">
+      <c r="B228" s="32" t="inlineStr">
         <is>
           <t>5e liste — relais (26/10)</t>
         </is>
       </c>
-      <c r="C228" t="n">
+      <c r="C228" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D228" s="32" t="inlineStr">
         <is>
           <t>TP rennais : routes et aménagements</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
+      <c r="E228" s="32" t="inlineStr">
         <is>
           <t>SRTP (Groupe Pigeon)</t>
         </is>
       </c>
-      <c r="F228" t="inlineStr">
+      <c r="F228" s="32" t="inlineStr">
         <is>
           <t>Domloup (35)</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
+      <c r="G228" s="32" t="inlineStr">
         <is>
           <t>Bretagne</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
+      <c r="H228" s="32" t="inlineStr">
         <is>
           <t>Idem — voir mémo marchés publics.</t>
         </is>
       </c>
-      <c r="J228" t="inlineStr">
+      <c r="J228" s="32" t="inlineStr">
         <is>
           <t>02 99 41 65 70</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr">
+      <c r="K228" s="32" t="inlineStr">
         <is>
           <t>Relais assistant (26/10)</t>
         </is>
@@ -16580,12 +16580,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N228" t="inlineStr">
+      <c r="N228" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
       </c>
-      <c r="O228" t="inlineStr">
+      <c r="O228" s="32" t="inlineStr">
         <is>
           <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
         </is>
@@ -16594,224 +16594,2334 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R228" t="inlineStr">
+      <c r="R228" s="32" t="inlineStr">
         <is>
           <t>srtp@groupe-pigeon.com</t>
         </is>
       </c>
     </row>
     <row r="229" ht="15" customHeight="1" s="33">
-      <c r="L229" s="32" t="n"/>
+      <c r="A229" t="n">
+        <v>229</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>1</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>importateurs</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Marbrerie Arnaud (SUD PIERRE)</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Colombiers / Béziers</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Confirmée : « Importateur et distributeur de pierre naturelle depuis 2012 », import direct Turquie, Égypte, Chine (page d'accueil) ; showroom 700 m² à Béziers, adresse Route de Nar…</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>https://www.marbreriearnaud34.com/</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>04 67 35 82 22</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L229" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : « Importateur et distributeur de pierre naturelle depuis 2012 », import direct Turquie, Égypte, Chine (page d'accueil) ; showroom 700 m² à Béziers, adresse Route de Narbonne à Colombiers. Villes conformes. E-mail lu textuellement dans les mentions légales (« e-mail : j.andreo@marbrerie-arnaud.com », propriétaire SUD PIERRE). Le domaine de l'e-mail (marbrerie-arnaud.com) diffère du domaine du site, mais c'est bien l'adresse publiée officiellement. Téléphone confirmé sur mentions légales et accueil. Domaine hors liste d'exclusion. Source e-mail : https://www.marbreriearnaud34.com/mentions-legales/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q229" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>j.andreo@marbrerie-arnaud.com</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="15" customHeight="1" s="33">
-      <c r="L230" s="32" t="n"/>
+      <c r="A230" t="n">
+        <v>230</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>1</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>importateurs</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Artemis (Artemis Prestige)</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Cabriès (Plan de Campagne) ; entrepôt à Simiane-Collongue</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Confirmée : importateur-vendeur de pierre naturelle (travertin, marbre, pierre d'Égypte, grès cérame), livraison France entière. Showroom Expobat Plan de Campagne 13480 Cabriès + e…</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>https://www.artemis-prestige.com/</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>04 42 31 41 40</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L230" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : importateur-vendeur de pierre naturelle (travertin, marbre, pierre d'Égypte, grès cérame), livraison France entière. Showroom Expobat Plan de Campagne 13480 Cabriès + entrepôt logistique 13109 Simiane-Collongue confirmés sur la page contact. E-mail présent textuellement sur la page contact (texte du lien et mailto). Téléphone confirmé. Pierre d'Égypte explicitement au catalogue. Domaine hors liste d'exclusion. Source e-mail : https://www.artemis-prestige.com/contact.html.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q230" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>artemis-prestige@orange.fr</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="15" customHeight="1" s="33">
-      <c r="L231" s="32" t="n"/>
+      <c r="A231" t="n">
+        <v>231</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>1</v>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>importateurs</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Minéral Pierre Naturelle (Pierre de l'Est SAS)</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Woustviller (magasins Lyon, Strasbourg, Nancy, Beaune, Thion</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>Confirmée : spécialiste pierre naturelle (travertin, calcaire, marbre, granit...), 7 magasins France/Allemagne dont Lyon, Strasbourg, Nancy, Beaune, Thionville. Mentions légales : …</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>https://www.mineral-pierre-naturelle.fr/</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>03 60 12 33 53</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L231" s="32" t="inlineStr">
+        <is>
+          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : spécialiste pierre naturelle (travertin, calcaire, marbre, granit...), 7 magasins France/Allemagne dont Lyon, Strasbourg, Nancy, Beaune, Thionville. Mentions légales : Pierre de l'Est SAS, 44 Rue de Nancy, 57915 Woustviller — raison sociale et ville confirmées. AUCUN e-mail publié : vérifié sur l'accueil et les mentions légales (contact par téléphone ou formulaire uniquement). Repli téléphone VÉRIFIÉ : 03 60 12 33 53 affiché sur l'accueil (« Conseil d'expert ») et dans les mentions légales. Le produit Sinai Pearl n'était pas visible sur la portion d'accueil lue, mais l'activité calcaire/travertin est confirmée. Domaine hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q231" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
     </row>
     <row r="232" ht="15" customHeight="1" s="33">
-      <c r="L232" s="32" t="n"/>
+      <c r="A232" t="n">
+        <v>232</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>1</v>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>importateurs</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Nimex International</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Caissargues (dépôt à Nîmes)</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>Confirmée : importateur-distributeur de pierre naturelle, marbre, granit, travertin ; approvisionnement direct carrières (Espagne, Italie, Portugal, Grèce, Turquie, ÉGYPTE, Inde) ;…</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>https://www.nimexinternational.fr/</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>04 30 22 01 75</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L232" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : importateur-distributeur de pierre naturelle, marbre, granit, travertin ; approvisionnement direct carrières (Espagne, Italie, Portugal, Grèce, Turquie, ÉGYPTE, Inde) ; dépôt à Nîmes, vente et livraison France entière. Adresse : 14 avenue de la Vistrenque, 30132 Caissargues — ville confirmée. E-mail présent textuellement dans le pied de page du site officiel. Téléphone confirmé. L'Égypte figure parmi les pays d'approvisionnement cités. Domaine hors liste d'exclusion. Source e-mail : https://www.nimexinternational.fr/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q232" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>nimex.international@wanadoo.fr</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="15" customHeight="1" s="33">
-      <c r="L233" s="32" t="n"/>
+      <c r="A233" t="n">
+        <v>233</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>1</v>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>importateurs</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Travertin.fr</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Fos-sur-Mer (centre logistique)</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>Confirmée : le site se décrit comme « un importateur et un grossiste spécialisé en travertin » (carrières Turquie/Italie), dalles, carrelages, margelles, livraison France entière. …</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>https://www.travertin.fr/</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>09 70 70 73 75</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L233" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : le site se décrit comme « un importateur et un grossiste spécialisé en travertin » (carrières Turquie/Italie), dalles, carrelages, margelles, livraison France entière. Adresse : Centre Logistique, 13270 Fos-sur-Mer — ville confirmée. E-mail présent textuellement dans le bloc contact du pied de page, sous l'adresse de Fos-sur-Mer. Téléphone confirmé (en-tête et pied de page). Domaine hors liste d'exclusion. Source e-mail : https://www.travertin.fr/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q233" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>info@travertin.fr</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="15" customHeight="1" s="33">
-      <c r="L234" s="32" t="n"/>
+      <c r="A234" t="n">
+        <v>234</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>2</v>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>importateurs</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>Espace Travertin (EURL GNPS Espace Carrelage)</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Bollène</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Confirmée partiellement : vente de travertin (dallage, margelles, plinthes, vasques, 200+ références) avec page « Devenir Revendeur » et prix de gros revendiqués ; adresse Impasse …</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>https://www.espace-travertin.fr/</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>07 68 18 70 32</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L234" s="32" t="inlineStr">
+        <is>
+          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée partiellement : vente de travertin (dallage, margelles, plinthes, vasques, 200+ références) avec page « Devenir Revendeur » et prix de gros revendiqués ; adresse Impasse de la Rode, 84500 Bollène confirmée. Le site vend aussi aux particuliers (pas uniquement B2B). Le siège à Étoile-sur-Rhône et la raison sociale GNPS n'apparaissent pas sur la page d'accueil (le PDF CGV mentionne « stone-diffusion-centre »). AUCUN e-mail publié sur la page d'accueil (vérifié). Repli téléphone VÉRIFIÉ : 07 68 18 70 32 affiché deux fois en haut de page en lien cliquable. Domaine hors liste d'exclusion. Profil un peu plus B2C que revendiqué, mais canal revendeur réel. Source e-mail : aucune (pas d e-mail publié). ⚠️ CONCURRENT suivi dans la veille prix (ambiguïtés marbre/calcaire) — approche uniquement « reprise de lot revendeur ». NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q234" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
     </row>
     <row r="235" ht="15" customHeight="1" s="33">
-      <c r="L235" s="32" t="n"/>
+      <c r="A235" t="n">
+        <v>235</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>1</v>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>importateurs</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>DMC Miller</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Pertuis (dépôt également à Gujan-Mestras, 33)</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Confirmée : distributeur spécialiste du travertin (dalles 1er/2e choix, margelles, plinthes, mosaïques, pavés granit), vente au m², livraison France entière. Adresse 315 Rue Benjam…</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>https://www.dmcmiller.com/</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>06 66 55 44 42</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L235" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : distributeur spécialiste du travertin (dalles 1er/2e choix, margelles, plinthes, mosaïques, pavés granit), vente au m², livraison France entière. Adresse 315 Rue Benjamin Franklin, 84120 Pertuis + dépôts Pertuis et Gujan-Mestras — villes confirmées. E-mail présent textuellement dans le pied de page (lien mailto). Téléphone confirmé (affiché 0666554442 en en-tête, pied de page et lien WhatsApp). Domaine hors liste d'exclusion. Source e-mail : https://www.dmcmiller.com/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q235" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>contact@dmcmiller.com</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="15" customHeight="1" s="33">
-      <c r="L236" s="32" t="n"/>
+      <c r="A236" t="n">
+        <v>236</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>1</v>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>importateurs</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Cupa Stone France (Cupa Pierres Distribution)</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Changé (Le Mans) — réseau national d'agences</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Confirmée : distributeur national de pierre naturelle avec agences au Mans (Changé), Tours, Rennes, Nantes, Lyon, Aix-en-Provence, Quimper, Pau, Limoges, Cholet, Muzillac, La Roche…</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>https://www.cupastone.fr/</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>+33 2 43 85 06 84</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L236" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : distributeur national de pierre naturelle avec agences au Mans (Changé), Tours, Rennes, Nantes, Lyon, Aix-en-Provence, Quimper, Pau, Limoges, Cholet, Muzillac, La Roche-sur-Yon, etc. (groupe présent aussi en Espagne/Portugal). Le téléphone +33 2 43 85 06 84 est bien celui de l'agence Le Mans (Changé), contact Amandine Renard. E-mail contact@cupastone.fr présent textuellement sur la page points de vente, répété pour la plupart des agences françaises (dont Le Mans). D'autres e-mails nominatifs existent (cleger@cupastone.fr Bordeaux, lgasse@cupastone.com Paris-IdF, sbatmale@cupastone.com Toulouse, fmadehors@cupastone.com Nord-Est) si un ciblage régional est préféré. Domaine hors liste d'exclusion. Source e-mail : https://www.cupastone.fr/points-de-vente/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q236" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>contact@cupastone.fr</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="15" customHeight="1" s="33">
-      <c r="L237" s="32" t="n"/>
+      <c r="A237" t="n">
+        <v>237</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>2</v>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>importateurs</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Ti'ma Stone</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Lunel (non confirmée sur le site)</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Confirmée pour l'activité : vente en ligne de pierre naturelle France entière (dallage, parement, margelles, zellige, vasques), travertin très présent, liens « Grossiste dallage » …</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>https://timastone.com/</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>04 15 54 01 25</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L237" s="32" t="inlineStr">
+        <is>
+          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
+        </is>
+      </c>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée pour l'activité : vente en ligne de pierre naturelle France entière (dallage, parement, margelles, zellige, vasques), travertin très présent, liens « Grossiste dallage » et « Fournisseur carrelage » + espace pro. La VILLE n'est PAS confirmée : aucune adresse ni ville sur la page d'accueil, et les pages /mentions-legales/ et /contact/ renvoient un 404 aux URL standards. AUCUN e-mail publié sur la page d'accueil (vérifié). Repli téléphone VÉRIFIÉ : 04 15 54 01 25 affiché en en-tête et pied de page (horaires lun-ven 9h-12h / 14h-18h). Domaine hors liste d'exclusion. Site vivant et actif, mais profil plutôt vente en ligne avec volet grossiste ; localisation Lunel à reconfirmer par téléphone avant tout engagement logistique. Source e-mail : aucune (pas d e-mail publié). ⚠️ CONCURRENT suivi dans la veille prix (42,46–59,96 €/m²) — approche uniquement « reprise de lot revendeur », aucune info sensible. NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q237" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
     </row>
     <row r="238" ht="15" customHeight="1" s="33">
-      <c r="L238" s="32" t="n"/>
+      <c r="A238" t="n">
+        <v>238</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>2</v>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>importateurs</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>BH Matériaux (groupe Holding Laffont)</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Lauzerte</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>Confirmée : grossiste revendiqué (« Votre grossiste ») en matériaux de construction/rénovation/décoration avec le travertin et le dallage pierre naturelle en gamme majeure (dallage…</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>https://bh-materiaux.com/</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>05 63 95 39 08</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L238" s="32" t="inlineStr">
+        <is>
+          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : grossiste revendiqué (« Votre grossiste ») en matériaux de construction/rénovation/décoration avec le travertin et le dallage pierre naturelle en gamme majeure (dallages du monde, parement, graviers, pas japonais) ; particuliers et professionnels ; retrait au dépôt de Lauzerte. Adresse 138 route de Montbarla, 82110 Lauzerte confirmée. Groupe Holding Laffont confirmé (Osagra, Laffont TP, Laffont Granulats...). AUCUN e-mail publié (vérifié sur la page d'accueil : téléphone et formulaire de rappel uniquement). Repli téléphone VÉRIFIÉ : 05 63 95 39 08 répété en en-tête et sections contact. ATTENTION : le site confirme « membre du réseau FRANCE MATERIAUX » dont le domaine france-materiaux.fr figure dans la liste d'exclusion ; le domaine propre bh-materiaux.com n'y figure pas — retenu, mais à arbitrer côté donneur d'ordre avant contact. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q238" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
     </row>
     <row r="239" ht="15" customHeight="1" s="33">
-      <c r="L239" s="32" t="n"/>
+      <c r="A239" t="n">
+        <v>239</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>2</v>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>marbreries-idf</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Les Marbreries de la Seine (LMS Paris)</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Les Pavillons-sous-Bois (ateliers) / Paris 7e (showroom)</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>Confirmée : marbrerie haute décoration (architecture, mobilier, objets d'art) ; showroom 33 rue de Verneuil 75007 Paris, ateliers et logistique 2/8 allée de Londres 93320 Les Pavil…</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>https://www.lesmarbreriesdelaseine.com</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>+33 1 48 48 10 00 (showroom) / +33 1 48 48 59 76 (ateliers)</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L239" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : marbrerie haute décoration (architecture, mobilier, objets d'art) ; showroom 33 rue de Verneuil 75007 Paris, ateliers et logistique 2/8 allée de Londres 93320 Les Pavillons-sous-Bois. E-mail info@lmsparis.com lu textuellement sur la page contact du site officiel (un second e-mail info@lmsmiami.com concerne l'antenne de Miami, à ignorer). Téléphones confirmés. Domaine hors liste d'exclusion. Site officiel, pas un annuaire. Source e-mail : https://www.lesmarbreriesdelaseine.com/contact.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q239" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>info@lmsparis.com</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="15" customHeight="1" s="33">
-      <c r="L240" s="32" t="n"/>
+      <c r="A240" t="n">
+        <v>240</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>2</v>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>marbreries-idf</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Marbre Import</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Paris 19e (118 av. Jean Jaurès) ; autre adresse affichée : B</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Confirmée : spécialiste de la pierre naturelle (marbre, granit, dalles, blocs), vente aux particuliers et professionnels (marbriers, architectes, constructeurs).</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>https://www.marbre-import.fr</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>09 72 15 80 01</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L240" s="32" t="inlineStr">
+        <is>
+          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
+        </is>
+      </c>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : spécialiste de la pierre naturelle (marbre, granit, dalles, blocs), vente aux particuliers et professionnels (marbriers, architectes, constructeurs). AUCUN e-mail publié sur la page contact du site officiel : formulaire de devis uniquement. Retenu sur la base du téléphone vérifié 09 72 15 80 01 (affiché textuellement et en lien tel: sur la page contact). Attention : la page contact affiche Paris 19e et Bordeaux ; le showroom de Villejuif annoncé dans le candidat n'y apparaît pas — à confirmer par téléphone. Domaine hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié). ⚠️ CONCURRENT suivi dans la veille prix (Crema Marfil Espagne, lot promo 20 € HT) — prudence, approche reprise de lot uniquement. NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q240" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
     </row>
     <row r="241" ht="15" customHeight="1" s="33">
-      <c r="L241" s="32" t="n"/>
+      <c r="A241" t="n">
+        <v>241</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>2</v>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>marbreries-idf</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Arthema Marbre (marbrerie SPIMA)</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Paris 3e (showroom 34 rue de Poitou, Le Marais)</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>Confirmée : marbrerie de décoration sur mesure (marbre, pierre calcaire, travertin, onyx, granit, quartzite), fabrication en atelier partenaire SPIMA et pose ; clientèle d'architec…</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>https://arthema-marbre.com</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>01 42 71 79 09 / 06 19 26 42 68</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L241" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : marbrerie de décoration sur mesure (marbre, pierre calcaire, travertin, onyx, granit, quartzite), fabrication en atelier partenaire SPIMA et pose ; clientèle d'architectes et décorateurs. E-mail lu textuellement sur la page d'accueil du site officiel. Un mobile supplémentaire (06 19 26 42 68) y figure aussi. Travail explicite des pierres calcaires et travertins confirmé. Domaine hors liste d'exclusion. Source e-mail : https://arthema-marbre.com/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q241" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>contact@arthema-marbre.com</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="15" customHeight="1" s="33">
-      <c r="L242" s="32" t="n"/>
+      <c r="A242" t="n">
+        <v>242</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>2</v>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>marbreries-idf</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Atelier Matière</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Paris 16e (19 rue Vital) et Paris 17e (36 rue Brunel)</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>Confirmée : studio/showroom de pierre naturelle, marbre et terrazzo haut de gamme depuis 2012, distribution et pose sur rendez-vous ; deux showrooms parisiens confirmés.</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>https://www.ateliermatiere.fr</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>01 45 04 57 65</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L242" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : studio/showroom de pierre naturelle, marbre et terrazzo haut de gamme depuis 2012, distribution et pose sur rendez-vous ; deux showrooms parisiens confirmés. E-mail lu textuellement sur la page Pierre du site officiel ; téléphone confirmé. Domaine hors liste d'exclusion. Site officiel, pas un annuaire. Source e-mail : https://www.ateliermatiere.fr/pierre.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q242" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>info@ateliermatiere.fr</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="15" customHeight="1" s="33">
-      <c r="L243" s="32" t="n"/>
+      <c r="A243" t="n">
+        <v>243</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>2</v>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>marbreries-idf</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Artefacts Paris</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Paris 7e (showroom 17 bis passage Jean Nicot) ; atelier à Né</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>Confirmée : marbrerie fine et pierre de taille, revêtements durs en pierre naturelle pour la construction et l'agencement de luxe ; showroom Paris 7e et atelier/bureau d'études à N…</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>https://www.artefacts-paris.com</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L243" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : marbrerie fine et pierre de taille, revêtements durs en pierre naturelle pour la construction et l'agencement de luxe ; showroom Paris 7e et atelier/bureau d'études à Nérac (47600) confirmés. E-mail lu textuellement sur le site officiel. Aucun téléphone affiché sur la page. L'atelier de façonnage est bien hors IdF (Nérac, 47) comme signalé, mais la vitrine commerciale et les chantiers sont parisiens. Domaine hors liste d'exclusion. Source e-mail : https://www.artefacts-paris.com.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q243" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>info@artefacts-paris.com</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="15" customHeight="1" s="33">
-      <c r="L244" s="32" t="n"/>
+      <c r="A244" t="n">
+        <v>244</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>2</v>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>marbreries-idf</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>H. Chevalier</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Suresnes (26 rue Henri Regnault, 92150)</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>Confirmée : restauration du patrimoine bâti depuis 1946 (maçonnerie-pierre, restauration de sculpture, hôtels particuliers et châteaux), 250 salariés, 80 M€ de CA ; adresse à Sures…</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>https://www.hchevalier.com</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>01 45 06 83 33</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L244" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : restauration du patrimoine bâti depuis 1946 (maçonnerie-pierre, restauration de sculpture, hôtels particuliers et châteaux), 250 salariés, 80 M€ de CA ; adresse à Suresnes confirmée. E-mail et téléphone lus textuellement sur la page d'accueil du site officiel. Domaine hors liste d'exclusion. Profil patrimoine/monuments : pertinence moyenne pour un calcaire égyptien standard, comme indiqué dans le candidat. Source e-mail : https://www.hchevalier.com.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q244" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>contact@hchevalier.com</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="15" customHeight="1" s="33">
-      <c r="L245" s="32" t="n"/>
+      <c r="A245" t="n">
+        <v>245</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>2</v>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>marbreries-idf</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>Vexin Patrimoine</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secteur Vexin / Île-de-France (95) — aucune adresse précise </t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Confirmée : tailleur de pierre (taille sur mesure intérieur/extérieur, restauration historique, création, sols en pierre), plus de 15 ans d'expérience, clients pro et particuliers,…</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>https://vexinpatrimoine.fr</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>01 30 73 86 50</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L245" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : tailleur de pierre (taille sur mesure intérieur/extérieur, restauration historique, création, sols en pierre), plus de 15 ans d'expérience, clients pro et particuliers, zone Vexin/Île-de-France. Deux graphies sur le site : le pied de page affiche textuellement contact@vexinpatrimoine.fr (correct) ; la barre latérale affiche la coquille « contat@vexinpatrimoine.fr ». Utiliser contact@vexinpatrimoine.fr. Téléphone confirmé (affiché deux fois). Aucune ville précise publiée, cohérent avec le candidat. Domaine hors liste d'exclusion. Source e-mail : https://vexinpatrimoine.fr/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q245" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>contact@vexinpatrimoine.fr</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="15" customHeight="1" s="33">
-      <c r="L246" s="32" t="n"/>
+      <c r="A246" t="n">
+        <v>246</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>2</v>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>marbreries-idf</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Accolade Artisans</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Viarmes (14 rue Kleinpeter, 95270)</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>Confirmée : taille de pierre et maçonnerie de restauration du bâti ancien (certification Qualibat restauration pierre de taille et maçonnerie du patrimoine) ; adresse à Viarmes (95…</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>https://www.accoladeartisans.fr</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>06 27 85 91 92</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L246" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : taille de pierre et maçonnerie de restauration du bâti ancien (certification Qualibat restauration pierre de taille et maçonnerie du patrimoine) ; adresse à Viarmes (95270) confirmée. E-mail lu textuellement dans la section Coordonnées du pied de page ; téléphone confirmé (en-tête et pied de page). Domaine hors liste d'exclusion. Site officiel, pas un annuaire. Source e-mail : https://www.accoladeartisans.fr/taille-de-pierre.htm.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q246" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>contact@accoladeartisans.fr</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="15" customHeight="1" s="33">
-      <c r="L247" s="32" t="n"/>
+      <c r="A247" t="n">
+        <v>247</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>2</v>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>marbreries-idf</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Techno Pierre</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Vanves (35 rue Aristide Briand, 92170)</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>Confirmée : tailleur de pierres et marbrier du bâtiment (taille de pierre, marbrerie, rénovation et revêtement de façades en pierre, marbre et granit) ; adresse à Vanves confirmée.</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>https://www.technopierre.fr</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>09 74 56 39 83</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L247" s="32" t="inlineStr">
+        <is>
+          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : tailleur de pierres et marbrier du bâtiment (taille de pierre, marbrerie, rénovation et revêtement de façades en pierre, marbre et granit) ; adresse à Vanves confirmée. AUCUN e-mail publié sur le site officiel : la page contactez-nous.php ne propose qu'un formulaire (le lien « E-mail » pointe vers ce formulaire, pas vers une adresse). Retenu sur la base du téléphone vérifié 09 74 56 39 83, affiché plusieurs fois sur la page. Domaine hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q247" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
     </row>
     <row r="248" ht="15" customHeight="1" s="33">
-      <c r="L248" s="32" t="n"/>
+      <c r="A248" t="n">
+        <v>248</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>1</v>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>normandie</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Guilloux Matériaux</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Cormeilles (27) et Rouen (76) — siège Saint-Pair-sur-Mer (50</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Confirmé : négoce indépendant de matériaux de construction, 10 agences en Normandie (dont Cormeilles 27 et Rouen 76), scierie/atelier à Vire, siège à Saint-Pair-sur-Mer (50380).</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>https://www.guillouxmateriaux.com</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>02 33 48 14 44 (siège) ; agence Cormeilles 02 32 57 15 98 ; agence Rouen 02 32 12 11 80</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L248" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé : négoce indépendant de matériaux de construction, 10 agences en Normandie (dont Cormeilles 27 et Rouen 76), scierie/atelier à Vire, siège à Saint-Pair-sur-Mer (50380). E-mail lu TEXTUELLEMENT sur les mentions légales (responsable de la publication). Attention : le domaine de l'e-mail (guilloux-materiaux.com, avec tiret) diffère du domaine du site (guillouxmateriaux.com) — c'est bien ce qu'affiche le site officiel. Téléphones siège/Cormeilles/Rouen tous confirmés sur la même page. Hors liste d'exclusion. Source e-mail : https://www.guillouxmateriaux.com/mentions-legales-guilloux-materiaux-le-specialiste-des-materiaux-de-construction/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q248" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>bonjour@guilloux-materiaux.com</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="15" customHeight="1" s="33">
-      <c r="L249" s="32" t="n"/>
+      <c r="A249" t="n">
+        <v>249</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>1</v>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>normandie</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Sani 27 (« Le Géant du carrelage »)</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Angerville-la-Campagne (27930), ZAC de Villeneuve — près d'É</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Confirmé : magasin spécialiste du carrelage (« le plus grand magasin de carrelage ») avec sanitaire, robinetterie et meubles de salle de bain ; adresse ZAC de Villeneuve, 27930 Ang…</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>https://sani27.com</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>02 32 28 00 12</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L249" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé : magasin spécialiste du carrelage (« le plus grand magasin de carrelage ») avec sanitaire, robinetterie et meubles de salle de bain ; adresse ZAC de Villeneuve, 27930 Angerville-la-Campagne, zone d'Évreux. contact@sani27.fr est écrit TEXTUELLEMENT dans le pied de page du site officiel. Divergence confirmée : le lien mailto associé pointe vers sani27@wanadoo.fr — en cas de non-réponse sur contact@sani27.fr, utiliser sani27@wanadoo.fr en seconde adresse. Téléphone 02 32 28 00 12 confirmé. Hors liste d'exclusion. Source e-mail : https://sani27.com/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q249" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>contact@sani27.fr</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="15" customHeight="1" s="33">
-      <c r="L250" s="32" t="n"/>
+      <c r="A250" t="n">
+        <v>250</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>1</v>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>normandie</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>BCA Matériaux Anciens</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Méry-Corbon (14370) et Pont-l'Évêque (14130) — siège Segré-e</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Confirmé : « Spécialiste des matériaux anciens » — dallages et carrelages anciens en pierre, parquets anciens, tomettes, pavés, parements pierre, cheminées ; deux agences normandes…</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>https://www.bca-materiauxanciens.com</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>02 31 23 95 87 (Méry-Corbon) ; 02 61 67 23 40 (Pont-l'Évêque) ; +33 (0)2 41 61 62 40 (siège)</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L250" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé : « Spécialiste des matériaux anciens » — dallages et carrelages anciens en pierre, parquets anciens, tomettes, pavés, parements pierre, cheminées ; deux agences normandes (Méry-Corbon et Pont-l'Évêque), siège en Pays de la Loire. normandie@bcamateriaux.com (agence Méry-Corbon) lu TEXTUELLEMENT sur le site officiel, ainsi que pontleveque@bcamateriaux.com, info@bcamateriaux.com et david@bcamateriaux.com (anglais). Tous les téléphones confirmés. Cœur de métier aligné (dallages pierre par lots). Hors liste d'exclusion. Source e-mail : https://www.bca-materiauxanciens.com.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q250" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>normandie@bcamateriaux.com</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="15" customHeight="1" s="33">
-      <c r="L251" s="32" t="n"/>
+      <c r="A251" t="n">
+        <v>251</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>2</v>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>normandie</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Adéquate - Marbrerie Décorative</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Seulline (14310), ZA Eco 5 — près de Caen</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Confirmé : marbrerie décorative avec showroom (visites sur rendez-vous), ZA Eco 5 n° 7 et 9, 14310 Seulline, « près de Caen en Normandie ».</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>https://www.adequatemarbrerie.fr</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>02 31 24 11 22</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L251" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé : marbrerie décorative avec showroom (visites sur rendez-vous), ZA Eco 5 n° 7 et 9, 14310 Seulline, « près de Caen en Normandie ». contact@adequatemarbrerie.fr lu TEXTUELLEMENT sur la page contact du site officiel (en texte et en lien mailto, concordants). Téléphone confirmé. Hors liste d'exclusion. Source e-mail : https://www.adequatemarbrerie.fr/contact.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q251" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>contact@adequatemarbrerie.fr</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="15" customHeight="1" s="33">
-      <c r="L252" s="32" t="n"/>
+      <c r="A252" t="n">
+        <v>252</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>2</v>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>normandie</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Motte Décoration</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Le Pré-d'Auge (14340), 10 Chemin des Vatines — entre Cambrem</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Confirmé via sources tierces : société MOTTE DECORATION immatriculée (SIREN 844835728, taille/façonnage/finissage de pierres) au Pré-d'Auge (14340) ; marbrerie décorative familiale…</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>https://www.mottedecoration.com</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>02 31 32 22 00</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L252" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé via sources tierces : société MOTTE DECORATION immatriculée (SIREN 844835728, taille/façonnage/finissage de pierres) au Pré-d'Auge (14340) ; marbrerie décorative familiale (marbre, granit, quartz, pierre naturelle) intervenant sur toute la Normandie — societe.com, Initiative Calvados, Pages Jaunes et index du site officiel concordants. E-mail NON confirmé textuellement : le site officiel refuse toute lecture automatisée (HTTP 401 sur l'accueil et la page contact), vérification visuelle impossible ici. L'index du moteur de recherche attribue bien contact@mottedecoration.com et le 02 31 32 22 00 au site officiel, et le téléphone est corroboré par plusieurs sources indépendantes. Retenu sur REPLI TÉLÉPHONE vérifié (02 31 32 22 00) ; ne pas utiliser l'e-mail avant confirmation visuelle sur le site. Hors liste d'exclusion. Entreprise réelle, en France, site vivant (blocage anti-robot, pas site mort). Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q252" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>contact@mottedecoration.com</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="15" customHeight="1" s="33">
-      <c r="L253" s="32" t="n"/>
+      <c r="A253" t="n">
+        <v>253</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>2</v>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>normandie</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Carreau Déco (SARL)</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Évreux (27) ; autres magasins : Barentin, Tourville-la-Riviè</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Confirmé : enseigne de carrelage (« Carrelage haut de gamme, sol et mur ») — grès cérame, dalles, faïence, intérieur/extérieur ; 6 points de vente confirmés dont Évreux, Barentin, …</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>https://www.carreaudeco.com</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>02 32 30 62 04 (Évreux) ; 02 37 21 27 80 (Lèves/standard) ; 02 78 77 51 00 (Barentin) ; 02 78 77 09 77 (Tourville) ; 02 78 93 05 05 (Montivilliers) ; 02 37 46 23 27 (Vernouillet)</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L253" s="32" t="inlineStr">
+        <is>
+          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
+        </is>
+      </c>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé : enseigne de carrelage (« Carrelage haut de gamme, sol et mur ») — grès cérame, dalles, faïence, intérieur/extérieur ; 6 points de vente confirmés dont Évreux, Barentin, Tourville-la-Rivière et Montivilliers. AUCUN e-mail publié textuellement sur le site officiel (formulaire de contact uniquement) — vérifié. Retenu sur REPLI TÉLÉPHONE : les 6 numéros de magasins sont confirmés sur le site officiel, dont Évreux 02 32 30 62 04 et le standard de Lèves 02 37 21 27 80. Hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q253" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
     </row>
     <row r="254" ht="15" customHeight="1" s="33">
-      <c r="L254" s="32" t="n"/>
+      <c r="A254" t="n">
+        <v>254</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>2</v>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>normandie</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Carré &amp; Déco (SAS Fortin Design)</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Colombelles (14460), 6 rue de la Métallurgie — agglomération</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>Confirmé : magasin de carrelage et céramique avec showroom (« votre expert en carrelage et céramique à proximité de Caen »), pierre naturelle présente en gamme extérieure (activité…</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>https://carre-deco.fr</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>02 31 34 40 50</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L254" s="32" t="inlineStr">
+        <is>
+          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
+        </is>
+      </c>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé : magasin de carrelage et céramique avec showroom (« votre expert en carrelage et céramique à proximité de Caen »), pierre naturelle présente en gamme extérieure (activité secondaire). AUCUN e-mail publié textuellement sur le site officiel (formulaire uniquement) — vérifié. Retenu sur REPLI TÉLÉPHONE : 02 31 34 40 50 confirmé sur le site officiel, adresse Colombelles confirmée. Nuance : la pierre naturelle n'est pas son cœur de métier (carrelage/céramique d'abord). Hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q254" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1" s="33">
-      <c r="L255" s="32" t="n"/>
+      <c r="A255" t="n">
+        <v>255</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>2</v>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>destockage-exterieur</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Vallois (groupe Spie batignolles paysage) — agence Val de Seine</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Val-de-Reuil (27100, Z.A la Comminière) — agence IDF à Trapp</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>Confirmée : « aménagements paysagers » dans le Grand Ouest, société de Spie batignolles paysage (vérifié sur la page d'accueil) ; la page contact confirme l'agence Val de Seine à V…</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>https://www.vallois.eu/</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>02 32 40 32 30 (Val de Seine) ; 01 30 16 07 00 (IDF Trappes)</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L255" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment destockage-exterieur). Confirmée : « aménagements paysagers » dans le Grand Ouest, société de Spie batignolles paysage (vérifié sur la page d'accueil) ; la page contact confirme l'agence Val de Seine à Val-de-Reuil 27100 et l'agence IDF à Trappes 78190. E-mail lu textuellement dans la fiche « Agence Val de Seine » de la page contact ; les deux téléphones y figurent aussi textuellement. Précision : la page contact donne comme siège social de Spie batignolles paysage Nanterre (92) et comme siège administratif St Hymer (14) ; Mirville (76210) est l'adresse de l'agence de l'Estuaire, pas du siège. Hors liste d'exclusion. Candidat solide. Source e-mail : https://www.vallois.eu/contact.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q255" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>agence-valdeseine@vallois.eu</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="15" customHeight="1" s="33">
-      <c r="L256" s="32" t="n"/>
+      <c r="A256" t="n">
+        <v>256</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>1</v>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>destockage-exterieur</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Tricycle Environnement / Bâticycle</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Gennevilliers (120 rue du Moulin de Cage, 92230)</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>Confirmée : « Matériaux BTP d'occasion », « Réemploi de matériaux de second œuvre », « Curage de bâtiment » — réemploi/revente de matériaux de construction, vérifié sur le site off…</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>https://www.tricycle-environnement.fr/</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>07 60 62 41 36</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L256" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment destockage-exterieur). Confirmée : « Matériaux BTP d'occasion », « Réemploi de matériaux de second œuvre », « Curage de bâtiment » — réemploi/revente de matériaux de construction, vérifié sur le site officiel. E-mail lu textuellement en en-tête ET en pied de page ; téléphone confirmé sous deux formats (+33 7 60 62 41 36 / 07 60 62 41 36) ; adresse 120 rue du Moulin de Cage, 92230 Gennevilliers confirmée en pied de page — la ville même du stock. Hors liste d'exclusion. Candidat solide. Source e-mail : https://www.tricycle-environnement.fr/.  📍 Même ville que le dépôt (Gennevilliers) — réemploi : bon candidat reprise de lot. NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q256" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>contact@tri-cycle.fr</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="15" customHeight="1" s="33">
-      <c r="L257" s="32" t="n"/>
+      <c r="A257" t="n">
+        <v>257</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>2</v>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>destockage-exterieur</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Minéka</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Villeurbanne (182 rue de la Poudrette, 69100)</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>Confirmée : adresse « 182 rue de la Poudrette 69100 VILLEURBANNE » vérifiée dans les mentions légales, qui mentionnent aussi le magasin « Minéstock » (« Venez nous voir au Minéstoc…</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>https://mineka.fr/</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L257" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment destockage-exterieur). Confirmée : adresse « 182 rue de la Poudrette 69100 VILLEURBANNE » vérifiée dans les mentions légales, qui mentionnent aussi le magasin « Minéstock » (« Venez nous voir au Minéstock ») — structure de collecte/revente avec point de vente physique, pas une pure marketplace. E-mail lu textuellement dans les mentions légales (« Adresse électronique : contact@mineka.fr »), seule adresse de la page. AUCUN téléphone publié : le contact ne pourra se faire que par e-mail (vérifié). En France (Lyon/Villeurbanne) ; limite logistique : loin des stocks de Vernon/Gennevilliers, retrait à organiser. Hors liste d'exclusion. Source e-mail : https://mineka.fr/mentions-legales/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q257" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>contact@mineka.fr</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="15" customHeight="1" s="33">
-      <c r="L258" s="32" t="n"/>
+      <c r="A258" t="n">
+        <v>258</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>2</v>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>destockage-exterieur</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Pinson Paysage (groupe Osmaïa)</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Andilly (13 avenue des Cures, 95580)</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>Confirmée : page « Nous contacter » vérifiée — siège « 13 Avenue des Cures, 95580 Andilly » ; activités « Création », « Entretien » (espaces verts) et « Génie écologique » affichée…</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>https://www.pinson-paysage.com/</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L258" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment destockage-exterieur). Confirmée : page « Nous contacter » vérifiée — siège « 13 Avenue des Cures, 95580 Andilly » ; activités « Création », « Entretien » (espaces verts) et « Génie écologique » affichées, cohérentes avec une entreprise paysagère IDF. E-mail lu textuellement (seule adresse de la page). AUCUN téléphone sur la page contact (formulaire uniquement) : contact par e-mail vérifié. Réserve maintenue : le site met en avant le végétal/génie écologique plus que la maçonnerie minérale — pertinence segment (b) à pondérer. Hors liste d'exclusion. Source e-mail : https://www.pinson-paysage.com/nous-contacter/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q258" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>pinson@pinson-paysage.com</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="15" customHeight="1" s="33">
-      <c r="L259" s="32" t="n"/>
+      <c r="A259" t="n">
+        <v>259</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>1</v>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>destockage-exterieur</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>NOZ (centrale d'achat S.F.N.)</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Saint-Berthevin (53940)</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>Confirmée : page contact vérifiée — adresse « 53940 Saint-Berthevin – France », formulaire avec champ « Vous êtes ? » incluant « Je suis un fournisseur » et objet « Besoin de désto…</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>https://www.noz.fr/</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>02 43 01 53 54</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L259" s="32" t="inlineStr">
+        <is>
+          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment destockage-exterieur). Confirmée : page contact vérifiée — adresse « 53940 Saint-Berthevin – France », formulaire avec champ « Vous êtes ? » incluant « Je suis un fournisseur » et objet « Besoin de déstockage », cohérent avec l'activité de rachat de surstocks/lots. RETENU SANS E-MAIL : aucun e-mail publié sur https://www.noz.fr/contactez-nous/ (revérifié le 26/10/2026 — le seul mot « Email » est un champ de formulaire), mais le téléphone 02 43 01 53 54 y est écrit textuellement et vérifié ; contact via ce numéro ou le formulaire fournisseur « Besoin de déstockage ». Hors liste d'exclusion. Réserve : lot minéral lourd atypique dans leur mix. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
       <c r="Q259" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -5936,7 +5936,11 @@
           <t>www.la-roche-taillee.fr</t>
         </is>
       </c>
-      <c r="J72" s="51" t="n"/>
+      <c r="J72" s="51" t="inlineStr">
+        <is>
+          <t>02 35 72 01 62</t>
+        </is>
+      </c>
       <c r="K72" s="52" t="inlineStr">
         <is>
           <t>Voir</t>
@@ -5949,11 +5953,20 @@
       </c>
       <c r="M72" s="54" t="n"/>
       <c r="N72" s="53" t="n"/>
-      <c r="O72" s="53" t="n"/>
+      <c r="O72" s="53" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> [26/10 croisement fichier propriétaire] E-mail et tél apportés par le fichier (Sotteville-lès-Rouen). NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
       <c r="P72" s="55" t="n"/>
       <c r="Q72" s="56">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>contact@la-roche-taillee.fr</t>
+        </is>
       </c>
     </row>
     <row r="73" ht="45.75" customHeight="1" s="33">
@@ -15621,7 +15634,7 @@
       </c>
       <c r="I215" s="32" t="inlineStr">
         <is>
-          <t>https://www.adi-roc.fr</t>
+          <t>https://www.adiroc.fr/produit/pierre-egypte/</t>
         </is>
       </c>
       <c r="J215" s="32" t="inlineStr">
@@ -15646,7 +15659,7 @@
       </c>
       <c r="O215" s="32" t="inlineStr">
         <is>
-          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi. Pas d'e-mail publié : formulaire du site ou téléphone. NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi. Pas d'e-mail publié : formulaire du site ou téléphone. NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi [26/10 croisement fichier propriétaire] Site/preuve (fichier) : adiroc.fr — page « pierre d'Égypte 20 mm » confirmée. Limite : peut déjà avoir un fournisseur égyptien.</t>
         </is>
       </c>
       <c r="Q215" s="44">
@@ -15872,7 +15885,7 @@
       </c>
       <c r="O218" s="32" t="inlineStr">
         <is>
-          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi [26/10 croisement fichier propriétaire] Le fichier précise : vend déjà une gamme « Egypta » → angle « second fournisseur différencié ».</t>
         </is>
       </c>
       <c r="Q218" s="44">
@@ -15991,7 +16004,7 @@
       </c>
       <c r="J220" s="32" t="inlineStr">
         <is>
-          <t>06 87 53 33 76</t>
+          <t>06 87 53 33 76 / 02 37 48 79 91</t>
         </is>
       </c>
       <c r="K220" s="32" t="inlineStr">
@@ -16063,7 +16076,7 @@
       </c>
       <c r="J221" s="32" t="inlineStr">
         <is>
-          <t>06 25 28 12 12</t>
+          <t>06 25 28 12 12 / 07 73 60 46 37</t>
         </is>
       </c>
       <c r="K221" s="32" t="inlineStr">
@@ -16371,7 +16384,7 @@
       </c>
       <c r="O225" s="32" t="inlineStr">
         <is>
-          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi [26/10 croisement fichier propriétaire] ⚠️ Coordonnées divergentes : relais du 26/10 matin = ille-de-vilaine@eurovia.com / 02 99 05 03 00 ; fichier du soir = « agence locale à confirmer ». À CONFIRMER avant tout contact.</t>
         </is>
       </c>
       <c r="Q225" s="44">
@@ -16515,7 +16528,7 @@
       </c>
       <c r="O227" s="32" t="inlineStr">
         <is>
-          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi.  NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi [26/10 croisement fichier propriétaire] Deux e-mails relevés : secretariat.keravis@lessard.fr (relais) et keravis@lessard.fr (fichier) — confirmer le bon.</t>
         </is>
       </c>
       <c r="Q227" s="44">
@@ -16601,53 +16614,53 @@
       </c>
     </row>
     <row r="229" ht="15" customHeight="1" s="33">
-      <c r="A229" t="n">
+      <c r="A229" s="32" t="n">
         <v>229</v>
       </c>
-      <c r="B229" t="inlineStr">
+      <c r="B229" s="32" t="inlineStr">
         <is>
           <t>5e liste — recherche (26/10)</t>
         </is>
       </c>
-      <c r="C229" t="n">
+      <c r="C229" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D229" t="inlineStr">
+      <c r="D229" s="32" t="inlineStr">
         <is>
           <t>importateurs</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr">
+      <c r="E229" s="32" t="inlineStr">
         <is>
           <t>Marbrerie Arnaud (SUD PIERRE)</t>
         </is>
       </c>
-      <c r="F229" t="inlineStr">
+      <c r="F229" s="32" t="inlineStr">
         <is>
           <t>Colombiers / Béziers</t>
         </is>
       </c>
-      <c r="G229" t="inlineStr">
+      <c r="G229" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
+      <c r="H229" s="32" t="inlineStr">
         <is>
           <t>Confirmée : « Importateur et distributeur de pierre naturelle depuis 2012 », import direct Turquie, Égypte, Chine (page d'accueil) ; showroom 700 m² à Béziers, adresse Route de Nar…</t>
         </is>
       </c>
-      <c r="I229" t="inlineStr">
+      <c r="I229" s="32" t="inlineStr">
         <is>
           <t>https://www.marbreriearnaud34.com/</t>
         </is>
       </c>
-      <c r="J229" t="inlineStr">
+      <c r="J229" s="32" t="inlineStr">
         <is>
           <t>04 67 35 82 22</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr">
+      <c r="K229" s="32" t="inlineStr">
         <is>
           <t>Recherche Claude (26/10)</t>
         </is>
@@ -16657,12 +16670,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N229" t="inlineStr">
+      <c r="N229" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
       </c>
-      <c r="O229" t="inlineStr">
+      <c r="O229" s="32" t="inlineStr">
         <is>
           <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : « Importateur et distributeur de pierre naturelle depuis 2012 », import direct Turquie, Égypte, Chine (page d'accueil) ; showroom 700 m² à Béziers, adresse Route de Narbonne à Colombiers. Villes conformes. E-mail lu textuellement dans les mentions légales (« e-mail : j.andreo@marbrerie-arnaud.com », propriétaire SUD PIERRE). Le domaine de l'e-mail (marbrerie-arnaud.com) diffère du domaine du site, mais c'est bien l'adresse publiée officiellement. Téléphone confirmé sur mentions légales et accueil. Domaine hors liste d'exclusion. Source e-mail : https://www.marbreriearnaud34.com/mentions-legales/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
@@ -16671,60 +16684,60 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R229" t="inlineStr">
+      <c r="R229" s="32" t="inlineStr">
         <is>
           <t>j.andreo@marbrerie-arnaud.com</t>
         </is>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1" s="33">
-      <c r="A230" t="n">
+      <c r="A230" s="32" t="n">
         <v>230</v>
       </c>
-      <c r="B230" t="inlineStr">
+      <c r="B230" s="32" t="inlineStr">
         <is>
           <t>5e liste — recherche (26/10)</t>
         </is>
       </c>
-      <c r="C230" t="n">
+      <c r="C230" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D230" t="inlineStr">
+      <c r="D230" s="32" t="inlineStr">
         <is>
           <t>importateurs</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
+      <c r="E230" s="32" t="inlineStr">
         <is>
           <t>Artemis (Artemis Prestige)</t>
         </is>
       </c>
-      <c r="F230" t="inlineStr">
+      <c r="F230" s="32" t="inlineStr">
         <is>
           <t>Cabriès (Plan de Campagne) ; entrepôt à Simiane-Collongue</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
+      <c r="G230" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
+      <c r="H230" s="32" t="inlineStr">
         <is>
           <t>Confirmée : importateur-vendeur de pierre naturelle (travertin, marbre, pierre d'Égypte, grès cérame), livraison France entière. Showroom Expobat Plan de Campagne 13480 Cabriès + e…</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr">
+      <c r="I230" s="32" t="inlineStr">
         <is>
           <t>https://www.artemis-prestige.com/</t>
         </is>
       </c>
-      <c r="J230" t="inlineStr">
+      <c r="J230" s="32" t="inlineStr">
         <is>
           <t>04 42 31 41 40</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
+      <c r="K230" s="32" t="inlineStr">
         <is>
           <t>Recherche Claude (26/10)</t>
         </is>
@@ -16734,12 +16747,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N230" t="inlineStr">
+      <c r="N230" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
       </c>
-      <c r="O230" t="inlineStr">
+      <c r="O230" s="32" t="inlineStr">
         <is>
           <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : importateur-vendeur de pierre naturelle (travertin, marbre, pierre d'Égypte, grès cérame), livraison France entière. Showroom Expobat Plan de Campagne 13480 Cabriès + entrepôt logistique 13109 Simiane-Collongue confirmés sur la page contact. E-mail présent textuellement sur la page contact (texte du lien et mailto). Téléphone confirmé. Pierre d'Égypte explicitement au catalogue. Domaine hors liste d'exclusion. Source e-mail : https://www.artemis-prestige.com/contact.html.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
@@ -16748,60 +16761,60 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R230" t="inlineStr">
+      <c r="R230" s="32" t="inlineStr">
         <is>
           <t>artemis-prestige@orange.fr</t>
         </is>
       </c>
     </row>
     <row r="231" ht="15" customHeight="1" s="33">
-      <c r="A231" t="n">
+      <c r="A231" s="32" t="n">
         <v>231</v>
       </c>
-      <c r="B231" t="inlineStr">
+      <c r="B231" s="32" t="inlineStr">
         <is>
           <t>5e liste — recherche (26/10)</t>
         </is>
       </c>
-      <c r="C231" t="n">
+      <c r="C231" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D231" t="inlineStr">
+      <c r="D231" s="32" t="inlineStr">
         <is>
           <t>importateurs</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr">
+      <c r="E231" s="32" t="inlineStr">
         <is>
           <t>Minéral Pierre Naturelle (Pierre de l'Est SAS)</t>
         </is>
       </c>
-      <c r="F231" t="inlineStr">
+      <c r="F231" s="32" t="inlineStr">
         <is>
           <t>Woustviller (magasins Lyon, Strasbourg, Nancy, Beaune, Thion</t>
         </is>
       </c>
-      <c r="G231" t="inlineStr">
+      <c r="G231" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
+      <c r="H231" s="32" t="inlineStr">
         <is>
           <t>Confirmée : spécialiste pierre naturelle (travertin, calcaire, marbre, granit...), 7 magasins France/Allemagne dont Lyon, Strasbourg, Nancy, Beaune, Thionville. Mentions légales : …</t>
         </is>
       </c>
-      <c r="I231" t="inlineStr">
+      <c r="I231" s="32" t="inlineStr">
         <is>
           <t>https://www.mineral-pierre-naturelle.fr/</t>
         </is>
       </c>
-      <c r="J231" t="inlineStr">
-        <is>
-          <t>03 60 12 33 53</t>
-        </is>
-      </c>
-      <c r="K231" t="inlineStr">
+      <c r="J231" s="32" t="inlineStr">
+        <is>
+          <t>03 60 12 33 53 / 03 87 98 67 37</t>
+        </is>
+      </c>
+      <c r="K231" s="32" t="inlineStr">
         <is>
           <t>Recherche Claude (26/10)</t>
         </is>
@@ -16811,14 +16824,14 @@
           <t>À contacter (formulaire/tél) — EN ATTENTE</t>
         </is>
       </c>
-      <c r="N231" t="inlineStr">
+      <c r="N231" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
       </c>
-      <c r="O231" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : spécialiste pierre naturelle (travertin, calcaire, marbre, granit...), 7 magasins France/Allemagne dont Lyon, Strasbourg, Nancy, Beaune, Thionville. Mentions légales : Pierre de l'Est SAS, 44 Rue de Nancy, 57915 Woustviller — raison sociale et ville confirmées. AUCUN e-mail publié : vérifié sur l'accueil et les mentions légales (contact par téléphone ou formulaire uniquement). Repli téléphone VÉRIFIÉ : 03 60 12 33 53 affiché sur l'accueil (« Conseil d'expert ») et dans les mentions légales. Le produit Sinai Pearl n'était pas visible sur la portion d'accueil lue, mais l'activité calcaire/travertin est confirmée. Domaine hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+      <c r="O231" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : spécialiste pierre naturelle (travertin, calcaire, marbre, granit...), 7 magasins France/Allemagne dont Lyon, Strasbourg, Nancy, Beaune, Thionville. Mentions légales : Pierre de l'Est SAS, 44 Rue de Nancy, 57915 Woustviller — raison sociale et ville confirmées. AUCUN e-mail publié : vérifié sur l'accueil et les mentions légales (contact par téléphone ou formulaire uniquement). Repli téléphone VÉRIFIÉ : 03 60 12 33 53 affiché sur l'accueil (« Conseil d'expert ») et dans les mentions légales. Le produit Sinai Pearl n'était pas visible sur la portion d'accueil lue, mais l'activité calcaire/travertin est confirmée. Domaine hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi [26/10 croisement fichier propriétaire] 2e téléphone (fichier) : 03 87 98 67 37.</t>
         </is>
       </c>
       <c r="Q231" s="44">
@@ -16827,53 +16840,53 @@
       </c>
     </row>
     <row r="232" ht="15" customHeight="1" s="33">
-      <c r="A232" t="n">
+      <c r="A232" s="32" t="n">
         <v>232</v>
       </c>
-      <c r="B232" t="inlineStr">
+      <c r="B232" s="32" t="inlineStr">
         <is>
           <t>5e liste — recherche (26/10)</t>
         </is>
       </c>
-      <c r="C232" t="n">
+      <c r="C232" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D232" t="inlineStr">
+      <c r="D232" s="32" t="inlineStr">
         <is>
           <t>importateurs</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr">
+      <c r="E232" s="32" t="inlineStr">
         <is>
           <t>Nimex International</t>
         </is>
       </c>
-      <c r="F232" t="inlineStr">
+      <c r="F232" s="32" t="inlineStr">
         <is>
           <t>Caissargues (dépôt à Nîmes)</t>
         </is>
       </c>
-      <c r="G232" t="inlineStr">
+      <c r="G232" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
+      <c r="H232" s="32" t="inlineStr">
         <is>
           <t>Confirmée : importateur-distributeur de pierre naturelle, marbre, granit, travertin ; approvisionnement direct carrières (Espagne, Italie, Portugal, Grèce, Turquie, ÉGYPTE, Inde) ;…</t>
         </is>
       </c>
-      <c r="I232" t="inlineStr">
+      <c r="I232" s="32" t="inlineStr">
         <is>
           <t>https://www.nimexinternational.fr/</t>
         </is>
       </c>
-      <c r="J232" t="inlineStr">
+      <c r="J232" s="32" t="inlineStr">
         <is>
           <t>04 30 22 01 75</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr">
+      <c r="K232" s="32" t="inlineStr">
         <is>
           <t>Recherche Claude (26/10)</t>
         </is>
@@ -16883,12 +16896,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N232" t="inlineStr">
+      <c r="N232" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
       </c>
-      <c r="O232" t="inlineStr">
+      <c r="O232" s="32" t="inlineStr">
         <is>
           <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : importateur-distributeur de pierre naturelle, marbre, granit, travertin ; approvisionnement direct carrières (Espagne, Italie, Portugal, Grèce, Turquie, ÉGYPTE, Inde) ; dépôt à Nîmes, vente et livraison France entière. Adresse : 14 avenue de la Vistrenque, 30132 Caissargues — ville confirmée. E-mail présent textuellement dans le pied de page du site officiel. Téléphone confirmé. L'Égypte figure parmi les pays d'approvisionnement cités. Domaine hors liste d'exclusion. Source e-mail : https://www.nimexinternational.fr/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
@@ -16897,60 +16910,60 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R232" t="inlineStr">
+      <c r="R232" s="32" t="inlineStr">
         <is>
           <t>nimex.international@wanadoo.fr</t>
         </is>
       </c>
     </row>
     <row r="233" ht="15" customHeight="1" s="33">
-      <c r="A233" t="n">
+      <c r="A233" s="32" t="n">
         <v>233</v>
       </c>
-      <c r="B233" t="inlineStr">
+      <c r="B233" s="32" t="inlineStr">
         <is>
           <t>5e liste — recherche (26/10)</t>
         </is>
       </c>
-      <c r="C233" t="n">
+      <c r="C233" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D233" t="inlineStr">
+      <c r="D233" s="32" t="inlineStr">
         <is>
           <t>importateurs</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr">
+      <c r="E233" s="32" t="inlineStr">
         <is>
           <t>Travertin.fr</t>
         </is>
       </c>
-      <c r="F233" t="inlineStr">
+      <c r="F233" s="32" t="inlineStr">
         <is>
           <t>Fos-sur-Mer (centre logistique)</t>
         </is>
       </c>
-      <c r="G233" t="inlineStr">
+      <c r="G233" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
+      <c r="H233" s="32" t="inlineStr">
         <is>
           <t>Confirmée : le site se décrit comme « un importateur et un grossiste spécialisé en travertin » (carrières Turquie/Italie), dalles, carrelages, margelles, livraison France entière. …</t>
         </is>
       </c>
-      <c r="I233" t="inlineStr">
+      <c r="I233" s="32" t="inlineStr">
         <is>
           <t>https://www.travertin.fr/</t>
         </is>
       </c>
-      <c r="J233" t="inlineStr">
+      <c r="J233" s="32" t="inlineStr">
         <is>
           <t>09 70 70 73 75</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr">
+      <c r="K233" s="32" t="inlineStr">
         <is>
           <t>Recherche Claude (26/10)</t>
         </is>
@@ -16960,12 +16973,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N233" t="inlineStr">
+      <c r="N233" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
       </c>
-      <c r="O233" t="inlineStr">
+      <c r="O233" s="32" t="inlineStr">
         <is>
           <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : le site se décrit comme « un importateur et un grossiste spécialisé en travertin » (carrières Turquie/Italie), dalles, carrelages, margelles, livraison France entière. Adresse : Centre Logistique, 13270 Fos-sur-Mer — ville confirmée. E-mail présent textuellement dans le bloc contact du pied de page, sous l'adresse de Fos-sur-Mer. Téléphone confirmé (en-tête et pied de page). Domaine hors liste d'exclusion. Source e-mail : https://www.travertin.fr/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
@@ -16974,60 +16987,60 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R233" t="inlineStr">
+      <c r="R233" s="32" t="inlineStr">
         <is>
           <t>info@travertin.fr</t>
         </is>
       </c>
     </row>
     <row r="234" ht="15" customHeight="1" s="33">
-      <c r="A234" t="n">
+      <c r="A234" s="32" t="n">
         <v>234</v>
       </c>
-      <c r="B234" t="inlineStr">
+      <c r="B234" s="32" t="inlineStr">
         <is>
           <t>5e liste — recherche (26/10)</t>
         </is>
       </c>
-      <c r="C234" t="n">
+      <c r="C234" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D234" t="inlineStr">
+      <c r="D234" s="32" t="inlineStr">
         <is>
           <t>importateurs</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr">
+      <c r="E234" s="32" t="inlineStr">
         <is>
           <t>Espace Travertin (EURL GNPS Espace Carrelage)</t>
         </is>
       </c>
-      <c r="F234" t="inlineStr">
+      <c r="F234" s="32" t="inlineStr">
         <is>
           <t>Bollène</t>
         </is>
       </c>
-      <c r="G234" t="inlineStr">
+      <c r="G234" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H234" t="inlineStr">
+      <c r="H234" s="32" t="inlineStr">
         <is>
           <t>Confirmée partiellement : vente de travertin (dallage, margelles, plinthes, vasques, 200+ références) avec page « Devenir Revendeur » et prix de gros revendiqués ; adresse Impasse …</t>
         </is>
       </c>
-      <c r="I234" t="inlineStr">
+      <c r="I234" s="32" t="inlineStr">
         <is>
           <t>https://www.espace-travertin.fr/</t>
         </is>
       </c>
-      <c r="J234" t="inlineStr">
+      <c r="J234" s="32" t="inlineStr">
         <is>
           <t>07 68 18 70 32</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr">
+      <c r="K234" s="32" t="inlineStr">
         <is>
           <t>Recherche Claude (26/10)</t>
         </is>
@@ -17037,69 +17050,74 @@
           <t>À contacter (formulaire/tél) — EN ATTENTE</t>
         </is>
       </c>
-      <c r="N234" t="inlineStr">
+      <c r="N234" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
       </c>
-      <c r="O234" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée partiellement : vente de travertin (dallage, margelles, plinthes, vasques, 200+ références) avec page « Devenir Revendeur » et prix de gros revendiqués ; adresse Impasse de la Rode, 84500 Bollène confirmée. Le site vend aussi aux particuliers (pas uniquement B2B). Le siège à Étoile-sur-Rhône et la raison sociale GNPS n'apparaissent pas sur la page d'accueil (le PDF CGV mentionne « stone-diffusion-centre »). AUCUN e-mail publié sur la page d'accueil (vérifié). Repli téléphone VÉRIFIÉ : 07 68 18 70 32 affiché deux fois en haut de page en lien cliquable. Domaine hors liste d'exclusion. Profil un peu plus B2C que revendiqué, mais canal revendeur réel. Source e-mail : aucune (pas d e-mail publié). ⚠️ CONCURRENT suivi dans la veille prix (ambiguïtés marbre/calcaire) — approche uniquement « reprise de lot revendeur ». NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+      <c r="O234" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée partiellement : vente de travertin (dallage, margelles, plinthes, vasques, 200+ références) avec page « Devenir Revendeur » et prix de gros revendiqués ; adresse Impasse de la Rode, 84500 Bollène confirmée. Le site vend aussi aux particuliers (pas uniquement B2B). Le siège à Étoile-sur-Rhône et la raison sociale GNPS n'apparaissent pas sur la page d'accueil (le PDF CGV mentionne « stone-diffusion-centre »). AUCUN e-mail publié sur la page d'accueil (vérifié). Repli téléphone VÉRIFIÉ : 07 68 18 70 32 affiché deux fois en haut de page en lien cliquable. Domaine hors liste d'exclusion. Profil un peu plus B2C que revendiqué, mais canal revendeur réel. Source e-mail : aucune (pas d e-mail publié). ⚠️ CONCURRENT suivi dans la veille prix (ambiguïtés marbre/calcaire) — approche uniquement « reprise de lot revendeur ». NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi [26/10 croisement fichier propriétaire] E-mail apporté par le fichier : contactgnps26@gmail.com (Étoile-sur-Rhône). ⚠️ Identité exploitant contradictoire — VALIDER LA SOCIÉTÉ avant contact (consigne fichier).</t>
         </is>
       </c>
       <c r="Q234" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>contactgnps26@gmail.com</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="15" customHeight="1" s="33">
-      <c r="A235" t="n">
+      <c r="A235" s="32" t="n">
         <v>235</v>
       </c>
-      <c r="B235" t="inlineStr">
+      <c r="B235" s="32" t="inlineStr">
         <is>
           <t>5e liste — recherche (26/10)</t>
         </is>
       </c>
-      <c r="C235" t="n">
+      <c r="C235" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D235" t="inlineStr">
+      <c r="D235" s="32" t="inlineStr">
         <is>
           <t>importateurs</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr">
+      <c r="E235" s="32" t="inlineStr">
         <is>
           <t>DMC Miller</t>
         </is>
       </c>
-      <c r="F235" t="inlineStr">
+      <c r="F235" s="32" t="inlineStr">
         <is>
           <t>Pertuis (dépôt également à Gujan-Mestras, 33)</t>
         </is>
       </c>
-      <c r="G235" t="inlineStr">
+      <c r="G235" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H235" t="inlineStr">
+      <c r="H235" s="32" t="inlineStr">
         <is>
           <t>Confirmée : distributeur spécialiste du travertin (dalles 1er/2e choix, margelles, plinthes, mosaïques, pavés granit), vente au m², livraison France entière. Adresse 315 Rue Benjam…</t>
         </is>
       </c>
-      <c r="I235" t="inlineStr">
+      <c r="I235" s="32" t="inlineStr">
         <is>
           <t>https://www.dmcmiller.com/</t>
         </is>
       </c>
-      <c r="J235" t="inlineStr">
+      <c r="J235" s="32" t="inlineStr">
         <is>
           <t>06 66 55 44 42</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr">
+      <c r="K235" s="32" t="inlineStr">
         <is>
           <t>Recherche Claude (26/10)</t>
         </is>
@@ -17109,12 +17127,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N235" t="inlineStr">
+      <c r="N235" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
       </c>
-      <c r="O235" t="inlineStr">
+      <c r="O235" s="32" t="inlineStr">
         <is>
           <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : distributeur spécialiste du travertin (dalles 1er/2e choix, margelles, plinthes, mosaïques, pavés granit), vente au m², livraison France entière. Adresse 315 Rue Benjamin Franklin, 84120 Pertuis + dépôts Pertuis et Gujan-Mestras — villes confirmées. E-mail présent textuellement dans le pied de page (lien mailto). Téléphone confirmé (affiché 0666554442 en en-tête, pied de page et lien WhatsApp). Domaine hors liste d'exclusion. Source e-mail : https://www.dmcmiller.com/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
@@ -17123,60 +17141,60 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R235" t="inlineStr">
+      <c r="R235" s="32" t="inlineStr">
         <is>
           <t>contact@dmcmiller.com</t>
         </is>
       </c>
     </row>
     <row r="236" ht="15" customHeight="1" s="33">
-      <c r="A236" t="n">
+      <c r="A236" s="32" t="n">
         <v>236</v>
       </c>
-      <c r="B236" t="inlineStr">
+      <c r="B236" s="32" t="inlineStr">
         <is>
           <t>5e liste — recherche (26/10)</t>
         </is>
       </c>
-      <c r="C236" t="n">
+      <c r="C236" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D236" t="inlineStr">
+      <c r="D236" s="32" t="inlineStr">
         <is>
           <t>importateurs</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr">
+      <c r="E236" s="32" t="inlineStr">
         <is>
           <t>Cupa Stone France (Cupa Pierres Distribution)</t>
         </is>
       </c>
-      <c r="F236" t="inlineStr">
+      <c r="F236" s="32" t="inlineStr">
         <is>
           <t>Changé (Le Mans) — réseau national d'agences</t>
         </is>
       </c>
-      <c r="G236" t="inlineStr">
+      <c r="G236" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H236" t="inlineStr">
+      <c r="H236" s="32" t="inlineStr">
         <is>
           <t>Confirmée : distributeur national de pierre naturelle avec agences au Mans (Changé), Tours, Rennes, Nantes, Lyon, Aix-en-Provence, Quimper, Pau, Limoges, Cholet, Muzillac, La Roche…</t>
         </is>
       </c>
-      <c r="I236" t="inlineStr">
+      <c r="I236" s="32" t="inlineStr">
         <is>
           <t>https://www.cupastone.fr/</t>
         </is>
       </c>
-      <c r="J236" t="inlineStr">
+      <c r="J236" s="32" t="inlineStr">
         <is>
           <t>+33 2 43 85 06 84</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr">
+      <c r="K236" s="32" t="inlineStr">
         <is>
           <t>Recherche Claude (26/10)</t>
         </is>
@@ -17186,74 +17204,74 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N236" t="inlineStr">
+      <c r="N236" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
       </c>
-      <c r="O236" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : distributeur national de pierre naturelle avec agences au Mans (Changé), Tours, Rennes, Nantes, Lyon, Aix-en-Provence, Quimper, Pau, Limoges, Cholet, Muzillac, La Roche-sur-Yon, etc. (groupe présent aussi en Espagne/Portugal). Le téléphone +33 2 43 85 06 84 est bien celui de l'agence Le Mans (Changé), contact Amandine Renard. E-mail contact@cupastone.fr présent textuellement sur la page points de vente, répété pour la plupart des agences françaises (dont Le Mans). D'autres e-mails nominatifs existent (cleger@cupastone.fr Bordeaux, lgasse@cupastone.com Paris-IdF, sbatmale@cupastone.com Toulouse, fmadehors@cupastone.com Nord-Est) si un ciblage régional est préféré. Domaine hors liste d'exclusion. Source e-mail : https://www.cupastone.fr/points-de-vente/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+      <c r="O236" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : distributeur national de pierre naturelle avec agences au Mans (Changé), Tours, Rennes, Nantes, Lyon, Aix-en-Provence, Quimper, Pau, Limoges, Cholet, Muzillac, La Roche-sur-Yon, etc. (groupe présent aussi en Espagne/Portugal). Le téléphone +33 2 43 85 06 84 est bien celui de l'agence Le Mans (Changé), contact Amandine Renard. E-mail contact@cupastone.fr présent textuellement sur la page points de vente, répété pour la plupart des agences françaises (dont Le Mans). D'autres e-mails nominatifs existent (cleger@cupastone.fr Bordeaux, lgasse@cupastone.com Paris-IdF, sbatmale@cupastone.com Toulouse, fmadehors@cupastone.com Nord-Est) si un ciblage régional est préféré. Domaine hors liste d'exclusion. Source e-mail : https://www.cupastone.fr/points-de-vente/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi [26/10 croisement fichier propriétaire] Ciblage régional préféré (fichier) : agence Paris/IdF à Coignières — lgasse@cupastone.com, 01 30 49 69 91. Sinon contact@cupastone.fr (Le Mans, vérifié).</t>
         </is>
       </c>
       <c r="Q236" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R236" t="inlineStr">
+      <c r="R236" s="32" t="inlineStr">
         <is>
           <t>contact@cupastone.fr</t>
         </is>
       </c>
     </row>
     <row r="237" ht="15" customHeight="1" s="33">
-      <c r="A237" t="n">
+      <c r="A237" s="32" t="n">
         <v>237</v>
       </c>
-      <c r="B237" t="inlineStr">
+      <c r="B237" s="32" t="inlineStr">
         <is>
           <t>5e liste — recherche (26/10)</t>
         </is>
       </c>
-      <c r="C237" t="n">
+      <c r="C237" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D237" t="inlineStr">
+      <c r="D237" s="32" t="inlineStr">
         <is>
           <t>importateurs</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr">
+      <c r="E237" s="32" t="inlineStr">
         <is>
           <t>Ti'ma Stone</t>
         </is>
       </c>
-      <c r="F237" t="inlineStr">
+      <c r="F237" s="32" t="inlineStr">
         <is>
           <t>Lunel (non confirmée sur le site)</t>
         </is>
       </c>
-      <c r="G237" t="inlineStr">
+      <c r="G237" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr">
+      <c r="H237" s="32" t="inlineStr">
         <is>
           <t>Confirmée pour l'activité : vente en ligne de pierre naturelle France entière (dallage, parement, margelles, zellige, vasques), travertin très présent, liens « Grossiste dallage » …</t>
         </is>
       </c>
-      <c r="I237" t="inlineStr">
+      <c r="I237" s="32" t="inlineStr">
         <is>
           <t>https://timastone.com/</t>
         </is>
       </c>
-      <c r="J237" t="inlineStr">
+      <c r="J237" s="32" t="inlineStr">
         <is>
           <t>04 15 54 01 25</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr">
+      <c r="K237" s="32" t="inlineStr">
         <is>
           <t>Recherche Claude (26/10)</t>
         </is>
@@ -17263,12 +17281,12 @@
           <t>À contacter (formulaire/tél) — EN ATTENTE</t>
         </is>
       </c>
-      <c r="N237" t="inlineStr">
+      <c r="N237" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
       </c>
-      <c r="O237" t="inlineStr">
+      <c r="O237" s="32" t="inlineStr">
         <is>
           <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée pour l'activité : vente en ligne de pierre naturelle France entière (dallage, parement, margelles, zellige, vasques), travertin très présent, liens « Grossiste dallage » et « Fournisseur carrelage » + espace pro. La VILLE n'est PAS confirmée : aucune adresse ni ville sur la page d'accueil, et les pages /mentions-legales/ et /contact/ renvoient un 404 aux URL standards. AUCUN e-mail publié sur la page d'accueil (vérifié). Repli téléphone VÉRIFIÉ : 04 15 54 01 25 affiché en en-tête et pied de page (horaires lun-ven 9h-12h / 14h-18h). Domaine hors liste d'exclusion. Site vivant et actif, mais profil plutôt vente en ligne avec volet grossiste ; localisation Lunel à reconfirmer par téléphone avant tout engagement logistique. Source e-mail : aucune (pas d e-mail publié). ⚠️ CONCURRENT suivi dans la veille prix (42,46–59,96 €/m²) — approche uniquement « reprise de lot revendeur », aucune info sensible. NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
@@ -17279,53 +17297,53 @@
       </c>
     </row>
     <row r="238" ht="15" customHeight="1" s="33">
-      <c r="A238" t="n">
+      <c r="A238" s="32" t="n">
         <v>238</v>
       </c>
-      <c r="B238" t="inlineStr">
+      <c r="B238" s="32" t="inlineStr">
         <is>
           <t>5e liste — recherche (26/10)</t>
         </is>
       </c>
-      <c r="C238" t="n">
+      <c r="C238" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D238" t="inlineStr">
+      <c r="D238" s="32" t="inlineStr">
         <is>
           <t>importateurs</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr">
+      <c r="E238" s="32" t="inlineStr">
         <is>
           <t>BH Matériaux (groupe Holding Laffont)</t>
         </is>
       </c>
-      <c r="F238" t="inlineStr">
+      <c r="F238" s="32" t="inlineStr">
         <is>
           <t>Lauzerte</t>
         </is>
       </c>
-      <c r="G238" t="inlineStr">
+      <c r="G238" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H238" t="inlineStr">
+      <c r="H238" s="32" t="inlineStr">
         <is>
           <t>Confirmée : grossiste revendiqué (« Votre grossiste ») en matériaux de construction/rénovation/décoration avec le travertin et le dallage pierre naturelle en gamme majeure (dallage…</t>
         </is>
       </c>
-      <c r="I238" t="inlineStr">
+      <c r="I238" s="32" t="inlineStr">
         <is>
           <t>https://bh-materiaux.com/</t>
         </is>
       </c>
-      <c r="J238" t="inlineStr">
+      <c r="J238" s="32" t="inlineStr">
         <is>
           <t>05 63 95 39 08</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr">
+      <c r="K238" s="32" t="inlineStr">
         <is>
           <t>Recherche Claude (26/10)</t>
         </is>
@@ -17335,12 +17353,12 @@
           <t>À contacter (formulaire/tél) — EN ATTENTE</t>
         </is>
       </c>
-      <c r="N238" t="inlineStr">
+      <c r="N238" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
       </c>
-      <c r="O238" t="inlineStr">
+      <c r="O238" s="32" t="inlineStr">
         <is>
           <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : grossiste revendiqué (« Votre grossiste ») en matériaux de construction/rénovation/décoration avec le travertin et le dallage pierre naturelle en gamme majeure (dallages du monde, parement, graviers, pas japonais) ; particuliers et professionnels ; retrait au dépôt de Lauzerte. Adresse 138 route de Montbarla, 82110 Lauzerte confirmée. Groupe Holding Laffont confirmé (Osagra, Laffont TP, Laffont Granulats...). AUCUN e-mail publié (vérifié sur la page d'accueil : téléphone et formulaire de rappel uniquement). Repli téléphone VÉRIFIÉ : 05 63 95 39 08 répété en en-tête et sections contact. ATTENTION : le site confirme « membre du réseau FRANCE MATERIAUX » dont le domaine france-materiaux.fr figure dans la liste d'exclusion ; le domaine propre bh-materiaux.com n'y figure pas — retenu, mais à arbitrer côté donneur d'ordre avant contact. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
@@ -17351,53 +17369,53 @@
       </c>
     </row>
     <row r="239" ht="15" customHeight="1" s="33">
-      <c r="A239" t="n">
+      <c r="A239" s="32" t="n">
         <v>239</v>
       </c>
-      <c r="B239" t="inlineStr">
+      <c r="B239" s="32" t="inlineStr">
         <is>
           <t>5e liste — recherche (26/10)</t>
         </is>
       </c>
-      <c r="C239" t="n">
+      <c r="C239" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D239" t="inlineStr">
+      <c r="D239" s="32" t="inlineStr">
         <is>
           <t>marbreries-idf</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr">
+      <c r="E239" s="32" t="inlineStr">
         <is>
           <t>Les Marbreries de la Seine (LMS Paris)</t>
         </is>
       </c>
-      <c r="F239" t="inlineStr">
+      <c r="F239" s="32" t="inlineStr">
         <is>
           <t>Les Pavillons-sous-Bois (ateliers) / Paris 7e (showroom)</t>
         </is>
       </c>
-      <c r="G239" t="inlineStr">
+      <c r="G239" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
+      <c r="H239" s="32" t="inlineStr">
         <is>
           <t>Confirmée : marbrerie haute décoration (architecture, mobilier, objets d'art) ; showroom 33 rue de Verneuil 75007 Paris, ateliers et logistique 2/8 allée de Londres 93320 Les Pavil…</t>
         </is>
       </c>
-      <c r="I239" t="inlineStr">
+      <c r="I239" s="32" t="inlineStr">
         <is>
           <t>https://www.lesmarbreriesdelaseine.com</t>
         </is>
       </c>
-      <c r="J239" t="inlineStr">
+      <c r="J239" s="32" t="inlineStr">
         <is>
           <t>+33 1 48 48 10 00 (showroom) / +33 1 48 48 59 76 (ateliers)</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr">
+      <c r="K239" s="32" t="inlineStr">
         <is>
           <t>Recherche Claude (26/10)</t>
         </is>
@@ -17407,12 +17425,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N239" t="inlineStr">
+      <c r="N239" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
       </c>
-      <c r="O239" t="inlineStr">
+      <c r="O239" s="32" t="inlineStr">
         <is>
           <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : marbrerie haute décoration (architecture, mobilier, objets d'art) ; showroom 33 rue de Verneuil 75007 Paris, ateliers et logistique 2/8 allée de Londres 93320 Les Pavillons-sous-Bois. E-mail info@lmsparis.com lu textuellement sur la page contact du site officiel (un second e-mail info@lmsmiami.com concerne l'antenne de Miami, à ignorer). Téléphones confirmés. Domaine hors liste d'exclusion. Site officiel, pas un annuaire. Source e-mail : https://www.lesmarbreriesdelaseine.com/contact.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
@@ -17421,1559 +17439,2029 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R239" t="inlineStr">
+      <c r="R239" s="32" t="inlineStr">
         <is>
           <t>info@lmsparis.com</t>
         </is>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1" s="33">
-      <c r="A240" t="n">
+      <c r="A240" s="32" t="n">
         <v>240</v>
       </c>
-      <c r="B240" t="inlineStr">
+      <c r="B240" s="32" t="inlineStr">
         <is>
           <t>5e liste — recherche (26/10)</t>
         </is>
       </c>
-      <c r="C240" t="n">
+      <c r="C240" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D240" t="inlineStr">
+      <c r="D240" s="32" t="inlineStr">
         <is>
           <t>marbreries-idf</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr">
+      <c r="E240" s="32" t="inlineStr">
         <is>
           <t>Marbre Import</t>
         </is>
       </c>
-      <c r="F240" t="inlineStr">
+      <c r="F240" s="32" t="inlineStr">
         <is>
           <t>Paris 19e (118 av. Jean Jaurès) ; autre adresse affichée : B</t>
         </is>
       </c>
-      <c r="G240" t="inlineStr">
+      <c r="G240" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr">
+      <c r="H240" s="32" t="inlineStr">
         <is>
           <t>Confirmée : spécialiste de la pierre naturelle (marbre, granit, dalles, blocs), vente aux particuliers et professionnels (marbriers, architectes, constructeurs).</t>
         </is>
       </c>
-      <c r="I240" t="inlineStr">
+      <c r="I240" s="32" t="inlineStr">
         <is>
           <t>https://www.marbre-import.fr</t>
         </is>
       </c>
-      <c r="J240" t="inlineStr">
+      <c r="J240" s="32" t="inlineStr">
         <is>
           <t>09 72 15 80 01</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr">
+      <c r="K240" s="32" t="inlineStr">
         <is>
           <t>Recherche Claude (26/10)</t>
         </is>
       </c>
       <c r="L240" s="32" t="inlineStr">
         <is>
+          <t>Contacté le 20/10 (Gmail) — ne pas réexpédier</t>
+        </is>
+      </c>
+      <c r="N240" s="32" t="inlineStr">
+        <is>
+          <t>Vérifier s'il y a eu réponse au message du 20/10 ; AUCUN nouvel envoi</t>
+        </is>
+      </c>
+      <c r="O240" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : spécialiste de la pierre naturelle (marbre, granit, dalles, blocs), vente aux particuliers et professionnels (marbriers, architectes, constructeurs). AUCUN e-mail publié sur la page contact du site officiel : formulaire de devis uniquement. Retenu sur la base du téléphone vérifié 09 72 15 80 01 (affiché textuellement et en lien tel: sur la page contact). Attention : la page contact affiche Paris 19e et Bordeaux ; le showroom de Villejuif annoncé dans le candidat n'y apparaît pas — à confirmer par téléphone. Domaine hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié). ⚠️ CONCURRENT suivi dans la veille prix (Crema Marfil Espagne, lot promo 20 € HT) — prudence, approche reprise de lot uniquement. NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi [26/10 croisement fichier propriétaire] Le fichier indique « Déjà contacté — Gmail 20/10/2026 » (canal propriétaire/tiers). Correction du statut : plus un prospect vierge.</t>
+        </is>
+      </c>
+      <c r="Q240" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>contact@marbre-import.fr</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="15" customHeight="1" s="33">
+      <c r="A241" s="32" t="n">
+        <v>241</v>
+      </c>
+      <c r="B241" s="32" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C241" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D241" s="32" t="inlineStr">
+        <is>
+          <t>marbreries-idf</t>
+        </is>
+      </c>
+      <c r="E241" s="32" t="inlineStr">
+        <is>
+          <t>Arthema Marbre (marbrerie SPIMA)</t>
+        </is>
+      </c>
+      <c r="F241" s="32" t="inlineStr">
+        <is>
+          <t>Paris 3e (showroom 34 rue de Poitou, Le Marais)</t>
+        </is>
+      </c>
+      <c r="G241" s="32" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H241" s="32" t="inlineStr">
+        <is>
+          <t>Confirmée : marbrerie de décoration sur mesure (marbre, pierre calcaire, travertin, onyx, granit, quartzite), fabrication en atelier partenaire SPIMA et pose ; clientèle d'architec…</t>
+        </is>
+      </c>
+      <c r="I241" s="32" t="inlineStr">
+        <is>
+          <t>https://arthema-marbre.com</t>
+        </is>
+      </c>
+      <c r="J241" s="32" t="inlineStr">
+        <is>
+          <t>01 42 71 79 09 / 06 19 26 42 68</t>
+        </is>
+      </c>
+      <c r="K241" s="32" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L241" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N241" s="32" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O241" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : marbrerie de décoration sur mesure (marbre, pierre calcaire, travertin, onyx, granit, quartzite), fabrication en atelier partenaire SPIMA et pose ; clientèle d'architectes et décorateurs. E-mail lu textuellement sur la page d'accueil du site officiel. Un mobile supplémentaire (06 19 26 42 68) y figure aussi. Travail explicite des pierres calcaires et travertins confirmé. Domaine hors liste d'exclusion. Source e-mail : https://arthema-marbre.com/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="Q241" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R241" s="32" t="inlineStr">
+        <is>
+          <t>contact@arthema-marbre.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="242" ht="15" customHeight="1" s="33">
+      <c r="A242" s="32" t="n">
+        <v>242</v>
+      </c>
+      <c r="B242" s="32" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C242" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D242" s="32" t="inlineStr">
+        <is>
+          <t>marbreries-idf</t>
+        </is>
+      </c>
+      <c r="E242" s="32" t="inlineStr">
+        <is>
+          <t>Atelier Matière</t>
+        </is>
+      </c>
+      <c r="F242" s="32" t="inlineStr">
+        <is>
+          <t>Paris 16e (19 rue Vital) et Paris 17e (36 rue Brunel)</t>
+        </is>
+      </c>
+      <c r="G242" s="32" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H242" s="32" t="inlineStr">
+        <is>
+          <t>Confirmée : studio/showroom de pierre naturelle, marbre et terrazzo haut de gamme depuis 2012, distribution et pose sur rendez-vous ; deux showrooms parisiens confirmés.</t>
+        </is>
+      </c>
+      <c r="I242" s="32" t="inlineStr">
+        <is>
+          <t>https://www.ateliermatiere.fr</t>
+        </is>
+      </c>
+      <c r="J242" s="32" t="inlineStr">
+        <is>
+          <t>01 45 04 57 65</t>
+        </is>
+      </c>
+      <c r="K242" s="32" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L242" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N242" s="32" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O242" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : studio/showroom de pierre naturelle, marbre et terrazzo haut de gamme depuis 2012, distribution et pose sur rendez-vous ; deux showrooms parisiens confirmés. E-mail lu textuellement sur la page Pierre du site officiel ; téléphone confirmé. Domaine hors liste d'exclusion. Site officiel, pas un annuaire. Source e-mail : https://www.ateliermatiere.fr/pierre.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="Q242" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R242" s="32" t="inlineStr">
+        <is>
+          <t>info@ateliermatiere.fr</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="15" customHeight="1" s="33">
+      <c r="A243" s="32" t="n">
+        <v>243</v>
+      </c>
+      <c r="B243" s="32" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C243" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D243" s="32" t="inlineStr">
+        <is>
+          <t>marbreries-idf</t>
+        </is>
+      </c>
+      <c r="E243" s="32" t="inlineStr">
+        <is>
+          <t>Artefacts Paris</t>
+        </is>
+      </c>
+      <c r="F243" s="32" t="inlineStr">
+        <is>
+          <t>Paris 7e (showroom 17 bis passage Jean Nicot) ; atelier à Né</t>
+        </is>
+      </c>
+      <c r="G243" s="32" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H243" s="32" t="inlineStr">
+        <is>
+          <t>Confirmée : marbrerie fine et pierre de taille, revêtements durs en pierre naturelle pour la construction et l'agencement de luxe ; showroom Paris 7e et atelier/bureau d'études à N…</t>
+        </is>
+      </c>
+      <c r="I243" s="32" t="inlineStr">
+        <is>
+          <t>https://www.artefacts-paris.com</t>
+        </is>
+      </c>
+      <c r="K243" s="32" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L243" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N243" s="32" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O243" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : marbrerie fine et pierre de taille, revêtements durs en pierre naturelle pour la construction et l'agencement de luxe ; showroom Paris 7e et atelier/bureau d'études à Nérac (47600) confirmés. E-mail lu textuellement sur le site officiel. Aucun téléphone affiché sur la page. L'atelier de façonnage est bien hors IdF (Nérac, 47) comme signalé, mais la vitrine commerciale et les chantiers sont parisiens. Domaine hors liste d'exclusion. Source e-mail : https://www.artefacts-paris.com.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="Q243" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R243" s="32" t="inlineStr">
+        <is>
+          <t>info@artefacts-paris.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="15" customHeight="1" s="33">
+      <c r="A244" s="32" t="n">
+        <v>244</v>
+      </c>
+      <c r="B244" s="32" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C244" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D244" s="32" t="inlineStr">
+        <is>
+          <t>marbreries-idf</t>
+        </is>
+      </c>
+      <c r="E244" s="32" t="inlineStr">
+        <is>
+          <t>H. Chevalier</t>
+        </is>
+      </c>
+      <c r="F244" s="32" t="inlineStr">
+        <is>
+          <t>Suresnes (26 rue Henri Regnault, 92150)</t>
+        </is>
+      </c>
+      <c r="G244" s="32" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H244" s="32" t="inlineStr">
+        <is>
+          <t>Confirmée : restauration du patrimoine bâti depuis 1946 (maçonnerie-pierre, restauration de sculpture, hôtels particuliers et châteaux), 250 salariés, 80 M€ de CA ; adresse à Sures…</t>
+        </is>
+      </c>
+      <c r="I244" s="32" t="inlineStr">
+        <is>
+          <t>https://www.hchevalier.com</t>
+        </is>
+      </c>
+      <c r="J244" s="32" t="inlineStr">
+        <is>
+          <t>01 45 06 83 33</t>
+        </is>
+      </c>
+      <c r="K244" s="32" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L244" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N244" s="32" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O244" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : restauration du patrimoine bâti depuis 1946 (maçonnerie-pierre, restauration de sculpture, hôtels particuliers et châteaux), 250 salariés, 80 M€ de CA ; adresse à Suresnes confirmée. E-mail et téléphone lus textuellement sur la page d'accueil du site officiel. Domaine hors liste d'exclusion. Profil patrimoine/monuments : pertinence moyenne pour un calcaire égyptien standard, comme indiqué dans le candidat. Source e-mail : https://www.hchevalier.com.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="Q244" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R244" s="32" t="inlineStr">
+        <is>
+          <t>contact@hchevalier.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="15" customHeight="1" s="33">
+      <c r="A245" s="32" t="n">
+        <v>245</v>
+      </c>
+      <c r="B245" s="32" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C245" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D245" s="32" t="inlineStr">
+        <is>
+          <t>marbreries-idf</t>
+        </is>
+      </c>
+      <c r="E245" s="32" t="inlineStr">
+        <is>
+          <t>Vexin Patrimoine</t>
+        </is>
+      </c>
+      <c r="F245" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secteur Vexin / Île-de-France (95) — aucune adresse précise </t>
+        </is>
+      </c>
+      <c r="G245" s="32" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H245" s="32" t="inlineStr">
+        <is>
+          <t>Confirmée : tailleur de pierre (taille sur mesure intérieur/extérieur, restauration historique, création, sols en pierre), plus de 15 ans d'expérience, clients pro et particuliers,…</t>
+        </is>
+      </c>
+      <c r="I245" s="32" t="inlineStr">
+        <is>
+          <t>https://vexinpatrimoine.fr</t>
+        </is>
+      </c>
+      <c r="J245" s="32" t="inlineStr">
+        <is>
+          <t>01 30 73 86 50</t>
+        </is>
+      </c>
+      <c r="K245" s="32" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L245" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N245" s="32" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O245" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : tailleur de pierre (taille sur mesure intérieur/extérieur, restauration historique, création, sols en pierre), plus de 15 ans d'expérience, clients pro et particuliers, zone Vexin/Île-de-France. Deux graphies sur le site : le pied de page affiche textuellement contact@vexinpatrimoine.fr (correct) ; la barre latérale affiche la coquille « contat@vexinpatrimoine.fr ». Utiliser contact@vexinpatrimoine.fr. Téléphone confirmé (affiché deux fois). Aucune ville précise publiée, cohérent avec le candidat. Domaine hors liste d'exclusion. Source e-mail : https://vexinpatrimoine.fr/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="Q245" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R245" s="32" t="inlineStr">
+        <is>
+          <t>contact@vexinpatrimoine.fr</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="15" customHeight="1" s="33">
+      <c r="A246" s="32" t="n">
+        <v>246</v>
+      </c>
+      <c r="B246" s="32" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C246" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D246" s="32" t="inlineStr">
+        <is>
+          <t>marbreries-idf</t>
+        </is>
+      </c>
+      <c r="E246" s="32" t="inlineStr">
+        <is>
+          <t>Accolade Artisans</t>
+        </is>
+      </c>
+      <c r="F246" s="32" t="inlineStr">
+        <is>
+          <t>Viarmes (14 rue Kleinpeter, 95270)</t>
+        </is>
+      </c>
+      <c r="G246" s="32" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H246" s="32" t="inlineStr">
+        <is>
+          <t>Confirmée : taille de pierre et maçonnerie de restauration du bâti ancien (certification Qualibat restauration pierre de taille et maçonnerie du patrimoine) ; adresse à Viarmes (95…</t>
+        </is>
+      </c>
+      <c r="I246" s="32" t="inlineStr">
+        <is>
+          <t>https://www.accoladeartisans.fr</t>
+        </is>
+      </c>
+      <c r="J246" s="32" t="inlineStr">
+        <is>
+          <t>06 27 85 91 92</t>
+        </is>
+      </c>
+      <c r="K246" s="32" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L246" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N246" s="32" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O246" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : taille de pierre et maçonnerie de restauration du bâti ancien (certification Qualibat restauration pierre de taille et maçonnerie du patrimoine) ; adresse à Viarmes (95270) confirmée. E-mail lu textuellement dans la section Coordonnées du pied de page ; téléphone confirmé (en-tête et pied de page). Domaine hors liste d'exclusion. Site officiel, pas un annuaire. Source e-mail : https://www.accoladeartisans.fr/taille-de-pierre.htm.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="Q246" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R246" s="32" t="inlineStr">
+        <is>
+          <t>contact@accoladeartisans.fr</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="15" customHeight="1" s="33">
+      <c r="A247" s="32" t="n">
+        <v>247</v>
+      </c>
+      <c r="B247" s="32" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C247" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D247" s="32" t="inlineStr">
+        <is>
+          <t>marbreries-idf</t>
+        </is>
+      </c>
+      <c r="E247" s="32" t="inlineStr">
+        <is>
+          <t>Techno Pierre</t>
+        </is>
+      </c>
+      <c r="F247" s="32" t="inlineStr">
+        <is>
+          <t>Vanves (35 rue Aristide Briand, 92170)</t>
+        </is>
+      </c>
+      <c r="G247" s="32" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H247" s="32" t="inlineStr">
+        <is>
+          <t>Confirmée : tailleur de pierres et marbrier du bâtiment (taille de pierre, marbrerie, rénovation et revêtement de façades en pierre, marbre et granit) ; adresse à Vanves confirmée.</t>
+        </is>
+      </c>
+      <c r="I247" s="32" t="inlineStr">
+        <is>
+          <t>https://www.technopierre.fr</t>
+        </is>
+      </c>
+      <c r="J247" s="32" t="inlineStr">
+        <is>
+          <t>09 74 56 39 83</t>
+        </is>
+      </c>
+      <c r="K247" s="32" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L247" s="32" t="inlineStr">
+        <is>
           <t>À contacter (formulaire/tél) — EN ATTENTE</t>
         </is>
       </c>
-      <c r="N240" t="inlineStr">
+      <c r="N247" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
       </c>
-      <c r="O240" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : spécialiste de la pierre naturelle (marbre, granit, dalles, blocs), vente aux particuliers et professionnels (marbriers, architectes, constructeurs). AUCUN e-mail publié sur la page contact du site officiel : formulaire de devis uniquement. Retenu sur la base du téléphone vérifié 09 72 15 80 01 (affiché textuellement et en lien tel: sur la page contact). Attention : la page contact affiche Paris 19e et Bordeaux ; le showroom de Villejuif annoncé dans le candidat n'y apparaît pas — à confirmer par téléphone. Domaine hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié). ⚠️ CONCURRENT suivi dans la veille prix (Crema Marfil Espagne, lot promo 20 € HT) — prudence, approche reprise de lot uniquement. NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q240" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="241" ht="15" customHeight="1" s="33">
-      <c r="A241" t="n">
-        <v>241</v>
-      </c>
-      <c r="B241" t="inlineStr">
+      <c r="O247" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : tailleur de pierres et marbrier du bâtiment (taille de pierre, marbrerie, rénovation et revêtement de façades en pierre, marbre et granit) ; adresse à Vanves confirmée. AUCUN e-mail publié sur le site officiel : la page contactez-nous.php ne propose qu'un formulaire (le lien « E-mail » pointe vers ce formulaire, pas vers une adresse). Retenu sur la base du téléphone vérifié 09 74 56 39 83, affiché plusieurs fois sur la page. Domaine hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="Q247" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248" ht="15" customHeight="1" s="33">
+      <c r="A248" s="32" t="n">
+        <v>248</v>
+      </c>
+      <c r="B248" s="32" t="inlineStr">
         <is>
           <t>5e liste — recherche (26/10)</t>
         </is>
       </c>
-      <c r="C241" t="n">
+      <c r="C248" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D248" s="32" t="inlineStr">
+        <is>
+          <t>normandie</t>
+        </is>
+      </c>
+      <c r="E248" s="32" t="inlineStr">
+        <is>
+          <t>Guilloux Matériaux</t>
+        </is>
+      </c>
+      <c r="F248" s="32" t="inlineStr">
+        <is>
+          <t>Cormeilles (27) et Rouen (76) — siège Saint-Pair-sur-Mer (50</t>
+        </is>
+      </c>
+      <c r="G248" s="32" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H248" s="32" t="inlineStr">
+        <is>
+          <t>Confirmé : négoce indépendant de matériaux de construction, 10 agences en Normandie (dont Cormeilles 27 et Rouen 76), scierie/atelier à Vire, siège à Saint-Pair-sur-Mer (50380).</t>
+        </is>
+      </c>
+      <c r="I248" s="32" t="inlineStr">
+        <is>
+          <t>https://www.guillouxmateriaux.com</t>
+        </is>
+      </c>
+      <c r="J248" s="32" t="inlineStr">
+        <is>
+          <t>02 33 48 14 44 (siège) ; agence Cormeilles 02 32 57 15 98 ; agence Rouen 02 32 12 11 80</t>
+        </is>
+      </c>
+      <c r="K248" s="32" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L248" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N248" s="32" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O248" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé : négoce indépendant de matériaux de construction, 10 agences en Normandie (dont Cormeilles 27 et Rouen 76), scierie/atelier à Vire, siège à Saint-Pair-sur-Mer (50380). E-mail lu TEXTUELLEMENT sur les mentions légales (responsable de la publication). Attention : le domaine de l'e-mail (guilloux-materiaux.com, avec tiret) diffère du domaine du site (guillouxmateriaux.com) — c'est bien ce qu'affiche le site officiel. Téléphones siège/Cormeilles/Rouen tous confirmés sur la même page. Hors liste d'exclusion. Source e-mail : https://www.guillouxmateriaux.com/mentions-legales-guilloux-materiaux-le-specialiste-des-materiaux-de-construction/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi [26/10 croisement fichier propriétaire] Divergence e-mail : fichier donne contact@guilloux-materiaux.com « à revalider » ; notre vérification site officielle a lu bonjour@guilloux-materiaux.com → conserver bonjour@.</t>
+        </is>
+      </c>
+      <c r="Q248" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R248" s="32" t="inlineStr">
+        <is>
+          <t>bonjour@guilloux-materiaux.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="15" customHeight="1" s="33">
+      <c r="A249" s="32" t="n">
+        <v>249</v>
+      </c>
+      <c r="B249" s="32" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C249" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D249" s="32" t="inlineStr">
+        <is>
+          <t>normandie</t>
+        </is>
+      </c>
+      <c r="E249" s="32" t="inlineStr">
+        <is>
+          <t>Sani 27 (« Le Géant du carrelage »)</t>
+        </is>
+      </c>
+      <c r="F249" s="32" t="inlineStr">
+        <is>
+          <t>Angerville-la-Campagne (27930), ZAC de Villeneuve — près d'É</t>
+        </is>
+      </c>
+      <c r="G249" s="32" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H249" s="32" t="inlineStr">
+        <is>
+          <t>Confirmé : magasin spécialiste du carrelage (« le plus grand magasin de carrelage ») avec sanitaire, robinetterie et meubles de salle de bain ; adresse ZAC de Villeneuve, 27930 Ang…</t>
+        </is>
+      </c>
+      <c r="I249" s="32" t="inlineStr">
+        <is>
+          <t>https://sani27.com</t>
+        </is>
+      </c>
+      <c r="J249" s="32" t="inlineStr">
+        <is>
+          <t>02 32 28 00 12</t>
+        </is>
+      </c>
+      <c r="K249" s="32" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L249" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N249" s="32" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O249" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé : magasin spécialiste du carrelage (« le plus grand magasin de carrelage ») avec sanitaire, robinetterie et meubles de salle de bain ; adresse ZAC de Villeneuve, 27930 Angerville-la-Campagne, zone d'Évreux. contact@sani27.fr est écrit TEXTUELLEMENT dans le pied de page du site officiel. Divergence confirmée : le lien mailto associé pointe vers sani27@wanadoo.fr — en cas de non-réponse sur contact@sani27.fr, utiliser sani27@wanadoo.fr en seconde adresse. Téléphone 02 32 28 00 12 confirmé. Hors liste d'exclusion. Source e-mail : https://sani27.com/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="Q249" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R249" s="32" t="inlineStr">
+        <is>
+          <t>contact@sani27.fr</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="15" customHeight="1" s="33">
+      <c r="A250" s="32" t="n">
+        <v>250</v>
+      </c>
+      <c r="B250" s="32" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C250" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D250" s="32" t="inlineStr">
+        <is>
+          <t>normandie</t>
+        </is>
+      </c>
+      <c r="E250" s="32" t="inlineStr">
+        <is>
+          <t>BCA Matériaux Anciens</t>
+        </is>
+      </c>
+      <c r="F250" s="32" t="inlineStr">
+        <is>
+          <t>Méry-Corbon (14370) et Pont-l'Évêque (14130) — siège Segré-e</t>
+        </is>
+      </c>
+      <c r="G250" s="32" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H250" s="32" t="inlineStr">
+        <is>
+          <t>Confirmé : « Spécialiste des matériaux anciens » — dallages et carrelages anciens en pierre, parquets anciens, tomettes, pavés, parements pierre, cheminées ; deux agences normandes…</t>
+        </is>
+      </c>
+      <c r="I250" s="32" t="inlineStr">
+        <is>
+          <t>https://www.bca-materiauxanciens.com</t>
+        </is>
+      </c>
+      <c r="J250" s="32" t="inlineStr">
+        <is>
+          <t>02 31 23 95 87 (Méry-Corbon) ; 02 61 67 23 40 (Pont-l'Évêque) ; +33 (0)2 41 61 62 40 (siège)</t>
+        </is>
+      </c>
+      <c r="K250" s="32" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L250" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N250" s="32" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O250" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé : « Spécialiste des matériaux anciens » — dallages et carrelages anciens en pierre, parquets anciens, tomettes, pavés, parements pierre, cheminées ; deux agences normandes (Méry-Corbon et Pont-l'Évêque), siège en Pays de la Loire. normandie@bcamateriaux.com (agence Méry-Corbon) lu TEXTUELLEMENT sur le site officiel, ainsi que pontleveque@bcamateriaux.com, info@bcamateriaux.com et david@bcamateriaux.com (anglais). Tous les téléphones confirmés. Cœur de métier aligné (dallages pierre par lots). Hors liste d'exclusion. Source e-mail : https://www.bca-materiauxanciens.com.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="Q250" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R250" s="32" t="inlineStr">
+        <is>
+          <t>normandie@bcamateriaux.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="15" customHeight="1" s="33">
+      <c r="A251" s="32" t="n">
+        <v>251</v>
+      </c>
+      <c r="B251" s="32" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C251" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>marbreries-idf</t>
-        </is>
-      </c>
-      <c r="E241" t="inlineStr">
-        <is>
-          <t>Arthema Marbre (marbrerie SPIMA)</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
-        <is>
-          <t>Paris 3e (showroom 34 rue de Poitou, Le Marais)</t>
-        </is>
-      </c>
-      <c r="G241" t="inlineStr">
+      <c r="D251" s="32" t="inlineStr">
+        <is>
+          <t>normandie</t>
+        </is>
+      </c>
+      <c r="E251" s="32" t="inlineStr">
+        <is>
+          <t>Adéquate - Marbrerie Décorative</t>
+        </is>
+      </c>
+      <c r="F251" s="32" t="inlineStr">
+        <is>
+          <t>Seulline (14310), ZA Eco 5 — près de Caen</t>
+        </is>
+      </c>
+      <c r="G251" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>Confirmée : marbrerie de décoration sur mesure (marbre, pierre calcaire, travertin, onyx, granit, quartzite), fabrication en atelier partenaire SPIMA et pose ; clientèle d'architec…</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>https://arthema-marbre.com</t>
-        </is>
-      </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t>01 42 71 79 09 / 06 19 26 42 68</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr">
+      <c r="H251" s="32" t="inlineStr">
+        <is>
+          <t>Confirmé : marbrerie décorative avec showroom (visites sur rendez-vous), ZA Eco 5 n° 7 et 9, 14310 Seulline, « près de Caen en Normandie ».</t>
+        </is>
+      </c>
+      <c r="I251" s="32" t="inlineStr">
+        <is>
+          <t>https://www.adequatemarbrerie.fr</t>
+        </is>
+      </c>
+      <c r="J251" s="32" t="inlineStr">
+        <is>
+          <t>02 31 24 11 22</t>
+        </is>
+      </c>
+      <c r="K251" s="32" t="inlineStr">
         <is>
           <t>Recherche Claude (26/10)</t>
         </is>
       </c>
-      <c r="L241" s="32" t="inlineStr">
+      <c r="L251" s="32" t="inlineStr">
         <is>
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N241" t="inlineStr">
+      <c r="N251" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
       </c>
-      <c r="O241" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : marbrerie de décoration sur mesure (marbre, pierre calcaire, travertin, onyx, granit, quartzite), fabrication en atelier partenaire SPIMA et pose ; clientèle d'architectes et décorateurs. E-mail lu textuellement sur la page d'accueil du site officiel. Un mobile supplémentaire (06 19 26 42 68) y figure aussi. Travail explicite des pierres calcaires et travertins confirmé. Domaine hors liste d'exclusion. Source e-mail : https://arthema-marbre.com/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q241" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R241" t="inlineStr">
-        <is>
-          <t>contact@arthema-marbre.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="242" ht="15" customHeight="1" s="33">
-      <c r="A242" t="n">
-        <v>242</v>
-      </c>
-      <c r="B242" t="inlineStr">
+      <c r="O251" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé : marbrerie décorative avec showroom (visites sur rendez-vous), ZA Eco 5 n° 7 et 9, 14310 Seulline, « près de Caen en Normandie ». contact@adequatemarbrerie.fr lu TEXTUELLEMENT sur la page contact du site officiel (en texte et en lien mailto, concordants). Téléphone confirmé. Hors liste d'exclusion. Source e-mail : https://www.adequatemarbrerie.fr/contact.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="Q251" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R251" s="32" t="inlineStr">
+        <is>
+          <t>contact@adequatemarbrerie.fr</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="15" customHeight="1" s="33">
+      <c r="A252" s="32" t="n">
+        <v>252</v>
+      </c>
+      <c r="B252" s="32" t="inlineStr">
         <is>
           <t>5e liste — recherche (26/10)</t>
         </is>
       </c>
-      <c r="C242" t="n">
+      <c r="C252" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>marbreries-idf</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>Atelier Matière</t>
-        </is>
-      </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>Paris 16e (19 rue Vital) et Paris 17e (36 rue Brunel)</t>
-        </is>
-      </c>
-      <c r="G242" t="inlineStr">
+      <c r="D252" s="32" t="inlineStr">
+        <is>
+          <t>normandie</t>
+        </is>
+      </c>
+      <c r="E252" s="32" t="inlineStr">
+        <is>
+          <t>Motte Décoration</t>
+        </is>
+      </c>
+      <c r="F252" s="32" t="inlineStr">
+        <is>
+          <t>Le Pré-d'Auge (14340), 10 Chemin des Vatines — entre Cambrem</t>
+        </is>
+      </c>
+      <c r="G252" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H242" t="inlineStr">
-        <is>
-          <t>Confirmée : studio/showroom de pierre naturelle, marbre et terrazzo haut de gamme depuis 2012, distribution et pose sur rendez-vous ; deux showrooms parisiens confirmés.</t>
-        </is>
-      </c>
-      <c r="I242" t="inlineStr">
-        <is>
-          <t>https://www.ateliermatiere.fr</t>
-        </is>
-      </c>
-      <c r="J242" t="inlineStr">
-        <is>
-          <t>01 45 04 57 65</t>
-        </is>
-      </c>
-      <c r="K242" t="inlineStr">
+      <c r="H252" s="32" t="inlineStr">
+        <is>
+          <t>Confirmé via sources tierces : société MOTTE DECORATION immatriculée (SIREN 844835728, taille/façonnage/finissage de pierres) au Pré-d'Auge (14340) ; marbrerie décorative familiale…</t>
+        </is>
+      </c>
+      <c r="I252" s="32" t="inlineStr">
+        <is>
+          <t>https://www.mottedecoration.com</t>
+        </is>
+      </c>
+      <c r="J252" s="32" t="inlineStr">
+        <is>
+          <t>02 31 32 22 00</t>
+        </is>
+      </c>
+      <c r="K252" s="32" t="inlineStr">
         <is>
           <t>Recherche Claude (26/10)</t>
         </is>
       </c>
-      <c r="L242" s="32" t="inlineStr">
+      <c r="L252" s="32" t="inlineStr">
         <is>
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N242" t="inlineStr">
+      <c r="N252" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
       </c>
-      <c r="O242" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : studio/showroom de pierre naturelle, marbre et terrazzo haut de gamme depuis 2012, distribution et pose sur rendez-vous ; deux showrooms parisiens confirmés. E-mail lu textuellement sur la page Pierre du site officiel ; téléphone confirmé. Domaine hors liste d'exclusion. Site officiel, pas un annuaire. Source e-mail : https://www.ateliermatiere.fr/pierre.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q242" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R242" t="inlineStr">
-        <is>
-          <t>info@ateliermatiere.fr</t>
-        </is>
-      </c>
-    </row>
-    <row r="243" ht="15" customHeight="1" s="33">
-      <c r="A243" t="n">
-        <v>243</v>
-      </c>
-      <c r="B243" t="inlineStr">
+      <c r="O252" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé via sources tierces : société MOTTE DECORATION immatriculée (SIREN 844835728, taille/façonnage/finissage de pierres) au Pré-d'Auge (14340) ; marbrerie décorative familiale (marbre, granit, quartz, pierre naturelle) intervenant sur toute la Normandie — societe.com, Initiative Calvados, Pages Jaunes et index du site officiel concordants. E-mail NON confirmé textuellement : le site officiel refuse toute lecture automatisée (HTTP 401 sur l'accueil et la page contact), vérification visuelle impossible ici. L'index du moteur de recherche attribue bien contact@mottedecoration.com et le 02 31 32 22 00 au site officiel, et le téléphone est corroboré par plusieurs sources indépendantes. Retenu sur REPLI TÉLÉPHONE vérifié (02 31 32 22 00) ; ne pas utiliser l'e-mail avant confirmation visuelle sur le site. Hors liste d'exclusion. Entreprise réelle, en France, site vivant (blocage anti-robot, pas site mort). Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="Q252" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R252" s="32" t="inlineStr">
+        <is>
+          <t>contact@mottedecoration.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="253" ht="15" customHeight="1" s="33">
+      <c r="A253" s="32" t="n">
+        <v>253</v>
+      </c>
+      <c r="B253" s="32" t="inlineStr">
         <is>
           <t>5e liste — recherche (26/10)</t>
         </is>
       </c>
-      <c r="C243" t="n">
+      <c r="C253" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D243" t="inlineStr">
-        <is>
-          <t>marbreries-idf</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr">
-        <is>
-          <t>Artefacts Paris</t>
-        </is>
-      </c>
-      <c r="F243" t="inlineStr">
-        <is>
-          <t>Paris 7e (showroom 17 bis passage Jean Nicot) ; atelier à Né</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
+      <c r="D253" s="32" t="inlineStr">
+        <is>
+          <t>normandie</t>
+        </is>
+      </c>
+      <c r="E253" s="32" t="inlineStr">
+        <is>
+          <t>Carreau Déco (SARL)</t>
+        </is>
+      </c>
+      <c r="F253" s="32" t="inlineStr">
+        <is>
+          <t>Évreux (27) ; autres magasins : Barentin, Tourville-la-Riviè</t>
+        </is>
+      </c>
+      <c r="G253" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H243" t="inlineStr">
-        <is>
-          <t>Confirmée : marbrerie fine et pierre de taille, revêtements durs en pierre naturelle pour la construction et l'agencement de luxe ; showroom Paris 7e et atelier/bureau d'études à N…</t>
-        </is>
-      </c>
-      <c r="I243" t="inlineStr">
-        <is>
-          <t>https://www.artefacts-paris.com</t>
-        </is>
-      </c>
-      <c r="K243" t="inlineStr">
+      <c r="H253" s="32" t="inlineStr">
+        <is>
+          <t>Confirmé : enseigne de carrelage (« Carrelage haut de gamme, sol et mur ») — grès cérame, dalles, faïence, intérieur/extérieur ; 6 points de vente confirmés dont Évreux, Barentin, …</t>
+        </is>
+      </c>
+      <c r="I253" s="32" t="inlineStr">
+        <is>
+          <t>https://www.carreaudeco.com</t>
+        </is>
+      </c>
+      <c r="J253" s="32" t="inlineStr">
+        <is>
+          <t>02 32 30 62 04 (Évreux) ; 02 37 21 27 80 (Lèves/standard) ; 02 78 77 51 00 (Barentin) ; 02 78 77 09 77 (Tourville) ; 02 78 93 05 05 (Montivilliers) ; 02 37 46 23 27 (Vernouillet)</t>
+        </is>
+      </c>
+      <c r="K253" s="32" t="inlineStr">
         <is>
           <t>Recherche Claude (26/10)</t>
         </is>
       </c>
-      <c r="L243" s="32" t="inlineStr">
+      <c r="L253" s="32" t="inlineStr">
+        <is>
+          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
+        </is>
+      </c>
+      <c r="N253" s="32" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O253" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé : enseigne de carrelage (« Carrelage haut de gamme, sol et mur ») — grès cérame, dalles, faïence, intérieur/extérieur ; 6 points de vente confirmés dont Évreux, Barentin, Tourville-la-Rivière et Montivilliers. AUCUN e-mail publié textuellement sur le site officiel (formulaire de contact uniquement) — vérifié. Retenu sur REPLI TÉLÉPHONE : les 6 numéros de magasins sont confirmés sur le site officiel, dont Évreux 02 32 30 62 04 et le standard de Lèves 02 37 21 27 80. Hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="Q253" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254" ht="15" customHeight="1" s="33">
+      <c r="A254" s="32" t="n">
+        <v>254</v>
+      </c>
+      <c r="B254" s="32" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C254" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D254" s="32" t="inlineStr">
+        <is>
+          <t>normandie</t>
+        </is>
+      </c>
+      <c r="E254" s="32" t="inlineStr">
+        <is>
+          <t>Carré &amp; Déco (SAS Fortin Design)</t>
+        </is>
+      </c>
+      <c r="F254" s="32" t="inlineStr">
+        <is>
+          <t>Colombelles (14460), 6 rue de la Métallurgie — agglomération</t>
+        </is>
+      </c>
+      <c r="G254" s="32" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H254" s="32" t="inlineStr">
+        <is>
+          <t>Confirmé : magasin de carrelage et céramique avec showroom (« votre expert en carrelage et céramique à proximité de Caen »), pierre naturelle présente en gamme extérieure (activité…</t>
+        </is>
+      </c>
+      <c r="I254" s="32" t="inlineStr">
+        <is>
+          <t>https://carre-deco.fr</t>
+        </is>
+      </c>
+      <c r="J254" s="32" t="inlineStr">
+        <is>
+          <t>02 31 34 40 50</t>
+        </is>
+      </c>
+      <c r="K254" s="32" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L254" s="32" t="inlineStr">
+        <is>
+          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
+        </is>
+      </c>
+      <c r="N254" s="32" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O254" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé : magasin de carrelage et céramique avec showroom (« votre expert en carrelage et céramique à proximité de Caen »), pierre naturelle présente en gamme extérieure (activité secondaire). AUCUN e-mail publié textuellement sur le site officiel (formulaire uniquement) — vérifié. Retenu sur REPLI TÉLÉPHONE : 02 31 34 40 50 confirmé sur le site officiel, adresse Colombelles confirmée. Nuance : la pierre naturelle n'est pas son cœur de métier (carrelage/céramique d'abord). Hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="Q254" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255" ht="15" customHeight="1" s="33">
+      <c r="A255" s="32" t="n">
+        <v>255</v>
+      </c>
+      <c r="B255" s="32" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C255" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D255" s="32" t="inlineStr">
+        <is>
+          <t>destockage-exterieur</t>
+        </is>
+      </c>
+      <c r="E255" s="32" t="inlineStr">
+        <is>
+          <t>Vallois (groupe Spie batignolles paysage) — agence Val de Seine</t>
+        </is>
+      </c>
+      <c r="F255" s="32" t="inlineStr">
+        <is>
+          <t>Val-de-Reuil (27100, Z.A la Comminière) — agence IDF à Trapp</t>
+        </is>
+      </c>
+      <c r="G255" s="32" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H255" s="32" t="inlineStr">
+        <is>
+          <t>Confirmée : « aménagements paysagers » dans le Grand Ouest, société de Spie batignolles paysage (vérifié sur la page d'accueil) ; la page contact confirme l'agence Val de Seine à V…</t>
+        </is>
+      </c>
+      <c r="I255" s="32" t="inlineStr">
+        <is>
+          <t>https://www.vallois.eu/</t>
+        </is>
+      </c>
+      <c r="J255" s="32" t="inlineStr">
+        <is>
+          <t>02 32 40 32 30 (Val de Seine) ; 01 30 16 07 00 (IDF Trappes)</t>
+        </is>
+      </c>
+      <c r="K255" s="32" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L255" s="32" t="inlineStr">
         <is>
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N243" t="inlineStr">
+      <c r="N255" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
       </c>
-      <c r="O243" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : marbrerie fine et pierre de taille, revêtements durs en pierre naturelle pour la construction et l'agencement de luxe ; showroom Paris 7e et atelier/bureau d'études à Nérac (47600) confirmés. E-mail lu textuellement sur le site officiel. Aucun téléphone affiché sur la page. L'atelier de façonnage est bien hors IdF (Nérac, 47) comme signalé, mais la vitrine commerciale et les chantiers sont parisiens. Domaine hors liste d'exclusion. Source e-mail : https://www.artefacts-paris.com.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q243" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R243" t="inlineStr">
-        <is>
-          <t>info@artefacts-paris.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="244" ht="15" customHeight="1" s="33">
-      <c r="A244" t="n">
-        <v>244</v>
-      </c>
-      <c r="B244" t="inlineStr">
+      <c r="O255" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment destockage-exterieur). Confirmée : « aménagements paysagers » dans le Grand Ouest, société de Spie batignolles paysage (vérifié sur la page d'accueil) ; la page contact confirme l'agence Val de Seine à Val-de-Reuil 27100 et l'agence IDF à Trappes 78190. E-mail lu textuellement dans la fiche « Agence Val de Seine » de la page contact ; les deux téléphones y figurent aussi textuellement. Précision : la page contact donne comme siège social de Spie batignolles paysage Nanterre (92) et comme siège administratif St Hymer (14) ; Mirville (76210) est l'adresse de l'agence de l'Estuaire, pas du siège. Hors liste d'exclusion. Candidat solide. Source e-mail : https://www.vallois.eu/contact.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi [26/10 croisement fichier propriétaire] Variante IdF (fichier) : agence-idf@vallois.eu / 01 30 16 07 00 — choisir l'agence selon le chantier.</t>
+        </is>
+      </c>
+      <c r="Q255" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R255" s="32" t="inlineStr">
+        <is>
+          <t>agence-valdeseine@vallois.eu</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="15" customHeight="1" s="33">
+      <c r="A256" s="32" t="n">
+        <v>256</v>
+      </c>
+      <c r="B256" s="32" t="inlineStr">
         <is>
           <t>5e liste — recherche (26/10)</t>
         </is>
       </c>
-      <c r="C244" t="n">
+      <c r="C256" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D256" s="32" t="inlineStr">
+        <is>
+          <t>destockage-exterieur</t>
+        </is>
+      </c>
+      <c r="E256" s="32" t="inlineStr">
+        <is>
+          <t>Tricycle Environnement / Bâticycle</t>
+        </is>
+      </c>
+      <c r="F256" s="32" t="inlineStr">
+        <is>
+          <t>Gennevilliers (120 rue du Moulin de Cage, 92230)</t>
+        </is>
+      </c>
+      <c r="G256" s="32" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H256" s="32" t="inlineStr">
+        <is>
+          <t>Confirmée : « Matériaux BTP d'occasion », « Réemploi de matériaux de second œuvre », « Curage de bâtiment » — réemploi/revente de matériaux de construction, vérifié sur le site off…</t>
+        </is>
+      </c>
+      <c r="I256" s="32" t="inlineStr">
+        <is>
+          <t>https://www.tricycle-environnement.fr/</t>
+        </is>
+      </c>
+      <c r="J256" s="32" t="inlineStr">
+        <is>
+          <t>07 60 62 41 36 / 06 99 57 37 28</t>
+        </is>
+      </c>
+      <c r="K256" s="32" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L256" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N256" s="32" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O256" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment destockage-exterieur). Confirmée : « Matériaux BTP d'occasion », « Réemploi de matériaux de second œuvre », « Curage de bâtiment » — réemploi/revente de matériaux de construction, vérifié sur le site officiel. E-mail lu textuellement en en-tête ET en pied de page ; téléphone confirmé sous deux formats (+33 7 60 62 41 36 / 07 60 62 41 36) ; adresse 120 rue du Moulin de Cage, 92230 Gennevilliers confirmée en pied de page — la ville même du stock. Hors liste d'exclusion. Candidat solide. Source e-mail : https://www.tricycle-environnement.fr/.  📍 Même ville que le dépôt (Gennevilliers) — réemploi : bon candidat reprise de lot. NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi [26/10 croisement fichier propriétaire] 2e canal relevé par le fichier : contact@bati-cycle.fr / 06 99 57 37 28 (marque Bâticycle). Choisir UNE voie à l'envoi.</t>
+        </is>
+      </c>
+      <c r="Q256" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R256" s="32" t="inlineStr">
+        <is>
+          <t>contact@tri-cycle.fr</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="15" customHeight="1" s="33">
+      <c r="A257" s="32" t="n">
+        <v>257</v>
+      </c>
+      <c r="B257" s="32" t="inlineStr">
+        <is>
+          <t>5e liste — recherche (26/10)</t>
+        </is>
+      </c>
+      <c r="C257" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>marbreries-idf</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>H. Chevalier</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>Suresnes (26 rue Henri Regnault, 92150)</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
+      <c r="D257" s="32" t="inlineStr">
+        <is>
+          <t>destockage-exterieur</t>
+        </is>
+      </c>
+      <c r="E257" s="32" t="inlineStr">
+        <is>
+          <t>Minéka</t>
+        </is>
+      </c>
+      <c r="F257" s="32" t="inlineStr">
+        <is>
+          <t>Villeurbanne (182 rue de la Poudrette, 69100)</t>
+        </is>
+      </c>
+      <c r="G257" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>Confirmée : restauration du patrimoine bâti depuis 1946 (maçonnerie-pierre, restauration de sculpture, hôtels particuliers et châteaux), 250 salariés, 80 M€ de CA ; adresse à Sures…</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>https://www.hchevalier.com</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>01 45 06 83 33</t>
-        </is>
-      </c>
-      <c r="K244" t="inlineStr">
+      <c r="H257" s="32" t="inlineStr">
+        <is>
+          <t>Confirmée : adresse « 182 rue de la Poudrette 69100 VILLEURBANNE » vérifiée dans les mentions légales, qui mentionnent aussi le magasin « Minéstock » (« Venez nous voir au Minéstoc…</t>
+        </is>
+      </c>
+      <c r="I257" s="32" t="inlineStr">
+        <is>
+          <t>https://mineka.fr/</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>04 78 52 86 28</t>
+        </is>
+      </c>
+      <c r="K257" s="32" t="inlineStr">
         <is>
           <t>Recherche Claude (26/10)</t>
         </is>
       </c>
-      <c r="L244" s="32" t="inlineStr">
+      <c r="L257" s="32" t="inlineStr">
         <is>
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N244" t="inlineStr">
+      <c r="N257" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
       </c>
-      <c r="O244" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : restauration du patrimoine bâti depuis 1946 (maçonnerie-pierre, restauration de sculpture, hôtels particuliers et châteaux), 250 salariés, 80 M€ de CA ; adresse à Suresnes confirmée. E-mail et téléphone lus textuellement sur la page d'accueil du site officiel. Domaine hors liste d'exclusion. Profil patrimoine/monuments : pertinence moyenne pour un calcaire égyptien standard, comme indiqué dans le candidat. Source e-mail : https://www.hchevalier.com.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q244" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R244" t="inlineStr">
-        <is>
-          <t>contact@hchevalier.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="245" ht="15" customHeight="1" s="33">
-      <c r="A245" t="n">
-        <v>245</v>
-      </c>
-      <c r="B245" t="inlineStr">
+      <c r="O257" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment destockage-exterieur). Confirmée : adresse « 182 rue de la Poudrette 69100 VILLEURBANNE » vérifiée dans les mentions légales, qui mentionnent aussi le magasin « Minéstock » (« Venez nous voir au Minéstock ») — structure de collecte/revente avec point de vente physique, pas une pure marketplace. E-mail lu textuellement dans les mentions légales (« Adresse électronique : contact@mineka.fr »), seule adresse de la page. AUCUN téléphone publié : le contact ne pourra se faire que par e-mail (vérifié). En France (Lyon/Villeurbanne) ; limite logistique : loin des stocks de Vernon/Gennevilliers, retrait à organiser. Hors liste d'exclusion. Source e-mail : https://mineka.fr/mentions-legales/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi [26/10 croisement fichier propriétaire] Canal collecte préféré (fichier) : collecte@mineka.fr.</t>
+        </is>
+      </c>
+      <c r="Q257" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R257" s="32" t="inlineStr">
+        <is>
+          <t>collecte@mineka.fr</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="15" customHeight="1" s="33">
+      <c r="A258" s="32" t="n">
+        <v>258</v>
+      </c>
+      <c r="B258" s="32" t="inlineStr">
         <is>
           <t>5e liste — recherche (26/10)</t>
         </is>
       </c>
-      <c r="C245" t="n">
+      <c r="C258" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>marbreries-idf</t>
-        </is>
-      </c>
-      <c r="E245" t="inlineStr">
-        <is>
-          <t>Vexin Patrimoine</t>
-        </is>
-      </c>
-      <c r="F245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Secteur Vexin / Île-de-France (95) — aucune adresse précise </t>
-        </is>
-      </c>
-      <c r="G245" t="inlineStr">
+      <c r="D258" s="32" t="inlineStr">
+        <is>
+          <t>destockage-exterieur</t>
+        </is>
+      </c>
+      <c r="E258" s="32" t="inlineStr">
+        <is>
+          <t>Pinson Paysage (groupe Osmaïa)</t>
+        </is>
+      </c>
+      <c r="F258" s="32" t="inlineStr">
+        <is>
+          <t>Andilly (13 avenue des Cures, 95580)</t>
+        </is>
+      </c>
+      <c r="G258" s="32" t="inlineStr">
         <is>
           <t>France</t>
         </is>
       </c>
-      <c r="H245" t="inlineStr">
-        <is>
-          <t>Confirmée : tailleur de pierre (taille sur mesure intérieur/extérieur, restauration historique, création, sols en pierre), plus de 15 ans d'expérience, clients pro et particuliers,…</t>
-        </is>
-      </c>
-      <c r="I245" t="inlineStr">
-        <is>
-          <t>https://vexinpatrimoine.fr</t>
-        </is>
-      </c>
-      <c r="J245" t="inlineStr">
-        <is>
-          <t>01 30 73 86 50</t>
-        </is>
-      </c>
-      <c r="K245" t="inlineStr">
+      <c r="H258" s="32" t="inlineStr">
+        <is>
+          <t>Confirmée : page « Nous contacter » vérifiée — siège « 13 Avenue des Cures, 95580 Andilly » ; activités « Création », « Entretien » (espaces verts) et « Génie écologique » affichée…</t>
+        </is>
+      </c>
+      <c r="I258" s="32" t="inlineStr">
+        <is>
+          <t>https://www.pinson-paysage.com/</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>01 34 16 61 01</t>
+        </is>
+      </c>
+      <c r="K258" s="32" t="inlineStr">
         <is>
           <t>Recherche Claude (26/10)</t>
         </is>
       </c>
-      <c r="L245" s="32" t="inlineStr">
+      <c r="L258" s="32" t="inlineStr">
         <is>
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N245" t="inlineStr">
+      <c r="N258" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
         </is>
       </c>
-      <c r="O245" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : tailleur de pierre (taille sur mesure intérieur/extérieur, restauration historique, création, sols en pierre), plus de 15 ans d'expérience, clients pro et particuliers, zone Vexin/Île-de-France. Deux graphies sur le site : le pied de page affiche textuellement contact@vexinpatrimoine.fr (correct) ; la barre latérale affiche la coquille « contat@vexinpatrimoine.fr ». Utiliser contact@vexinpatrimoine.fr. Téléphone confirmé (affiché deux fois). Aucune ville précise publiée, cohérent avec le candidat. Domaine hors liste d'exclusion. Source e-mail : https://vexinpatrimoine.fr/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q245" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R245" t="inlineStr">
-        <is>
-          <t>contact@vexinpatrimoine.fr</t>
-        </is>
-      </c>
-    </row>
-    <row r="246" ht="15" customHeight="1" s="33">
-      <c r="A246" t="n">
-        <v>246</v>
-      </c>
-      <c r="B246" t="inlineStr">
+      <c r="O258" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment destockage-exterieur). Confirmée : page « Nous contacter » vérifiée — siège « 13 Avenue des Cures, 95580 Andilly » ; activités « Création », « Entretien » (espaces verts) et « Génie écologique » affichées, cohérentes avec une entreprise paysagère IDF. E-mail lu textuellement (seule adresse de la page). AUCUN téléphone sur la page contact (formulaire uniquement) : contact par e-mail vérifié. Réserve maintenue : le site met en avant le végétal/génie écologique plus que la maçonnerie minérale — pertinence segment (b) à pondérer. Hors liste d'exclusion. Source e-mail : https://www.pinson-paysage.com/nous-contacter/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="Q258" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R258" s="32" t="inlineStr">
+        <is>
+          <t>pinson@pinson-paysage.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="15" customHeight="1" s="33">
+      <c r="A259" s="32" t="n">
+        <v>259</v>
+      </c>
+      <c r="B259" s="32" t="inlineStr">
         <is>
           <t>5e liste — recherche (26/10)</t>
         </is>
       </c>
-      <c r="C246" t="n">
+      <c r="C259" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D259" s="32" t="inlineStr">
+        <is>
+          <t>destockage-exterieur</t>
+        </is>
+      </c>
+      <c r="E259" s="32" t="inlineStr">
+        <is>
+          <t>NOZ (centrale d'achat S.F.N.)</t>
+        </is>
+      </c>
+      <c r="F259" s="32" t="inlineStr">
+        <is>
+          <t>Saint-Berthevin (53940)</t>
+        </is>
+      </c>
+      <c r="G259" s="32" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="H259" s="32" t="inlineStr">
+        <is>
+          <t>Confirmée : page contact vérifiée — adresse « 53940 Saint-Berthevin – France », formulaire avec champ « Vous êtes ? » incluant « Je suis un fournisseur » et objet « Besoin de désto…</t>
+        </is>
+      </c>
+      <c r="I259" s="32" t="inlineStr">
+        <is>
+          <t>https://www.noz.fr/</t>
+        </is>
+      </c>
+      <c r="J259" s="32" t="inlineStr">
+        <is>
+          <t>02 43 01 53 54</t>
+        </is>
+      </c>
+      <c r="K259" s="32" t="inlineStr">
+        <is>
+          <t>Recherche Claude (26/10)</t>
+        </is>
+      </c>
+      <c r="L259" s="32" t="inlineStr">
+        <is>
+          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
+        </is>
+      </c>
+      <c r="N259" s="32" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
+        </is>
+      </c>
+      <c r="O259" s="32" t="inlineStr">
+        <is>
+          <t>[26/10] Recherche vérifiée (segment destockage-exterieur). Confirmée : page contact vérifiée — adresse « 53940 Saint-Berthevin – France », formulaire avec champ « Vous êtes ? » incluant « Je suis un fournisseur » et objet « Besoin de déstockage », cohérent avec l'activité de rachat de surstocks/lots. RETENU SANS E-MAIL : aucun e-mail publié sur https://www.noz.fr/contactez-nous/ (revérifié le 26/10/2026 — le seul mot « Email » est un champ de formulaire), mais le téléphone 02 43 01 53 54 y est écrit textuellement et vérifié ; contact via ce numéro ou le formulaire fournisseur « Besoin de déstockage ». Hors liste d'exclusion. Réserve : lot minéral lourd atypique dans leur mix. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi [26/10 croisement fichier propriétaire] E-mail noz@noz.fr apporté par le fichier — NON vérifié sur site officiel, à confirmer avant envoi.</t>
+        </is>
+      </c>
+      <c r="Q259" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>noz@noz.fr</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="15" customHeight="1" s="33">
+      <c r="A260" t="n">
+        <v>260</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>5e liste — croisement (26/10)</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
         <v>2</v>
       </c>
-      <c r="D246" t="inlineStr">
-        <is>
-          <t>marbreries-idf</t>
-        </is>
-      </c>
-      <c r="E246" t="inlineStr">
-        <is>
-          <t>Accolade Artisans</t>
-        </is>
-      </c>
-      <c r="F246" t="inlineStr">
-        <is>
-          <t>Viarmes (14 rue Kleinpeter, 95270)</t>
-        </is>
-      </c>
-      <c r="G246" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr">
-        <is>
-          <t>Confirmée : taille de pierre et maçonnerie de restauration du bâti ancien (certification Qualibat restauration pierre de taille et maçonnerie du patrimoine) ; adresse à Viarmes (95…</t>
-        </is>
-      </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>https://www.accoladeartisans.fr</t>
-        </is>
-      </c>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t>06 27 85 91 92</t>
-        </is>
-      </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t>Recherche Claude (26/10)</t>
-        </is>
-      </c>
-      <c r="L246" s="32" t="inlineStr">
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Marbrerie / pierre</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>ILDEI</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Le Plessis-Pâté (91)</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>Marbrerie / pierre</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>01 60 84 11 00</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Croisement fichier (26/10)</t>
+        </is>
+      </c>
+      <c r="L260" s="32" t="inlineStr">
         <is>
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N246" t="inlineStr">
-        <is>
-          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="O246" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : taille de pierre et maçonnerie de restauration du bâti ancien (certification Qualibat restauration pierre de taille et maçonnerie du patrimoine) ; adresse à Viarmes (95270) confirmée. E-mail lu textuellement dans la section Coordonnées du pied de page ; téléphone confirmé (en-tête et pied de page). Domaine hors liste d'exclusion. Site officiel, pas un annuaire. Source e-mail : https://www.accoladeartisans.fr/taille-de-pierre.htm.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q246" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R246" t="inlineStr">
-        <is>
-          <t>contact@accoladeartisans.fr</t>
-        </is>
-      </c>
-    </row>
-    <row r="247" ht="15" customHeight="1" s="33">
-      <c r="A247" t="n">
-        <v>247</v>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>5e liste — recherche (26/10)</t>
-        </is>
-      </c>
-      <c r="C247" t="n">
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>[26/10 croisement fichier propriétaire] Apporté par le fichier propriétaire du 26/10 (origine « Recherche 31 » de son côté). E-mail à re-vérifier sur site officiel avant envoi. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="Q260" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>contact@ildei.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="15" customHeight="1" s="33">
+      <c r="A261" t="n">
+        <v>261</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>5e liste — croisement (26/10)</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
         <v>2</v>
       </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>marbreries-idf</t>
-        </is>
-      </c>
-      <c r="E247" t="inlineStr">
-        <is>
-          <t>Techno Pierre</t>
-        </is>
-      </c>
-      <c r="F247" t="inlineStr">
-        <is>
-          <t>Vanves (35 rue Aristide Briand, 92170)</t>
-        </is>
-      </c>
-      <c r="G247" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H247" t="inlineStr">
-        <is>
-          <t>Confirmée : tailleur de pierres et marbrier du bâtiment (taille de pierre, marbrerie, rénovation et revêtement de façades en pierre, marbre et granit) ; adresse à Vanves confirmée.</t>
-        </is>
-      </c>
-      <c r="I247" t="inlineStr">
-        <is>
-          <t>https://www.technopierre.fr</t>
-        </is>
-      </c>
-      <c r="J247" t="inlineStr">
-        <is>
-          <t>09 74 56 39 83</t>
-        </is>
-      </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>Recherche Claude (26/10)</t>
-        </is>
-      </c>
-      <c r="L247" s="32" t="inlineStr">
-        <is>
-          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
-        </is>
-      </c>
-      <c r="N247" t="inlineStr">
-        <is>
-          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="O247" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment marbreries-idf). Confirmée : tailleur de pierres et marbrier du bâtiment (taille de pierre, marbrerie, rénovation et revêtement de façades en pierre, marbre et granit) ; adresse à Vanves confirmée. AUCUN e-mail publié sur le site officiel : la page contactez-nous.php ne propose qu'un formulaire (le lien « E-mail » pointe vers ce formulaire, pas vers une adresse). Retenu sur la base du téléphone vérifié 09 74 56 39 83, affiché plusieurs fois sur la page. Domaine hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q247" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="248" ht="15" customHeight="1" s="33">
-      <c r="A248" t="n">
-        <v>248</v>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>5e liste — recherche (26/10)</t>
-        </is>
-      </c>
-      <c r="C248" t="n">
-        <v>1</v>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>normandie</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>Guilloux Matériaux</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>Cormeilles (27) et Rouen (76) — siège Saint-Pair-sur-Mer (50</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>Confirmé : négoce indépendant de matériaux de construction, 10 agences en Normandie (dont Cormeilles 27 et Rouen 76), scierie/atelier à Vire, siège à Saint-Pair-sur-Mer (50380).</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>https://www.guillouxmateriaux.com</t>
-        </is>
-      </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t>02 33 48 14 44 (siège) ; agence Cormeilles 02 32 57 15 98 ; agence Rouen 02 32 12 11 80</t>
-        </is>
-      </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>Recherche Claude (26/10)</t>
-        </is>
-      </c>
-      <c r="L248" s="32" t="inlineStr">
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Marbrerie</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>La Marbrerie Contemporaine</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Bagnolet (93)</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>Marbrerie</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>01 48 97 00 13</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Croisement fichier (26/10)</t>
+        </is>
+      </c>
+      <c r="L261" s="32" t="inlineStr">
         <is>
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N248" t="inlineStr">
-        <is>
-          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="O248" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé : négoce indépendant de matériaux de construction, 10 agences en Normandie (dont Cormeilles 27 et Rouen 76), scierie/atelier à Vire, siège à Saint-Pair-sur-Mer (50380). E-mail lu TEXTUELLEMENT sur les mentions légales (responsable de la publication). Attention : le domaine de l'e-mail (guilloux-materiaux.com, avec tiret) diffère du domaine du site (guillouxmateriaux.com) — c'est bien ce qu'affiche le site officiel. Téléphones siège/Cormeilles/Rouen tous confirmés sur la même page. Hors liste d'exclusion. Source e-mail : https://www.guillouxmateriaux.com/mentions-legales-guilloux-materiaux-le-specialiste-des-materiaux-de-construction/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q248" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R248" t="inlineStr">
-        <is>
-          <t>bonjour@guilloux-materiaux.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="249" ht="15" customHeight="1" s="33">
-      <c r="A249" t="n">
-        <v>249</v>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>5e liste — recherche (26/10)</t>
-        </is>
-      </c>
-      <c r="C249" t="n">
-        <v>1</v>
-      </c>
-      <c r="D249" t="inlineStr">
-        <is>
-          <t>normandie</t>
-        </is>
-      </c>
-      <c r="E249" t="inlineStr">
-        <is>
-          <t>Sani 27 (« Le Géant du carrelage »)</t>
-        </is>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>Angerville-la-Campagne (27930), ZAC de Villeneuve — près d'É</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Confirmé : magasin spécialiste du carrelage (« le plus grand magasin de carrelage ») avec sanitaire, robinetterie et meubles de salle de bain ; adresse ZAC de Villeneuve, 27930 Ang…</t>
-        </is>
-      </c>
-      <c r="I249" t="inlineStr">
-        <is>
-          <t>https://sani27.com</t>
-        </is>
-      </c>
-      <c r="J249" t="inlineStr">
-        <is>
-          <t>02 32 28 00 12</t>
-        </is>
-      </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t>Recherche Claude (26/10)</t>
-        </is>
-      </c>
-      <c r="L249" s="32" t="inlineStr">
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>[26/10 croisement fichier propriétaire] Apporté par le fichier propriétaire du 26/10 (origine « Recherche 31 » de son côté). E-mail à re-vérifier sur site officiel avant envoi. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="Q261" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>contact@la-marbrerie-contemporaine.fr</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="15" customHeight="1" s="33">
+      <c r="A262" t="n">
+        <v>262</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>5e liste — croisement (26/10)</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>2</v>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Marbrerie / négoce pierre</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Paris Roches</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Vitry-sur-Seine (94)</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>Marbrerie / négoce pierre</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>01 47 26 00 99</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Croisement fichier (26/10)</t>
+        </is>
+      </c>
+      <c r="L262" s="32" t="inlineStr">
         <is>
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N249" t="inlineStr">
-        <is>
-          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="O249" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé : magasin spécialiste du carrelage (« le plus grand magasin de carrelage ») avec sanitaire, robinetterie et meubles de salle de bain ; adresse ZAC de Villeneuve, 27930 Angerville-la-Campagne, zone d'Évreux. contact@sani27.fr est écrit TEXTUELLEMENT dans le pied de page du site officiel. Divergence confirmée : le lien mailto associé pointe vers sani27@wanadoo.fr — en cas de non-réponse sur contact@sani27.fr, utiliser sani27@wanadoo.fr en seconde adresse. Téléphone 02 32 28 00 12 confirmé. Hors liste d'exclusion. Source e-mail : https://sani27.com/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q249" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R249" t="inlineStr">
-        <is>
-          <t>contact@sani27.fr</t>
-        </is>
-      </c>
-    </row>
-    <row r="250" ht="15" customHeight="1" s="33">
-      <c r="A250" t="n">
-        <v>250</v>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>5e liste — recherche (26/10)</t>
-        </is>
-      </c>
-      <c r="C250" t="n">
-        <v>1</v>
-      </c>
-      <c r="D250" t="inlineStr">
-        <is>
-          <t>normandie</t>
-        </is>
-      </c>
-      <c r="E250" t="inlineStr">
-        <is>
-          <t>BCA Matériaux Anciens</t>
-        </is>
-      </c>
-      <c r="F250" t="inlineStr">
-        <is>
-          <t>Méry-Corbon (14370) et Pont-l'Évêque (14130) — siège Segré-e</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>Confirmé : « Spécialiste des matériaux anciens » — dallages et carrelages anciens en pierre, parquets anciens, tomettes, pavés, parements pierre, cheminées ; deux agences normandes…</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>https://www.bca-materiauxanciens.com</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>02 31 23 95 87 (Méry-Corbon) ; 02 61 67 23 40 (Pont-l'Évêque) ; +33 (0)2 41 61 62 40 (siège)</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>Recherche Claude (26/10)</t>
-        </is>
-      </c>
-      <c r="L250" s="32" t="inlineStr">
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>[26/10 croisement fichier propriétaire] Apporté par le fichier propriétaire du 26/10 (origine « Recherche 31 » de son côté). E-mail à re-vérifier sur site officiel avant envoi. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="Q262" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>paris-roches@orange.fr</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="15" customHeight="1" s="33">
+      <c r="A263" t="n">
+        <v>263</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>5e liste — croisement (26/10)</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>2</v>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Marbrerie</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Alpha Marbre</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Coubert (77)</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>Marbrerie</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>01 64 16 03 69</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Croisement fichier (26/10)</t>
+        </is>
+      </c>
+      <c r="L263" s="32" t="inlineStr">
         <is>
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N250" t="inlineStr">
-        <is>
-          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="O250" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé : « Spécialiste des matériaux anciens » — dallages et carrelages anciens en pierre, parquets anciens, tomettes, pavés, parements pierre, cheminées ; deux agences normandes (Méry-Corbon et Pont-l'Évêque), siège en Pays de la Loire. normandie@bcamateriaux.com (agence Méry-Corbon) lu TEXTUELLEMENT sur le site officiel, ainsi que pontleveque@bcamateriaux.com, info@bcamateriaux.com et david@bcamateriaux.com (anglais). Tous les téléphones confirmés. Cœur de métier aligné (dallages pierre par lots). Hors liste d'exclusion. Source e-mail : https://www.bca-materiauxanciens.com.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q250" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R250" t="inlineStr">
-        <is>
-          <t>normandie@bcamateriaux.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="251" ht="15" customHeight="1" s="33">
-      <c r="A251" t="n">
-        <v>251</v>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>5e liste — recherche (26/10)</t>
-        </is>
-      </c>
-      <c r="C251" t="n">
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>[26/10 croisement fichier propriétaire] Apporté par le fichier propriétaire du 26/10 (origine « Recherche 31 » de son côté). E-mail à re-vérifier sur site officiel avant envoi. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="Q263" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>alpha.marbre@laposte.net</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="15" customHeight="1" s="33">
+      <c r="A264" t="n">
+        <v>264</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>5e liste — croisement (26/10)</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
         <v>2</v>
       </c>
-      <c r="D251" t="inlineStr">
-        <is>
-          <t>normandie</t>
-        </is>
-      </c>
-      <c r="E251" t="inlineStr">
-        <is>
-          <t>Adéquate - Marbrerie Décorative</t>
-        </is>
-      </c>
-      <c r="F251" t="inlineStr">
-        <is>
-          <t>Seulline (14310), ZA Eco 5 — près de Caen</t>
-        </is>
-      </c>
-      <c r="G251" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>Confirmé : marbrerie décorative avec showroom (visites sur rendez-vous), ZA Eco 5 n° 7 et 9, 14310 Seulline, « près de Caen en Normandie ».</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>https://www.adequatemarbrerie.fr</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t>02 31 24 11 22</t>
-        </is>
-      </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t>Recherche Claude (26/10)</t>
-        </is>
-      </c>
-      <c r="L251" s="32" t="inlineStr">
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Marbrerie</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Marbrerie Christian Caudron</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Noisy-le-Sec (93)</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Île-de-France</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Marbrerie</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>06 30 60 75 01</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Croisement fichier (26/10)</t>
+        </is>
+      </c>
+      <c r="L264" s="32" t="inlineStr">
         <is>
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N251" t="inlineStr">
-        <is>
-          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="O251" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé : marbrerie décorative avec showroom (visites sur rendez-vous), ZA Eco 5 n° 7 et 9, 14310 Seulline, « près de Caen en Normandie ». contact@adequatemarbrerie.fr lu TEXTUELLEMENT sur la page contact du site officiel (en texte et en lien mailto, concordants). Téléphone confirmé. Hors liste d'exclusion. Source e-mail : https://www.adequatemarbrerie.fr/contact.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q251" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R251" t="inlineStr">
-        <is>
-          <t>contact@adequatemarbrerie.fr</t>
-        </is>
-      </c>
-    </row>
-    <row r="252" ht="15" customHeight="1" s="33">
-      <c r="A252" t="n">
-        <v>252</v>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>5e liste — recherche (26/10)</t>
-        </is>
-      </c>
-      <c r="C252" t="n">
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>[26/10 croisement fichier propriétaire] Apporté par le fichier propriétaire du 26/10 (origine « Recherche 31 » de son côté). E-mail à re-vérifier sur site officiel avant envoi. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="Q264" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>atelier-marbre@orange.fr</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="15" customHeight="1" s="33">
+      <c r="A265" t="n">
+        <v>265</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>5e liste — croisement (26/10)</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
         <v>2</v>
       </c>
-      <c r="D252" t="inlineStr">
-        <is>
-          <t>normandie</t>
-        </is>
-      </c>
-      <c r="E252" t="inlineStr">
-        <is>
-          <t>Motte Décoration</t>
-        </is>
-      </c>
-      <c r="F252" t="inlineStr">
-        <is>
-          <t>Le Pré-d'Auge (14340), 10 Chemin des Vatines — entre Cambrem</t>
-        </is>
-      </c>
-      <c r="G252" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H252" t="inlineStr">
-        <is>
-          <t>Confirmé via sources tierces : société MOTTE DECORATION immatriculée (SIREN 844835728, taille/façonnage/finissage de pierres) au Pré-d'Auge (14340) ; marbrerie décorative familiale…</t>
-        </is>
-      </c>
-      <c r="I252" t="inlineStr">
-        <is>
-          <t>https://www.mottedecoration.com</t>
-        </is>
-      </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t>02 31 32 22 00</t>
-        </is>
-      </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t>Recherche Claude (26/10)</t>
-        </is>
-      </c>
-      <c r="L252" s="32" t="inlineStr">
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Négoce matériaux</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Facomat</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Buchy (76)</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Normandie</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>Négoce matériaux</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Croisement fichier (26/10)</t>
+        </is>
+      </c>
+      <c r="L265" s="32" t="inlineStr">
         <is>
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N252" t="inlineStr">
-        <is>
-          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="O252" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé via sources tierces : société MOTTE DECORATION immatriculée (SIREN 844835728, taille/façonnage/finissage de pierres) au Pré-d'Auge (14340) ; marbrerie décorative familiale (marbre, granit, quartz, pierre naturelle) intervenant sur toute la Normandie — societe.com, Initiative Calvados, Pages Jaunes et index du site officiel concordants. E-mail NON confirmé textuellement : le site officiel refuse toute lecture automatisée (HTTP 401 sur l'accueil et la page contact), vérification visuelle impossible ici. L'index du moteur de recherche attribue bien contact@mottedecoration.com et le 02 31 32 22 00 au site officiel, et le téléphone est corroboré par plusieurs sources indépendantes. Retenu sur REPLI TÉLÉPHONE vérifié (02 31 32 22 00) ; ne pas utiliser l'e-mail avant confirmation visuelle sur le site. Hors liste d'exclusion. Entreprise réelle, en France, site vivant (blocage anti-robot, pas site mort). Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q252" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R252" t="inlineStr">
-        <is>
-          <t>contact@mottedecoration.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="253" ht="15" customHeight="1" s="33">
-      <c r="A253" t="n">
-        <v>253</v>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>5e liste — recherche (26/10)</t>
-        </is>
-      </c>
-      <c r="C253" t="n">
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>[26/10 croisement fichier propriétaire] Apporté par le fichier propriétaire du 26/10 (origine « Recherche 31 » de son côté). E-mail à re-vérifier sur site officiel avant envoi. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="Q265" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>facomat76@wanadoo.fr</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="15" customHeight="1" s="33">
+      <c r="A266" t="n">
+        <v>266</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>5e liste — croisement (26/10)</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
         <v>2</v>
       </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>normandie</t>
-        </is>
-      </c>
-      <c r="E253" t="inlineStr">
-        <is>
-          <t>Carreau Déco (SARL)</t>
-        </is>
-      </c>
-      <c r="F253" t="inlineStr">
-        <is>
-          <t>Évreux (27) ; autres magasins : Barentin, Tourville-la-Riviè</t>
-        </is>
-      </c>
-      <c r="G253" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H253" t="inlineStr">
-        <is>
-          <t>Confirmé : enseigne de carrelage (« Carrelage haut de gamme, sol et mur ») — grès cérame, dalles, faïence, intérieur/extérieur ; 6 points de vente confirmés dont Évreux, Barentin, …</t>
-        </is>
-      </c>
-      <c r="I253" t="inlineStr">
-        <is>
-          <t>https://www.carreaudeco.com</t>
-        </is>
-      </c>
-      <c r="J253" t="inlineStr">
-        <is>
-          <t>02 32 30 62 04 (Évreux) ; 02 37 21 27 80 (Lèves/standard) ; 02 78 77 51 00 (Barentin) ; 02 78 77 09 77 (Tourville) ; 02 78 93 05 05 (Montivilliers) ; 02 37 46 23 27 (Vernouillet)</t>
-        </is>
-      </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t>Recherche Claude (26/10)</t>
-        </is>
-      </c>
-      <c r="L253" s="32" t="inlineStr">
-        <is>
-          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
-        </is>
-      </c>
-      <c r="N253" t="inlineStr">
-        <is>
-          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="O253" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé : enseigne de carrelage (« Carrelage haut de gamme, sol et mur ») — grès cérame, dalles, faïence, intérieur/extérieur ; 6 points de vente confirmés dont Évreux, Barentin, Tourville-la-Rivière et Montivilliers. AUCUN e-mail publié textuellement sur le site officiel (formulaire de contact uniquement) — vérifié. Retenu sur REPLI TÉLÉPHONE : les 6 numéros de magasins sont confirmés sur le site officiel, dont Évreux 02 32 30 62 04 et le standard de Lèves 02 37 21 27 80. Hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q253" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="254" ht="15" customHeight="1" s="33">
-      <c r="A254" t="n">
-        <v>254</v>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>5e liste — recherche (26/10)</t>
-        </is>
-      </c>
-      <c r="C254" t="n">
-        <v>2</v>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>normandie</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>Carré &amp; Déco (SAS Fortin Design)</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>Colombelles (14460), 6 rue de la Métallurgie — agglomération</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>Confirmé : magasin de carrelage et céramique avec showroom (« votre expert en carrelage et céramique à proximité de Caen »), pierre naturelle présente en gamme extérieure (activité…</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>https://carre-deco.fr</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>02 31 34 40 50</t>
-        </is>
-      </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t>Recherche Claude (26/10)</t>
-        </is>
-      </c>
-      <c r="L254" s="32" t="inlineStr">
-        <is>
-          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
-        </is>
-      </c>
-      <c r="N254" t="inlineStr">
-        <is>
-          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="O254" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment normandie). Confirmé : magasin de carrelage et céramique avec showroom (« votre expert en carrelage et céramique à proximité de Caen »), pierre naturelle présente en gamme extérieure (activité secondaire). AUCUN e-mail publié textuellement sur le site officiel (formulaire uniquement) — vérifié. Retenu sur REPLI TÉLÉPHONE : 02 31 34 40 50 confirmé sur le site officiel, adresse Colombelles confirmée. Nuance : la pierre naturelle n'est pas son cœur de métier (carrelage/céramique d'abord). Hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q254" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="255" ht="15" customHeight="1" s="33">
-      <c r="A255" t="n">
-        <v>255</v>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>5e liste — recherche (26/10)</t>
-        </is>
-      </c>
-      <c r="C255" t="n">
-        <v>2</v>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>destockage-exterieur</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>Vallois (groupe Spie batignolles paysage) — agence Val de Seine</t>
-        </is>
-      </c>
-      <c r="F255" t="inlineStr">
-        <is>
-          <t>Val-de-Reuil (27100, Z.A la Comminière) — agence IDF à Trapp</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H255" t="inlineStr">
-        <is>
-          <t>Confirmée : « aménagements paysagers » dans le Grand Ouest, société de Spie batignolles paysage (vérifié sur la page d'accueil) ; la page contact confirme l'agence Val de Seine à V…</t>
-        </is>
-      </c>
-      <c r="I255" t="inlineStr">
-        <is>
-          <t>https://www.vallois.eu/</t>
-        </is>
-      </c>
-      <c r="J255" t="inlineStr">
-        <is>
-          <t>02 32 40 32 30 (Val de Seine) ; 01 30 16 07 00 (IDF Trappes)</t>
-        </is>
-      </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>Recherche Claude (26/10)</t>
-        </is>
-      </c>
-      <c r="L255" s="32" t="inlineStr">
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Négoce pierre</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>MasterPierre Caen</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Mondeville (14)</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Normandie</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>Négoce pierre</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>02 31 52 42 77</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Croisement fichier (26/10)</t>
+        </is>
+      </c>
+      <c r="L266" s="32" t="inlineStr">
         <is>
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N255" t="inlineStr">
-        <is>
-          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="O255" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment destockage-exterieur). Confirmée : « aménagements paysagers » dans le Grand Ouest, société de Spie batignolles paysage (vérifié sur la page d'accueil) ; la page contact confirme l'agence Val de Seine à Val-de-Reuil 27100 et l'agence IDF à Trappes 78190. E-mail lu textuellement dans la fiche « Agence Val de Seine » de la page contact ; les deux téléphones y figurent aussi textuellement. Précision : la page contact donne comme siège social de Spie batignolles paysage Nanterre (92) et comme siège administratif St Hymer (14) ; Mirville (76210) est l'adresse de l'agence de l'Estuaire, pas du siège. Hors liste d'exclusion. Candidat solide. Source e-mail : https://www.vallois.eu/contact.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q255" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R255" t="inlineStr">
-        <is>
-          <t>agence-valdeseine@vallois.eu</t>
-        </is>
-      </c>
-    </row>
-    <row r="256" ht="15" customHeight="1" s="33">
-      <c r="A256" t="n">
-        <v>256</v>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>5e liste — recherche (26/10)</t>
-        </is>
-      </c>
-      <c r="C256" t="n">
-        <v>1</v>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>destockage-exterieur</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>Tricycle Environnement / Bâticycle</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>Gennevilliers (120 rue du Moulin de Cage, 92230)</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>Confirmée : « Matériaux BTP d'occasion », « Réemploi de matériaux de second œuvre », « Curage de bâtiment » — réemploi/revente de matériaux de construction, vérifié sur le site off…</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>https://www.tricycle-environnement.fr/</t>
-        </is>
-      </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>07 60 62 41 36</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t>Recherche Claude (26/10)</t>
-        </is>
-      </c>
-      <c r="L256" s="32" t="inlineStr">
-        <is>
-          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
-        </is>
-      </c>
-      <c r="N256" t="inlineStr">
-        <is>
-          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="O256" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment destockage-exterieur). Confirmée : « Matériaux BTP d'occasion », « Réemploi de matériaux de second œuvre », « Curage de bâtiment » — réemploi/revente de matériaux de construction, vérifié sur le site officiel. E-mail lu textuellement en en-tête ET en pied de page ; téléphone confirmé sous deux formats (+33 7 60 62 41 36 / 07 60 62 41 36) ; adresse 120 rue du Moulin de Cage, 92230 Gennevilliers confirmée en pied de page — la ville même du stock. Hors liste d'exclusion. Candidat solide. Source e-mail : https://www.tricycle-environnement.fr/.  📍 Même ville que le dépôt (Gennevilliers) — réemploi : bon candidat reprise de lot. NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q256" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R256" t="inlineStr">
-        <is>
-          <t>contact@tri-cycle.fr</t>
-        </is>
-      </c>
-    </row>
-    <row r="257" ht="15" customHeight="1" s="33">
-      <c r="A257" t="n">
-        <v>257</v>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>5e liste — recherche (26/10)</t>
-        </is>
-      </c>
-      <c r="C257" t="n">
-        <v>2</v>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>destockage-exterieur</t>
-        </is>
-      </c>
-      <c r="E257" t="inlineStr">
-        <is>
-          <t>Minéka</t>
-        </is>
-      </c>
-      <c r="F257" t="inlineStr">
-        <is>
-          <t>Villeurbanne (182 rue de la Poudrette, 69100)</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>Confirmée : adresse « 182 rue de la Poudrette 69100 VILLEURBANNE » vérifiée dans les mentions légales, qui mentionnent aussi le magasin « Minéstock » (« Venez nous voir au Minéstoc…</t>
-        </is>
-      </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>https://mineka.fr/</t>
-        </is>
-      </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>Recherche Claude (26/10)</t>
-        </is>
-      </c>
-      <c r="L257" s="32" t="inlineStr">
-        <is>
-          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
-        </is>
-      </c>
-      <c r="N257" t="inlineStr">
-        <is>
-          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="O257" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment destockage-exterieur). Confirmée : adresse « 182 rue de la Poudrette 69100 VILLEURBANNE » vérifiée dans les mentions légales, qui mentionnent aussi le magasin « Minéstock » (« Venez nous voir au Minéstock ») — structure de collecte/revente avec point de vente physique, pas une pure marketplace. E-mail lu textuellement dans les mentions légales (« Adresse électronique : contact@mineka.fr »), seule adresse de la page. AUCUN téléphone publié : le contact ne pourra se faire que par e-mail (vérifié). En France (Lyon/Villeurbanne) ; limite logistique : loin des stocks de Vernon/Gennevilliers, retrait à organiser. Hors liste d'exclusion. Source e-mail : https://mineka.fr/mentions-legales/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q257" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R257" t="inlineStr">
-        <is>
-          <t>contact@mineka.fr</t>
-        </is>
-      </c>
-    </row>
-    <row r="258" ht="15" customHeight="1" s="33">
-      <c r="A258" t="n">
-        <v>258</v>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>5e liste — recherche (26/10)</t>
-        </is>
-      </c>
-      <c r="C258" t="n">
-        <v>2</v>
-      </c>
-      <c r="D258" t="inlineStr">
-        <is>
-          <t>destockage-exterieur</t>
-        </is>
-      </c>
-      <c r="E258" t="inlineStr">
-        <is>
-          <t>Pinson Paysage (groupe Osmaïa)</t>
-        </is>
-      </c>
-      <c r="F258" t="inlineStr">
-        <is>
-          <t>Andilly (13 avenue des Cures, 95580)</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>Confirmée : page « Nous contacter » vérifiée — siège « 13 Avenue des Cures, 95580 Andilly » ; activités « Création », « Entretien » (espaces verts) et « Génie écologique » affichée…</t>
-        </is>
-      </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>https://www.pinson-paysage.com/</t>
-        </is>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>Recherche Claude (26/10)</t>
-        </is>
-      </c>
-      <c r="L258" s="32" t="inlineStr">
-        <is>
-          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
-        </is>
-      </c>
-      <c r="N258" t="inlineStr">
-        <is>
-          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="O258" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment destockage-exterieur). Confirmée : page « Nous contacter » vérifiée — siège « 13 Avenue des Cures, 95580 Andilly » ; activités « Création », « Entretien » (espaces verts) et « Génie écologique » affichées, cohérentes avec une entreprise paysagère IDF. E-mail lu textuellement (seule adresse de la page). AUCUN téléphone sur la page contact (formulaire uniquement) : contact par e-mail vérifié. Réserve maintenue : le site met en avant le végétal/génie écologique plus que la maçonnerie minérale — pertinence segment (b) à pondérer. Hors liste d'exclusion. Source e-mail : https://www.pinson-paysage.com/nous-contacter/.  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q258" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R258" t="inlineStr">
-        <is>
-          <t>pinson@pinson-paysage.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="259" ht="15" customHeight="1" s="33">
-      <c r="A259" t="n">
-        <v>259</v>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>5e liste — recherche (26/10)</t>
-        </is>
-      </c>
-      <c r="C259" t="n">
-        <v>1</v>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>destockage-exterieur</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>NOZ (centrale d'achat S.F.N.)</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>Saint-Berthevin (53940)</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Confirmée : page contact vérifiée — adresse « 53940 Saint-Berthevin – France », formulaire avec champ « Vous êtes ? » incluant « Je suis un fournisseur » et objet « Besoin de désto…</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>https://www.noz.fr/</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>02 43 01 53 54</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>Recherche Claude (26/10)</t>
-        </is>
-      </c>
-      <c r="L259" s="32" t="inlineStr">
-        <is>
-          <t>À contacter (formulaire/tél) — EN ATTENTE</t>
-        </is>
-      </c>
-      <c r="N259" t="inlineStr">
-        <is>
-          <t>NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="O259" t="inlineStr">
-        <is>
-          <t>[26/10] Recherche vérifiée (segment destockage-exterieur). Confirmée : page contact vérifiée — adresse « 53940 Saint-Berthevin – France », formulaire avec champ « Vous êtes ? » incluant « Je suis un fournisseur » et objet « Besoin de déstockage », cohérent avec l'activité de rachat de surstocks/lots. RETENU SANS E-MAIL : aucun e-mail publié sur https://www.noz.fr/contactez-nous/ (revérifié le 26/10/2026 — le seul mot « Email » est un champ de formulaire), mais le téléphone 02 43 01 53 54 y est écrit textuellement et vérifié ; contact via ce numéro ou le formulaire fournisseur « Besoin de déstockage ». Hors liste d'exclusion. Réserve : lot minéral lourd atypique dans leur mix. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi</t>
-        </is>
-      </c>
-      <c r="Q259" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="260" ht="15" customHeight="1" s="33">
-      <c r="L260" s="32" t="n"/>
-      <c r="Q260" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="261" ht="15" customHeight="1" s="33">
-      <c r="L261" s="32" t="n"/>
-      <c r="Q261" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="262" ht="15" customHeight="1" s="33">
-      <c r="L262" s="32" t="n"/>
-      <c r="Q262" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="263" ht="15" customHeight="1" s="33">
-      <c r="L263" s="32" t="n"/>
-      <c r="Q263" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="264" ht="15" customHeight="1" s="33">
-      <c r="L264" s="32" t="n"/>
-      <c r="Q264" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="265" ht="15" customHeight="1" s="33">
-      <c r="L265" s="32" t="n"/>
-      <c r="Q265" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="266" ht="15" customHeight="1" s="33">
-      <c r="L266" s="32" t="n"/>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>[26/10 croisement fichier propriétaire] Apporté par le fichier propriétaire du 26/10 (origine « Recherche 31 » de son côté). E-mail à re-vérifier sur site officiel avant envoi. ⚠️ Domaine masterpierre.com déjà croisé dans nos sources : vérifier l'historique avant envoi. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
       <c r="Q266" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>caen@masterpierre.com</t>
+        </is>
       </c>
     </row>
     <row r="267" ht="15" customHeight="1" s="33">

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -5963,7 +5963,7 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="R72" s="32" t="inlineStr">
         <is>
           <t>contact@la-roche-taillee.fr</t>
         </is>
@@ -15957,7 +15957,7 @@
       </c>
       <c r="O219" s="32" t="inlineStr">
         <is>
-          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi. Pas d'e-mail publié : téléphone. NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi</t>
+          <t>[26/10] Relais assistant tiers du 26/10 (dédupliqué Gmail/Contacts) — e-mail « vérifié » par le relais, à re-confirmer sur site officiel avant envoi. Pas d'e-mail publié : téléphone. NE RIEN ENVOYER (ordre du 26/10) — vérifier d'abord l'expéditeur réel info@pierredegypte.online (Network Solutions), puis re-vérifier l'e-mail sur le site officiel avant tout envoi [26/10 relevé revendeurs] Angle revendeur confirmé : importateur de pierre depuis 1972, à ~30 min du stock de Gennevilliers, achète en lot — cible « Revendeurs à 35 € » (revente au détail plus chère). Jamais contacté.</t>
         </is>
       </c>
       <c r="Q219" s="44">
@@ -17064,7 +17064,7 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R234" t="inlineStr">
+      <c r="R234" s="32" t="inlineStr">
         <is>
           <t>contactgnps26@gmail.com</t>
         </is>
@@ -17516,7 +17516,7 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R240" t="inlineStr">
+      <c r="R240" s="32" t="inlineStr">
         <is>
           <t>contact@marbre-import.fr</t>
         </is>
@@ -18776,7 +18776,7 @@
           <t>https://mineka.fr/</t>
         </is>
       </c>
-      <c r="J257" t="inlineStr">
+      <c r="J257" s="32" t="inlineStr">
         <is>
           <t>04 78 52 86 28</t>
         </is>
@@ -18853,7 +18853,7 @@
           <t>https://www.pinson-paysage.com/</t>
         </is>
       </c>
-      <c r="J258" t="inlineStr">
+      <c r="J258" s="32" t="inlineStr">
         <is>
           <t>01 34 16 61 01</t>
         </is>
@@ -18959,55 +18959,55 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R259" t="inlineStr">
+      <c r="R259" s="32" t="inlineStr">
         <is>
           <t>noz@noz.fr</t>
         </is>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1" s="33">
-      <c r="A260" t="n">
+      <c r="A260" s="32" t="n">
         <v>260</v>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B260" s="32" t="inlineStr">
         <is>
           <t>5e liste — croisement (26/10)</t>
         </is>
       </c>
-      <c r="C260" t="n">
+      <c r="C260" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D260" t="inlineStr">
+      <c r="D260" s="32" t="inlineStr">
         <is>
           <t>Marbrerie / pierre</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
+      <c r="E260" s="32" t="inlineStr">
         <is>
           <t>ILDEI</t>
         </is>
       </c>
-      <c r="F260" t="inlineStr">
+      <c r="F260" s="32" t="inlineStr">
         <is>
           <t>Le Plessis-Pâté (91)</t>
         </is>
       </c>
-      <c r="G260" t="inlineStr">
+      <c r="G260" s="32" t="inlineStr">
         <is>
           <t>Île-de-France</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr">
+      <c r="H260" s="32" t="inlineStr">
         <is>
           <t>Marbrerie / pierre</t>
         </is>
       </c>
-      <c r="J260" t="inlineStr">
+      <c r="J260" s="32" t="inlineStr">
         <is>
           <t>01 60 84 11 00</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr">
+      <c r="K260" s="32" t="inlineStr">
         <is>
           <t>Croisement fichier (26/10)</t>
         </is>
@@ -19017,12 +19017,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N260" t="inlineStr">
+      <c r="N260" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
       </c>
-      <c r="O260" t="inlineStr">
+      <c r="O260" s="32" t="inlineStr">
         <is>
           <t>[26/10 croisement fichier propriétaire] Apporté par le fichier propriétaire du 26/10 (origine « Recherche 31 » de son côté). E-mail à re-vérifier sur site officiel avant envoi. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
@@ -19031,55 +19031,55 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R260" t="inlineStr">
+      <c r="R260" s="32" t="inlineStr">
         <is>
           <t>contact@ildei.com</t>
         </is>
       </c>
     </row>
     <row r="261" ht="15" customHeight="1" s="33">
-      <c r="A261" t="n">
+      <c r="A261" s="32" t="n">
         <v>261</v>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B261" s="32" t="inlineStr">
         <is>
           <t>5e liste — croisement (26/10)</t>
         </is>
       </c>
-      <c r="C261" t="n">
+      <c r="C261" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D261" t="inlineStr">
+      <c r="D261" s="32" t="inlineStr">
         <is>
           <t>Marbrerie</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
+      <c r="E261" s="32" t="inlineStr">
         <is>
           <t>La Marbrerie Contemporaine</t>
         </is>
       </c>
-      <c r="F261" t="inlineStr">
+      <c r="F261" s="32" t="inlineStr">
         <is>
           <t>Bagnolet (93)</t>
         </is>
       </c>
-      <c r="G261" t="inlineStr">
+      <c r="G261" s="32" t="inlineStr">
         <is>
           <t>Île-de-France</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
+      <c r="H261" s="32" t="inlineStr">
         <is>
           <t>Marbrerie</t>
         </is>
       </c>
-      <c r="J261" t="inlineStr">
+      <c r="J261" s="32" t="inlineStr">
         <is>
           <t>01 48 97 00 13</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr">
+      <c r="K261" s="32" t="inlineStr">
         <is>
           <t>Croisement fichier (26/10)</t>
         </is>
@@ -19089,12 +19089,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N261" t="inlineStr">
+      <c r="N261" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
       </c>
-      <c r="O261" t="inlineStr">
+      <c r="O261" s="32" t="inlineStr">
         <is>
           <t>[26/10 croisement fichier propriétaire] Apporté par le fichier propriétaire du 26/10 (origine « Recherche 31 » de son côté). E-mail à re-vérifier sur site officiel avant envoi. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
@@ -19103,55 +19103,55 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R261" t="inlineStr">
+      <c r="R261" s="32" t="inlineStr">
         <is>
           <t>contact@la-marbrerie-contemporaine.fr</t>
         </is>
       </c>
     </row>
     <row r="262" ht="15" customHeight="1" s="33">
-      <c r="A262" t="n">
+      <c r="A262" s="32" t="n">
         <v>262</v>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B262" s="32" t="inlineStr">
         <is>
           <t>5e liste — croisement (26/10)</t>
         </is>
       </c>
-      <c r="C262" t="n">
+      <c r="C262" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D262" t="inlineStr">
+      <c r="D262" s="32" t="inlineStr">
         <is>
           <t>Marbrerie / négoce pierre</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
+      <c r="E262" s="32" t="inlineStr">
         <is>
           <t>Paris Roches</t>
         </is>
       </c>
-      <c r="F262" t="inlineStr">
+      <c r="F262" s="32" t="inlineStr">
         <is>
           <t>Vitry-sur-Seine (94)</t>
         </is>
       </c>
-      <c r="G262" t="inlineStr">
+      <c r="G262" s="32" t="inlineStr">
         <is>
           <t>Île-de-France</t>
         </is>
       </c>
-      <c r="H262" t="inlineStr">
+      <c r="H262" s="32" t="inlineStr">
         <is>
           <t>Marbrerie / négoce pierre</t>
         </is>
       </c>
-      <c r="J262" t="inlineStr">
+      <c r="J262" s="32" t="inlineStr">
         <is>
           <t>01 47 26 00 99</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr">
+      <c r="K262" s="32" t="inlineStr">
         <is>
           <t>Croisement fichier (26/10)</t>
         </is>
@@ -19161,12 +19161,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N262" t="inlineStr">
+      <c r="N262" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
       </c>
-      <c r="O262" t="inlineStr">
+      <c r="O262" s="32" t="inlineStr">
         <is>
           <t>[26/10 croisement fichier propriétaire] Apporté par le fichier propriétaire du 26/10 (origine « Recherche 31 » de son côté). E-mail à re-vérifier sur site officiel avant envoi. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
@@ -19175,55 +19175,55 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R262" t="inlineStr">
+      <c r="R262" s="32" t="inlineStr">
         <is>
           <t>paris-roches@orange.fr</t>
         </is>
       </c>
     </row>
     <row r="263" ht="15" customHeight="1" s="33">
-      <c r="A263" t="n">
+      <c r="A263" s="32" t="n">
         <v>263</v>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B263" s="32" t="inlineStr">
         <is>
           <t>5e liste — croisement (26/10)</t>
         </is>
       </c>
-      <c r="C263" t="n">
+      <c r="C263" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D263" t="inlineStr">
+      <c r="D263" s="32" t="inlineStr">
         <is>
           <t>Marbrerie</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
+      <c r="E263" s="32" t="inlineStr">
         <is>
           <t>Alpha Marbre</t>
         </is>
       </c>
-      <c r="F263" t="inlineStr">
+      <c r="F263" s="32" t="inlineStr">
         <is>
           <t>Coubert (77)</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
+      <c r="G263" s="32" t="inlineStr">
         <is>
           <t>Île-de-France</t>
         </is>
       </c>
-      <c r="H263" t="inlineStr">
+      <c r="H263" s="32" t="inlineStr">
         <is>
           <t>Marbrerie</t>
         </is>
       </c>
-      <c r="J263" t="inlineStr">
+      <c r="J263" s="32" t="inlineStr">
         <is>
           <t>01 64 16 03 69</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr">
+      <c r="K263" s="32" t="inlineStr">
         <is>
           <t>Croisement fichier (26/10)</t>
         </is>
@@ -19233,12 +19233,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N263" t="inlineStr">
+      <c r="N263" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
       </c>
-      <c r="O263" t="inlineStr">
+      <c r="O263" s="32" t="inlineStr">
         <is>
           <t>[26/10 croisement fichier propriétaire] Apporté par le fichier propriétaire du 26/10 (origine « Recherche 31 » de son côté). E-mail à re-vérifier sur site officiel avant envoi. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
@@ -19247,55 +19247,55 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R263" t="inlineStr">
+      <c r="R263" s="32" t="inlineStr">
         <is>
           <t>alpha.marbre@laposte.net</t>
         </is>
       </c>
     </row>
     <row r="264" ht="15" customHeight="1" s="33">
-      <c r="A264" t="n">
+      <c r="A264" s="32" t="n">
         <v>264</v>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B264" s="32" t="inlineStr">
         <is>
           <t>5e liste — croisement (26/10)</t>
         </is>
       </c>
-      <c r="C264" t="n">
+      <c r="C264" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D264" t="inlineStr">
+      <c r="D264" s="32" t="inlineStr">
         <is>
           <t>Marbrerie</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
+      <c r="E264" s="32" t="inlineStr">
         <is>
           <t>Marbrerie Christian Caudron</t>
         </is>
       </c>
-      <c r="F264" t="inlineStr">
+      <c r="F264" s="32" t="inlineStr">
         <is>
           <t>Noisy-le-Sec (93)</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr">
+      <c r="G264" s="32" t="inlineStr">
         <is>
           <t>Île-de-France</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
+      <c r="H264" s="32" t="inlineStr">
         <is>
           <t>Marbrerie</t>
         </is>
       </c>
-      <c r="J264" t="inlineStr">
+      <c r="J264" s="32" t="inlineStr">
         <is>
           <t>06 30 60 75 01</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr">
+      <c r="K264" s="32" t="inlineStr">
         <is>
           <t>Croisement fichier (26/10)</t>
         </is>
@@ -19305,12 +19305,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N264" t="inlineStr">
+      <c r="N264" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
       </c>
-      <c r="O264" t="inlineStr">
+      <c r="O264" s="32" t="inlineStr">
         <is>
           <t>[26/10 croisement fichier propriétaire] Apporté par le fichier propriétaire du 26/10 (origine « Recherche 31 » de son côté). E-mail à re-vérifier sur site officiel avant envoi. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
@@ -19319,50 +19319,50 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R264" t="inlineStr">
+      <c r="R264" s="32" t="inlineStr">
         <is>
           <t>atelier-marbre@orange.fr</t>
         </is>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1" s="33">
-      <c r="A265" t="n">
+      <c r="A265" s="32" t="n">
         <v>265</v>
       </c>
-      <c r="B265" t="inlineStr">
+      <c r="B265" s="32" t="inlineStr">
         <is>
           <t>5e liste — croisement (26/10)</t>
         </is>
       </c>
-      <c r="C265" t="n">
+      <c r="C265" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D265" t="inlineStr">
+      <c r="D265" s="32" t="inlineStr">
         <is>
           <t>Négoce matériaux</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr">
+      <c r="E265" s="32" t="inlineStr">
         <is>
           <t>Facomat</t>
         </is>
       </c>
-      <c r="F265" t="inlineStr">
+      <c r="F265" s="32" t="inlineStr">
         <is>
           <t>Buchy (76)</t>
         </is>
       </c>
-      <c r="G265" t="inlineStr">
+      <c r="G265" s="32" t="inlineStr">
         <is>
           <t>Normandie</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
+      <c r="H265" s="32" t="inlineStr">
         <is>
           <t>Négoce matériaux</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr">
+      <c r="K265" s="32" t="inlineStr">
         <is>
           <t>Croisement fichier (26/10)</t>
         </is>
@@ -19372,12 +19372,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N265" t="inlineStr">
+      <c r="N265" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
       </c>
-      <c r="O265" t="inlineStr">
+      <c r="O265" s="32" t="inlineStr">
         <is>
           <t>[26/10 croisement fichier propriétaire] Apporté par le fichier propriétaire du 26/10 (origine « Recherche 31 » de son côté). E-mail à re-vérifier sur site officiel avant envoi. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
@@ -19386,55 +19386,55 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R265" t="inlineStr">
+      <c r="R265" s="32" t="inlineStr">
         <is>
           <t>facomat76@wanadoo.fr</t>
         </is>
       </c>
     </row>
     <row r="266" ht="15" customHeight="1" s="33">
-      <c r="A266" t="n">
+      <c r="A266" s="32" t="n">
         <v>266</v>
       </c>
-      <c r="B266" t="inlineStr">
+      <c r="B266" s="32" t="inlineStr">
         <is>
           <t>5e liste — croisement (26/10)</t>
         </is>
       </c>
-      <c r="C266" t="n">
+      <c r="C266" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D266" t="inlineStr">
+      <c r="D266" s="32" t="inlineStr">
         <is>
           <t>Négoce pierre</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr">
+      <c r="E266" s="32" t="inlineStr">
         <is>
           <t>MasterPierre Caen</t>
         </is>
       </c>
-      <c r="F266" t="inlineStr">
+      <c r="F266" s="32" t="inlineStr">
         <is>
           <t>Mondeville (14)</t>
         </is>
       </c>
-      <c r="G266" t="inlineStr">
+      <c r="G266" s="32" t="inlineStr">
         <is>
           <t>Normandie</t>
         </is>
       </c>
-      <c r="H266" t="inlineStr">
+      <c r="H266" s="32" t="inlineStr">
         <is>
           <t>Négoce pierre</t>
         </is>
       </c>
-      <c r="J266" t="inlineStr">
+      <c r="J266" s="32" t="inlineStr">
         <is>
           <t>02 31 52 42 77</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr">
+      <c r="K266" s="32" t="inlineStr">
         <is>
           <t>Croisement fichier (26/10)</t>
         </is>
@@ -19444,12 +19444,12 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N266" t="inlineStr">
+      <c r="N266" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
       </c>
-      <c r="O266" t="inlineStr">
+      <c r="O266" s="32" t="inlineStr">
         <is>
           <t>[26/10 croisement fichier propriétaire] Apporté par le fichier propriétaire du 26/10 (origine « Recherche 31 » de son côté). E-mail à re-vérifier sur site officiel avant envoi. ⚠️ Domaine masterpierre.com déjà croisé dans nos sources : vérifier l'historique avant envoi. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
@@ -19458,7 +19458,7 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R266" t="inlineStr">
+      <c r="R266" s="32" t="inlineStr">
         <is>
           <t>caen@masterpierre.com</t>
         </is>

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -16831,7 +16831,7 @@
       </c>
       <c r="O231" s="32" t="inlineStr">
         <is>
-          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : spécialiste pierre naturelle (travertin, calcaire, marbre, granit...), 7 magasins France/Allemagne dont Lyon, Strasbourg, Nancy, Beaune, Thionville. Mentions légales : Pierre de l'Est SAS, 44 Rue de Nancy, 57915 Woustviller — raison sociale et ville confirmées. AUCUN e-mail publié : vérifié sur l'accueil et les mentions légales (contact par téléphone ou formulaire uniquement). Repli téléphone VÉRIFIÉ : 03 60 12 33 53 affiché sur l'accueil (« Conseil d'expert ») et dans les mentions légales. Le produit Sinai Pearl n'était pas visible sur la portion d'accueil lue, mais l'activité calcaire/travertin est confirmée. Domaine hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi [26/10 croisement fichier propriétaire] 2e téléphone (fichier) : 03 87 98 67 37.</t>
+          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : spécialiste pierre naturelle (travertin, calcaire, marbre, granit...), 7 magasins France/Allemagne dont Lyon, Strasbourg, Nancy, Beaune, Thionville. Mentions légales : Pierre de l'Est SAS, 44 Rue de Nancy, 57915 Woustviller — raison sociale et ville confirmées. AUCUN e-mail publié : vérifié sur l'accueil et les mentions légales (contact par téléphone ou formulaire uniquement). Repli téléphone VÉRIFIÉ : 03 60 12 33 53 affiché sur l'accueil (« Conseil d'expert ») et dans les mentions légales. Le produit Sinai Pearl n'était pas visible sur la portion d'accueil lue, mais l'activité calcaire/travertin est confirmée. Domaine hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi [26/10 croisement fichier propriétaire] 2e téléphone (fichier) : 03 87 98 67 37. [26/10 vérifié] Vend le Sinaï Pearl (calcaire égyptien) ~60,90 €/m² TTC → marge brute +25,90 €/m² à 35 €. Showrooms Est : Bischheim/Strasbourg, Thionville, Champigneulles, Givors, Ladoix-Serrigny, Woustviller. 3e tél relevé : 03 60 12 33 53. NB : la fiche « Cubik Minéral Outdoor » (Sélestat) du relevé est une société fantôme — introuvable au registre national ; le vrai vendeur de Sinaï Pearl dans l'Est, c'est cette fiche-ci.</t>
         </is>
       </c>
       <c r="Q231" s="44">
@@ -19465,38 +19465,388 @@
       </c>
     </row>
     <row r="267" ht="15" customHeight="1" s="33">
-      <c r="L267" s="32" t="n"/>
+      <c r="A267" t="n">
+        <v>267</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Revendeurs à 35 € (26/10)</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>1</v>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Négoce / revendeur pierre</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>C-Négoce (Centre Négoce SARL)</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Saint-Priest (69800)</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Auvergne-Rhône-Alpes</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Revendeur vendant déjà une pierre comparable plus cher.</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>https://www.c-negoce.com</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>04 72 51 77 70</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Relevé revendeurs (26/10), vérifié</t>
+        </is>
+      </c>
+      <c r="L267" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>[26/10 vérifié] Vend « marbre d'Égypte Gala » brossé 76,50 € TTC/m² (page produit officielle, réf. 005001) → marge brute +41,50 €/m² à 35 €. Importateur, NAF 46.90Z, 5 showrooms (Lyon Est, Dardilly, Dijon, Annemasse). Stock « 80 000 m² » = auto-déclaration marketing (fiche Leroy Merlin), non vérifiée. ⚠️ Site en maintenance (503) le 26/10 — prix lu sur version indexée récente, re-vérifier au retour en ligne. E-mails secondaires : contact94@ (Outdoor), dardilly@, dijon@, contact74@. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
       <c r="Q267" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>contact@c-negoce.com</t>
+        </is>
+      </c>
     </row>
     <row r="268" ht="15" customHeight="1" s="33">
-      <c r="L268" s="32" t="n"/>
+      <c r="A268" t="n">
+        <v>268</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Revendeurs à 35 € (26/10)</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>1</v>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Négoce matériaux multi-agences</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Thomas Sograma Matériaux</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Andrézieux-Bouthéon (42160)</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Auvergne-Rhône-Alpes</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Revendeur vendant déjà une pierre comparable plus cher.</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>https://www.thomas-sograma.com</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>04 77 55 21 35</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Relevé revendeurs (26/10), vérifié</t>
+        </is>
+      </c>
+      <c r="L268" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>[26/10 vérifié] Vend Crema Sinai calcaire égyptien : opus romain 2 cm à 55,57 € TTC/m² (confirmé page officielle, réf. 510001), autres variantes 1,8 cm 60,65–75,10 €. Vend aussi pierre « Kemet » (provenance Égypte) 55,26 €. Marge brute +20,57 €/m² à 35 €. Groupe Thomas Peres et Fils, 8 établissements Loire. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
       <c r="Q268" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>contact@thomas-sograma.com</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="15" customHeight="1" s="33">
-      <c r="L269" s="32" t="n"/>
+      <c r="A269" t="n">
+        <v>269</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Revendeurs à 35 € (26/10)</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>1</v>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Revendeur pierre naturelle (showroom)</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Pierres &amp; Décors (L'univers de la Pierre SASU)</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Portet-sur-Garonne (31120)</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Occitanie</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Revendeur vendant déjà une pierre comparable plus cher.</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>https://pierres-decors.com</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>09 84 40 18 41 / 07 67 89 52 78</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Relevé revendeurs (26/10), vérifié</t>
+        </is>
+      </c>
+      <c r="L269" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>[26/10 vérifié] Catégorie « Pierres d'Égypte » : dallages pierre du Sinaï (KEROS, SAHARA) à partir de 50 €/m², grands formats à partir de 89 €/m² (confirmé pages officielles). Marge brute +15 à +54 €/m² à 35 €. SIREN 799 580 188, Toulouse. ⚠️ Ne pas confondre avec « Pierres et Décors » de Royan (autre société). NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
       <c r="Q269" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>contact@pierres-decors.com</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="15" customHeight="1" s="33">
-      <c r="L270" s="32" t="n"/>
+      <c r="A270" t="n">
+        <v>270</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Revendeurs à 35 € (26/10)</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>3</v>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Atelier-producteur pierre + boutique en ligne</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>La Maison des Cailloux</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Capvern (65130)</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Occitanie</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Revendeur vendant déjà une pierre comparable plus cher.</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>https://www.lamaisondescailloux.com</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>05 62 98 11 97</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Relevé revendeurs (26/10), vérifié</t>
+        </is>
+      </c>
+      <c r="L270" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>[26/10 vérifié] ⚠️ Angle marge FRAGILE : pas un pur revendeur (atelier-producteur pyrénéen, marbres Sarrancolin) ; son calcaire du Causse est à 60–80 €/m² mais son travertin import est à 29–30 €/m², DÉJÀ SOUS nos 35 €. Aucune pierre d'Égypte au catalogue. ~800 km de Gennevilliers, transport à chiffrer. SIREN 423 325 000. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
       <c r="Q270" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>contact@lamaisondescailloux.com</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="15" customHeight="1" s="33">
-      <c r="L271" s="32" t="n"/>
+      <c r="A271" t="n">
+        <v>271</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Revendeurs à 35 € (26/10)</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>3</v>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Négoce gros matériaux / vente en ligne</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Carrelage Market (Vente Pierre Naturelle.com SAS)</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Puget-sur-Argens (83480)</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>PACA</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Revendeur vendant déjà une pierre comparable plus cher.</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>https://www.carrelage-market.com</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>06 51 49 72 78</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Relevé revendeurs (26/10), vérifié</t>
+        </is>
+      </c>
+      <c r="L271" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>[26/10 vérifié] ⚠️ Marge annoncée (48 €/m²) NON retrouvée : leur seul Sinaï en ligne est un déstockage à ≈35,12 €/m² TTC (lot 41 m² à 1 440 €), quasiment notre prix. Argument marge inopérant tant que ce lot est affiché. SIREN 537 699 506, NAF 46.73A, siège Cannes, showroom Var. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
       <c r="Q271" s="44">
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>info@carrelage-market.com</t>
+        </is>
       </c>
     </row>
     <row r="272" ht="15" customHeight="1" s="33">

--- a/minyala/prospects-minyala.xlsx
+++ b/minyala/prospects-minyala.xlsx
@@ -16831,7 +16831,7 @@
       </c>
       <c r="O231" s="32" t="inlineStr">
         <is>
-          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : spécialiste pierre naturelle (travertin, calcaire, marbre, granit...), 7 magasins France/Allemagne dont Lyon, Strasbourg, Nancy, Beaune, Thionville. Mentions légales : Pierre de l'Est SAS, 44 Rue de Nancy, 57915 Woustviller — raison sociale et ville confirmées. AUCUN e-mail publié : vérifié sur l'accueil et les mentions légales (contact par téléphone ou formulaire uniquement). Repli téléphone VÉRIFIÉ : 03 60 12 33 53 affiché sur l'accueil (« Conseil d'expert ») et dans les mentions légales. Le produit Sinai Pearl n'était pas visible sur la portion d'accueil lue, mais l'activité calcaire/travertin est confirmée. Domaine hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi [26/10 croisement fichier propriétaire] 2e téléphone (fichier) : 03 87 98 67 37. [26/10 vérifié] Vend le Sinaï Pearl (calcaire égyptien) ~60,90 €/m² TTC → marge brute +25,90 €/m² à 35 €. Showrooms Est : Bischheim/Strasbourg, Thionville, Champigneulles, Givors, Ladoix-Serrigny, Woustviller. 3e tél relevé : 03 60 12 33 53. NB : la fiche « Cubik Minéral Outdoor » (Sélestat) du relevé est une société fantôme — introuvable au registre national ; le vrai vendeur de Sinaï Pearl dans l'Est, c'est cette fiche-ci.</t>
+          <t>[26/10] Recherche vérifiée (segment importateurs). Confirmée : spécialiste pierre naturelle (travertin, calcaire, marbre, granit...), 7 magasins France/Allemagne dont Lyon, Strasbourg, Nancy, Beaune, Thionville. Mentions légales : Pierre de l'Est SAS, 44 Rue de Nancy, 57915 Woustviller — raison sociale et ville confirmées. AUCUN e-mail publié : vérifié sur l'accueil et les mentions légales (contact par téléphone ou formulaire uniquement). Repli téléphone VÉRIFIÉ : 03 60 12 33 53 affiché sur l'accueil (« Conseil d'expert ») et dans les mentions légales. Le produit Sinai Pearl n'était pas visible sur la portion d'accueil lue, mais l'activité calcaire/travertin est confirmée. Domaine hors liste d'exclusion. Source e-mail : aucune (pas d e-mail publié).  NE RIEN ENVOYER (ordre du 26/10) — vérification expéditeur info@pierredegypte.online préalable à tout envoi [26/10 croisement fichier propriétaire] 2e téléphone (fichier) : 03 87 98 67 37. [26/10 vérifié] Vend le Sinaï Pearl (calcaire égyptien) ~60,90 €/m² TTC → écart de prix affiché de +25,90 €/m² à 35 €. Showrooms Est : Bischheim/Strasbourg, Thionville, Champigneulles, Givors, Ladoix-Serrigny, Woustviller. 3e tél relevé : 03 60 12 33 53. NB : la fiche « Cubik Minéral Outdoor » (Sélestat) du relevé n'a pas été identifiée le 26/10 (registre national + web) — à écarter tant que son existence n'est pas établie ; le vrai vendeur de Sinaï Pearl dans l'Est, c'est cette fiche-ci. [27/10] ⚠️ DIVERGENCE PRIX à rapprocher avant tout appel : notre bilan de veille du 26/10 donne SINAI PEARL vieilli 60×40×2 à 48,50 €/m² TTC ; la lecture du 26/10 soir donnait ~60,90 € (référence/finition possiblement différente). Ne citer AUCUN prix Minéral tant que non tranché.</t>
         </is>
       </c>
       <c r="Q231" s="44">
@@ -19465,53 +19465,53 @@
       </c>
     </row>
     <row r="267" ht="15" customHeight="1" s="33">
-      <c r="A267" t="n">
+      <c r="A267" s="32" t="n">
         <v>267</v>
       </c>
-      <c r="B267" t="inlineStr">
+      <c r="B267" s="32" t="inlineStr">
         <is>
           <t>Revendeurs à 35 € (26/10)</t>
         </is>
       </c>
-      <c r="C267" t="n">
+      <c r="C267" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D267" t="inlineStr">
+      <c r="D267" s="32" t="inlineStr">
         <is>
           <t>Négoce / revendeur pierre</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr">
+      <c r="E267" s="32" t="inlineStr">
         <is>
           <t>C-Négoce (Centre Négoce SARL)</t>
         </is>
       </c>
-      <c r="F267" t="inlineStr">
+      <c r="F267" s="32" t="inlineStr">
         <is>
           <t>Saint-Priest (69800)</t>
         </is>
       </c>
-      <c r="G267" t="inlineStr">
+      <c r="G267" s="32" t="inlineStr">
         <is>
           <t>Auvergne-Rhône-Alpes</t>
         </is>
       </c>
-      <c r="H267" t="inlineStr">
+      <c r="H267" s="32" t="inlineStr">
         <is>
           <t>Revendeur vendant déjà une pierre comparable plus cher.</t>
         </is>
       </c>
-      <c r="I267" t="inlineStr">
+      <c r="I267" s="32" t="inlineStr">
         <is>
           <t>https://www.c-negoce.com</t>
         </is>
       </c>
-      <c r="J267" t="inlineStr">
+      <c r="J267" s="32" t="inlineStr">
         <is>
           <t>04 72 51 77 70</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr">
+      <c r="K267" s="32" t="inlineStr">
         <is>
           <t>Relevé revendeurs (26/10), vérifié</t>
         </is>
@@ -19521,320 +19521,320 @@
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N267" t="inlineStr">
+      <c r="N267" s="32" t="inlineStr">
+        <is>
+          <t>Reconfirmer le prix Gala (site en maintenance le 26/10) avant tout envoi — puis attendre validation propriétaire. NE RIEN ENVOYER d'ici là.</t>
+        </is>
+      </c>
+      <c r="O267" s="32" t="inlineStr">
+        <is>
+          <t>[26/10 vérifié] Vend « marbre d'Égypte Gala » brossé 76,50 € TTC/m² (page produit officielle, réf. 005001) → écart de prix affiché de +41,50 €/m² à 35 €. Importateur, NAF 46.90Z, 5 showrooms (Lyon Est, Dardilly, Dijon, Annemasse). Stock « 80 000 m² » = auto-déclaration marketing (fiche Leroy Merlin), non vérifiée. ⚠️ Site en maintenance (503) le 26/10 — prix lu sur version indexée récente, re-vérifier au retour en ligne. E-mails secondaires : contact94@ (Outdoor), dardilly@, dijon@, contact74@. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="Q267" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R267" s="32" t="inlineStr">
+        <is>
+          <t>contact@c-negoce.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="15" customHeight="1" s="33">
+      <c r="A268" s="32" t="n">
+        <v>268</v>
+      </c>
+      <c r="B268" s="32" t="inlineStr">
+        <is>
+          <t>Revendeurs à 35 € (26/10)</t>
+        </is>
+      </c>
+      <c r="C268" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D268" s="32" t="inlineStr">
+        <is>
+          <t>Négoce matériaux multi-agences</t>
+        </is>
+      </c>
+      <c r="E268" s="32" t="inlineStr">
+        <is>
+          <t>Thomas Sograma Matériaux</t>
+        </is>
+      </c>
+      <c r="F268" s="32" t="inlineStr">
+        <is>
+          <t>Andrézieux-Bouthéon (42160)</t>
+        </is>
+      </c>
+      <c r="G268" s="32" t="inlineStr">
+        <is>
+          <t>Auvergne-Rhône-Alpes</t>
+        </is>
+      </c>
+      <c r="H268" s="32" t="inlineStr">
+        <is>
+          <t>Revendeur vendant déjà une pierre comparable plus cher.</t>
+        </is>
+      </c>
+      <c r="I268" s="32" t="inlineStr">
+        <is>
+          <t>https://www.thomas-sograma.com</t>
+        </is>
+      </c>
+      <c r="J268" s="32" t="inlineStr">
+        <is>
+          <t>04 77 55 21 35</t>
+        </is>
+      </c>
+      <c r="K268" s="32" t="inlineStr">
+        <is>
+          <t>Relevé revendeurs (26/10), vérifié</t>
+        </is>
+      </c>
+      <c r="L268" s="32" t="inlineStr">
+        <is>
+          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
+        </is>
+      </c>
+      <c r="N268" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
       </c>
-      <c r="O267" t="inlineStr">
-        <is>
-          <t>[26/10 vérifié] Vend « marbre d'Égypte Gala » brossé 76,50 € TTC/m² (page produit officielle, réf. 005001) → marge brute +41,50 €/m² à 35 €. Importateur, NAF 46.90Z, 5 showrooms (Lyon Est, Dardilly, Dijon, Annemasse). Stock « 80 000 m² » = auto-déclaration marketing (fiche Leroy Merlin), non vérifiée. ⚠️ Site en maintenance (503) le 26/10 — prix lu sur version indexée récente, re-vérifier au retour en ligne. E-mails secondaires : contact94@ (Outdoor), dardilly@, dijon@, contact74@. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
-        </is>
-      </c>
-      <c r="Q267" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R267" t="inlineStr">
-        <is>
-          <t>contact@c-negoce.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="268" ht="15" customHeight="1" s="33">
-      <c r="A268" t="n">
-        <v>268</v>
-      </c>
-      <c r="B268" t="inlineStr">
+      <c r="O268" s="32" t="inlineStr">
+        <is>
+          <t>[26/10 vérifié] Vend Crema Sinai calcaire égyptien : opus romain 2 cm à 55,57 € TTC/m² (confirmé page officielle, réf. 510001), autres variantes 1,8 cm 60,65–75,10 €. Vend aussi pierre « Kemet » (provenance Égypte) 55,26 €. Écart de prix affiché +20,57 €/m² à 35 €. Groupe Thomas Peres et Fils, 8 établissements Loire. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="Q268" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R268" s="32" t="inlineStr">
+        <is>
+          <t>contact@thomas-sograma.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="15" customHeight="1" s="33">
+      <c r="A269" s="32" t="n">
+        <v>269</v>
+      </c>
+      <c r="B269" s="32" t="inlineStr">
         <is>
           <t>Revendeurs à 35 € (26/10)</t>
         </is>
       </c>
-      <c r="C268" t="n">
+      <c r="C269" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>Négoce matériaux multi-agences</t>
-        </is>
-      </c>
-      <c r="E268" t="inlineStr">
-        <is>
-          <t>Thomas Sograma Matériaux</t>
-        </is>
-      </c>
-      <c r="F268" t="inlineStr">
-        <is>
-          <t>Andrézieux-Bouthéon (42160)</t>
-        </is>
-      </c>
-      <c r="G268" t="inlineStr">
-        <is>
-          <t>Auvergne-Rhône-Alpes</t>
-        </is>
-      </c>
-      <c r="H268" t="inlineStr">
+      <c r="D269" s="32" t="inlineStr">
+        <is>
+          <t>Revendeur pierre naturelle (showroom)</t>
+        </is>
+      </c>
+      <c r="E269" s="32" t="inlineStr">
+        <is>
+          <t>Pierres &amp; Décors (L'univers de la Pierre SASU)</t>
+        </is>
+      </c>
+      <c r="F269" s="32" t="inlineStr">
+        <is>
+          <t>Portet-sur-Garonne (31120)</t>
+        </is>
+      </c>
+      <c r="G269" s="32" t="inlineStr">
+        <is>
+          <t>Occitanie</t>
+        </is>
+      </c>
+      <c r="H269" s="32" t="inlineStr">
         <is>
           <t>Revendeur vendant déjà une pierre comparable plus cher.</t>
         </is>
       </c>
-      <c r="I268" t="inlineStr">
-        <is>
-          <t>https://www.thomas-sograma.com</t>
-        </is>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>04 77 55 21 35</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr">
+      <c r="I269" s="32" t="inlineStr">
+        <is>
+          <t>https://pierres-decors.com</t>
+        </is>
+      </c>
+      <c r="J269" s="32" t="inlineStr">
+        <is>
+          <t>09 84 40 18 41 / 07 67 89 52 78</t>
+        </is>
+      </c>
+      <c r="K269" s="32" t="inlineStr">
         <is>
           <t>Relevé revendeurs (26/10), vérifié</t>
         </is>
       </c>
-      <c r="L268" s="32" t="inlineStr">
+      <c r="L269" s="32" t="inlineStr">
         <is>
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N268" t="inlineStr">
+      <c r="N269" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
       </c>
-      <c r="O268" t="inlineStr">
-        <is>
-          <t>[26/10 vérifié] Vend Crema Sinai calcaire égyptien : opus romain 2 cm à 55,57 € TTC/m² (confirmé page officielle, réf. 510001), autres variantes 1,8 cm 60,65–75,10 €. Vend aussi pierre « Kemet » (provenance Égypte) 55,26 €. Marge brute +20,57 €/m² à 35 €. Groupe Thomas Peres et Fils, 8 établissements Loire. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
-        </is>
-      </c>
-      <c r="Q268" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R268" t="inlineStr">
-        <is>
-          <t>contact@thomas-sograma.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="269" ht="15" customHeight="1" s="33">
-      <c r="A269" t="n">
-        <v>269</v>
-      </c>
-      <c r="B269" t="inlineStr">
+      <c r="O269" s="32" t="inlineStr">
+        <is>
+          <t>[26/10 vérifié] Catégorie « Pierres d'Égypte » : dallages pierre du Sinaï (KEROS, SAHARA) à partir de 50 €/m², grands formats à partir de 89 €/m² (confirmé pages officielles). Écart de prix affiché +15 à +54 €/m² à 35 €. SIREN 799 580 188, Toulouse. ⚠️ Ne pas confondre avec « Pierres et Décors » de Royan (autre société). NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact [27/10] Avant envoi : confirmer identité exacte (L'univers de la Pierre, SIREN 799 580 188 — pas l'homonyme de Royan) + coût du transport IdF→31 à chiffrer avant envoi.</t>
+        </is>
+      </c>
+      <c r="Q269" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R269" s="32" t="inlineStr">
+        <is>
+          <t>contact@pierres-decors.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="15" customHeight="1" s="33">
+      <c r="A270" s="32" t="n">
+        <v>270</v>
+      </c>
+      <c r="B270" s="32" t="inlineStr">
         <is>
           <t>Revendeurs à 35 € (26/10)</t>
         </is>
       </c>
-      <c r="C269" t="n">
-        <v>1</v>
-      </c>
-      <c r="D269" t="inlineStr">
-        <is>
-          <t>Revendeur pierre naturelle (showroom)</t>
-        </is>
-      </c>
-      <c r="E269" t="inlineStr">
-        <is>
-          <t>Pierres &amp; Décors (L'univers de la Pierre SASU)</t>
-        </is>
-      </c>
-      <c r="F269" t="inlineStr">
-        <is>
-          <t>Portet-sur-Garonne (31120)</t>
-        </is>
-      </c>
-      <c r="G269" t="inlineStr">
+      <c r="C270" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D270" s="32" t="inlineStr">
+        <is>
+          <t>Atelier-producteur pierre + boutique en ligne</t>
+        </is>
+      </c>
+      <c r="E270" s="32" t="inlineStr">
+        <is>
+          <t>La Maison des Cailloux</t>
+        </is>
+      </c>
+      <c r="F270" s="32" t="inlineStr">
+        <is>
+          <t>Capvern (65130)</t>
+        </is>
+      </c>
+      <c r="G270" s="32" t="inlineStr">
         <is>
           <t>Occitanie</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr">
+      <c r="H270" s="32" t="inlineStr">
         <is>
           <t>Revendeur vendant déjà une pierre comparable plus cher.</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>https://pierres-decors.com</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>09 84 40 18 41 / 07 67 89 52 78</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr">
+      <c r="I270" s="32" t="inlineStr">
+        <is>
+          <t>https://www.lamaisondescailloux.com</t>
+        </is>
+      </c>
+      <c r="J270" s="32" t="inlineStr">
+        <is>
+          <t>05 62 98 11 97</t>
+        </is>
+      </c>
+      <c r="K270" s="32" t="inlineStr">
         <is>
           <t>Relevé revendeurs (26/10), vérifié</t>
         </is>
       </c>
-      <c r="L269" s="32" t="inlineStr">
+      <c r="L270" s="32" t="inlineStr">
         <is>
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N269" t="inlineStr">
+      <c r="N270" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
       </c>
-      <c r="O269" t="inlineStr">
-        <is>
-          <t>[26/10 vérifié] Catégorie « Pierres d'Égypte » : dallages pierre du Sinaï (KEROS, SAHARA) à partir de 50 €/m², grands formats à partir de 89 €/m² (confirmé pages officielles). Marge brute +15 à +54 €/m² à 35 €. SIREN 799 580 188, Toulouse. ⚠️ Ne pas confondre avec « Pierres et Décors » de Royan (autre société). NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
-        </is>
-      </c>
-      <c r="Q269" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R269" t="inlineStr">
-        <is>
-          <t>contact@pierres-decors.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="270" ht="15" customHeight="1" s="33">
-      <c r="A270" t="n">
-        <v>270</v>
-      </c>
-      <c r="B270" t="inlineStr">
+      <c r="O270" s="32" t="inlineStr">
+        <is>
+          <t>[26/10 vérifié] ⚠️ Angle marge FRAGILE : pas un pur revendeur (atelier-producteur pyrénéen, marbres Sarrancolin) ; son calcaire du Causse est à 60–80 €/m² mais son travertin import est à 29–30 €/m², DÉJÀ SOUS nos 35 €. Aucune pierre d'Égypte au catalogue. ~800 km de Gennevilliers, transport à chiffrer. SIREN 423 325 000. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
+        </is>
+      </c>
+      <c r="Q270" s="44">
+        <f>'Mode d''emploi'!$B$29</f>
+        <v/>
+      </c>
+      <c r="R270" s="32" t="inlineStr">
+        <is>
+          <t>contact@lamaisondescailloux.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="15" customHeight="1" s="33">
+      <c r="A271" s="32" t="n">
+        <v>271</v>
+      </c>
+      <c r="B271" s="32" t="inlineStr">
         <is>
           <t>Revendeurs à 35 € (26/10)</t>
         </is>
       </c>
-      <c r="C270" t="n">
+      <c r="C271" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="D270" t="inlineStr">
-        <is>
-          <t>Atelier-producteur pierre + boutique en ligne</t>
-        </is>
-      </c>
-      <c r="E270" t="inlineStr">
-        <is>
-          <t>La Maison des Cailloux</t>
-        </is>
-      </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>Capvern (65130)</t>
-        </is>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>Occitanie</t>
-        </is>
-      </c>
-      <c r="H270" t="inlineStr">
+      <c r="D271" s="32" t="inlineStr">
+        <is>
+          <t>Négoce gros matériaux / vente en ligne</t>
+        </is>
+      </c>
+      <c r="E271" s="32" t="inlineStr">
+        <is>
+          <t>Carrelage Market (Vente Pierre Naturelle.com SAS)</t>
+        </is>
+      </c>
+      <c r="F271" s="32" t="inlineStr">
+        <is>
+          <t>Puget-sur-Argens (83480)</t>
+        </is>
+      </c>
+      <c r="G271" s="32" t="inlineStr">
+        <is>
+          <t>PACA</t>
+        </is>
+      </c>
+      <c r="H271" s="32" t="inlineStr">
         <is>
           <t>Revendeur vendant déjà une pierre comparable plus cher.</t>
         </is>
       </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>https://www.lamaisondescailloux.com</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>05 62 98 11 97</t>
-        </is>
-      </c>
-      <c r="K270" t="inlineStr">
+      <c r="I271" s="32" t="inlineStr">
+        <is>
+          <t>https://www.carrelage-market.com</t>
+        </is>
+      </c>
+      <c r="J271" s="32" t="inlineStr">
+        <is>
+          <t>06 51 49 72 78</t>
+        </is>
+      </c>
+      <c r="K271" s="32" t="inlineStr">
         <is>
           <t>Relevé revendeurs (26/10), vérifié</t>
         </is>
       </c>
-      <c r="L270" s="32" t="inlineStr">
+      <c r="L271" s="32" t="inlineStr">
         <is>
           <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
         </is>
       </c>
-      <c r="N270" t="inlineStr">
+      <c r="N271" s="32" t="inlineStr">
         <is>
           <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
       </c>
-      <c r="O270" t="inlineStr">
-        <is>
-          <t>[26/10 vérifié] ⚠️ Angle marge FRAGILE : pas un pur revendeur (atelier-producteur pyrénéen, marbres Sarrancolin) ; son calcaire du Causse est à 60–80 €/m² mais son travertin import est à 29–30 €/m², DÉJÀ SOUS nos 35 €. Aucune pierre d'Égypte au catalogue. ~800 km de Gennevilliers, transport à chiffrer. SIREN 423 325 000. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
-        </is>
-      </c>
-      <c r="Q270" s="44">
-        <f>'Mode d''emploi'!$B$29</f>
-        <v/>
-      </c>
-      <c r="R270" t="inlineStr">
-        <is>
-          <t>contact@lamaisondescailloux.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="271" ht="15" customHeight="1" s="33">
-      <c r="A271" t="n">
-        <v>271</v>
-      </c>
-      <c r="B271" t="inlineStr">
-        <is>
-          <t>Revendeurs à 35 € (26/10)</t>
-        </is>
-      </c>
-      <c r="C271" t="n">
-        <v>3</v>
-      </c>
-      <c r="D271" t="inlineStr">
-        <is>
-          <t>Négoce gros matériaux / vente en ligne</t>
-        </is>
-      </c>
-      <c r="E271" t="inlineStr">
-        <is>
-          <t>Carrelage Market (Vente Pierre Naturelle.com SAS)</t>
-        </is>
-      </c>
-      <c r="F271" t="inlineStr">
-        <is>
-          <t>Puget-sur-Argens (83480)</t>
-        </is>
-      </c>
-      <c r="G271" t="inlineStr">
-        <is>
-          <t>PACA</t>
-        </is>
-      </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>Revendeur vendant déjà une pierre comparable plus cher.</t>
-        </is>
-      </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>https://www.carrelage-market.com</t>
-        </is>
-      </c>
-      <c r="J271" t="inlineStr">
-        <is>
-          <t>06 51 49 72 78</t>
-        </is>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>Relevé revendeurs (26/10), vérifié</t>
-        </is>
-      </c>
-      <c r="L271" s="32" t="inlineStr">
-        <is>
-          <t>À contacter — EN ATTENTE (ne rien envoyer)</t>
-        </is>
-      </c>
-      <c r="N271" t="inlineStr">
-        <is>
-          <t>NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
-        </is>
-      </c>
-      <c r="O271" t="inlineStr">
+      <c r="O271" s="32" t="inlineStr">
         <is>
           <t>[26/10 vérifié] ⚠️ Marge annoncée (48 €/m²) NON retrouvée : leur seul Sinaï en ligne est un déstockage à ≈35,12 €/m² TTC (lot 41 m² à 1 440 €), quasiment notre prix. Argument marge inopérant tant que ce lot est affiché. SIREN 537 699 506, NAF 46.73A, siège Cannes, showroom Var. NE RIEN ENVOYER — vrai From info@pierredegypte.online via Network Solutions à vérifier avant tout contact</t>
         </is>
@@ -19843,7 +19843,7 @@
         <f>'Mode d''emploi'!$B$29</f>
         <v/>
       </c>
-      <c r="R271" t="inlineStr">
+      <c r="R271" s="32" t="inlineStr">
         <is>
           <t>info@carrelage-market.com</t>
         </is>
